--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -250,21 +250,21 @@
     <t>EURCNH</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
@@ -397,34 +397,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.008296,naive=0.002654,drift4=0.008575; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01455,naive=0.00203,drift4=0.00502; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1185,naive=0.01552,drift4=0.04632; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01238,naive=0.002645,drift4=0.004008; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.06105,naive=0.007207,drift4=0.02741; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01735,naive=0.003187,drift4=0.00773; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=209.4,naive=40.81,drift4=192.4; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.08121,naive=0.02905,drift4=0.05601; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.05437,naive=0.01183,drift4=0.01427; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=4.622,naive=2.052,drift4=3.087; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.007438,naive=0.002337,drift4=0.00696; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01459,naive=0.00175,drift4=0.003908; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1093,naive=0.01208,drift4=0.03581; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05575,naive=0.006978,drift4=0.02585; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.012,naive=0.00243,drift4=0.003766; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0148,naive=0.00236,drift4=0.005999; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.07679,naive=0.02574,drift4=0.04576; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=189.6,naive=38.02,drift4=185.2; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.05437,naive=0.01262,drift4=0.01363; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=4.955,naive=2.151,drift4=3.195; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1033,7 +1033,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1057,19 +1057,19 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.9186078254815326</v>
+        <v>0.8502707438499056</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
         <v>90</v>
@@ -1087,10 +1087,10 @@
         <v>105</v>
       </c>
       <c r="T2">
-        <v>0.6167893698679255</v>
+        <v>0.6302822519807366</v>
       </c>
       <c r="U2">
-        <v>0.6774518439681305</v>
+        <v>0.6835214301323543</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1099,22 +1099,22 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9995865101102562</v>
+        <v>0.9995776669640914</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>-69.0216477734084</v>
+        <v>-67.6280732430146</v>
       </c>
       <c r="AA2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="AB2">
-        <v>0.3580151940233368</v>
+        <v>0.3806173303234104</v>
       </c>
       <c r="AC2">
-        <v>-0.9337157602013755</v>
+        <v>-0.9247326358777871</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1129,58 +1129,58 @@
         <v>121</v>
       </c>
       <c r="AH2">
-        <v>0.3578671583602335</v>
+        <v>0.3804565830507756</v>
       </c>
       <c r="AI2">
-        <v>0.7973894243064548</v>
+        <v>0.8045241285136036</v>
       </c>
       <c r="AJ2">
-        <v>0.8363871539247474</v>
+        <v>0.7608842998777121</v>
       </c>
       <c r="AK2">
-        <v>-1.987102177146234</v>
+        <v>-1.73260066518788</v>
       </c>
       <c r="AL2">
-        <v>0.5224674247282514</v>
+        <v>0.5363422346182095</v>
       </c>
       <c r="AM2">
-        <v>-2.490430584919363</v>
+        <v>-1.987207813225518</v>
       </c>
       <c r="AN2">
-        <v>0.4621968101108876</v>
+        <v>0.440719185432676</v>
       </c>
       <c r="AO2">
-        <v>0.06580274959423874</v>
+        <v>0.06342169347234336</v>
       </c>
       <c r="AP2">
-        <v>1.35291</v>
+        <v>1.35177</v>
       </c>
       <c r="AQ2">
-        <v>1.352321984678142</v>
+        <v>1.35092298277353</v>
       </c>
       <c r="AR2">
-        <v>1.349696814459358</v>
+        <v>1.348699182758458</v>
       </c>
       <c r="AS2">
-        <v>1.35291</v>
+        <v>1.35177</v>
       </c>
       <c r="AT2">
-        <v>1.35595</v>
+        <v>1.35367</v>
       </c>
       <c r="AW2">
-        <v>-0.0004346300358918787</v>
+        <v>-0.0006265986273327758</v>
       </c>
       <c r="AY2">
-        <v>0.0004346300358918787</v>
+        <v>0.0006265986273327758</v>
       </c>
       <c r="AZ2">
-        <v>0.4829562951923306</v>
+        <v>0.4761827102972768</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3170437048076694</v>
+        <v>0.3238172897027232</v>
       </c>
       <c r="BC2" t="s">
         <v>127</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.008296101729646848</v>
+        <v>0.007437802443123573</v>
       </c>
       <c r="BP2">
-        <v>0.00265363753488225</v>
+        <v>0.002336947028346388</v>
       </c>
       <c r="BQ2">
-        <v>0.008575065263555445</v>
+        <v>0.006959601399292075</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT2" t="s">
         <v>137</v>
@@ -1240,7 +1240,7 @@
         <v>139</v>
       </c>
       <c r="BW2" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1272,19 +1272,19 @@
         <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.3948205979537826</v>
+        <v>0.4445940546269952</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1302,10 +1302,10 @@
         <v>106</v>
       </c>
       <c r="T3">
-        <v>0.7395504278905823</v>
+        <v>0.7798578699661117</v>
       </c>
       <c r="U3">
-        <v>0.7327718985221117</v>
+        <v>0.7509089809896883</v>
       </c>
       <c r="V3" t="s">
         <v>93</v>
@@ -1314,22 +1314,22 @@
         <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9998968238853981</v>
+        <v>0.9998917580197519</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>76.2784825904794</v>
+        <v>69.19110496674028</v>
       </c>
       <c r="AA3">
-        <v>-20</v>
+        <v>-31.99999999999999</v>
       </c>
       <c r="AB3">
-        <v>0.2372029942803253</v>
+        <v>0.3552520875871892</v>
       </c>
       <c r="AC3">
-        <v>0.9714601070061745</v>
+        <v>0.9347705356208784</v>
       </c>
       <c r="AD3" t="s">
         <v>93</v>
@@ -1344,67 +1344,67 @@
         <v>122</v>
       </c>
       <c r="AH3">
-        <v>0.1185892602985018</v>
+        <v>0.1776068171988708</v>
       </c>
       <c r="AI3">
-        <v>0.5518979704898639</v>
+        <v>0.590344826896922</v>
       </c>
       <c r="AJ3">
-        <v>0.2055446885482178</v>
+        <v>0.2482940020501148</v>
       </c>
       <c r="AK3">
-        <v>0.9612997197379524</v>
+        <v>0.7932259820012609</v>
       </c>
       <c r="AL3">
-        <v>0.9259332079045794</v>
+        <v>0.9684795646683404</v>
       </c>
       <c r="AM3">
-        <v>0.3837967364151892</v>
+        <v>0.2161796770962048</v>
       </c>
       <c r="AN3">
-        <v>0.9065788629734597</v>
+        <v>0.936830457341394</v>
       </c>
       <c r="AO3">
-        <v>0.1281787743608199</v>
+        <v>0.1079527645743192</v>
       </c>
       <c r="AP3">
-        <v>0.80913</v>
+        <v>0.8100149999999999</v>
       </c>
       <c r="AQ3">
-        <v>0.8159183297191033</v>
+        <v>0.8170180736184469</v>
       </c>
       <c r="AR3">
-        <v>0.8281627834721237</v>
+        <v>0.8294289641170285</v>
       </c>
       <c r="AS3">
-        <v>0.80913</v>
+        <v>0.8100149999999999</v>
       </c>
       <c r="AT3">
-        <v>0.8055950000000001</v>
+        <v>0.8073649999999999</v>
       </c>
       <c r="AU3">
-        <v>0.8159183297191033</v>
+        <v>0.8170180736184469</v>
       </c>
       <c r="AV3">
-        <v>0.799095</v>
+        <v>0.7999799999999999</v>
       </c>
       <c r="AW3">
-        <v>0.008389665095971301</v>
+        <v>0.008645609795432168</v>
       </c>
       <c r="AX3">
-        <v>0.6764653432090948</v>
+        <v>0.6978648349224709</v>
       </c>
       <c r="AY3">
-        <v>0.008389665095971301</v>
+        <v>0.008645609795432168</v>
       </c>
       <c r="AZ3">
-        <v>0.4261087373060557</v>
+        <v>0.4134829793076963</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3738912626939444</v>
+        <v>0.3865170206923037</v>
       </c>
       <c r="BC3" t="s">
         <v>128</v>
@@ -1419,22 +1419,22 @@
         <v>375</v>
       </c>
       <c r="BG3">
-        <v>0.01240220978087574</v>
+        <v>0.01238865946926907</v>
       </c>
       <c r="BH3">
-        <v>40315.39611360244</v>
+        <v>40359.49177877433</v>
       </c>
       <c r="BI3">
-        <v>30236.54708520183</v>
+        <v>30269.61883408075</v>
       </c>
       <c r="BJ3">
         <v>37369.20777279526</v>
       </c>
       <c r="BK3">
-        <v>302.3654708520182</v>
+        <v>302.6961883408075</v>
       </c>
       <c r="BL3">
-        <v>0.003023654708520182</v>
+        <v>0.003026961883408075</v>
       </c>
       <c r="BM3">
         <v>375</v>
@@ -1443,19 +1443,19 @@
         <v>0.00375</v>
       </c>
       <c r="BO3">
-        <v>0.0145487171437469</v>
+        <v>0.01459425477017675</v>
       </c>
       <c r="BP3">
-        <v>0.002029943995925192</v>
+        <v>0.001750012689922765</v>
       </c>
       <c r="BQ3">
-        <v>0.005020395057383301</v>
+        <v>0.003908176223950665</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT3" t="s">
         <v>138</v>
@@ -1467,7 +1467,7 @@
         <v>140</v>
       </c>
       <c r="BW3" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1475,7 +1475,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1598,10 +1598,10 @@
         <v>7.7899</v>
       </c>
       <c r="AQ4">
-        <v>7.8513455317206</v>
+        <v>7.849161339113996</v>
       </c>
       <c r="AR4">
-        <v>7.933268498435856</v>
+        <v>7.930163689113234</v>
       </c>
       <c r="AS4">
         <v>7.7899</v>
@@ -1610,28 +1610,28 @@
         <v>7.786200000000001</v>
       </c>
       <c r="AU4">
-        <v>7.8513455317206</v>
+        <v>7.849161339113996</v>
       </c>
       <c r="AV4">
         <v>7.734975</v>
       </c>
       <c r="AW4">
-        <v>0.007887846021206943</v>
+        <v>0.007607458261851344</v>
       </c>
       <c r="AX4">
-        <v>1.118717009023215</v>
+        <v>1.078950188693599</v>
       </c>
       <c r="AY4">
-        <v>0.007887846021206943</v>
+        <v>0.007607458261851344</v>
       </c>
       <c r="AZ4">
-        <v>0.437928804642621</v>
+        <v>0.4322016162357126</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3620711953573791</v>
+        <v>0.3677983837642874</v>
       </c>
       <c r="BC4" t="s">
         <v>129</v>
@@ -1670,19 +1670,19 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="BO4">
-        <v>0.1185294091843965</v>
+        <v>0.1093161290134215</v>
       </c>
       <c r="BP4">
-        <v>0.01552049338379618</v>
+        <v>0.01207749478290436</v>
       </c>
       <c r="BQ4">
-        <v>0.0463159296520238</v>
+        <v>0.03580519702942954</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT4" t="s">
         <v>138</v>
@@ -1694,7 +1694,7 @@
         <v>140</v>
       </c>
       <c r="BW4" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1702,7 +1702,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1726,19 +1726,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="K5">
-        <v>0.8534647213814789</v>
+        <v>0.2433881329000335</v>
       </c>
       <c r="L5">
-        <v>2.222467764607518</v>
+        <v>0.9386445228628102</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O5" t="s">
         <v>95</v>
@@ -1747,7 +1747,7 @@
         <v>98</v>
       </c>
       <c r="Q5">
-        <v>0.9633661803453697</v>
+        <v>0.8108470332250084</v>
       </c>
       <c r="R5" t="s">
         <v>102</v>
@@ -1756,10 +1756,10 @@
         <v>107</v>
       </c>
       <c r="T5">
-        <v>0.9918750949342574</v>
+        <v>0.9999886134501064</v>
       </c>
       <c r="U5">
-        <v>0.9742663912120111</v>
+        <v>0.8864448097489284</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1768,22 +1768,22 @@
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9996115611374938</v>
+        <v>0.9997668550455016</v>
       </c>
       <c r="Y5">
-        <v>0.7699287088893266</v>
+        <v>0.05397374160614632</v>
       </c>
       <c r="Z5">
-        <v>-10.6504711470484</v>
+        <v>0.4703143851624944</v>
       </c>
       <c r="AA5">
-        <v>-12.99999999999999</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB5">
-        <v>0.982772927328829</v>
+        <v>0.9999663101695172</v>
       </c>
       <c r="AC5">
-        <v>-0.1848171347833424</v>
+        <v>0.00820844235899219</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1798,67 +1798,67 @@
         <v>124</v>
       </c>
       <c r="AH5">
-        <v>0.8693811765366158</v>
+        <v>0.526846256513993</v>
       </c>
       <c r="AI5">
-        <v>0.9431664961641471</v>
+        <v>0.8050287699562102</v>
       </c>
       <c r="AJ5">
-        <v>1.775534307736559</v>
+        <v>0.7682394663389822</v>
       </c>
       <c r="AK5">
-        <v>-0.2828761497928835</v>
+        <v>0.01696259708175796</v>
       </c>
       <c r="AL5">
-        <v>2.361775434609422</v>
+        <v>0.9143838870640846</v>
       </c>
       <c r="AM5">
-        <v>-3.357562199673891</v>
+        <v>-1.661593666137039</v>
       </c>
       <c r="AN5">
-        <v>2.09144541419215</v>
+        <v>0.7790072515078634</v>
       </c>
       <c r="AO5">
-        <v>0.03676780140326514</v>
+        <v>0.03782847121199816</v>
       </c>
       <c r="AP5">
-        <v>0.720425</v>
+        <v>4.83103</v>
       </c>
       <c r="AQ5">
-        <v>0.7257886120790883</v>
+        <v>4.866147433177178</v>
       </c>
       <c r="AR5">
-        <v>0.7200565571719618</v>
+        <v>4.858067986514525</v>
       </c>
       <c r="AS5">
-        <v>0.720425</v>
+        <v>4.83103</v>
       </c>
       <c r="AT5">
-        <v>0.7343299999999999</v>
+        <v>4.896780000000001</v>
       </c>
       <c r="AU5">
-        <v>0.7257886120790883</v>
+        <v>4.866147433177178</v>
       </c>
       <c r="AV5">
-        <v>0.7132162500000001</v>
+        <v>4.791230000000001</v>
       </c>
       <c r="AW5">
-        <v>0.00744506656360941</v>
+        <v>0.007269139950937625</v>
       </c>
       <c r="AX5">
-        <v>0.7440419045033273</v>
+        <v>0.8823475672657825</v>
       </c>
       <c r="AY5">
-        <v>0.00744506656360941</v>
+        <v>0.007269139950937625</v>
       </c>
       <c r="AZ5">
-        <v>0.403573825201887</v>
+        <v>0.4516057225848565</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3964261747981129</v>
+        <v>0.3483942774151435</v>
       </c>
       <c r="BC5" t="s">
         <v>130</v>
@@ -1870,46 +1870,46 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>481.6830901726848</v>
+        <v>405.4235166125042</v>
       </c>
       <c r="BG5">
-        <v>0.01000624631294018</v>
+        <v>0.008238408786532076</v>
       </c>
       <c r="BH5">
-        <v>49968.78793133393</v>
+        <v>60691.33165829137</v>
       </c>
       <c r="BI5">
-        <v>48138.24036589698</v>
+        <v>49211.38621760059</v>
       </c>
       <c r="BJ5">
-        <v>66819.22527105108</v>
+        <v>10186.5205179021</v>
       </c>
       <c r="BK5">
-        <v>481.3824036589698</v>
+        <v>492.1138621760059</v>
       </c>
       <c r="BL5">
-        <v>0.004813824036589698</v>
+        <v>0.004921138621760059</v>
       </c>
       <c r="BM5">
-        <v>481.6830901726849</v>
+        <v>405.4235166125042</v>
       </c>
       <c r="BN5">
-        <v>0.004816830901726849</v>
+        <v>0.004054235166125042</v>
       </c>
       <c r="BO5">
-        <v>0.01238420695785792</v>
+        <v>0.05574627618925981</v>
       </c>
       <c r="BP5">
-        <v>0.002644813533568509</v>
+        <v>0.006978339985505324</v>
       </c>
       <c r="BQ5">
-        <v>0.004007920577673129</v>
+        <v>0.02584637592939295</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT5" t="s">
         <v>138</v>
@@ -1921,7 +1921,7 @@
         <v>140</v>
       </c>
       <c r="BW5" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1929,7 +1929,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1956,16 +1956,16 @@
         <v>46269</v>
       </c>
       <c r="K6">
-        <v>0.2433881329000335</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0.9386445228628102</v>
+        <v>2.400270608960956</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
@@ -1974,7 +1974,7 @@
         <v>98</v>
       </c>
       <c r="Q6">
-        <v>0.8108470332250084</v>
+        <v>1</v>
       </c>
       <c r="R6" t="s">
         <v>102</v>
@@ -1983,10 +1983,10 @@
         <v>107</v>
       </c>
       <c r="T6">
-        <v>0.9999886134501064</v>
+        <v>0.9999315107325071</v>
       </c>
       <c r="U6">
-        <v>0.8864448097489284</v>
+        <v>0.9998800412718265</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1995,22 +1995,22 @@
         <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9997668550455016</v>
+        <v>0.999643445768793</v>
       </c>
       <c r="Y6">
-        <v>0.05397374160614632</v>
+        <v>0.9324241592517576</v>
       </c>
       <c r="Z6">
-        <v>0.4703143851624944</v>
+        <v>-0.9592686334412081</v>
       </c>
       <c r="AA6">
-        <v>-5.999999999999996</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AB6">
-        <v>0.9999663101695172</v>
+        <v>0.9998598493608297</v>
       </c>
       <c r="AC6">
-        <v>0.00820844235899219</v>
+        <v>-0.01674161390484424</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -2025,67 +2025,67 @@
         <v>124</v>
       </c>
       <c r="AH6">
-        <v>0.526846256513993</v>
+        <v>0.9657322056629883</v>
       </c>
       <c r="AI6">
-        <v>0.8050287699562102</v>
+        <v>0.980802500865403</v>
       </c>
       <c r="AJ6">
-        <v>0.7682394663389822</v>
+        <v>1.913248459490064</v>
       </c>
       <c r="AK6">
-        <v>0.01696259708175796</v>
+        <v>-0.04453097012997838</v>
       </c>
       <c r="AL6">
-        <v>0.9143838870640846</v>
+        <v>2.572103441121658</v>
       </c>
       <c r="AM6">
-        <v>-1.661593666137039</v>
+        <v>-3.634458303085958</v>
       </c>
       <c r="AN6">
-        <v>0.7790072515078634</v>
+        <v>2.272213487908998</v>
       </c>
       <c r="AO6">
-        <v>0.03782847121199816</v>
+        <v>0.0367699454151666</v>
       </c>
       <c r="AP6">
-        <v>4.83103</v>
+        <v>0.720145</v>
       </c>
       <c r="AQ6">
-        <v>4.866849064568433</v>
+        <v>0.7251762442677103</v>
       </c>
       <c r="AR6">
-        <v>4.859616847376507</v>
+        <v>0.7192133433374162</v>
       </c>
       <c r="AS6">
-        <v>4.83103</v>
+        <v>0.720145</v>
       </c>
       <c r="AT6">
-        <v>4.896780000000001</v>
+        <v>0.73377</v>
       </c>
       <c r="AU6">
-        <v>4.866849064568433</v>
+        <v>0.7251762442677103</v>
       </c>
       <c r="AV6">
-        <v>4.791230000000001</v>
+        <v>0.71293625</v>
       </c>
       <c r="AW6">
-        <v>0.007414374278038518</v>
+        <v>0.006986432270876405</v>
       </c>
       <c r="AX6">
-        <v>0.8999764966942807</v>
+        <v>0.6979357402754066</v>
       </c>
       <c r="AY6">
-        <v>0.007414374278038518</v>
+        <v>0.006986432270876405</v>
       </c>
       <c r="AZ6">
-        <v>0.4515476822318744</v>
+        <v>0.403166459738972</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3484523177681255</v>
+        <v>0.396833540261028</v>
       </c>
       <c r="BC6" t="s">
         <v>131</v>
@@ -2097,46 +2097,46 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>405.4235166125042</v>
+        <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.008238408786532076</v>
+        <v>0.01001013684744035</v>
       </c>
       <c r="BH6">
-        <v>60691.33165829137</v>
+        <v>49949.36708860807</v>
       </c>
       <c r="BI6">
-        <v>49211.38621760059</v>
+        <v>49949.36708860807</v>
       </c>
       <c r="BJ6">
-        <v>10186.5205179021</v>
+        <v>69360.15259233637</v>
       </c>
       <c r="BK6">
-        <v>492.1138621760059</v>
+        <v>499.4936708860807</v>
       </c>
       <c r="BL6">
-        <v>0.004921138621760059</v>
+        <v>0.004994936708860807</v>
       </c>
       <c r="BM6">
-        <v>405.4235166125042</v>
+        <v>500</v>
       </c>
       <c r="BN6">
-        <v>0.004054235166125042</v>
+        <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.06104732220946936</v>
+        <v>0.01200107888063609</v>
       </c>
       <c r="BP6">
-        <v>0.007206675303819426</v>
+        <v>0.002430329182507534</v>
       </c>
       <c r="BQ6">
-        <v>0.02740929979525783</v>
+        <v>0.003766072708663907</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT6" t="s">
         <v>138</v>
@@ -2148,7 +2148,7 @@
         <v>140</v>
       </c>
       <c r="BW6" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2156,7 +2156,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2180,19 +2180,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="K7">
-        <v>0.2636007990743293</v>
+        <v>0.1652916187970465</v>
       </c>
       <c r="L7">
-        <v>1.326965625014153</v>
+        <v>1.265249584116171</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O7" t="s">
         <v>95</v>
@@ -2201,7 +2201,7 @@
         <v>98</v>
       </c>
       <c r="Q7">
-        <v>0.8159001997685823</v>
+        <v>0.7913229046992616</v>
       </c>
       <c r="R7" t="s">
         <v>100</v>
@@ -2210,10 +2210,10 @@
         <v>105</v>
       </c>
       <c r="T7">
-        <v>0.7768253538447389</v>
+        <v>0.8830884112597904</v>
       </c>
       <c r="U7">
-        <v>0.7889382675797985</v>
+        <v>0.8215786912494414</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2222,22 +2222,22 @@
         <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9993069539540662</v>
+        <v>0.9975806534519147</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0.5362757071870204</v>
       </c>
       <c r="Z7">
-        <v>-52.63104527986711</v>
+        <v>-40.46197234739928</v>
       </c>
       <c r="AA7">
-        <v>-17</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AB7">
-        <v>0.6069453030980961</v>
+        <v>0.7608368417853951</v>
       </c>
       <c r="AC7">
-        <v>-0.7947436058548444</v>
+        <v>-0.6489432179952462</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
@@ -2252,67 +2252,67 @@
         <v>121</v>
       </c>
       <c r="AH7">
-        <v>0.6065246620556859</v>
+        <v>0.5830136457390457</v>
       </c>
       <c r="AI7">
-        <v>0.874887377985875</v>
+        <v>0.8280291120453563</v>
       </c>
       <c r="AJ7">
-        <v>1.163721289215734</v>
+        <v>1.106657712431845</v>
       </c>
       <c r="AK7">
-        <v>-1.407477171735819</v>
+        <v>-0.9700211311844404</v>
       </c>
       <c r="AL7">
-        <v>0.9366970932541001</v>
+        <v>0.9066759669440969</v>
       </c>
       <c r="AM7">
-        <v>-2.934195662306072</v>
+        <v>-2.787668985716782</v>
       </c>
       <c r="AN7">
-        <v>0.756058952806959</v>
+        <v>0.7286936216643226</v>
       </c>
       <c r="AO7">
-        <v>0.04635764551651293</v>
+        <v>0.04420207090557568</v>
       </c>
       <c r="AP7">
-        <v>1.162855</v>
+        <v>1.161345</v>
       </c>
       <c r="AQ7">
-        <v>1.167255965986062</v>
+        <v>1.164562120245709</v>
       </c>
       <c r="AR7">
-        <v>1.167551348785327</v>
+        <v>1.164579176164103</v>
       </c>
       <c r="AS7">
-        <v>1.162855</v>
+        <v>1.161345</v>
       </c>
       <c r="AT7">
-        <v>1.169315</v>
+        <v>1.166295</v>
       </c>
       <c r="AU7">
-        <v>1.167255965986062</v>
+        <v>1.164562120245709</v>
       </c>
       <c r="AV7">
-        <v>1.152495</v>
+        <v>1.150985</v>
       </c>
       <c r="AW7">
-        <v>0.003784621458446849</v>
+        <v>0.002770167560637856</v>
       </c>
       <c r="AX7">
-        <v>0.42480366660832</v>
+        <v>0.3105328422498996</v>
       </c>
       <c r="AY7">
-        <v>0.003784621458446849</v>
+        <v>0.002770167560637856</v>
       </c>
       <c r="AZ7">
-        <v>0.4349125312059218</v>
+        <v>0.4329580570855683</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3650874687940783</v>
+        <v>0.3670419429144318</v>
       </c>
       <c r="BC7" t="s">
         <v>132</v>
@@ -2324,46 +2324,46 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>407.9500998842911</v>
+        <v>395.6614523496308</v>
       </c>
       <c r="BG7">
-        <v>0.008909107326364882</v>
+        <v>0.00892069109523874</v>
       </c>
       <c r="BH7">
-        <v>56122.34555984537</v>
+        <v>56049.46911196892</v>
       </c>
       <c r="BI7">
-        <v>45790.23295375924</v>
+        <v>44353.22870453479</v>
       </c>
       <c r="BJ7">
-        <v>39377.42276875384</v>
+        <v>38191.25987930787</v>
       </c>
       <c r="BK7">
-        <v>457.9023295375924</v>
+        <v>443.5322870453479</v>
       </c>
       <c r="BL7">
-        <v>0.004579023295375924</v>
+        <v>0.004435322870453479</v>
       </c>
       <c r="BM7">
-        <v>407.9500998842911</v>
+        <v>395.6614523496308</v>
       </c>
       <c r="BN7">
-        <v>0.004079500998842911</v>
+        <v>0.003956614523496308</v>
       </c>
       <c r="BO7">
-        <v>0.01734616442801591</v>
+        <v>0.01480034685695315</v>
       </c>
       <c r="BP7">
-        <v>0.003187073016716227</v>
+        <v>0.002359690683237485</v>
       </c>
       <c r="BQ7">
-        <v>0.007729758413791508</v>
+        <v>0.005999236469214154</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT7" t="s">
         <v>138</v>
@@ -2375,7 +2375,7 @@
         <v>140</v>
       </c>
       <c r="BW7" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2383,7 +2383,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2395,40 +2395,40 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1.119541820677235</v>
+        <v>0.1215937009524473</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
         <v>100</v>
@@ -2437,109 +2437,109 @@
         <v>105</v>
       </c>
       <c r="T8">
-        <v>0.7040538250039452</v>
+        <v>0.3461365148896858</v>
       </c>
       <c r="U8">
-        <v>0.7166488838727829</v>
+        <v>0.455716061937822</v>
       </c>
       <c r="V8" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="W8" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="X8">
-        <v>0.9992986504840303</v>
+        <v>0.9998185209498537</v>
       </c>
       <c r="Y8">
-        <v>0.7180225199428284</v>
+        <v>0.5563029909034597</v>
       </c>
       <c r="Z8">
-        <v>-62.65883005435044</v>
+        <v>-94.30625840196588</v>
       </c>
       <c r="AA8">
-        <v>-27</v>
+        <v>-21</v>
       </c>
       <c r="AB8">
-        <v>0.4592879529193528</v>
+        <v>-0.07508764863196088</v>
       </c>
       <c r="AC8">
-        <v>-0.8882874401358777</v>
+        <v>-0.9971769376710049</v>
       </c>
       <c r="AD8" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="AE8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AH8">
-        <v>0.3942568172314658</v>
+        <v>-0.05841896233076303</v>
       </c>
       <c r="AI8">
-        <v>0.7725565058440367</v>
+        <v>0.5927124787755713</v>
       </c>
       <c r="AJ8">
-        <v>1.033817696551966</v>
+        <v>-0.03085567019374423</v>
       </c>
       <c r="AK8">
-        <v>-1.76904826894771</v>
+        <v>-0.9256928380483996</v>
       </c>
       <c r="AL8">
-        <v>0.5619524885783533</v>
+        <v>-0.4875919132620308</v>
       </c>
       <c r="AM8">
-        <v>-3.17769607539686</v>
+        <v>-0.617506360995302</v>
       </c>
       <c r="AN8">
-        <v>0.5214568482096681</v>
+        <v>0.499935264061904</v>
       </c>
       <c r="AO8">
-        <v>0.05725941126497041</v>
+        <v>0.2734059755143843</v>
       </c>
       <c r="AP8">
-        <v>4469.23</v>
+        <v>9.069750000000001</v>
       </c>
       <c r="AQ8">
-        <v>4474.688561358203</v>
+        <v>9.047913442817689</v>
       </c>
       <c r="AR8">
-        <v>4331.636132738266</v>
+        <v>9.040742348927619</v>
       </c>
       <c r="AS8">
-        <v>4469.23</v>
+        <v>9.069750000000001</v>
       </c>
       <c r="AT8">
-        <v>4696.66</v>
+        <v>9.044540000000001</v>
       </c>
       <c r="AU8">
-        <v>4475.933845</v>
+        <v>9.047913442817689</v>
       </c>
       <c r="AV8">
-        <v>4320.8675</v>
+        <v>9.152540000000002</v>
       </c>
       <c r="AW8">
-        <v>0.001221365058008436</v>
+        <v>-0.002407625037328632</v>
       </c>
       <c r="AX8">
-        <v>0.04518557586991351</v>
+        <v>0.2637583908963804</v>
       </c>
       <c r="AY8">
-        <v>0.001221365058008436</v>
+        <v>0.002407625037328632</v>
       </c>
       <c r="AZ8">
-        <v>0.483490134400587</v>
+        <v>0.4393655842809088</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3165098655994131</v>
+        <v>0.3606344157190912</v>
       </c>
       <c r="BC8" t="s">
         <v>133</v>
@@ -2551,58 +2551,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.03319643428510036</v>
+        <v>0.009128145759254681</v>
       </c>
       <c r="BH8">
-        <v>15061.8586233045</v>
+        <v>54775.63715424559</v>
       </c>
       <c r="BI8">
-        <v>11296.39396747838</v>
+        <v>54775.63715424559</v>
       </c>
       <c r="BJ8">
-        <v>2.527592889038688</v>
+        <v>6039.376736320801</v>
       </c>
       <c r="BK8">
-        <v>112.9639396747838</v>
+        <v>547.7563715424559</v>
       </c>
       <c r="BL8">
-        <v>0.001129639396747838</v>
+        <v>0.005477563715424559</v>
       </c>
       <c r="BM8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BN8">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>209.3555219855693</v>
+        <v>0.07678987129326678</v>
       </c>
       <c r="BP8">
-        <v>40.80568232170194</v>
+        <v>0.02573821460852699</v>
       </c>
       <c r="BQ8">
-        <v>192.4023166674251</v>
+        <v>0.04575610168102937</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT8" t="s">
         <v>138</v>
       </c>
       <c r="BU8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV8" t="s">
         <v>140</v>
       </c>
       <c r="BW8" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2610,7 +2610,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2622,7 +2622,7 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
         <v>92</v>
@@ -2640,13 +2640,13 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.1215937009524473</v>
+        <v>1.037737926002288</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O9" t="s">
         <v>96</v>
@@ -2664,109 +2664,109 @@
         <v>105</v>
       </c>
       <c r="T9">
-        <v>0.3461365148896858</v>
+        <v>0.75060117602011</v>
       </c>
       <c r="U9">
-        <v>0.455716061937822</v>
+        <v>0.7376234054156443</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W9" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9998185209498537</v>
+        <v>0.9994115048263792</v>
       </c>
       <c r="Y9">
-        <v>0.5563029909034597</v>
+        <v>0.4550776311383243</v>
       </c>
       <c r="Z9">
-        <v>-94.30625840196588</v>
+        <v>-60.67437586482892</v>
       </c>
       <c r="AA9">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="AB9">
-        <v>-0.07508764863196088</v>
+        <v>0.4897724144346818</v>
       </c>
       <c r="AC9">
-        <v>-0.9971769376710049</v>
+        <v>-0.8718503209030908</v>
       </c>
       <c r="AD9" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AH9">
-        <v>-0.05841896233076303</v>
+        <v>0.3561187447277421</v>
       </c>
       <c r="AI9">
-        <v>0.5927124787755713</v>
+        <v>0.7291459083404572</v>
       </c>
       <c r="AJ9">
-        <v>-0.03085567019374423</v>
+        <v>0.9620947343368633</v>
       </c>
       <c r="AK9">
-        <v>-0.9256928380483996</v>
+        <v>-1.542431762774853</v>
       </c>
       <c r="AL9">
-        <v>-0.4875919132620308</v>
+        <v>0.5009769649772509</v>
       </c>
       <c r="AM9">
-        <v>-0.617506360995302</v>
+        <v>-2.930959714356365</v>
       </c>
       <c r="AN9">
-        <v>0.499935264061904</v>
+        <v>0.4725572360986167</v>
       </c>
       <c r="AO9">
-        <v>0.2734059755143843</v>
+        <v>0.05730245937896543</v>
       </c>
       <c r="AP9">
-        <v>9.069750000000001</v>
+        <v>4430.299999999999</v>
       </c>
       <c r="AQ9">
-        <v>9.047987534778738</v>
+        <v>4413.190502762716</v>
       </c>
       <c r="AR9">
-        <v>9.040995736840548</v>
+        <v>4273.742088853462</v>
       </c>
       <c r="AS9">
-        <v>9.069750000000001</v>
+        <v>4430.299999999999</v>
       </c>
       <c r="AT9">
-        <v>9.044540000000001</v>
+        <v>4618.799999999999</v>
       </c>
       <c r="AU9">
-        <v>9.047987534778738</v>
+        <v>4413.190502762716</v>
       </c>
       <c r="AV9">
-        <v>9.152540000000002</v>
+        <v>4578.662499999999</v>
       </c>
       <c r="AW9">
-        <v>-0.002399455907964732</v>
+        <v>-0.003861927462538202</v>
       </c>
       <c r="AX9">
-        <v>0.2628634523645741</v>
+        <v>0.1153222494719562</v>
       </c>
       <c r="AY9">
-        <v>0.002399455907964732</v>
+        <v>0.003861927462538202</v>
       </c>
       <c r="AZ9">
-        <v>0.4498721312527437</v>
+        <v>0.4866125128949031</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3501278687472564</v>
+        <v>0.3133874871050969</v>
       </c>
       <c r="BC9" t="s">
         <v>134</v>
@@ -2781,22 +2781,22 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.009128145759254681</v>
+        <v>0.03348813850077852</v>
       </c>
       <c r="BH9">
-        <v>54775.63715424559</v>
+        <v>14930.65970174413</v>
       </c>
       <c r="BI9">
-        <v>54775.63715424559</v>
+        <v>14930.65970174413</v>
       </c>
       <c r="BJ9">
-        <v>6039.376736320801</v>
+        <v>3.370123852051584</v>
       </c>
       <c r="BK9">
-        <v>547.7563715424559</v>
+        <v>149.3065970174413</v>
       </c>
       <c r="BL9">
-        <v>0.005477563715424559</v>
+        <v>0.001493065970174413</v>
       </c>
       <c r="BM9">
         <v>500</v>
@@ -2805,19 +2805,19 @@
         <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.08120600017311809</v>
+        <v>189.6303301829709</v>
       </c>
       <c r="BP9">
-        <v>0.0290548258950232</v>
+        <v>38.01687340826754</v>
       </c>
       <c r="BQ9">
-        <v>0.05600744548366927</v>
+        <v>185.1584155904734</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT9" t="s">
         <v>138</v>
@@ -2829,7 +2829,7 @@
         <v>140</v>
       </c>
       <c r="BW9" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2837,7 +2837,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2861,19 +2861,19 @@
         <v>94</v>
       </c>
       <c r="J10" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="K10">
-        <v>0.549014817771017</v>
+        <v>0.7383830957075519</v>
       </c>
       <c r="L10">
-        <v>3.070870196303257</v>
+        <v>3.315084039482191</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O10" t="s">
         <v>95</v>
@@ -2882,7 +2882,7 @@
         <v>98</v>
       </c>
       <c r="Q10">
-        <v>0.8872537044427542</v>
+        <v>0.934595773926888</v>
       </c>
       <c r="R10" t="s">
         <v>103</v>
@@ -2891,10 +2891,10 @@
         <v>108</v>
       </c>
       <c r="T10">
-        <v>-0.9948881507480453</v>
+        <v>-0.9959730809498482</v>
       </c>
       <c r="U10">
-        <v>0.9299900733444458</v>
+        <v>0.958839200969604</v>
       </c>
       <c r="V10" t="s">
         <v>94</v>
@@ -2903,22 +2903,22 @@
         <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9997527313686917</v>
+        <v>0.9995754007441581</v>
       </c>
       <c r="Y10">
-        <v>0.8060787105429703</v>
+        <v>0.9784433336488914</v>
       </c>
       <c r="Z10">
-        <v>171.8478895639152</v>
+        <v>-172.8550226638579</v>
       </c>
       <c r="AA10">
-        <v>4.000000000000005</v>
+        <v>16</v>
       </c>
       <c r="AB10">
-        <v>-0.9898950987814116</v>
+        <v>-0.9922346046624108</v>
       </c>
       <c r="AC10">
-        <v>0.1418015987517047</v>
+        <v>-0.1243804217328009</v>
       </c>
       <c r="AD10" t="s">
         <v>94</v>
@@ -2933,67 +2933,67 @@
         <v>125</v>
       </c>
       <c r="AH10">
-        <v>-0.8936931948413673</v>
+        <v>-0.9811232083644139</v>
       </c>
       <c r="AI10">
-        <v>0.9526322926880262</v>
+        <v>0.9874653868282052</v>
       </c>
       <c r="AJ10">
-        <v>-2.317200621738648</v>
+        <v>-2.486799220209178</v>
       </c>
       <c r="AK10">
-        <v>0.3499698600855806</v>
+        <v>-0.2386370094443492</v>
       </c>
       <c r="AL10">
-        <v>-3.880769218498545</v>
+        <v>-4.253807111421811</v>
       </c>
       <c r="AM10">
-        <v>2.975008256556966</v>
+        <v>3.054540062391226</v>
       </c>
       <c r="AN10">
-        <v>3.628535748176443</v>
+        <v>3.981884980820916</v>
       </c>
       <c r="AO10">
-        <v>0.03643623356022297</v>
+        <v>0.03830034373834421</v>
       </c>
       <c r="AP10">
-        <v>6.709125</v>
+        <v>6.707285000000001</v>
       </c>
       <c r="AQ10">
-        <v>6.68536303152074</v>
+        <v>6.680126834375407</v>
       </c>
       <c r="AR10">
-        <v>6.683711858767081</v>
+        <v>6.675097417663345</v>
       </c>
       <c r="AS10">
-        <v>6.709125</v>
+        <v>6.707285000000001</v>
       </c>
       <c r="AT10">
-        <v>6.67543</v>
+        <v>6.671750000000001</v>
       </c>
       <c r="AU10">
-        <v>6.68536303152074</v>
+        <v>6.680126834375407</v>
       </c>
       <c r="AV10">
-        <v>6.73130375</v>
+        <v>6.73079125</v>
       </c>
       <c r="AW10">
-        <v>-0.003541738822761643</v>
+        <v>-0.004049054964056718</v>
       </c>
       <c r="AX10">
-        <v>1.07138447745076</v>
+        <v>1.15535934590135</v>
       </c>
       <c r="AY10">
-        <v>0.003541738822761643</v>
+        <v>0.004049054964056718</v>
       </c>
       <c r="AZ10">
-        <v>0.3856660214292673</v>
+        <v>0.3793474561931316</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.4143339785707327</v>
+        <v>0.4206525438068684</v>
       </c>
       <c r="BC10" t="s">
         <v>135</v>
@@ -3005,46 +3005,46 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>443.6268522213771</v>
+        <v>467.297886963444</v>
       </c>
       <c r="BG10">
-        <v>0.003305758947701778</v>
+        <v>0.003504584940106111</v>
       </c>
       <c r="BH10">
-        <v>151251.1976554155</v>
+        <v>142670.2472746633</v>
       </c>
       <c r="BI10">
-        <v>134198.1854211706</v>
+        <v>133339.0101680045</v>
       </c>
       <c r="BJ10">
-        <v>20002.33792352515</v>
+        <v>19879.72930448079</v>
       </c>
       <c r="BK10">
-        <v>1341.981854211706</v>
+        <v>1333.390101680045</v>
       </c>
       <c r="BL10">
-        <v>0.01341981854211706</v>
+        <v>0.01333390101680045</v>
       </c>
       <c r="BM10">
-        <v>443.6268522213771</v>
+        <v>467.297886963444</v>
       </c>
       <c r="BN10">
-        <v>0.004436268522213771</v>
+        <v>0.00467297886963444</v>
       </c>
       <c r="BO10">
-        <v>0.05436738593239326</v>
+        <v>0.05437088262846084</v>
       </c>
       <c r="BP10">
-        <v>0.01182626102404518</v>
+        <v>0.01261996488776739</v>
       </c>
       <c r="BQ10">
-        <v>0.0142658243993479</v>
+        <v>0.0136252563628105</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT10" t="s">
         <v>138</v>
@@ -3056,7 +3056,7 @@
         <v>140</v>
       </c>
       <c r="BW10" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3064,7 +3064,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3088,19 +3088,19 @@
         <v>94</v>
       </c>
       <c r="J11" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="K11">
-        <v>0.06357175292922376</v>
+        <v>0.466976522414023</v>
       </c>
       <c r="L11">
-        <v>1.646754074149344</v>
+        <v>2.015694159796184</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O11" t="s">
         <v>95</v>
@@ -3109,7 +3109,7 @@
         <v>98</v>
       </c>
       <c r="Q11">
-        <v>0.765892938232306</v>
+        <v>0.8667441306035057</v>
       </c>
       <c r="R11" t="s">
         <v>104</v>
@@ -3118,10 +3118,10 @@
         <v>109</v>
       </c>
       <c r="T11">
-        <v>-0.8744581198095189</v>
+        <v>-0.778959500904514</v>
       </c>
       <c r="U11">
-        <v>0.8028025154358138</v>
+        <v>0.8205065222934803</v>
       </c>
       <c r="V11" t="s">
         <v>94</v>
@@ -3130,22 +3130,22 @@
         <v>95</v>
       </c>
       <c r="X11">
-        <v>0.999042394328587</v>
+        <v>0.9997130740973819</v>
       </c>
       <c r="Y11">
-        <v>0.4045172305550302</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <v>-137.0405313824414</v>
+        <v>-126.5952258455755</v>
       </c>
       <c r="AA11">
-        <v>31.00000000000001</v>
+        <v>18</v>
       </c>
       <c r="AB11">
-        <v>-0.7318359683680616</v>
+        <v>-0.5961579783596169</v>
       </c>
       <c r="AC11">
-        <v>-0.6814808254109439</v>
+        <v>-0.8028671526710844</v>
       </c>
       <c r="AD11" t="s">
         <v>94</v>
@@ -3160,67 +3160,67 @@
         <v>126</v>
       </c>
       <c r="AH11">
-        <v>-0.5134459637039459</v>
+        <v>-0.5959869251935731</v>
       </c>
       <c r="AI11">
-        <v>0.7900713387179813</v>
+        <v>0.868858137498096</v>
       </c>
       <c r="AJ11">
-        <v>-1.169217851117298</v>
+        <v>-1.44781087598651</v>
       </c>
       <c r="AK11">
-        <v>-1.031464816053185</v>
+        <v>-1.872466266693213</v>
       </c>
       <c r="AL11">
-        <v>-2.357658758448784</v>
+        <v>-2.838133221771392</v>
       </c>
       <c r="AM11">
-        <v>-0.2336889736355396</v>
+        <v>0.5896476876126722</v>
       </c>
       <c r="AN11">
-        <v>2.360102963382795</v>
+        <v>2.734505105853313</v>
       </c>
       <c r="AO11">
-        <v>0.06698490612299135</v>
+        <v>0.06592554629248365</v>
       </c>
       <c r="AP11">
-        <v>156.266</v>
+        <v>156.014</v>
       </c>
       <c r="AQ11">
-        <v>155.3383564403943</v>
+        <v>154.8545709086821</v>
       </c>
       <c r="AR11">
-        <v>155.3401792487174</v>
+        <v>154.7705643253629</v>
       </c>
       <c r="AS11">
-        <v>156.266</v>
+        <v>156.014</v>
       </c>
       <c r="AT11">
-        <v>154.8175</v>
+        <v>154.3135</v>
       </c>
       <c r="AU11">
-        <v>155.3383564403943</v>
+        <v>154.8545709086821</v>
       </c>
       <c r="AV11">
-        <v>157.4295</v>
+        <v>157.1775</v>
       </c>
       <c r="AW11">
-        <v>-0.005936310903239705</v>
+        <v>-0.007431570829015</v>
       </c>
       <c r="AX11">
-        <v>0.7972871161200217</v>
+        <v>0.996501152830196</v>
       </c>
       <c r="AY11">
-        <v>0.005936310903239705</v>
+        <v>0.007431570829015</v>
       </c>
       <c r="AZ11">
-        <v>0.4422529514259067</v>
+        <v>0.4396993979402487</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3577470485740933</v>
+        <v>0.3603006020597513</v>
       </c>
       <c r="BC11" t="s">
         <v>136</v>
@@ -3232,46 +3232,46 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>382.946469116153</v>
+        <v>433.3720653017529</v>
       </c>
       <c r="BG11">
-        <v>0.007445637566713254</v>
+        <v>0.00745766405578995</v>
       </c>
       <c r="BH11">
-        <v>67153.41641598547</v>
+        <v>67045.1224752893</v>
       </c>
       <c r="BI11">
-        <v>51432.32741117668</v>
+        <v>58110.96639105019</v>
       </c>
       <c r="BJ11">
-        <v>329.1331921926503</v>
+        <v>372.4727677711628</v>
       </c>
       <c r="BK11">
-        <v>514.3232741117668</v>
+        <v>581.1096639105019</v>
       </c>
       <c r="BL11">
-        <v>0.005143232741117667</v>
+        <v>0.005811096639105019</v>
       </c>
       <c r="BM11">
-        <v>382.946469116153</v>
+        <v>433.3720653017529</v>
       </c>
       <c r="BN11">
-        <v>0.00382946469116153</v>
+        <v>0.004333720653017529</v>
       </c>
       <c r="BO11">
-        <v>4.621939649478507</v>
+        <v>4.955082120677464</v>
       </c>
       <c r="BP11">
-        <v>2.051950435257889</v>
+        <v>2.150583600468407</v>
       </c>
       <c r="BQ11">
-        <v>3.08712127926876</v>
+        <v>3.194757311146474</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.0478264430776803</v>
+        <v>0.04881253544601418</v>
       </c>
       <c r="BT11" t="s">
         <v>138</v>
@@ -3283,7 +3283,7 @@
         <v>140</v>
       </c>
       <c r="BW11" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -241,48 +241,48 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>USDCHF</t>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
   </si>
   <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>LOW</t>
   </si>
   <si>
@@ -316,30 +316,30 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
     <t>多头减速</t>
   </si>
   <si>
     <t>多头加速</t>
   </si>
   <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
     <t>空头稳态</t>
   </si>
   <si>
@@ -361,70 +361,70 @@
     <t>下跌</t>
   </si>
   <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>地形转换区</t>
-  </si>
-  <si>
-    <t>上升坡延续</t>
-  </si>
-  <si>
     <t>下降坡延续</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.007438,naive=0.002337,drift4=0.00696; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01459,naive=0.00175,drift4=0.003908; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1093,naive=0.01208,drift4=0.03581; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05575,naive=0.006978,drift4=0.02585; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.012,naive=0.00243,drift4=0.003766; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0148,naive=0.00236,drift4=0.005999; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.07679,naive=0.02574,drift4=0.04576; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=189.6,naive=38.02,drift4=185.2; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.05437,naive=0.01262,drift4=0.01363; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=4.955,naive=2.151,drift4=3.195; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05222,naive=0.009403,drift4=0.02521; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.09725,naive=0.01747,drift4=0.03131; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=286.6,naive=28.78,drift4=163; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01177,naive=0.001403,drift4=0.002606; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0156,naive=0.002358,drift4=0.004339; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01375,naive=0.001727,drift4=0.003649; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0171,naive=0.001524,drift4=0.003553; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.05216,naive=0.0101,drift4=0.01448; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=6.646,naive=2.376,drift4=3.361; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1208,naive=0.006531,drift4=0.01932; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1033,7 +1033,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1057,19 +1057,19 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.3664169303597309</v>
       </c>
       <c r="L2">
-        <v>0.8502707438499056</v>
+        <v>1.002342793513443</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O2" t="s">
         <v>90</v>
@@ -1087,10 +1087,10 @@
         <v>105</v>
       </c>
       <c r="T2">
-        <v>0.6302822519807366</v>
+        <v>0.994515672133489</v>
       </c>
       <c r="U2">
-        <v>0.6835214301323543</v>
+        <v>0.9024328318020196</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1099,22 +1099,22 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9995776669640914</v>
+        <v>0.9997529591519594</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0.169381509783897</v>
       </c>
       <c r="Z2">
-        <v>-67.6280732430146</v>
+        <v>9.920448444963712</v>
       </c>
       <c r="AA2">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="AB2">
-        <v>0.3806173303234104</v>
+        <v>0.9850479031788599</v>
       </c>
       <c r="AC2">
-        <v>-0.9247326358777871</v>
+        <v>0.1722806676412979</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1129,58 +1129,58 @@
         <v>121</v>
       </c>
       <c r="AH2">
-        <v>0.3804565830507756</v>
+        <v>0.5758061193326925</v>
       </c>
       <c r="AI2">
-        <v>0.8045241285136036</v>
+        <v>0.8234993582085794</v>
       </c>
       <c r="AJ2">
-        <v>0.7608842998777121</v>
+        <v>0.8108816373906355</v>
       </c>
       <c r="AK2">
-        <v>-1.73260066518788</v>
+        <v>0.1251687777128305</v>
       </c>
       <c r="AL2">
-        <v>0.5363422346182095</v>
+        <v>1.017977037020363</v>
       </c>
       <c r="AM2">
-        <v>-1.987207813225518</v>
+        <v>-1.640169259271452</v>
       </c>
       <c r="AN2">
-        <v>0.440719185432676</v>
+        <v>0.8820401676251696</v>
       </c>
       <c r="AO2">
-        <v>0.06342169347234336</v>
+        <v>0.03869900270029161</v>
       </c>
       <c r="AP2">
-        <v>1.35177</v>
+        <v>4.84069</v>
       </c>
       <c r="AQ2">
-        <v>1.35092298277353</v>
+        <v>4.842959146938227</v>
       </c>
       <c r="AR2">
-        <v>1.348699182758458</v>
+        <v>4.793063380117568</v>
       </c>
       <c r="AS2">
-        <v>1.35177</v>
+        <v>4.84069</v>
       </c>
       <c r="AT2">
-        <v>1.35367</v>
+        <v>4.905740000000001</v>
       </c>
       <c r="AW2">
-        <v>-0.0006265986273327758</v>
+        <v>0.0004687651839359669</v>
       </c>
       <c r="AY2">
-        <v>0.0006265986273327758</v>
+        <v>0.0004687651839359669</v>
       </c>
       <c r="AZ2">
-        <v>0.4761827102972768</v>
+        <v>0.4417141117092844</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3238172897027232</v>
+        <v>0.3582858882907156</v>
       </c>
       <c r="BC2" t="s">
         <v>127</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.007437802443123573</v>
+        <v>0.05222457394889583</v>
       </c>
       <c r="BP2">
-        <v>0.002336947028346388</v>
+        <v>0.009403030329300963</v>
       </c>
       <c r="BQ2">
-        <v>0.006959601399292075</v>
+        <v>0.02521125915406773</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT2" t="s">
         <v>137</v>
@@ -1240,7 +1240,7 @@
         <v>139</v>
       </c>
       <c r="BW2" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1263,37 +1263,37 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
         <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.4445940546269952</v>
+        <v>0.1227504124957605</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q3">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R3" t="s">
         <v>101</v>
@@ -1302,40 +1302,40 @@
         <v>106</v>
       </c>
       <c r="T3">
-        <v>0.7798578699661117</v>
+        <v>0.3969018922560495</v>
       </c>
       <c r="U3">
-        <v>0.7509089809896883</v>
+        <v>0.4535576362848359</v>
       </c>
       <c r="V3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="W3" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="X3">
-        <v>0.9998917580197519</v>
+        <v>0.9998071390784544</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>0.1880285614085631</v>
       </c>
       <c r="Z3">
-        <v>69.19110496674028</v>
+        <v>-96.85647803352097</v>
       </c>
       <c r="AA3">
-        <v>-31.99999999999999</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AB3">
-        <v>0.3552520875871892</v>
+        <v>-0.119382704170757</v>
       </c>
       <c r="AC3">
-        <v>0.9347705356208784</v>
+        <v>-0.992848311649306</v>
       </c>
       <c r="AD3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="AE3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF3" t="s">
         <v>116</v>
@@ -1344,67 +1344,58 @@
         <v>122</v>
       </c>
       <c r="AH3">
-        <v>0.1776068171988708</v>
+        <v>-0.07090135440826592</v>
       </c>
       <c r="AI3">
-        <v>0.590344826896922</v>
+        <v>0.5380106563305191</v>
       </c>
       <c r="AJ3">
-        <v>0.2482940020501148</v>
+        <v>-0.05377530696909347</v>
       </c>
       <c r="AK3">
-        <v>0.7932259820012609</v>
+        <v>-0.7820390644770328</v>
       </c>
       <c r="AL3">
-        <v>0.9684795646683404</v>
+        <v>-0.4085404372394565</v>
       </c>
       <c r="AM3">
-        <v>0.2161796770962048</v>
+        <v>-0.2464802607138144</v>
       </c>
       <c r="AN3">
-        <v>0.936830457341394</v>
+        <v>0.3924626088054131</v>
       </c>
       <c r="AO3">
-        <v>0.1079527645743192</v>
+        <v>0.2356157725325308</v>
       </c>
       <c r="AP3">
-        <v>0.8100149999999999</v>
+        <v>9.08291</v>
       </c>
       <c r="AQ3">
-        <v>0.8170180736184469</v>
+        <v>9.084786785476714</v>
       </c>
       <c r="AR3">
-        <v>0.8294289641170285</v>
+        <v>9.127532885296398</v>
       </c>
       <c r="AS3">
-        <v>0.8100149999999999</v>
+        <v>9.08291</v>
       </c>
       <c r="AT3">
-        <v>0.8073649999999999</v>
-      </c>
-      <c r="AU3">
-        <v>0.8170180736184469</v>
-      </c>
-      <c r="AV3">
-        <v>0.7999799999999999</v>
+        <v>9.04078</v>
       </c>
       <c r="AW3">
-        <v>0.008645609795432168</v>
-      </c>
-      <c r="AX3">
-        <v>0.6978648349224709</v>
+        <v>0.0002066282146045821</v>
       </c>
       <c r="AY3">
-        <v>0.008645609795432168</v>
+        <v>0.0002066282146045821</v>
       </c>
       <c r="AZ3">
-        <v>0.4134829793076963</v>
+        <v>0.4101395055063513</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3865170206923037</v>
+        <v>0.3898604944936488</v>
       </c>
       <c r="BC3" t="s">
         <v>128</v>
@@ -1416,58 +1407,55 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>375</v>
-      </c>
-      <c r="BG3">
-        <v>0.01238865946926907</v>
+        <v>0</v>
       </c>
       <c r="BH3">
-        <v>40359.49177877433</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>30269.61883408075</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>37369.20777279526</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>302.6961883408075</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>0.003026961883408075</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>0.00375</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>0.01459425477017675</v>
+        <v>0.09725107472064448</v>
       </c>
       <c r="BP3">
-        <v>0.001750012689922765</v>
+        <v>0.01746639280434566</v>
       </c>
       <c r="BQ3">
-        <v>0.003908176223950665</v>
+        <v>0.03131129397347893</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW3" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1475,7 +1463,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1487,7 +1475,7 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
@@ -1499,19 +1487,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.02266680764321327</v>
+        <v>0.9012724993344023</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1523,46 +1511,46 @@
         <v>0.75</v>
       </c>
       <c r="R4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T4">
-        <v>0.6602921187952704</v>
+        <v>0.8396326438744856</v>
       </c>
       <c r="U4">
-        <v>0.6470492783123629</v>
+        <v>0.7775815498610414</v>
       </c>
       <c r="V4" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W4" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9996712994179653</v>
+        <v>0.9989874404700918</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>0.05544383545829693</v>
       </c>
       <c r="Z4">
-        <v>-83.67845655133443</v>
+        <v>-56.01739052334261</v>
       </c>
       <c r="AA4">
-        <v>-41.99999999999999</v>
+        <v>-11</v>
       </c>
       <c r="AB4">
-        <v>0.1101080367310409</v>
+        <v>0.5589412466649271</v>
       </c>
       <c r="AC4">
-        <v>-0.993919624641367</v>
+        <v>-0.8292072616521501</v>
       </c>
       <c r="AD4" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF4" t="s">
         <v>117</v>
@@ -1571,67 +1559,67 @@
         <v>123</v>
       </c>
       <c r="AH4">
-        <v>0.05503592207764033</v>
+        <v>0.2946668764127441</v>
       </c>
       <c r="AI4">
-        <v>0.5061050693369583</v>
+        <v>0.669243529618861</v>
       </c>
       <c r="AJ4">
-        <v>0.2001709252836051</v>
+        <v>0.8545968567970055</v>
       </c>
       <c r="AK4">
-        <v>-0.9317671805205791</v>
+        <v>-1.188568195147521</v>
       </c>
       <c r="AL4">
-        <v>-0.5822557722998513</v>
+        <v>0.3498533311468189</v>
       </c>
       <c r="AM4">
-        <v>-1.636158976104565</v>
+        <v>-2.763163284504506</v>
       </c>
       <c r="AN4">
-        <v>0.7054265234644145</v>
+        <v>0.3955920105007742</v>
       </c>
       <c r="AO4">
-        <v>0.1787486431909451</v>
+        <v>0.06115477091205695</v>
       </c>
       <c r="AP4">
-        <v>7.7899</v>
+        <v>4403.84</v>
       </c>
       <c r="AQ4">
-        <v>7.849161339113996</v>
+        <v>4545.985323292545</v>
       </c>
       <c r="AR4">
-        <v>7.930163689113234</v>
+        <v>4685.802938654239</v>
       </c>
       <c r="AS4">
-        <v>7.7899</v>
+        <v>4403.84</v>
       </c>
       <c r="AT4">
-        <v>7.786200000000001</v>
+        <v>4431.950000000001</v>
       </c>
       <c r="AU4">
-        <v>7.849161339113996</v>
+        <v>4545.985323292545</v>
       </c>
       <c r="AV4">
-        <v>7.734975</v>
+        <v>4265.02</v>
       </c>
       <c r="AW4">
-        <v>0.007607458261851344</v>
+        <v>0.03227758576436589</v>
       </c>
       <c r="AX4">
-        <v>1.078950188693599</v>
+        <v>1.023954208993991</v>
       </c>
       <c r="AY4">
-        <v>0.007607458261851344</v>
+        <v>0.03227758576436589</v>
       </c>
       <c r="AZ4">
-        <v>0.4322016162357126</v>
+        <v>0.4713647355310885</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3677983837642874</v>
+        <v>0.3286352644689115</v>
       </c>
       <c r="BC4" t="s">
         <v>129</v>
@@ -1646,43 +1634,43 @@
         <v>375</v>
       </c>
       <c r="BG4">
-        <v>0.007050796544243172</v>
+        <v>0.03152248946374057</v>
       </c>
       <c r="BH4">
-        <v>70913.97360036428</v>
+        <v>15861.69139893396</v>
       </c>
       <c r="BI4">
-        <v>53185.4802002732</v>
+        <v>11896.26854920047</v>
       </c>
       <c r="BJ4">
-        <v>6827.492034592639</v>
+        <v>2.701339864572843</v>
       </c>
       <c r="BK4">
-        <v>531.8548020027321</v>
+        <v>118.9626854920047</v>
       </c>
       <c r="BL4">
-        <v>0.005318548020027321</v>
+        <v>0.001189626854920047</v>
       </c>
       <c r="BM4">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="BN4">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="BO4">
-        <v>0.1093161290134215</v>
+        <v>286.5752129019122</v>
       </c>
       <c r="BP4">
-        <v>0.01207749478290436</v>
+        <v>28.77532413890723</v>
       </c>
       <c r="BQ4">
-        <v>0.03580519702942954</v>
+        <v>162.9552252720018</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT4" t="s">
         <v>138</v>
@@ -1694,7 +1682,7 @@
         <v>140</v>
       </c>
       <c r="BW4" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1702,7 +1690,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1714,7 +1702,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1726,19 +1714,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K5">
-        <v>0.2433881329000335</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>0.9386445228628102</v>
+        <v>0.5257793442834557</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="O5" t="s">
         <v>95</v>
@@ -1747,7 +1735,7 @@
         <v>98</v>
       </c>
       <c r="Q5">
-        <v>0.8108470332250084</v>
+        <v>0.75</v>
       </c>
       <c r="R5" t="s">
         <v>102</v>
@@ -1756,10 +1744,10 @@
         <v>107</v>
       </c>
       <c r="T5">
-        <v>0.9999886134501064</v>
+        <v>0.8345605825612374</v>
       </c>
       <c r="U5">
-        <v>0.8864448097489284</v>
+        <v>0.775395298077429</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1768,22 +1756,22 @@
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9997668550455016</v>
+        <v>0.9993721436994882</v>
       </c>
       <c r="Y5">
-        <v>0.05397374160614632</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>0.4703143851624944</v>
+        <v>58.98259758085585</v>
       </c>
       <c r="AA5">
-        <v>-5.999999999999996</v>
+        <v>-44</v>
       </c>
       <c r="AB5">
-        <v>0.9999663101695172</v>
+        <v>0.5152983981553437</v>
       </c>
       <c r="AC5">
-        <v>0.00820844235899219</v>
+        <v>0.8570108289038925</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1798,67 +1786,67 @@
         <v>124</v>
       </c>
       <c r="AH5">
-        <v>0.526846256513993</v>
+        <v>0.2574874324047091</v>
       </c>
       <c r="AI5">
-        <v>0.8050287699562102</v>
+        <v>0.6404964866540324</v>
       </c>
       <c r="AJ5">
-        <v>0.7682394663389822</v>
+        <v>0.3106804279234047</v>
       </c>
       <c r="AK5">
-        <v>0.01696259708175796</v>
+        <v>0.6383908648513057</v>
       </c>
       <c r="AL5">
-        <v>0.9143838870640846</v>
+        <v>1.063794997024615</v>
       </c>
       <c r="AM5">
-        <v>-1.661593666137039</v>
+        <v>0.1748740564399984</v>
       </c>
       <c r="AN5">
-        <v>0.7790072515078634</v>
+        <v>1.032793010352023</v>
       </c>
       <c r="AO5">
-        <v>0.03782847121199816</v>
+        <v>0.09248855391594409</v>
       </c>
       <c r="AP5">
-        <v>4.83103</v>
+        <v>0.8115250000000001</v>
       </c>
       <c r="AQ5">
-        <v>4.866147433177178</v>
+        <v>0.8197947911307546</v>
       </c>
       <c r="AR5">
-        <v>4.858067986514525</v>
+        <v>0.834106457132913</v>
       </c>
       <c r="AS5">
-        <v>4.83103</v>
+        <v>0.8115250000000001</v>
       </c>
       <c r="AT5">
-        <v>4.896780000000001</v>
+        <v>0.8096750000000001</v>
       </c>
       <c r="AU5">
-        <v>4.866147433177178</v>
+        <v>0.8197947911307546</v>
       </c>
       <c r="AV5">
-        <v>4.791230000000001</v>
+        <v>0.8022350000000001</v>
       </c>
       <c r="AW5">
-        <v>0.007269139950937625</v>
+        <v>0.01019043298820683</v>
       </c>
       <c r="AX5">
-        <v>0.8823475672657825</v>
+        <v>0.8901820377561465</v>
       </c>
       <c r="AY5">
-        <v>0.007269139950937625</v>
+        <v>0.01019043298820683</v>
       </c>
       <c r="AZ5">
-        <v>0.4516057225848565</v>
+        <v>0.3990671157153338</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3483942774151435</v>
+        <v>0.4009328842846662</v>
       </c>
       <c r="BC5" t="s">
         <v>130</v>
@@ -1870,46 +1858,46 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>405.4235166125042</v>
+        <v>375</v>
       </c>
       <c r="BG5">
-        <v>0.008238408786532076</v>
+        <v>0.01144758325375058</v>
       </c>
       <c r="BH5">
-        <v>60691.33165829137</v>
+        <v>43677.34122712624</v>
       </c>
       <c r="BI5">
-        <v>49211.38621760059</v>
+        <v>32758.00592034468</v>
       </c>
       <c r="BJ5">
-        <v>10186.5205179021</v>
+        <v>40365.98493003256</v>
       </c>
       <c r="BK5">
-        <v>492.1138621760059</v>
+        <v>327.5800592034468</v>
       </c>
       <c r="BL5">
-        <v>0.004921138621760059</v>
+        <v>0.003275800592034468</v>
       </c>
       <c r="BM5">
-        <v>405.4235166125042</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN5">
-        <v>0.004054235166125042</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO5">
-        <v>0.05574627618925981</v>
+        <v>0.01177170371041717</v>
       </c>
       <c r="BP5">
-        <v>0.006978339985505324</v>
+        <v>0.001403001178787998</v>
       </c>
       <c r="BQ5">
-        <v>0.02584637592939295</v>
+        <v>0.002605872439464153</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT5" t="s">
         <v>138</v>
@@ -1921,7 +1909,7 @@
         <v>140</v>
       </c>
       <c r="BW5" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1929,7 +1917,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1941,7 +1929,7 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
         <v>91</v>
@@ -1953,19 +1941,19 @@
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2.400270608960956</v>
+        <v>2.603017088231519</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
@@ -1977,16 +1965,16 @@
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T6">
-        <v>0.9999315107325071</v>
+        <v>0.9902667861457664</v>
       </c>
       <c r="U6">
-        <v>0.9998800412718265</v>
+        <v>0.9955117299807449</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1995,22 +1983,22 @@
         <v>95</v>
       </c>
       <c r="X6">
-        <v>0.999643445768793</v>
+        <v>0.9995667048606002</v>
       </c>
       <c r="Y6">
-        <v>0.9324241592517576</v>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>-0.9592686334412081</v>
+        <v>11.32491668756644</v>
       </c>
       <c r="AA6">
-        <v>3.000000000000004</v>
+        <v>16</v>
       </c>
       <c r="AB6">
-        <v>0.9998598493608297</v>
+        <v>0.9805293531091277</v>
       </c>
       <c r="AC6">
-        <v>-0.01674161390484424</v>
+        <v>0.1963725736741146</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -2019,73 +2007,73 @@
         <v>112</v>
       </c>
       <c r="AF6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AH6">
-        <v>0.9657322056629883</v>
+        <v>0.9801044945063867</v>
       </c>
       <c r="AI6">
-        <v>0.980802500865403</v>
+        <v>0.9884276915057459</v>
       </c>
       <c r="AJ6">
-        <v>1.913248459490064</v>
+        <v>2.064471096028702</v>
       </c>
       <c r="AK6">
-        <v>-0.04453097012997838</v>
+        <v>0.3423932881954153</v>
       </c>
       <c r="AL6">
-        <v>2.572103441121658</v>
+        <v>2.836125209226585</v>
       </c>
       <c r="AM6">
-        <v>-3.634458303085958</v>
+        <v>-3.832640055995153</v>
       </c>
       <c r="AN6">
-        <v>2.272213487908998</v>
+        <v>2.513968953375532</v>
       </c>
       <c r="AO6">
-        <v>0.0367699454151666</v>
+        <v>0.0371964075213495</v>
       </c>
       <c r="AP6">
-        <v>0.720145</v>
+        <v>0.721345</v>
       </c>
       <c r="AQ6">
-        <v>0.7251762442677103</v>
+        <v>0.7256652517565074</v>
       </c>
       <c r="AR6">
-        <v>0.7192133433374162</v>
+        <v>0.7193029858387769</v>
       </c>
       <c r="AS6">
-        <v>0.720145</v>
+        <v>0.721345</v>
       </c>
       <c r="AT6">
-        <v>0.73377</v>
+        <v>0.73441</v>
       </c>
       <c r="AU6">
-        <v>0.7251762442677103</v>
+        <v>0.7256652517565074</v>
       </c>
       <c r="AV6">
-        <v>0.71293625</v>
+        <v>0.7141362500000001</v>
       </c>
       <c r="AW6">
-        <v>0.006986432270876405</v>
+        <v>0.005989161575262058</v>
       </c>
       <c r="AX6">
-        <v>0.6979357402754066</v>
+        <v>0.5993066421373263</v>
       </c>
       <c r="AY6">
-        <v>0.006986432270876405</v>
+        <v>0.005989161575262058</v>
       </c>
       <c r="AZ6">
-        <v>0.403166459738972</v>
+        <v>0.4058875021929551</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.396833540261028</v>
+        <v>0.3941124978070449</v>
       </c>
       <c r="BC6" t="s">
         <v>131</v>
@@ -2100,22 +2088,22 @@
         <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.01001013684744035</v>
+        <v>0.009993484393736604</v>
       </c>
       <c r="BH6">
-        <v>49949.36708860807</v>
+        <v>50032.59927171888</v>
       </c>
       <c r="BI6">
-        <v>49949.36708860807</v>
+        <v>50032.59927171888</v>
       </c>
       <c r="BJ6">
         <v>69360.15259233637</v>
       </c>
       <c r="BK6">
-        <v>499.4936708860807</v>
+        <v>500.3259927171888</v>
       </c>
       <c r="BL6">
-        <v>0.004994936708860807</v>
+        <v>0.005003259927171888</v>
       </c>
       <c r="BM6">
         <v>500</v>
@@ -2124,19 +2112,19 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.01200107888063609</v>
+        <v>0.01559726356532664</v>
       </c>
       <c r="BP6">
-        <v>0.002430329182507534</v>
+        <v>0.002358064579542581</v>
       </c>
       <c r="BQ6">
-        <v>0.003766072708663907</v>
+        <v>0.004339398325697697</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT6" t="s">
         <v>138</v>
@@ -2148,7 +2136,7 @@
         <v>140</v>
       </c>
       <c r="BW6" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2156,7 +2144,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2168,7 +2156,7 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
@@ -2180,19 +2168,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K7">
-        <v>0.1652916187970465</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.265249584116171</v>
+        <v>0.9145432411443594</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O7" t="s">
         <v>95</v>
@@ -2201,19 +2189,19 @@
         <v>98</v>
       </c>
       <c r="Q7">
-        <v>0.7913229046992616</v>
+        <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T7">
-        <v>0.8830884112597904</v>
+        <v>0.720610870143059</v>
       </c>
       <c r="U7">
-        <v>0.8215786912494414</v>
+        <v>0.7238971039999447</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2222,22 +2210,22 @@
         <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9975806534519147</v>
+        <v>0.9984888497422726</v>
       </c>
       <c r="Y7">
-        <v>0.5362757071870204</v>
+        <v>0.8360836497435948</v>
       </c>
       <c r="Z7">
-        <v>-40.46197234739928</v>
+        <v>-59.38848286026088</v>
       </c>
       <c r="AA7">
-        <v>5.000000000000007</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AB7">
-        <v>0.7608368417853951</v>
+        <v>0.5092144249490446</v>
       </c>
       <c r="AC7">
-        <v>-0.6489432179952462</v>
+        <v>-0.8606396861775628</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
@@ -2246,73 +2234,73 @@
         <v>112</v>
       </c>
       <c r="AF7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AH7">
-        <v>0.5830136457390457</v>
+        <v>0.4667737071973243</v>
       </c>
       <c r="AI7">
-        <v>0.8280291120453563</v>
+        <v>0.812129388705314</v>
       </c>
       <c r="AJ7">
-        <v>1.106657712431845</v>
+        <v>0.7685281417255759</v>
       </c>
       <c r="AK7">
-        <v>-0.9700211311844404</v>
+        <v>-1.355771977675915</v>
       </c>
       <c r="AL7">
-        <v>0.9066759669440969</v>
+        <v>0.7897851815310688</v>
       </c>
       <c r="AM7">
-        <v>-2.787668985716782</v>
+        <v>-1.350891593156276</v>
       </c>
       <c r="AN7">
-        <v>0.7286936216643226</v>
+        <v>0.737424183407118</v>
       </c>
       <c r="AO7">
-        <v>0.04420207090557568</v>
+        <v>0.04881844091942383</v>
       </c>
       <c r="AP7">
-        <v>1.161345</v>
+        <v>1.3545</v>
       </c>
       <c r="AQ7">
-        <v>1.164562120245709</v>
+        <v>1.3568298478857</v>
       </c>
       <c r="AR7">
-        <v>1.164579176164103</v>
+        <v>1.359500589092673</v>
       </c>
       <c r="AS7">
-        <v>1.161345</v>
+        <v>1.3545</v>
       </c>
       <c r="AT7">
-        <v>1.166295</v>
+        <v>1.35521</v>
       </c>
       <c r="AU7">
-        <v>1.164562120245709</v>
+        <v>1.3568298478857</v>
       </c>
       <c r="AV7">
-        <v>1.150985</v>
+        <v>1.343075</v>
       </c>
       <c r="AW7">
-        <v>0.002770167560637856</v>
+        <v>0.001720079649833976</v>
       </c>
       <c r="AX7">
-        <v>0.3105328422498996</v>
+        <v>0.2039254166914763</v>
       </c>
       <c r="AY7">
-        <v>0.002770167560637856</v>
+        <v>0.001720079649833976</v>
       </c>
       <c r="AZ7">
-        <v>0.4329580570855683</v>
+        <v>0.4106307659964421</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3670419429144318</v>
+        <v>0.3893692340035579</v>
       </c>
       <c r="BC7" t="s">
         <v>132</v>
@@ -2324,46 +2312,46 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>395.6614523496308</v>
+        <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.00892069109523874</v>
+        <v>0.008434846806939844</v>
       </c>
       <c r="BH7">
-        <v>56049.46911196892</v>
+        <v>59277.89934354476</v>
       </c>
       <c r="BI7">
-        <v>44353.22870453479</v>
+        <v>44458.42450765857</v>
       </c>
       <c r="BJ7">
-        <v>38191.25987930787</v>
+        <v>32822.75711159732</v>
       </c>
       <c r="BK7">
-        <v>443.5322870453479</v>
+        <v>444.5842450765857</v>
       </c>
       <c r="BL7">
-        <v>0.004435322870453479</v>
+        <v>0.004445842450765857</v>
       </c>
       <c r="BM7">
-        <v>395.6614523496308</v>
+        <v>375</v>
       </c>
       <c r="BN7">
-        <v>0.003956614523496308</v>
+        <v>0.00375</v>
       </c>
       <c r="BO7">
-        <v>0.01480034685695315</v>
+        <v>0.0137472192395769</v>
       </c>
       <c r="BP7">
-        <v>0.002359690683237485</v>
+        <v>0.001727049226814625</v>
       </c>
       <c r="BQ7">
-        <v>0.005999236469214154</v>
+        <v>0.003648729307490551</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT7" t="s">
         <v>138</v>
@@ -2375,7 +2363,7 @@
         <v>140</v>
       </c>
       <c r="BW7" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2383,7 +2371,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2407,19 +2395,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.1096653187544404</v>
       </c>
       <c r="L8">
-        <v>0.1215937009524473</v>
+        <v>1.230944690076117</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O8" t="s">
         <v>96</v>
@@ -2428,49 +2416,49 @@
         <v>99</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.9177510109341698</v>
       </c>
       <c r="R8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T8">
-        <v>0.3461365148896858</v>
+        <v>0.9392227807266568</v>
       </c>
       <c r="U8">
-        <v>0.455716061937822</v>
+        <v>0.8381969984093558</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9998185209498537</v>
+        <v>0.9963877970767767</v>
       </c>
       <c r="Y8">
-        <v>0.5563029909034597</v>
+        <v>0.2813168943633795</v>
       </c>
       <c r="Z8">
-        <v>-94.30625840196588</v>
+        <v>-30.92133310190683</v>
       </c>
       <c r="AA8">
-        <v>-21</v>
+        <v>22.00000000000001</v>
       </c>
       <c r="AB8">
-        <v>-0.07508764863196088</v>
+        <v>0.857873637963354</v>
       </c>
       <c r="AC8">
-        <v>-0.9971769376710049</v>
+        <v>-0.5138607022214484</v>
       </c>
       <c r="AD8" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF8" t="s">
         <v>117</v>
@@ -2479,67 +2467,67 @@
         <v>123</v>
       </c>
       <c r="AH8">
-        <v>-0.05841896233076303</v>
+        <v>0.5476187116263899</v>
       </c>
       <c r="AI8">
-        <v>0.5927124787755713</v>
+        <v>0.8059770240761885</v>
       </c>
       <c r="AJ8">
-        <v>-0.03085567019374423</v>
+        <v>1.073903918500121</v>
       </c>
       <c r="AK8">
-        <v>-0.9256928380483996</v>
+        <v>-0.7376161852156446</v>
       </c>
       <c r="AL8">
-        <v>-0.4875919132620308</v>
+        <v>0.8950066191053321</v>
       </c>
       <c r="AM8">
-        <v>-0.617506360995302</v>
+        <v>-2.700938541313292</v>
       </c>
       <c r="AN8">
-        <v>0.499935264061904</v>
+        <v>0.7179606737755675</v>
       </c>
       <c r="AO8">
-        <v>0.2734059755143843</v>
+        <v>0.04256116774910201</v>
       </c>
       <c r="AP8">
-        <v>9.069750000000001</v>
+        <v>1.161235</v>
       </c>
       <c r="AQ8">
-        <v>9.047913442817689</v>
+        <v>1.158242911673746</v>
       </c>
       <c r="AR8">
-        <v>9.040742348927619</v>
+        <v>1.149876771886211</v>
       </c>
       <c r="AS8">
-        <v>9.069750000000001</v>
+        <v>1.161235</v>
       </c>
       <c r="AT8">
-        <v>9.044540000000001</v>
+        <v>1.165455</v>
       </c>
       <c r="AU8">
-        <v>9.047913442817689</v>
+        <v>1.158242911673746</v>
       </c>
       <c r="AV8">
-        <v>9.152540000000002</v>
+        <v>1.17105875</v>
       </c>
       <c r="AW8">
-        <v>-0.002407625037328632</v>
+        <v>-0.002576643251584902</v>
       </c>
       <c r="AX8">
-        <v>0.2637583908963804</v>
+        <v>0.304577002290794</v>
       </c>
       <c r="AY8">
-        <v>0.002407625037328632</v>
+        <v>0.002576643251584902</v>
       </c>
       <c r="AZ8">
-        <v>0.4393655842809088</v>
+        <v>0.4087812991143387</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3606344157190912</v>
+        <v>0.3912187008856614</v>
       </c>
       <c r="BC8" t="s">
         <v>133</v>
@@ -2551,46 +2539,46 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>500</v>
+        <v>458.8755054670849</v>
       </c>
       <c r="BG8">
-        <v>0.009128145759254681</v>
+        <v>0.008459743290548442</v>
       </c>
       <c r="BH8">
-        <v>54775.63715424559</v>
+        <v>59103.44827586195</v>
       </c>
       <c r="BI8">
-        <v>54775.63715424559</v>
+        <v>54242.24940486772</v>
       </c>
       <c r="BJ8">
-        <v>6039.376736320801</v>
+        <v>46710.82890617981</v>
       </c>
       <c r="BK8">
-        <v>547.7563715424559</v>
+        <v>542.4224940486772</v>
       </c>
       <c r="BL8">
-        <v>0.005477563715424559</v>
+        <v>0.005424224940486772</v>
       </c>
       <c r="BM8">
-        <v>500</v>
+        <v>458.8755054670849</v>
       </c>
       <c r="BN8">
-        <v>0.005</v>
+        <v>0.004588755054670849</v>
       </c>
       <c r="BO8">
-        <v>0.07678987129326678</v>
+        <v>0.01709971436505893</v>
       </c>
       <c r="BP8">
-        <v>0.02573821460852699</v>
+        <v>0.001524268786529646</v>
       </c>
       <c r="BQ8">
-        <v>0.04575610168102937</v>
+        <v>0.003553375048062908</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT8" t="s">
         <v>138</v>
@@ -2602,7 +2590,7 @@
         <v>140</v>
       </c>
       <c r="BW8" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2610,7 +2598,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2622,7 +2610,7 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
         <v>92</v>
@@ -2631,142 +2619,142 @@
         <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.9038475664035587</v>
       </c>
       <c r="L9">
-        <v>1.037737926002288</v>
+        <v>3.53105594817804</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="O9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.9759618916008896</v>
       </c>
       <c r="R9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="S9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="T9">
-        <v>0.75060117602011</v>
+        <v>-0.9917129125256611</v>
       </c>
       <c r="U9">
-        <v>0.7376234054156443</v>
+        <v>0.9817957314688525</v>
       </c>
       <c r="V9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W9" t="s">
         <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9994115048263792</v>
+        <v>0.9997911434870851</v>
       </c>
       <c r="Y9">
-        <v>0.4550776311383243</v>
+        <v>1</v>
       </c>
       <c r="Z9">
-        <v>-60.67437586482892</v>
+        <v>-169.6354953647062</v>
       </c>
       <c r="AA9">
-        <v>-20</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="AB9">
-        <v>0.4897724144346818</v>
+        <v>-0.9836831156550757</v>
       </c>
       <c r="AC9">
-        <v>-0.8718503209030908</v>
+        <v>-0.1799097773194191</v>
       </c>
       <c r="AD9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AG9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AH9">
-        <v>0.3561187447277421</v>
+        <v>-0.9834776670297267</v>
       </c>
       <c r="AI9">
-        <v>0.7291459083404572</v>
+        <v>0.9893743134434058</v>
       </c>
       <c r="AJ9">
-        <v>0.9620947343368633</v>
+        <v>-2.659346103125017</v>
       </c>
       <c r="AK9">
-        <v>-1.542431762774853</v>
+        <v>-0.4214259324925717</v>
       </c>
       <c r="AL9">
-        <v>0.5009769649772509</v>
+        <v>-4.492511969630058</v>
       </c>
       <c r="AM9">
-        <v>-2.930959714356365</v>
+        <v>3.605115645282452</v>
       </c>
       <c r="AN9">
-        <v>0.4725572360986167</v>
+        <v>4.162264000732653</v>
       </c>
       <c r="AO9">
-        <v>0.05730245937896543</v>
+        <v>0.03771680982397817</v>
       </c>
       <c r="AP9">
-        <v>4430.299999999999</v>
+        <v>6.708855</v>
       </c>
       <c r="AQ9">
-        <v>4413.190502762716</v>
+        <v>6.680778965123105</v>
       </c>
       <c r="AR9">
-        <v>4273.742088853462</v>
+        <v>6.672611602970512</v>
       </c>
       <c r="AS9">
-        <v>4430.299999999999</v>
+        <v>6.708855</v>
       </c>
       <c r="AT9">
-        <v>4618.799999999999</v>
+        <v>6.67488</v>
       </c>
       <c r="AU9">
-        <v>4413.190502762716</v>
+        <v>6.680778965123105</v>
       </c>
       <c r="AV9">
-        <v>4578.662499999999</v>
+        <v>6.732361249999999</v>
       </c>
       <c r="AW9">
-        <v>-0.003861927462538202</v>
+        <v>-0.004184921998894699</v>
       </c>
       <c r="AX9">
-        <v>0.1153222494719562</v>
+        <v>1.194407226882006</v>
       </c>
       <c r="AY9">
-        <v>0.003861927462538202</v>
+        <v>0.004184921998894699</v>
       </c>
       <c r="AZ9">
-        <v>0.4866125128949031</v>
+        <v>0.3950079572699075</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3133874871050969</v>
+        <v>0.4049920427300925</v>
       </c>
       <c r="BC9" t="s">
         <v>134</v>
@@ -2778,46 +2766,46 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>500</v>
+        <v>487.9809458004448</v>
       </c>
       <c r="BG9">
-        <v>0.03348813850077852</v>
+        <v>0.0035037648004018</v>
       </c>
       <c r="BH9">
-        <v>14930.65970174413</v>
+        <v>142703.6426482342</v>
       </c>
       <c r="BI9">
-        <v>14930.65970174413</v>
+        <v>139273.317017308</v>
       </c>
       <c r="BJ9">
-        <v>3.370123852051584</v>
+        <v>20759.62545282437</v>
       </c>
       <c r="BK9">
-        <v>149.3065970174413</v>
+        <v>1392.73317017308</v>
       </c>
       <c r="BL9">
-        <v>0.001493065970174413</v>
+        <v>0.0139273317017308</v>
       </c>
       <c r="BM9">
-        <v>500</v>
+        <v>487.9809458004449</v>
       </c>
       <c r="BN9">
-        <v>0.005</v>
+        <v>0.004879809458004449</v>
       </c>
       <c r="BO9">
-        <v>189.6303301829709</v>
+        <v>0.0521618205979701</v>
       </c>
       <c r="BP9">
-        <v>38.01687340826754</v>
+        <v>0.01009645267807642</v>
       </c>
       <c r="BQ9">
-        <v>185.1584155904734</v>
+        <v>0.01447502051532265</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT9" t="s">
         <v>138</v>
@@ -2829,7 +2817,7 @@
         <v>140</v>
       </c>
       <c r="BW9" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2837,7 +2825,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2849,7 +2837,7 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s">
         <v>92</v>
@@ -2861,19 +2849,19 @@
         <v>94</v>
       </c>
       <c r="J10" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K10">
-        <v>0.7383830957075519</v>
+        <v>0.6713171198624325</v>
       </c>
       <c r="L10">
-        <v>3.315084039482191</v>
+        <v>2.202363507106859</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="O10" t="s">
         <v>95</v>
@@ -2882,19 +2870,19 @@
         <v>98</v>
       </c>
       <c r="Q10">
-        <v>0.934595773926888</v>
+        <v>0.9178292799656081</v>
       </c>
       <c r="R10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T10">
-        <v>-0.9959730809498482</v>
+        <v>-0.7474814155486789</v>
       </c>
       <c r="U10">
-        <v>0.958839200969604</v>
+        <v>0.8370417231215145</v>
       </c>
       <c r="V10" t="s">
         <v>94</v>
@@ -2903,22 +2891,22 @@
         <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9995754007441581</v>
+        <v>0.9999100725809763</v>
       </c>
       <c r="Y10">
-        <v>0.9784433336488914</v>
+        <v>1</v>
       </c>
       <c r="Z10">
-        <v>-172.8550226638579</v>
+        <v>-121.4609328829015</v>
       </c>
       <c r="AA10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AB10">
-        <v>-0.9922346046624108</v>
+        <v>-0.5219170707563664</v>
       </c>
       <c r="AC10">
-        <v>-0.1243804217328009</v>
+        <v>-0.8529962316757876</v>
       </c>
       <c r="AD10" t="s">
         <v>94</v>
@@ -2927,73 +2915,73 @@
         <v>114</v>
       </c>
       <c r="AF10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH10">
-        <v>-0.9811232083644139</v>
+        <v>-0.5218701361012489</v>
       </c>
       <c r="AI10">
-        <v>0.9874653868282052</v>
+        <v>0.8464482310779792</v>
       </c>
       <c r="AJ10">
-        <v>-2.486799220209178</v>
+        <v>-1.571460909393736</v>
       </c>
       <c r="AK10">
-        <v>-0.2386370094443492</v>
+        <v>-2.4989291304811</v>
       </c>
       <c r="AL10">
-        <v>-4.253807111421811</v>
+        <v>-3.155973934756926</v>
       </c>
       <c r="AM10">
-        <v>3.054540062391226</v>
+        <v>0.7191873413693028</v>
       </c>
       <c r="AN10">
-        <v>3.981884980820916</v>
+        <v>3.025631969106124</v>
       </c>
       <c r="AO10">
-        <v>0.03830034373834421</v>
+        <v>0.06730277034848185</v>
       </c>
       <c r="AP10">
-        <v>6.707285000000001</v>
+        <v>154.24</v>
       </c>
       <c r="AQ10">
-        <v>6.680126834375407</v>
+        <v>153.1751170512499</v>
       </c>
       <c r="AR10">
-        <v>6.675097417663345</v>
+        <v>156.2356832636131</v>
       </c>
       <c r="AS10">
-        <v>6.707285000000001</v>
+        <v>154.24</v>
       </c>
       <c r="AT10">
-        <v>6.671750000000001</v>
+        <v>149.164</v>
       </c>
       <c r="AU10">
-        <v>6.680126834375407</v>
+        <v>153.1751170512499</v>
       </c>
       <c r="AV10">
-        <v>6.73079125</v>
+        <v>155.4035</v>
       </c>
       <c r="AW10">
-        <v>-0.004049054964056718</v>
+        <v>-0.006904064761087425</v>
       </c>
       <c r="AX10">
-        <v>1.15535934590135</v>
+        <v>0.9152410388913729</v>
       </c>
       <c r="AY10">
-        <v>0.004049054964056718</v>
+        <v>0.006904064761087425</v>
       </c>
       <c r="AZ10">
-        <v>0.3793474561931316</v>
+        <v>0.4236497789239482</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.4206525438068684</v>
+        <v>0.3763502210760518</v>
       </c>
       <c r="BC10" t="s">
         <v>135</v>
@@ -3005,46 +2993,46 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>467.297886963444</v>
+        <v>458.9146399828041</v>
       </c>
       <c r="BG10">
-        <v>0.003504584940106111</v>
+        <v>0.007543438796680584</v>
       </c>
       <c r="BH10">
-        <v>142670.2472746633</v>
+        <v>66282.76751181703</v>
       </c>
       <c r="BI10">
-        <v>133339.0101680045</v>
+        <v>60836.26477949883</v>
       </c>
       <c r="BJ10">
-        <v>19879.72930448079</v>
+        <v>394.425990530983</v>
       </c>
       <c r="BK10">
-        <v>1333.390101680045</v>
+        <v>608.3626477949883</v>
       </c>
       <c r="BL10">
-        <v>0.01333390101680045</v>
+        <v>0.006083626477949884</v>
       </c>
       <c r="BM10">
-        <v>467.297886963444</v>
+        <v>458.914639982804</v>
       </c>
       <c r="BN10">
-        <v>0.00467297886963444</v>
+        <v>0.00458914639982804</v>
       </c>
       <c r="BO10">
-        <v>0.05437088262846084</v>
+        <v>6.646021895373139</v>
       </c>
       <c r="BP10">
-        <v>0.01261996488776739</v>
+        <v>2.375825713141223</v>
       </c>
       <c r="BQ10">
-        <v>0.0136252563628105</v>
+        <v>3.360918353661905</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT10" t="s">
         <v>138</v>
@@ -3056,7 +3044,7 @@
         <v>140</v>
       </c>
       <c r="BW10" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3064,7 +3052,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3085,142 +3073,142 @@
         <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="K11">
-        <v>0.466976522414023</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2.015694159796184</v>
+        <v>0.01657963019459711</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q11">
-        <v>0.8667441306035057</v>
+        <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="S11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T11">
-        <v>-0.778959500904514</v>
+        <v>0.6496908965436862</v>
       </c>
       <c r="U11">
-        <v>0.8205065222934803</v>
+        <v>0.6422283636159762</v>
       </c>
       <c r="V11" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="X11">
-        <v>0.9997130740973819</v>
+        <v>0.9994698406852699</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>-126.5952258455755</v>
+        <v>-85.2836487829335</v>
       </c>
       <c r="AA11">
-        <v>18</v>
+        <v>-44</v>
       </c>
       <c r="AB11">
-        <v>-0.5961579783596169</v>
+        <v>0.0822229282328244</v>
       </c>
       <c r="AC11">
-        <v>-0.8028671526710844</v>
+        <v>-0.9966139624111333</v>
       </c>
       <c r="AD11" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AE11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AG11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AH11">
-        <v>-0.5959869251935731</v>
+        <v>0.04108966849076869</v>
       </c>
       <c r="AI11">
-        <v>0.868858137498096</v>
+        <v>0.4967065775528007</v>
       </c>
       <c r="AJ11">
-        <v>-1.44781087598651</v>
+        <v>0.1601042929883315</v>
       </c>
       <c r="AK11">
-        <v>-1.872466266693213</v>
+        <v>-0.7825234523324572</v>
       </c>
       <c r="AL11">
-        <v>-2.838133221771392</v>
+        <v>-0.5227757194932624</v>
       </c>
       <c r="AM11">
-        <v>0.5896476876126722</v>
+        <v>-1.26713315497497</v>
       </c>
       <c r="AN11">
-        <v>2.734505105853313</v>
+        <v>0.6065858699962972</v>
       </c>
       <c r="AO11">
-        <v>0.06592554629248365</v>
+        <v>0.1851649677126074</v>
       </c>
       <c r="AP11">
-        <v>156.014</v>
+        <v>7.7968</v>
       </c>
       <c r="AQ11">
-        <v>154.8545709086821</v>
+        <v>7.715657824812026</v>
       </c>
       <c r="AR11">
-        <v>154.7705643253629</v>
+        <v>7.6071170105688</v>
       </c>
       <c r="AS11">
-        <v>156.014</v>
+        <v>7.7968</v>
       </c>
       <c r="AT11">
-        <v>154.3135</v>
+        <v>7.7911</v>
       </c>
       <c r="AU11">
-        <v>154.8545709086821</v>
+        <v>7.715657824812026</v>
       </c>
       <c r="AV11">
-        <v>157.1775</v>
+        <v>7.850894783458649</v>
       </c>
       <c r="AW11">
-        <v>-0.007431570829015</v>
+        <v>-0.01040711255745616</v>
       </c>
       <c r="AX11">
-        <v>0.996501152830196</v>
+        <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.007431570829015</v>
+        <v>0.01040711255745616</v>
       </c>
       <c r="AZ11">
-        <v>0.4396993979402487</v>
+        <v>0.4162459552632278</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3603006020597513</v>
+        <v>0.3837540447367722</v>
       </c>
       <c r="BC11" t="s">
         <v>136</v>
@@ -3232,46 +3220,46 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>433.3720653017529</v>
+        <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.00745766405578995</v>
+        <v>0.006938075038304106</v>
       </c>
       <c r="BH11">
-        <v>67045.1224752893</v>
+        <v>72066.09862816019</v>
       </c>
       <c r="BI11">
-        <v>58110.96639105019</v>
+        <v>72066.09862816019</v>
       </c>
       <c r="BJ11">
-        <v>372.4727677711628</v>
+        <v>9243.035428401421</v>
       </c>
       <c r="BK11">
-        <v>581.1096639105019</v>
+        <v>720.6609862816019</v>
       </c>
       <c r="BL11">
-        <v>0.005811096639105019</v>
+        <v>0.007206609862816019</v>
       </c>
       <c r="BM11">
-        <v>433.3720653017529</v>
+        <v>500</v>
       </c>
       <c r="BN11">
-        <v>0.004333720653017529</v>
+        <v>0.005</v>
       </c>
       <c r="BO11">
-        <v>4.955082120677464</v>
+        <v>0.1207978876027291</v>
       </c>
       <c r="BP11">
-        <v>2.150583600468407</v>
+        <v>0.00653130801811761</v>
       </c>
       <c r="BQ11">
-        <v>3.194757311146474</v>
+        <v>0.01931623541681202</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04881253544601418</v>
+        <v>0.04655632280787573</v>
       </c>
       <c r="BT11" t="s">
         <v>138</v>
@@ -3283,7 +3271,7 @@
         <v>140</v>
       </c>
       <c r="BW11" s="2">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -241,51 +241,51 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -295,12 +295,12 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
@@ -316,115 +316,115 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
     <t>UP_STEADY</t>
   </si>
   <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
-    <t>UP_ACCELERATING</t>
-  </si>
-  <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
-    <t>DOWN_ACCELERATING</t>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>多头减速</t>
+  </si>
+  <si>
+    <t>多头加速</t>
   </si>
   <si>
     <t>多头稳态</t>
   </si>
   <si>
-    <t>多头减速</t>
-  </si>
-  <si>
-    <t>多头加速</t>
-  </si>
-  <si>
     <t>空头稳态</t>
   </si>
   <si>
-    <t>空头加速</t>
-  </si>
-  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>下跌</t>
+  </si>
+  <si>
     <t>上涨</t>
   </si>
   <si>
     <t>转换</t>
   </si>
   <si>
-    <t>下跌</t>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
   </si>
   <si>
     <t>UP_SLOPE</t>
   </si>
   <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
-    <t>UP_STEEPENING</t>
-  </si>
-  <si>
-    <t>DOWN_SLOPE</t>
-  </si>
-  <si>
-    <t>DOWN_STEEPENING</t>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
   </si>
   <si>
     <t>上升坡延续</t>
   </si>
   <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
     <t>地形转换区</t>
   </si>
   <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>上升陡坡形成</t>
-  </si>
-  <si>
-    <t>下降坡延续</t>
-  </si>
-  <si>
-    <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05222,naive=0.009403,drift4=0.02521; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.09725,naive=0.01747,drift4=0.03131; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=286.6,naive=28.78,drift4=163; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01177,naive=0.001403,drift4=0.002606; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0156,naive=0.002358,drift4=0.004339; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01375,naive=0.001727,drift4=0.003649; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0171,naive=0.001524,drift4=0.003553; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.05216,naive=0.0101,drift4=0.01448; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=6.646,naive=2.376,drift4=3.361; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1208,naive=0.006531,drift4=0.01932; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.09294,naive=0.01485,drift4=0.02298; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=290.5,naive=21.71,drift4=141.6; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01526,naive=0.002519,drift4=0.004085; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.01348,naive=0.001283,drift4=0.001667; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.01466,naive=0.002309,drift4=0.002166; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.0483,naive=0.007211,drift4=0.02544; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=0.01787,naive=0.002757,drift4=0.002172; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.05265,naive=0.01052,drift4=0.013; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.1114,naive=0.002884,drift4=0.0067; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=7.224,naive=2.656,drift4=3.592; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1033,7 +1033,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1057,19 +1057,19 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K2">
-        <v>0.3664169303597309</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1.002342793513443</v>
+        <v>0.1709770580259295</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O2" t="s">
         <v>90</v>
@@ -1087,10 +1087,10 @@
         <v>105</v>
       </c>
       <c r="T2">
-        <v>0.994515672133489</v>
+        <v>-0.7294718844236066</v>
       </c>
       <c r="U2">
-        <v>0.9024328318020196</v>
+        <v>0.7281208447294604</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1099,22 +1099,22 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9997529591519594</v>
+        <v>0.9994339869553498</v>
       </c>
       <c r="Y2">
-        <v>0.169381509783897</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>9.920448444963712</v>
+        <v>-101.9725834939739</v>
       </c>
       <c r="AA2">
-        <v>9</v>
+        <v>-29</v>
       </c>
       <c r="AB2">
-        <v>0.9850479031788599</v>
+        <v>-0.2074436152876978</v>
       </c>
       <c r="AC2">
-        <v>0.1722806676412979</v>
+        <v>-0.9782469762163181</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1129,58 +1129,58 @@
         <v>121</v>
       </c>
       <c r="AH2">
-        <v>0.5758061193326925</v>
+        <v>-0.1036630997477078</v>
       </c>
       <c r="AI2">
-        <v>0.8234993582085794</v>
+        <v>0.536036785176411</v>
       </c>
       <c r="AJ2">
-        <v>0.8108816373906355</v>
+        <v>-0.0919466019147635</v>
       </c>
       <c r="AK2">
-        <v>0.1251687777128305</v>
+        <v>-0.6900769913542941</v>
       </c>
       <c r="AL2">
-        <v>1.017977037020363</v>
+        <v>-0.4284720386196494</v>
       </c>
       <c r="AM2">
-        <v>-1.640169259271452</v>
+        <v>-0.07415299124684954</v>
       </c>
       <c r="AN2">
-        <v>0.8820401676251696</v>
+        <v>0.4001715686241753</v>
       </c>
       <c r="AO2">
-        <v>0.03869900270029161</v>
+        <v>0.1733212989618051</v>
       </c>
       <c r="AP2">
-        <v>4.84069</v>
+        <v>9.077780000000001</v>
       </c>
       <c r="AQ2">
-        <v>4.842959146938227</v>
+        <v>9.075585146390887</v>
       </c>
       <c r="AR2">
-        <v>4.793063380117568</v>
+        <v>9.120899112849862</v>
       </c>
       <c r="AS2">
-        <v>4.84069</v>
+        <v>9.077780000000001</v>
       </c>
       <c r="AT2">
-        <v>4.905740000000001</v>
+        <v>9.030520000000001</v>
       </c>
       <c r="AW2">
-        <v>0.0004687651839359669</v>
+        <v>-0.0002417830801267956</v>
       </c>
       <c r="AY2">
-        <v>0.0004687651839359669</v>
+        <v>0.0002417830801267956</v>
       </c>
       <c r="AZ2">
-        <v>0.4417141117092844</v>
+        <v>0.3940417787685856</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3582858882907156</v>
+        <v>0.4059582212314145</v>
       </c>
       <c r="BC2" t="s">
         <v>127</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.05222457394889583</v>
+        <v>0.09294066985104246</v>
       </c>
       <c r="BP2">
-        <v>0.009403030329300963</v>
+        <v>0.01485155853136989</v>
       </c>
       <c r="BQ2">
-        <v>0.02521125915406773</v>
+        <v>0.02298453678573368</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT2" t="s">
         <v>137</v>
@@ -1240,7 +1240,7 @@
         <v>139</v>
       </c>
       <c r="BW2" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1263,37 +1263,37 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.1227504124957605</v>
+        <v>0.8562544998741403</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R3" t="s">
         <v>101</v>
@@ -1302,37 +1302,37 @@
         <v>106</v>
       </c>
       <c r="T3">
-        <v>0.3969018922560495</v>
+        <v>0.9065486428219646</v>
       </c>
       <c r="U3">
-        <v>0.4535576362848359</v>
+        <v>0.8059623723914771</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="W3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9998071390784544</v>
+        <v>0.992061932486372</v>
       </c>
       <c r="Y3">
-        <v>0.1880285614085631</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>-96.85647803352097</v>
+        <v>-43.54122375681116</v>
       </c>
       <c r="AA3">
-        <v>-21.99999999999999</v>
+        <v>16</v>
       </c>
       <c r="AB3">
-        <v>-0.119382704170757</v>
+        <v>0.7248789188732947</v>
       </c>
       <c r="AC3">
-        <v>-0.992848311649306</v>
+        <v>-0.6888762972937039</v>
       </c>
       <c r="AD3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AE3" t="s">
         <v>113</v>
@@ -1344,58 +1344,67 @@
         <v>122</v>
       </c>
       <c r="AH3">
-        <v>-0.07090135440826592</v>
+        <v>0.3595623905380364</v>
       </c>
       <c r="AI3">
-        <v>0.5380106563305191</v>
+        <v>0.7051231573892797</v>
       </c>
       <c r="AJ3">
-        <v>-0.05377530696909347</v>
+        <v>0.8196469094764647</v>
       </c>
       <c r="AK3">
-        <v>-0.7820390644770328</v>
+        <v>-0.8636007334220179</v>
       </c>
       <c r="AL3">
-        <v>-0.4085404372394565</v>
+        <v>0.2949296292788891</v>
       </c>
       <c r="AM3">
-        <v>-0.2464802607138144</v>
+        <v>-2.642194266982881</v>
       </c>
       <c r="AN3">
-        <v>0.3924626088054131</v>
+        <v>0.3626478390434086</v>
       </c>
       <c r="AO3">
-        <v>0.2356157725325308</v>
+        <v>0.06374796428625953</v>
       </c>
       <c r="AP3">
-        <v>9.08291</v>
+        <v>4403.620000000001</v>
       </c>
       <c r="AQ3">
-        <v>9.084786785476714</v>
+        <v>4546.241513801897</v>
       </c>
       <c r="AR3">
-        <v>9.127532885296398</v>
+        <v>4686.496935671032</v>
       </c>
       <c r="AS3">
-        <v>9.08291</v>
+        <v>4403.620000000001</v>
       </c>
       <c r="AT3">
-        <v>9.04078</v>
+        <v>4431.510000000002</v>
+      </c>
+      <c r="AU3">
+        <v>4546.241513801897</v>
+      </c>
+      <c r="AV3">
+        <v>4264.800000000001</v>
       </c>
       <c r="AW3">
-        <v>0.0002066282146045821</v>
+        <v>0.03238733446616558</v>
+      </c>
+      <c r="AX3">
+        <v>1.027384482076767</v>
       </c>
       <c r="AY3">
-        <v>0.0002066282146045821</v>
+        <v>0.03238733446616558</v>
       </c>
       <c r="AZ3">
-        <v>0.4101395055063513</v>
+        <v>0.4718261878212905</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3898604944936488</v>
+        <v>0.3281738121787096</v>
       </c>
       <c r="BC3" t="s">
         <v>128</v>
@@ -1407,55 +1416,58 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="BG3">
+        <v>0.03152406429255913</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>15860.89900590702</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>11895.67425443026</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>2.701339864572843</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>118.9567425443026</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>0.001189567425443026</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="BO3">
-        <v>0.09725107472064448</v>
+        <v>290.4581654073233</v>
       </c>
       <c r="BP3">
-        <v>0.01746639280434566</v>
+        <v>21.71227834915223</v>
       </c>
       <c r="BQ3">
-        <v>0.03131129397347893</v>
+        <v>141.567579535281</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BU3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BW3" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1463,7 +1475,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1484,22 +1496,22 @@
         <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J4" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0.9012724993344023</v>
+        <v>2.899548383439985</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1508,49 +1520,49 @@
         <v>98</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T4">
-        <v>0.8396326438744856</v>
+        <v>0.9713649670067009</v>
       </c>
       <c r="U4">
-        <v>0.7775815498610414</v>
+        <v>0.9870345771689445</v>
       </c>
       <c r="V4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W4" t="s">
         <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9989874404700918</v>
+        <v>0.9996813680637163</v>
       </c>
       <c r="Y4">
-        <v>0.05544383545829693</v>
+        <v>1</v>
       </c>
       <c r="Z4">
-        <v>-56.01739052334261</v>
+        <v>19.48638135698798</v>
       </c>
       <c r="AA4">
-        <v>-11</v>
+        <v>19</v>
       </c>
       <c r="AB4">
-        <v>0.5589412466649271</v>
+        <v>0.9427208070692576</v>
       </c>
       <c r="AC4">
-        <v>-0.8292072616521501</v>
+        <v>0.3335827931993607</v>
       </c>
       <c r="AD4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF4" t="s">
         <v>117</v>
@@ -1559,67 +1571,67 @@
         <v>123</v>
       </c>
       <c r="AH4">
-        <v>0.2946668764127441</v>
+        <v>0.9424204261131263</v>
       </c>
       <c r="AI4">
-        <v>0.669243529618861</v>
+        <v>0.9770942979932045</v>
       </c>
       <c r="AJ4">
-        <v>0.8545968567970055</v>
+        <v>2.291777580912676</v>
       </c>
       <c r="AK4">
-        <v>-1.188568195147521</v>
+        <v>0.714733802331325</v>
       </c>
       <c r="AL4">
-        <v>0.3498533311468189</v>
+        <v>3.196126880711641</v>
       </c>
       <c r="AM4">
-        <v>-2.763163284504506</v>
+        <v>-4.219988204615172</v>
       </c>
       <c r="AN4">
-        <v>0.3955920105007742</v>
+        <v>2.835316583281092</v>
       </c>
       <c r="AO4">
-        <v>0.06115477091205695</v>
+        <v>0.03740281966582361</v>
       </c>
       <c r="AP4">
-        <v>4403.84</v>
+        <v>0.72218</v>
       </c>
       <c r="AQ4">
-        <v>4545.985323292545</v>
+        <v>0.7269174154977962</v>
       </c>
       <c r="AR4">
-        <v>4685.802938654239</v>
+        <v>0.7200813556084027</v>
       </c>
       <c r="AS4">
-        <v>4403.84</v>
+        <v>0.72218</v>
       </c>
       <c r="AT4">
-        <v>4431.950000000001</v>
+        <v>0.7360800000000001</v>
       </c>
       <c r="AU4">
-        <v>4545.985323292545</v>
+        <v>0.7269174154977962</v>
       </c>
       <c r="AV4">
-        <v>4265.02</v>
+        <v>0.7149712500000001</v>
       </c>
       <c r="AW4">
-        <v>0.03227758576436589</v>
+        <v>0.006559881882350882</v>
       </c>
       <c r="AX4">
-        <v>1.023954208993991</v>
+        <v>0.6571757236408817</v>
       </c>
       <c r="AY4">
-        <v>0.03227758576436589</v>
+        <v>0.006559881882350882</v>
       </c>
       <c r="AZ4">
-        <v>0.4713647355310885</v>
+        <v>0.3989453322405221</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3286352644689115</v>
+        <v>0.4010546677594779</v>
       </c>
       <c r="BC4" t="s">
         <v>129</v>
@@ -1631,46 +1643,46 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.03152248946374057</v>
+        <v>0.009981929712813883</v>
       </c>
       <c r="BH4">
-        <v>15861.69139893396</v>
+        <v>50090.51499913348</v>
       </c>
       <c r="BI4">
-        <v>11896.26854920047</v>
+        <v>50090.51499913348</v>
       </c>
       <c r="BJ4">
-        <v>2.701339864572843</v>
+        <v>69360.15259233637</v>
       </c>
       <c r="BK4">
-        <v>118.9626854920047</v>
+        <v>500.9051499913348</v>
       </c>
       <c r="BL4">
-        <v>0.001189626854920047</v>
+        <v>0.005009051499913348</v>
       </c>
       <c r="BM4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BN4">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>286.5752129019122</v>
+        <v>0.01525705132295244</v>
       </c>
       <c r="BP4">
-        <v>28.77532413890723</v>
+        <v>0.002518965772624566</v>
       </c>
       <c r="BQ4">
-        <v>162.9552252720018</v>
+        <v>0.004085416732090668</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT4" t="s">
         <v>138</v>
@@ -1682,7 +1694,7 @@
         <v>140</v>
       </c>
       <c r="BW4" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1690,7 +1702,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1702,7 +1714,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1711,22 +1723,22 @@
         <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.5257793442834557</v>
+        <v>0.4791918109621205</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" t="s">
         <v>95</v>
@@ -1738,46 +1750,46 @@
         <v>0.75</v>
       </c>
       <c r="R5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T5">
-        <v>0.8345605825612374</v>
+        <v>0.9926047311091624</v>
       </c>
       <c r="U5">
-        <v>0.775395298077429</v>
+        <v>0.8380318182616666</v>
       </c>
       <c r="V5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W5" t="s">
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9993721436994882</v>
+        <v>0.9654387570501746</v>
       </c>
       <c r="Y5">
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>58.98259758085585</v>
+        <v>12.08670299803667</v>
       </c>
       <c r="AA5">
-        <v>-44</v>
+        <v>-90</v>
       </c>
       <c r="AB5">
-        <v>0.5152983981553437</v>
+        <v>0.9778318579617756</v>
       </c>
       <c r="AC5">
-        <v>0.8570108289038925</v>
+        <v>0.2093916367838551</v>
       </c>
       <c r="AD5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF5" t="s">
         <v>118</v>
@@ -1786,67 +1798,67 @@
         <v>124</v>
       </c>
       <c r="AH5">
-        <v>0.2574874324047091</v>
+        <v>0.4720183867773398</v>
       </c>
       <c r="AI5">
-        <v>0.6404964866540324</v>
+        <v>0.7699726661680064</v>
       </c>
       <c r="AJ5">
-        <v>0.3106804279234047</v>
+        <v>0.2975742665917043</v>
       </c>
       <c r="AK5">
-        <v>0.6383908648513057</v>
+        <v>0.09727233782722064</v>
       </c>
       <c r="AL5">
-        <v>1.063794997024615</v>
+        <v>0.922849257509929</v>
       </c>
       <c r="AM5">
-        <v>0.1748740564399984</v>
+        <v>-0.3984701105700039</v>
       </c>
       <c r="AN5">
-        <v>1.032793010352023</v>
+        <v>0.8391839145740082</v>
       </c>
       <c r="AO5">
-        <v>0.09248855391594409</v>
+        <v>0.07520304125391587</v>
       </c>
       <c r="AP5">
-        <v>0.8115250000000001</v>
+        <v>0.80757</v>
       </c>
       <c r="AQ5">
-        <v>0.8197947911307546</v>
+        <v>0.8124564632507294</v>
       </c>
       <c r="AR5">
-        <v>0.834106457132913</v>
+        <v>0.8278054867905001</v>
       </c>
       <c r="AS5">
-        <v>0.8115250000000001</v>
+        <v>0.80757</v>
       </c>
       <c r="AT5">
-        <v>0.8096750000000001</v>
+        <v>0.8017650000000001</v>
       </c>
       <c r="AU5">
-        <v>0.8197947911307546</v>
+        <v>0.8124564632507294</v>
       </c>
       <c r="AV5">
-        <v>0.8022350000000001</v>
+        <v>0.7982800000000001</v>
       </c>
       <c r="AW5">
-        <v>0.01019043298820683</v>
+        <v>0.006050823149360909</v>
       </c>
       <c r="AX5">
-        <v>0.8901820377561465</v>
+        <v>0.5259917385069346</v>
       </c>
       <c r="AY5">
-        <v>0.01019043298820683</v>
+        <v>0.006050823149360909</v>
       </c>
       <c r="AZ5">
-        <v>0.3990671157153338</v>
+        <v>0.3659863706620946</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.4009328842846662</v>
+        <v>0.4340136293379054</v>
       </c>
       <c r="BC5" t="s">
         <v>130</v>
@@ -1861,43 +1873,43 @@
         <v>375</v>
       </c>
       <c r="BG5">
-        <v>0.01144758325375058</v>
+        <v>0.01150364674269715</v>
       </c>
       <c r="BH5">
-        <v>43677.34122712624</v>
+        <v>43464.47793326186</v>
       </c>
       <c r="BI5">
-        <v>32758.00592034468</v>
+        <v>32598.3584499464</v>
       </c>
       <c r="BJ5">
-        <v>40365.98493003256</v>
+        <v>40365.98493003257</v>
       </c>
       <c r="BK5">
-        <v>327.5800592034468</v>
+        <v>325.983584499464</v>
       </c>
       <c r="BL5">
-        <v>0.003275800592034468</v>
+        <v>0.00325983584499464</v>
       </c>
       <c r="BM5">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="BN5">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="BO5">
-        <v>0.01177170371041717</v>
+        <v>0.01347548081552756</v>
       </c>
       <c r="BP5">
-        <v>0.001403001178787998</v>
+        <v>0.001283260082589581</v>
       </c>
       <c r="BQ5">
-        <v>0.002605872439464153</v>
+        <v>0.001666836770422137</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT5" t="s">
         <v>138</v>
@@ -1909,7 +1921,7 @@
         <v>140</v>
       </c>
       <c r="BW5" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1917,7 +1929,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1938,22 +1950,22 @@
         <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0.05901926764080149</v>
       </c>
       <c r="L6">
-        <v>2.603017088231519</v>
+        <v>1.138358467706816</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
@@ -1962,118 +1974,118 @@
         <v>98</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.7647548169102004</v>
       </c>
       <c r="R6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T6">
-        <v>0.9902667861457664</v>
+        <v>0.9438699622389386</v>
       </c>
       <c r="U6">
-        <v>0.9955117299807449</v>
+        <v>0.8305876903728253</v>
       </c>
       <c r="V6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W6" t="s">
         <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9995667048606002</v>
+        <v>0.987973268876731</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>0.3009372436950627</v>
       </c>
       <c r="Z6">
-        <v>11.32491668756644</v>
+        <v>-29.35651878186547</v>
       </c>
       <c r="AA6">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="AB6">
-        <v>0.9805293531091277</v>
+        <v>0.8715861023674165</v>
       </c>
       <c r="AC6">
-        <v>0.1963725736741146</v>
+        <v>-0.4902424565049169</v>
       </c>
       <c r="AD6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AH6">
-        <v>0.9801044945063867</v>
+        <v>0.5601209829711771</v>
       </c>
       <c r="AI6">
-        <v>0.9884276915057459</v>
+        <v>0.8116297563197563</v>
       </c>
       <c r="AJ6">
-        <v>2.064471096028702</v>
+        <v>0.9074164174822598</v>
       </c>
       <c r="AK6">
-        <v>0.3423932881954153</v>
+        <v>-0.7624225353650035</v>
       </c>
       <c r="AL6">
-        <v>2.836125209226585</v>
+        <v>1.199043329782393</v>
       </c>
       <c r="AM6">
-        <v>-3.832640055995153</v>
+        <v>-1.070579516087418</v>
       </c>
       <c r="AN6">
-        <v>2.513968953375532</v>
+        <v>1.158870645631176</v>
       </c>
       <c r="AO6">
-        <v>0.0371964075213495</v>
+        <v>0.03882778157557992</v>
       </c>
       <c r="AP6">
-        <v>0.721345</v>
+        <v>1.35616</v>
       </c>
       <c r="AQ6">
-        <v>0.7256652517565074</v>
+        <v>1.359314705828964</v>
       </c>
       <c r="AR6">
-        <v>0.7193029858387769</v>
+        <v>1.362078697478407</v>
       </c>
       <c r="AS6">
-        <v>0.721345</v>
+        <v>1.35616</v>
       </c>
       <c r="AT6">
-        <v>0.73441</v>
+        <v>1.35853</v>
       </c>
       <c r="AU6">
-        <v>0.7256652517565074</v>
+        <v>1.359314705828964</v>
       </c>
       <c r="AV6">
-        <v>0.7141362500000001</v>
+        <v>1.344735</v>
       </c>
       <c r="AW6">
-        <v>0.005989161575262058</v>
+        <v>0.002326204746463576</v>
       </c>
       <c r="AX6">
-        <v>0.5993066421373263</v>
+        <v>0.2761230484870056</v>
       </c>
       <c r="AY6">
-        <v>0.005989161575262058</v>
+        <v>0.002326204746463576</v>
       </c>
       <c r="AZ6">
-        <v>0.4058875021929551</v>
+        <v>0.354695162555541</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3941124978070449</v>
+        <v>0.445304837444459</v>
       </c>
       <c r="BC6" t="s">
         <v>131</v>
@@ -2085,46 +2097,46 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>500</v>
+        <v>382.3774084551002</v>
       </c>
       <c r="BG6">
-        <v>0.009993484393736604</v>
+        <v>0.008424522180273727</v>
       </c>
       <c r="BH6">
-        <v>50032.59927171888</v>
+        <v>59350.54704595177</v>
       </c>
       <c r="BI6">
-        <v>50032.59927171888</v>
+        <v>45388.61673964708</v>
       </c>
       <c r="BJ6">
-        <v>69360.15259233637</v>
+        <v>33468.48214049012</v>
       </c>
       <c r="BK6">
-        <v>500.3259927171888</v>
+        <v>453.8861673964708</v>
       </c>
       <c r="BL6">
-        <v>0.005003259927171888</v>
+        <v>0.004538861673964708</v>
       </c>
       <c r="BM6">
-        <v>500</v>
+        <v>382.3774084551002</v>
       </c>
       <c r="BN6">
-        <v>0.005</v>
+        <v>0.003823774084551002</v>
       </c>
       <c r="BO6">
-        <v>0.01559726356532664</v>
+        <v>0.0146624186181922</v>
       </c>
       <c r="BP6">
-        <v>0.002358064579542581</v>
+        <v>0.002308587013720335</v>
       </c>
       <c r="BQ6">
-        <v>0.004339398325697697</v>
+        <v>0.002165880751733257</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT6" t="s">
         <v>138</v>
@@ -2136,7 +2148,7 @@
         <v>140</v>
       </c>
       <c r="BW6" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2144,7 +2156,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2156,82 +2168,82 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J7" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.5193430657141522</v>
       </c>
       <c r="L7">
-        <v>0.9145432411443594</v>
+        <v>1.082279446828884</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>0.6104927007143859</v>
       </c>
       <c r="R7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T7">
-        <v>0.720610870143059</v>
+        <v>0.9760507447377137</v>
       </c>
       <c r="U7">
-        <v>0.7238971039999447</v>
+        <v>0.9170497758265125</v>
       </c>
       <c r="V7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W7" t="s">
         <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9984888497422726</v>
+        <v>0.9997019233496741</v>
       </c>
       <c r="Y7">
-        <v>0.8360836497435948</v>
+        <v>0.395486038893807</v>
       </c>
       <c r="Z7">
-        <v>-59.38848286026088</v>
+        <v>19.48089570545192</v>
       </c>
       <c r="AA7">
-        <v>6.999999999999997</v>
+        <v>18</v>
       </c>
       <c r="AB7">
-        <v>0.5092144249490446</v>
+        <v>0.9427527408593379</v>
       </c>
       <c r="AC7">
-        <v>-0.8606396861775628</v>
+        <v>0.3334925330531495</v>
       </c>
       <c r="AD7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF7" t="s">
         <v>117</v>
@@ -2240,67 +2252,67 @@
         <v>123</v>
       </c>
       <c r="AH7">
-        <v>0.4667737071973243</v>
+        <v>0.6576030694336081</v>
       </c>
       <c r="AI7">
-        <v>0.812129388705314</v>
+        <v>0.8561915320118576</v>
       </c>
       <c r="AJ7">
-        <v>0.7685281417255759</v>
+        <v>0.879279519383606</v>
       </c>
       <c r="AK7">
-        <v>-1.355771977675915</v>
+        <v>0.2734570025611356</v>
       </c>
       <c r="AL7">
-        <v>0.7897851815310688</v>
+        <v>1.085511373077254</v>
       </c>
       <c r="AM7">
-        <v>-1.350891593156276</v>
+        <v>-1.886107645787611</v>
       </c>
       <c r="AN7">
-        <v>0.737424183407118</v>
+        <v>0.9265917411423564</v>
       </c>
       <c r="AO7">
-        <v>0.04881844091942383</v>
+        <v>0.03751447464727287</v>
       </c>
       <c r="AP7">
-        <v>1.3545</v>
+        <v>4.83697</v>
       </c>
       <c r="AQ7">
-        <v>1.3568298478857</v>
+        <v>4.832009361932613</v>
       </c>
       <c r="AR7">
-        <v>1.359500589092673</v>
+        <v>4.779376999579524</v>
       </c>
       <c r="AS7">
-        <v>1.3545</v>
+        <v>4.83697</v>
       </c>
       <c r="AT7">
-        <v>1.35521</v>
+        <v>4.8983</v>
       </c>
       <c r="AU7">
-        <v>1.3568298478857</v>
+        <v>4.829714545</v>
       </c>
       <c r="AV7">
-        <v>1.343075</v>
+        <v>4.87677</v>
       </c>
       <c r="AW7">
-        <v>0.001720079649833976</v>
+        <v>-0.001025567259542028</v>
       </c>
       <c r="AX7">
-        <v>0.2039254166914763</v>
+        <v>0.1822978643216078</v>
       </c>
       <c r="AY7">
-        <v>0.001720079649833976</v>
+        <v>0.001025567259542028</v>
       </c>
       <c r="AZ7">
-        <v>0.4106307659964421</v>
+        <v>0.4542825010836617</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3893692340035579</v>
+        <v>0.3457174989163383</v>
       </c>
       <c r="BC7" t="s">
         <v>132</v>
@@ -2312,58 +2324,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>375</v>
+        <v>305.246350357193</v>
       </c>
       <c r="BG7">
-        <v>0.008434846806939844</v>
+        <v>0.008228291678468143</v>
       </c>
       <c r="BH7">
-        <v>59277.89934354476</v>
+        <v>60765.95477386926</v>
       </c>
       <c r="BI7">
-        <v>44458.42450765857</v>
+        <v>37097.17184138767</v>
       </c>
       <c r="BJ7">
-        <v>32822.75711159732</v>
+        <v>7669.506290381721</v>
       </c>
       <c r="BK7">
-        <v>444.5842450765857</v>
+        <v>370.9717184138767</v>
       </c>
       <c r="BL7">
-        <v>0.004445842450765857</v>
+        <v>0.003709717184138767</v>
       </c>
       <c r="BM7">
-        <v>375</v>
+        <v>305.2463503571929</v>
       </c>
       <c r="BN7">
-        <v>0.00375</v>
+        <v>0.003052463503571929</v>
       </c>
       <c r="BO7">
-        <v>0.0137472192395769</v>
+        <v>0.04829928148651322</v>
       </c>
       <c r="BP7">
-        <v>0.001727049226814625</v>
+        <v>0.007210858228480506</v>
       </c>
       <c r="BQ7">
-        <v>0.003648729307490551</v>
+        <v>0.02543622309844493</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT7" t="s">
         <v>138</v>
       </c>
       <c r="BU7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV7" t="s">
         <v>140</v>
       </c>
       <c r="BW7" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2371,7 +2383,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2383,7 +2395,7 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
         <v>92</v>
@@ -2392,22 +2404,22 @@
         <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J8" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K8">
-        <v>0.1096653187544404</v>
+        <v>0.6416158443203563</v>
       </c>
       <c r="L8">
-        <v>1.230944690076117</v>
+        <v>1.592148382521257</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O8" t="s">
         <v>96</v>
@@ -2416,118 +2428,118 @@
         <v>99</v>
       </c>
       <c r="Q8">
-        <v>0.9177510109341698</v>
+        <v>0.5187881167597328</v>
       </c>
       <c r="R8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T8">
-        <v>0.9392227807266568</v>
+        <v>0.9999063779159618</v>
       </c>
       <c r="U8">
-        <v>0.8381969984093558</v>
+        <v>0.944930317589195</v>
       </c>
       <c r="V8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W8" t="s">
         <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9963877970767767</v>
+        <v>0.9949202835158347</v>
       </c>
       <c r="Y8">
-        <v>0.2813168943633795</v>
+        <v>0.3940351668400586</v>
       </c>
       <c r="Z8">
-        <v>-30.92133310190683</v>
+        <v>-1.230986268728187</v>
       </c>
       <c r="AA8">
-        <v>22.00000000000001</v>
+        <v>58.00000000000001</v>
       </c>
       <c r="AB8">
-        <v>0.857873637963354</v>
+        <v>0.9997692113478265</v>
       </c>
       <c r="AC8">
-        <v>-0.5138607022214484</v>
+        <v>-0.02148311059751658</v>
       </c>
       <c r="AD8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH8">
-        <v>0.5476187116263899</v>
+        <v>0.6933168851053944</v>
       </c>
       <c r="AI8">
-        <v>0.8059770240761885</v>
+        <v>0.8711177658960196</v>
       </c>
       <c r="AJ8">
-        <v>1.073903918500121</v>
+        <v>1.32061768692522</v>
       </c>
       <c r="AK8">
-        <v>-0.7376161852156446</v>
+        <v>-0.2145555625788086</v>
       </c>
       <c r="AL8">
-        <v>0.8950066191053321</v>
+        <v>1.453872140759293</v>
       </c>
       <c r="AM8">
-        <v>-2.700938541313292</v>
+        <v>-2.480284097118669</v>
       </c>
       <c r="AN8">
-        <v>0.7179606737755675</v>
+        <v>1.29164197434492</v>
       </c>
       <c r="AO8">
-        <v>0.04256116774910201</v>
+        <v>0.03894753404588104</v>
       </c>
       <c r="AP8">
-        <v>1.161235</v>
+        <v>1.1649</v>
       </c>
       <c r="AQ8">
-        <v>1.158242911673746</v>
+        <v>1.163508651696742</v>
       </c>
       <c r="AR8">
-        <v>1.149876771886211</v>
+        <v>1.150240671751585</v>
       </c>
       <c r="AS8">
-        <v>1.161235</v>
+        <v>1.1649</v>
       </c>
       <c r="AT8">
-        <v>1.165455</v>
+        <v>1.172785</v>
       </c>
       <c r="AU8">
-        <v>1.158242911673746</v>
+        <v>1.16315265</v>
       </c>
       <c r="AV8">
-        <v>1.17105875</v>
+        <v>1.17472375</v>
       </c>
       <c r="AW8">
-        <v>-0.002576643251584902</v>
+        <v>-0.001194392912059728</v>
       </c>
       <c r="AX8">
-        <v>0.304577002290794</v>
+        <v>0.1778699580099246</v>
       </c>
       <c r="AY8">
-        <v>0.002576643251584902</v>
+        <v>0.001194392912059728</v>
       </c>
       <c r="AZ8">
-        <v>0.4087812991143387</v>
+        <v>0.3415204134015237</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3912187008856614</v>
+        <v>0.4584795865984763</v>
       </c>
       <c r="BC8" t="s">
         <v>133</v>
@@ -2539,46 +2551,46 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>458.8755054670849</v>
+        <v>259.3940583798664</v>
       </c>
       <c r="BG8">
-        <v>0.008459743290548442</v>
+        <v>0.008433127307065</v>
       </c>
       <c r="BH8">
-        <v>59103.44827586195</v>
+        <v>59289.98600330819</v>
       </c>
       <c r="BI8">
-        <v>54242.24940486772</v>
+        <v>30758.94018136718</v>
       </c>
       <c r="BJ8">
-        <v>46710.82890617981</v>
+        <v>26404.79026643246</v>
       </c>
       <c r="BK8">
-        <v>542.4224940486772</v>
+        <v>307.5894018136718</v>
       </c>
       <c r="BL8">
-        <v>0.005424224940486772</v>
+        <v>0.003075894018136718</v>
       </c>
       <c r="BM8">
-        <v>458.8755054670849</v>
+        <v>259.3940583798664</v>
       </c>
       <c r="BN8">
-        <v>0.004588755054670849</v>
+        <v>0.002593940583798664</v>
       </c>
       <c r="BO8">
-        <v>0.01709971436505893</v>
+        <v>0.01787470460156478</v>
       </c>
       <c r="BP8">
-        <v>0.001524268786529646</v>
+        <v>0.002756739006467116</v>
       </c>
       <c r="BQ8">
-        <v>0.003553375048062908</v>
+        <v>0.00217152045102649</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT8" t="s">
         <v>138</v>
@@ -2590,7 +2602,7 @@
         <v>140</v>
       </c>
       <c r="BW8" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2598,7 +2610,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2610,7 +2622,7 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
         <v>92</v>
@@ -2619,22 +2631,22 @@
         <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K9">
-        <v>0.9038475664035587</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>3.53105594817804</v>
+        <v>4.165795617825229</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
@@ -2643,49 +2655,49 @@
         <v>98</v>
       </c>
       <c r="Q9">
-        <v>0.9759618916008896</v>
+        <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T9">
-        <v>-0.9917129125256611</v>
+        <v>-0.9851604609161748</v>
       </c>
       <c r="U9">
-        <v>0.9817957314688525</v>
+        <v>0.993286050618328</v>
       </c>
       <c r="V9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W9" t="s">
         <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9997911434870851</v>
+        <v>0.999855372824197</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-169.6354953647062</v>
+        <v>-166.0054598837859</v>
       </c>
       <c r="AA9">
-        <v>13.00000000000001</v>
+        <v>11</v>
       </c>
       <c r="AB9">
-        <v>-0.9836831156550757</v>
+        <v>-0.9703187753212777</v>
       </c>
       <c r="AC9">
-        <v>-0.1799097773194191</v>
+        <v>-0.2418294321603881</v>
       </c>
       <c r="AD9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AF9" t="s">
         <v>119</v>
@@ -2694,67 +2706,67 @@
         <v>125</v>
       </c>
       <c r="AH9">
-        <v>-0.9834776670297267</v>
+        <v>-0.9701784408571744</v>
       </c>
       <c r="AI9">
-        <v>0.9893743134434058</v>
+        <v>0.9852935984492057</v>
       </c>
       <c r="AJ9">
-        <v>-2.659346103125017</v>
+        <v>-3.131355127430962</v>
       </c>
       <c r="AK9">
-        <v>-0.4214259324925717</v>
+        <v>-0.7145870463445099</v>
       </c>
       <c r="AL9">
-        <v>-4.492511969630058</v>
+        <v>-5.327837454877005</v>
       </c>
       <c r="AM9">
-        <v>3.605115645282452</v>
+        <v>4.218171759738232</v>
       </c>
       <c r="AN9">
-        <v>4.162264000732653</v>
+        <v>4.934981558661325</v>
       </c>
       <c r="AO9">
-        <v>0.03771680982397817</v>
+        <v>0.03834276423764264</v>
       </c>
       <c r="AP9">
-        <v>6.708855</v>
+        <v>6.704045</v>
       </c>
       <c r="AQ9">
-        <v>6.680778965123105</v>
+        <v>6.672222987770875</v>
       </c>
       <c r="AR9">
-        <v>6.672611602970512</v>
+        <v>6.663193384290818</v>
       </c>
       <c r="AS9">
-        <v>6.708855</v>
+        <v>6.704045</v>
       </c>
       <c r="AT9">
-        <v>6.67488</v>
+        <v>6.66526</v>
       </c>
       <c r="AU9">
-        <v>6.680778965123105</v>
+        <v>6.672222987770875</v>
       </c>
       <c r="AV9">
-        <v>6.732361249999999</v>
+        <v>6.727551249999999</v>
       </c>
       <c r="AW9">
-        <v>-0.004184921998894699</v>
+        <v>-0.004746688339521183</v>
       </c>
       <c r="AX9">
-        <v>1.194407226882006</v>
+        <v>1.353768135245979</v>
       </c>
       <c r="AY9">
-        <v>0.004184921998894699</v>
+        <v>0.004746688339521183</v>
       </c>
       <c r="AZ9">
-        <v>0.3950079572699075</v>
+        <v>0.3842089390873399</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.4049920427300925</v>
+        <v>0.4157910609126602</v>
       </c>
       <c r="BC9" t="s">
         <v>134</v>
@@ -2766,46 +2778,46 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>487.9809458004448</v>
+        <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.0035037648004018</v>
+        <v>0.003506278672055396</v>
       </c>
       <c r="BH9">
-        <v>142703.6426482342</v>
+        <v>142601.3294336636</v>
       </c>
       <c r="BI9">
-        <v>139273.317017308</v>
+        <v>142601.3294336636</v>
       </c>
       <c r="BJ9">
-        <v>20759.62545282437</v>
+        <v>21270.9385801652</v>
       </c>
       <c r="BK9">
-        <v>1392.73317017308</v>
+        <v>1426.013294336636</v>
       </c>
       <c r="BL9">
-        <v>0.0139273317017308</v>
+        <v>0.01426013294336636</v>
       </c>
       <c r="BM9">
-        <v>487.9809458004449</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN9">
-        <v>0.004879809458004449</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO9">
-        <v>0.0521618205979701</v>
+        <v>0.05264860236982584</v>
       </c>
       <c r="BP9">
-        <v>0.01009645267807642</v>
+        <v>0.01052204141888442</v>
       </c>
       <c r="BQ9">
-        <v>0.01447502051532265</v>
+        <v>0.0129990162955787</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT9" t="s">
         <v>138</v>
@@ -2817,7 +2829,7 @@
         <v>140</v>
       </c>
       <c r="BW9" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2825,7 +2837,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2849,67 +2861,67 @@
         <v>94</v>
       </c>
       <c r="J10" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K10">
-        <v>0.6713171198624325</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2.202363507106859</v>
+        <v>0.003428391748841053</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N10">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q10">
-        <v>0.9178292799656081</v>
+        <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="S10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T10">
-        <v>-0.7474814155486789</v>
+        <v>0.6218300357302415</v>
       </c>
       <c r="U10">
-        <v>0.8370417231215145</v>
+        <v>0.6289619180383681</v>
       </c>
       <c r="V10" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="X10">
-        <v>0.9999100725809763</v>
+        <v>0.9965536078390376</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>-121.4609328829015</v>
+        <v>-89.57386343343255</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>-58.99999999999999</v>
       </c>
       <c r="AB10">
-        <v>-0.5219170707563664</v>
+        <v>0.007437417581023465</v>
       </c>
       <c r="AC10">
-        <v>-0.8529962316757876</v>
+        <v>-0.9999723420273811</v>
       </c>
       <c r="AD10" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="AE10" t="s">
         <v>114</v>
@@ -2921,67 +2933,67 @@
         <v>126</v>
       </c>
       <c r="AH10">
-        <v>-0.5218701361012489</v>
+        <v>0.003705892661687211</v>
       </c>
       <c r="AI10">
-        <v>0.8464482310779792</v>
+        <v>0.4715908125182166</v>
       </c>
       <c r="AJ10">
-        <v>-1.571460909393736</v>
+        <v>0.1311248043795806</v>
       </c>
       <c r="AK10">
-        <v>-2.4989291304811</v>
+        <v>-0.66664186787868</v>
       </c>
       <c r="AL10">
-        <v>-3.155973934756926</v>
+        <v>-0.5699903874016419</v>
       </c>
       <c r="AM10">
-        <v>0.7191873413693028</v>
+        <v>-1.180169988254712</v>
       </c>
       <c r="AN10">
-        <v>3.025631969106124</v>
+        <v>0.6360865082059438</v>
       </c>
       <c r="AO10">
-        <v>0.06730277034848185</v>
+        <v>0.1962278366650238</v>
       </c>
       <c r="AP10">
-        <v>154.24</v>
+        <v>7.7943</v>
       </c>
       <c r="AQ10">
-        <v>153.1751170512499</v>
+        <v>7.718319538964758</v>
       </c>
       <c r="AR10">
-        <v>156.2356832636131</v>
+        <v>7.608305224251734</v>
       </c>
       <c r="AS10">
-        <v>154.24</v>
+        <v>7.7943</v>
       </c>
       <c r="AT10">
-        <v>149.164</v>
+        <v>7.786099999999999</v>
       </c>
       <c r="AU10">
-        <v>153.1751170512499</v>
+        <v>7.718319538964758</v>
       </c>
       <c r="AV10">
-        <v>155.4035</v>
+        <v>7.844953640690161</v>
       </c>
       <c r="AW10">
-        <v>-0.006904064761087425</v>
+        <v>-0.009748208438890148</v>
       </c>
       <c r="AX10">
-        <v>0.9152410388913729</v>
+        <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.006904064761087425</v>
+        <v>0.009748208438890148</v>
       </c>
       <c r="AZ10">
-        <v>0.4236497789239482</v>
+        <v>0.3904527607353936</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3763502210760518</v>
+        <v>0.4095472392646064</v>
       </c>
       <c r="BC10" t="s">
         <v>135</v>
@@ -2993,46 +3005,46 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>458.9146399828041</v>
+        <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.007543438796680584</v>
+        <v>0.006498805625926765</v>
       </c>
       <c r="BH10">
-        <v>66282.76751181703</v>
+        <v>76937.21412520278</v>
       </c>
       <c r="BI10">
-        <v>60836.26477949883</v>
+        <v>76937.21412520278</v>
       </c>
       <c r="BJ10">
-        <v>394.425990530983</v>
+        <v>9870.9587936316</v>
       </c>
       <c r="BK10">
-        <v>608.3626477949883</v>
+        <v>769.3721412520277</v>
       </c>
       <c r="BL10">
-        <v>0.006083626477949884</v>
+        <v>0.007693721412520277</v>
       </c>
       <c r="BM10">
-        <v>458.914639982804</v>
+        <v>500</v>
       </c>
       <c r="BN10">
-        <v>0.00458914639982804</v>
+        <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>6.646021895373139</v>
+        <v>0.1113991296207739</v>
       </c>
       <c r="BP10">
-        <v>2.375825713141223</v>
+        <v>0.002883571181683295</v>
       </c>
       <c r="BQ10">
-        <v>3.360918353661905</v>
+        <v>0.006699925802214547</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT10" t="s">
         <v>138</v>
@@ -3044,7 +3056,7 @@
         <v>140</v>
       </c>
       <c r="BW10" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3052,7 +3064,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3064,7 +3076,7 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
         <v>92</v>
@@ -3076,139 +3088,139 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0.01657963019459711</v>
+        <v>2.673427082224345</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T11">
-        <v>0.6496908965436862</v>
+        <v>-0.7516003784162759</v>
       </c>
       <c r="U11">
-        <v>0.6422283636159762</v>
+        <v>0.8882102736206549</v>
       </c>
       <c r="V11" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W11" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="X11">
-        <v>0.9994698406852699</v>
+        <v>0.9999604133333229</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <v>-85.2836487829335</v>
+        <v>-120.2113352789085</v>
       </c>
       <c r="AA11">
-        <v>-44</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AB11">
-        <v>0.0822229282328244</v>
+        <v>-0.5031909231302459</v>
       </c>
       <c r="AC11">
-        <v>-0.9966139624111333</v>
+        <v>-0.8641752686112528</v>
       </c>
       <c r="AD11" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AH11">
-        <v>0.04108966849076869</v>
+        <v>-0.503171003478897</v>
       </c>
       <c r="AI11">
-        <v>0.4967065775528007</v>
+        <v>0.8410872634518578</v>
       </c>
       <c r="AJ11">
-        <v>0.1601042929883315</v>
+        <v>-1.918066642025004</v>
       </c>
       <c r="AK11">
-        <v>-0.7825234523324572</v>
+        <v>-3.231606556425515</v>
       </c>
       <c r="AL11">
-        <v>-0.5227757194932624</v>
+        <v>-3.797562043692175</v>
       </c>
       <c r="AM11">
-        <v>-1.26713315497497</v>
+        <v>1.316207346677813</v>
       </c>
       <c r="AN11">
-        <v>0.6065858699962972</v>
+        <v>3.592251439094361</v>
       </c>
       <c r="AO11">
-        <v>0.1851649677126074</v>
+        <v>0.06570772102586056</v>
       </c>
       <c r="AP11">
-        <v>7.7968</v>
+        <v>153.278</v>
       </c>
       <c r="AQ11">
-        <v>7.715657824812026</v>
+        <v>151.4684720347847</v>
       </c>
       <c r="AR11">
-        <v>7.6071170105688</v>
+        <v>154.4086474509068</v>
       </c>
       <c r="AS11">
-        <v>7.7968</v>
+        <v>153.278</v>
       </c>
       <c r="AT11">
-        <v>7.7911</v>
+        <v>147.24</v>
       </c>
       <c r="AU11">
-        <v>7.715657824812026</v>
+        <v>151.4684720347847</v>
       </c>
       <c r="AV11">
-        <v>7.850894783458649</v>
+        <v>154.4843519768102</v>
       </c>
       <c r="AW11">
-        <v>-0.01040711255745616</v>
+        <v>-0.01180552959469262</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.01040711255745616</v>
+        <v>0.01180552959469262</v>
       </c>
       <c r="AZ11">
-        <v>0.4162459552632278</v>
+        <v>0.4214005578419917</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3837540447367722</v>
+        <v>0.3785994421580083</v>
       </c>
       <c r="BC11" t="s">
         <v>136</v>
@@ -3223,22 +3235,22 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.006938075038304106</v>
+        <v>0.007870353063128414</v>
       </c>
       <c r="BH11">
-        <v>72066.09862816019</v>
+        <v>63529.55146859107</v>
       </c>
       <c r="BI11">
-        <v>72066.09862816019</v>
+        <v>63529.55146859107</v>
       </c>
       <c r="BJ11">
-        <v>9243.035428401421</v>
+        <v>414.4727323463973</v>
       </c>
       <c r="BK11">
-        <v>720.6609862816019</v>
+        <v>635.2955146859108</v>
       </c>
       <c r="BL11">
-        <v>0.007206609862816019</v>
+        <v>0.006352955146859108</v>
       </c>
       <c r="BM11">
         <v>500</v>
@@ -3247,19 +3259,19 @@
         <v>0.005</v>
       </c>
       <c r="BO11">
-        <v>0.1207978876027291</v>
+        <v>7.223708712032332</v>
       </c>
       <c r="BP11">
-        <v>0.00653130801811761</v>
+        <v>2.655782117189557</v>
       </c>
       <c r="BQ11">
-        <v>0.01931623541681202</v>
+        <v>3.5920308156903</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04655632280787573</v>
+        <v>0.04908973714933696</v>
       </c>
       <c r="BT11" t="s">
         <v>138</v>
@@ -3271,7 +3283,7 @@
         <v>140</v>
       </c>
       <c r="BW11" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -241,51 +241,51 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
     <t>XAUUSD</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -295,12 +295,12 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
@@ -316,30 +316,30 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>UP_ACCELERATING</t>
-  </si>
-  <si>
     <t>UP_STEADY</t>
   </si>
   <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
+    <t>多头加速</t>
+  </si>
+  <si>
     <t>空头加速</t>
   </si>
   <si>
     <t>多头减速</t>
   </si>
   <si>
-    <t>多头加速</t>
-  </si>
-  <si>
     <t>多头稳态</t>
   </si>
   <si>
@@ -352,24 +352,24 @@
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>上涨</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
-    <t>上涨</t>
-  </si>
-  <si>
     <t>转换</t>
   </si>
   <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
-    <t>UP_STEEPENING</t>
-  </si>
-  <si>
     <t>UP_SLOPE</t>
   </si>
   <si>
@@ -379,15 +379,15 @@
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
-    <t>上升陡坡形成</t>
-  </si>
-  <si>
     <t>上升坡延续</t>
   </si>
   <si>
@@ -397,34 +397,34 @@
     <t>地形转换区</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.09294,naive=0.01485,drift4=0.02298; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=290.5,naive=21.71,drift4=141.6; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01526,naive=0.002519,drift4=0.004085; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.01348,naive=0.001283,drift4=0.001667; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.01466,naive=0.002309,drift4=0.002166; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.0483,naive=0.007211,drift4=0.02544; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=0.01787,naive=0.002757,drift4=0.002172; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.05265,naive=0.01052,drift4=0.013; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.1114,naive=0.002884,drift4=0.0067; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=7.224,naive=2.656,drift4=3.592; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.04433,naive=0.007975,drift4=0.02399; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.09433,naive=0.0137,drift4=0.02229; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=272.5,naive=37.39,drift4=146.6; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.01099,naive=0.001182,drift4=0.001731; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01542,naive=0.001614,drift4=0.005485; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01176,naive=0.0006147,drift4=0.001564; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.01502,naive=0.00118,drift4=0.001702; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.04768,naive=0.00845,drift4=0.01425; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=6.598,naive=2.072,drift4=2.948; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.1075,naive=0.005741,drift4=0.007831; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1033,7 +1033,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1057,19 +1057,19 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.5692800216481988</v>
       </c>
       <c r="L2">
-        <v>0.1709770580259295</v>
+        <v>1.109282431255643</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
         <v>90</v>
@@ -1087,10 +1087,10 @@
         <v>105</v>
       </c>
       <c r="T2">
-        <v>-0.7294718844236066</v>
+        <v>0.9724499547242961</v>
       </c>
       <c r="U2">
-        <v>0.7281208447294604</v>
+        <v>0.9229624934160302</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1099,22 +1099,22 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9994339869553498</v>
+        <v>0.9998720421714683</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>0.4630903664045969</v>
       </c>
       <c r="Z2">
-        <v>-101.9725834939739</v>
+        <v>20.60150864564121</v>
       </c>
       <c r="AA2">
-        <v>-29</v>
+        <v>16</v>
       </c>
       <c r="AB2">
-        <v>-0.2074436152876978</v>
+        <v>0.9360502711305557</v>
       </c>
       <c r="AC2">
-        <v>-0.9782469762163181</v>
+        <v>0.3518662955106855</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1129,58 +1129,58 @@
         <v>121</v>
       </c>
       <c r="AH2">
-        <v>-0.1036630997477078</v>
+        <v>0.6846754462856411</v>
       </c>
       <c r="AI2">
-        <v>0.536036785176411</v>
+        <v>0.8678659499928586</v>
       </c>
       <c r="AJ2">
-        <v>-0.0919466019147635</v>
+        <v>0.9020457495733645</v>
       </c>
       <c r="AK2">
-        <v>-0.6900769913542941</v>
+        <v>0.3040788133693674</v>
       </c>
       <c r="AL2">
-        <v>-0.4284720386196494</v>
+        <v>1.110409765564364</v>
       </c>
       <c r="AM2">
-        <v>-0.07415299124684954</v>
+        <v>-1.973152759960435</v>
       </c>
       <c r="AN2">
-        <v>0.4001715686241753</v>
+        <v>0.9435296817973353</v>
       </c>
       <c r="AO2">
-        <v>0.1733212989618051</v>
+        <v>0.03681612924827607</v>
       </c>
       <c r="AP2">
-        <v>9.077780000000001</v>
+        <v>4.84001</v>
       </c>
       <c r="AQ2">
-        <v>9.075585146390887</v>
+        <v>4.844084477957162</v>
       </c>
       <c r="AR2">
-        <v>9.120899112849862</v>
+        <v>4.799039615517158</v>
       </c>
       <c r="AS2">
-        <v>9.077780000000001</v>
+        <v>4.84001</v>
       </c>
       <c r="AT2">
-        <v>9.030520000000001</v>
+        <v>4.904380000000001</v>
       </c>
       <c r="AW2">
-        <v>-0.0002417830801267956</v>
+        <v>0.0008418325493463818</v>
       </c>
       <c r="AY2">
-        <v>0.0002417830801267956</v>
+        <v>0.0008418325493463818</v>
       </c>
       <c r="AZ2">
-        <v>0.3940417787685856</v>
+        <v>0.4501741879493744</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.4059582212314145</v>
+        <v>0.3498258120506256</v>
       </c>
       <c r="BC2" t="s">
         <v>127</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.09294066985104246</v>
+        <v>0.04432829067544009</v>
       </c>
       <c r="BP2">
-        <v>0.01485155853136989</v>
+        <v>0.007974590056161444</v>
       </c>
       <c r="BQ2">
-        <v>0.02298453678573368</v>
+        <v>0.02398571596866162</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT2" t="s">
         <v>137</v>
@@ -1240,7 +1240,7 @@
         <v>139</v>
       </c>
       <c r="BW2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1263,37 +1263,37 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
         <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.8562544998741403</v>
+        <v>0.1899500130054068</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q3">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R3" t="s">
         <v>101</v>
@@ -1302,10 +1302,10 @@
         <v>106</v>
       </c>
       <c r="T3">
-        <v>0.9065486428219646</v>
+        <v>-0.8280617309978223</v>
       </c>
       <c r="U3">
-        <v>0.8059623723914771</v>
+        <v>0.7686373726648043</v>
       </c>
       <c r="V3" t="s">
         <v>94</v>
@@ -1314,22 +1314,22 @@
         <v>95</v>
       </c>
       <c r="X3">
-        <v>0.992061932486372</v>
+        <v>0.9840383748631368</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>-43.54122375681116</v>
+        <v>-119.4121077146081</v>
       </c>
       <c r="AA3">
-        <v>16</v>
+        <v>-77</v>
       </c>
       <c r="AB3">
-        <v>0.7248789188732947</v>
+        <v>-0.4910878471066095</v>
       </c>
       <c r="AC3">
-        <v>-0.6888762972937039</v>
+        <v>-0.8711100541402305</v>
       </c>
       <c r="AD3" t="s">
         <v>94</v>
@@ -1344,67 +1344,58 @@
         <v>122</v>
       </c>
       <c r="AH3">
-        <v>0.3595623905380364</v>
+        <v>-0.2416246434909123</v>
       </c>
       <c r="AI3">
-        <v>0.7051231573892797</v>
+        <v>0.6221468121514782</v>
       </c>
       <c r="AJ3">
-        <v>0.8196469094764647</v>
+        <v>-0.1118580393334388</v>
       </c>
       <c r="AK3">
-        <v>-0.8636007334220179</v>
+        <v>-0.4291765003638253</v>
       </c>
       <c r="AL3">
-        <v>0.2949296292788891</v>
+        <v>-0.3912646910892517</v>
       </c>
       <c r="AM3">
-        <v>-2.642194266982881</v>
+        <v>0.1062995051137328</v>
       </c>
       <c r="AN3">
-        <v>0.3626478390434086</v>
+        <v>0.3528146985862998</v>
       </c>
       <c r="AO3">
-        <v>0.06374796428625953</v>
+        <v>0.1306198212173499</v>
       </c>
       <c r="AP3">
-        <v>4403.620000000001</v>
+        <v>9.081810000000001</v>
       </c>
       <c r="AQ3">
-        <v>4546.241513801897</v>
+        <v>9.081111207477486</v>
       </c>
       <c r="AR3">
-        <v>4686.496935671032</v>
+        <v>9.124408026328425</v>
       </c>
       <c r="AS3">
-        <v>4403.620000000001</v>
+        <v>9.081810000000001</v>
       </c>
       <c r="AT3">
-        <v>4431.510000000002</v>
-      </c>
-      <c r="AU3">
-        <v>4546.241513801897</v>
-      </c>
-      <c r="AV3">
-        <v>4264.800000000001</v>
+        <v>9.038580000000001</v>
       </c>
       <c r="AW3">
-        <v>0.03238733446616558</v>
-      </c>
-      <c r="AX3">
-        <v>1.027384482076767</v>
+        <v>-7.6944190917343E-05</v>
       </c>
       <c r="AY3">
-        <v>0.03238733446616558</v>
+        <v>7.6944190917343E-05</v>
       </c>
       <c r="AZ3">
-        <v>0.4718261878212905</v>
+        <v>0.3948035266221882</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3281738121787096</v>
+        <v>0.4051964733778118</v>
       </c>
       <c r="BC3" t="s">
         <v>128</v>
@@ -1416,58 +1407,55 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>375</v>
-      </c>
-      <c r="BG3">
-        <v>0.03152406429255913</v>
+        <v>0</v>
       </c>
       <c r="BH3">
-        <v>15860.89900590702</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>11895.67425443026</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>2.701339864572843</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>118.9567425443026</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>0.001189567425443026</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>0.00375</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>290.4581654073233</v>
+        <v>0.09433473931780446</v>
       </c>
       <c r="BP3">
-        <v>21.71227834915223</v>
+        <v>0.01369619244868784</v>
       </c>
       <c r="BQ3">
-        <v>141.567579535281</v>
+        <v>0.02229287295341999</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW3" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1475,7 +1463,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1496,22 +1484,22 @@
         <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2.899548383439985</v>
+        <v>0.7303045623762349</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1520,7 +1508,7 @@
         <v>98</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="s">
         <v>102</v>
@@ -1529,40 +1517,40 @@
         <v>107</v>
       </c>
       <c r="T4">
-        <v>0.9713649670067009</v>
+        <v>0.8375578481369297</v>
       </c>
       <c r="U4">
-        <v>0.9870345771689445</v>
+        <v>0.7768735799681212</v>
       </c>
       <c r="V4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W4" t="s">
         <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9996813680637163</v>
+        <v>0.9998901932260111</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>19.48638135698798</v>
+        <v>-58.38276076350893</v>
       </c>
       <c r="AA4">
-        <v>19</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB4">
-        <v>0.9427208070692576</v>
+        <v>0.5242421510722166</v>
       </c>
       <c r="AC4">
-        <v>0.3335827931993607</v>
+        <v>-0.8515692379596478</v>
       </c>
       <c r="AD4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF4" t="s">
         <v>117</v>
@@ -1571,67 +1559,67 @@
         <v>123</v>
       </c>
       <c r="AH4">
-        <v>0.9424204261131263</v>
+        <v>0.2620922928664092</v>
       </c>
       <c r="AI4">
-        <v>0.9770942979932045</v>
+        <v>0.6461128338479821</v>
       </c>
       <c r="AJ4">
-        <v>2.291777580912676</v>
+        <v>0.7319605414246987</v>
       </c>
       <c r="AK4">
-        <v>0.714733802331325</v>
+        <v>-1.09376710170299</v>
       </c>
       <c r="AL4">
-        <v>3.196126880711641</v>
+        <v>0.1047188308951358</v>
       </c>
       <c r="AM4">
-        <v>-4.219988204615172</v>
+        <v>-2.629511894418323</v>
       </c>
       <c r="AN4">
-        <v>2.835316583281092</v>
+        <v>0.3324834843152654</v>
       </c>
       <c r="AO4">
-        <v>0.03740281966582361</v>
+        <v>0.07414252735191168</v>
       </c>
       <c r="AP4">
-        <v>0.72218</v>
+        <v>4371.049999999999</v>
       </c>
       <c r="AQ4">
-        <v>0.7269174154977962</v>
+        <v>4498.918522063601</v>
       </c>
       <c r="AR4">
-        <v>0.7200813556084027</v>
+        <v>4653.448959710856</v>
       </c>
       <c r="AS4">
-        <v>0.72218</v>
+        <v>4371.049999999999</v>
       </c>
       <c r="AT4">
-        <v>0.7360800000000001</v>
+        <v>4366.369999999999</v>
       </c>
       <c r="AU4">
-        <v>0.7269174154977962</v>
+        <v>4498.918522063601</v>
       </c>
       <c r="AV4">
-        <v>0.7149712500000001</v>
+        <v>4232.23</v>
       </c>
       <c r="AW4">
-        <v>0.006559881882350882</v>
+        <v>0.02925350249107232</v>
       </c>
       <c r="AX4">
-        <v>0.6571757236408817</v>
+        <v>0.9211102295317845</v>
       </c>
       <c r="AY4">
-        <v>0.006559881882350882</v>
+        <v>0.02925350249107232</v>
       </c>
       <c r="AZ4">
-        <v>0.3989453322405221</v>
+        <v>0.4584540859286959</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.4010546677594779</v>
+        <v>0.3415459140713041</v>
       </c>
       <c r="BC4" t="s">
         <v>129</v>
@@ -1643,46 +1631,46 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG4">
-        <v>0.009981929712813883</v>
+        <v>0.03175895951773585</v>
       </c>
       <c r="BH4">
-        <v>50090.51499913348</v>
+        <v>15743.58882005483</v>
       </c>
       <c r="BI4">
-        <v>50090.51499913348</v>
+        <v>11807.69161504112</v>
       </c>
       <c r="BJ4">
-        <v>69360.15259233637</v>
+        <v>2.701339864572842</v>
       </c>
       <c r="BK4">
-        <v>500.9051499913348</v>
+        <v>118.0769161504112</v>
       </c>
       <c r="BL4">
-        <v>0.005009051499913348</v>
+        <v>0.001180769161504112</v>
       </c>
       <c r="BM4">
-        <v>500</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN4">
-        <v>0.005</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO4">
-        <v>0.01525705132295244</v>
+        <v>272.516572414176</v>
       </c>
       <c r="BP4">
-        <v>0.002518965772624566</v>
+        <v>37.38565950804563</v>
       </c>
       <c r="BQ4">
-        <v>0.004085416732090668</v>
+        <v>146.6156434370814</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT4" t="s">
         <v>138</v>
@@ -1694,7 +1682,7 @@
         <v>140</v>
       </c>
       <c r="BW4" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1702,7 +1690,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1714,7 +1702,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1723,22 +1711,22 @@
         <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.4791918109621205</v>
+        <v>0.6005909781916019</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" t="s">
         <v>95</v>
@@ -1750,115 +1738,115 @@
         <v>0.75</v>
       </c>
       <c r="R5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T5">
-        <v>0.9926047311091624</v>
+        <v>0.9556874599152398</v>
       </c>
       <c r="U5">
-        <v>0.8380318182616666</v>
+        <v>0.8292741833208217</v>
       </c>
       <c r="V5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W5" t="s">
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9654387570501746</v>
+        <v>0.9968593054358549</v>
       </c>
       <c r="Y5">
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>12.08670299803667</v>
+        <v>29.54620453941579</v>
       </c>
       <c r="AA5">
-        <v>-90</v>
+        <v>-70</v>
       </c>
       <c r="AB5">
-        <v>0.9778318579617756</v>
+        <v>0.8699583121118509</v>
       </c>
       <c r="AC5">
-        <v>0.2093916367838551</v>
+        <v>0.4931252733205828</v>
       </c>
       <c r="AD5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="AG5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AH5">
-        <v>0.4720183867773398</v>
+        <v>0.4336130193849842</v>
       </c>
       <c r="AI5">
-        <v>0.7699726661680064</v>
+        <v>0.7493466694651054</v>
       </c>
       <c r="AJ5">
-        <v>0.2975742665917043</v>
+        <v>0.3751948373740336</v>
       </c>
       <c r="AK5">
-        <v>0.09727233782722064</v>
+        <v>0.2771824625604786</v>
       </c>
       <c r="AL5">
-        <v>0.922849257509929</v>
+        <v>1.126869207941201</v>
       </c>
       <c r="AM5">
-        <v>-0.3984701105700039</v>
+        <v>-0.06969369288327512</v>
       </c>
       <c r="AN5">
-        <v>0.8391839145740082</v>
+        <v>1.081140949300065</v>
       </c>
       <c r="AO5">
-        <v>0.07520304125391587</v>
+        <v>0.07027720713999359</v>
       </c>
       <c r="AP5">
-        <v>0.80757</v>
+        <v>0.81182</v>
       </c>
       <c r="AQ5">
-        <v>0.8124564632507294</v>
+        <v>0.8200380366663871</v>
       </c>
       <c r="AR5">
-        <v>0.8278054867905001</v>
+        <v>0.8353024049923961</v>
       </c>
       <c r="AS5">
-        <v>0.80757</v>
+        <v>0.81182</v>
       </c>
       <c r="AT5">
-        <v>0.8017650000000001</v>
+        <v>0.810265</v>
       </c>
       <c r="AU5">
-        <v>0.8124564632507294</v>
+        <v>0.8200380366663871</v>
       </c>
       <c r="AV5">
-        <v>0.7982800000000001</v>
+        <v>0.8025300000000001</v>
       </c>
       <c r="AW5">
-        <v>0.006050823149360909</v>
+        <v>0.010122978820905</v>
       </c>
       <c r="AX5">
-        <v>0.5259917385069346</v>
+        <v>0.8846110512795643</v>
       </c>
       <c r="AY5">
-        <v>0.006050823149360909</v>
+        <v>0.010122978820905</v>
       </c>
       <c r="AZ5">
-        <v>0.3659863706620946</v>
+        <v>0.3779160288081272</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.4340136293379054</v>
+        <v>0.4220839711918728</v>
       </c>
       <c r="BC5" t="s">
         <v>130</v>
@@ -1873,43 +1861,43 @@
         <v>375</v>
       </c>
       <c r="BG5">
-        <v>0.01150364674269715</v>
+        <v>0.01144342341898443</v>
       </c>
       <c r="BH5">
-        <v>43464.47793326186</v>
+        <v>43693.21851453205</v>
       </c>
       <c r="BI5">
-        <v>32598.3584499464</v>
+        <v>32769.91388589903</v>
       </c>
       <c r="BJ5">
-        <v>40365.98493003257</v>
+        <v>40365.98493003256</v>
       </c>
       <c r="BK5">
-        <v>325.983584499464</v>
+        <v>327.6991388589904</v>
       </c>
       <c r="BL5">
-        <v>0.00325983584499464</v>
+        <v>0.003276991388589904</v>
       </c>
       <c r="BM5">
-        <v>375</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN5">
-        <v>0.00375</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO5">
-        <v>0.01347548081552756</v>
+        <v>0.01098509312371254</v>
       </c>
       <c r="BP5">
-        <v>0.001283260082589581</v>
+        <v>0.001181758122724756</v>
       </c>
       <c r="BQ5">
-        <v>0.001666836770422137</v>
+        <v>0.001730638248537051</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT5" t="s">
         <v>138</v>
@@ -1921,7 +1909,7 @@
         <v>140</v>
       </c>
       <c r="BW5" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1929,7 +1917,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1950,16 +1938,16 @@
         <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K6">
-        <v>0.05901926764080149</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>1.138358467706816</v>
+        <v>2.80948747210962</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1974,118 +1962,118 @@
         <v>98</v>
       </c>
       <c r="Q6">
-        <v>0.7647548169102004</v>
+        <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T6">
-        <v>0.9438699622389386</v>
+        <v>0.995854994680618</v>
       </c>
       <c r="U6">
-        <v>0.8305876903728253</v>
+        <v>0.9981218429706541</v>
       </c>
       <c r="V6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W6" t="s">
         <v>95</v>
       </c>
       <c r="X6">
-        <v>0.987973268876731</v>
+        <v>0.9999483814575042</v>
       </c>
       <c r="Y6">
-        <v>0.3009372436950627</v>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>-29.35651878186547</v>
+        <v>7.382802814430751</v>
       </c>
       <c r="AA6">
-        <v>65</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AB6">
-        <v>0.8715861023674165</v>
+        <v>0.9917097753910579</v>
       </c>
       <c r="AC6">
-        <v>-0.4902424565049169</v>
+        <v>0.1284979431501433</v>
       </c>
       <c r="AD6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AH6">
-        <v>0.5601209829711771</v>
+        <v>0.9916585847778734</v>
       </c>
       <c r="AI6">
-        <v>0.8116297563197563</v>
+        <v>0.9924783265735199</v>
       </c>
       <c r="AJ6">
-        <v>0.9074164174822598</v>
+        <v>2.272900400454537</v>
       </c>
       <c r="AK6">
-        <v>-0.7624225353650035</v>
+        <v>0.2790768090568564</v>
       </c>
       <c r="AL6">
-        <v>1.199043329782393</v>
+        <v>2.881898475879362</v>
       </c>
       <c r="AM6">
-        <v>-1.070579516087418</v>
+        <v>-5.135591575188919</v>
       </c>
       <c r="AN6">
-        <v>1.158870645631176</v>
+        <v>2.443644714065337</v>
       </c>
       <c r="AO6">
-        <v>0.03882778157557992</v>
+        <v>0.0334435970261589</v>
       </c>
       <c r="AP6">
-        <v>1.35616</v>
+        <v>0.718595</v>
       </c>
       <c r="AQ6">
-        <v>1.359314705828964</v>
+        <v>0.7211831308897334</v>
       </c>
       <c r="AR6">
-        <v>1.362078697478407</v>
+        <v>0.7160472781406976</v>
       </c>
       <c r="AS6">
-        <v>1.35616</v>
+        <v>0.718595</v>
       </c>
       <c r="AT6">
-        <v>1.35853</v>
+        <v>0.7289099999999999</v>
       </c>
       <c r="AU6">
-        <v>1.359314705828964</v>
+        <v>0.7211831308897334</v>
       </c>
       <c r="AV6">
-        <v>1.344735</v>
+        <v>0.7113862500000001</v>
       </c>
       <c r="AW6">
-        <v>0.002326204746463576</v>
+        <v>0.003601654464244004</v>
       </c>
       <c r="AX6">
-        <v>0.2761230484870056</v>
+        <v>0.3590263068816986</v>
       </c>
       <c r="AY6">
-        <v>0.002326204746463576</v>
+        <v>0.003601654464244004</v>
       </c>
       <c r="AZ6">
-        <v>0.354695162555541</v>
+        <v>0.4403320830707722</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.445304837444459</v>
+        <v>0.3596679169292279</v>
       </c>
       <c r="BC6" t="s">
         <v>131</v>
@@ -2097,46 +2085,46 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>382.3774084551002</v>
+        <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.008424522180273727</v>
+        <v>0.01003172858146791</v>
       </c>
       <c r="BH6">
-        <v>59350.54704595177</v>
+        <v>49841.85885208996</v>
       </c>
       <c r="BI6">
-        <v>45388.61673964708</v>
+        <v>49841.85885208996</v>
       </c>
       <c r="BJ6">
-        <v>33468.48214049012</v>
+        <v>69360.15259233638</v>
       </c>
       <c r="BK6">
-        <v>453.8861673964708</v>
+        <v>498.4185885208996</v>
       </c>
       <c r="BL6">
-        <v>0.004538861673964708</v>
+        <v>0.004984185885208996</v>
       </c>
       <c r="BM6">
-        <v>382.3774084551002</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN6">
-        <v>0.003823774084551002</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO6">
-        <v>0.0146624186181922</v>
+        <v>0.01541890469811921</v>
       </c>
       <c r="BP6">
-        <v>0.002308587013720335</v>
+        <v>0.001614286703750476</v>
       </c>
       <c r="BQ6">
-        <v>0.002165880751733257</v>
+        <v>0.005484945190208731</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT6" t="s">
         <v>138</v>
@@ -2148,7 +2136,7 @@
         <v>140</v>
       </c>
       <c r="BW6" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2156,7 +2144,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2168,40 +2156,40 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K7">
-        <v>0.5193430657141522</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.082279446828884</v>
+        <v>1.016772576813987</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q7">
-        <v>0.6104927007143859</v>
+        <v>0.75</v>
       </c>
       <c r="R7" t="s">
         <v>102</v>
@@ -2210,40 +2198,40 @@
         <v>107</v>
       </c>
       <c r="T7">
-        <v>0.9760507447377137</v>
+        <v>0.9805254827859041</v>
       </c>
       <c r="U7">
-        <v>0.9170497758265125</v>
+        <v>0.8386678405219214</v>
       </c>
       <c r="V7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W7" t="s">
         <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9997019233496741</v>
+        <v>0.9897254930730585</v>
       </c>
       <c r="Y7">
-        <v>0.395486038893807</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>19.48089570545192</v>
+        <v>-19.51096534603836</v>
       </c>
       <c r="AA7">
-        <v>18</v>
+        <v>74.99999999999999</v>
       </c>
       <c r="AB7">
-        <v>0.9427527408593379</v>
+        <v>0.9425775894082042</v>
       </c>
       <c r="AC7">
-        <v>0.3334925330531495</v>
+        <v>-0.3339872571602375</v>
       </c>
       <c r="AD7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF7" t="s">
         <v>117</v>
@@ -2252,67 +2240,67 @@
         <v>123</v>
       </c>
       <c r="AH7">
-        <v>0.6576030694336081</v>
+        <v>0.4664465347183249</v>
       </c>
       <c r="AI7">
-        <v>0.8561915320118576</v>
+        <v>0.7739317707643107</v>
       </c>
       <c r="AJ7">
-        <v>0.879279519383606</v>
+        <v>0.8262128267408263</v>
       </c>
       <c r="AK7">
-        <v>0.2734570025611356</v>
+        <v>-0.5082568125725563</v>
       </c>
       <c r="AL7">
-        <v>1.085511373077254</v>
+        <v>1.011677001301629</v>
       </c>
       <c r="AM7">
-        <v>-1.886107645787611</v>
+        <v>-1.407178365885063</v>
       </c>
       <c r="AN7">
-        <v>0.9265917411423564</v>
+        <v>0.9269730964381281</v>
       </c>
       <c r="AO7">
-        <v>0.03751447464727287</v>
+        <v>0.03496952422480668</v>
       </c>
       <c r="AP7">
-        <v>4.83697</v>
+        <v>1.35248</v>
       </c>
       <c r="AQ7">
-        <v>4.832009361932613</v>
+        <v>1.353848398810026</v>
       </c>
       <c r="AR7">
-        <v>4.779376999579524</v>
+        <v>1.357137735475286</v>
       </c>
       <c r="AS7">
-        <v>4.83697</v>
+        <v>1.35248</v>
       </c>
       <c r="AT7">
-        <v>4.8983</v>
+        <v>1.35117</v>
       </c>
       <c r="AU7">
-        <v>4.829714545</v>
+        <v>1.35450872</v>
       </c>
       <c r="AV7">
-        <v>4.87677</v>
+        <v>1.341055</v>
       </c>
       <c r="AW7">
-        <v>-0.001025567259542028</v>
+        <v>0.001011770089040984</v>
       </c>
       <c r="AX7">
-        <v>0.1822978643216078</v>
+        <v>0.1775684901531726</v>
       </c>
       <c r="AY7">
-        <v>0.001025567259542028</v>
+        <v>0.001011770089040984</v>
       </c>
       <c r="AZ7">
-        <v>0.4542825010836617</v>
+        <v>0.4049105091928277</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3457174989163383</v>
+        <v>0.3950894908071723</v>
       </c>
       <c r="BC7" t="s">
         <v>132</v>
@@ -2324,58 +2312,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>305.246350357193</v>
+        <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.008228291678468143</v>
+        <v>0.008447444694191425</v>
       </c>
       <c r="BH7">
-        <v>60765.95477386926</v>
+        <v>59189.49671772419</v>
       </c>
       <c r="BI7">
-        <v>37097.17184138767</v>
+        <v>44392.12253829314</v>
       </c>
       <c r="BJ7">
-        <v>7669.506290381721</v>
+        <v>32822.75711159733</v>
       </c>
       <c r="BK7">
-        <v>370.9717184138767</v>
+        <v>443.9212253829314</v>
       </c>
       <c r="BL7">
-        <v>0.003709717184138767</v>
+        <v>0.004439212253829314</v>
       </c>
       <c r="BM7">
-        <v>305.2463503571929</v>
+        <v>375</v>
       </c>
       <c r="BN7">
-        <v>0.003052463503571929</v>
+        <v>0.00375</v>
       </c>
       <c r="BO7">
-        <v>0.04829928148651322</v>
+        <v>0.01175581516502146</v>
       </c>
       <c r="BP7">
-        <v>0.007210858228480506</v>
+        <v>0.0006147316938812383</v>
       </c>
       <c r="BQ7">
-        <v>0.02543622309844493</v>
+        <v>0.001563859085667526</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT7" t="s">
         <v>138</v>
       </c>
       <c r="BU7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV7" t="s">
         <v>140</v>
       </c>
       <c r="BW7" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2383,7 +2371,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2395,7 +2383,7 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
         <v>92</v>
@@ -2404,22 +2392,22 @@
         <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K8">
-        <v>0.6416158443203563</v>
+        <v>0.4266819783946858</v>
       </c>
       <c r="L8">
-        <v>1.592148382521257</v>
+        <v>1.450868759022682</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O8" t="s">
         <v>96</v>
@@ -2428,7 +2416,7 @@
         <v>99</v>
       </c>
       <c r="Q8">
-        <v>0.5187881167597328</v>
+        <v>0.6799885162039856</v>
       </c>
       <c r="R8" t="s">
         <v>103</v>
@@ -2437,40 +2425,40 @@
         <v>108</v>
       </c>
       <c r="T8">
-        <v>0.9999063779159618</v>
+        <v>0.9965186387595244</v>
       </c>
       <c r="U8">
-        <v>0.944930317589195</v>
+        <v>0.9119427220414751</v>
       </c>
       <c r="V8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W8" t="s">
         <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9949202835158347</v>
+        <v>0.9980281513619448</v>
       </c>
       <c r="Y8">
-        <v>0.3940351668400586</v>
+        <v>0.2329782802410662</v>
       </c>
       <c r="Z8">
-        <v>-1.230986268728187</v>
+        <v>-7.753214303499411</v>
       </c>
       <c r="AA8">
-        <v>58.00000000000001</v>
+        <v>40.99999999999999</v>
       </c>
       <c r="AB8">
-        <v>0.9997692113478265</v>
+        <v>0.990858330666288</v>
       </c>
       <c r="AC8">
-        <v>-0.02148311059751658</v>
+        <v>-0.1349065178159199</v>
       </c>
       <c r="AD8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF8" t="s">
         <v>118</v>
@@ -2479,67 +2467,67 @@
         <v>124</v>
       </c>
       <c r="AH8">
-        <v>0.6933168851053944</v>
+        <v>0.6096488898083851</v>
       </c>
       <c r="AI8">
-        <v>0.8711177658960196</v>
+        <v>0.837692027098163</v>
       </c>
       <c r="AJ8">
-        <v>1.32061768692522</v>
+        <v>1.225754760766346</v>
       </c>
       <c r="AK8">
-        <v>-0.2145555625788086</v>
+        <v>-0.3016279754365427</v>
       </c>
       <c r="AL8">
-        <v>1.453872140759293</v>
+        <v>1.236600414817661</v>
       </c>
       <c r="AM8">
-        <v>-2.480284097118669</v>
+        <v>-2.808461627930354</v>
       </c>
       <c r="AN8">
-        <v>1.29164197434492</v>
+        <v>1.03317886421508</v>
       </c>
       <c r="AO8">
-        <v>0.03894753404588104</v>
+        <v>0.03647320751078251</v>
       </c>
       <c r="AP8">
-        <v>1.1649</v>
+        <v>1.161515</v>
       </c>
       <c r="AQ8">
-        <v>1.163508651696742</v>
+        <v>1.159322422666424</v>
       </c>
       <c r="AR8">
-        <v>1.150240671751585</v>
+        <v>1.150352464187454</v>
       </c>
       <c r="AS8">
-        <v>1.1649</v>
+        <v>1.161515</v>
       </c>
       <c r="AT8">
-        <v>1.172785</v>
+        <v>1.166015</v>
       </c>
       <c r="AU8">
-        <v>1.16315265</v>
+        <v>1.159322422666424</v>
       </c>
       <c r="AV8">
-        <v>1.17472375</v>
+        <v>1.17133875</v>
       </c>
       <c r="AW8">
-        <v>-0.001194392912059728</v>
+        <v>-0.001887687488819369</v>
       </c>
       <c r="AX8">
-        <v>0.1778699580099246</v>
+        <v>0.2231914832498816</v>
       </c>
       <c r="AY8">
-        <v>0.001194392912059728</v>
+        <v>0.001887687488819369</v>
       </c>
       <c r="AZ8">
-        <v>0.3415204134015237</v>
+        <v>0.3698364940967112</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.4584795865984763</v>
+        <v>0.4301635059032888</v>
       </c>
       <c r="BC8" t="s">
         <v>133</v>
@@ -2551,46 +2539,46 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>259.3940583798664</v>
+        <v>339.9942581019928</v>
       </c>
       <c r="BG8">
-        <v>0.008433127307065</v>
+        <v>0.00845770394700027</v>
       </c>
       <c r="BH8">
-        <v>59289.98600330819</v>
+        <v>59117.69945285648</v>
       </c>
       <c r="BI8">
-        <v>30758.94018136718</v>
+        <v>40199.35673234105</v>
       </c>
       <c r="BJ8">
-        <v>26404.79026643246</v>
+        <v>34609.4167809637</v>
       </c>
       <c r="BK8">
-        <v>307.5894018136718</v>
+        <v>401.9935673234106</v>
       </c>
       <c r="BL8">
-        <v>0.003075894018136718</v>
+        <v>0.004019935673234106</v>
       </c>
       <c r="BM8">
-        <v>259.3940583798664</v>
+        <v>339.9942581019928</v>
       </c>
       <c r="BN8">
-        <v>0.002593940583798664</v>
+        <v>0.003399942581019928</v>
       </c>
       <c r="BO8">
-        <v>0.01787470460156478</v>
+        <v>0.01502311307480023</v>
       </c>
       <c r="BP8">
-        <v>0.002756739006467116</v>
+        <v>0.001180301067312868</v>
       </c>
       <c r="BQ8">
-        <v>0.00217152045102649</v>
+        <v>0.001702400516222229</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT8" t="s">
         <v>138</v>
@@ -2602,7 +2590,7 @@
         <v>140</v>
       </c>
       <c r="BW8" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2610,7 +2598,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2622,7 +2610,7 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
         <v>92</v>
@@ -2631,22 +2619,22 @@
         <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>4.165795617825229</v>
+        <v>4.168882434469204</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
@@ -2664,40 +2652,40 @@
         <v>109</v>
       </c>
       <c r="T9">
-        <v>-0.9851604609161748</v>
+        <v>-0.9897352629795897</v>
       </c>
       <c r="U9">
-        <v>0.993286050618328</v>
+        <v>0.9953623838234893</v>
       </c>
       <c r="V9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W9" t="s">
         <v>95</v>
       </c>
       <c r="X9">
-        <v>0.999855372824197</v>
+        <v>0.9999260619306957</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-166.0054598837859</v>
+        <v>-168.3699817462219</v>
       </c>
       <c r="AA9">
-        <v>11</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AB9">
-        <v>-0.9703187753212777</v>
+        <v>-0.9794697669482223</v>
       </c>
       <c r="AC9">
-        <v>-0.2418294321603881</v>
+        <v>-0.201591110008341</v>
       </c>
       <c r="AD9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF9" t="s">
         <v>119</v>
@@ -2706,67 +2694,67 @@
         <v>125</v>
       </c>
       <c r="AH9">
-        <v>-0.9701784408571744</v>
+        <v>-0.9793973468447121</v>
       </c>
       <c r="AI9">
-        <v>0.9852935984492057</v>
+        <v>0.988449476258463</v>
       </c>
       <c r="AJ9">
-        <v>-3.131355127430962</v>
+        <v>-3.166403133240801</v>
       </c>
       <c r="AK9">
-        <v>-0.7145870463445099</v>
+        <v>-0.6205442492079006</v>
       </c>
       <c r="AL9">
-        <v>-5.327837454877005</v>
+        <v>-5.201157229962569</v>
       </c>
       <c r="AM9">
-        <v>4.218171759738232</v>
+        <v>4.963366596708446</v>
       </c>
       <c r="AN9">
-        <v>4.934981558661325</v>
+        <v>4.741587371836053</v>
       </c>
       <c r="AO9">
-        <v>0.03834276423764264</v>
+        <v>0.0357705033449802</v>
       </c>
       <c r="AP9">
-        <v>6.704045</v>
+        <v>6.709215</v>
       </c>
       <c r="AQ9">
-        <v>6.672222987770875</v>
+        <v>6.679261014119083</v>
       </c>
       <c r="AR9">
-        <v>6.663193384290818</v>
+        <v>6.668034120346375</v>
       </c>
       <c r="AS9">
-        <v>6.704045</v>
+        <v>6.709215</v>
       </c>
       <c r="AT9">
-        <v>6.66526</v>
+        <v>6.675600000000001</v>
       </c>
       <c r="AU9">
-        <v>6.672222987770875</v>
+        <v>6.679261014119083</v>
       </c>
       <c r="AV9">
-        <v>6.727551249999999</v>
+        <v>6.73272125</v>
       </c>
       <c r="AW9">
-        <v>-0.004746688339521183</v>
+        <v>-0.004464603665394124</v>
       </c>
       <c r="AX9">
-        <v>1.353768135245979</v>
+        <v>1.274298787808252</v>
       </c>
       <c r="AY9">
-        <v>0.004746688339521183</v>
+        <v>0.004464603665394124</v>
       </c>
       <c r="AZ9">
-        <v>0.3842089390873399</v>
+        <v>0.4047098316520368</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.4157910609126602</v>
+        <v>0.3952901683479632</v>
       </c>
       <c r="BC9" t="s">
         <v>134</v>
@@ -2781,22 +2769,22 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.003506278672055396</v>
+        <v>0.00350357679698737</v>
       </c>
       <c r="BH9">
-        <v>142601.3294336636</v>
+        <v>142711.300186123</v>
       </c>
       <c r="BI9">
-        <v>142601.3294336636</v>
+        <v>142711.300186123</v>
       </c>
       <c r="BJ9">
         <v>21270.9385801652</v>
       </c>
       <c r="BK9">
-        <v>1426.013294336636</v>
+        <v>1427.11300186123</v>
       </c>
       <c r="BL9">
-        <v>0.01426013294336636</v>
+        <v>0.0142711300186123</v>
       </c>
       <c r="BM9">
         <v>499.9999999999999</v>
@@ -2805,19 +2793,19 @@
         <v>0.004999999999999999</v>
       </c>
       <c r="BO9">
-        <v>0.05264860236982584</v>
+        <v>0.0476808082991944</v>
       </c>
       <c r="BP9">
-        <v>0.01052204141888442</v>
+        <v>0.008450340028112065</v>
       </c>
       <c r="BQ9">
-        <v>0.0129990162955787</v>
+        <v>0.01425021812008477</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT9" t="s">
         <v>138</v>
@@ -2829,7 +2817,7 @@
         <v>140</v>
       </c>
       <c r="BW9" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2837,7 +2825,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2861,25 +2849,25 @@
         <v>94</v>
       </c>
       <c r="J10" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0.003428391748841053</v>
+        <v>2.770835826498998</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="O10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -2891,109 +2879,109 @@
         <v>106</v>
       </c>
       <c r="T10">
-        <v>0.6218300357302415</v>
+        <v>-0.8021105853176919</v>
       </c>
       <c r="U10">
-        <v>0.6289619180383681</v>
+        <v>0.9109192273751268</v>
       </c>
       <c r="V10" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="W10" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9965536078390376</v>
+        <v>0.9998778559286617</v>
       </c>
       <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>-127.1710804786239</v>
+      </c>
+      <c r="AA10">
         <v>0</v>
       </c>
-      <c r="Z10">
-        <v>-89.57386343343255</v>
-      </c>
-      <c r="AA10">
-        <v>-58.99999999999999</v>
-      </c>
       <c r="AB10">
-        <v>0.007437417581023465</v>
+        <v>-0.6041969966638925</v>
       </c>
       <c r="AC10">
-        <v>-0.9999723420273811</v>
+        <v>-0.7968349824288165</v>
       </c>
       <c r="AD10" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AE10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AG10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AH10">
-        <v>0.003705892661687211</v>
+        <v>-0.6041231975828296</v>
       </c>
       <c r="AI10">
-        <v>0.4715908125182166</v>
+        <v>0.8725029968446851</v>
       </c>
       <c r="AJ10">
-        <v>0.1311248043795806</v>
+        <v>-2.046261352372307</v>
       </c>
       <c r="AK10">
-        <v>-0.66664186787868</v>
+        <v>-2.698677149614167</v>
       </c>
       <c r="AL10">
-        <v>-0.5699903874016419</v>
+        <v>-3.704382662691871</v>
       </c>
       <c r="AM10">
-        <v>-1.180169988254712</v>
+        <v>2.745353844411959</v>
       </c>
       <c r="AN10">
-        <v>0.6360865082059438</v>
+        <v>3.36365172865137</v>
       </c>
       <c r="AO10">
-        <v>0.1962278366650238</v>
+        <v>0.05808901153009509</v>
       </c>
       <c r="AP10">
-        <v>7.7943</v>
+        <v>154.19</v>
       </c>
       <c r="AQ10">
-        <v>7.718319538964758</v>
+        <v>153.0075739955537</v>
       </c>
       <c r="AR10">
-        <v>7.608305224251734</v>
+        <v>156.0643862307935</v>
       </c>
       <c r="AS10">
-        <v>7.7943</v>
+        <v>154.19</v>
       </c>
       <c r="AT10">
-        <v>7.786099999999999</v>
+        <v>149.064</v>
       </c>
       <c r="AU10">
-        <v>7.718319538964758</v>
+        <v>153.0075739955537</v>
       </c>
       <c r="AV10">
-        <v>7.844953640690161</v>
+        <v>155.3535</v>
       </c>
       <c r="AW10">
-        <v>-0.009748208438890148</v>
+        <v>-0.007668629641651574</v>
       </c>
       <c r="AX10">
-        <v>1.5</v>
+        <v>1.016266441294579</v>
       </c>
       <c r="AY10">
-        <v>0.009748208438890148</v>
+        <v>0.007668629641651574</v>
       </c>
       <c r="AZ10">
-        <v>0.3904527607353936</v>
+        <v>0.4168875686767561</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.4095472392646064</v>
+        <v>0.3831124313232439</v>
       </c>
       <c r="BC10" t="s">
         <v>135</v>
@@ -3008,43 +2996,43 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.006498805625926765</v>
+        <v>0.007545884947143222</v>
       </c>
       <c r="BH10">
-        <v>76937.21412520278</v>
+        <v>66261.28061882177</v>
       </c>
       <c r="BI10">
-        <v>76937.21412520278</v>
+        <v>66261.28061882177</v>
       </c>
       <c r="BJ10">
-        <v>9870.9587936316</v>
+        <v>429.7378599054528</v>
       </c>
       <c r="BK10">
-        <v>769.3721412520277</v>
+        <v>662.6128061882176</v>
       </c>
       <c r="BL10">
-        <v>0.007693721412520277</v>
+        <v>0.006626128061882177</v>
       </c>
       <c r="BM10">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN10">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO10">
-        <v>0.1113991296207739</v>
+        <v>6.597824858704986</v>
       </c>
       <c r="BP10">
-        <v>0.002883571181683295</v>
+        <v>2.072476781230577</v>
       </c>
       <c r="BQ10">
-        <v>0.006699925802214547</v>
+        <v>2.947712057334392</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT10" t="s">
         <v>138</v>
@@ -3056,7 +3044,7 @@
         <v>140</v>
       </c>
       <c r="BW10" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3064,7 +3052,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3076,7 +3064,7 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
         <v>92</v>
@@ -3088,139 +3076,139 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2.673427082224345</v>
+        <v>0.01403701514849852</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T11">
-        <v>-0.7516003784162759</v>
+        <v>0.6038783655477967</v>
       </c>
       <c r="U11">
-        <v>0.8882102736206549</v>
+        <v>0.6069459207557859</v>
       </c>
       <c r="V11" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="X11">
-        <v>0.9999604133333229</v>
+        <v>0.9408026250371093</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>-120.2113352789085</v>
+        <v>-94.46303669474203</v>
       </c>
       <c r="AA11">
-        <v>6.000000000000009</v>
+        <v>-90</v>
       </c>
       <c r="AB11">
-        <v>-0.5031909231302459</v>
+        <v>-0.07781593679090455</v>
       </c>
       <c r="AC11">
-        <v>-0.8641752686112528</v>
+        <v>-0.9969677426985057</v>
       </c>
       <c r="AD11" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="AE11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="AH11">
-        <v>-0.503171003478897</v>
+        <v>-0.03660471880130239</v>
       </c>
       <c r="AI11">
-        <v>0.8410872634518578</v>
+        <v>0.4759844382618538</v>
       </c>
       <c r="AJ11">
-        <v>-1.918066642025004</v>
+        <v>0.1292815129190201</v>
       </c>
       <c r="AK11">
-        <v>-3.231606556425515</v>
+        <v>-0.3742686717291679</v>
       </c>
       <c r="AL11">
-        <v>-3.797562043692175</v>
+        <v>-0.4592823010889686</v>
       </c>
       <c r="AM11">
-        <v>1.316207346677813</v>
+        <v>-0.9123482222380772</v>
       </c>
       <c r="AN11">
-        <v>3.592251439094361</v>
+        <v>0.5084784036395883</v>
       </c>
       <c r="AO11">
-        <v>0.06570772102586056</v>
+        <v>0.1776084102560392</v>
       </c>
       <c r="AP11">
-        <v>153.278</v>
+        <v>7.8009</v>
       </c>
       <c r="AQ11">
-        <v>151.4684720347847</v>
+        <v>7.733237874175519</v>
       </c>
       <c r="AR11">
-        <v>154.4086474509068</v>
+        <v>7.614672511703978</v>
       </c>
       <c r="AS11">
-        <v>153.278</v>
+        <v>7.8009</v>
       </c>
       <c r="AT11">
-        <v>147.24</v>
+        <v>7.799300000000001</v>
       </c>
       <c r="AU11">
-        <v>151.4684720347847</v>
+        <v>7.733237874175519</v>
       </c>
       <c r="AV11">
-        <v>154.4843519768102</v>
+        <v>7.850575000000001</v>
       </c>
       <c r="AW11">
-        <v>-0.01180552959469262</v>
+        <v>-0.008673630712415469</v>
       </c>
       <c r="AX11">
-        <v>1.5</v>
+        <v>1.362096141408778</v>
       </c>
       <c r="AY11">
-        <v>0.01180552959469262</v>
+        <v>0.008673630712415469</v>
       </c>
       <c r="AZ11">
-        <v>0.4214005578419917</v>
+        <v>0.3595462757855906</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3785994421580083</v>
+        <v>0.4404537242144094</v>
       </c>
       <c r="BC11" t="s">
         <v>136</v>
@@ -3235,43 +3223,43 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.007870353063128414</v>
+        <v>0.006367854991090846</v>
       </c>
       <c r="BH11">
-        <v>63529.55146859107</v>
+        <v>78519.37594363271</v>
       </c>
       <c r="BI11">
-        <v>63529.55146859107</v>
+        <v>78519.37594363271</v>
       </c>
       <c r="BJ11">
-        <v>414.4727323463973</v>
+        <v>10065.4252642173</v>
       </c>
       <c r="BK11">
-        <v>635.2955146859108</v>
+        <v>785.1937594363271</v>
       </c>
       <c r="BL11">
-        <v>0.006352955146859108</v>
+        <v>0.007851937594363272</v>
       </c>
       <c r="BM11">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN11">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO11">
-        <v>7.223708712032332</v>
+        <v>0.1075386526984</v>
       </c>
       <c r="BP11">
-        <v>2.655782117189557</v>
+        <v>0.005741164827874829</v>
       </c>
       <c r="BQ11">
-        <v>3.5920308156903</v>
+        <v>0.007830908578209507</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04908973714933696</v>
+        <v>0.04665029003722419</v>
       </c>
       <c r="BT11" t="s">
         <v>138</v>
@@ -3283,7 +3271,7 @@
         <v>140</v>
       </c>
       <c r="BW11" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -241,30 +241,30 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>USDJPY</t>
   </si>
   <si>
@@ -277,15 +277,15 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -316,30 +316,30 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_ACCELERATING</t>
-  </si>
-  <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
     <t>UP_STEADY</t>
   </si>
   <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
+    <t>多头减速</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
     <t>多头加速</t>
   </si>
   <si>
-    <t>空头加速</t>
-  </si>
-  <si>
-    <t>多头减速</t>
-  </si>
-  <si>
     <t>多头稳态</t>
   </si>
   <si>
@@ -361,15 +361,15 @@
     <t>转换</t>
   </si>
   <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_STEEPENING</t>
-  </si>
-  <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
     <t>UP_SLOPE</t>
   </si>
   <si>
@@ -379,15 +379,15 @@
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
     <t>上升坡延续</t>
   </si>
   <si>
@@ -397,34 +397,34 @@
     <t>地形转换区</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.04433,naive=0.007975,drift4=0.02399; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.09433,naive=0.0137,drift4=0.02229; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=272.5,naive=37.39,drift4=146.6; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.01099,naive=0.001182,drift4=0.001731; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01542,naive=0.001614,drift4=0.005485; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01176,naive=0.0006147,drift4=0.001564; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.01502,naive=0.00118,drift4=0.001702; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.04768,naive=0.00845,drift4=0.01425; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=6.598,naive=2.072,drift4=2.948; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.1075,naive=0.005741,drift4=0.007831; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01058,naive=0.0008404,drift4=0.002095; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.08733,naive=0.01229,drift4=0.02063; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=251.3,naive=54.99,drift4=154; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.009298,naive=0.002891,drift4=0.003579; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01529,naive=0.001746,drift4=0.006008; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01342,naive=0.001242,drift4=0.002569; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.04614,naive=0.007417,drift4=0.01423; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.05792,naive=0.0142,drift4=0.03948; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=6.648,naive=1.943,drift4=2.727; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.1002,naive=0.002691,drift4=0.005859; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1033,7 +1033,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1057,19 +1057,19 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K2">
-        <v>0.5692800216481988</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1.109282431255643</v>
+        <v>0.8139260349039491</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="O2" t="s">
         <v>90</v>
@@ -1087,10 +1087,10 @@
         <v>105</v>
       </c>
       <c r="T2">
-        <v>0.9724499547242961</v>
+        <v>0.9316469936104604</v>
       </c>
       <c r="U2">
-        <v>0.9229624934160302</v>
+        <v>0.818771331126668</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1099,22 +1099,22 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9998720421714683</v>
+        <v>0.9981207360078433</v>
       </c>
       <c r="Y2">
-        <v>0.4630903664045969</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>20.60150864564121</v>
+        <v>-36.91044960373866</v>
       </c>
       <c r="AA2">
-        <v>16</v>
+        <v>37.00000000000001</v>
       </c>
       <c r="AB2">
-        <v>0.9360502711305557</v>
+        <v>0.7995751405528057</v>
       </c>
       <c r="AC2">
-        <v>0.3518662955106855</v>
+        <v>-0.6005660618199808</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1129,58 +1129,58 @@
         <v>121</v>
       </c>
       <c r="AH2">
-        <v>0.6846754462856411</v>
+        <v>0.3990362638910706</v>
       </c>
       <c r="AI2">
-        <v>0.8678659499928586</v>
+        <v>0.7338323803457383</v>
       </c>
       <c r="AJ2">
-        <v>0.9020457495733645</v>
+        <v>0.6822975428952236</v>
       </c>
       <c r="AK2">
-        <v>0.3040788133693674</v>
+        <v>-0.6387562523090935</v>
       </c>
       <c r="AL2">
-        <v>1.110409765564364</v>
+        <v>0.7250910476433676</v>
       </c>
       <c r="AM2">
-        <v>-1.973152759960435</v>
+        <v>-1.550986721546837</v>
       </c>
       <c r="AN2">
-        <v>0.9435296817973353</v>
+        <v>0.6218725144078714</v>
       </c>
       <c r="AO2">
-        <v>0.03681612924827607</v>
+        <v>0.03588279615232357</v>
       </c>
       <c r="AP2">
-        <v>4.84001</v>
+        <v>1.35085</v>
       </c>
       <c r="AQ2">
-        <v>4.844084477957162</v>
+        <v>1.351716906333036</v>
       </c>
       <c r="AR2">
-        <v>4.799039615517158</v>
+        <v>1.355739376581349</v>
       </c>
       <c r="AS2">
-        <v>4.84001</v>
+        <v>1.35085</v>
       </c>
       <c r="AT2">
-        <v>4.904380000000001</v>
+        <v>1.34791</v>
       </c>
       <c r="AW2">
-        <v>0.0008418325493463818</v>
+        <v>0.0006417487752420818</v>
       </c>
       <c r="AY2">
-        <v>0.0008418325493463818</v>
+        <v>0.0006417487752420818</v>
       </c>
       <c r="AZ2">
-        <v>0.4501741879493744</v>
+        <v>0.411131882544</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3498258120506256</v>
+        <v>0.388868117456</v>
       </c>
       <c r="BC2" t="s">
         <v>127</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.04432829067544009</v>
+        <v>0.01057971044759011</v>
       </c>
       <c r="BP2">
-        <v>0.007974590056161444</v>
+        <v>0.0008403720652294348</v>
       </c>
       <c r="BQ2">
-        <v>0.02398571596866162</v>
+        <v>0.002094711743995104</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT2" t="s">
         <v>137</v>
@@ -1240,7 +1240,7 @@
         <v>139</v>
       </c>
       <c r="BW2" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1260,7 +1260,7 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
         <v>90</v>
@@ -1272,19 +1272,19 @@
         <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.1899500130054068</v>
+        <v>0.2384300129785058</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="s">
         <v>90</v>
@@ -1302,10 +1302,10 @@
         <v>106</v>
       </c>
       <c r="T3">
-        <v>-0.8280617309978223</v>
+        <v>-0.8386833152190706</v>
       </c>
       <c r="U3">
-        <v>0.7686373726648043</v>
+        <v>0.7762214031496457</v>
       </c>
       <c r="V3" t="s">
         <v>94</v>
@@ -1314,22 +1314,22 @@
         <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9840383748631368</v>
+        <v>0.9952556452042558</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>-119.4121077146081</v>
+        <v>-121.7416175324508</v>
       </c>
       <c r="AA3">
-        <v>-77</v>
+        <v>-61</v>
       </c>
       <c r="AB3">
-        <v>-0.4910878471066095</v>
+        <v>-0.526089510080176</v>
       </c>
       <c r="AC3">
-        <v>-0.8711100541402305</v>
+        <v>-0.8504292018643294</v>
       </c>
       <c r="AD3" t="s">
         <v>94</v>
@@ -1344,58 +1344,58 @@
         <v>122</v>
       </c>
       <c r="AH3">
-        <v>-0.2416246434909123</v>
+        <v>-0.2617967773950182</v>
       </c>
       <c r="AI3">
-        <v>0.6221468121514782</v>
+        <v>0.6417163165867966</v>
       </c>
       <c r="AJ3">
-        <v>-0.1118580393334388</v>
+        <v>-0.1519236588311104</v>
       </c>
       <c r="AK3">
-        <v>-0.4291765003638253</v>
+        <v>-0.3918344817619402</v>
       </c>
       <c r="AL3">
-        <v>-0.3912646910892517</v>
+        <v>-0.4339082491779432</v>
       </c>
       <c r="AM3">
-        <v>0.1062995051137328</v>
+        <v>0.1170630111252183</v>
       </c>
       <c r="AN3">
-        <v>0.3528146985862998</v>
+        <v>0.4009972801686971</v>
       </c>
       <c r="AO3">
-        <v>0.1306198212173499</v>
+        <v>0.09633341505830399</v>
       </c>
       <c r="AP3">
-        <v>9.081810000000001</v>
+        <v>9.06995</v>
       </c>
       <c r="AQ3">
-        <v>9.081111207477486</v>
+        <v>9.062264986405948</v>
       </c>
       <c r="AR3">
-        <v>9.124408026328425</v>
+        <v>9.106694719785541</v>
       </c>
       <c r="AS3">
-        <v>9.081810000000001</v>
+        <v>9.06995</v>
       </c>
       <c r="AT3">
-        <v>9.038580000000001</v>
+        <v>9.014860000000001</v>
       </c>
       <c r="AW3">
-        <v>-7.6944190917343E-05</v>
+        <v>-0.0008473049569239623</v>
       </c>
       <c r="AY3">
-        <v>7.6944190917343E-05</v>
+        <v>0.0008473049569239623</v>
       </c>
       <c r="AZ3">
-        <v>0.3948035266221882</v>
+        <v>0.3962225451432942</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.4051964733778118</v>
+        <v>0.4037774548567058</v>
       </c>
       <c r="BC3" t="s">
         <v>128</v>
@@ -1431,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="BO3">
-        <v>0.09433473931780446</v>
+        <v>0.08733135580296883</v>
       </c>
       <c r="BP3">
-        <v>0.01369619244868784</v>
+        <v>0.0122927090686126</v>
       </c>
       <c r="BQ3">
-        <v>0.02229287295341999</v>
+        <v>0.02063253114057767</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT3" t="s">
         <v>137</v>
@@ -1455,7 +1455,7 @@
         <v>139</v>
       </c>
       <c r="BW3" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1463,7 +1463,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1475,7 +1475,7 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
@@ -1487,19 +1487,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.7303045623762349</v>
+        <v>0.322878077889677</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1511,16 +1511,16 @@
         <v>0.75</v>
       </c>
       <c r="R4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T4">
-        <v>0.8375578481369297</v>
+        <v>0.7568632986052749</v>
       </c>
       <c r="U4">
-        <v>0.7768735799681212</v>
+        <v>0.740508961547742</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1529,22 +1529,22 @@
         <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9998901932260111</v>
+        <v>0.9996819087014734</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>0.02142553806564812</v>
       </c>
       <c r="Z4">
-        <v>-58.38276076350893</v>
+        <v>-72.19627297879811</v>
       </c>
       <c r="AA4">
-        <v>-12.99999999999999</v>
+        <v>-24</v>
       </c>
       <c r="AB4">
-        <v>0.5242421510722166</v>
+        <v>0.3057572391824364</v>
       </c>
       <c r="AC4">
-        <v>-0.8515692379596478</v>
+        <v>-0.9521095056176755</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
@@ -1553,73 +1553,73 @@
         <v>112</v>
       </c>
       <c r="AF4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AH4">
-        <v>0.2620922928664092</v>
+        <v>0.1561044550058966</v>
       </c>
       <c r="AI4">
-        <v>0.6461128338479821</v>
+        <v>0.5807521591084351</v>
       </c>
       <c r="AJ4">
-        <v>0.7319605414246987</v>
+        <v>0.5147719817282685</v>
       </c>
       <c r="AK4">
-        <v>-1.09376710170299</v>
+        <v>-1.330552561932046</v>
       </c>
       <c r="AL4">
-        <v>0.1047188308951358</v>
+        <v>-0.1771006120820895</v>
       </c>
       <c r="AM4">
-        <v>-2.629511894418323</v>
+        <v>-2.280037637543915</v>
       </c>
       <c r="AN4">
-        <v>0.3324834843152654</v>
+        <v>0.481562497732405</v>
       </c>
       <c r="AO4">
-        <v>0.07414252735191168</v>
+        <v>0.1009919220329404</v>
       </c>
       <c r="AP4">
-        <v>4371.049999999999</v>
+        <v>4334.84</v>
       </c>
       <c r="AQ4">
-        <v>4498.918522063601</v>
+        <v>4446.281548879775</v>
       </c>
       <c r="AR4">
-        <v>4653.448959710856</v>
+        <v>4611.885077891402</v>
       </c>
       <c r="AS4">
-        <v>4371.049999999999</v>
+        <v>4334.84</v>
       </c>
       <c r="AT4">
-        <v>4366.369999999999</v>
+        <v>4293.950000000001</v>
       </c>
       <c r="AU4">
-        <v>4498.918522063601</v>
+        <v>4446.281548879775</v>
       </c>
       <c r="AV4">
-        <v>4232.23</v>
+        <v>4196.02</v>
       </c>
       <c r="AW4">
-        <v>0.02925350249107232</v>
+        <v>0.02570834191798888</v>
       </c>
       <c r="AX4">
-        <v>0.9211102295317845</v>
+        <v>0.8027773294898107</v>
       </c>
       <c r="AY4">
-        <v>0.02925350249107232</v>
+        <v>0.02570834191798888</v>
       </c>
       <c r="AZ4">
-        <v>0.4584540859286959</v>
+        <v>0.4534056129818229</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3415459140713041</v>
+        <v>0.3465943870181771</v>
       </c>
       <c r="BC4" t="s">
         <v>129</v>
@@ -1634,43 +1634,43 @@
         <v>375</v>
       </c>
       <c r="BG4">
-        <v>0.03175895951773585</v>
+        <v>0.0320242500299894</v>
       </c>
       <c r="BH4">
-        <v>15743.58882005483</v>
+        <v>15613.16813139326</v>
       </c>
       <c r="BI4">
-        <v>11807.69161504112</v>
+        <v>11709.87609854494</v>
       </c>
       <c r="BJ4">
-        <v>2.701339864572842</v>
+        <v>2.701339864572843</v>
       </c>
       <c r="BK4">
-        <v>118.0769161504112</v>
+        <v>117.0987609854494</v>
       </c>
       <c r="BL4">
-        <v>0.001180769161504112</v>
+        <v>0.001170987609854494</v>
       </c>
       <c r="BM4">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="BN4">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="BO4">
-        <v>272.516572414176</v>
+        <v>251.2786261803798</v>
       </c>
       <c r="BP4">
-        <v>37.38565950804563</v>
+        <v>54.98597491165516</v>
       </c>
       <c r="BQ4">
-        <v>146.6156434370814</v>
+        <v>153.9943401860568</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT4" t="s">
         <v>138</v>
@@ -1682,7 +1682,7 @@
         <v>140</v>
       </c>
       <c r="BW4" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1690,7 +1690,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1702,7 +1702,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1714,19 +1714,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.6005909781916019</v>
+        <v>0.842535182301704</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O5" t="s">
         <v>95</v>
@@ -1738,16 +1738,16 @@
         <v>0.75</v>
       </c>
       <c r="R5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T5">
-        <v>0.9556874599152398</v>
+        <v>0.8990306146348624</v>
       </c>
       <c r="U5">
-        <v>0.8292741833208217</v>
+        <v>0.8043107252188452</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1756,22 +1756,22 @@
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9968593054358549</v>
+        <v>0.9989877945326281</v>
       </c>
       <c r="Y5">
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>29.54620453941579</v>
+        <v>45.24258405442502</v>
       </c>
       <c r="AA5">
-        <v>-70</v>
+        <v>-26</v>
       </c>
       <c r="AB5">
-        <v>0.8699583121118509</v>
+        <v>0.7041066397461356</v>
       </c>
       <c r="AC5">
-        <v>0.4931252733205828</v>
+        <v>0.7100942471710396</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1780,73 +1780,73 @@
         <v>112</v>
       </c>
       <c r="AF5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AH5">
-        <v>0.4336130193849842</v>
+        <v>0.3516969695778859</v>
       </c>
       <c r="AI5">
-        <v>0.7493466694651054</v>
+        <v>0.6998346222889451</v>
       </c>
       <c r="AJ5">
-        <v>0.3751948373740336</v>
+        <v>0.5343667599788634</v>
       </c>
       <c r="AK5">
-        <v>0.2771824625604786</v>
+        <v>0.583276607482987</v>
       </c>
       <c r="AL5">
-        <v>1.126869207941201</v>
+        <v>1.524969502733192</v>
       </c>
       <c r="AM5">
-        <v>-0.06969369288327512</v>
+        <v>0.2222349447075852</v>
       </c>
       <c r="AN5">
-        <v>1.081140949300065</v>
+        <v>1.503406852245616</v>
       </c>
       <c r="AO5">
-        <v>0.07027720713999359</v>
+        <v>0.07362065147543613</v>
       </c>
       <c r="AP5">
-        <v>0.81182</v>
+        <v>0.81514</v>
       </c>
       <c r="AQ5">
-        <v>0.8200380366663871</v>
+        <v>0.8263414089051424</v>
       </c>
       <c r="AR5">
-        <v>0.8353024049923961</v>
+        <v>0.8411058795030792</v>
       </c>
       <c r="AS5">
-        <v>0.81182</v>
+        <v>0.81514</v>
       </c>
       <c r="AT5">
-        <v>0.810265</v>
+        <v>0.816905</v>
       </c>
       <c r="AU5">
-        <v>0.8200380366663871</v>
+        <v>0.8263414089051424</v>
       </c>
       <c r="AV5">
-        <v>0.8025300000000001</v>
+        <v>0.8058500000000001</v>
       </c>
       <c r="AW5">
-        <v>0.010122978820905</v>
+        <v>0.01374169946897764</v>
       </c>
       <c r="AX5">
-        <v>0.8846110512795643</v>
+        <v>1.205749074826965</v>
       </c>
       <c r="AY5">
-        <v>0.010122978820905</v>
+        <v>0.01374169946897764</v>
       </c>
       <c r="AZ5">
-        <v>0.3779160288081272</v>
+        <v>0.4045063281231875</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.4220839711918728</v>
+        <v>0.3954936718768126</v>
       </c>
       <c r="BC5" t="s">
         <v>130</v>
@@ -1861,43 +1861,43 @@
         <v>375</v>
       </c>
       <c r="BG5">
-        <v>0.01144342341898443</v>
+        <v>0.01139681527099632</v>
       </c>
       <c r="BH5">
-        <v>43693.21851453205</v>
+        <v>43871.90527448899</v>
       </c>
       <c r="BI5">
-        <v>32769.91388589903</v>
+        <v>32903.92895586674</v>
       </c>
       <c r="BJ5">
-        <v>40365.98493003256</v>
+        <v>40365.98493003257</v>
       </c>
       <c r="BK5">
-        <v>327.6991388589904</v>
+        <v>329.0392895586675</v>
       </c>
       <c r="BL5">
-        <v>0.003276991388589904</v>
+        <v>0.003290392895586675</v>
       </c>
       <c r="BM5">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="BN5">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="BO5">
-        <v>0.01098509312371254</v>
+        <v>0.009297778296498053</v>
       </c>
       <c r="BP5">
-        <v>0.001181758122724756</v>
+        <v>0.002890902141619793</v>
       </c>
       <c r="BQ5">
-        <v>0.001730638248537051</v>
+        <v>0.003579236066269589</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT5" t="s">
         <v>138</v>
@@ -1909,7 +1909,7 @@
         <v>140</v>
       </c>
       <c r="BW5" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1917,7 +1917,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1929,7 +1929,7 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s">
         <v>91</v>
@@ -1941,19 +1941,19 @@
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0.9831164404353598</v>
       </c>
       <c r="L6">
-        <v>2.80948747210962</v>
+        <v>2.401175662286452</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
@@ -1962,7 +1962,7 @@
         <v>98</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.99577911010884</v>
       </c>
       <c r="R6" t="s">
         <v>103</v>
@@ -1971,10 +1971,10 @@
         <v>108</v>
       </c>
       <c r="T6">
-        <v>0.995854994680618</v>
+        <v>0.9928059095650883</v>
       </c>
       <c r="U6">
-        <v>0.9981218429706541</v>
+        <v>0.9940720574079374</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1983,22 +1983,22 @@
         <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9999483814575042</v>
+        <v>0.9993677281533742</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>7.382802814430751</v>
+        <v>-9.719262686398665</v>
       </c>
       <c r="AA6">
-        <v>3.000000000000004</v>
+        <v>-15</v>
       </c>
       <c r="AB6">
-        <v>0.9917097753910579</v>
+        <v>0.9856467677090055</v>
       </c>
       <c r="AC6">
-        <v>0.1284979431501433</v>
+        <v>-0.1688207608820363</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -2013,67 +2013,67 @@
         <v>124</v>
       </c>
       <c r="AH6">
-        <v>0.9916585847778734</v>
+        <v>0.9850235710070653</v>
       </c>
       <c r="AI6">
-        <v>0.9924783265735199</v>
+        <v>0.9907626449903175</v>
       </c>
       <c r="AJ6">
-        <v>2.272900400454537</v>
+        <v>1.983129691611978</v>
       </c>
       <c r="AK6">
-        <v>0.2790768090568564</v>
+        <v>-0.2703621536126906</v>
       </c>
       <c r="AL6">
-        <v>2.881898475879362</v>
+        <v>2.291754641934131</v>
       </c>
       <c r="AM6">
-        <v>-5.135591575188919</v>
+        <v>-5.059268123616951</v>
       </c>
       <c r="AN6">
-        <v>2.443644714065337</v>
+        <v>1.871991524109026</v>
       </c>
       <c r="AO6">
-        <v>0.0334435970261589</v>
+        <v>0.03140060117376767</v>
       </c>
       <c r="AP6">
-        <v>0.718595</v>
+        <v>0.717435</v>
       </c>
       <c r="AQ6">
-        <v>0.7211831308897334</v>
+        <v>0.7191015946846109</v>
       </c>
       <c r="AR6">
-        <v>0.7160472781406976</v>
+        <v>0.7138404000294738</v>
       </c>
       <c r="AS6">
-        <v>0.718595</v>
+        <v>0.717435</v>
       </c>
       <c r="AT6">
-        <v>0.7289099999999999</v>
+        <v>0.7265900000000001</v>
       </c>
       <c r="AU6">
-        <v>0.7211831308897334</v>
+        <v>0.7191015946846109</v>
       </c>
       <c r="AV6">
-        <v>0.7113862500000001</v>
+        <v>0.7102262500000001</v>
       </c>
       <c r="AW6">
-        <v>0.003601654464244004</v>
+        <v>0.002322990493369899</v>
       </c>
       <c r="AX6">
-        <v>0.3590263068816986</v>
+        <v>0.2311905232683683</v>
       </c>
       <c r="AY6">
-        <v>0.003601654464244004</v>
+        <v>0.002322990493369899</v>
       </c>
       <c r="AZ6">
-        <v>0.4403320830707722</v>
+        <v>0.4437319859813307</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3596679169292279</v>
+        <v>0.3562680140186693</v>
       </c>
       <c r="BC6" t="s">
         <v>131</v>
@@ -2085,46 +2085,46 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>500</v>
+        <v>497.88955505442</v>
       </c>
       <c r="BG6">
-        <v>0.01003172858146791</v>
+        <v>0.01004794859464611</v>
       </c>
       <c r="BH6">
-        <v>49841.85885208996</v>
+        <v>49761.40107508285</v>
       </c>
       <c r="BI6">
-        <v>49841.85885208996</v>
+        <v>49551.36368031507</v>
       </c>
       <c r="BJ6">
-        <v>69360.15259233638</v>
+        <v>69067.39102541006</v>
       </c>
       <c r="BK6">
-        <v>498.4185885208996</v>
+        <v>495.5136368031507</v>
       </c>
       <c r="BL6">
-        <v>0.004984185885208996</v>
+        <v>0.004955136368031507</v>
       </c>
       <c r="BM6">
-        <v>500.0000000000001</v>
+        <v>497.88955505442</v>
       </c>
       <c r="BN6">
-        <v>0.005000000000000001</v>
+        <v>0.0049788955505442</v>
       </c>
       <c r="BO6">
-        <v>0.01541890469811921</v>
+        <v>0.01528697777717799</v>
       </c>
       <c r="BP6">
-        <v>0.001614286703750476</v>
+        <v>0.001745837371191456</v>
       </c>
       <c r="BQ6">
-        <v>0.005484945190208731</v>
+        <v>0.006007722439466404</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT6" t="s">
         <v>138</v>
@@ -2136,7 +2136,7 @@
         <v>140</v>
       </c>
       <c r="BW6" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2144,7 +2144,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2156,52 +2156,52 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.06213464408790158</v>
       </c>
       <c r="L7">
-        <v>1.016772576813987</v>
+        <v>1.205848195906553</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>0.9533990169340738</v>
       </c>
       <c r="R7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T7">
-        <v>0.9805254827859041</v>
+        <v>0.9404449150584619</v>
       </c>
       <c r="U7">
-        <v>0.8386678405219214</v>
+        <v>0.8324109017031668</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2210,22 +2210,22 @@
         <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9897254930730585</v>
+        <v>0.9995619732546944</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>0.1778889054644588</v>
       </c>
       <c r="Z7">
-        <v>-19.51096534603836</v>
+        <v>-31.62603587327359</v>
       </c>
       <c r="AA7">
-        <v>74.99999999999999</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="AB7">
-        <v>0.9425775894082042</v>
+        <v>0.8514887408819645</v>
       </c>
       <c r="AC7">
-        <v>-0.3339872571602375</v>
+        <v>-0.5243728865523529</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
@@ -2234,73 +2234,73 @@
         <v>112</v>
       </c>
       <c r="AF7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AH7">
-        <v>0.4664465347183249</v>
+        <v>0.5012599090422775</v>
       </c>
       <c r="AI7">
-        <v>0.7739317707643107</v>
+        <v>0.7852230296161203</v>
       </c>
       <c r="AJ7">
-        <v>0.8262128267408263</v>
+        <v>1.060783840176871</v>
       </c>
       <c r="AK7">
-        <v>-0.5082568125725563</v>
+        <v>-0.6571496114157754</v>
       </c>
       <c r="AL7">
-        <v>1.011677001301629</v>
+        <v>0.8512635793615695</v>
       </c>
       <c r="AM7">
-        <v>-1.407178365885063</v>
+        <v>-3.082724975108901</v>
       </c>
       <c r="AN7">
-        <v>0.9269730964381281</v>
+        <v>0.6491904612606465</v>
       </c>
       <c r="AO7">
-        <v>0.03496952422480668</v>
+        <v>0.03765376253669189</v>
       </c>
       <c r="AP7">
-        <v>1.35248</v>
+        <v>1.159365</v>
       </c>
       <c r="AQ7">
-        <v>1.353848398810026</v>
+        <v>1.155339066821759</v>
       </c>
       <c r="AR7">
-        <v>1.357137735475286</v>
+        <v>1.146974055969008</v>
       </c>
       <c r="AS7">
-        <v>1.35248</v>
+        <v>1.159365</v>
       </c>
       <c r="AT7">
-        <v>1.35117</v>
+        <v>1.161715</v>
       </c>
       <c r="AU7">
-        <v>1.35450872</v>
+        <v>1.155339066821759</v>
       </c>
       <c r="AV7">
-        <v>1.341055</v>
+        <v>1.16918875</v>
       </c>
       <c r="AW7">
-        <v>0.001011770089040984</v>
+        <v>-0.003472532962648196</v>
       </c>
       <c r="AX7">
-        <v>0.1775684901531726</v>
+        <v>0.4098163306517997</v>
       </c>
       <c r="AY7">
-        <v>0.001011770089040984</v>
+        <v>0.003472532962648196</v>
       </c>
       <c r="AZ7">
-        <v>0.4049105091928277</v>
+        <v>0.400648232964173</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3950894908071723</v>
+        <v>0.399351767035827</v>
       </c>
       <c r="BC7" t="s">
         <v>132</v>
@@ -2312,58 +2312,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>375</v>
+        <v>476.6995084670369</v>
       </c>
       <c r="BG7">
-        <v>0.008447444694191425</v>
+        <v>0.008473388449711712</v>
       </c>
       <c r="BH7">
-        <v>59189.49671772419</v>
+        <v>59008.27077236278</v>
       </c>
       <c r="BI7">
-        <v>44392.12253829314</v>
+        <v>56258.42734535032</v>
       </c>
       <c r="BJ7">
-        <v>32822.75711159733</v>
+        <v>48525.20763120356</v>
       </c>
       <c r="BK7">
-        <v>443.9212253829314</v>
+        <v>562.5842734535032</v>
       </c>
       <c r="BL7">
-        <v>0.004439212253829314</v>
+        <v>0.005625842734535032</v>
       </c>
       <c r="BM7">
-        <v>375</v>
+        <v>476.6995084670369</v>
       </c>
       <c r="BN7">
-        <v>0.00375</v>
+        <v>0.004766995084670368</v>
       </c>
       <c r="BO7">
-        <v>0.01175581516502146</v>
+        <v>0.01341962399988159</v>
       </c>
       <c r="BP7">
-        <v>0.0006147316938812383</v>
+        <v>0.001242150364604664</v>
       </c>
       <c r="BQ7">
-        <v>0.001563859085667526</v>
+        <v>0.00256926938828844</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT7" t="s">
         <v>138</v>
       </c>
       <c r="BU7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV7" t="s">
         <v>140</v>
       </c>
       <c r="BW7" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2371,7 +2371,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2392,142 +2392,142 @@
         <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J8" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K8">
-        <v>0.4266819783946858</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>1.450868759022682</v>
+        <v>3.856630204854587</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="O8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q8">
-        <v>0.6799885162039856</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T8">
-        <v>0.9965186387595244</v>
+        <v>-0.9995502225675734</v>
       </c>
       <c r="U8">
-        <v>0.9119427220414751</v>
+        <v>0.9997581877229801</v>
       </c>
       <c r="V8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W8" t="s">
         <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9980281513619448</v>
+        <v>0.999842350270288</v>
       </c>
       <c r="Y8">
-        <v>0.2329782802410662</v>
+        <v>1</v>
       </c>
       <c r="Z8">
-        <v>-7.753214303499411</v>
+        <v>-177.5694691317406</v>
       </c>
       <c r="AA8">
-        <v>40.99999999999999</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB8">
-        <v>0.990858330666288</v>
+        <v>-0.9991003742166761</v>
       </c>
       <c r="AC8">
-        <v>-0.1349065178159199</v>
+        <v>-0.0424080445210326</v>
       </c>
       <c r="AD8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AH8">
-        <v>0.6096488898083851</v>
+        <v>-0.9989428663127257</v>
       </c>
       <c r="AI8">
-        <v>0.837692027098163</v>
+        <v>0.9945802336410562</v>
       </c>
       <c r="AJ8">
-        <v>1.225754760766346</v>
+        <v>-2.946833510094436</v>
       </c>
       <c r="AK8">
-        <v>-0.3016279754365427</v>
+        <v>-0.1538033138105544</v>
       </c>
       <c r="AL8">
-        <v>1.236600414817661</v>
+        <v>-4.73947218000892</v>
       </c>
       <c r="AM8">
-        <v>-2.808461627930354</v>
+        <v>4.920456880994661</v>
       </c>
       <c r="AN8">
-        <v>1.03317886421508</v>
+        <v>4.291788192979363</v>
       </c>
       <c r="AO8">
-        <v>0.03647320751078251</v>
+        <v>0.03396467479031572</v>
       </c>
       <c r="AP8">
-        <v>1.161515</v>
+        <v>6.708905</v>
       </c>
       <c r="AQ8">
-        <v>1.159322422666424</v>
+        <v>6.67613667042478</v>
       </c>
       <c r="AR8">
-        <v>1.150352464187454</v>
+        <v>6.661298338846341</v>
       </c>
       <c r="AS8">
-        <v>1.161515</v>
+        <v>6.708905</v>
       </c>
       <c r="AT8">
-        <v>1.166015</v>
+        <v>6.67498</v>
       </c>
       <c r="AU8">
-        <v>1.159322422666424</v>
+        <v>6.67613667042478</v>
       </c>
       <c r="AV8">
-        <v>1.17133875</v>
+        <v>6.732411249999999</v>
       </c>
       <c r="AW8">
-        <v>-0.001887687488819369</v>
+        <v>-0.004884303709058254</v>
       </c>
       <c r="AX8">
-        <v>0.2231914832498816</v>
+        <v>1.394026251538208</v>
       </c>
       <c r="AY8">
-        <v>0.001887687488819369</v>
+        <v>0.004884303709058254</v>
       </c>
       <c r="AZ8">
-        <v>0.3698364940967112</v>
+        <v>0.411377647202952</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.4301635059032888</v>
+        <v>0.388622352797048</v>
       </c>
       <c r="BC8" t="s">
         <v>133</v>
@@ -2539,46 +2539,46 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>339.9942581019928</v>
+        <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.00845770394700027</v>
+        <v>0.003503738687609918</v>
       </c>
       <c r="BH8">
-        <v>59117.69945285648</v>
+        <v>142704.7061951632</v>
       </c>
       <c r="BI8">
-        <v>40199.35673234105</v>
+        <v>142704.7061951632</v>
       </c>
       <c r="BJ8">
-        <v>34609.4167809637</v>
+        <v>21270.9385801652</v>
       </c>
       <c r="BK8">
-        <v>401.9935673234106</v>
+        <v>1427.047061951632</v>
       </c>
       <c r="BL8">
-        <v>0.004019935673234106</v>
+        <v>0.01427047061951632</v>
       </c>
       <c r="BM8">
-        <v>339.9942581019928</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN8">
-        <v>0.003399942581019928</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO8">
-        <v>0.01502311307480023</v>
+        <v>0.04613806075758249</v>
       </c>
       <c r="BP8">
-        <v>0.001180301067312868</v>
+        <v>0.00741716609185992</v>
       </c>
       <c r="BQ8">
-        <v>0.001702400516222229</v>
+        <v>0.01423138400495298</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT8" t="s">
         <v>138</v>
@@ -2590,7 +2590,7 @@
         <v>140</v>
       </c>
       <c r="BW8" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2598,7 +2598,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2610,7 +2610,7 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
         <v>92</v>
@@ -2619,142 +2619,142 @@
         <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0.1466153677489054</v>
       </c>
       <c r="L9">
-        <v>4.168882434469204</v>
+        <v>0.8916981049182402</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.8900384741883209</v>
       </c>
       <c r="R9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T9">
-        <v>-0.9897352629795897</v>
+        <v>0.9937501621635167</v>
       </c>
       <c r="U9">
-        <v>0.9953623838234893</v>
+        <v>0.8687640725410471</v>
       </c>
       <c r="V9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W9" t="s">
         <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9999260619306957</v>
+        <v>0.9983367776205151</v>
       </c>
       <c r="Y9">
-        <v>1</v>
+        <v>0.0861904706490934</v>
       </c>
       <c r="Z9">
-        <v>-168.3699817462219</v>
+        <v>-10.70146987287008</v>
       </c>
       <c r="AA9">
-        <v>5.000000000000007</v>
+        <v>-25</v>
       </c>
       <c r="AB9">
-        <v>-0.9794697669482223</v>
+        <v>0.9826080331064223</v>
       </c>
       <c r="AC9">
-        <v>-0.201591110008341</v>
+        <v>-0.185691823392222</v>
       </c>
       <c r="AD9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AH9">
-        <v>-0.9793973468447121</v>
+        <v>0.532762162779732</v>
       </c>
       <c r="AI9">
-        <v>0.988449476258463</v>
+        <v>0.8065536943702535</v>
       </c>
       <c r="AJ9">
-        <v>-3.166403133240801</v>
+        <v>0.7721394961939267</v>
       </c>
       <c r="AK9">
-        <v>-0.6205442492079006</v>
+        <v>-0.09740858997026673</v>
       </c>
       <c r="AL9">
-        <v>-5.201157229962569</v>
+        <v>0.6952620954468656</v>
       </c>
       <c r="AM9">
-        <v>4.963366596708446</v>
+        <v>-2.436636701598483</v>
       </c>
       <c r="AN9">
-        <v>4.741587371836053</v>
+        <v>0.5520612450243971</v>
       </c>
       <c r="AO9">
-        <v>0.0357705033449802</v>
+        <v>0.0325645457244813</v>
       </c>
       <c r="AP9">
-        <v>6.709215</v>
+        <v>4.80355</v>
       </c>
       <c r="AQ9">
-        <v>6.679261014119083</v>
+        <v>4.774964635314872</v>
       </c>
       <c r="AR9">
-        <v>6.668034120346375</v>
+        <v>4.720351963962985</v>
       </c>
       <c r="AS9">
-        <v>6.709215</v>
+        <v>4.80355</v>
       </c>
       <c r="AT9">
-        <v>6.675600000000001</v>
+        <v>4.831460000000001</v>
       </c>
       <c r="AU9">
-        <v>6.679261014119083</v>
+        <v>4.774964635314872</v>
       </c>
       <c r="AV9">
-        <v>6.73272125</v>
+        <v>4.843350000000001</v>
       </c>
       <c r="AW9">
-        <v>-0.004464603665394124</v>
+        <v>-0.005950883135416089</v>
       </c>
       <c r="AX9">
-        <v>1.274298787808252</v>
+        <v>0.7182252433449224</v>
       </c>
       <c r="AY9">
-        <v>0.004464603665394124</v>
+        <v>0.005950883135416089</v>
       </c>
       <c r="AZ9">
-        <v>0.4047098316520368</v>
+        <v>0.4582329640690144</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3952901683479632</v>
+        <v>0.3417670359309857</v>
       </c>
       <c r="BC9" t="s">
         <v>134</v>
@@ -2766,46 +2766,46 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>500</v>
+        <v>445.0192370941605</v>
       </c>
       <c r="BG9">
-        <v>0.00350357679698737</v>
+        <v>0.008285538820247537</v>
       </c>
       <c r="BH9">
-        <v>142711.300186123</v>
+        <v>60346.10552763811</v>
       </c>
       <c r="BI9">
-        <v>142711.300186123</v>
+        <v>53710.35568702642</v>
       </c>
       <c r="BJ9">
-        <v>21270.9385801652</v>
+        <v>11181.38786668743</v>
       </c>
       <c r="BK9">
-        <v>1427.11300186123</v>
+        <v>537.1035568702642</v>
       </c>
       <c r="BL9">
-        <v>0.0142711300186123</v>
+        <v>0.005371035568702643</v>
       </c>
       <c r="BM9">
-        <v>499.9999999999999</v>
+        <v>445.0192370941605</v>
       </c>
       <c r="BN9">
-        <v>0.004999999999999999</v>
+        <v>0.004450192370941605</v>
       </c>
       <c r="BO9">
-        <v>0.0476808082991944</v>
+        <v>0.05791762915334398</v>
       </c>
       <c r="BP9">
-        <v>0.008450340028112065</v>
+        <v>0.01420306494004293</v>
       </c>
       <c r="BQ9">
-        <v>0.01425021812008477</v>
+        <v>0.03947596667097171</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT9" t="s">
         <v>138</v>
@@ -2817,7 +2817,7 @@
         <v>140</v>
       </c>
       <c r="BW9" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2825,7 +2825,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2837,7 +2837,7 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
         <v>92</v>
@@ -2849,19 +2849,19 @@
         <v>94</v>
       </c>
       <c r="J10" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>2.770835826498998</v>
+        <v>2.798196837805659</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O10" t="s">
         <v>95</v>
@@ -2879,10 +2879,10 @@
         <v>106</v>
       </c>
       <c r="T10">
-        <v>-0.8021105853176919</v>
+        <v>-0.8377920202772901</v>
       </c>
       <c r="U10">
-        <v>0.9109192273751268</v>
+        <v>0.9269575719191055</v>
       </c>
       <c r="V10" t="s">
         <v>94</v>
@@ -2891,22 +2891,22 @@
         <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9998778559286617</v>
+        <v>0.9998046511773003</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-127.1710804786239</v>
+        <v>-132.4970578377665</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB10">
-        <v>-0.6041969966638925</v>
+        <v>-0.6755523472254542</v>
       </c>
       <c r="AC10">
-        <v>-0.7968349824288165</v>
+        <v>-0.737312027677685</v>
       </c>
       <c r="AD10" t="s">
         <v>94</v>
@@ -2921,67 +2921,67 @@
         <v>122</v>
       </c>
       <c r="AH10">
-        <v>-0.6041231975828296</v>
+        <v>-0.6754203788697517</v>
       </c>
       <c r="AI10">
-        <v>0.8725029968446851</v>
+        <v>0.8948797732391993</v>
       </c>
       <c r="AJ10">
-        <v>-2.046261352372307</v>
+        <v>-2.10867769958606</v>
       </c>
       <c r="AK10">
-        <v>-2.698677149614167</v>
+        <v>-2.347407935325795</v>
       </c>
       <c r="AL10">
-        <v>-3.704382662691871</v>
+        <v>-3.568394250874231</v>
       </c>
       <c r="AM10">
-        <v>2.745353844411959</v>
+        <v>3.619139089034123</v>
       </c>
       <c r="AN10">
-        <v>3.36365172865137</v>
+        <v>3.158217086892496</v>
       </c>
       <c r="AO10">
-        <v>0.05808901153009509</v>
+        <v>0.05145039226994787</v>
       </c>
       <c r="AP10">
-        <v>154.19</v>
+        <v>154.005</v>
       </c>
       <c r="AQ10">
-        <v>153.0075739955537</v>
+        <v>152.8274495046455</v>
       </c>
       <c r="AR10">
-        <v>156.0643862307935</v>
+        <v>156.1492651411993</v>
       </c>
       <c r="AS10">
-        <v>154.19</v>
+        <v>154.005</v>
       </c>
       <c r="AT10">
-        <v>149.064</v>
+        <v>148.694</v>
       </c>
       <c r="AU10">
-        <v>153.0075739955537</v>
+        <v>152.8274495046455</v>
       </c>
       <c r="AV10">
-        <v>155.3535</v>
+        <v>155.1685</v>
       </c>
       <c r="AW10">
-        <v>-0.007668629641651574</v>
+        <v>-0.007646183535303833</v>
       </c>
       <c r="AX10">
-        <v>1.016266441294579</v>
+        <v>1.012076059608469</v>
       </c>
       <c r="AY10">
-        <v>0.007668629641651574</v>
+        <v>0.007646183535303833</v>
       </c>
       <c r="AZ10">
-        <v>0.4168875686767561</v>
+        <v>0.4119571130573444</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3831124313232439</v>
+        <v>0.3880428869426555</v>
       </c>
       <c r="BC10" t="s">
         <v>135</v>
@@ -2996,22 +2996,22 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.007545884947143222</v>
+        <v>0.007554949514626235</v>
       </c>
       <c r="BH10">
-        <v>66261.28061882177</v>
+        <v>66181.77911473926</v>
       </c>
       <c r="BI10">
-        <v>66261.28061882177</v>
+        <v>66181.77911473926</v>
       </c>
       <c r="BJ10">
         <v>429.7378599054528</v>
       </c>
       <c r="BK10">
-        <v>662.6128061882176</v>
+        <v>661.8177911473925</v>
       </c>
       <c r="BL10">
-        <v>0.006626128061882177</v>
+        <v>0.006618177911473925</v>
       </c>
       <c r="BM10">
         <v>500.0000000000001</v>
@@ -3020,19 +3020,19 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO10">
-        <v>6.597824858704986</v>
+        <v>6.647980933792516</v>
       </c>
       <c r="BP10">
-        <v>2.072476781230577</v>
+        <v>1.943333086653392</v>
       </c>
       <c r="BQ10">
-        <v>2.947712057334392</v>
+        <v>2.727261215210651</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT10" t="s">
         <v>138</v>
@@ -3044,7 +3044,7 @@
         <v>140</v>
       </c>
       <c r="BW10" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3052,7 +3052,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3064,7 +3064,7 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
         <v>92</v>
@@ -3076,19 +3076,19 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.01403701514849852</v>
+        <v>0.007077295597485317</v>
       </c>
       <c r="M11">
         <v>4</v>
       </c>
       <c r="N11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" t="s">
         <v>96</v>
@@ -3100,16 +3100,16 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T11">
-        <v>0.6038783655477967</v>
+        <v>0.6039828205957997</v>
       </c>
       <c r="U11">
-        <v>0.6069459207557859</v>
+        <v>0.6206553275968192</v>
       </c>
       <c r="V11" t="s">
         <v>110</v>
@@ -3118,22 +3118,22 @@
         <v>110</v>
       </c>
       <c r="X11">
-        <v>0.9408026250371093</v>
+        <v>0.9954522333148373</v>
       </c>
       <c r="Y11">
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>-94.46303669474203</v>
+        <v>-92.29915559941685</v>
       </c>
       <c r="AA11">
-        <v>-90</v>
+        <v>-68</v>
       </c>
       <c r="AB11">
-        <v>-0.07781593679090455</v>
+        <v>-0.040117066830479</v>
       </c>
       <c r="AC11">
-        <v>-0.9969677426985057</v>
+        <v>-0.9991949864510524</v>
       </c>
       <c r="AD11" t="s">
         <v>111</v>
@@ -3148,67 +3148,67 @@
         <v>126</v>
       </c>
       <c r="AH11">
-        <v>-0.03660471880130239</v>
+        <v>-0.01996731188522045</v>
       </c>
       <c r="AI11">
-        <v>0.4759844382618538</v>
+        <v>0.4827768605672526</v>
       </c>
       <c r="AJ11">
-        <v>0.1292815129190201</v>
+        <v>0.09041128214031938</v>
       </c>
       <c r="AK11">
-        <v>-0.3742686717291679</v>
+        <v>-0.4586118257574019</v>
       </c>
       <c r="AL11">
-        <v>-0.4592823010889686</v>
+        <v>-0.4808385627583562</v>
       </c>
       <c r="AM11">
-        <v>-0.9123482222380772</v>
+        <v>-0.8782450330104122</v>
       </c>
       <c r="AN11">
-        <v>0.5084784036395883</v>
+        <v>0.5245460561227651</v>
       </c>
       <c r="AO11">
-        <v>0.1776084102560392</v>
+        <v>0.1844436076138944</v>
       </c>
       <c r="AP11">
-        <v>7.8009</v>
+        <v>7.7944</v>
       </c>
       <c r="AQ11">
-        <v>7.733237874175519</v>
+        <v>7.71940724798757</v>
       </c>
       <c r="AR11">
-        <v>7.614672511703978</v>
+        <v>7.608833488588298</v>
       </c>
       <c r="AS11">
-        <v>7.8009</v>
+        <v>7.7944</v>
       </c>
       <c r="AT11">
-        <v>7.799300000000001</v>
+        <v>7.786300000000001</v>
       </c>
       <c r="AU11">
-        <v>7.733237874175519</v>
+        <v>7.71940724798757</v>
       </c>
       <c r="AV11">
-        <v>7.850575000000001</v>
+        <v>7.844395168008287</v>
       </c>
       <c r="AW11">
-        <v>-0.008673630712415469</v>
+        <v>-0.009621363031462339</v>
       </c>
       <c r="AX11">
-        <v>1.362096141408778</v>
+        <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.008673630712415469</v>
+        <v>0.009621363031462339</v>
       </c>
       <c r="AZ11">
-        <v>0.3595462757855906</v>
+        <v>0.3860601725217242</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4404537242144094</v>
+        <v>0.4139398274782758</v>
       </c>
       <c r="BC11" t="s">
         <v>136</v>
@@ -3223,22 +3223,22 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.006367854991090846</v>
+        <v>0.006414242020974893</v>
       </c>
       <c r="BH11">
-        <v>78519.37594363271</v>
+        <v>77951.53322325148</v>
       </c>
       <c r="BI11">
-        <v>78519.37594363271</v>
+        <v>77951.53322325148</v>
       </c>
       <c r="BJ11">
-        <v>10065.4252642173</v>
+        <v>10000.96649174426</v>
       </c>
       <c r="BK11">
-        <v>785.1937594363271</v>
+        <v>779.5153322325148</v>
       </c>
       <c r="BL11">
-        <v>0.007851937594363272</v>
+        <v>0.007795153322325147</v>
       </c>
       <c r="BM11">
         <v>500.0000000000001</v>
@@ -3247,19 +3247,19 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO11">
-        <v>0.1075386526984</v>
+        <v>0.1002197002616151</v>
       </c>
       <c r="BP11">
-        <v>0.005741164827874829</v>
+        <v>0.002691348015251937</v>
       </c>
       <c r="BQ11">
-        <v>0.007830908578209507</v>
+        <v>0.005858586046772279</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04665029003722419</v>
+        <v>0.04909719703002575</v>
       </c>
       <c r="BT11" t="s">
         <v>138</v>
@@ -3271,7 +3271,7 @@
         <v>140</v>
       </c>
       <c r="BW11" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="140">
   <si>
     <t>Pair</t>
   </si>
@@ -241,30 +241,30 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>USDJPY</t>
   </si>
   <si>
@@ -277,15 +277,15 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -319,37 +319,37 @@
     <t>UP_DECELERATING</t>
   </si>
   <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_ACCELERATING</t>
-  </si>
-  <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
+    <t>UP_REVERSAL_WATCH</t>
+  </si>
+  <si>
     <t>多头减速</t>
   </si>
   <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
     <t>空头加速</t>
   </si>
   <si>
-    <t>多头加速</t>
-  </si>
-  <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
     <t>空头稳态</t>
   </si>
   <si>
-    <t>NEUTRAL</t>
-  </si>
-  <si>
-    <t>TRANSITION</t>
+    <t>多头反转预警</t>
   </si>
   <si>
     <t>上涨</t>
@@ -358,73 +358,70 @@
     <t>下跌</t>
   </si>
   <si>
-    <t>转换</t>
-  </si>
-  <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>UP_STEEPENING</t>
-  </si>
-  <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
+    <t>TURNING_DOWN</t>
   </si>
   <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>上升陡坡形成</t>
-  </si>
-  <si>
-    <t>上升坡延续</t>
-  </si>
-  <si>
     <t>下降坡延续</t>
   </si>
   <si>
-    <t>地形转换区</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01058,naive=0.0008404,drift4=0.002095; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.08733,naive=0.01229,drift4=0.02063; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=251.3,naive=54.99,drift4=154; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.009298,naive=0.002891,drift4=0.003579; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01529,naive=0.001746,drift4=0.006008; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01342,naive=0.001242,drift4=0.002569; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.04614,naive=0.007417,drift4=0.01423; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.05792,naive=0.0142,drift4=0.03948; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=6.648,naive=1.943,drift4=2.727; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.1002,naive=0.002691,drift4=0.005859; naive_cap_applied</t>
+    <t>向下转折带</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.05416,naive=0.01193,drift4=0.03615; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=253.6,naive=52.74,drift4=141.2; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.008038,naive=0.002787,drift4=0.003561; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.015,naive=0.001633,drift4=0.006001; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01014,naive=0.000744,drift4=0.001884; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.08505,naive=0.01084,drift4=0.01879; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01296,naive=0.001168,drift4=0.002574; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.04501,naive=0.006183,drift4=0.01426; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=6.575,naive=1.71,drift4=2.4; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.09929,naive=0.006481,drift4=0.009285; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1033,7 +1030,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1057,19 +1054,19 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.8139260349039491</v>
+        <v>0.7627340899366188</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="O2" t="s">
         <v>90</v>
@@ -1084,13 +1081,13 @@
         <v>100</v>
       </c>
       <c r="S2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T2">
-        <v>0.9316469936104604</v>
+        <v>0.9519909109868182</v>
       </c>
       <c r="U2">
-        <v>0.818771331126668</v>
+        <v>0.8279369155102769</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1099,22 +1096,22 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9981207360078433</v>
+        <v>0.9981640222648349</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>0.04010881987763081</v>
       </c>
       <c r="Z2">
-        <v>-36.91044960373866</v>
+        <v>-30.04160606895899</v>
       </c>
       <c r="AA2">
-        <v>37.00000000000001</v>
+        <v>-37</v>
       </c>
       <c r="AB2">
-        <v>0.7995751405528057</v>
+        <v>0.8656620940372549</v>
       </c>
       <c r="AC2">
-        <v>-0.6005660618199808</v>
+        <v>-0.5006287436284845</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1123,67 +1120,67 @@
         <v>112</v>
       </c>
       <c r="AF2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH2">
-        <v>0.3990362638910706</v>
+        <v>0.4493648481532204</v>
       </c>
       <c r="AI2">
-        <v>0.7338323803457383</v>
+        <v>0.7614545481235691</v>
       </c>
       <c r="AJ2">
-        <v>0.6822975428952236</v>
+        <v>0.6795446964577995</v>
       </c>
       <c r="AK2">
-        <v>-0.6387562523090935</v>
+        <v>-0.32049312701577</v>
       </c>
       <c r="AL2">
-        <v>0.7250910476433676</v>
+        <v>0.5106168384412557</v>
       </c>
       <c r="AM2">
-        <v>-1.550986721546837</v>
+        <v>-2.309988956264086</v>
       </c>
       <c r="AN2">
-        <v>0.6218725144078714</v>
+        <v>0.4159035631018527</v>
       </c>
       <c r="AO2">
-        <v>0.03588279615232357</v>
+        <v>0.03748834570550436</v>
       </c>
       <c r="AP2">
-        <v>1.35085</v>
+        <v>4.80765</v>
       </c>
       <c r="AQ2">
-        <v>1.351716906333036</v>
+        <v>4.805976526640246</v>
       </c>
       <c r="AR2">
-        <v>1.355739376581349</v>
+        <v>4.780286426575325</v>
       </c>
       <c r="AS2">
-        <v>1.35085</v>
+        <v>4.80765</v>
       </c>
       <c r="AT2">
-        <v>1.34791</v>
+        <v>4.839659999999999</v>
       </c>
       <c r="AW2">
-        <v>0.0006417487752420818</v>
+        <v>-0.0003480855219813069</v>
       </c>
       <c r="AY2">
-        <v>0.0006417487752420818</v>
+        <v>0.0003480855219813069</v>
       </c>
       <c r="AZ2">
-        <v>0.411131882544</v>
+        <v>0.4594884859737252</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.388868117456</v>
+        <v>0.3405115140262748</v>
       </c>
       <c r="BC2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1216,31 +1213,31 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.01057971044759011</v>
+        <v>0.05416322462120172</v>
       </c>
       <c r="BP2">
-        <v>0.0008403720652294348</v>
+        <v>0.01192824951053599</v>
       </c>
       <c r="BQ2">
-        <v>0.002094711743995104</v>
+        <v>0.03614778818163265</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BW2" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1245,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1260,16 +1257,16 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
         <v>46275</v>
@@ -1278,127 +1275,136 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.2384300129785058</v>
+        <v>0.322878077889677</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S3" t="s">
         <v>106</v>
       </c>
       <c r="T3">
-        <v>-0.8386833152190706</v>
+        <v>0.7568632986052749</v>
       </c>
       <c r="U3">
-        <v>0.7762214031496457</v>
+        <v>0.740508961547742</v>
       </c>
       <c r="V3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W3" t="s">
         <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9952556452042558</v>
+        <v>0.9996819087014734</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>0.02142553806564812</v>
       </c>
       <c r="Z3">
-        <v>-121.7416175324508</v>
+        <v>-72.19627297879811</v>
       </c>
       <c r="AA3">
-        <v>-61</v>
+        <v>-24</v>
       </c>
       <c r="AB3">
-        <v>-0.526089510080176</v>
+        <v>0.3057572391824364</v>
       </c>
       <c r="AC3">
-        <v>-0.8504292018643294</v>
+        <v>-0.9521095056176755</v>
       </c>
       <c r="AD3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AH3">
-        <v>-0.2617967773950182</v>
+        <v>0.1561044550058966</v>
       </c>
       <c r="AI3">
-        <v>0.6417163165867966</v>
+        <v>0.5807521591084351</v>
       </c>
       <c r="AJ3">
-        <v>-0.1519236588311104</v>
+        <v>0.5147719817282685</v>
       </c>
       <c r="AK3">
-        <v>-0.3918344817619402</v>
+        <v>-1.330552561932046</v>
       </c>
       <c r="AL3">
-        <v>-0.4339082491779432</v>
+        <v>-0.1771006120820895</v>
       </c>
       <c r="AM3">
-        <v>0.1170630111252183</v>
+        <v>-2.280037637543915</v>
       </c>
       <c r="AN3">
-        <v>0.4009972801686971</v>
+        <v>0.481562497732405</v>
       </c>
       <c r="AO3">
-        <v>0.09633341505830399</v>
+        <v>0.1009919220329404</v>
       </c>
       <c r="AP3">
-        <v>9.06995</v>
+        <v>4334.84</v>
       </c>
       <c r="AQ3">
-        <v>9.062264986405948</v>
+        <v>4427.834717083972</v>
       </c>
       <c r="AR3">
-        <v>9.106694719785541</v>
+        <v>4574.722889727434</v>
       </c>
       <c r="AS3">
-        <v>9.06995</v>
+        <v>4334.84</v>
       </c>
       <c r="AT3">
-        <v>9.014860000000001</v>
+        <v>4293.950000000001</v>
+      </c>
+      <c r="AU3">
+        <v>4427.834717083972</v>
+      </c>
+      <c r="AV3">
+        <v>4196.02</v>
       </c>
       <c r="AW3">
-        <v>-0.0008473049569239623</v>
+        <v>0.02145286033255491</v>
+      </c>
+      <c r="AX3">
+        <v>0.6698942305429536</v>
       </c>
       <c r="AY3">
-        <v>0.0008473049569239623</v>
+        <v>0.02145286033255491</v>
       </c>
       <c r="AZ3">
-        <v>0.3962225451432942</v>
+        <v>0.4477167193955393</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.4037774548567058</v>
+        <v>0.3522832806044607</v>
       </c>
       <c r="BC3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1407,55 +1413,58 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="BG3">
+        <v>0.0320242500299894</v>
       </c>
       <c r="BH3">
-        <v>0</v>
+        <v>15613.16813139326</v>
       </c>
       <c r="BI3">
-        <v>0</v>
+        <v>11709.87609854494</v>
       </c>
       <c r="BJ3">
-        <v>0</v>
+        <v>2.701339864572843</v>
       </c>
       <c r="BK3">
-        <v>0</v>
+        <v>117.0987609854494</v>
       </c>
       <c r="BL3">
-        <v>0</v>
+        <v>0.001170987609854494</v>
       </c>
       <c r="BM3">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="BN3">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="BO3">
-        <v>0.08733135580296883</v>
+        <v>253.640770068784</v>
       </c>
       <c r="BP3">
-        <v>0.0122927090686126</v>
+        <v>52.73837309403296</v>
       </c>
       <c r="BQ3">
-        <v>0.02063253114057767</v>
+        <v>141.173553180838</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT3" t="s">
         <v>137</v>
       </c>
       <c r="BU3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV3" t="s">
         <v>139</v>
       </c>
       <c r="BW3" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1463,7 +1472,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1493,13 +1502,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.322878077889677</v>
+        <v>0.842535182301704</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1511,16 +1520,16 @@
         <v>0.75</v>
       </c>
       <c r="R4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T4">
-        <v>0.7568632986052749</v>
+        <v>0.8990306146348624</v>
       </c>
       <c r="U4">
-        <v>0.740508961547742</v>
+        <v>0.8043107252188452</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1529,22 +1538,22 @@
         <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9996819087014734</v>
+        <v>0.9989877945326281</v>
       </c>
       <c r="Y4">
-        <v>0.02142553806564812</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>-72.19627297879811</v>
+        <v>45.24258405442502</v>
       </c>
       <c r="AA4">
-        <v>-24</v>
+        <v>-26</v>
       </c>
       <c r="AB4">
-        <v>0.3057572391824364</v>
+        <v>0.7041066397461356</v>
       </c>
       <c r="AC4">
-        <v>-0.9521095056176755</v>
+        <v>0.7100942471710396</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
@@ -1559,70 +1568,70 @@
         <v>121</v>
       </c>
       <c r="AH4">
-        <v>0.1561044550058966</v>
+        <v>0.3516969695778859</v>
       </c>
       <c r="AI4">
-        <v>0.5807521591084351</v>
+        <v>0.6998346222889451</v>
       </c>
       <c r="AJ4">
-        <v>0.5147719817282685</v>
+        <v>0.5343667599788634</v>
       </c>
       <c r="AK4">
-        <v>-1.330552561932046</v>
+        <v>0.583276607482987</v>
       </c>
       <c r="AL4">
-        <v>-0.1771006120820895</v>
+        <v>1.524969502733192</v>
       </c>
       <c r="AM4">
-        <v>-2.280037637543915</v>
+        <v>0.2222349447075852</v>
       </c>
       <c r="AN4">
-        <v>0.481562497732405</v>
+        <v>1.503406852245616</v>
       </c>
       <c r="AO4">
-        <v>0.1009919220329404</v>
+        <v>0.07362065147543613</v>
       </c>
       <c r="AP4">
-        <v>4334.84</v>
+        <v>0.81514</v>
       </c>
       <c r="AQ4">
-        <v>4446.281548879775</v>
+        <v>0.8282931887068834</v>
       </c>
       <c r="AR4">
-        <v>4611.885077891402</v>
+        <v>0.8453263477493367</v>
       </c>
       <c r="AS4">
-        <v>4334.84</v>
+        <v>0.81514</v>
       </c>
       <c r="AT4">
-        <v>4293.950000000001</v>
+        <v>0.816905</v>
       </c>
       <c r="AU4">
-        <v>4446.281548879775</v>
+        <v>0.8282931887068834</v>
       </c>
       <c r="AV4">
-        <v>4196.02</v>
+        <v>0.8058500000000001</v>
       </c>
       <c r="AW4">
-        <v>0.02570834191798888</v>
+        <v>0.01613611000181984</v>
       </c>
       <c r="AX4">
-        <v>0.8027773294898107</v>
+        <v>1.415843778997149</v>
       </c>
       <c r="AY4">
-        <v>0.02570834191798888</v>
+        <v>0.01613611000181984</v>
       </c>
       <c r="AZ4">
-        <v>0.4534056129818229</v>
+        <v>0.4131116092887429</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3465943870181771</v>
+        <v>0.386888390711257</v>
       </c>
       <c r="BC4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1634,22 +1643,22 @@
         <v>375</v>
       </c>
       <c r="BG4">
-        <v>0.0320242500299894</v>
+        <v>0.01139681527099632</v>
       </c>
       <c r="BH4">
-        <v>15613.16813139326</v>
+        <v>43871.90527448899</v>
       </c>
       <c r="BI4">
-        <v>11709.87609854494</v>
+        <v>32903.92895586674</v>
       </c>
       <c r="BJ4">
-        <v>2.701339864572843</v>
+        <v>40365.98493003257</v>
       </c>
       <c r="BK4">
-        <v>117.0987609854494</v>
+        <v>329.0392895586675</v>
       </c>
       <c r="BL4">
-        <v>0.001170987609854494</v>
+        <v>0.003290392895586675</v>
       </c>
       <c r="BM4">
         <v>375</v>
@@ -1658,31 +1667,31 @@
         <v>0.00375</v>
       </c>
       <c r="BO4">
-        <v>251.2786261803798</v>
+        <v>0.0080377624977401</v>
       </c>
       <c r="BP4">
-        <v>54.98597491165516</v>
+        <v>0.002787161062652727</v>
       </c>
       <c r="BQ4">
-        <v>153.9943401860568</v>
+        <v>0.00356056961030392</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU4" t="s">
         <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW4" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1690,7 +1699,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1702,7 +1711,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1717,16 +1726,16 @@
         <v>46275</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.9831164404353598</v>
       </c>
       <c r="L5">
-        <v>0.842535182301704</v>
+        <v>2.401175662286452</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="O5" t="s">
         <v>95</v>
@@ -1735,19 +1744,19 @@
         <v>98</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>0.99577911010884</v>
       </c>
       <c r="R5" t="s">
         <v>102</v>
       </c>
       <c r="S5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T5">
-        <v>0.8990306146348624</v>
+        <v>0.9928059095650883</v>
       </c>
       <c r="U5">
-        <v>0.8043107252188452</v>
+        <v>0.9940720574079374</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1756,22 +1765,22 @@
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9989877945326281</v>
+        <v>0.9993677281533742</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>45.24258405442502</v>
+        <v>-9.719262686398665</v>
       </c>
       <c r="AA5">
-        <v>-26</v>
+        <v>-15</v>
       </c>
       <c r="AB5">
-        <v>0.7041066397461356</v>
+        <v>0.9856467677090055</v>
       </c>
       <c r="AC5">
-        <v>0.7100942471710396</v>
+        <v>-0.1688207608820363</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1780,76 +1789,76 @@
         <v>112</v>
       </c>
       <c r="AF5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AH5">
-        <v>0.3516969695778859</v>
+        <v>0.9850235710070653</v>
       </c>
       <c r="AI5">
-        <v>0.6998346222889451</v>
+        <v>0.9907626449903175</v>
       </c>
       <c r="AJ5">
-        <v>0.5343667599788634</v>
+        <v>1.983129691611978</v>
       </c>
       <c r="AK5">
-        <v>0.583276607482987</v>
+        <v>-0.2703621536126906</v>
       </c>
       <c r="AL5">
-        <v>1.524969502733192</v>
+        <v>2.291754641934131</v>
       </c>
       <c r="AM5">
-        <v>0.2222349447075852</v>
+        <v>-5.059268123616951</v>
       </c>
       <c r="AN5">
-        <v>1.503406852245616</v>
+        <v>1.871991524109026</v>
       </c>
       <c r="AO5">
-        <v>0.07362065147543613</v>
+        <v>0.03140060117376767</v>
       </c>
       <c r="AP5">
-        <v>0.81514</v>
+        <v>0.717435</v>
       </c>
       <c r="AQ5">
-        <v>0.8263414089051424</v>
+        <v>0.7199496164202837</v>
       </c>
       <c r="AR5">
-        <v>0.8411058795030792</v>
+        <v>0.715826619335206</v>
       </c>
       <c r="AS5">
-        <v>0.81514</v>
+        <v>0.717435</v>
       </c>
       <c r="AT5">
-        <v>0.816905</v>
+        <v>0.7265900000000001</v>
       </c>
       <c r="AU5">
-        <v>0.8263414089051424</v>
+        <v>0.7199496164202837</v>
       </c>
       <c r="AV5">
-        <v>0.8058500000000001</v>
+        <v>0.7102262500000001</v>
       </c>
       <c r="AW5">
-        <v>0.01374169946897764</v>
+        <v>0.003505009401943884</v>
       </c>
       <c r="AX5">
-        <v>1.205749074826965</v>
+        <v>0.3488283572441318</v>
       </c>
       <c r="AY5">
-        <v>0.01374169946897764</v>
+        <v>0.003505009401943884</v>
       </c>
       <c r="AZ5">
-        <v>0.4045063281231875</v>
+        <v>0.4468283459905349</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3954936718768126</v>
+        <v>0.3531716540094652</v>
       </c>
       <c r="BC5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1858,58 +1867,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>375</v>
+        <v>497.88955505442</v>
       </c>
       <c r="BG5">
-        <v>0.01139681527099632</v>
+        <v>0.01004794859464611</v>
       </c>
       <c r="BH5">
-        <v>43871.90527448899</v>
+        <v>49761.40107508285</v>
       </c>
       <c r="BI5">
-        <v>32903.92895586674</v>
+        <v>49551.36368031507</v>
       </c>
       <c r="BJ5">
-        <v>40365.98493003257</v>
+        <v>69067.39102541006</v>
       </c>
       <c r="BK5">
-        <v>329.0392895586675</v>
+        <v>495.5136368031507</v>
       </c>
       <c r="BL5">
-        <v>0.003290392895586675</v>
+        <v>0.004955136368031507</v>
       </c>
       <c r="BM5">
-        <v>375</v>
+        <v>497.88955505442</v>
       </c>
       <c r="BN5">
-        <v>0.00375</v>
+        <v>0.0049788955505442</v>
       </c>
       <c r="BO5">
-        <v>0.009297778296498053</v>
+        <v>0.0149960787581731</v>
       </c>
       <c r="BP5">
-        <v>0.002890902141619793</v>
+        <v>0.0016328793473709</v>
       </c>
       <c r="BQ5">
-        <v>0.003579236066269589</v>
+        <v>0.006000820785021219</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW5" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1917,7 +1926,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1944,16 +1953,16 @@
         <v>46275</v>
       </c>
       <c r="K6">
-        <v>0.9831164404353598</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>2.401175662286452</v>
+        <v>0.8139260349039491</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
@@ -1962,19 +1971,19 @@
         <v>98</v>
       </c>
       <c r="Q6">
-        <v>0.99577911010884</v>
+        <v>0.75</v>
       </c>
       <c r="R6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="T6">
-        <v>0.9928059095650883</v>
+        <v>0.9316469936104604</v>
       </c>
       <c r="U6">
-        <v>0.9940720574079374</v>
+        <v>0.818771331126668</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1983,22 +1992,22 @@
         <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9993677281533742</v>
+        <v>0.9981207360078433</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>-9.719262686398665</v>
+        <v>-36.91044960373866</v>
       </c>
       <c r="AA6">
-        <v>-15</v>
+        <v>37.00000000000001</v>
       </c>
       <c r="AB6">
-        <v>0.9856467677090055</v>
+        <v>0.7995751405528057</v>
       </c>
       <c r="AC6">
-        <v>-0.1688207608820363</v>
+        <v>-0.6005660618199808</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -2007,76 +2016,76 @@
         <v>112</v>
       </c>
       <c r="AF6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AH6">
-        <v>0.9850235710070653</v>
+        <v>0.3990362638910706</v>
       </c>
       <c r="AI6">
-        <v>0.9907626449903175</v>
+        <v>0.7338323803457383</v>
       </c>
       <c r="AJ6">
-        <v>1.983129691611978</v>
+        <v>0.6822975428952236</v>
       </c>
       <c r="AK6">
-        <v>-0.2703621536126906</v>
+        <v>-0.6387562523090935</v>
       </c>
       <c r="AL6">
-        <v>2.291754641934131</v>
+        <v>0.7250910476433676</v>
       </c>
       <c r="AM6">
-        <v>-5.059268123616951</v>
+        <v>-1.550986721546837</v>
       </c>
       <c r="AN6">
-        <v>1.871991524109026</v>
+        <v>0.6218725144078714</v>
       </c>
       <c r="AO6">
-        <v>0.03140060117376767</v>
+        <v>0.03588279615232357</v>
       </c>
       <c r="AP6">
-        <v>0.717435</v>
+        <v>1.35085</v>
       </c>
       <c r="AQ6">
-        <v>0.7191015946846109</v>
+        <v>1.352546653195616</v>
       </c>
       <c r="AR6">
-        <v>0.7138404000294738</v>
+        <v>1.357770299305861</v>
       </c>
       <c r="AS6">
-        <v>0.717435</v>
+        <v>1.35085</v>
       </c>
       <c r="AT6">
-        <v>0.7265900000000001</v>
+        <v>1.34791</v>
       </c>
       <c r="AU6">
-        <v>0.7191015946846109</v>
+        <v>1.352876275</v>
       </c>
       <c r="AV6">
-        <v>0.7102262500000001</v>
+        <v>1.339425</v>
       </c>
       <c r="AW6">
-        <v>0.002322990493369899</v>
+        <v>0.001255989336799763</v>
       </c>
       <c r="AX6">
-        <v>0.2311905232683683</v>
+        <v>0.177354485776805</v>
       </c>
       <c r="AY6">
-        <v>0.002322990493369899</v>
+        <v>0.001255989336799763</v>
       </c>
       <c r="AZ6">
-        <v>0.4437319859813307</v>
+        <v>0.4106014503240862</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3562680140186693</v>
+        <v>0.3893985496759138</v>
       </c>
       <c r="BC6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2085,58 +2094,58 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>497.88955505442</v>
+        <v>375</v>
       </c>
       <c r="BG6">
-        <v>0.01004794859464611</v>
+        <v>0.008457637783617735</v>
       </c>
       <c r="BH6">
-        <v>49761.40107508285</v>
+        <v>59118.16192560166</v>
       </c>
       <c r="BI6">
-        <v>49551.36368031507</v>
+        <v>44338.62144420124</v>
       </c>
       <c r="BJ6">
-        <v>69067.39102541006</v>
+        <v>32822.75711159732</v>
       </c>
       <c r="BK6">
-        <v>495.5136368031507</v>
+        <v>443.3862144420124</v>
       </c>
       <c r="BL6">
-        <v>0.004955136368031507</v>
+        <v>0.004433862144420124</v>
       </c>
       <c r="BM6">
-        <v>497.88955505442</v>
+        <v>375</v>
       </c>
       <c r="BN6">
-        <v>0.0049788955505442</v>
+        <v>0.00375</v>
       </c>
       <c r="BO6">
-        <v>0.01528697777717799</v>
+        <v>0.01014450835210188</v>
       </c>
       <c r="BP6">
-        <v>0.001745837371191456</v>
+        <v>0.0007440307316506343</v>
       </c>
       <c r="BQ6">
-        <v>0.006007722439466404</v>
+        <v>0.001883996649498649</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU6" t="s">
         <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW6" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2144,7 +2153,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2165,145 +2174,145 @@
         <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J7" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K7">
-        <v>0.06213464408790158</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.205848195906553</v>
+        <v>0.281499877920296</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q7">
-        <v>0.9533990169340738</v>
+        <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="S7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="T7">
-        <v>0.9404449150584619</v>
+        <v>-0.8897938918869088</v>
       </c>
       <c r="U7">
-        <v>0.8324109017031668</v>
+        <v>0.7992171690588966</v>
       </c>
       <c r="V7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W7" t="s">
         <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9995619732546944</v>
+        <v>0.9952396708391507</v>
       </c>
       <c r="Y7">
-        <v>0.1778889054644588</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>-31.62603587327359</v>
+        <v>-132.5502794454923</v>
       </c>
       <c r="AA7">
-        <v>1.000000000000001</v>
+        <v>-68</v>
       </c>
       <c r="AB7">
-        <v>0.8514887408819645</v>
+        <v>-0.6762369391362666</v>
       </c>
       <c r="AC7">
-        <v>-0.5243728865523529</v>
+        <v>-0.736684194310977</v>
       </c>
       <c r="AD7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AH7">
-        <v>0.5012599090422775</v>
+        <v>-0.3365089143576264</v>
       </c>
       <c r="AI7">
-        <v>0.7852230296161203</v>
+        <v>0.6894951858989864</v>
       </c>
       <c r="AJ7">
-        <v>1.060783840176871</v>
+        <v>-0.1888515677004071</v>
       </c>
       <c r="AK7">
-        <v>-0.6571496114157754</v>
+        <v>-0.3091809003988046</v>
       </c>
       <c r="AL7">
-        <v>0.8512635793615695</v>
+        <v>-0.4667626019016398</v>
       </c>
       <c r="AM7">
-        <v>-3.082724975108901</v>
+        <v>0.1693803799238007</v>
       </c>
       <c r="AN7">
-        <v>0.6491904612606465</v>
+        <v>0.4334020959173555</v>
       </c>
       <c r="AO7">
-        <v>0.03765376253669189</v>
+        <v>0.07806520423730776</v>
       </c>
       <c r="AP7">
-        <v>1.159365</v>
+        <v>9.066660000000001</v>
       </c>
       <c r="AQ7">
-        <v>1.155339066821759</v>
+        <v>9.051729262597892</v>
       </c>
       <c r="AR7">
-        <v>1.146974055969008</v>
+        <v>9.088577291440565</v>
       </c>
       <c r="AS7">
-        <v>1.159365</v>
+        <v>9.066660000000001</v>
       </c>
       <c r="AT7">
-        <v>1.161715</v>
+        <v>9.008280000000001</v>
       </c>
       <c r="AU7">
-        <v>1.155339066821759</v>
+        <v>9.051729262597892</v>
       </c>
       <c r="AV7">
-        <v>1.16918875</v>
+        <v>9.146257500000001</v>
       </c>
       <c r="AW7">
-        <v>-0.003472532962648196</v>
+        <v>-0.00164677371844856</v>
       </c>
       <c r="AX7">
-        <v>0.4098163306517997</v>
+        <v>0.1875779691838169</v>
       </c>
       <c r="AY7">
-        <v>0.003472532962648196</v>
+        <v>0.00164677371844856</v>
       </c>
       <c r="AZ7">
-        <v>0.400648232964173</v>
+        <v>0.3956953220695952</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.399351767035827</v>
+        <v>0.4043046779304048</v>
       </c>
       <c r="BC7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2312,58 +2321,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>476.6995084670369</v>
+        <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.008473388449711712</v>
+        <v>0.008779142484663565</v>
       </c>
       <c r="BH7">
-        <v>59008.27077236278</v>
+        <v>56953.17063978157</v>
       </c>
       <c r="BI7">
-        <v>56258.42734535032</v>
+        <v>42714.87797983618</v>
       </c>
       <c r="BJ7">
-        <v>48525.20763120356</v>
+        <v>4711.203241307844</v>
       </c>
       <c r="BK7">
-        <v>562.5842734535032</v>
+        <v>427.1487797983618</v>
       </c>
       <c r="BL7">
-        <v>0.005625842734535032</v>
+        <v>0.004271487797983618</v>
       </c>
       <c r="BM7">
-        <v>476.6995084670369</v>
+        <v>375</v>
       </c>
       <c r="BN7">
-        <v>0.004766995084670368</v>
+        <v>0.00375</v>
       </c>
       <c r="BO7">
-        <v>0.01341962399988159</v>
+        <v>0.0850540746492163</v>
       </c>
       <c r="BP7">
-        <v>0.001242150364604664</v>
+        <v>0.01083563724936053</v>
       </c>
       <c r="BQ7">
-        <v>0.00256926938828844</v>
+        <v>0.01879409358478494</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU7" t="s">
         <v>92</v>
       </c>
       <c r="BV7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW7" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2371,7 +2380,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2383,7 +2392,7 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
         <v>92</v>
@@ -2392,145 +2401,145 @@
         <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J8" s="2">
         <v>46275</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.06213464408790158</v>
       </c>
       <c r="L8">
-        <v>3.856630204854587</v>
+        <v>1.205848195906553</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.9533990169340738</v>
       </c>
       <c r="R8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T8">
-        <v>-0.9995502225675734</v>
+        <v>0.9404449150584619</v>
       </c>
       <c r="U8">
-        <v>0.9997581877229801</v>
+        <v>0.8324109017031668</v>
       </c>
       <c r="V8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W8" t="s">
         <v>95</v>
       </c>
       <c r="X8">
-        <v>0.999842350270288</v>
+        <v>0.9995619732546944</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0.1778889054644588</v>
       </c>
       <c r="Z8">
-        <v>-177.5694691317406</v>
+        <v>-31.62603587327359</v>
       </c>
       <c r="AA8">
-        <v>-4.999999999999995</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="AB8">
-        <v>-0.9991003742166761</v>
+        <v>0.8514887408819645</v>
       </c>
       <c r="AC8">
-        <v>-0.0424080445210326</v>
+        <v>-0.5243728865523529</v>
       </c>
       <c r="AD8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF8" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AH8">
-        <v>-0.9989428663127257</v>
+        <v>0.5012599090422775</v>
       </c>
       <c r="AI8">
-        <v>0.9945802336410562</v>
+        <v>0.7852230296161203</v>
       </c>
       <c r="AJ8">
-        <v>-2.946833510094436</v>
+        <v>1.060783840176871</v>
       </c>
       <c r="AK8">
-        <v>-0.1538033138105544</v>
+        <v>-0.6571496114157754</v>
       </c>
       <c r="AL8">
-        <v>-4.73947218000892</v>
+        <v>0.8512635793615695</v>
       </c>
       <c r="AM8">
-        <v>4.920456880994661</v>
+        <v>-3.082724975108901</v>
       </c>
       <c r="AN8">
-        <v>4.291788192979363</v>
+        <v>0.6491904612606465</v>
       </c>
       <c r="AO8">
-        <v>0.03396467479031572</v>
+        <v>0.03765376253669189</v>
       </c>
       <c r="AP8">
-        <v>6.708905</v>
+        <v>1.159365</v>
       </c>
       <c r="AQ8">
-        <v>6.67613667042478</v>
+        <v>1.157394789335092</v>
       </c>
       <c r="AR8">
-        <v>6.661298338846341</v>
+        <v>1.152203839598265</v>
       </c>
       <c r="AS8">
-        <v>6.708905</v>
+        <v>1.159365</v>
       </c>
       <c r="AT8">
-        <v>6.67498</v>
+        <v>1.161715</v>
       </c>
       <c r="AU8">
-        <v>6.67613667042478</v>
+        <v>1.157394789335092</v>
       </c>
       <c r="AV8">
-        <v>6.732411249999999</v>
+        <v>1.16918875</v>
       </c>
       <c r="AW8">
-        <v>-0.004884303709058254</v>
+        <v>-0.001699387738035516</v>
       </c>
       <c r="AX8">
-        <v>1.394026251538208</v>
+        <v>0.2005558635864656</v>
       </c>
       <c r="AY8">
-        <v>0.004884303709058254</v>
+        <v>0.001699387738035516</v>
       </c>
       <c r="AZ8">
-        <v>0.411377647202952</v>
+        <v>0.4048097710774992</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.388622352797048</v>
+        <v>0.3951902289225008</v>
       </c>
       <c r="BC8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2539,58 +2548,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>500</v>
+        <v>476.6995084670369</v>
       </c>
       <c r="BG8">
-        <v>0.003503738687609918</v>
+        <v>0.008473388449711712</v>
       </c>
       <c r="BH8">
-        <v>142704.7061951632</v>
+        <v>59008.27077236278</v>
       </c>
       <c r="BI8">
-        <v>142704.7061951632</v>
+        <v>56258.42734535032</v>
       </c>
       <c r="BJ8">
-        <v>21270.9385801652</v>
+        <v>48525.20763120356</v>
       </c>
       <c r="BK8">
-        <v>1427.047061951632</v>
+        <v>562.5842734535032</v>
       </c>
       <c r="BL8">
-        <v>0.01427047061951632</v>
+        <v>0.005625842734535032</v>
       </c>
       <c r="BM8">
-        <v>499.9999999999999</v>
+        <v>476.6995084670369</v>
       </c>
       <c r="BN8">
-        <v>0.004999999999999999</v>
+        <v>0.004766995084670368</v>
       </c>
       <c r="BO8">
-        <v>0.04613806075758249</v>
+        <v>0.01295604445848304</v>
       </c>
       <c r="BP8">
-        <v>0.00741716609185992</v>
+        <v>0.001168285683265811</v>
       </c>
       <c r="BQ8">
-        <v>0.01423138400495298</v>
+        <v>0.002574122045654231</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU8" t="s">
         <v>92</v>
       </c>
       <c r="BV8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW8" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2598,7 +2607,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2619,73 +2628,73 @@
         <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
         <v>46275</v>
       </c>
       <c r="K9">
-        <v>0.1466153677489054</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0.8916981049182402</v>
+        <v>3.856630204854587</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="O9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q9">
-        <v>0.8900384741883209</v>
+        <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T9">
-        <v>0.9937501621635167</v>
+        <v>-0.9995502225675734</v>
       </c>
       <c r="U9">
-        <v>0.8687640725410471</v>
+        <v>0.9997581877229801</v>
       </c>
       <c r="V9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W9" t="s">
         <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9983367776205151</v>
+        <v>0.999842350270288</v>
       </c>
       <c r="Y9">
-        <v>0.0861904706490934</v>
+        <v>1</v>
       </c>
       <c r="Z9">
-        <v>-10.70146987287008</v>
+        <v>-177.5694691317406</v>
       </c>
       <c r="AA9">
-        <v>-25</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB9">
-        <v>0.9826080331064223</v>
+        <v>-0.9991003742166761</v>
       </c>
       <c r="AC9">
-        <v>-0.185691823392222</v>
+        <v>-0.0424080445210326</v>
       </c>
       <c r="AD9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF9" t="s">
         <v>118</v>
@@ -2694,70 +2703,70 @@
         <v>124</v>
       </c>
       <c r="AH9">
-        <v>0.532762162779732</v>
+        <v>-0.9989428663127257</v>
       </c>
       <c r="AI9">
-        <v>0.8065536943702535</v>
+        <v>0.9945802336410562</v>
       </c>
       <c r="AJ9">
-        <v>0.7721394961939267</v>
+        <v>-2.946833510094436</v>
       </c>
       <c r="AK9">
-        <v>-0.09740858997026673</v>
+        <v>-0.1538033138105544</v>
       </c>
       <c r="AL9">
-        <v>0.6952620954468656</v>
+        <v>-4.73947218000892</v>
       </c>
       <c r="AM9">
-        <v>-2.436636701598483</v>
+        <v>4.920456880994661</v>
       </c>
       <c r="AN9">
-        <v>0.5520612450243971</v>
+        <v>4.291788192979363</v>
       </c>
       <c r="AO9">
-        <v>0.0325645457244813</v>
+        <v>0.03396467479031572</v>
       </c>
       <c r="AP9">
-        <v>4.80355</v>
+        <v>6.708905</v>
       </c>
       <c r="AQ9">
-        <v>4.774964635314872</v>
+        <v>6.691302020365384</v>
       </c>
       <c r="AR9">
-        <v>4.720351963962985</v>
+        <v>6.697674712959005</v>
       </c>
       <c r="AS9">
-        <v>4.80355</v>
+        <v>6.708905</v>
       </c>
       <c r="AT9">
-        <v>4.831460000000001</v>
+        <v>6.67498</v>
       </c>
       <c r="AU9">
-        <v>4.774964635314872</v>
+        <v>6.691302020365384</v>
       </c>
       <c r="AV9">
-        <v>4.843350000000001</v>
+        <v>6.732411249999999</v>
       </c>
       <c r="AW9">
-        <v>-0.005950883135416089</v>
+        <v>-0.002623823058250985</v>
       </c>
       <c r="AX9">
-        <v>0.7182252433449224</v>
+        <v>0.7488637972716027</v>
       </c>
       <c r="AY9">
-        <v>0.005950883135416089</v>
+        <v>0.002623823058250985</v>
       </c>
       <c r="AZ9">
-        <v>0.4582329640690144</v>
+        <v>0.4202309314337658</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3417670359309857</v>
+        <v>0.3797690685662343</v>
       </c>
       <c r="BC9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2766,58 +2775,58 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>445.0192370941605</v>
+        <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.008285538820247537</v>
+        <v>0.003503738687609918</v>
       </c>
       <c r="BH9">
-        <v>60346.10552763811</v>
+        <v>142704.7061951632</v>
       </c>
       <c r="BI9">
-        <v>53710.35568702642</v>
+        <v>142704.7061951632</v>
       </c>
       <c r="BJ9">
-        <v>11181.38786668743</v>
+        <v>21270.9385801652</v>
       </c>
       <c r="BK9">
-        <v>537.1035568702642</v>
+        <v>1427.047061951632</v>
       </c>
       <c r="BL9">
-        <v>0.005371035568702643</v>
+        <v>0.01427047061951632</v>
       </c>
       <c r="BM9">
-        <v>445.0192370941605</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN9">
-        <v>0.004450192370941605</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO9">
-        <v>0.05791762915334398</v>
+        <v>0.04501432006535262</v>
       </c>
       <c r="BP9">
-        <v>0.01420306494004293</v>
+        <v>0.006182702321116425</v>
       </c>
       <c r="BQ9">
-        <v>0.03947596667097171</v>
+        <v>0.01425612675470795</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU9" t="s">
         <v>92</v>
       </c>
       <c r="BV9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW9" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2825,7 +2834,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2873,10 +2882,10 @@
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T10">
         <v>-0.8377920202772901</v>
@@ -2915,10 +2924,10 @@
         <v>113</v>
       </c>
       <c r="AF10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AH10">
         <v>-0.6754203788697517</v>
@@ -2948,10 +2957,10 @@
         <v>154.005</v>
       </c>
       <c r="AQ10">
-        <v>152.8274495046455</v>
+        <v>153.4923920928062</v>
       </c>
       <c r="AR10">
-        <v>156.1492651411993</v>
+        <v>157.8927700151773</v>
       </c>
       <c r="AS10">
         <v>154.005</v>
@@ -2960,31 +2969,31 @@
         <v>148.694</v>
       </c>
       <c r="AU10">
-        <v>152.8274495046455</v>
+        <v>153.4923920928062</v>
       </c>
       <c r="AV10">
         <v>155.1685</v>
       </c>
       <c r="AW10">
-        <v>-0.007646183535303833</v>
+        <v>-0.003328514705326244</v>
       </c>
       <c r="AX10">
-        <v>1.012076059608469</v>
+        <v>0.4405740500161257</v>
       </c>
       <c r="AY10">
-        <v>0.007646183535303833</v>
+        <v>0.003328514705326244</v>
       </c>
       <c r="AZ10">
-        <v>0.4119571130573444</v>
+        <v>0.4061621376164218</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3880428869426555</v>
+        <v>0.3938378623835782</v>
       </c>
       <c r="BC10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -3020,31 +3029,31 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO10">
-        <v>6.647980933792516</v>
+        <v>6.575172045332947</v>
       </c>
       <c r="BP10">
-        <v>1.943333086653392</v>
+        <v>1.709764413386216</v>
       </c>
       <c r="BQ10">
-        <v>2.727261215210651</v>
+        <v>2.400296257769454</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU10" t="s">
         <v>92</v>
       </c>
       <c r="BV10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW10" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3052,7 +3061,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3076,19 +3085,19 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.007077295597485317</v>
+        <v>0.138907574804795</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O11" t="s">
         <v>96</v>
@@ -3100,118 +3109,118 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="S11" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="T11">
-        <v>0.6039828205957997</v>
+        <v>0.4648788460450831</v>
       </c>
       <c r="U11">
-        <v>0.6206553275968192</v>
+        <v>0.5085445576424406</v>
       </c>
       <c r="V11" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="W11" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="X11">
-        <v>0.9954522333148373</v>
+        <v>0.9973963076886128</v>
       </c>
       <c r="Y11">
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>-92.29915559941685</v>
+        <v>-103.7510891352802</v>
       </c>
       <c r="AA11">
-        <v>-68</v>
+        <v>-71</v>
       </c>
       <c r="AB11">
-        <v>-0.040117066830479</v>
+        <v>-0.2377043565213686</v>
       </c>
       <c r="AC11">
-        <v>-0.9991949864510524</v>
+        <v>-0.9713375514674402</v>
       </c>
       <c r="AD11" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AH11">
-        <v>-0.01996731188522045</v>
+        <v>-0.1185427237579554</v>
       </c>
       <c r="AI11">
-        <v>0.4827768605672526</v>
+        <v>0.5419526672058479</v>
       </c>
       <c r="AJ11">
-        <v>0.09041128214031938</v>
+        <v>-0.01724737476143526</v>
       </c>
       <c r="AK11">
-        <v>-0.4586118257574019</v>
+        <v>-0.4600429033012642</v>
       </c>
       <c r="AL11">
-        <v>-0.4808385627583562</v>
+        <v>-0.6831301709401844</v>
       </c>
       <c r="AM11">
-        <v>-0.8782450330104122</v>
+        <v>-0.9812357988182752</v>
       </c>
       <c r="AN11">
-        <v>0.5245460561227651</v>
+        <v>0.7337126753893859</v>
       </c>
       <c r="AO11">
-        <v>0.1844436076138944</v>
+        <v>0.1896489829438474</v>
       </c>
       <c r="AP11">
-        <v>7.7944</v>
+        <v>7.7789</v>
       </c>
       <c r="AQ11">
-        <v>7.71940724798757</v>
+        <v>7.736027912478734</v>
       </c>
       <c r="AR11">
-        <v>7.608833488588298</v>
+        <v>7.689760141772378</v>
       </c>
       <c r="AS11">
-        <v>7.7944</v>
+        <v>7.7789</v>
       </c>
       <c r="AT11">
-        <v>7.786300000000001</v>
+        <v>7.7553</v>
       </c>
       <c r="AU11">
-        <v>7.71940724798757</v>
+        <v>7.736027912478734</v>
       </c>
       <c r="AV11">
-        <v>7.844395168008287</v>
+        <v>7.828575000000001</v>
       </c>
       <c r="AW11">
-        <v>-0.009621363031462339</v>
+        <v>-0.005511330332214813</v>
       </c>
       <c r="AX11">
-        <v>1.5</v>
+        <v>0.8630515857325679</v>
       </c>
       <c r="AY11">
-        <v>0.009621363031462339</v>
+        <v>0.005511330332214813</v>
       </c>
       <c r="AZ11">
-        <v>0.3860601725217242</v>
+        <v>0.3660686515057779</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4139398274782758</v>
+        <v>0.4339313484942221</v>
       </c>
       <c r="BC11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3223,22 +3232,22 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.006414242020974893</v>
+        <v>0.006385864325290282</v>
       </c>
       <c r="BH11">
-        <v>77951.53322325148</v>
+        <v>78297.93658781993</v>
       </c>
       <c r="BI11">
-        <v>77951.53322325148</v>
+        <v>78297.93658781993</v>
       </c>
       <c r="BJ11">
-        <v>10000.96649174426</v>
+        <v>10065.4252642173</v>
       </c>
       <c r="BK11">
-        <v>779.5153322325148</v>
+        <v>782.9793658781994</v>
       </c>
       <c r="BL11">
-        <v>0.007795153322325147</v>
+        <v>0.007829793658781994</v>
       </c>
       <c r="BM11">
         <v>500.0000000000001</v>
@@ -3247,31 +3256,31 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO11">
-        <v>0.1002197002616151</v>
+        <v>0.09928691399953375</v>
       </c>
       <c r="BP11">
-        <v>0.002691348015251937</v>
+        <v>0.00648060160307601</v>
       </c>
       <c r="BQ11">
-        <v>0.005858586046772279</v>
+        <v>0.009285078474765153</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04909719703002575</v>
+        <v>0.05246615174018369</v>
       </c>
       <c r="BT11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BU11" t="s">
         <v>92</v>
       </c>
       <c r="BV11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BW11" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="136">
   <si>
     <t>Pair</t>
   </si>
@@ -322,9 +322,6 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
@@ -340,9 +337,6 @@
     <t>多头加速</t>
   </si>
   <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
@@ -364,9 +358,6 @@
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
@@ -382,9 +373,6 @@
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>上升坡延续</t>
-  </si>
-  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
@@ -394,34 +382,34 @@
     <t>向下转折带</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.05416,naive=0.01193,drift4=0.03615; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=253.6,naive=52.74,drift4=141.2; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.008038,naive=0.002787,drift4=0.003561; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.015,naive=0.001633,drift4=0.006001; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01014,naive=0.000744,drift4=0.001884; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.08505,naive=0.01084,drift4=0.01879; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01296,naive=0.001168,drift4=0.002574; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.04501,naive=0.006183,drift4=0.01426; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=6.575,naive=1.71,drift4=2.4; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.09929,naive=0.006481,drift4=0.009285; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.05362,naive=0.01169,drift4=0.03465; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=263.4,naive=44.17,drift4=120.9; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.006517,naive=0.00333,drift4=0.004275; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01509,naive=0.001974,drift4=0.006409; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.01062,naive=0.0004887,drift4=0.0009109; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.08314,naive=0.008313,drift4=0.01722; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01271,naive=0.0008818,drift4=0.002332; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04378,naive=0.004756,drift4=0.01396; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=6.775,naive=1.663,drift4=2.246; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.09618,naive=0.006031,drift4=0.008515; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1030,7 +1018,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1081,7 +1069,7 @@
         <v>100</v>
       </c>
       <c r="S2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T2">
         <v>0.9519909109868182</v>
@@ -1117,13 +1105,13 @@
         <v>93</v>
       </c>
       <c r="AE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF2" t="s">
         <v>112</v>
       </c>
-      <c r="AF2" t="s">
-        <v>114</v>
-      </c>
       <c r="AG2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AH2">
         <v>0.4493648481532204</v>
@@ -1153,10 +1141,10 @@
         <v>4.80765</v>
       </c>
       <c r="AQ2">
-        <v>4.805976526640246</v>
+        <v>4.806058921660817</v>
       </c>
       <c r="AR2">
-        <v>4.780286426575325</v>
+        <v>4.780197812316881</v>
       </c>
       <c r="AS2">
         <v>4.80765</v>
@@ -1165,22 +1153,22 @@
         <v>4.839659999999999</v>
       </c>
       <c r="AW2">
-        <v>-0.0003480855219813069</v>
+        <v>-0.0003309472068854003</v>
       </c>
       <c r="AY2">
-        <v>0.0003480855219813069</v>
+        <v>0.0003309472068854003</v>
       </c>
       <c r="AZ2">
-        <v>0.4594884859737252</v>
+        <v>0.4574180567342999</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3405115140262748</v>
+        <v>0.3425819432657001</v>
       </c>
       <c r="BC2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1213,31 +1201,31 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.05416322462120172</v>
+        <v>0.053620916871239</v>
       </c>
       <c r="BP2">
-        <v>0.01192824951053599</v>
+        <v>0.01168718323510357</v>
       </c>
       <c r="BQ2">
-        <v>0.03614778818163265</v>
+        <v>0.03464851327399297</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW2" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1245,7 +1233,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1269,19 +1257,19 @@
         <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.322878077889677</v>
+        <v>0.1968159997324024</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1296,13 +1284,13 @@
         <v>100</v>
       </c>
       <c r="S3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T3">
-        <v>0.7568632986052749</v>
+        <v>0.6949642886995006</v>
       </c>
       <c r="U3">
-        <v>0.740508961547742</v>
+        <v>0.7126617526412041</v>
       </c>
       <c r="V3" t="s">
         <v>93</v>
@@ -1311,100 +1299,100 @@
         <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9996819087014734</v>
+        <v>0.9997112909057156</v>
       </c>
       <c r="Y3">
-        <v>0.02142553806564812</v>
+        <v>0.1406307919426623</v>
       </c>
       <c r="Z3">
-        <v>-72.19627297879811</v>
+        <v>-76.798764247509</v>
       </c>
       <c r="AA3">
-        <v>-24</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AB3">
-        <v>0.3057572391824364</v>
+        <v>0.228371868158356</v>
       </c>
       <c r="AC3">
-        <v>-0.9521095056176755</v>
+        <v>-0.9735739775866354</v>
       </c>
       <c r="AD3" t="s">
         <v>93</v>
       </c>
       <c r="AE3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF3" t="s">
         <v>112</v>
       </c>
-      <c r="AF3" t="s">
-        <v>114</v>
-      </c>
       <c r="AG3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AH3">
-        <v>0.1561044550058966</v>
+        <v>0.1302063897923587</v>
       </c>
       <c r="AI3">
-        <v>0.5807521591084351</v>
+        <v>0.5783253456726923</v>
       </c>
       <c r="AJ3">
-        <v>0.5147719817282685</v>
+        <v>0.4285505175192901</v>
       </c>
       <c r="AK3">
-        <v>-1.330552561932046</v>
+        <v>-1.46968865365661</v>
       </c>
       <c r="AL3">
-        <v>-0.1771006120820895</v>
+        <v>-0.2616187175915644</v>
       </c>
       <c r="AM3">
-        <v>-2.280037637543915</v>
+        <v>-1.91773203214572</v>
       </c>
       <c r="AN3">
-        <v>0.481562497732405</v>
+        <v>0.4823579895471006</v>
       </c>
       <c r="AO3">
-        <v>0.1009919220329404</v>
+        <v>0.1214088332023164</v>
       </c>
       <c r="AP3">
-        <v>4334.84</v>
+        <v>4346.68</v>
       </c>
       <c r="AQ3">
-        <v>4427.834717083972</v>
+        <v>4443.375369279991</v>
       </c>
       <c r="AR3">
-        <v>4574.722889727434</v>
+        <v>4589.93906020166</v>
       </c>
       <c r="AS3">
-        <v>4334.84</v>
+        <v>4346.68</v>
       </c>
       <c r="AT3">
-        <v>4293.950000000001</v>
+        <v>4317.630000000001</v>
       </c>
       <c r="AU3">
-        <v>4427.834717083972</v>
+        <v>4443.375369279991</v>
       </c>
       <c r="AV3">
-        <v>4196.02</v>
+        <v>4207.860000000001</v>
       </c>
       <c r="AW3">
-        <v>0.02145286033255491</v>
+        <v>0.02224579892699502</v>
       </c>
       <c r="AX3">
-        <v>0.6698942305429536</v>
+        <v>0.6965521486816829</v>
       </c>
       <c r="AY3">
-        <v>0.02145286033255491</v>
+        <v>0.02224579892699502</v>
       </c>
       <c r="AZ3">
-        <v>0.4477167193955393</v>
+        <v>0.4404384091780535</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3522832806044607</v>
+        <v>0.3595615908219465</v>
       </c>
       <c r="BC3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1416,55 +1404,55 @@
         <v>375</v>
       </c>
       <c r="BG3">
-        <v>0.0320242500299894</v>
+        <v>0.03193701859810229</v>
       </c>
       <c r="BH3">
-        <v>15613.16813139326</v>
+        <v>15655.81328338864</v>
       </c>
       <c r="BI3">
-        <v>11709.87609854494</v>
+        <v>11741.85996254148</v>
       </c>
       <c r="BJ3">
-        <v>2.701339864572843</v>
+        <v>2.701339864572842</v>
       </c>
       <c r="BK3">
-        <v>117.0987609854494</v>
+        <v>117.4185996254148</v>
       </c>
       <c r="BL3">
-        <v>0.001170987609854494</v>
+        <v>0.001174185996254148</v>
       </c>
       <c r="BM3">
-        <v>375</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN3">
-        <v>0.00375</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO3">
-        <v>253.640770068784</v>
+        <v>263.4138454923627</v>
       </c>
       <c r="BP3">
-        <v>52.73837309403296</v>
+        <v>44.16820764603839</v>
       </c>
       <c r="BQ3">
-        <v>141.173553180838</v>
+        <v>120.906850500924</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU3" t="s">
         <v>91</v>
       </c>
       <c r="BV3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW3" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1472,7 +1460,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1496,19 +1484,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.009441760357892058</v>
       </c>
       <c r="L4">
-        <v>0.842535182301704</v>
+        <v>1.088462135949222</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1517,19 +1505,19 @@
         <v>98</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>0.752360440089473</v>
       </c>
       <c r="R4" t="s">
         <v>101</v>
       </c>
       <c r="S4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T4">
-        <v>0.8990306146348624</v>
+        <v>0.875180513618772</v>
       </c>
       <c r="U4">
-        <v>0.8043107252188452</v>
+        <v>0.7951338869404498</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1538,100 +1526,100 @@
         <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9989877945326281</v>
+        <v>0.9995455670332747</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>0.06857142533282168</v>
       </c>
       <c r="Z4">
-        <v>45.24258405442502</v>
+        <v>48.65576573871741</v>
       </c>
       <c r="AA4">
-        <v>-26</v>
+        <v>-16</v>
       </c>
       <c r="AB4">
-        <v>0.7041066397461356</v>
+        <v>0.6605814722906341</v>
       </c>
       <c r="AC4">
-        <v>0.7100942471710396</v>
+        <v>0.7507543662652507</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AH4">
-        <v>0.3516969695778859</v>
+        <v>0.3527788554698958</v>
       </c>
       <c r="AI4">
-        <v>0.6998346222889451</v>
+        <v>0.7008202970272939</v>
       </c>
       <c r="AJ4">
-        <v>0.5343667599788634</v>
+        <v>0.7097267830372</v>
       </c>
       <c r="AK4">
-        <v>0.583276607482987</v>
+        <v>0.8465006369284063</v>
       </c>
       <c r="AL4">
-        <v>1.524969502733192</v>
+        <v>1.878834130420117</v>
       </c>
       <c r="AM4">
-        <v>0.2222349447075852</v>
+        <v>0.1147461191625324</v>
       </c>
       <c r="AN4">
-        <v>1.503406852245616</v>
+        <v>1.838899944721231</v>
       </c>
       <c r="AO4">
-        <v>0.07362065147543613</v>
+        <v>0.07272918792071138</v>
       </c>
       <c r="AP4">
-        <v>0.81514</v>
+        <v>0.816445</v>
       </c>
       <c r="AQ4">
-        <v>0.8282931887068834</v>
+        <v>0.8316700325145399</v>
       </c>
       <c r="AR4">
-        <v>0.8453263477493367</v>
+        <v>0.848692960966775</v>
       </c>
       <c r="AS4">
-        <v>0.81514</v>
+        <v>0.816445</v>
       </c>
       <c r="AT4">
-        <v>0.816905</v>
+        <v>0.819515</v>
       </c>
       <c r="AU4">
-        <v>0.8282931887068834</v>
+        <v>0.8316700325145399</v>
       </c>
       <c r="AV4">
-        <v>0.8058500000000001</v>
+        <v>0.8062949783236401</v>
       </c>
       <c r="AW4">
-        <v>0.01613611000181984</v>
+        <v>0.01864795854532747</v>
       </c>
       <c r="AX4">
-        <v>1.415843778997149</v>
+        <v>1.5</v>
       </c>
       <c r="AY4">
-        <v>0.01613611000181984</v>
+        <v>0.01864795854532747</v>
       </c>
       <c r="AZ4">
-        <v>0.4131116092887429</v>
+        <v>0.4376259372298113</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.386888390711257</v>
+        <v>0.3623740627701888</v>
       </c>
       <c r="BC4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1640,58 +1628,58 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>375</v>
+        <v>376.1802200447365</v>
       </c>
       <c r="BG4">
-        <v>0.01139681527099632</v>
+        <v>0.01243197236355164</v>
       </c>
       <c r="BH4">
-        <v>43871.90527448899</v>
+        <v>40218.87962572312</v>
       </c>
       <c r="BI4">
-        <v>32903.92895586674</v>
+        <v>30259.09397511458</v>
       </c>
       <c r="BJ4">
-        <v>40365.98493003257</v>
+        <v>37062.01149509714</v>
       </c>
       <c r="BK4">
-        <v>329.0392895586675</v>
+        <v>302.5909397511458</v>
       </c>
       <c r="BL4">
-        <v>0.003290392895586675</v>
+        <v>0.003025909397511458</v>
       </c>
       <c r="BM4">
-        <v>375</v>
+        <v>376.1802200447365</v>
       </c>
       <c r="BN4">
-        <v>0.00375</v>
+        <v>0.003761802200447365</v>
       </c>
       <c r="BO4">
-        <v>0.0080377624977401</v>
+        <v>0.00651714662483238</v>
       </c>
       <c r="BP4">
-        <v>0.002787161062652727</v>
+        <v>0.003329966646145246</v>
       </c>
       <c r="BQ4">
-        <v>0.00356056961030392</v>
+        <v>0.004274606681452132</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU4" t="s">
         <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW4" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1699,7 +1687,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1723,19 +1711,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K5">
-        <v>0.9831164404353598</v>
+        <v>0.703221216942846</v>
       </c>
       <c r="L5">
-        <v>2.401175662286452</v>
+        <v>2.167902143529543</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O5" t="s">
         <v>95</v>
@@ -1744,19 +1732,19 @@
         <v>98</v>
       </c>
       <c r="Q5">
-        <v>0.99577911010884</v>
+        <v>0.9258053042357115</v>
       </c>
       <c r="R5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T5">
-        <v>0.9928059095650883</v>
+        <v>0.9502927037673258</v>
       </c>
       <c r="U5">
-        <v>0.9940720574079374</v>
+        <v>0.9328738465763199</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1765,100 +1753,100 @@
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9993677281533742</v>
+        <v>0.9990357893583854</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0.992041590135873</v>
       </c>
       <c r="Z5">
-        <v>-9.719262686398665</v>
+        <v>-25.1628791310978</v>
       </c>
       <c r="AA5">
-        <v>-15</v>
+        <v>-25</v>
       </c>
       <c r="AB5">
-        <v>0.9856467677090055</v>
+        <v>0.9051027170225241</v>
       </c>
       <c r="AC5">
-        <v>-0.1688207608820363</v>
+        <v>-0.4251929816429767</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
       </c>
       <c r="AE5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF5" t="s">
         <v>112</v>
       </c>
-      <c r="AF5" t="s">
-        <v>116</v>
-      </c>
       <c r="AG5" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="AH5">
-        <v>0.9850235710070653</v>
+        <v>0.9006318908460458</v>
       </c>
       <c r="AI5">
-        <v>0.9907626449903175</v>
+        <v>0.9647992452175191</v>
       </c>
       <c r="AJ5">
-        <v>1.983129691611978</v>
+        <v>1.82472219597571</v>
       </c>
       <c r="AK5">
-        <v>-0.2703621536126906</v>
+        <v>-0.7384305222231893</v>
       </c>
       <c r="AL5">
-        <v>2.291754641934131</v>
+        <v>1.921060464331321</v>
       </c>
       <c r="AM5">
-        <v>-5.059268123616951</v>
+        <v>-5.034163411394008</v>
       </c>
       <c r="AN5">
-        <v>1.871991524109026</v>
+        <v>1.519758685396873</v>
       </c>
       <c r="AO5">
-        <v>0.03140060117376767</v>
+        <v>0.03201609461231736</v>
       </c>
       <c r="AP5">
-        <v>0.717435</v>
+        <v>0.71635</v>
       </c>
       <c r="AQ5">
-        <v>0.7199496164202837</v>
+        <v>0.7185032517562275</v>
       </c>
       <c r="AR5">
-        <v>0.715826619335206</v>
+        <v>0.7147275199379235</v>
       </c>
       <c r="AS5">
-        <v>0.717435</v>
+        <v>0.71635</v>
       </c>
       <c r="AT5">
-        <v>0.7265900000000001</v>
+        <v>0.7244200000000001</v>
       </c>
       <c r="AU5">
-        <v>0.7199496164202837</v>
+        <v>0.7185032517562275</v>
       </c>
       <c r="AV5">
-        <v>0.7102262500000001</v>
+        <v>0.7091412500000001</v>
       </c>
       <c r="AW5">
-        <v>0.003505009401943884</v>
+        <v>0.003005865507402097</v>
       </c>
       <c r="AX5">
-        <v>0.3488283572441318</v>
+        <v>0.2986997407633103</v>
       </c>
       <c r="AY5">
-        <v>0.003505009401943884</v>
+        <v>0.003005865507402097</v>
       </c>
       <c r="AZ5">
-        <v>0.4468283459905349</v>
+        <v>0.4439264477424864</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3531716540094652</v>
+        <v>0.3560735522575136</v>
       </c>
       <c r="BC5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1867,58 +1855,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>497.88955505442</v>
+        <v>462.9026521178557</v>
       </c>
       <c r="BG5">
-        <v>0.01004794859464611</v>
+        <v>0.01006316744608073</v>
       </c>
       <c r="BH5">
-        <v>49761.40107508285</v>
+        <v>49686.14530952016</v>
       </c>
       <c r="BI5">
-        <v>49551.36368031507</v>
+        <v>45999.69687458008</v>
       </c>
       <c r="BJ5">
-        <v>69067.39102541006</v>
+        <v>64213.99717258334</v>
       </c>
       <c r="BK5">
-        <v>495.5136368031507</v>
+        <v>459.9969687458008</v>
       </c>
       <c r="BL5">
-        <v>0.004955136368031507</v>
+        <v>0.004599969687458008</v>
       </c>
       <c r="BM5">
-        <v>497.88955505442</v>
+        <v>462.9026521178557</v>
       </c>
       <c r="BN5">
-        <v>0.0049788955505442</v>
+        <v>0.004629026521178557</v>
       </c>
       <c r="BO5">
-        <v>0.0149960787581731</v>
+        <v>0.0150887628279826</v>
       </c>
       <c r="BP5">
-        <v>0.0016328793473709</v>
+        <v>0.001974182841889695</v>
       </c>
       <c r="BQ5">
-        <v>0.006000820785021219</v>
+        <v>0.006408603985254602</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW5" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1926,7 +1914,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1950,19 +1938,19 @@
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.8139260349039491</v>
+        <v>0.7795846339819062</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
@@ -1977,13 +1965,13 @@
         <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T6">
-        <v>0.9316469936104604</v>
+        <v>0.9451365324997493</v>
       </c>
       <c r="U6">
-        <v>0.818771331126668</v>
+        <v>0.8248317097822648</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1992,100 +1980,100 @@
         <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9981207360078433</v>
+        <v>0.9980810806295107</v>
       </c>
       <c r="Y6">
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>-36.91044960373866</v>
+        <v>-32.95216435618324</v>
       </c>
       <c r="AA6">
-        <v>37.00000000000001</v>
+        <v>42.00000000000001</v>
       </c>
       <c r="AB6">
-        <v>0.7995751405528057</v>
+        <v>0.8391249890020952</v>
       </c>
       <c r="AC6">
-        <v>-0.6005660618199808</v>
+        <v>-0.5439386480405981</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
       </c>
       <c r="AE6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF6" t="s">
         <v>112</v>
       </c>
-      <c r="AF6" t="s">
-        <v>114</v>
-      </c>
       <c r="AG6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AH6">
-        <v>0.3990362638910706</v>
+        <v>0.4187573879032188</v>
       </c>
       <c r="AI6">
-        <v>0.7338323803457383</v>
+        <v>0.7460396725337519</v>
       </c>
       <c r="AJ6">
-        <v>0.6822975428952236</v>
+        <v>0.636973055942427</v>
       </c>
       <c r="AK6">
-        <v>-0.6387562523090935</v>
+        <v>-0.5305780552845913</v>
       </c>
       <c r="AL6">
-        <v>0.7250910476433676</v>
+        <v>0.7658837827235925</v>
       </c>
       <c r="AM6">
-        <v>-1.550986721546837</v>
+        <v>-1.21489278594029</v>
       </c>
       <c r="AN6">
-        <v>0.6218725144078714</v>
+        <v>0.6890771073644926</v>
       </c>
       <c r="AO6">
-        <v>0.03588279615232357</v>
+        <v>0.03350801591470254</v>
       </c>
       <c r="AP6">
-        <v>1.35085</v>
+        <v>1.352595</v>
       </c>
       <c r="AQ6">
-        <v>1.352546653195616</v>
+        <v>1.354687964260656</v>
       </c>
       <c r="AR6">
-        <v>1.357770299305861</v>
+        <v>1.359416933354913</v>
       </c>
       <c r="AS6">
-        <v>1.35085</v>
+        <v>1.352595</v>
       </c>
       <c r="AT6">
-        <v>1.34791</v>
+        <v>1.3514</v>
       </c>
       <c r="AU6">
-        <v>1.352876275</v>
+        <v>1.354687964260656</v>
       </c>
       <c r="AV6">
-        <v>1.339425</v>
+        <v>1.34117</v>
       </c>
       <c r="AW6">
-        <v>0.001255989336799763</v>
+        <v>0.001547369508726866</v>
       </c>
       <c r="AX6">
-        <v>0.177354485776805</v>
+        <v>0.1831916201887451</v>
       </c>
       <c r="AY6">
-        <v>0.001255989336799763</v>
+        <v>0.001547369508726866</v>
       </c>
       <c r="AZ6">
-        <v>0.4106014503240862</v>
+        <v>0.3803155303502502</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3893985496759138</v>
+        <v>0.4196844696497497</v>
       </c>
       <c r="BC6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2097,22 +2085,22 @@
         <v>375</v>
       </c>
       <c r="BG6">
-        <v>0.008457637783617735</v>
+        <v>0.008446726477622658</v>
       </c>
       <c r="BH6">
-        <v>59118.16192560166</v>
+        <v>59194.5295404813</v>
       </c>
       <c r="BI6">
-        <v>44338.62144420124</v>
+        <v>44395.89715536097</v>
       </c>
       <c r="BJ6">
         <v>32822.75711159732</v>
       </c>
       <c r="BK6">
-        <v>443.3862144420124</v>
+        <v>443.9589715536097</v>
       </c>
       <c r="BL6">
-        <v>0.004433862144420124</v>
+        <v>0.004439589715536096</v>
       </c>
       <c r="BM6">
         <v>375</v>
@@ -2121,31 +2109,31 @@
         <v>0.00375</v>
       </c>
       <c r="BO6">
-        <v>0.01014450835210188</v>
+        <v>0.0106178369493113</v>
       </c>
       <c r="BP6">
-        <v>0.0007440307316506343</v>
+        <v>0.0004887141527307132</v>
       </c>
       <c r="BQ6">
-        <v>0.001883996649498649</v>
+        <v>0.0009108716995400334</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU6" t="s">
         <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW6" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2153,7 +2141,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2201,10 +2189,10 @@
         <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T7">
         <v>-0.8897938918869088</v>
@@ -2240,13 +2228,13 @@
         <v>94</v>
       </c>
       <c r="AE7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AG7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AH7">
         <v>-0.3365089143576264</v>
@@ -2276,10 +2264,10 @@
         <v>9.066660000000001</v>
       </c>
       <c r="AQ7">
-        <v>9.051729262597892</v>
+        <v>9.053092559219079</v>
       </c>
       <c r="AR7">
-        <v>9.088577291440565</v>
+        <v>9.09056688054887</v>
       </c>
       <c r="AS7">
         <v>9.066660000000001</v>
@@ -2288,31 +2276,31 @@
         <v>9.008280000000001</v>
       </c>
       <c r="AU7">
-        <v>9.051729262597892</v>
+        <v>9.053060010000001</v>
       </c>
       <c r="AV7">
         <v>9.146257500000001</v>
       </c>
       <c r="AW7">
-        <v>-0.00164677371844856</v>
+        <v>-0.001496410009961905</v>
       </c>
       <c r="AX7">
-        <v>0.1875779691838169</v>
+        <v>0.1708595119193447</v>
       </c>
       <c r="AY7">
-        <v>0.00164677371844856</v>
+        <v>0.001496410009961905</v>
       </c>
       <c r="AZ7">
-        <v>0.3956953220695952</v>
+        <v>0.4026955329701536</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.4043046779304048</v>
+        <v>0.3973044670298464</v>
       </c>
       <c r="BC7" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2348,31 +2336,31 @@
         <v>0.00375</v>
       </c>
       <c r="BO7">
-        <v>0.0850540746492163</v>
+        <v>0.08314150362562781</v>
       </c>
       <c r="BP7">
-        <v>0.01083563724936053</v>
+        <v>0.008312621349684281</v>
       </c>
       <c r="BQ7">
-        <v>0.01879409358478494</v>
+        <v>0.01722297342610176</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU7" t="s">
         <v>92</v>
       </c>
       <c r="BV7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW7" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2380,7 +2368,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2404,19 +2392,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K8">
-        <v>0.06213464408790158</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1.205848195906553</v>
+        <v>1.103416729551548</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O8" t="s">
         <v>96</v>
@@ -2425,19 +2413,19 @@
         <v>99</v>
       </c>
       <c r="Q8">
-        <v>0.9533990169340738</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
         <v>100</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T8">
-        <v>0.9404449150584619</v>
+        <v>0.9115597468132107</v>
       </c>
       <c r="U8">
-        <v>0.8324109017031668</v>
+        <v>0.8101149323188382</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2446,100 +2434,100 @@
         <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9995619732546944</v>
+        <v>0.9996521850115739</v>
       </c>
       <c r="Y8">
-        <v>0.1778889054644588</v>
+        <v>0.1663286017293179</v>
       </c>
       <c r="Z8">
-        <v>-31.62603587327359</v>
+        <v>-38.62909547814716</v>
       </c>
       <c r="AA8">
-        <v>1.000000000000001</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB8">
-        <v>0.8514887408819645</v>
+        <v>0.7812035581881254</v>
       </c>
       <c r="AC8">
-        <v>-0.5243728865523529</v>
+        <v>-0.6242763816405457</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
       </c>
       <c r="AE8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF8" t="s">
         <v>112</v>
       </c>
-      <c r="AF8" t="s">
-        <v>114</v>
-      </c>
       <c r="AG8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="AH8">
-        <v>0.5012599090422775</v>
+        <v>0.4554115727601482</v>
       </c>
       <c r="AI8">
-        <v>0.7852230296161203</v>
+        <v>0.761421320401063</v>
       </c>
       <c r="AJ8">
-        <v>1.060783840176871</v>
+        <v>0.9804872790627667</v>
       </c>
       <c r="AK8">
-        <v>-0.6571496114157754</v>
+        <v>-0.7627172546633524</v>
       </c>
       <c r="AL8">
-        <v>0.8512635793615695</v>
+        <v>0.7356685751804637</v>
       </c>
       <c r="AM8">
-        <v>-3.082724975108901</v>
+        <v>-2.91952979581337</v>
       </c>
       <c r="AN8">
-        <v>0.6491904612606465</v>
+        <v>0.5659491287338677</v>
       </c>
       <c r="AO8">
-        <v>0.03765376253669189</v>
+        <v>0.04055821436859326</v>
       </c>
       <c r="AP8">
-        <v>1.159365</v>
+        <v>1.159895</v>
       </c>
       <c r="AQ8">
-        <v>1.157394789335092</v>
+        <v>1.158085895744269</v>
       </c>
       <c r="AR8">
-        <v>1.152203839598265</v>
+        <v>1.152808348824308</v>
       </c>
       <c r="AS8">
-        <v>1.159365</v>
+        <v>1.159895</v>
       </c>
       <c r="AT8">
-        <v>1.161715</v>
+        <v>1.162775</v>
       </c>
       <c r="AU8">
-        <v>1.157394789335092</v>
+        <v>1.158085895744269</v>
       </c>
       <c r="AV8">
-        <v>1.16918875</v>
+        <v>1.16971875</v>
       </c>
       <c r="AW8">
-        <v>-0.001699387738035516</v>
+        <v>-0.001559713815243044</v>
       </c>
       <c r="AX8">
-        <v>0.2005558635864656</v>
+        <v>0.1841561782141572</v>
       </c>
       <c r="AY8">
-        <v>0.001699387738035516</v>
+        <v>0.001559713815243044</v>
       </c>
       <c r="AZ8">
-        <v>0.4048097710774992</v>
+        <v>0.4126866871555832</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3951902289225008</v>
+        <v>0.3873133128444168</v>
       </c>
       <c r="BC8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2548,58 +2536,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>476.6995084670369</v>
+        <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.008473388449711712</v>
+        <v>0.008469516637281842</v>
       </c>
       <c r="BH8">
-        <v>59008.27077236278</v>
+        <v>59035.24621453098</v>
       </c>
       <c r="BI8">
-        <v>56258.42734535032</v>
+        <v>59035.24621453098</v>
       </c>
       <c r="BJ8">
-        <v>48525.20763120356</v>
+        <v>50897.06069474477</v>
       </c>
       <c r="BK8">
-        <v>562.5842734535032</v>
+        <v>590.3524621453098</v>
       </c>
       <c r="BL8">
-        <v>0.005625842734535032</v>
+        <v>0.005903524621453098</v>
       </c>
       <c r="BM8">
-        <v>476.6995084670369</v>
+        <v>500</v>
       </c>
       <c r="BN8">
-        <v>0.004766995084670368</v>
+        <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.01295604445848304</v>
+        <v>0.01270558188313968</v>
       </c>
       <c r="BP8">
-        <v>0.001168285683265811</v>
+        <v>0.0008817606738997141</v>
       </c>
       <c r="BQ8">
-        <v>0.002574122045654231</v>
+        <v>0.002332406046000059</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU8" t="s">
         <v>92</v>
       </c>
       <c r="BV8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW8" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2607,7 +2595,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2631,19 +2619,19 @@
         <v>94</v>
       </c>
       <c r="J9" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>3.856630204854587</v>
+        <v>4.018325932385717</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
@@ -2655,16 +2643,16 @@
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T9">
-        <v>-0.9995502225675734</v>
+        <v>-0.9982527805535222</v>
       </c>
       <c r="U9">
-        <v>0.9997581877229801</v>
+        <v>0.9991612286773894</v>
       </c>
       <c r="V9" t="s">
         <v>94</v>
@@ -2673,100 +2661,100 @@
         <v>95</v>
       </c>
       <c r="X9">
-        <v>0.999842350270288</v>
+        <v>0.9997899097132181</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-177.5694691317406</v>
+        <v>175.2084532296269</v>
       </c>
       <c r="AA9">
-        <v>-4.999999999999995</v>
+        <v>-9</v>
       </c>
       <c r="AB9">
-        <v>-0.9991003742166761</v>
+        <v>-0.9965051939560751</v>
       </c>
       <c r="AC9">
-        <v>-0.0424080445210326</v>
+        <v>0.08353082316465722</v>
       </c>
       <c r="AD9" t="s">
         <v>94</v>
       </c>
       <c r="AE9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AH9">
-        <v>-0.9989428663127257</v>
+        <v>-0.9962958378940973</v>
       </c>
       <c r="AI9">
-        <v>0.9945802336410562</v>
+        <v>0.9939200917282511</v>
       </c>
       <c r="AJ9">
-        <v>-2.946833510094436</v>
+        <v>-3.076666537320581</v>
       </c>
       <c r="AK9">
-        <v>-0.1538033138105544</v>
+        <v>0.2040071555934416</v>
       </c>
       <c r="AL9">
-        <v>-4.73947218000892</v>
+        <v>-4.911067845256198</v>
       </c>
       <c r="AM9">
-        <v>4.920456880994661</v>
+        <v>5.187757736561392</v>
       </c>
       <c r="AN9">
-        <v>4.291788192979363</v>
+        <v>4.447543961691609</v>
       </c>
       <c r="AO9">
-        <v>0.03396467479031572</v>
+        <v>0.03305289905465125</v>
       </c>
       <c r="AP9">
-        <v>6.708905</v>
+        <v>6.707825</v>
       </c>
       <c r="AQ9">
-        <v>6.691302020365384</v>
+        <v>6.688794182403486</v>
       </c>
       <c r="AR9">
-        <v>6.697674712959005</v>
+        <v>6.693638997427371</v>
       </c>
       <c r="AS9">
-        <v>6.708905</v>
+        <v>6.707825</v>
       </c>
       <c r="AT9">
-        <v>6.67498</v>
+        <v>6.67282</v>
       </c>
       <c r="AU9">
-        <v>6.691302020365384</v>
+        <v>6.688794182403486</v>
       </c>
       <c r="AV9">
-        <v>6.732411249999999</v>
+        <v>6.731331249999999</v>
       </c>
       <c r="AW9">
-        <v>-0.002623823058250985</v>
+        <v>-0.002837107049828212</v>
       </c>
       <c r="AX9">
-        <v>0.7488637972716027</v>
+        <v>0.8096067044515496</v>
       </c>
       <c r="AY9">
-        <v>0.002623823058250985</v>
+        <v>0.002837107049828212</v>
       </c>
       <c r="AZ9">
-        <v>0.4202309314337658</v>
+        <v>0.4310093430190536</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3797690685662343</v>
+        <v>0.3689906569809465</v>
       </c>
       <c r="BC9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2778,55 +2766,55 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.003503738687609918</v>
+        <v>0.003504302810523473</v>
       </c>
       <c r="BH9">
-        <v>142704.7061951632</v>
+        <v>142681.7335814966</v>
       </c>
       <c r="BI9">
-        <v>142704.7061951632</v>
+        <v>142681.7335814966</v>
       </c>
       <c r="BJ9">
         <v>21270.9385801652</v>
       </c>
       <c r="BK9">
-        <v>1427.047061951632</v>
+        <v>1426.817335814966</v>
       </c>
       <c r="BL9">
-        <v>0.01427047061951632</v>
+        <v>0.01426817335814966</v>
       </c>
       <c r="BM9">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="BN9">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.04501432006535262</v>
+        <v>0.04378055989317193</v>
       </c>
       <c r="BP9">
-        <v>0.006182702321116425</v>
+        <v>0.004755734834621987</v>
       </c>
       <c r="BQ9">
-        <v>0.01425612675470795</v>
+        <v>0.01396230318024459</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU9" t="s">
         <v>92</v>
       </c>
       <c r="BV9" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW9" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2834,7 +2822,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2858,19 +2846,19 @@
         <v>94</v>
       </c>
       <c r="J10" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>2.798196837805659</v>
+        <v>2.931110464579591</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O10" t="s">
         <v>95</v>
@@ -2882,16 +2870,16 @@
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T10">
-        <v>-0.8377920202772901</v>
+        <v>-0.8628123004240695</v>
       </c>
       <c r="U10">
-        <v>0.9269575719191055</v>
+        <v>0.9382192925622748</v>
       </c>
       <c r="V10" t="s">
         <v>94</v>
@@ -2900,100 +2888,100 @@
         <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9998046511773003</v>
+        <v>0.9998150294857738</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-132.4970578377665</v>
+        <v>-136.5187187590342</v>
       </c>
       <c r="AA10">
-        <v>-4.999999999999995</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB10">
-        <v>-0.6755523472254542</v>
+        <v>-0.725599220474182</v>
       </c>
       <c r="AC10">
-        <v>-0.737312027677685</v>
+        <v>-0.6881175562701909</v>
       </c>
       <c r="AD10" t="s">
         <v>94</v>
       </c>
       <c r="AE10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AG10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AH10">
-        <v>-0.6754203788697517</v>
+        <v>-0.7254650060132488</v>
       </c>
       <c r="AI10">
-        <v>0.8948797732391993</v>
+        <v>0.9105481239043232</v>
       </c>
       <c r="AJ10">
-        <v>-2.10867769958606</v>
+        <v>-2.232711898249784</v>
       </c>
       <c r="AK10">
-        <v>-2.347407935325795</v>
+        <v>-2.179010281576294</v>
       </c>
       <c r="AL10">
-        <v>-3.568394250874231</v>
+        <v>-3.63642016197765</v>
       </c>
       <c r="AM10">
-        <v>3.619139089034123</v>
+        <v>4.150513773132973</v>
       </c>
       <c r="AN10">
-        <v>3.158217086892496</v>
+        <v>3.190145770786708</v>
       </c>
       <c r="AO10">
-        <v>0.05145039226994787</v>
+        <v>0.04711268371968138</v>
       </c>
       <c r="AP10">
-        <v>154.005</v>
+        <v>153.515</v>
       </c>
       <c r="AQ10">
-        <v>153.4923920928062</v>
+        <v>152.6753736678687</v>
       </c>
       <c r="AR10">
-        <v>157.8927700151773</v>
+        <v>157.2116758835287</v>
       </c>
       <c r="AS10">
-        <v>154.005</v>
+        <v>153.515</v>
       </c>
       <c r="AT10">
-        <v>148.694</v>
+        <v>147.714</v>
       </c>
       <c r="AU10">
-        <v>153.4923920928062</v>
+        <v>152.6753736678687</v>
       </c>
       <c r="AV10">
-        <v>155.1685</v>
+        <v>154.6785</v>
       </c>
       <c r="AW10">
-        <v>-0.003328514705326244</v>
+        <v>-0.005469343921644625</v>
       </c>
       <c r="AX10">
-        <v>0.4405740500161257</v>
+        <v>0.7216384461807176</v>
       </c>
       <c r="AY10">
-        <v>0.003328514705326244</v>
+        <v>0.005469343921644625</v>
       </c>
       <c r="AZ10">
-        <v>0.4061621376164218</v>
+        <v>0.4002214556995863</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3938378623835782</v>
+        <v>0.3997785443004138</v>
       </c>
       <c r="BC10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -3005,55 +2993,55 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.007554949514626235</v>
+        <v>0.007579063935120434</v>
       </c>
       <c r="BH10">
-        <v>66181.77911473926</v>
+        <v>65971.20756338557</v>
       </c>
       <c r="BI10">
-        <v>66181.77911473926</v>
+        <v>65971.20756338557</v>
       </c>
       <c r="BJ10">
         <v>429.7378599054528</v>
       </c>
       <c r="BK10">
-        <v>661.8177911473925</v>
+        <v>659.7120756338558</v>
       </c>
       <c r="BL10">
-        <v>0.006618177911473925</v>
+        <v>0.006597120756338557</v>
       </c>
       <c r="BM10">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN10">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>6.575172045332947</v>
+        <v>6.774899913928272</v>
       </c>
       <c r="BP10">
-        <v>1.709764413386216</v>
+        <v>1.663454593822132</v>
       </c>
       <c r="BQ10">
-        <v>2.400296257769454</v>
+        <v>2.246153643447592</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU10" t="s">
         <v>92</v>
       </c>
       <c r="BV10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW10" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3061,7 +3049,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3109,10 +3097,10 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="T11">
         <v>0.4648788460450831</v>
@@ -3148,13 +3136,13 @@
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AG11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AH11">
         <v>-0.1185427237579554</v>
@@ -3184,10 +3172,10 @@
         <v>7.7789</v>
       </c>
       <c r="AQ11">
-        <v>7.736027912478734</v>
+        <v>7.736330709359215</v>
       </c>
       <c r="AR11">
-        <v>7.689760141772378</v>
+        <v>7.690283631948146</v>
       </c>
       <c r="AS11">
         <v>7.7789</v>
@@ -3196,31 +3184,31 @@
         <v>7.7553</v>
       </c>
       <c r="AU11">
-        <v>7.736027912478734</v>
+        <v>7.736330709359215</v>
       </c>
       <c r="AV11">
         <v>7.828575000000001</v>
       </c>
       <c r="AW11">
-        <v>-0.005511330332214813</v>
+        <v>-0.005472404921105236</v>
       </c>
       <c r="AX11">
-        <v>0.8630515857325679</v>
+        <v>0.8569560269911428</v>
       </c>
       <c r="AY11">
-        <v>0.005511330332214813</v>
+        <v>0.005472404921105236</v>
       </c>
       <c r="AZ11">
-        <v>0.3660686515057779</v>
+        <v>0.3643588737822553</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4339313484942221</v>
+        <v>0.4356411262177448</v>
       </c>
       <c r="BC11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3256,31 +3244,31 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO11">
-        <v>0.09928691399953375</v>
+        <v>0.0961830062996353</v>
       </c>
       <c r="BP11">
-        <v>0.00648060160307601</v>
+        <v>0.006031064790047641</v>
       </c>
       <c r="BQ11">
-        <v>0.009285078474765153</v>
+        <v>0.008515154607371136</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05246615174018369</v>
+        <v>0.05210975498946663</v>
       </c>
       <c r="BT11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="BU11" t="s">
         <v>92</v>
       </c>
       <c r="BV11" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="BW11" s="2">
-        <v>46305</v>
+        <v>46307</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="133">
   <si>
     <t>Pair</t>
   </si>
@@ -241,36 +241,36 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
+    <t>EURCNH</t>
   </si>
   <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -286,9 +286,6 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
@@ -307,118 +304,112 @@
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>UP_ACCELERATING</t>
-  </si>
-  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
-    <t>UP_REVERSAL_WATCH</t>
+    <t>多头加速</t>
   </si>
   <si>
     <t>多头减速</t>
   </si>
   <si>
-    <t>多头加速</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
     <t>空头稳态</t>
   </si>
   <si>
-    <t>多头反转预警</t>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
   </si>
   <si>
     <t>上涨</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
-    <t>UP_STEEPENING</t>
-  </si>
-  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
-    <t>TURNING_DOWN</t>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
   </si>
   <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
-    <t>上升陡坡形成</t>
-  </si>
-  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
     <t>下降坡延续</t>
   </si>
   <si>
-    <t>向下转折带</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.05362,naive=0.01169,drift4=0.03465; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=263.4,naive=44.17,drift4=120.9; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.006517,naive=0.00333,drift4=0.004275; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01509,naive=0.001974,drift4=0.006409; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.01062,naive=0.0004887,drift4=0.0009109; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.08314,naive=0.008313,drift4=0.01722; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01271,naive=0.0008818,drift4=0.002332; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04378,naive=0.004756,drift4=0.01396; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=6.775,naive=1.663,drift4=2.246; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.09618,naive=0.006031,drift4=0.008515; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.007699,naive=0.003406,drift4=0.004984; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=259.6,naive=62.08,drift4=131.7; naive_cap_applied; model_divergence_guard(abs=734.4,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01243,naive=0.002562,drift4=0.003591; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.08222,naive=0.009725,drift4=0.02178; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01649,naive=0.003169,drift4=0.008294; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=5.774,naive=1.228,drift4=2.791; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.03321,naive=0.003771,drift4=0.01876; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.07702,naive=0.01818,drift4=0.04279; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1065,naive=0.02119,drift4=0.02374; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01647,naive=0.003696,drift4=0.006069; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -1018,7 +1009,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1039,136 +1030,145 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.4085139427329589</v>
       </c>
       <c r="L2">
-        <v>0.7627340899366188</v>
+        <v>1.373498749861369</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="O2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.8521284856832397</v>
       </c>
       <c r="R2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T2">
-        <v>0.9519909109868182</v>
+        <v>0.8398296143974808</v>
       </c>
       <c r="U2">
-        <v>0.8279369155102769</v>
+        <v>0.8391478778747419</v>
       </c>
       <c r="V2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9981640222648349</v>
+        <v>0.9997898399437267</v>
       </c>
       <c r="Y2">
-        <v>0.04010881987763081</v>
+        <v>0.577851014516473</v>
       </c>
       <c r="Z2">
-        <v>-30.04160606895899</v>
+        <v>48.58678857679728</v>
       </c>
       <c r="AA2">
-        <v>-37</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB2">
-        <v>0.8656620940372549</v>
+        <v>0.6614848104777297</v>
       </c>
       <c r="AC2">
-        <v>-0.5006287436284845</v>
+        <v>0.7499585625267853</v>
       </c>
       <c r="AD2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AH2">
-        <v>0.4493648481532204</v>
+        <v>0.5217525650521097</v>
       </c>
       <c r="AI2">
-        <v>0.7614545481235691</v>
+        <v>0.8033716330019459</v>
       </c>
       <c r="AJ2">
-        <v>0.6795446964577995</v>
+        <v>0.9177807134602085</v>
       </c>
       <c r="AK2">
-        <v>-0.32049312701577</v>
+        <v>1.083436570067038</v>
       </c>
       <c r="AL2">
-        <v>0.5106168384412557</v>
+        <v>2.270108714869733</v>
       </c>
       <c r="AM2">
-        <v>-2.309988956264086</v>
+        <v>-0.1250406182136466</v>
       </c>
       <c r="AN2">
-        <v>0.4159035631018527</v>
+        <v>2.198550716678369</v>
       </c>
       <c r="AO2">
-        <v>0.03748834570550436</v>
+        <v>0.07046971349981229</v>
       </c>
       <c r="AP2">
-        <v>4.80765</v>
+        <v>0.818375</v>
       </c>
       <c r="AQ2">
-        <v>4.806058921660817</v>
+        <v>0.8312767040135847</v>
       </c>
       <c r="AR2">
-        <v>4.780197812316881</v>
+        <v>0.8340652925914924</v>
       </c>
       <c r="AS2">
-        <v>4.80765</v>
+        <v>0.818375</v>
       </c>
       <c r="AT2">
-        <v>4.839659999999999</v>
+        <v>0.835035</v>
+      </c>
+      <c r="AU2">
+        <v>0.8312767040135847</v>
+      </c>
+      <c r="AV2">
+        <v>0.8090850000000001</v>
       </c>
       <c r="AW2">
-        <v>-0.0003309472068854003</v>
+        <v>0.01576502705188294</v>
+      </c>
+      <c r="AX2">
+        <v>1.388773306090936</v>
       </c>
       <c r="AY2">
-        <v>0.0003309472068854003</v>
+        <v>0.01576502705188294</v>
       </c>
       <c r="AZ2">
-        <v>0.4574180567342999</v>
+        <v>0.4396130035466421</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3425819432657001</v>
+        <v>0.3603869964533579</v>
       </c>
       <c r="BC2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1177,55 +1177,58 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>426.0642428416199</v>
+      </c>
+      <c r="BG2">
+        <v>0.01135176416679388</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>44046.01722282053</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>37532.86595645995</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>45862.6741487215</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>375.3286595645995</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>0.003753286595645995</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>426.0642428416198</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>0.004260642428416198</v>
       </c>
       <c r="BO2">
-        <v>0.053620916871239</v>
+        <v>0.007698962775353239</v>
       </c>
       <c r="BP2">
-        <v>0.01168718323510357</v>
+        <v>0.003406451810919801</v>
       </c>
       <c r="BQ2">
-        <v>0.03464851327399297</v>
+        <v>0.004983986311605522</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="BW2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1233,7 +1236,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1248,79 +1251,79 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J3" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.1968159997324024</v>
+        <v>0.04729329014570197</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q3">
         <v>0.75</v>
       </c>
       <c r="R3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T3">
-        <v>0.6949642886995006</v>
+        <v>0.5729881006925248</v>
       </c>
       <c r="U3">
-        <v>0.7126617526412041</v>
+        <v>0.6077600739464163</v>
       </c>
       <c r="V3" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="W3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="X3">
-        <v>0.9997112909057156</v>
+        <v>0.9996617145391203</v>
       </c>
       <c r="Y3">
-        <v>0.1406307919426623</v>
+        <v>0.2117179824501232</v>
       </c>
       <c r="Z3">
-        <v>-76.798764247509</v>
+        <v>-85.60780292807019</v>
       </c>
       <c r="AA3">
-        <v>-21.99999999999999</v>
+        <v>-24</v>
       </c>
       <c r="AB3">
-        <v>0.228371868158356</v>
+        <v>0.07658324200587172</v>
       </c>
       <c r="AC3">
-        <v>-0.9735739775866354</v>
+        <v>-0.9970631910986736</v>
       </c>
       <c r="AD3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF3" t="s">
         <v>112</v>
@@ -1329,70 +1332,70 @@
         <v>117</v>
       </c>
       <c r="AH3">
-        <v>0.1302063897923587</v>
+        <v>0.04638294975916168</v>
       </c>
       <c r="AI3">
-        <v>0.5783253456726923</v>
+        <v>0.5320886528497983</v>
       </c>
       <c r="AJ3">
-        <v>0.4285505175192901</v>
+        <v>0.2078487712189059</v>
       </c>
       <c r="AK3">
-        <v>-1.46968865365661</v>
+        <v>-1.57576333828175</v>
       </c>
       <c r="AL3">
-        <v>-0.2616187175915644</v>
+        <v>-0.6075882353552399</v>
       </c>
       <c r="AM3">
-        <v>-1.91773203214572</v>
+        <v>-1.713534707069807</v>
       </c>
       <c r="AN3">
-        <v>0.4823579895471006</v>
+        <v>0.7187090165714427</v>
       </c>
       <c r="AO3">
-        <v>0.1214088332023164</v>
+        <v>0.2207434422045328</v>
       </c>
       <c r="AP3">
-        <v>4346.68</v>
+        <v>4283.450000000001</v>
       </c>
       <c r="AQ3">
-        <v>4443.375369279991</v>
+        <v>4325.150049144342</v>
       </c>
       <c r="AR3">
-        <v>4589.93906020166</v>
+        <v>4855.47683048114</v>
       </c>
       <c r="AS3">
-        <v>4346.68</v>
+        <v>4283.450000000001</v>
       </c>
       <c r="AT3">
-        <v>4317.630000000001</v>
+        <v>3958.680000000002</v>
       </c>
       <c r="AU3">
-        <v>4443.375369279991</v>
+        <v>4325.150049144342</v>
       </c>
       <c r="AV3">
-        <v>4207.860000000001</v>
+        <v>4149.812500000001</v>
       </c>
       <c r="AW3">
-        <v>0.02224579892699502</v>
+        <v>0.009735154873838001</v>
       </c>
       <c r="AX3">
-        <v>0.6965521486816829</v>
+        <v>0.3120385306844362</v>
       </c>
       <c r="AY3">
-        <v>0.02224579892699502</v>
+        <v>0.009735154873838001</v>
       </c>
       <c r="AZ3">
-        <v>0.4404384091780535</v>
+        <v>0.3</v>
       </c>
       <c r="BA3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BB3">
-        <v>0.3595615908219465</v>
+        <v>0.4</v>
       </c>
       <c r="BC3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1404,55 +1407,55 @@
         <v>375</v>
       </c>
       <c r="BG3">
-        <v>0.03193701859810229</v>
+        <v>0.03119856657600769</v>
       </c>
       <c r="BH3">
-        <v>15655.81328338864</v>
+        <v>16026.3773267234</v>
       </c>
       <c r="BI3">
-        <v>11741.85996254148</v>
+        <v>12019.78299504255</v>
       </c>
       <c r="BJ3">
-        <v>2.701339864572842</v>
+        <v>2.806098587597041</v>
       </c>
       <c r="BK3">
-        <v>117.4185996254148</v>
+        <v>120.1978299504255</v>
       </c>
       <c r="BL3">
-        <v>0.001174185996254148</v>
+        <v>0.001201978299504255</v>
       </c>
       <c r="BM3">
-        <v>374.9999999999999</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN3">
-        <v>0.003749999999999999</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO3">
-        <v>263.4138454923627</v>
+        <v>259.60316546862</v>
       </c>
       <c r="BP3">
-        <v>44.16820764603839</v>
+        <v>62.08359204545108</v>
       </c>
       <c r="BQ3">
-        <v>120.906850500924</v>
+        <v>131.7358748030563</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW3" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1460,7 +1463,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1472,7 +1475,7 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
@@ -1481,73 +1484,73 @@
         <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J4" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K4">
-        <v>0.009441760357892058</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1.088462135949222</v>
+        <v>0.3272372832527371</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q4">
-        <v>0.752360440089473</v>
+        <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T4">
-        <v>0.875180513618772</v>
+        <v>0.7986004666080007</v>
       </c>
       <c r="U4">
-        <v>0.7951338869404498</v>
+        <v>0.7592379857681434</v>
       </c>
       <c r="V4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9995455670332747</v>
+        <v>0.9994711031781724</v>
       </c>
       <c r="Y4">
-        <v>0.06857142533282168</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>48.65576573871741</v>
+        <v>-65.79632472936247</v>
       </c>
       <c r="AA4">
-        <v>-16</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB4">
-        <v>0.6605814722906341</v>
+        <v>0.409981541466164</v>
       </c>
       <c r="AC4">
-        <v>0.7507543662652507</v>
+        <v>-0.9120938195476538</v>
       </c>
       <c r="AD4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF4" t="s">
         <v>113</v>
@@ -1556,70 +1559,70 @@
         <v>118</v>
       </c>
       <c r="AH4">
-        <v>0.3527788554698958</v>
+        <v>0.2048823517659373</v>
       </c>
       <c r="AI4">
-        <v>0.7008202970272939</v>
+        <v>0.6144344292101485</v>
       </c>
       <c r="AJ4">
-        <v>0.7097267830372</v>
+        <v>0.417513994869618</v>
       </c>
       <c r="AK4">
-        <v>0.8465006369284063</v>
+        <v>-0.8842918748851024</v>
       </c>
       <c r="AL4">
-        <v>1.878834130420117</v>
+        <v>0.3092411070603037</v>
       </c>
       <c r="AM4">
-        <v>0.1147461191625324</v>
+        <v>-1.358901367601592</v>
       </c>
       <c r="AN4">
-        <v>1.838899944721231</v>
+        <v>0.2652449766801828</v>
       </c>
       <c r="AO4">
-        <v>0.07272918792071138</v>
+        <v>0.0558327956137401</v>
       </c>
       <c r="AP4">
-        <v>0.816445</v>
+        <v>1.348165</v>
       </c>
       <c r="AQ4">
-        <v>0.8316700325145399</v>
+        <v>1.346474786203371</v>
       </c>
       <c r="AR4">
-        <v>0.848692960966775</v>
+        <v>1.358739410674721</v>
       </c>
       <c r="AS4">
-        <v>0.816445</v>
+        <v>1.348165</v>
       </c>
       <c r="AT4">
-        <v>0.819515</v>
+        <v>1.333635</v>
       </c>
       <c r="AU4">
-        <v>0.8316700325145399</v>
+        <v>1.3461427525</v>
       </c>
       <c r="AV4">
-        <v>0.8062949783236401</v>
+        <v>1.35844625</v>
       </c>
       <c r="AW4">
-        <v>0.01864795854532747</v>
+        <v>-0.001253714342554124</v>
       </c>
       <c r="AX4">
-        <v>1.5</v>
+        <v>0.1966927659574475</v>
       </c>
       <c r="AY4">
-        <v>0.01864795854532747</v>
+        <v>0.001253714342554124</v>
       </c>
       <c r="AZ4">
-        <v>0.4376259372298113</v>
+        <v>0.3956988408165804</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3623740627701888</v>
+        <v>0.4043011591834196</v>
       </c>
       <c r="BC4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1628,58 +1631,58 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>376.1802200447365</v>
+        <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.01243197236355164</v>
+        <v>0.007626106596744437</v>
       </c>
       <c r="BH4">
-        <v>40218.87962572312</v>
+        <v>65564.25531914918</v>
       </c>
       <c r="BI4">
-        <v>30259.09397511458</v>
+        <v>65564.25531914918</v>
       </c>
       <c r="BJ4">
-        <v>37062.01149509714</v>
+        <v>48632.21884498498</v>
       </c>
       <c r="BK4">
-        <v>302.5909397511458</v>
+        <v>655.6425531914917</v>
       </c>
       <c r="BL4">
-        <v>0.003025909397511458</v>
+        <v>0.006556425531914918</v>
       </c>
       <c r="BM4">
-        <v>376.1802200447365</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN4">
-        <v>0.003761802200447365</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO4">
-        <v>0.00651714662483238</v>
+        <v>0.01243205092965955</v>
       </c>
       <c r="BP4">
-        <v>0.003329966646145246</v>
+        <v>0.002561741985094416</v>
       </c>
       <c r="BQ4">
-        <v>0.004274606681452132</v>
+        <v>0.003591201772234903</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU4" t="s">
         <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW4" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1687,7 +1690,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1711,64 +1714,64 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K5">
-        <v>0.703221216942846</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>2.167902143529543</v>
+        <v>0.3541415674016754</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q5">
-        <v>0.9258053042357115</v>
+        <v>0.75</v>
       </c>
       <c r="R5" t="s">
         <v>100</v>
       </c>
       <c r="S5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T5">
-        <v>0.9502927037673258</v>
+        <v>-0.8686042979154364</v>
       </c>
       <c r="U5">
-        <v>0.9328738465763199</v>
+        <v>0.790585254275402</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
       </c>
       <c r="W5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X5">
-        <v>0.9990357893583854</v>
+        <v>0.998853280853823</v>
       </c>
       <c r="Y5">
-        <v>0.992041590135873</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>-25.1628791310978</v>
+        <v>-127.9451908038636</v>
       </c>
       <c r="AA5">
-        <v>-25</v>
+        <v>-34</v>
       </c>
       <c r="AB5">
-        <v>0.9051027170225241</v>
+        <v>-0.6149073819271738</v>
       </c>
       <c r="AC5">
-        <v>-0.4251929816429767</v>
+        <v>-0.7885993353100602</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1777,76 +1780,76 @@
         <v>110</v>
       </c>
       <c r="AF5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AH5">
-        <v>0.9006318908460458</v>
+        <v>-0.3071011279295962</v>
       </c>
       <c r="AI5">
-        <v>0.9647992452175191</v>
+        <v>0.673461485962789</v>
       </c>
       <c r="AJ5">
-        <v>1.82472219597571</v>
+        <v>-0.2430084362936052</v>
       </c>
       <c r="AK5">
-        <v>-0.7384305222231893</v>
+        <v>-0.368910953746</v>
       </c>
       <c r="AL5">
-        <v>1.921060464331321</v>
+        <v>-0.5581255149946011</v>
       </c>
       <c r="AM5">
-        <v>-5.034163411394008</v>
+        <v>0.1596279715553374</v>
       </c>
       <c r="AN5">
-        <v>1.519758685396873</v>
+        <v>0.5280506619945343</v>
       </c>
       <c r="AO5">
-        <v>0.03201609461231736</v>
+        <v>0.07072917942800762</v>
       </c>
       <c r="AP5">
-        <v>0.71635</v>
+        <v>9.05326</v>
       </c>
       <c r="AQ5">
-        <v>0.7185032517562275</v>
+        <v>9.035173236319688</v>
       </c>
       <c r="AR5">
-        <v>0.7147275199379235</v>
+        <v>9.109759016717833</v>
       </c>
       <c r="AS5">
-        <v>0.71635</v>
+        <v>9.05326</v>
       </c>
       <c r="AT5">
-        <v>0.7244200000000001</v>
+        <v>8.946099999999999</v>
       </c>
       <c r="AU5">
-        <v>0.7185032517562275</v>
+        <v>9.035173236319688</v>
       </c>
       <c r="AV5">
-        <v>0.7091412500000001</v>
+        <v>9.122024999999999</v>
       </c>
       <c r="AW5">
-        <v>0.003005865507402097</v>
+        <v>-0.001997817767335981</v>
       </c>
       <c r="AX5">
-        <v>0.2986997407633103</v>
+        <v>0.2630228121909732</v>
       </c>
       <c r="AY5">
-        <v>0.003005865507402097</v>
+        <v>0.001997817767335981</v>
       </c>
       <c r="AZ5">
-        <v>0.4439264477424864</v>
+        <v>0.4133058946352306</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3560735522575136</v>
+        <v>0.3866941053647696</v>
       </c>
       <c r="BC5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1855,58 +1858,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>462.9026521178557</v>
+        <v>375</v>
       </c>
       <c r="BG5">
-        <v>0.01006316744608073</v>
+        <v>0.007595606444529321</v>
       </c>
       <c r="BH5">
-        <v>49686.14530952016</v>
+        <v>65827.52853922827</v>
       </c>
       <c r="BI5">
-        <v>45999.69687458008</v>
+        <v>49370.6464044212</v>
       </c>
       <c r="BJ5">
-        <v>64213.99717258334</v>
+        <v>5453.355631498621</v>
       </c>
       <c r="BK5">
-        <v>459.9969687458008</v>
+        <v>493.7064640442121</v>
       </c>
       <c r="BL5">
-        <v>0.004599969687458008</v>
+        <v>0.004937064640442121</v>
       </c>
       <c r="BM5">
-        <v>462.9026521178557</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN5">
-        <v>0.004629026521178557</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO5">
-        <v>0.0150887628279826</v>
+        <v>0.08222126838410586</v>
       </c>
       <c r="BP5">
-        <v>0.001974182841889695</v>
+        <v>0.009724693555918514</v>
       </c>
       <c r="BQ5">
-        <v>0.006408603985254602</v>
+        <v>0.02178360326623655</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW5" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1914,7 +1917,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1935,16 +1938,16 @@
         <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.1070399265804761</v>
       </c>
       <c r="L6">
-        <v>0.7795846339819062</v>
+        <v>1.648978363959246</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1956,124 +1959,124 @@
         <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>0.9197200550646429</v>
       </c>
       <c r="R6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T6">
-        <v>0.9451365324997493</v>
+        <v>0.8040844093871631</v>
       </c>
       <c r="U6">
-        <v>0.8248317097822648</v>
+        <v>0.7776074934517428</v>
       </c>
       <c r="V6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X6">
-        <v>0.9980810806295107</v>
+        <v>0.9988540809617921</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>-32.95216435618324</v>
+        <v>-48.32792734363106</v>
       </c>
       <c r="AA6">
-        <v>42.00000000000001</v>
+        <v>-32.99999999999999</v>
       </c>
       <c r="AB6">
-        <v>0.8391249890020952</v>
+        <v>0.6648663462030032</v>
       </c>
       <c r="AC6">
-        <v>-0.5439386480405981</v>
+        <v>-0.7469623428839424</v>
       </c>
       <c r="AD6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AH6">
-        <v>0.4187573879032188</v>
+        <v>0.6641044631990255</v>
       </c>
       <c r="AI6">
-        <v>0.7460396725337519</v>
+        <v>0.8931011357392076</v>
       </c>
       <c r="AJ6">
-        <v>0.636973055942427</v>
+        <v>1.457216143767806</v>
       </c>
       <c r="AK6">
-        <v>-0.5305780552845913</v>
+        <v>-1.447007669928777</v>
       </c>
       <c r="AL6">
-        <v>0.7658837827235925</v>
+        <v>1.164795403623578</v>
       </c>
       <c r="AM6">
-        <v>-1.21489278594029</v>
+        <v>-4.882106732060211</v>
       </c>
       <c r="AN6">
-        <v>0.6890771073644926</v>
+        <v>0.9319104903366719</v>
       </c>
       <c r="AO6">
-        <v>0.03350801591470254</v>
+        <v>0.03971797638880459</v>
       </c>
       <c r="AP6">
-        <v>1.352595</v>
+        <v>0.7127250000000001</v>
       </c>
       <c r="AQ6">
-        <v>1.354687964260656</v>
+        <v>0.7112725820268464</v>
       </c>
       <c r="AR6">
-        <v>1.359416933354913</v>
+        <v>0.7120275076874063</v>
       </c>
       <c r="AS6">
-        <v>1.352595</v>
+        <v>0.7127250000000001</v>
       </c>
       <c r="AT6">
-        <v>1.3514</v>
+        <v>0.7095250000000002</v>
       </c>
       <c r="AU6">
-        <v>1.354687964260656</v>
+        <v>0.7112725820268464</v>
       </c>
       <c r="AV6">
-        <v>1.34117</v>
+        <v>0.71993375</v>
       </c>
       <c r="AW6">
-        <v>0.001547369508726866</v>
+        <v>-0.002037837838091343</v>
       </c>
       <c r="AX6">
-        <v>0.1831916201887451</v>
+        <v>0.2014798644915785</v>
       </c>
       <c r="AY6">
-        <v>0.001547369508726866</v>
+        <v>0.002037837838091343</v>
       </c>
       <c r="AZ6">
-        <v>0.3803155303502502</v>
+        <v>0.4425888609334516</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.4196844696497497</v>
+        <v>0.3574111390665484</v>
       </c>
       <c r="BC6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2082,58 +2085,58 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>375</v>
+        <v>459.8600275323215</v>
       </c>
       <c r="BG6">
-        <v>0.008446726477622658</v>
+        <v>0.01011434985443184</v>
       </c>
       <c r="BH6">
-        <v>59194.5295404813</v>
+        <v>49434.71475637294</v>
       </c>
       <c r="BI6">
-        <v>44395.89715536097</v>
+        <v>45466.09857783624</v>
       </c>
       <c r="BJ6">
-        <v>32822.75711159732</v>
+        <v>63791.92336151565</v>
       </c>
       <c r="BK6">
-        <v>443.9589715536097</v>
+        <v>454.6609857783624</v>
       </c>
       <c r="BL6">
-        <v>0.004439589715536096</v>
+        <v>0.004546609857783624</v>
       </c>
       <c r="BM6">
-        <v>375</v>
+        <v>459.8600275323215</v>
       </c>
       <c r="BN6">
-        <v>0.00375</v>
+        <v>0.004598600275323215</v>
       </c>
       <c r="BO6">
-        <v>0.0106178369493113</v>
+        <v>0.01649315601316503</v>
       </c>
       <c r="BP6">
-        <v>0.0004887141527307132</v>
+        <v>0.003169140742807844</v>
       </c>
       <c r="BQ6">
-        <v>0.0009108716995400334</v>
+        <v>0.008294056341780378</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU6" t="s">
         <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW6" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2141,7 +2144,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2153,82 +2156,82 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.9854140213095479</v>
       </c>
       <c r="L7">
-        <v>0.281499877920296</v>
+        <v>2.506061488315238</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>0.996353505327387</v>
       </c>
       <c r="R7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T7">
-        <v>-0.8897938918869088</v>
+        <v>-0.941786007256101</v>
       </c>
       <c r="U7">
-        <v>0.7992171690588966</v>
+        <v>0.9712317342149173</v>
       </c>
       <c r="V7" t="s">
+        <v>93</v>
+      </c>
+      <c r="W7" t="s">
         <v>94</v>
       </c>
-      <c r="W7" t="s">
-        <v>95</v>
-      </c>
       <c r="X7">
-        <v>0.9952396708391507</v>
+        <v>0.9984637110129587</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7">
-        <v>-132.5502794454923</v>
+        <v>-152.0991671420752</v>
       </c>
       <c r="AA7">
-        <v>-68</v>
+        <v>-25</v>
       </c>
       <c r="AB7">
-        <v>-0.6762369391362666</v>
+        <v>-0.8837588281146735</v>
       </c>
       <c r="AC7">
-        <v>-0.736684194310977</v>
+        <v>-0.4679426607281911</v>
       </c>
       <c r="AD7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="s">
         <v>114</v>
@@ -2237,70 +2240,70 @@
         <v>119</v>
       </c>
       <c r="AH7">
-        <v>-0.3365089143576264</v>
+        <v>-0.8824011191598404</v>
       </c>
       <c r="AI7">
-        <v>0.6894951858989864</v>
+        <v>0.9588462785035203</v>
       </c>
       <c r="AJ7">
-        <v>-0.1888515677004071</v>
+        <v>-1.971462694951287</v>
       </c>
       <c r="AK7">
-        <v>-0.3091809003988046</v>
+        <v>-1.194890811441123</v>
       </c>
       <c r="AL7">
-        <v>-0.4667626019016398</v>
+        <v>-2.849982399328737</v>
       </c>
       <c r="AM7">
-        <v>0.1693803799238007</v>
+        <v>4.732644937606127</v>
       </c>
       <c r="AN7">
-        <v>0.4334020959173555</v>
+        <v>2.376526241075518</v>
       </c>
       <c r="AO7">
-        <v>0.07806520423730776</v>
+        <v>0.03829112523611434</v>
       </c>
       <c r="AP7">
-        <v>9.066660000000001</v>
+        <v>154.927</v>
       </c>
       <c r="AQ7">
-        <v>9.053092559219079</v>
+        <v>154.5612991412848</v>
       </c>
       <c r="AR7">
-        <v>9.09056688054887</v>
+        <v>157.4961405110065</v>
       </c>
       <c r="AS7">
-        <v>9.066660000000001</v>
+        <v>154.927</v>
       </c>
       <c r="AT7">
-        <v>9.008280000000001</v>
+        <v>150.8425</v>
       </c>
       <c r="AU7">
-        <v>9.053060010000001</v>
+        <v>154.5612991412848</v>
       </c>
       <c r="AV7">
-        <v>9.146257500000001</v>
+        <v>156.283</v>
       </c>
       <c r="AW7">
-        <v>-0.001496410009961905</v>
+        <v>-0.002360472085015528</v>
       </c>
       <c r="AX7">
-        <v>0.1708595119193447</v>
+        <v>0.2696908987575208</v>
       </c>
       <c r="AY7">
-        <v>0.001496410009961905</v>
+        <v>0.002360472085015528</v>
       </c>
       <c r="AZ7">
-        <v>0.4026955329701536</v>
+        <v>0.4361370495572269</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3973044670298464</v>
+        <v>0.3638629504427731</v>
       </c>
       <c r="BC7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2309,58 +2312,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>375</v>
+        <v>498.1767526636935</v>
       </c>
       <c r="BG7">
-        <v>0.008779142484663565</v>
+        <v>0.008752509246290245</v>
       </c>
       <c r="BH7">
-        <v>56953.17063978157</v>
+        <v>57126.47492625332</v>
       </c>
       <c r="BI7">
-        <v>42714.87797983618</v>
+        <v>56918.16353976957</v>
       </c>
       <c r="BJ7">
-        <v>4711.203241307844</v>
+        <v>367.3869857401846</v>
       </c>
       <c r="BK7">
-        <v>427.1487797983618</v>
+        <v>569.1816353976957</v>
       </c>
       <c r="BL7">
-        <v>0.004271487797983618</v>
+        <v>0.005691816353976957</v>
       </c>
       <c r="BM7">
-        <v>375</v>
+        <v>498.1767526636935</v>
       </c>
       <c r="BN7">
-        <v>0.00375</v>
+        <v>0.004981767526636935</v>
       </c>
       <c r="BO7">
-        <v>0.08314150362562781</v>
+        <v>5.773753891071316</v>
       </c>
       <c r="BP7">
-        <v>0.008312621349684281</v>
+        <v>1.227606902167189</v>
       </c>
       <c r="BQ7">
-        <v>0.01722297342610176</v>
+        <v>2.790657085785341</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW7" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2368,7 +2371,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2383,73 +2386,73 @@
         <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.9407221123010578</v>
       </c>
       <c r="L8">
-        <v>1.103416729551548</v>
+        <v>3.62860109327589</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="O8" t="s">
+        <v>94</v>
+      </c>
+      <c r="P8" t="s">
         <v>96</v>
       </c>
-      <c r="P8" t="s">
-        <v>99</v>
-      </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.9851805280752645</v>
       </c>
       <c r="R8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s">
         <v>105</v>
       </c>
       <c r="T8">
-        <v>0.9115597468132107</v>
+        <v>-0.9867058542560161</v>
       </c>
       <c r="U8">
-        <v>0.8101149323188382</v>
+        <v>0.9850481836537166</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
       </c>
       <c r="W8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9996521850115739</v>
+        <v>0.9996889295734031</v>
       </c>
       <c r="Y8">
-        <v>0.1663286017293179</v>
+        <v>1</v>
       </c>
       <c r="Z8">
-        <v>-38.62909547814716</v>
+        <v>166.8213103505525</v>
       </c>
       <c r="AA8">
-        <v>-4.999999999999995</v>
+        <v>-12</v>
       </c>
       <c r="AB8">
-        <v>0.7812035581881254</v>
+        <v>-0.9736637673900084</v>
       </c>
       <c r="AC8">
-        <v>-0.6242763816405457</v>
+        <v>0.2279887454939294</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
@@ -2458,76 +2461,76 @@
         <v>110</v>
       </c>
       <c r="AF8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AH8">
-        <v>0.4554115727601482</v>
+        <v>-0.9733608893865243</v>
       </c>
       <c r="AI8">
-        <v>0.761421320401063</v>
+        <v>0.9874202203026983</v>
       </c>
       <c r="AJ8">
-        <v>0.9804872790627667</v>
+        <v>-2.80716301597792</v>
       </c>
       <c r="AK8">
-        <v>-0.7627172546633524</v>
+        <v>0.5887923391863664</v>
       </c>
       <c r="AL8">
-        <v>0.7356685751804637</v>
+        <v>-4.315599903873433</v>
       </c>
       <c r="AM8">
-        <v>-2.91952979581337</v>
+        <v>5.207316204213797</v>
       </c>
       <c r="AN8">
-        <v>0.5659491287338677</v>
+        <v>3.861539043783517</v>
       </c>
       <c r="AO8">
-        <v>0.04055821436859326</v>
+        <v>0.03046690176663491</v>
       </c>
       <c r="AP8">
-        <v>1.159895</v>
+        <v>6.712825</v>
       </c>
       <c r="AQ8">
-        <v>1.158085895744269</v>
+        <v>6.693006122101684</v>
       </c>
       <c r="AR8">
-        <v>1.152808348824308</v>
+        <v>6.676094807777051</v>
       </c>
       <c r="AS8">
-        <v>1.159895</v>
+        <v>6.712825</v>
       </c>
       <c r="AT8">
-        <v>1.162775</v>
+        <v>6.704849999999998</v>
       </c>
       <c r="AU8">
-        <v>1.158085895744269</v>
+        <v>6.693006122101684</v>
       </c>
       <c r="AV8">
-        <v>1.16971875</v>
+        <v>6.736331249999999</v>
       </c>
       <c r="AW8">
-        <v>-0.001559713815243044</v>
+        <v>-0.002952390073972689</v>
       </c>
       <c r="AX8">
-        <v>0.1841561782141572</v>
+        <v>0.843132269005734</v>
       </c>
       <c r="AY8">
-        <v>0.001559713815243044</v>
+        <v>0.002952390073972689</v>
       </c>
       <c r="AZ8">
-        <v>0.4126866871555832</v>
+        <v>0.4673548274036912</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3873133128444168</v>
+        <v>0.3326451725963088</v>
       </c>
       <c r="BC8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2536,58 +2539,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>500</v>
+        <v>492.5902640376322</v>
       </c>
       <c r="BG8">
-        <v>0.008469516637281842</v>
+        <v>0.003501692655476587</v>
       </c>
       <c r="BH8">
-        <v>59035.24621453098</v>
+        <v>142788.0882743974</v>
       </c>
       <c r="BI8">
-        <v>59035.24621453098</v>
+        <v>140672.0442090283</v>
       </c>
       <c r="BJ8">
-        <v>50897.06069474477</v>
+        <v>20955.71450306366</v>
       </c>
       <c r="BK8">
-        <v>590.3524621453098</v>
+        <v>1406.720442090283</v>
       </c>
       <c r="BL8">
-        <v>0.005903524621453098</v>
+        <v>0.01406720442090283</v>
       </c>
       <c r="BM8">
-        <v>500</v>
+        <v>492.5902640376323</v>
       </c>
       <c r="BN8">
-        <v>0.005</v>
+        <v>0.004925902640376323</v>
       </c>
       <c r="BO8">
-        <v>0.01270558188313968</v>
+        <v>0.03321321267119558</v>
       </c>
       <c r="BP8">
-        <v>0.0008817606738997141</v>
+        <v>0.003770943632486092</v>
       </c>
       <c r="BQ8">
-        <v>0.002332406046000059</v>
+        <v>0.01875569766750368</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW8" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2595,7 +2598,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2610,151 +2613,151 @@
         <v>89</v>
       </c>
       <c r="G9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" t="s">
         <v>92</v>
       </c>
-      <c r="H9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" t="s">
-        <v>94</v>
-      </c>
       <c r="J9" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>4.018325932385717</v>
+        <v>0.5322898086271723</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9" t="s">
+        <v>99</v>
+      </c>
+      <c r="S9" t="s">
         <v>103</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9">
+        <v>0.8040328903044585</v>
+      </c>
+      <c r="U9">
+        <v>0.7614848539166132</v>
+      </c>
+      <c r="V9" t="s">
+        <v>92</v>
+      </c>
+      <c r="W9" t="s">
+        <v>94</v>
+      </c>
+      <c r="X9">
+        <v>0.9986802131184278</v>
+      </c>
+      <c r="Y9">
+        <v>0.2633578518385805</v>
+      </c>
+      <c r="Z9">
+        <v>-56.64023767166175</v>
+      </c>
+      <c r="AA9">
+        <v>-40</v>
+      </c>
+      <c r="AB9">
+        <v>0.5498943075500854</v>
+      </c>
+      <c r="AC9">
+        <v>-0.8352342488930947</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE9" t="s">
         <v>108</v>
       </c>
-      <c r="T9">
-        <v>-0.9982527805535222</v>
-      </c>
-      <c r="U9">
-        <v>0.9991612286773894</v>
-      </c>
-      <c r="V9" t="s">
-        <v>94</v>
-      </c>
-      <c r="W9" t="s">
-        <v>95</v>
-      </c>
-      <c r="X9">
-        <v>0.9997899097132181</v>
-      </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="Z9">
-        <v>175.2084532296269</v>
-      </c>
-      <c r="AA9">
-        <v>-9</v>
-      </c>
-      <c r="AB9">
-        <v>-0.9965051939560751</v>
-      </c>
-      <c r="AC9">
-        <v>0.08353082316465722</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>111</v>
-      </c>
       <c r="AF9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AH9">
-        <v>-0.9962958378940973</v>
+        <v>0.3468982088183297</v>
       </c>
       <c r="AI9">
-        <v>0.9939200917282511</v>
+        <v>0.7087548104940669</v>
       </c>
       <c r="AJ9">
-        <v>-3.076666537320581</v>
+        <v>0.5140238509020666</v>
       </c>
       <c r="AK9">
-        <v>0.2040071555934416</v>
+        <v>-0.6735337538144014</v>
       </c>
       <c r="AL9">
-        <v>-4.911067845256198</v>
+        <v>0.1840277826922503</v>
       </c>
       <c r="AM9">
-        <v>5.187757736561392</v>
+        <v>-2.183203764413147</v>
       </c>
       <c r="AN9">
-        <v>4.447543961691609</v>
+        <v>0.2761722435110276</v>
       </c>
       <c r="AO9">
-        <v>0.03305289905465125</v>
+        <v>0.05615417820083014</v>
       </c>
       <c r="AP9">
-        <v>6.707825</v>
+        <v>4.78793</v>
       </c>
       <c r="AQ9">
-        <v>6.688794182403486</v>
+        <v>4.769986137370822</v>
       </c>
       <c r="AR9">
-        <v>6.693638997427371</v>
+        <v>4.77088881690915</v>
       </c>
       <c r="AS9">
-        <v>6.707825</v>
+        <v>4.78793</v>
       </c>
       <c r="AT9">
-        <v>6.67282</v>
+        <v>4.75879</v>
       </c>
       <c r="AU9">
-        <v>6.688794182403486</v>
+        <v>4.769986137370822</v>
       </c>
       <c r="AV9">
-        <v>6.731331249999999</v>
+        <v>4.827730000000001</v>
       </c>
       <c r="AW9">
-        <v>-0.002837107049828212</v>
+        <v>-0.003747728690515228</v>
       </c>
       <c r="AX9">
-        <v>0.8096067044515496</v>
+        <v>0.4508508198286068</v>
       </c>
       <c r="AY9">
-        <v>0.002837107049828212</v>
+        <v>0.003747728690515228</v>
       </c>
       <c r="AZ9">
-        <v>0.4310093430190536</v>
+        <v>0.4436910989835226</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3689906569809465</v>
+        <v>0.3563089010164774</v>
       </c>
       <c r="BC9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2766,22 +2769,22 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.003504302810523473</v>
+        <v>0.008312569314923163</v>
       </c>
       <c r="BH9">
-        <v>142681.7335814966</v>
+        <v>60149.87437185921</v>
       </c>
       <c r="BI9">
-        <v>142681.7335814966</v>
+        <v>60149.87437185921</v>
       </c>
       <c r="BJ9">
-        <v>21270.9385801652</v>
+        <v>12562.81407035174</v>
       </c>
       <c r="BK9">
-        <v>1426.817335814966</v>
+        <v>601.4987437185921</v>
       </c>
       <c r="BL9">
-        <v>0.01426817335814966</v>
+        <v>0.006014987437185921</v>
       </c>
       <c r="BM9">
         <v>500</v>
@@ -2790,31 +2793,31 @@
         <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.04378055989317193</v>
+        <v>0.07702222360827576</v>
       </c>
       <c r="BP9">
-        <v>0.004755734834621987</v>
+        <v>0.01817767000981878</v>
       </c>
       <c r="BQ9">
-        <v>0.01396230318024459</v>
+        <v>0.04278758499429432</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW9" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2822,7 +2825,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2834,82 +2837,82 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2.931110464579591</v>
+        <v>0.4644705373884119</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S10" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T10">
-        <v>-0.8628123004240695</v>
+        <v>-0.7737186465331317</v>
       </c>
       <c r="U10">
-        <v>0.9382192925622748</v>
+        <v>0.7479743913347484</v>
       </c>
       <c r="V10" t="s">
+        <v>93</v>
+      </c>
+      <c r="W10" t="s">
         <v>94</v>
       </c>
-      <c r="W10" t="s">
-        <v>95</v>
-      </c>
       <c r="X10">
-        <v>0.9998150294857738</v>
+        <v>0.9992040015793563</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>-136.5187187590342</v>
+        <v>-109.6924528889363</v>
       </c>
       <c r="AA10">
-        <v>-6.999999999999997</v>
+        <v>-34</v>
       </c>
       <c r="AB10">
-        <v>-0.725599220474182</v>
+        <v>-0.3369712431751639</v>
       </c>
       <c r="AC10">
-        <v>-0.6881175562701909</v>
+        <v>-0.9415149394847564</v>
       </c>
       <c r="AD10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="s">
         <v>114</v>
@@ -2918,70 +2921,70 @@
         <v>119</v>
       </c>
       <c r="AH10">
-        <v>-0.7254650060132488</v>
+        <v>-0.168351507298897</v>
       </c>
       <c r="AI10">
-        <v>0.9105481239043232</v>
+        <v>0.5809853472856928</v>
       </c>
       <c r="AJ10">
-        <v>-2.232711898249784</v>
+        <v>-0.2259080226308482</v>
       </c>
       <c r="AK10">
-        <v>-2.179010281576294</v>
+        <v>-0.7709752963208648</v>
       </c>
       <c r="AL10">
-        <v>-3.63642016197765</v>
+        <v>-1.137502229099049</v>
       </c>
       <c r="AM10">
-        <v>4.150513773132973</v>
+        <v>-1.173432794323517</v>
       </c>
       <c r="AN10">
-        <v>3.190145770786708</v>
+        <v>1.202387605559851</v>
       </c>
       <c r="AO10">
-        <v>0.04711268371968138</v>
+        <v>0.1321828414642066</v>
       </c>
       <c r="AP10">
-        <v>153.515</v>
+        <v>7.7475</v>
       </c>
       <c r="AQ10">
-        <v>152.6753736678687</v>
+        <v>7.701996141752345</v>
       </c>
       <c r="AR10">
-        <v>157.2116758835287</v>
+        <v>7.739082650518592</v>
       </c>
       <c r="AS10">
-        <v>153.515</v>
+        <v>7.7475</v>
       </c>
       <c r="AT10">
-        <v>147.714</v>
+        <v>7.647599999999999</v>
       </c>
       <c r="AU10">
-        <v>152.6753736678687</v>
+        <v>7.701996141752345</v>
       </c>
       <c r="AV10">
-        <v>154.6785</v>
+        <v>7.792775</v>
       </c>
       <c r="AW10">
-        <v>-0.005469343921644625</v>
+        <v>-0.005873360212669165</v>
       </c>
       <c r="AX10">
-        <v>0.7216384461807176</v>
+        <v>1.005054848098385</v>
       </c>
       <c r="AY10">
-        <v>0.005469343921644625</v>
+        <v>0.005873360212669165</v>
       </c>
       <c r="AZ10">
-        <v>0.4002214556995863</v>
+        <v>0.3762040294771592</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3997785443004138</v>
+        <v>0.4237959705228408</v>
       </c>
       <c r="BC10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2990,58 +2993,58 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG10">
-        <v>0.007579063935120434</v>
+        <v>0.005843820587286216</v>
       </c>
       <c r="BH10">
-        <v>65971.20756338557</v>
+        <v>85560.46383213703</v>
       </c>
       <c r="BI10">
-        <v>65971.20756338557</v>
+        <v>64170.34787410277</v>
       </c>
       <c r="BJ10">
-        <v>429.7378599054528</v>
+        <v>8282.716731087805</v>
       </c>
       <c r="BK10">
-        <v>659.7120756338558</v>
+        <v>641.7034787410278</v>
       </c>
       <c r="BL10">
-        <v>0.006597120756338557</v>
+        <v>0.006417034787410278</v>
       </c>
       <c r="BM10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BN10">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="BO10">
-        <v>6.774899913928272</v>
+        <v>0.1065144894943804</v>
       </c>
       <c r="BP10">
-        <v>1.663454593822132</v>
+        <v>0.02118811331738078</v>
       </c>
       <c r="BQ10">
-        <v>2.246153643447592</v>
+        <v>0.02374174763745496</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW10" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3049,7 +3052,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3061,154 +3064,154 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I11" t="s">
         <v>92</v>
       </c>
-      <c r="H11" t="s">
-        <v>92</v>
-      </c>
-      <c r="I11" t="s">
-        <v>93</v>
-      </c>
       <c r="J11" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.138907574804795</v>
+        <v>0.3284909043607342</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="S11" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="T11">
-        <v>0.4648788460450831</v>
+        <v>0.740562428887295</v>
       </c>
       <c r="U11">
-        <v>0.5085445576424406</v>
+        <v>0.7330167150300032</v>
       </c>
       <c r="V11" t="s">
+        <v>92</v>
+      </c>
+      <c r="W11" t="s">
         <v>94</v>
       </c>
-      <c r="W11" t="s">
-        <v>96</v>
-      </c>
       <c r="X11">
-        <v>0.9973963076886128</v>
+        <v>0.9990544881228819</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>0.2295652278539875</v>
       </c>
       <c r="Z11">
-        <v>-103.7510891352802</v>
+        <v>-67.08029985022648</v>
       </c>
       <c r="AA11">
-        <v>-71</v>
+        <v>-29</v>
       </c>
       <c r="AB11">
-        <v>-0.2377043565213686</v>
+        <v>0.3894406605921795</v>
       </c>
       <c r="AC11">
-        <v>-0.9713375514674402</v>
+        <v>-0.9210515576652193</v>
       </c>
       <c r="AD11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AG11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AH11">
-        <v>-0.1185427237579554</v>
+        <v>0.2391949715608186</v>
       </c>
       <c r="AI11">
-        <v>0.5419526672058479</v>
+        <v>0.6501215412376978</v>
       </c>
       <c r="AJ11">
-        <v>-0.01724737476143526</v>
+        <v>0.5678357415307461</v>
       </c>
       <c r="AK11">
-        <v>-0.4600429033012642</v>
+        <v>-1.14220262248422</v>
       </c>
       <c r="AL11">
-        <v>-0.6831301709401844</v>
+        <v>-0.06179268083553235</v>
       </c>
       <c r="AM11">
-        <v>-0.9812357988182752</v>
+        <v>-2.900968096772592</v>
       </c>
       <c r="AN11">
-        <v>0.7337126753893859</v>
+        <v>0.5133339514840164</v>
       </c>
       <c r="AO11">
-        <v>0.1896489829438474</v>
+        <v>0.0819518223584141</v>
       </c>
       <c r="AP11">
-        <v>7.7789</v>
+        <v>1.15419</v>
       </c>
       <c r="AQ11">
-        <v>7.736330709359215</v>
+        <v>1.132164210723205</v>
       </c>
       <c r="AR11">
-        <v>7.690283631948146</v>
+        <v>1.113282386034773</v>
       </c>
       <c r="AS11">
-        <v>7.7789</v>
+        <v>1.15419</v>
       </c>
       <c r="AT11">
-        <v>7.7553</v>
+        <v>1.140885</v>
       </c>
       <c r="AU11">
-        <v>7.736330709359215</v>
+        <v>1.132164210723205</v>
       </c>
       <c r="AV11">
-        <v>7.828575000000001</v>
+        <v>1.168873859517864</v>
       </c>
       <c r="AW11">
-        <v>-0.005472404921105236</v>
+        <v>-0.01908333054072158</v>
       </c>
       <c r="AX11">
-        <v>0.8569560269911428</v>
+        <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.005472404921105236</v>
+        <v>0.01908333054072158</v>
       </c>
       <c r="AZ11">
-        <v>0.3643588737822553</v>
+        <v>0.4123446167502119</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4356411262177448</v>
+        <v>0.3876553832497882</v>
       </c>
       <c r="BC11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3220,22 +3223,22 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.006385864325290282</v>
+        <v>0.01272222036048105</v>
       </c>
       <c r="BH11">
-        <v>78297.93658781993</v>
+        <v>39301.31579493362</v>
       </c>
       <c r="BI11">
-        <v>78297.93658781993</v>
+        <v>39301.31579493362</v>
       </c>
       <c r="BJ11">
-        <v>10065.4252642173</v>
+        <v>34050.99315964756</v>
       </c>
       <c r="BK11">
-        <v>782.9793658781994</v>
+        <v>393.0131579493362</v>
       </c>
       <c r="BL11">
-        <v>0.007829793658781994</v>
+        <v>0.003930131579493362</v>
       </c>
       <c r="BM11">
         <v>500.0000000000001</v>
@@ -3244,31 +3247,31 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO11">
-        <v>0.0961830062996353</v>
+        <v>0.01646882618068097</v>
       </c>
       <c r="BP11">
-        <v>0.006031064790047641</v>
+        <v>0.003695575496791865</v>
       </c>
       <c r="BQ11">
-        <v>0.008515154607371136</v>
+        <v>0.006069088779006103</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05210975498946663</v>
+        <v>0.05711653950426025</v>
       </c>
       <c r="BT11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BU11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="BW11" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="137">
   <si>
     <t>Pair</t>
   </si>
@@ -247,18 +247,18 @@
     <t>XAUUSD</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
@@ -316,10 +316,13 @@
     <t>UP_DECELERATING</t>
   </si>
   <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_STEADY</t>
+    <t>DOWN_DECELERATING</t>
   </si>
   <si>
     <t>多头加速</t>
@@ -328,10 +331,13 @@
     <t>多头减速</t>
   </si>
   <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
     <t>空头加速</t>
   </si>
   <si>
-    <t>空头稳态</t>
+    <t>空头减速</t>
   </si>
   <si>
     <t>NEUTRAL</t>
@@ -355,13 +361,16 @@
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_SLOPE</t>
+    <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
@@ -370,43 +379,46 @@
     <t>地形转换区</t>
   </si>
   <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>下降坡延续</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.007699,naive=0.003406,drift4=0.004984; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=259.6,naive=62.08,drift4=131.7; naive_cap_applied; model_divergence_guard(abs=734.4,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01243,naive=0.002562,drift4=0.003591; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.08222,naive=0.009725,drift4=0.02178; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01649,naive=0.003169,drift4=0.008294; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=5.774,naive=1.228,drift4=2.791; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.03321,naive=0.003771,drift4=0.01876; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.07702,naive=0.01818,drift4=0.04279; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1065,naive=0.02119,drift4=0.02374; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01647,naive=0.003696,drift4=0.006069; naive_cap_applied</t>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.00755,naive=0.00338,drift4=0.005006; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=277.8,naive=34.05,drift4=98.97; naive_cap_applied; model_divergence_guard(abs=714.9,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=5.467,naive=1.109,drift4=2.771; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.0158,naive=0.002863,drift4=0.007745; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01105,naive=0.004024,drift4=0.005052; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.08659,naive=0.01483,drift4=0.02162; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.03166,naive=0.0002335,drift4=0.01583; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.08029,naive=0.0193,drift4=0.0423; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1046,naive=0.0212,drift4=0.02398; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01671,naive=0.003898,drift4=0.006269; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -1009,7 +1021,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1033,19 +1045,19 @@
         <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K2">
-        <v>0.4085139427329589</v>
+        <v>0.6827852171250517</v>
       </c>
       <c r="L2">
-        <v>1.373498749861369</v>
+        <v>1.570696400134309</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O2" t="s">
         <v>94</v>
@@ -1054,19 +1066,19 @@
         <v>96</v>
       </c>
       <c r="Q2">
-        <v>0.8521284856832397</v>
+        <v>0.9206963042812629</v>
       </c>
       <c r="R2" t="s">
         <v>98</v>
       </c>
       <c r="S2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T2">
-        <v>0.8398296143974808</v>
+        <v>0.7763367086703723</v>
       </c>
       <c r="U2">
-        <v>0.8391478778747419</v>
+        <v>0.8517324938063381</v>
       </c>
       <c r="V2" t="s">
         <v>92</v>
@@ -1075,100 +1087,100 @@
         <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9997898399437267</v>
+        <v>0.9998527693436513</v>
       </c>
       <c r="Y2">
-        <v>0.577851014516473</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>48.58678857679728</v>
+        <v>54.85116337480898</v>
       </c>
       <c r="AA2">
-        <v>-12.99999999999999</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB2">
-        <v>0.6614848104777297</v>
+        <v>0.5757024010987276</v>
       </c>
       <c r="AC2">
-        <v>0.7499585625267853</v>
+        <v>0.8176593088622912</v>
       </c>
       <c r="AD2" t="s">
         <v>92</v>
       </c>
       <c r="AE2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AH2">
-        <v>0.5217525650521097</v>
+        <v>0.5756176400563523</v>
       </c>
       <c r="AI2">
-        <v>0.8033716330019459</v>
+        <v>0.8627898672340636</v>
       </c>
       <c r="AJ2">
-        <v>0.9177807134602085</v>
+        <v>1.077613557470728</v>
       </c>
       <c r="AK2">
-        <v>1.083436570067038</v>
+        <v>1.560975069807629</v>
       </c>
       <c r="AL2">
-        <v>2.270108714869733</v>
+        <v>2.475284634128603</v>
       </c>
       <c r="AM2">
-        <v>-0.1250406182136466</v>
+        <v>-0.6124997590557972</v>
       </c>
       <c r="AN2">
-        <v>2.198550716678369</v>
+        <v>2.353697948581886</v>
       </c>
       <c r="AO2">
-        <v>0.07046971349981229</v>
+        <v>0.06579548243888363</v>
       </c>
       <c r="AP2">
-        <v>0.818375</v>
+        <v>0.818925</v>
       </c>
       <c r="AQ2">
-        <v>0.8312767040135847</v>
+        <v>0.8328311285731935</v>
       </c>
       <c r="AR2">
-        <v>0.8340652925914924</v>
+        <v>0.8364479110144607</v>
       </c>
       <c r="AS2">
-        <v>0.818375</v>
+        <v>0.818925</v>
       </c>
       <c r="AT2">
-        <v>0.835035</v>
+        <v>0.8361350000000001</v>
       </c>
       <c r="AU2">
-        <v>0.8312767040135847</v>
+        <v>0.8328311285731935</v>
       </c>
       <c r="AV2">
-        <v>0.8090850000000001</v>
+        <v>0.8096350000000001</v>
       </c>
       <c r="AW2">
-        <v>0.01576502705188294</v>
+        <v>0.01698095499977838</v>
       </c>
       <c r="AX2">
-        <v>1.388773306090936</v>
+        <v>1.496892203788332</v>
       </c>
       <c r="AY2">
-        <v>0.01576502705188294</v>
+        <v>0.01698095499977838</v>
       </c>
       <c r="AZ2">
-        <v>0.4396130035466421</v>
+        <v>0.4414308439465426</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3603869964533579</v>
+        <v>0.3585691560534573</v>
       </c>
       <c r="BC2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1177,58 +1189,58 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>426.0642428416199</v>
+        <v>460.3481521406314</v>
       </c>
       <c r="BG2">
-        <v>0.01135176416679388</v>
+        <v>0.01134414018377744</v>
       </c>
       <c r="BH2">
-        <v>44046.01722282053</v>
+        <v>44075.61894510256</v>
       </c>
       <c r="BI2">
-        <v>37532.86595645995</v>
+        <v>40580.25947166514</v>
       </c>
       <c r="BJ2">
-        <v>45862.6741487215</v>
+        <v>49553.08419167218</v>
       </c>
       <c r="BK2">
-        <v>375.3286595645995</v>
+        <v>405.8025947166514</v>
       </c>
       <c r="BL2">
-        <v>0.003753286595645995</v>
+        <v>0.004058025947166514</v>
       </c>
       <c r="BM2">
-        <v>426.0642428416198</v>
+        <v>460.3481521406315</v>
       </c>
       <c r="BN2">
-        <v>0.004260642428416198</v>
+        <v>0.004603481521406315</v>
       </c>
       <c r="BO2">
-        <v>0.007698962775353239</v>
+        <v>0.007549638144235616</v>
       </c>
       <c r="BP2">
-        <v>0.003406451810919801</v>
+        <v>0.003380064857932428</v>
       </c>
       <c r="BQ2">
-        <v>0.004983986311605522</v>
+        <v>0.005005785034447026</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW2" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1236,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1260,19 +1272,19 @@
         <v>92</v>
       </c>
       <c r="J3" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.04729329014570197</v>
+        <v>0.03165600104598355</v>
       </c>
       <c r="M3">
         <v>4</v>
       </c>
       <c r="N3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
         <v>94</v>
@@ -1287,103 +1299,103 @@
         <v>99</v>
       </c>
       <c r="S3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T3">
-        <v>0.5729881006925248</v>
+        <v>0.6158939918839855</v>
       </c>
       <c r="U3">
-        <v>0.6077600739464163</v>
+        <v>0.6270906499783299</v>
       </c>
       <c r="V3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="W3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="X3">
-        <v>0.9996617145391203</v>
+        <v>0.9997534145221455</v>
       </c>
       <c r="Y3">
-        <v>0.2117179824501232</v>
+        <v>0.05871282590859755</v>
       </c>
       <c r="Z3">
-        <v>-85.60780292807019</v>
+        <v>-86.84644237015766</v>
       </c>
       <c r="AA3">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="AB3">
-        <v>0.07658324200587172</v>
+        <v>0.05501217834529652</v>
       </c>
       <c r="AC3">
-        <v>-0.9970631910986736</v>
+        <v>-0.9984856835396817</v>
       </c>
       <c r="AD3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AE3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AH3">
-        <v>0.04638294975916168</v>
+        <v>0.02911386856978697</v>
       </c>
       <c r="AI3">
-        <v>0.5320886528497983</v>
+        <v>0.4914746051588749</v>
       </c>
       <c r="AJ3">
-        <v>0.2078487712189059</v>
+        <v>0.1514988887513829</v>
       </c>
       <c r="AK3">
-        <v>-1.57576333828175</v>
+        <v>-1.4513013772579</v>
       </c>
       <c r="AL3">
-        <v>-0.6075882353552399</v>
+        <v>-0.4478905679736006</v>
       </c>
       <c r="AM3">
-        <v>-1.713534707069807</v>
+        <v>-0.9173147340484979</v>
       </c>
       <c r="AN3">
-        <v>0.7187090165714427</v>
+        <v>0.4763741290751481</v>
       </c>
       <c r="AO3">
-        <v>0.2207434422045328</v>
+        <v>0.2445687240612294</v>
       </c>
       <c r="AP3">
-        <v>4283.450000000001</v>
+        <v>4342.18</v>
       </c>
       <c r="AQ3">
-        <v>4325.150049144342</v>
+        <v>4410.328675161845</v>
       </c>
       <c r="AR3">
-        <v>4855.47683048114</v>
+        <v>4924.062250539482</v>
       </c>
       <c r="AS3">
-        <v>4283.450000000001</v>
+        <v>4342.18</v>
       </c>
       <c r="AT3">
-        <v>3958.680000000002</v>
+        <v>4076.140000000001</v>
       </c>
       <c r="AU3">
-        <v>4325.150049144342</v>
+        <v>4410.328675161845</v>
       </c>
       <c r="AV3">
-        <v>4149.812500000001</v>
+        <v>4208.5425</v>
       </c>
       <c r="AW3">
-        <v>0.009735154873838001</v>
+        <v>0.01569457626396072</v>
       </c>
       <c r="AX3">
-        <v>0.3120385306844362</v>
+        <v>0.5099517363153671</v>
       </c>
       <c r="AY3">
-        <v>0.009735154873838001</v>
+        <v>0.01569457626396072</v>
       </c>
       <c r="AZ3">
         <v>0.3</v>
@@ -1395,7 +1407,7 @@
         <v>0.4</v>
       </c>
       <c r="BC3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1407,55 +1419,55 @@
         <v>375</v>
       </c>
       <c r="BG3">
-        <v>0.03119856657600769</v>
+        <v>0.03077659148169817</v>
       </c>
       <c r="BH3">
-        <v>16026.3773267234</v>
+        <v>16246.11355345616</v>
       </c>
       <c r="BI3">
-        <v>12019.78299504255</v>
+        <v>12184.58516509212</v>
       </c>
       <c r="BJ3">
         <v>2.806098587597041</v>
       </c>
       <c r="BK3">
-        <v>120.1978299504255</v>
+        <v>121.8458516509212</v>
       </c>
       <c r="BL3">
-        <v>0.001201978299504255</v>
+        <v>0.001218458516509212</v>
       </c>
       <c r="BM3">
-        <v>375.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="BN3">
-        <v>0.003750000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="BO3">
-        <v>259.60316546862</v>
+        <v>277.8144473498009</v>
       </c>
       <c r="BP3">
-        <v>62.08359204545108</v>
+        <v>34.05499934398202</v>
       </c>
       <c r="BQ3">
-        <v>131.7358748030563</v>
+        <v>98.9728638107014</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU3" t="s">
         <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW3" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1463,7 +1475,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1475,7 +1487,7 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
@@ -1484,16 +1496,16 @@
         <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.7767584709530562</v>
       </c>
       <c r="L4">
-        <v>0.3272372832527371</v>
+        <v>2.324637152564254</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -1502,127 +1514,127 @@
         <v>31</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.944189617738264</v>
       </c>
       <c r="R4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T4">
-        <v>0.7986004666080007</v>
+        <v>-0.9982818662459734</v>
       </c>
       <c r="U4">
-        <v>0.7592379857681434</v>
+        <v>0.9648302177448576</v>
       </c>
       <c r="V4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W4" t="s">
         <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9994711031781724</v>
+        <v>0.9963584291648447</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>0.8446382050838273</v>
       </c>
       <c r="Z4">
-        <v>-65.79632472936247</v>
+        <v>-175.2068921605852</v>
       </c>
       <c r="AA4">
-        <v>-7.999999999999998</v>
+        <v>-48</v>
       </c>
       <c r="AB4">
-        <v>0.409981541466164</v>
+        <v>-0.9965029177225527</v>
       </c>
       <c r="AC4">
-        <v>-0.9120938195476538</v>
+        <v>-0.08355797370951025</v>
       </c>
       <c r="AD4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AF4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AG4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AH4">
-        <v>0.2048823517659373</v>
+        <v>-0.9157467320262193</v>
       </c>
       <c r="AI4">
-        <v>0.6144344292101485</v>
+        <v>0.961691872397425</v>
       </c>
       <c r="AJ4">
-        <v>0.417513994869618</v>
+        <v>-1.868098377030235</v>
       </c>
       <c r="AK4">
-        <v>-0.8842918748851024</v>
+        <v>-0.3613618935501299</v>
       </c>
       <c r="AL4">
-        <v>0.3092411070603037</v>
+        <v>-2.474844600796342</v>
       </c>
       <c r="AM4">
-        <v>-1.358901367601592</v>
+        <v>4.966267091630977</v>
       </c>
       <c r="AN4">
-        <v>0.2652449766801828</v>
+        <v>2.005753682561695</v>
       </c>
       <c r="AO4">
-        <v>0.0558327956137401</v>
+        <v>0.03274729429201255</v>
       </c>
       <c r="AP4">
-        <v>1.348165</v>
+        <v>155.042</v>
       </c>
       <c r="AQ4">
-        <v>1.346474786203371</v>
+        <v>154.8528436124573</v>
       </c>
       <c r="AR4">
-        <v>1.358739410674721</v>
+        <v>157.8386199549882</v>
       </c>
       <c r="AS4">
-        <v>1.348165</v>
+        <v>155.042</v>
       </c>
       <c r="AT4">
-        <v>1.333635</v>
+        <v>151.0725</v>
       </c>
       <c r="AU4">
-        <v>1.3461427525</v>
+        <v>154.809437</v>
       </c>
       <c r="AV4">
-        <v>1.35844625</v>
+        <v>156.48425</v>
       </c>
       <c r="AW4">
-        <v>-0.001253714342554124</v>
+        <v>-0.00122003320095676</v>
       </c>
       <c r="AX4">
-        <v>0.1966927659574475</v>
+        <v>0.1612501300051985</v>
       </c>
       <c r="AY4">
-        <v>0.001253714342554124</v>
+        <v>0.00122003320095676</v>
       </c>
       <c r="AZ4">
-        <v>0.3956988408165804</v>
+        <v>0.441382008052564</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.4043011591834196</v>
+        <v>0.358617991947436</v>
       </c>
       <c r="BC4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1631,58 +1643,58 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>500</v>
+        <v>472.094808869132</v>
       </c>
       <c r="BG4">
-        <v>0.007626106596744437</v>
+        <v>0.009302318081552196</v>
       </c>
       <c r="BH4">
-        <v>65564.25531914918</v>
+        <v>53750.04333506616</v>
       </c>
       <c r="BI4">
-        <v>65564.25531914918</v>
+        <v>50750.23286995124</v>
       </c>
       <c r="BJ4">
-        <v>48632.21884498498</v>
+        <v>327.3321607690254</v>
       </c>
       <c r="BK4">
-        <v>655.6425531914917</v>
+        <v>507.5023286995124</v>
       </c>
       <c r="BL4">
-        <v>0.006556425531914918</v>
+        <v>0.005075023286995124</v>
       </c>
       <c r="BM4">
-        <v>500.0000000000001</v>
+        <v>472.094808869132</v>
       </c>
       <c r="BN4">
-        <v>0.005000000000000001</v>
+        <v>0.00472094808869132</v>
       </c>
       <c r="BO4">
-        <v>0.01243205092965955</v>
+        <v>5.467363562190165</v>
       </c>
       <c r="BP4">
-        <v>0.002561741985094416</v>
+        <v>1.109304475026002</v>
       </c>
       <c r="BQ4">
-        <v>0.003591201772234903</v>
+        <v>2.771100890025697</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU4" t="s">
         <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW4" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1690,7 +1702,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1702,7 +1714,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1711,145 +1723,145 @@
         <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.3541415674016754</v>
+        <v>1.387655313461933</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="O5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S5" t="s">
         <v>104</v>
       </c>
       <c r="T5">
-        <v>-0.8686042979154364</v>
+        <v>0.6911000426247549</v>
       </c>
       <c r="U5">
-        <v>0.790585254275402</v>
+        <v>0.7108173139027903</v>
       </c>
       <c r="V5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W5" t="s">
         <v>94</v>
       </c>
       <c r="X5">
-        <v>0.998853280853823</v>
+        <v>0.9992891788866024</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>-127.9451908038636</v>
+        <v>-61.15483782159379</v>
       </c>
       <c r="AA5">
-        <v>-34</v>
+        <v>-26</v>
       </c>
       <c r="AB5">
-        <v>-0.6149073819271738</v>
+        <v>0.4824442544568019</v>
       </c>
       <c r="AC5">
-        <v>-0.7885993353100602</v>
+        <v>-0.8759266757792119</v>
       </c>
       <c r="AD5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE5" t="s">
         <v>110</v>
       </c>
       <c r="AF5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AH5">
-        <v>-0.3071011279295962</v>
+        <v>0.4821013228946967</v>
       </c>
       <c r="AI5">
-        <v>0.673461485962789</v>
+        <v>0.8369788651536564</v>
       </c>
       <c r="AJ5">
-        <v>-0.2430084362936052</v>
+        <v>1.252958774079383</v>
       </c>
       <c r="AK5">
-        <v>-0.368910953746</v>
+        <v>-2.050207935731843</v>
       </c>
       <c r="AL5">
-        <v>-0.5581255149946011</v>
+        <v>0.8579562417671847</v>
       </c>
       <c r="AM5">
-        <v>0.1596279715553374</v>
+        <v>-4.270417556524586</v>
       </c>
       <c r="AN5">
-        <v>0.5280506619945343</v>
+        <v>0.7591683021197938</v>
       </c>
       <c r="AO5">
-        <v>0.07072917942800762</v>
+        <v>0.05003749195796645</v>
       </c>
       <c r="AP5">
-        <v>9.05326</v>
+        <v>0.7130799999999999</v>
       </c>
       <c r="AQ5">
-        <v>9.035173236319688</v>
+        <v>0.7121706157788064</v>
       </c>
       <c r="AR5">
-        <v>9.109759016717833</v>
+        <v>0.7133225344523686</v>
       </c>
       <c r="AS5">
-        <v>9.05326</v>
+        <v>0.7130799999999999</v>
       </c>
       <c r="AT5">
-        <v>8.946099999999999</v>
+        <v>0.7102349999999999</v>
       </c>
       <c r="AU5">
-        <v>9.035173236319688</v>
+        <v>0.7120103799999999</v>
       </c>
       <c r="AV5">
-        <v>9.122024999999999</v>
+        <v>0.7202887499999999</v>
       </c>
       <c r="AW5">
-        <v>-0.001997817767335981</v>
+        <v>-0.001275290600204152</v>
       </c>
       <c r="AX5">
-        <v>0.2630228121909732</v>
+        <v>0.1483780128316296</v>
       </c>
       <c r="AY5">
-        <v>0.001997817767335981</v>
+        <v>0.001275290600204152</v>
       </c>
       <c r="AZ5">
-        <v>0.4133058946352306</v>
+        <v>0.4426236532382621</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3866941053647696</v>
+        <v>0.3573763467617379</v>
       </c>
       <c r="BC5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1858,58 +1870,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.007595606444529321</v>
+        <v>0.01010931452291458</v>
       </c>
       <c r="BH5">
-        <v>65827.52853922827</v>
+        <v>49459.33761054322</v>
       </c>
       <c r="BI5">
-        <v>49370.6464044212</v>
+        <v>49459.33761054322</v>
       </c>
       <c r="BJ5">
-        <v>5453.355631498621</v>
+        <v>69360.15259233638</v>
       </c>
       <c r="BK5">
-        <v>493.7064640442121</v>
+        <v>494.5933761054322</v>
       </c>
       <c r="BL5">
-        <v>0.004937064640442121</v>
+        <v>0.004945933761054322</v>
       </c>
       <c r="BM5">
-        <v>375.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN5">
-        <v>0.003750000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.08222126838410586</v>
+        <v>0.01580466155341744</v>
       </c>
       <c r="BP5">
-        <v>0.009724693555918514</v>
+        <v>0.002863405541138317</v>
       </c>
       <c r="BQ5">
-        <v>0.02178360326623655</v>
+        <v>0.007744731431072243</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW5" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1917,7 +1929,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1929,7 +1941,7 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
         <v>91</v>
@@ -1941,19 +1953,19 @@
         <v>92</v>
       </c>
       <c r="J6" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K6">
-        <v>0.1070399265804761</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1.648978363959246</v>
+        <v>0.03416955490130145</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
@@ -1962,121 +1974,121 @@
         <v>97</v>
       </c>
       <c r="Q6">
-        <v>0.9197200550646429</v>
+        <v>1</v>
       </c>
       <c r="R6" t="s">
         <v>99</v>
       </c>
       <c r="S6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T6">
-        <v>0.8040844093871631</v>
+        <v>0.5036694739926805</v>
       </c>
       <c r="U6">
-        <v>0.7776074934517428</v>
+        <v>0.6015757688088759</v>
       </c>
       <c r="V6" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="W6" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="X6">
-        <v>0.9988540809617921</v>
+        <v>0.9996980220486789</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>0.6668888251877514</v>
       </c>
       <c r="Z6">
-        <v>-48.32792734363106</v>
+        <v>-83.66999434434932</v>
       </c>
       <c r="AA6">
-        <v>-32.99999999999999</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB6">
-        <v>0.6648663462030032</v>
+        <v>0.11025483087232</v>
       </c>
       <c r="AC6">
-        <v>-0.7469623428839424</v>
+        <v>-0.9939033515736407</v>
       </c>
       <c r="AD6" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AE6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AF6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AH6">
-        <v>0.6641044631990255</v>
+        <v>0.09186352361372788</v>
       </c>
       <c r="AI6">
-        <v>0.8931011357392076</v>
+        <v>0.6392194039758973</v>
       </c>
       <c r="AJ6">
-        <v>1.457216143767806</v>
+        <v>0.1958238010424785</v>
       </c>
       <c r="AK6">
-        <v>-1.447007669928777</v>
+        <v>-1.45654358879843</v>
       </c>
       <c r="AL6">
-        <v>1.164795403623578</v>
+        <v>-0.1512775050486639</v>
       </c>
       <c r="AM6">
-        <v>-4.882106732060211</v>
+        <v>-1.358708286649757</v>
       </c>
       <c r="AN6">
-        <v>0.9319104903366719</v>
+        <v>0.3236101391705627</v>
       </c>
       <c r="AO6">
-        <v>0.03971797638880459</v>
+        <v>0.1808607869359098</v>
       </c>
       <c r="AP6">
-        <v>0.7127250000000001</v>
+        <v>1.345665</v>
       </c>
       <c r="AQ6">
-        <v>0.7112725820268464</v>
+        <v>1.343345133276248</v>
       </c>
       <c r="AR6">
-        <v>0.7120275076874063</v>
+        <v>1.355913952071206</v>
       </c>
       <c r="AS6">
-        <v>0.7127250000000001</v>
+        <v>1.345665</v>
       </c>
       <c r="AT6">
-        <v>0.7095250000000002</v>
+        <v>1.328635</v>
       </c>
       <c r="AU6">
-        <v>0.7112725820268464</v>
+        <v>1.343345133276248</v>
       </c>
       <c r="AV6">
-        <v>0.71993375</v>
+        <v>1.35594625</v>
       </c>
       <c r="AW6">
-        <v>-0.002037837838091343</v>
+        <v>-0.001723955608380703</v>
       </c>
       <c r="AX6">
-        <v>0.2014798644915785</v>
+        <v>0.225640532401374</v>
       </c>
       <c r="AY6">
-        <v>0.002037837838091343</v>
+        <v>0.001723955608380703</v>
       </c>
       <c r="AZ6">
-        <v>0.4425888609334516</v>
+        <v>0.4143903052705776</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3574111390665484</v>
+        <v>0.3856096947294223</v>
       </c>
       <c r="BC6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2085,58 +2097,58 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>459.8600275323215</v>
+        <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.01011434985443184</v>
+        <v>0.007640274511115296</v>
       </c>
       <c r="BH6">
-        <v>49434.71475637294</v>
+        <v>65442.6747720367</v>
       </c>
       <c r="BI6">
-        <v>45466.09857783624</v>
+        <v>65442.6747720367</v>
       </c>
       <c r="BJ6">
-        <v>63791.92336151565</v>
+        <v>48632.21884498497</v>
       </c>
       <c r="BK6">
-        <v>454.6609857783624</v>
+        <v>654.426747720367</v>
       </c>
       <c r="BL6">
-        <v>0.004546609857783624</v>
+        <v>0.006544267477203669</v>
       </c>
       <c r="BM6">
-        <v>459.8600275323215</v>
+        <v>500</v>
       </c>
       <c r="BN6">
-        <v>0.004598600275323215</v>
+        <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.01649315601316503</v>
+        <v>0.01105031693147255</v>
       </c>
       <c r="BP6">
-        <v>0.003169140742807844</v>
+        <v>0.004024105606280066</v>
       </c>
       <c r="BQ6">
-        <v>0.008294056341780378</v>
+        <v>0.005052235042368639</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU6" t="s">
         <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW6" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2144,7 +2156,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2156,7 +2168,7 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
@@ -2168,19 +2180,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K7">
-        <v>0.9854140213095479</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>2.506061488315238</v>
+        <v>0.457979184325273</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="O7" t="s">
         <v>94</v>
@@ -2189,19 +2201,19 @@
         <v>96</v>
       </c>
       <c r="Q7">
-        <v>0.996353505327387</v>
+        <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T7">
-        <v>-0.941786007256101</v>
+        <v>-0.8677601508868771</v>
       </c>
       <c r="U7">
-        <v>0.9712317342149173</v>
+        <v>0.7903499084832597</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2210,100 +2222,100 @@
         <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9984637110129587</v>
+        <v>0.9994313623366604</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>-152.0991671420752</v>
+        <v>-127.7763647042577</v>
       </c>
       <c r="AA7">
-        <v>-25</v>
+        <v>-21</v>
       </c>
       <c r="AB7">
-        <v>-0.8837588281146735</v>
+        <v>-0.612581051722029</v>
       </c>
       <c r="AC7">
-        <v>-0.4679426607281911</v>
+        <v>-0.7904077777142207</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AF7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AH7">
-        <v>-0.8824011191598404</v>
+        <v>-0.3061163575320859</v>
       </c>
       <c r="AI7">
-        <v>0.9588462785035203</v>
+        <v>0.6735269321142432</v>
       </c>
       <c r="AJ7">
-        <v>-1.971462694951287</v>
+        <v>-0.3197280199864684</v>
       </c>
       <c r="AK7">
-        <v>-1.194890811441123</v>
+        <v>-0.4517362144464229</v>
       </c>
       <c r="AL7">
-        <v>-2.849982399328737</v>
+        <v>-0.6943676706362006</v>
       </c>
       <c r="AM7">
-        <v>4.732644937606127</v>
+        <v>0.2027265347920631</v>
       </c>
       <c r="AN7">
-        <v>2.376526241075518</v>
+        <v>0.6599940573354511</v>
       </c>
       <c r="AO7">
-        <v>0.03829112523611434</v>
+        <v>0.06698906813464363</v>
       </c>
       <c r="AP7">
-        <v>154.927</v>
+        <v>9.042540000000001</v>
       </c>
       <c r="AQ7">
-        <v>154.5612991412848</v>
+        <v>9.016160174813486</v>
       </c>
       <c r="AR7">
-        <v>157.4961405110065</v>
+        <v>9.098060665280402</v>
       </c>
       <c r="AS7">
-        <v>154.927</v>
+        <v>9.042540000000001</v>
       </c>
       <c r="AT7">
-        <v>150.8425</v>
+        <v>8.924660000000001</v>
       </c>
       <c r="AU7">
-        <v>154.5612991412848</v>
+        <v>9.016160174813486</v>
       </c>
       <c r="AV7">
-        <v>156.283</v>
+        <v>9.111305</v>
       </c>
       <c r="AW7">
-        <v>-0.002360472085015528</v>
+        <v>-0.002917302570573649</v>
       </c>
       <c r="AX7">
-        <v>0.2696908987575208</v>
+        <v>0.3836228486368826</v>
       </c>
       <c r="AY7">
-        <v>0.002360472085015528</v>
+        <v>0.002917302570573649</v>
       </c>
       <c r="AZ7">
-        <v>0.4361370495572269</v>
+        <v>0.3917180750353307</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3638629504427731</v>
+        <v>0.4082819249646693</v>
       </c>
       <c r="BC7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2312,58 +2324,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>498.1767526636935</v>
+        <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.008752509246290245</v>
+        <v>0.007604611093785542</v>
       </c>
       <c r="BH7">
-        <v>57126.47492625332</v>
+        <v>65749.58190940206</v>
       </c>
       <c r="BI7">
-        <v>56918.16353976957</v>
+        <v>49312.18643205155</v>
       </c>
       <c r="BJ7">
-        <v>367.3869857401846</v>
+        <v>5453.355631498621</v>
       </c>
       <c r="BK7">
-        <v>569.1816353976957</v>
+        <v>493.1218643205154</v>
       </c>
       <c r="BL7">
-        <v>0.005691816353976957</v>
+        <v>0.004931218643205153</v>
       </c>
       <c r="BM7">
-        <v>498.1767526636935</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN7">
-        <v>0.004981767526636935</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO7">
-        <v>5.773753891071316</v>
+        <v>0.0865933624677471</v>
       </c>
       <c r="BP7">
-        <v>1.227606902167189</v>
+        <v>0.01482929944942263</v>
       </c>
       <c r="BQ7">
-        <v>2.790657085785341</v>
+        <v>0.02161703774408886</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU7" t="s">
         <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW7" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2371,7 +2383,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2395,19 +2407,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K8">
-        <v>0.9407221123010578</v>
+        <v>0.7971463881552604</v>
       </c>
       <c r="L8">
-        <v>3.62860109327589</v>
+        <v>3.451571604623169</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O8" t="s">
         <v>94</v>
@@ -2416,19 +2428,19 @@
         <v>96</v>
       </c>
       <c r="Q8">
-        <v>0.9851805280752645</v>
+        <v>0.9492865970388151</v>
       </c>
       <c r="R8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T8">
-        <v>-0.9867058542560161</v>
+        <v>-0.9725963678079926</v>
       </c>
       <c r="U8">
-        <v>0.9850481836537166</v>
+        <v>0.9571777461701203</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2437,100 +2449,100 @@
         <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9996889295734031</v>
+        <v>0.9997496897329385</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>166.8213103505525</v>
+        <v>161.2612057631207</v>
       </c>
       <c r="AA8">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="AB8">
-        <v>-0.9736637673900084</v>
+        <v>-0.9469929776991087</v>
       </c>
       <c r="AC8">
-        <v>0.2279887454939294</v>
+        <v>0.3212542609656335</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AF8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AG8" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="AH8">
-        <v>-0.9733608893865243</v>
+        <v>-0.9467559356339555</v>
       </c>
       <c r="AI8">
-        <v>0.9874202203026983</v>
+        <v>0.9793602774739623</v>
       </c>
       <c r="AJ8">
-        <v>-2.80716301597792</v>
+        <v>-2.656004153757917</v>
       </c>
       <c r="AK8">
-        <v>0.5887923391863664</v>
+        <v>0.8395840436118809</v>
       </c>
       <c r="AL8">
-        <v>-4.315599903873433</v>
+        <v>-4.160384258272138</v>
       </c>
       <c r="AM8">
-        <v>5.207316204213797</v>
+        <v>4.559363097133033</v>
       </c>
       <c r="AN8">
-        <v>3.861539043783517</v>
+        <v>3.772165455730732</v>
       </c>
       <c r="AO8">
-        <v>0.03046690176663491</v>
+        <v>0.03100004828199295</v>
       </c>
       <c r="AP8">
-        <v>6.712825</v>
+        <v>6.7079</v>
       </c>
       <c r="AQ8">
-        <v>6.693006122101684</v>
+        <v>6.682849357636917</v>
       </c>
       <c r="AR8">
-        <v>6.676094807777051</v>
+        <v>6.666196346007435</v>
       </c>
       <c r="AS8">
-        <v>6.712825</v>
+        <v>6.7079</v>
       </c>
       <c r="AT8">
-        <v>6.704849999999998</v>
+        <v>6.694999999999999</v>
       </c>
       <c r="AU8">
-        <v>6.693006122101684</v>
+        <v>6.682849357636917</v>
       </c>
       <c r="AV8">
-        <v>6.736331249999999</v>
+        <v>6.73140625</v>
       </c>
       <c r="AW8">
-        <v>-0.002952390073972689</v>
+        <v>-0.003734498481355262</v>
       </c>
       <c r="AX8">
-        <v>0.843132269005734</v>
+        <v>1.065701350197644</v>
       </c>
       <c r="AY8">
-        <v>0.002952390073972689</v>
+        <v>0.003734498481355262</v>
       </c>
       <c r="AZ8">
-        <v>0.4673548274036912</v>
+        <v>0.5114157518655246</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3326451725963088</v>
+        <v>0.2885842481344755</v>
       </c>
       <c r="BC8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2539,58 +2551,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>492.5902640376322</v>
+        <v>474.6432985194076</v>
       </c>
       <c r="BG8">
-        <v>0.003501692655476587</v>
+        <v>0.003504263629451783</v>
       </c>
       <c r="BH8">
-        <v>142788.0882743974</v>
+        <v>142683.3289018901</v>
       </c>
       <c r="BI8">
-        <v>140672.0442090283</v>
+        <v>135447.3717474453</v>
       </c>
       <c r="BJ8">
-        <v>20955.71450306366</v>
+        <v>20192.21690058666</v>
       </c>
       <c r="BK8">
-        <v>1406.720442090283</v>
+        <v>1354.473717474453</v>
       </c>
       <c r="BL8">
-        <v>0.01406720442090283</v>
+        <v>0.01354473717474453</v>
       </c>
       <c r="BM8">
-        <v>492.5902640376323</v>
+        <v>474.6432985194076</v>
       </c>
       <c r="BN8">
-        <v>0.004925902640376323</v>
+        <v>0.004746432985194076</v>
       </c>
       <c r="BO8">
-        <v>0.03321321267119558</v>
+        <v>0.03166055367540967</v>
       </c>
       <c r="BP8">
-        <v>0.003770943632486092</v>
+        <v>0.0002334721750549825</v>
       </c>
       <c r="BQ8">
-        <v>0.01875569766750368</v>
+        <v>0.01583180661918541</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU8" t="s">
         <v>91</v>
       </c>
       <c r="BV8" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW8" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2598,7 +2610,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2622,19 +2634,19 @@
         <v>92</v>
       </c>
       <c r="J9" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.5322898086271723</v>
+        <v>0.3022150780607559</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
@@ -2649,13 +2661,13 @@
         <v>99</v>
       </c>
       <c r="S9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T9">
-        <v>0.8040328903044585</v>
+        <v>0.6492674853593453</v>
       </c>
       <c r="U9">
-        <v>0.7614848539166132</v>
+        <v>0.6919866239514849</v>
       </c>
       <c r="V9" t="s">
         <v>92</v>
@@ -2664,100 +2676,100 @@
         <v>94</v>
       </c>
       <c r="X9">
-        <v>0.9986802131184278</v>
+        <v>0.9992650221591181</v>
       </c>
       <c r="Y9">
-        <v>0.2633578518385805</v>
+        <v>0.6388297233188638</v>
       </c>
       <c r="Z9">
-        <v>-56.64023767166175</v>
+        <v>-70.14342172803055</v>
       </c>
       <c r="AA9">
-        <v>-40</v>
+        <v>-30.99999999999999</v>
       </c>
       <c r="AB9">
-        <v>0.5498943075500854</v>
+        <v>0.3396668531830572</v>
       </c>
       <c r="AC9">
-        <v>-0.8352342488930947</v>
+        <v>-0.9405458143273614</v>
       </c>
       <c r="AD9" t="s">
         <v>92</v>
       </c>
       <c r="AE9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AG9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="AH9">
-        <v>0.3468982088183297</v>
+        <v>0.2781235025491731</v>
       </c>
       <c r="AI9">
-        <v>0.7087548104940669</v>
+        <v>0.7167910906636098</v>
       </c>
       <c r="AJ9">
-        <v>0.5140238509020666</v>
+        <v>0.3954637777536929</v>
       </c>
       <c r="AK9">
-        <v>-0.6735337538144014</v>
+        <v>-0.9428404704996661</v>
       </c>
       <c r="AL9">
-        <v>0.1840277826922503</v>
+        <v>-0.01195494673094893</v>
       </c>
       <c r="AM9">
-        <v>-2.183203764413147</v>
+        <v>-1.908957297092834</v>
       </c>
       <c r="AN9">
-        <v>0.2761722435110276</v>
+        <v>0.3148565047003864</v>
       </c>
       <c r="AO9">
-        <v>0.05615417820083014</v>
+        <v>0.08411778473847624</v>
       </c>
       <c r="AP9">
-        <v>4.78793</v>
+        <v>4.78434</v>
       </c>
       <c r="AQ9">
-        <v>4.769986137370822</v>
+        <v>4.765828513174137</v>
       </c>
       <c r="AR9">
-        <v>4.77088881690915</v>
+        <v>4.76908983510834</v>
       </c>
       <c r="AS9">
-        <v>4.78793</v>
+        <v>4.78434</v>
       </c>
       <c r="AT9">
-        <v>4.75879</v>
+        <v>4.75161</v>
       </c>
       <c r="AU9">
-        <v>4.769986137370822</v>
+        <v>4.765828513174137</v>
       </c>
       <c r="AV9">
-        <v>4.827730000000001</v>
+        <v>4.82414</v>
       </c>
       <c r="AW9">
-        <v>-0.003747728690515228</v>
+        <v>-0.003869182964810892</v>
       </c>
       <c r="AX9">
-        <v>0.4508508198286068</v>
+        <v>0.4651127343181738</v>
       </c>
       <c r="AY9">
-        <v>0.003747728690515228</v>
+        <v>0.003869182964810892</v>
       </c>
       <c r="AZ9">
-        <v>0.4436910989835226</v>
+        <v>0.4389351001644417</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3563089010164774</v>
+        <v>0.3610648998355583</v>
       </c>
       <c r="BC9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2769,22 +2781,22 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.008312569314923163</v>
+        <v>0.008318806773766091</v>
       </c>
       <c r="BH9">
-        <v>60149.87437185921</v>
+        <v>60104.77386934665</v>
       </c>
       <c r="BI9">
-        <v>60149.87437185921</v>
+        <v>60104.77386934665</v>
       </c>
       <c r="BJ9">
         <v>12562.81407035174</v>
       </c>
       <c r="BK9">
-        <v>601.4987437185921</v>
+        <v>601.0477386934665</v>
       </c>
       <c r="BL9">
-        <v>0.006014987437185921</v>
+        <v>0.006010477386934665</v>
       </c>
       <c r="BM9">
         <v>500</v>
@@ -2793,31 +2805,31 @@
         <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.07702222360827576</v>
+        <v>0.08029298674455136</v>
       </c>
       <c r="BP9">
-        <v>0.01817767000981878</v>
+        <v>0.01930475870951393</v>
       </c>
       <c r="BQ9">
-        <v>0.04278758499429432</v>
+        <v>0.04229612592417363</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT9" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU9" t="s">
         <v>91</v>
       </c>
       <c r="BV9" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW9" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2825,7 +2837,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2849,19 +2861,19 @@
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.4644705373884119</v>
+        <v>0.672766288446513</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O10" t="s">
         <v>94</v>
@@ -2873,16 +2885,16 @@
         <v>0.75</v>
       </c>
       <c r="R10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T10">
-        <v>-0.7737186465331317</v>
+        <v>-0.7923531373068823</v>
       </c>
       <c r="U10">
-        <v>0.7479743913347484</v>
+        <v>0.7564604566596984</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
@@ -2891,100 +2903,100 @@
         <v>94</v>
       </c>
       <c r="X10">
-        <v>0.9992040015793563</v>
+        <v>0.9996061794864057</v>
       </c>
       <c r="Y10">
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>-109.6924528889363</v>
+        <v>-113.0624095566154</v>
       </c>
       <c r="AA10">
-        <v>-34</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AB10">
-        <v>-0.3369712431751639</v>
+        <v>-0.3917335584761495</v>
       </c>
       <c r="AC10">
-        <v>-0.9415149394847564</v>
+        <v>-0.9200787027008142</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
       </c>
       <c r="AE10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AF10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AH10">
-        <v>-0.168351507298897</v>
+        <v>-0.1957896428824792</v>
       </c>
       <c r="AI10">
-        <v>0.5809853472856928</v>
+        <v>0.6009195802152922</v>
       </c>
       <c r="AJ10">
-        <v>-0.2259080226308482</v>
+        <v>-0.3849972177905258</v>
       </c>
       <c r="AK10">
-        <v>-0.7709752963208648</v>
+        <v>-1.00807633477444</v>
       </c>
       <c r="AL10">
-        <v>-1.137502229099049</v>
+        <v>-1.393443476071012</v>
       </c>
       <c r="AM10">
-        <v>-1.173432794323517</v>
+        <v>-0.8654607001560514</v>
       </c>
       <c r="AN10">
-        <v>1.202387605559851</v>
+        <v>1.421876780670325</v>
       </c>
       <c r="AO10">
-        <v>0.1321828414642066</v>
+        <v>0.1097510009852973</v>
       </c>
       <c r="AP10">
-        <v>7.7475</v>
+        <v>7.7466</v>
       </c>
       <c r="AQ10">
-        <v>7.701996141752345</v>
+        <v>7.705092681459379</v>
       </c>
       <c r="AR10">
-        <v>7.739082650518592</v>
+        <v>7.74941414163875</v>
       </c>
       <c r="AS10">
-        <v>7.7475</v>
+        <v>7.7466</v>
       </c>
       <c r="AT10">
-        <v>7.647599999999999</v>
+        <v>7.645799999999999</v>
       </c>
       <c r="AU10">
-        <v>7.701996141752345</v>
+        <v>7.705092681459379</v>
       </c>
       <c r="AV10">
-        <v>7.792775</v>
+        <v>7.791875</v>
       </c>
       <c r="AW10">
-        <v>-0.005873360212669165</v>
+        <v>-0.00535813370260769</v>
       </c>
       <c r="AX10">
-        <v>1.005054848098385</v>
+        <v>0.916782297970641</v>
       </c>
       <c r="AY10">
-        <v>0.005873360212669165</v>
+        <v>0.00535813370260769</v>
       </c>
       <c r="AZ10">
-        <v>0.3762040294771592</v>
+        <v>0.3776770317300432</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.4237959705228408</v>
+        <v>0.4223229682699567</v>
       </c>
       <c r="BC10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2996,22 +3008,22 @@
         <v>375</v>
       </c>
       <c r="BG10">
-        <v>0.005843820587286216</v>
+        <v>0.005844499522371099</v>
       </c>
       <c r="BH10">
-        <v>85560.46383213703</v>
+        <v>85550.52457205972</v>
       </c>
       <c r="BI10">
-        <v>64170.34787410277</v>
+        <v>64162.89342904479</v>
       </c>
       <c r="BJ10">
         <v>8282.716731087805</v>
       </c>
       <c r="BK10">
-        <v>641.7034787410278</v>
+        <v>641.6289342904479</v>
       </c>
       <c r="BL10">
-        <v>0.006417034787410278</v>
+        <v>0.006416289342904479</v>
       </c>
       <c r="BM10">
         <v>375</v>
@@ -3020,31 +3032,31 @@
         <v>0.00375</v>
       </c>
       <c r="BO10">
-        <v>0.1065144894943804</v>
+        <v>0.1045528493910911</v>
       </c>
       <c r="BP10">
-        <v>0.02118811331738078</v>
+        <v>0.02119859648397986</v>
       </c>
       <c r="BQ10">
-        <v>0.02374174763745496</v>
+        <v>0.02397693756524604</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU10" t="s">
         <v>91</v>
       </c>
       <c r="BV10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW10" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3052,7 +3064,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3064,7 +3076,7 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
         <v>91</v>
@@ -3076,19 +3088,19 @@
         <v>92</v>
       </c>
       <c r="J11" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.3284909043607342</v>
+        <v>0.113902919212323</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O11" t="s">
         <v>95</v>
@@ -3103,115 +3115,115 @@
         <v>99</v>
       </c>
       <c r="S11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T11">
-        <v>0.740562428887295</v>
+        <v>0.4711543821923891</v>
       </c>
       <c r="U11">
-        <v>0.7330167150300032</v>
+        <v>0.5869151630352247</v>
       </c>
       <c r="V11" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="W11" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="X11">
-        <v>0.9990544881228819</v>
+        <v>0.9995827641945983</v>
       </c>
       <c r="Y11">
-        <v>0.2295652278539875</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <v>-67.08029985022648</v>
+        <v>-81.79632906096435</v>
       </c>
       <c r="AA11">
-        <v>-29</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AB11">
-        <v>0.3894406605921795</v>
+        <v>0.1426923483489294</v>
       </c>
       <c r="AC11">
-        <v>-0.9210515576652193</v>
+        <v>-0.9897670906443938</v>
       </c>
       <c r="AD11" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="AE11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AF11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AH11">
-        <v>0.2391949715608186</v>
+        <v>0.1426328119920414</v>
       </c>
       <c r="AI11">
-        <v>0.6501215412376978</v>
+        <v>0.7178144135710045</v>
       </c>
       <c r="AJ11">
-        <v>0.5678357415307461</v>
+        <v>0.3292356874036996</v>
       </c>
       <c r="AK11">
-        <v>-1.14220262248422</v>
+        <v>-1.80479932208779</v>
       </c>
       <c r="AL11">
-        <v>-0.06179268083553235</v>
+        <v>-0.471504674148112</v>
       </c>
       <c r="AM11">
-        <v>-2.900968096772592</v>
+        <v>-2.50829722002397</v>
       </c>
       <c r="AN11">
-        <v>0.5133339514840164</v>
+        <v>0.7362429268641191</v>
       </c>
       <c r="AO11">
-        <v>0.0819518223584141</v>
+        <v>0.1656483893452242</v>
       </c>
       <c r="AP11">
-        <v>1.15419</v>
+        <v>1.153755</v>
       </c>
       <c r="AQ11">
-        <v>1.132164210723205</v>
+        <v>1.131078063908566</v>
       </c>
       <c r="AR11">
-        <v>1.113282386034773</v>
+        <v>1.111678706946564</v>
       </c>
       <c r="AS11">
-        <v>1.15419</v>
+        <v>1.153755</v>
       </c>
       <c r="AT11">
-        <v>1.140885</v>
+        <v>1.140015</v>
       </c>
       <c r="AU11">
-        <v>1.132164210723205</v>
+        <v>1.131078063908566</v>
       </c>
       <c r="AV11">
-        <v>1.168873859517864</v>
+        <v>1.16887295739429</v>
       </c>
       <c r="AW11">
-        <v>-0.01908333054072158</v>
+        <v>-0.01965489734946718</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.01908333054072158</v>
+        <v>0.01965489734946718</v>
       </c>
       <c r="AZ11">
-        <v>0.4123446167502119</v>
+        <v>0.4123664330192898</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3876553832497882</v>
+        <v>0.3876335669807102</v>
       </c>
       <c r="BC11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3223,55 +3235,55 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.01272222036048105</v>
+        <v>0.01310326489964479</v>
       </c>
       <c r="BH11">
-        <v>39301.31579493362</v>
+        <v>38158.42874500342</v>
       </c>
       <c r="BI11">
-        <v>39301.31579493362</v>
+        <v>38158.42874500342</v>
       </c>
       <c r="BJ11">
-        <v>34050.99315964756</v>
+        <v>33073.2510325012</v>
       </c>
       <c r="BK11">
-        <v>393.0131579493362</v>
+        <v>381.5842874500343</v>
       </c>
       <c r="BL11">
-        <v>0.003930131579493362</v>
+        <v>0.003815842874500343</v>
       </c>
       <c r="BM11">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN11">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO11">
-        <v>0.01646882618068097</v>
+        <v>0.01671159516044496</v>
       </c>
       <c r="BP11">
-        <v>0.003695575496791865</v>
+        <v>0.003898085672842075</v>
       </c>
       <c r="BQ11">
-        <v>0.006069088779006103</v>
+        <v>0.006268572057646876</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05711653950426025</v>
+        <v>0.05656027441121802</v>
       </c>
       <c r="BT11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="BU11" t="s">
         <v>91</v>
       </c>
       <c r="BV11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="BW11" s="2">
-        <v>46308</v>
+        <v>46310</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="141">
   <si>
     <t>Pair</t>
   </si>
@@ -241,30 +241,30 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -277,52 +277,61 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
+    <t>FLAT</t>
+  </si>
+  <si>
     <t>LONG</t>
   </si>
   <si>
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>DOWN_STEADY</t>
+    <t>DOWN_DECELERATING</t>
   </si>
   <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_DECELERATING</t>
+    <t>空头稳态</t>
   </si>
   <si>
     <t>多头加速</t>
@@ -331,28 +340,28 @@
     <t>多头减速</t>
   </si>
   <si>
-    <t>空头稳态</t>
+    <t>空头减速</t>
   </si>
   <si>
     <t>空头加速</t>
   </si>
   <si>
-    <t>空头减速</t>
-  </si>
-  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>下跌</t>
+  </si>
+  <si>
     <t>上涨</t>
   </si>
   <si>
     <t>转换</t>
   </si>
   <si>
-    <t>下跌</t>
+    <t>DOWN_SLOPE</t>
   </si>
   <si>
     <t>UP_STEEPENING</t>
@@ -361,16 +370,16 @@
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
-    <t>DOWN_SLOPE</t>
-  </si>
-  <si>
     <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
+    <t>下降坡延续</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
@@ -379,49 +388,52 @@
     <t>地形转换区</t>
   </si>
   <si>
-    <t>下降坡延续</t>
-  </si>
-  <si>
     <t>上升坡顶钝化</t>
   </si>
   <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.00755,naive=0.00338,drift4=0.005006; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=277.8,naive=34.05,drift4=98.97; naive_cap_applied; model_divergence_guard(abs=714.9,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=5.467,naive=1.109,drift4=2.771; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.0158,naive=0.002863,drift4=0.007745; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01105,naive=0.004024,drift4=0.005052; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.08659,naive=0.01483,drift4=0.02162; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.03166,naive=0.0002335,drift4=0.01583; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.08029,naive=0.0193,drift4=0.0423; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1046,naive=0.0212,drift4=0.02398; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01671,naive=0.003898,drift4=0.006269; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=5.052,naive=1.373,drift4=3.19; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.008055,naive=0.00613,drift4=0.007622; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=287.9,naive=29.21,drift4=93.52; naive_cap_applied; model_divergence_guard(abs=728.8,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01644,naive=0.003674,drift4=0.008291; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.02929,naive=0.001134,drift4=0.01375; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01179,naive=0.008942,drift4=0.0103; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1014,naive=0.03384,drift4=0.05618; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.1317,naive=0.05016,drift4=0.04863; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1343,naive=0.05068,drift4=0.05415; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02187,naive=0.007608,drift4=0.01034; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -1042,145 +1054,136 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K2">
-        <v>0.6827852171250517</v>
+        <v>0.3707565925524526</v>
       </c>
       <c r="L2">
-        <v>1.570696400134309</v>
+        <v>1.964198137243035</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q2">
-        <v>0.9206963042812629</v>
+        <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T2">
-        <v>0.7763367086703723</v>
+        <v>-0.9875211525167262</v>
       </c>
       <c r="U2">
-        <v>0.8517324938063381</v>
+        <v>0.8991693313402891</v>
       </c>
       <c r="V2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9998527693436513</v>
+        <v>0.9966852952995774</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0.4866481629492806</v>
       </c>
       <c r="Z2">
-        <v>54.85116337480898</v>
+        <v>166.5500764688677</v>
       </c>
       <c r="AA2">
-        <v>-5.999999999999996</v>
+        <v>-53</v>
       </c>
       <c r="AB2">
-        <v>0.5757024010987276</v>
+        <v>-0.9725735800624781</v>
       </c>
       <c r="AC2">
-        <v>0.8176593088622912</v>
+        <v>0.2325954242122029</v>
       </c>
       <c r="AD2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AF2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AG2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AH2">
-        <v>0.5756176400563523</v>
+        <v>-0.7205410391909765</v>
       </c>
       <c r="AI2">
-        <v>0.8627898672340636</v>
+        <v>0.8836085414058914</v>
       </c>
       <c r="AJ2">
-        <v>1.077613557470728</v>
+        <v>-1.623134483653261</v>
       </c>
       <c r="AK2">
-        <v>1.560975069807629</v>
+        <v>0.2070668931491191</v>
       </c>
       <c r="AL2">
-        <v>2.475284634128603</v>
+        <v>-1.899610962887603</v>
       </c>
       <c r="AM2">
-        <v>-0.6124997590557972</v>
+        <v>4.86306506272691</v>
       </c>
       <c r="AN2">
-        <v>2.353697948581886</v>
+        <v>1.465803668699609</v>
       </c>
       <c r="AO2">
-        <v>0.06579548243888363</v>
+        <v>0.02888679038373533</v>
       </c>
       <c r="AP2">
-        <v>0.818925</v>
+        <v>155.804</v>
       </c>
       <c r="AQ2">
-        <v>0.8328311285731935</v>
+        <v>155.839095664998</v>
       </c>
       <c r="AR2">
-        <v>0.8364479110144607</v>
+        <v>158.3808808643354</v>
       </c>
       <c r="AS2">
-        <v>0.818925</v>
+        <v>155.804</v>
       </c>
       <c r="AT2">
-        <v>0.8361350000000001</v>
-      </c>
-      <c r="AU2">
-        <v>0.8328311285731935</v>
-      </c>
-      <c r="AV2">
-        <v>0.8096350000000001</v>
+        <v>152.5965</v>
       </c>
       <c r="AW2">
-        <v>0.01698095499977838</v>
-      </c>
-      <c r="AX2">
-        <v>1.496892203788332</v>
+        <v>0.0002252552245000804</v>
       </c>
       <c r="AY2">
-        <v>0.01698095499977838</v>
+        <v>0.0002252552245000804</v>
       </c>
       <c r="AZ2">
-        <v>0.4414308439465426</v>
+        <v>0.4496757260635274</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3585691560534573</v>
+        <v>0.3503242739364726</v>
       </c>
       <c r="BC2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1189,55 +1192,52 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>460.3481521406314</v>
-      </c>
-      <c r="BG2">
-        <v>0.01134414018377744</v>
+        <v>0</v>
       </c>
       <c r="BH2">
-        <v>44075.61894510256</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>40580.25947166514</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>49553.08419167218</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>405.8025947166514</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>0.004058025947166514</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>460.3481521406315</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>0.004603481521406315</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.007549638144235616</v>
+        <v>5.052143871227323</v>
       </c>
       <c r="BP2">
-        <v>0.003380064857932428</v>
+        <v>1.372965314464161</v>
       </c>
       <c r="BQ2">
-        <v>0.005005785034447026</v>
+        <v>3.189849697138333</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BW2" s="2">
         <v>46310</v>
@@ -1263,151 +1263,151 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0.03165600104598355</v>
+        <v>1.833137795769725</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="O3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P3" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
+        <v>101</v>
+      </c>
+      <c r="S3" t="s">
+        <v>106</v>
+      </c>
+      <c r="T3">
+        <v>0.7877561267150857</v>
+      </c>
+      <c r="U3">
+        <v>0.9044774195220939</v>
+      </c>
+      <c r="V3" t="s">
         <v>94</v>
       </c>
-      <c r="P3" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q3">
-        <v>0.75</v>
-      </c>
-      <c r="R3" t="s">
-        <v>99</v>
-      </c>
-      <c r="S3" t="s">
-        <v>104</v>
-      </c>
-      <c r="T3">
-        <v>0.6158939918839855</v>
-      </c>
-      <c r="U3">
-        <v>0.6270906499783299</v>
-      </c>
-      <c r="V3" t="s">
-        <v>108</v>
-      </c>
       <c r="W3" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9997534145221455</v>
+        <v>0.9999486500012214</v>
       </c>
       <c r="Y3">
-        <v>0.05871282590859755</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>-86.84644237015766</v>
+        <v>54.86525010363052</v>
       </c>
       <c r="AA3">
-        <v>-20</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB3">
-        <v>0.05501217834529652</v>
+        <v>0.5755013541478592</v>
       </c>
       <c r="AC3">
-        <v>-0.9984856835396817</v>
+        <v>0.817800826224809</v>
       </c>
       <c r="AD3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="AE3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AH3">
-        <v>0.02911386856978697</v>
+        <v>0.5754718021540266</v>
       </c>
       <c r="AI3">
-        <v>0.4914746051588749</v>
+        <v>0.8626418778182841</v>
       </c>
       <c r="AJ3">
-        <v>0.1514988887513829</v>
+        <v>1.262083861462606</v>
       </c>
       <c r="AK3">
-        <v>-1.4513013772579</v>
+        <v>1.823380424929133</v>
       </c>
       <c r="AL3">
-        <v>-0.4478905679736006</v>
+        <v>2.857590311835407</v>
       </c>
       <c r="AM3">
-        <v>-0.9173147340484979</v>
+        <v>-0.5195046719087689</v>
       </c>
       <c r="AN3">
-        <v>0.4763741290751481</v>
+        <v>2.742310406239305</v>
       </c>
       <c r="AO3">
-        <v>0.2445687240612294</v>
+        <v>0.0666037061766743</v>
       </c>
       <c r="AP3">
-        <v>4342.18</v>
+        <v>0.8248800000000001</v>
       </c>
       <c r="AQ3">
-        <v>4410.328675161845</v>
+        <v>0.84336055150081</v>
       </c>
       <c r="AR3">
-        <v>4924.062250539482</v>
+        <v>0.8479340869091947</v>
       </c>
       <c r="AS3">
-        <v>4342.18</v>
+        <v>0.8248800000000001</v>
       </c>
       <c r="AT3">
-        <v>4076.140000000001</v>
+        <v>0.8480450000000002</v>
       </c>
       <c r="AU3">
-        <v>4410.328675161845</v>
+        <v>0.84336055150081</v>
       </c>
       <c r="AV3">
-        <v>4208.5425</v>
+        <v>0.8125596323327934</v>
       </c>
       <c r="AW3">
-        <v>0.01569457626396072</v>
+        <v>0.02240392723888318</v>
       </c>
       <c r="AX3">
-        <v>0.5099517363153671</v>
+        <v>1.5</v>
       </c>
       <c r="AY3">
-        <v>0.01569457626396072</v>
+        <v>0.02240392723888318</v>
       </c>
       <c r="AZ3">
-        <v>0.3</v>
+        <v>0.463863181671429</v>
       </c>
       <c r="BA3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.4</v>
+        <v>0.336136818328571</v>
       </c>
       <c r="BC3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1416,55 +1416,55 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.03077659148169817</v>
+        <v>0.01493595149258879</v>
       </c>
       <c r="BH3">
-        <v>16246.11355345616</v>
+        <v>33476.27369090611</v>
       </c>
       <c r="BI3">
-        <v>12184.58516509212</v>
+        <v>33476.27369090611</v>
       </c>
       <c r="BJ3">
-        <v>2.806098587597041</v>
+        <v>40583.20445507966</v>
       </c>
       <c r="BK3">
-        <v>121.8458516509212</v>
+        <v>334.7627369090611</v>
       </c>
       <c r="BL3">
-        <v>0.001218458516509212</v>
+        <v>0.003347627369090611</v>
       </c>
       <c r="BM3">
-        <v>375</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN3">
-        <v>0.00375</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO3">
-        <v>277.8144473498009</v>
+        <v>0.008055194325067029</v>
       </c>
       <c r="BP3">
-        <v>34.05499934398202</v>
+        <v>0.006129924800057054</v>
       </c>
       <c r="BQ3">
-        <v>98.9728638107014</v>
+        <v>0.007621729172504024</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW3" s="2">
         <v>46310</v>
@@ -1487,7 +1487,7 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
@@ -1496,145 +1496,145 @@
         <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J4" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K4">
-        <v>0.7767584709530562</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2.324637152564254</v>
+        <v>0.02492614749915493</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q4">
-        <v>0.944189617738264</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T4">
-        <v>-0.9982818662459734</v>
+        <v>0.6373752912759435</v>
       </c>
       <c r="U4">
-        <v>0.9648302177448576</v>
+        <v>0.6367709655424278</v>
       </c>
       <c r="V4" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="W4" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="X4">
-        <v>0.9963584291648447</v>
+        <v>0.9998083378730133</v>
       </c>
       <c r="Y4">
-        <v>0.8446382050838273</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>-175.2068921605852</v>
+        <v>-87.12506249802411</v>
       </c>
       <c r="AA4">
-        <v>-48</v>
+        <v>-17</v>
       </c>
       <c r="AB4">
-        <v>-0.9965029177225527</v>
+        <v>0.05015607232391142</v>
       </c>
       <c r="AC4">
-        <v>-0.08355797370951025</v>
+        <v>-0.9987413921576689</v>
       </c>
       <c r="AD4" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="AE4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AH4">
-        <v>-0.9157467320262193</v>
+        <v>0.02507322965220426</v>
       </c>
       <c r="AI4">
-        <v>0.961691872397425</v>
+        <v>0.4781089601370971</v>
       </c>
       <c r="AJ4">
-        <v>-1.868098377030235</v>
+        <v>0.1122588171426417</v>
       </c>
       <c r="AK4">
-        <v>-0.3613618935501299</v>
+        <v>-1.152165940047503</v>
       </c>
       <c r="AL4">
-        <v>-2.474844600796342</v>
+        <v>-0.2881312433733745</v>
       </c>
       <c r="AM4">
-        <v>4.966267091630977</v>
+        <v>-0.4037334404284169</v>
       </c>
       <c r="AN4">
-        <v>2.005753682561695</v>
+        <v>0.2766360853880414</v>
       </c>
       <c r="AO4">
-        <v>0.03274729429201255</v>
+        <v>0.2458051987708726</v>
       </c>
       <c r="AP4">
-        <v>155.042</v>
+        <v>4349.870000000001</v>
       </c>
       <c r="AQ4">
-        <v>154.8528436124573</v>
+        <v>4426.432037046988</v>
       </c>
       <c r="AR4">
-        <v>157.8386199549882</v>
+        <v>4949.543456823289</v>
       </c>
       <c r="AS4">
-        <v>155.042</v>
+        <v>4349.870000000001</v>
       </c>
       <c r="AT4">
-        <v>151.0725</v>
+        <v>4091.520000000002</v>
       </c>
       <c r="AU4">
-        <v>154.809437</v>
+        <v>4426.432037046988</v>
       </c>
       <c r="AV4">
-        <v>156.48425</v>
+        <v>4216.232500000001</v>
       </c>
       <c r="AW4">
-        <v>-0.00122003320095676</v>
+        <v>0.01760099429338967</v>
       </c>
       <c r="AX4">
-        <v>0.1612501300051985</v>
+        <v>0.5729083307229395</v>
       </c>
       <c r="AY4">
-        <v>0.00122003320095676</v>
+        <v>0.01760099429338967</v>
       </c>
       <c r="AZ4">
-        <v>0.441382008052564</v>
+        <v>0.3</v>
       </c>
       <c r="BA4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BB4">
-        <v>0.358617991947436</v>
+        <v>0.4</v>
       </c>
       <c r="BC4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1643,55 +1643,55 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>472.094808869132</v>
+        <v>375</v>
       </c>
       <c r="BG4">
-        <v>0.009302318081552196</v>
+        <v>0.03072218250200584</v>
       </c>
       <c r="BH4">
-        <v>53750.04333506616</v>
+        <v>16274.88541764099</v>
       </c>
       <c r="BI4">
-        <v>50750.23286995124</v>
+        <v>12206.16406323074</v>
       </c>
       <c r="BJ4">
-        <v>327.3321607690254</v>
+        <v>2.806098587597041</v>
       </c>
       <c r="BK4">
-        <v>507.5023286995124</v>
+        <v>122.0616406323074</v>
       </c>
       <c r="BL4">
-        <v>0.005075023286995124</v>
+        <v>0.001220616406323074</v>
       </c>
       <c r="BM4">
-        <v>472.094808869132</v>
+        <v>375</v>
       </c>
       <c r="BN4">
-        <v>0.00472094808869132</v>
+        <v>0.00375</v>
       </c>
       <c r="BO4">
-        <v>5.467363562190165</v>
+        <v>287.9188629709716</v>
       </c>
       <c r="BP4">
-        <v>1.109304475026002</v>
+        <v>29.21205878589468</v>
       </c>
       <c r="BQ4">
-        <v>2.771100890025697</v>
+        <v>93.51594663334197</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU4" t="s">
         <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW4" s="2">
         <v>46310</v>
@@ -1717,151 +1717,151 @@
         <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J5" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>1.387655313461933</v>
+        <v>0.8577256191889026</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="S5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T5">
-        <v>0.6911000426247549</v>
+        <v>0.6159994718469458</v>
       </c>
       <c r="U5">
-        <v>0.7108173139027903</v>
+        <v>0.677076930841619</v>
       </c>
       <c r="V5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9992891788866024</v>
+        <v>0.9995086740419734</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-61.15483782159379</v>
+        <v>-69.10406610064956</v>
       </c>
       <c r="AA5">
-        <v>-26</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AB5">
-        <v>0.4824442544568019</v>
+        <v>0.3566717008781201</v>
       </c>
       <c r="AC5">
-        <v>-0.8759266757792119</v>
+        <v>-0.9342297885385098</v>
       </c>
       <c r="AD5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AF5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AH5">
-        <v>0.4821013228946967</v>
+        <v>0.3564964588129852</v>
       </c>
       <c r="AI5">
-        <v>0.8369788651536564</v>
+        <v>0.7966078738714228</v>
       </c>
       <c r="AJ5">
-        <v>1.252958774079383</v>
+        <v>0.9181959811564773</v>
       </c>
       <c r="AK5">
-        <v>-2.050207935731843</v>
+        <v>-2.142791983416557</v>
       </c>
       <c r="AL5">
-        <v>0.8579562417671847</v>
+        <v>0.4198628180733306</v>
       </c>
       <c r="AM5">
-        <v>-4.270417556524586</v>
+        <v>-3.418587270096519</v>
       </c>
       <c r="AN5">
-        <v>0.7591683021197938</v>
+        <v>0.5071495902468289</v>
       </c>
       <c r="AO5">
-        <v>0.05003749195796645</v>
+        <v>0.06814448204469208</v>
       </c>
       <c r="AP5">
-        <v>0.7130799999999999</v>
+        <v>0.7112700000000001</v>
       </c>
       <c r="AQ5">
-        <v>0.7121706157788064</v>
+        <v>0.7091669558493195</v>
       </c>
       <c r="AR5">
-        <v>0.7133225344523686</v>
+        <v>0.7103173493284834</v>
       </c>
       <c r="AS5">
-        <v>0.7130799999999999</v>
+        <v>0.7112700000000001</v>
       </c>
       <c r="AT5">
-        <v>0.7102349999999999</v>
+        <v>0.7066150000000002</v>
       </c>
       <c r="AU5">
-        <v>0.7120103799999999</v>
+        <v>0.7091669558493195</v>
       </c>
       <c r="AV5">
-        <v>0.7202887499999999</v>
+        <v>0.7184787500000001</v>
       </c>
       <c r="AW5">
-        <v>-0.001275290600204152</v>
+        <v>-0.002956745189141285</v>
       </c>
       <c r="AX5">
-        <v>0.1483780128316296</v>
+        <v>0.2917349263992429</v>
       </c>
       <c r="AY5">
-        <v>0.001275290600204152</v>
+        <v>0.002956745189141285</v>
       </c>
       <c r="AZ5">
-        <v>0.4426236532382621</v>
+        <v>0.4378181812420854</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3573763467617379</v>
+        <v>0.3621818187579146</v>
       </c>
       <c r="BC5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1873,22 +1873,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.01010931452291458</v>
+        <v>0.01013504013946874</v>
       </c>
       <c r="BH5">
-        <v>49459.33761054322</v>
+        <v>49333.7957343511</v>
       </c>
       <c r="BI5">
-        <v>49459.33761054322</v>
+        <v>49333.7957343511</v>
       </c>
       <c r="BJ5">
         <v>69360.15259233638</v>
       </c>
       <c r="BK5">
-        <v>494.5933761054322</v>
+        <v>493.337957343511</v>
       </c>
       <c r="BL5">
-        <v>0.004945933761054322</v>
+        <v>0.00493337957343511</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1897,28 +1897,28 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.01580466155341744</v>
+        <v>0.01644435989176263</v>
       </c>
       <c r="BP5">
-        <v>0.002863405541138317</v>
+        <v>0.003673898616329937</v>
       </c>
       <c r="BQ5">
-        <v>0.007744731431072243</v>
+        <v>0.008291365289813231</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW5" s="2">
         <v>46310</v>
@@ -1941,154 +1941,154 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.6838933934311553</v>
       </c>
       <c r="L6">
-        <v>0.03416955490130145</v>
+        <v>3.312044073047681</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q6">
+        <v>0.9209733483577889</v>
+      </c>
+      <c r="R6" t="s">
+        <v>103</v>
+      </c>
+      <c r="S6" t="s">
+        <v>108</v>
+      </c>
+      <c r="T6">
+        <v>-0.9776490232765577</v>
+      </c>
+      <c r="U6">
+        <v>0.9425015538993265</v>
+      </c>
+      <c r="V6" t="s">
+        <v>93</v>
+      </c>
+      <c r="W6" t="s">
+        <v>95</v>
+      </c>
+      <c r="X6">
+        <v>0.9999019376408095</v>
+      </c>
+      <c r="Y6">
         <v>1</v>
       </c>
-      <c r="R6" t="s">
-        <v>99</v>
-      </c>
-      <c r="S6" t="s">
-        <v>104</v>
-      </c>
-      <c r="T6">
-        <v>0.5036694739926805</v>
-      </c>
-      <c r="U6">
-        <v>0.6015757688088759</v>
-      </c>
-      <c r="V6" t="s">
-        <v>108</v>
-      </c>
-      <c r="W6" t="s">
-        <v>108</v>
-      </c>
-      <c r="X6">
-        <v>0.9996980220486789</v>
-      </c>
-      <c r="Y6">
-        <v>0.6668888251877514</v>
-      </c>
       <c r="Z6">
-        <v>-83.66999434434932</v>
+        <v>163.2541632768595</v>
       </c>
       <c r="AA6">
-        <v>-12.99999999999999</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AB6">
-        <v>0.11025483087232</v>
+        <v>-0.9575922994502618</v>
       </c>
       <c r="AC6">
-        <v>-0.9939033515736407</v>
+        <v>0.2881266874719525</v>
       </c>
       <c r="AD6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="AE6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AF6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AH6">
-        <v>0.09186352361372788</v>
+        <v>-0.9574983956902351</v>
       </c>
       <c r="AI6">
-        <v>0.6392194039758973</v>
+        <v>0.982465254189971</v>
       </c>
       <c r="AJ6">
-        <v>0.1958238010424785</v>
+        <v>-2.532529145371306</v>
       </c>
       <c r="AK6">
-        <v>-1.45654358879843</v>
+        <v>0.7407625272065881</v>
       </c>
       <c r="AL6">
-        <v>-0.1512775050486639</v>
+        <v>-4.057636880023013</v>
       </c>
       <c r="AM6">
-        <v>-1.358708286649757</v>
+        <v>4.020113645045003</v>
       </c>
       <c r="AN6">
-        <v>0.3236101391705627</v>
+        <v>3.718235628769614</v>
       </c>
       <c r="AO6">
-        <v>0.1808607869359098</v>
+        <v>0.03185409212927249</v>
       </c>
       <c r="AP6">
-        <v>1.345665</v>
+        <v>6.705825</v>
       </c>
       <c r="AQ6">
-        <v>1.343345133276248</v>
+        <v>6.681239077143534</v>
       </c>
       <c r="AR6">
-        <v>1.355913952071206</v>
+        <v>6.665022738036885</v>
       </c>
       <c r="AS6">
-        <v>1.345665</v>
+        <v>6.705825</v>
       </c>
       <c r="AT6">
-        <v>1.328635</v>
+        <v>6.690849999999998</v>
       </c>
       <c r="AU6">
-        <v>1.343345133276248</v>
+        <v>6.681239077143534</v>
       </c>
       <c r="AV6">
-        <v>1.35594625</v>
+        <v>6.72933125</v>
       </c>
       <c r="AW6">
-        <v>-0.001723955608380703</v>
+        <v>-0.003666353186441041</v>
       </c>
       <c r="AX6">
-        <v>0.225640532401374</v>
+        <v>1.045931310033136</v>
       </c>
       <c r="AY6">
-        <v>0.001723955608380703</v>
+        <v>0.003666353186441041</v>
       </c>
       <c r="AZ6">
-        <v>0.4143903052705776</v>
+        <v>0.4880859176814781</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3856096947294223</v>
+        <v>0.3119140823185219</v>
       </c>
       <c r="BC6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2097,55 +2097,55 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>500</v>
+        <v>460.4866741788944</v>
       </c>
       <c r="BG6">
-        <v>0.007640274511115296</v>
+        <v>0.003505347962405762</v>
       </c>
       <c r="BH6">
-        <v>65442.6747720367</v>
+        <v>142639.1917043363</v>
       </c>
       <c r="BI6">
-        <v>65442.6747720367</v>
+        <v>131366.8939909911</v>
       </c>
       <c r="BJ6">
-        <v>48632.21884498497</v>
+        <v>19589.96752688762</v>
       </c>
       <c r="BK6">
-        <v>654.426747720367</v>
+        <v>1313.668939909911</v>
       </c>
       <c r="BL6">
-        <v>0.006544267477203669</v>
+        <v>0.01313668939909911</v>
       </c>
       <c r="BM6">
-        <v>500</v>
+        <v>460.4866741788945</v>
       </c>
       <c r="BN6">
-        <v>0.005</v>
+        <v>0.004604866741788944</v>
       </c>
       <c r="BO6">
-        <v>0.01105031693147255</v>
+        <v>0.02928839371334552</v>
       </c>
       <c r="BP6">
-        <v>0.004024105606280066</v>
+        <v>0.001133733140364289</v>
       </c>
       <c r="BQ6">
-        <v>0.005052235042368639</v>
+        <v>0.01374960726467883</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW6" s="2">
         <v>46310</v>
@@ -2168,82 +2168,82 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.457979184325273</v>
+        <v>0.3223109922322406</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T7">
-        <v>-0.8677601508868771</v>
+        <v>-0.4848709250354737</v>
       </c>
       <c r="U7">
-        <v>0.7903499084832597</v>
+        <v>0.6181497420822262</v>
       </c>
       <c r="V7" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="W7" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="X7">
-        <v>0.9994313623366604</v>
+        <v>0.9998313032650523</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7">
-        <v>-127.7763647042577</v>
+        <v>-97.88007791281441</v>
       </c>
       <c r="AA7">
-        <v>-21</v>
+        <v>-11</v>
       </c>
       <c r="AB7">
-        <v>-0.612581051722029</v>
+        <v>-0.1371001316370621</v>
       </c>
       <c r="AC7">
-        <v>-0.7904077777142207</v>
+        <v>-0.9905571936567319</v>
       </c>
       <c r="AD7" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="AE7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF7" t="s">
         <v>117</v>
@@ -2252,70 +2252,70 @@
         <v>123</v>
       </c>
       <c r="AH7">
-        <v>-0.3061163575320859</v>
+        <v>-0.137077003292494</v>
       </c>
       <c r="AI7">
-        <v>0.6735269321142432</v>
+        <v>0.7112252278539652</v>
       </c>
       <c r="AJ7">
-        <v>-0.3197280199864684</v>
+        <v>-0.2247172167165957</v>
       </c>
       <c r="AK7">
-        <v>-0.4517362144464229</v>
+        <v>-1.855469446779309</v>
       </c>
       <c r="AL7">
-        <v>-0.6943676706362006</v>
+        <v>-1.054361149087296</v>
       </c>
       <c r="AM7">
-        <v>0.2027265347920631</v>
+        <v>-1.453125711083343</v>
       </c>
       <c r="AN7">
-        <v>0.6599940573354511</v>
+        <v>1.134914451439164</v>
       </c>
       <c r="AO7">
-        <v>0.06698906813464363</v>
+        <v>0.1989717851994777</v>
       </c>
       <c r="AP7">
-        <v>9.042540000000001</v>
+        <v>1.337245</v>
       </c>
       <c r="AQ7">
-        <v>9.016160174813486</v>
+        <v>1.332331332521422</v>
       </c>
       <c r="AR7">
-        <v>9.098060665280402</v>
+        <v>1.345615160085486</v>
       </c>
       <c r="AS7">
-        <v>9.042540000000001</v>
+        <v>1.337245</v>
       </c>
       <c r="AT7">
-        <v>8.924660000000001</v>
+        <v>1.311795</v>
       </c>
       <c r="AU7">
-        <v>9.016160174813486</v>
+        <v>1.332331332521422</v>
       </c>
       <c r="AV7">
-        <v>9.111305</v>
+        <v>1.348895</v>
       </c>
       <c r="AW7">
-        <v>-0.002917302570573649</v>
+        <v>-0.003674470630720722</v>
       </c>
       <c r="AX7">
-        <v>0.3836228486368826</v>
+        <v>0.4217740324959772</v>
       </c>
       <c r="AY7">
-        <v>0.002917302570573649</v>
+        <v>0.003674470630720722</v>
       </c>
       <c r="AZ7">
-        <v>0.3917180750353307</v>
+        <v>0.4567196749624623</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.4082819249646693</v>
+        <v>0.3432803250375378</v>
       </c>
       <c r="BC7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2327,22 +2327,22 @@
         <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.007604611093785542</v>
+        <v>0.008711941342087645</v>
       </c>
       <c r="BH7">
-        <v>65749.58190940206</v>
+        <v>57392.4892703863</v>
       </c>
       <c r="BI7">
-        <v>49312.18643205155</v>
+        <v>43044.36695278973</v>
       </c>
       <c r="BJ7">
-        <v>5453.355631498621</v>
+        <v>32188.84120171676</v>
       </c>
       <c r="BK7">
-        <v>493.1218643205154</v>
+        <v>430.4436695278973</v>
       </c>
       <c r="BL7">
-        <v>0.004931218643205153</v>
+        <v>0.004304436695278973</v>
       </c>
       <c r="BM7">
         <v>375.0000000000001</v>
@@ -2351,28 +2351,28 @@
         <v>0.003750000000000001</v>
       </c>
       <c r="BO7">
-        <v>0.0865933624677471</v>
+        <v>0.01178681730397356</v>
       </c>
       <c r="BP7">
-        <v>0.01482929944942263</v>
+        <v>0.008941883202846395</v>
       </c>
       <c r="BQ7">
-        <v>0.02161703774408886</v>
+        <v>0.01030111114841202</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW7" s="2">
         <v>46310</v>
@@ -2395,40 +2395,40 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J8" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K8">
-        <v>0.7971463881552604</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>3.451571604623169</v>
+        <v>0.06524719674745511</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q8">
-        <v>0.9492865970388151</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
         <v>102</v>
@@ -2437,112 +2437,112 @@
         <v>107</v>
       </c>
       <c r="T8">
-        <v>-0.9725963678079926</v>
+        <v>0.4344034749202256</v>
       </c>
       <c r="U8">
-        <v>0.9571777461701203</v>
+        <v>0.545387314894983</v>
       </c>
       <c r="V8" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="W8" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="X8">
-        <v>0.9997496897329385</v>
+        <v>0.9996230047235263</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>161.2612057631207</v>
+        <v>-83.46685860511681</v>
       </c>
       <c r="AA8">
-        <v>-11</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AB8">
-        <v>-0.9469929776991087</v>
+        <v>0.1137779030489081</v>
       </c>
       <c r="AC8">
-        <v>0.3212542609656335</v>
+        <v>-0.99350620973288</v>
       </c>
       <c r="AD8" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="AE8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AH8">
-        <v>-0.9467559356339555</v>
+        <v>0.1137350093168916</v>
       </c>
       <c r="AI8">
-        <v>0.9793602774739623</v>
+        <v>0.7051261272952865</v>
       </c>
       <c r="AJ8">
-        <v>-2.656004153757917</v>
+        <v>0.1910823272299699</v>
       </c>
       <c r="AK8">
-        <v>0.8395840436118809</v>
+        <v>-1.28837034492356</v>
       </c>
       <c r="AL8">
-        <v>-4.160384258272138</v>
+        <v>-0.3878254263067406</v>
       </c>
       <c r="AM8">
-        <v>4.559363097133033</v>
+        <v>-1.709134775113346</v>
       </c>
       <c r="AN8">
-        <v>3.772165455730732</v>
+        <v>0.5484235748821181</v>
       </c>
       <c r="AO8">
-        <v>0.03100004828199295</v>
+        <v>0.1925019684841343</v>
       </c>
       <c r="AP8">
-        <v>6.7079</v>
+        <v>4.75648</v>
       </c>
       <c r="AQ8">
-        <v>6.682849357636917</v>
+        <v>4.727469534237068</v>
       </c>
       <c r="AR8">
-        <v>6.666196346007435</v>
+        <v>4.740797338810489</v>
       </c>
       <c r="AS8">
-        <v>6.7079</v>
+        <v>4.75648</v>
       </c>
       <c r="AT8">
-        <v>6.694999999999999</v>
+        <v>4.695889999999999</v>
       </c>
       <c r="AU8">
-        <v>6.682849357636917</v>
+        <v>4.727469534237068</v>
       </c>
       <c r="AV8">
-        <v>6.73140625</v>
+        <v>4.805215</v>
       </c>
       <c r="AW8">
-        <v>-0.003734498481355262</v>
+        <v>-0.006099145957290214</v>
       </c>
       <c r="AX8">
-        <v>1.065701350197644</v>
+        <v>0.5952696370766754</v>
       </c>
       <c r="AY8">
-        <v>0.003734498481355262</v>
+        <v>0.006099145957290214</v>
       </c>
       <c r="AZ8">
-        <v>0.5114157518655246</v>
+        <v>0.4333709089108385</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.2885842481344755</v>
+        <v>0.3666290910891615</v>
       </c>
       <c r="BC8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2551,55 +2551,55 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>474.6432985194076</v>
+        <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.003504263629451783</v>
+        <v>0.01024602226856835</v>
       </c>
       <c r="BH8">
-        <v>142683.3289018901</v>
+        <v>48799.42546424543</v>
       </c>
       <c r="BI8">
-        <v>135447.3717474453</v>
+        <v>48799.42546424543</v>
       </c>
       <c r="BJ8">
-        <v>20192.21690058666</v>
+        <v>10259.56704627065</v>
       </c>
       <c r="BK8">
-        <v>1354.473717474453</v>
+        <v>487.9942546424543</v>
       </c>
       <c r="BL8">
-        <v>0.01354473717474453</v>
+        <v>0.004879942546424543</v>
       </c>
       <c r="BM8">
-        <v>474.6432985194076</v>
+        <v>500</v>
       </c>
       <c r="BN8">
-        <v>0.004746432985194076</v>
+        <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.03166055367540967</v>
+        <v>0.1014184106043558</v>
       </c>
       <c r="BP8">
-        <v>0.0002334721750549825</v>
+        <v>0.03383798261114321</v>
       </c>
       <c r="BQ8">
-        <v>0.01583180661918541</v>
+        <v>0.05618473652729796</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW8" s="2">
         <v>46310</v>
@@ -2622,154 +2622,154 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.01880191757619046</v>
       </c>
       <c r="L9">
-        <v>0.3022150780607559</v>
+        <v>0.6964939566289734</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.7547004793940476</v>
       </c>
       <c r="R9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="S9" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="T9">
-        <v>0.6492674853593453</v>
+        <v>-0.7794743312517826</v>
       </c>
       <c r="U9">
-        <v>0.6919866239514849</v>
+        <v>0.7535444680721862</v>
       </c>
       <c r="V9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9992650221591181</v>
+        <v>0.9998429254898222</v>
       </c>
       <c r="Y9">
-        <v>0.6388297233188638</v>
+        <v>0.4370428318113841</v>
       </c>
       <c r="Z9">
-        <v>-70.14342172803055</v>
+        <v>-122.8576661840473</v>
       </c>
       <c r="AA9">
-        <v>-30.99999999999999</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB9">
-        <v>0.3396668531830572</v>
+        <v>-0.5425539364530436</v>
       </c>
       <c r="AC9">
-        <v>-0.9405458143273614</v>
+        <v>-0.8400209676188486</v>
       </c>
       <c r="AD9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AF9" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AH9">
-        <v>0.2781235025491731</v>
+        <v>-0.3897753892288995</v>
       </c>
       <c r="AI9">
-        <v>0.7167910906636098</v>
+        <v>0.7390183193719653</v>
       </c>
       <c r="AJ9">
-        <v>0.3954637777536929</v>
+        <v>-0.4755050419453364</v>
       </c>
       <c r="AK9">
-        <v>-0.9428404704996661</v>
+        <v>-0.7517380353983013</v>
       </c>
       <c r="AL9">
-        <v>-0.01195494673094893</v>
+        <v>-1.093101510666785</v>
       </c>
       <c r="AM9">
-        <v>-1.908957297092834</v>
+        <v>-0.07158285209649816</v>
       </c>
       <c r="AN9">
-        <v>0.3148565047003864</v>
+        <v>1.078841554071325</v>
       </c>
       <c r="AO9">
-        <v>0.08411778473847624</v>
+        <v>0.07400967898441663</v>
       </c>
       <c r="AP9">
-        <v>4.78434</v>
+        <v>8.981999999999999</v>
       </c>
       <c r="AQ9">
-        <v>4.765828513174137</v>
+        <v>8.927056110058018</v>
       </c>
       <c r="AR9">
-        <v>4.76908983510834</v>
+        <v>9.026107434366153</v>
       </c>
       <c r="AS9">
-        <v>4.78434</v>
+        <v>8.981999999999999</v>
       </c>
       <c r="AT9">
-        <v>4.75161</v>
+        <v>8.803579999999998</v>
       </c>
       <c r="AU9">
-        <v>4.765828513174137</v>
+        <v>8.927056110058018</v>
       </c>
       <c r="AV9">
-        <v>4.82414</v>
+        <v>9.063067499999999</v>
       </c>
       <c r="AW9">
-        <v>-0.003869182964810892</v>
+        <v>-0.0061171108819841</v>
       </c>
       <c r="AX9">
-        <v>0.4651127343181738</v>
+        <v>0.6777548332189982</v>
       </c>
       <c r="AY9">
-        <v>0.003869182964810892</v>
+        <v>0.0061171108819841</v>
       </c>
       <c r="AZ9">
-        <v>0.4389351001644417</v>
+        <v>0.3945226363126192</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3610648998355583</v>
+        <v>0.4054773636873809</v>
       </c>
       <c r="BC9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2778,55 +2778,55 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>500</v>
+        <v>377.3502396970238</v>
       </c>
       <c r="BG9">
-        <v>0.008318806773766091</v>
+        <v>0.009025551102204417</v>
       </c>
       <c r="BH9">
-        <v>60104.77386934665</v>
+        <v>55398.27921176793</v>
       </c>
       <c r="BI9">
-        <v>60104.77386934665</v>
+        <v>41809.10787872656</v>
       </c>
       <c r="BJ9">
-        <v>12562.81407035174</v>
+        <v>4654.765962895409</v>
       </c>
       <c r="BK9">
-        <v>601.0477386934665</v>
+        <v>418.0910787872656</v>
       </c>
       <c r="BL9">
-        <v>0.006010477386934665</v>
+        <v>0.004180910787872655</v>
       </c>
       <c r="BM9">
-        <v>500</v>
+        <v>377.3502396970238</v>
       </c>
       <c r="BN9">
-        <v>0.005</v>
+        <v>0.003773502396970238</v>
       </c>
       <c r="BO9">
-        <v>0.08029298674455136</v>
+        <v>0.131666544532077</v>
       </c>
       <c r="BP9">
-        <v>0.01930475870951393</v>
+        <v>0.05015578782799125</v>
       </c>
       <c r="BQ9">
-        <v>0.04229612592417363</v>
+        <v>0.04862684645879806</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW9" s="2">
         <v>46310</v>
@@ -2849,76 +2849,76 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.672766288446513</v>
+        <v>1.070761368424196</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q10">
         <v>0.75</v>
       </c>
       <c r="R10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="S10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T10">
-        <v>-0.7923531373068823</v>
+        <v>-0.714030007035483</v>
       </c>
       <c r="U10">
-        <v>0.7564604566596984</v>
+        <v>0.7212776062636812</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
       </c>
       <c r="W10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9996061794864057</v>
+        <v>0.9998564123908554</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>0.4451120696948463</v>
       </c>
       <c r="Z10">
-        <v>-113.0624095566154</v>
+        <v>-114.3341943260237</v>
       </c>
       <c r="AA10">
-        <v>-22.99999999999999</v>
+        <v>-12</v>
       </c>
       <c r="AB10">
-        <v>-0.3917335584761495</v>
+        <v>-0.4120582140207711</v>
       </c>
       <c r="AC10">
-        <v>-0.9200787027008142</v>
+        <v>-0.9111575211005023</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
@@ -2927,76 +2927,76 @@
         <v>112</v>
       </c>
       <c r="AF10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AH10">
-        <v>-0.1957896428824792</v>
+        <v>-0.2976923981709202</v>
       </c>
       <c r="AI10">
-        <v>0.6009195802152922</v>
+        <v>0.6982067874420025</v>
       </c>
       <c r="AJ10">
-        <v>-0.3849972177905258</v>
+        <v>-0.663143586345423</v>
       </c>
       <c r="AK10">
-        <v>-1.00807633477444</v>
+        <v>-1.535824737971604</v>
       </c>
       <c r="AL10">
-        <v>-1.393443476071012</v>
+        <v>-1.983768835891844</v>
       </c>
       <c r="AM10">
-        <v>-0.8654607001560514</v>
+        <v>-0.943282125898916</v>
       </c>
       <c r="AN10">
-        <v>1.421876780670325</v>
+        <v>2.010883721962682</v>
       </c>
       <c r="AO10">
-        <v>0.1097510009852973</v>
+        <v>0.09588556693331662</v>
       </c>
       <c r="AP10">
-        <v>7.7466</v>
+        <v>7.6952</v>
       </c>
       <c r="AQ10">
-        <v>7.705092681459379</v>
+        <v>7.620994286062185</v>
       </c>
       <c r="AR10">
-        <v>7.74941414163875</v>
+        <v>7.661168106456968</v>
       </c>
       <c r="AS10">
-        <v>7.7466</v>
+        <v>7.6952</v>
       </c>
       <c r="AT10">
-        <v>7.645799999999999</v>
+        <v>7.542999999999999</v>
       </c>
       <c r="AU10">
-        <v>7.705092681459379</v>
+        <v>7.620994286062185</v>
       </c>
       <c r="AV10">
-        <v>7.791875</v>
+        <v>7.744875</v>
       </c>
       <c r="AW10">
-        <v>-0.00535813370260769</v>
+        <v>-0.009643116999923942</v>
       </c>
       <c r="AX10">
-        <v>0.916782297970641</v>
+        <v>1.493824135637924</v>
       </c>
       <c r="AY10">
-        <v>0.00535813370260769</v>
+        <v>0.009643116999923942</v>
       </c>
       <c r="AZ10">
-        <v>0.3776770317300432</v>
+        <v>0.4024291112721</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.4223229682699567</v>
+        <v>0.3975708887279</v>
       </c>
       <c r="BC10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -3008,52 +3008,52 @@
         <v>375</v>
       </c>
       <c r="BG10">
-        <v>0.005844499522371099</v>
+        <v>0.006455322798627792</v>
       </c>
       <c r="BH10">
-        <v>85550.52457205972</v>
+        <v>77455.46049320493</v>
       </c>
       <c r="BI10">
-        <v>64162.89342904479</v>
+        <v>58091.59536990369</v>
       </c>
       <c r="BJ10">
-        <v>8282.716731087805</v>
+        <v>7549.068948162971</v>
       </c>
       <c r="BK10">
-        <v>641.6289342904479</v>
+        <v>580.9159536990369</v>
       </c>
       <c r="BL10">
-        <v>0.006416289342904479</v>
+        <v>0.005809159536990369</v>
       </c>
       <c r="BM10">
-        <v>375</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN10">
-        <v>0.00375</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO10">
-        <v>0.1045528493910911</v>
+        <v>0.1342660224642186</v>
       </c>
       <c r="BP10">
-        <v>0.02119859648397986</v>
+        <v>0.05067553755355485</v>
       </c>
       <c r="BQ10">
-        <v>0.02397693756524604</v>
+        <v>0.05415077402845746</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW10" s="2">
         <v>46310</v>
@@ -3076,154 +3076,154 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J11" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.113902919212323</v>
+        <v>0.2823585839149488</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="S11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="T11">
-        <v>0.4711543821923891</v>
+        <v>0.2673946141720625</v>
       </c>
       <c r="U11">
-        <v>0.5869151630352247</v>
+        <v>0.420269735781742</v>
       </c>
       <c r="V11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="X11">
-        <v>0.9995827641945983</v>
+        <v>0.9997686376172555</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-81.79632906096435</v>
+        <v>-93.92557157819374</v>
       </c>
       <c r="AA11">
-        <v>-21.99999999999999</v>
+        <v>-17</v>
       </c>
       <c r="AB11">
-        <v>0.1426923483489294</v>
+        <v>-0.06846055858543516</v>
       </c>
       <c r="AC11">
-        <v>-0.9897670906443938</v>
+        <v>-0.9976538236874403</v>
       </c>
       <c r="AD11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AE11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AF11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AG11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AH11">
-        <v>0.1426328119920414</v>
+        <v>-0.06844471938747682</v>
       </c>
       <c r="AI11">
-        <v>0.7178144135710045</v>
+        <v>0.6812703624360725</v>
       </c>
       <c r="AJ11">
-        <v>0.3292356874036996</v>
+        <v>-0.09177323229322928</v>
       </c>
       <c r="AK11">
-        <v>-1.80479932208779</v>
+        <v>-2.185662763802843</v>
       </c>
       <c r="AL11">
-        <v>-0.471504674148112</v>
+        <v>-1.226663472154302</v>
       </c>
       <c r="AM11">
-        <v>-2.50829722002397</v>
+        <v>-2.187890960935691</v>
       </c>
       <c r="AN11">
-        <v>0.7362429268641191</v>
+        <v>1.346423448110695</v>
       </c>
       <c r="AO11">
-        <v>0.1656483893452242</v>
+        <v>0.2612455220373168</v>
       </c>
       <c r="AP11">
-        <v>1.153755</v>
+        <v>1.14728</v>
       </c>
       <c r="AQ11">
-        <v>1.131078063908566</v>
+        <v>1.119843012655404</v>
       </c>
       <c r="AR11">
-        <v>1.111678706946564</v>
+        <v>1.100156089037617</v>
       </c>
       <c r="AS11">
-        <v>1.153755</v>
+        <v>1.14728</v>
       </c>
       <c r="AT11">
-        <v>1.140015</v>
+        <v>1.127065</v>
       </c>
       <c r="AU11">
-        <v>1.131078063908566</v>
+        <v>1.119843012655404</v>
       </c>
       <c r="AV11">
-        <v>1.16887295739429</v>
+        <v>1.165571324896397</v>
       </c>
       <c r="AW11">
-        <v>-0.01965489734946718</v>
+        <v>-0.02391481359789753</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.01965489734946718</v>
+        <v>0.02391481359789753</v>
       </c>
       <c r="AZ11">
-        <v>0.4123664330192898</v>
+        <v>0.4186340859480997</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3876335669807102</v>
+        <v>0.3813659140519003</v>
       </c>
       <c r="BC11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3235,22 +3235,22 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.01310326489964479</v>
+        <v>0.01594320906526502</v>
       </c>
       <c r="BH11">
-        <v>38158.42874500342</v>
+        <v>31361.31489922783</v>
       </c>
       <c r="BI11">
-        <v>38158.42874500342</v>
+        <v>31361.31489922783</v>
       </c>
       <c r="BJ11">
-        <v>33073.2510325012</v>
+        <v>27335.36268324021</v>
       </c>
       <c r="BK11">
-        <v>381.5842874500343</v>
+        <v>313.6131489922784</v>
       </c>
       <c r="BL11">
-        <v>0.003815842874500343</v>
+        <v>0.003136131489922784</v>
       </c>
       <c r="BM11">
         <v>500</v>
@@ -3259,28 +3259,28 @@
         <v>0.005</v>
       </c>
       <c r="BO11">
-        <v>0.01671159516044496</v>
+        <v>0.02186621370010488</v>
       </c>
       <c r="BP11">
-        <v>0.003898085672842075</v>
+        <v>0.007607723167977256</v>
       </c>
       <c r="BQ11">
-        <v>0.006268572057646876</v>
+        <v>0.01033844380630339</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05656027441121802</v>
+        <v>0.04494889380443722</v>
       </c>
       <c r="BT11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW11" s="2">
         <v>46310</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="137">
   <si>
     <t>Pair</t>
   </si>
@@ -241,15 +241,15 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
@@ -277,72 +277,66 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
-    <t>UP_ACCELERATING</t>
-  </si>
-  <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头减速</t>
+  </si>
+  <si>
+    <t>空头减速</t>
+  </si>
+  <si>
     <t>空头稳态</t>
   </si>
   <si>
-    <t>多头加速</t>
-  </si>
-  <si>
-    <t>多头减速</t>
-  </si>
-  <si>
-    <t>空头减速</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
@@ -352,88 +346,82 @@
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
-    <t>上涨</t>
-  </si>
-  <si>
-    <t>转换</t>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
-    <t>UP_STEEPENING</t>
-  </si>
-  <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
-  </si>
-  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
     <t>下降坡延续</t>
   </si>
   <si>
-    <t>上升陡坡形成</t>
-  </si>
-  <si>
-    <t>地形转换区</t>
-  </si>
-  <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>下降谷底收敛</t>
-  </si>
-  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=5.052,naive=1.373,drift4=3.19; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.008055,naive=0.00613,drift4=0.007622; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=287.9,naive=29.21,drift4=93.52; naive_cap_applied; model_divergence_guard(abs=728.8,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01644,naive=0.003674,drift4=0.008291; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.02929,naive=0.001134,drift4=0.01375; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01179,naive=0.008942,drift4=0.0103; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1014,naive=0.03384,drift4=0.05618; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.1317,naive=0.05016,drift4=0.04863; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1343,naive=0.05068,drift4=0.05415; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02187,naive=0.007608,drift4=0.01034; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.008401,naive=0.006561,drift4=0.008057; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=299,naive=29.49,drift4=90.52; naive_cap_applied; model_divergence_guard(abs=725.7,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=5.261,naive=2.412,drift4=4.31; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01576,naive=0.003185,drift4=0.007782; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03182,naive=0.005634,drift4=0.01081; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01308,naive=0.01055,drift4=0.01203; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.09426,naive=0.02858,drift4=0.05057; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1561,naive=0.06724,drift4=0.06576; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1368,naive=0.05261,drift4=0.05618; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.0229,naive=0.008356,drift4=0.01118; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -1033,7 +1021,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1054,136 +1042,145 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K2">
-        <v>0.3707565925524526</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1.964198137243035</v>
+        <v>2.219972358040653</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="O2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T2">
-        <v>-0.9875211525167262</v>
+        <v>0.8080428531121724</v>
       </c>
       <c r="U2">
-        <v>0.8991693313402891</v>
+        <v>0.913616507569292</v>
       </c>
       <c r="V2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9966852952995774</v>
+        <v>0.9999888946752581</v>
       </c>
       <c r="Y2">
-        <v>0.4866481629492806</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>166.5500764688677</v>
+        <v>51.96930300464032</v>
       </c>
       <c r="AA2">
-        <v>-53</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB2">
-        <v>-0.9725735800624781</v>
+        <v>0.6160835744542178</v>
       </c>
       <c r="AC2">
-        <v>0.2325954242122029</v>
+        <v>0.7876807914934287</v>
       </c>
       <c r="AD2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AH2">
-        <v>-0.7205410391909765</v>
+        <v>0.6160767326460553</v>
       </c>
       <c r="AI2">
-        <v>0.8836085414058914</v>
+        <v>0.8753104062886309</v>
       </c>
       <c r="AJ2">
-        <v>-1.623134483653261</v>
+        <v>1.556851134476295</v>
       </c>
       <c r="AK2">
-        <v>0.2070668931491191</v>
+        <v>2.039565441109928</v>
       </c>
       <c r="AL2">
-        <v>-1.899610962887603</v>
+        <v>3.338512226818299</v>
       </c>
       <c r="AM2">
-        <v>4.86306506272691</v>
+        <v>-1.112094145329638</v>
       </c>
       <c r="AN2">
-        <v>1.465803668699609</v>
+        <v>3.157360108686769</v>
       </c>
       <c r="AO2">
-        <v>0.02888679038373533</v>
+        <v>0.06340519455983201</v>
       </c>
       <c r="AP2">
-        <v>155.804</v>
+        <v>0.8256600000000001</v>
       </c>
       <c r="AQ2">
-        <v>155.839095664998</v>
+        <v>0.8448130489169474</v>
       </c>
       <c r="AR2">
-        <v>158.3808808643354</v>
+        <v>0.8495986504576727</v>
       </c>
       <c r="AS2">
-        <v>155.804</v>
+        <v>0.8256600000000001</v>
       </c>
       <c r="AT2">
-        <v>152.5965</v>
+        <v>0.8496050000000002</v>
+      </c>
+      <c r="AU2">
+        <v>0.8448130489169474</v>
+      </c>
+      <c r="AV2">
+        <v>0.8128913007220352</v>
       </c>
       <c r="AW2">
-        <v>0.0002252552245000804</v>
+        <v>0.02319725906177767</v>
+      </c>
+      <c r="AX2">
+        <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.0002252552245000804</v>
+        <v>0.02319725906177767</v>
       </c>
       <c r="AZ2">
-        <v>0.4496757260635274</v>
+        <v>0.4647709867175697</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3503242739364726</v>
+        <v>0.3352290132824303</v>
       </c>
       <c r="BC2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1192,55 +1189,58 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="BG2">
+        <v>0.01546483937451845</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>32331.40596493064</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>32331.40596493064</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>39158.25638268856</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>323.3140596493064</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>0.003233140596493064</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="BO2">
-        <v>5.052143871227323</v>
+        <v>0.00840071228868911</v>
       </c>
       <c r="BP2">
-        <v>1.372965314464161</v>
+        <v>0.006561205526185899</v>
       </c>
       <c r="BQ2">
-        <v>3.189849697138333</v>
+        <v>0.008057314406635653</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BW2" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1263,151 +1263,151 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J3" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>1.833137795769725</v>
+        <v>0.04969460202241648</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T3">
-        <v>0.7877561267150857</v>
+        <v>0.7023511159933751</v>
       </c>
       <c r="U3">
-        <v>0.9044774195220939</v>
+        <v>0.7158272077718091</v>
       </c>
       <c r="V3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="W3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="X3">
-        <v>0.9999486500012214</v>
+        <v>0.9990768222991612</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>54.86525010363052</v>
+        <v>-82.65846887999095</v>
       </c>
       <c r="AA3">
-        <v>-4.999999999999995</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB3">
-        <v>0.5755013541478592</v>
+        <v>0.1277835545917157</v>
       </c>
       <c r="AC3">
-        <v>0.817800826224809</v>
+        <v>-0.9918020786305632</v>
       </c>
       <c r="AD3" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="AE3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AH3">
-        <v>0.5754718021540266</v>
+        <v>0.06383279383179137</v>
       </c>
       <c r="AI3">
-        <v>0.8626418778182841</v>
+        <v>0.5135323923098526</v>
       </c>
       <c r="AJ3">
-        <v>1.262083861462606</v>
+        <v>0.1318101331374104</v>
       </c>
       <c r="AK3">
-        <v>1.823380424929133</v>
+        <v>-0.836292051867517</v>
       </c>
       <c r="AL3">
-        <v>2.857590311835407</v>
+        <v>-0.08946860949674705</v>
       </c>
       <c r="AM3">
-        <v>-0.5195046719087689</v>
+        <v>-0.05403530635355595</v>
       </c>
       <c r="AN3">
-        <v>2.742310406239305</v>
+        <v>0.1139465447500654</v>
       </c>
       <c r="AO3">
-        <v>0.0666037061766743</v>
+        <v>0.1631970791491234</v>
       </c>
       <c r="AP3">
-        <v>0.8248800000000001</v>
+        <v>4372.83</v>
       </c>
       <c r="AQ3">
-        <v>0.84336055150081</v>
+        <v>4461.07432301373</v>
       </c>
       <c r="AR3">
-        <v>0.8479340869091947</v>
+        <v>4980.831076712437</v>
       </c>
       <c r="AS3">
-        <v>0.8248800000000001</v>
+        <v>4372.83</v>
       </c>
       <c r="AT3">
-        <v>0.8480450000000002</v>
+        <v>4137.440000000001</v>
       </c>
       <c r="AU3">
-        <v>0.84336055150081</v>
+        <v>4461.07432301373</v>
       </c>
       <c r="AV3">
-        <v>0.8125596323327934</v>
+        <v>4239.1925</v>
       </c>
       <c r="AW3">
-        <v>0.02240392723888318</v>
+        <v>0.02018014032416777</v>
       </c>
       <c r="AX3">
-        <v>1.5</v>
+        <v>0.6603260537927635</v>
       </c>
       <c r="AY3">
-        <v>0.02240392723888318</v>
+        <v>0.02018014032416777</v>
       </c>
       <c r="AZ3">
-        <v>0.463863181671429</v>
+        <v>0.3</v>
       </c>
       <c r="BA3">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BB3">
-        <v>0.336136818328571</v>
+        <v>0.4</v>
       </c>
       <c r="BC3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1416,58 +1416,58 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG3">
-        <v>0.01493595149258879</v>
+        <v>0.03056087247846364</v>
       </c>
       <c r="BH3">
-        <v>33476.27369090611</v>
+        <v>16360.78944906929</v>
       </c>
       <c r="BI3">
-        <v>33476.27369090611</v>
+        <v>12270.59208680197</v>
       </c>
       <c r="BJ3">
-        <v>40583.20445507966</v>
+        <v>2.806098587597041</v>
       </c>
       <c r="BK3">
-        <v>334.7627369090611</v>
+        <v>122.7059208680197</v>
       </c>
       <c r="BL3">
-        <v>0.003347627369090611</v>
+        <v>0.001227059208680197</v>
       </c>
       <c r="BM3">
-        <v>499.9999999999999</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN3">
-        <v>0.004999999999999999</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO3">
-        <v>0.008055194325067029</v>
+        <v>298.9793015788462</v>
       </c>
       <c r="BP3">
-        <v>0.006129924800057054</v>
+        <v>29.49056249664705</v>
       </c>
       <c r="BQ3">
-        <v>0.007621729172504024</v>
+        <v>90.51925756513735</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW3" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1475,7 +1475,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1490,151 +1490,151 @@
         <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.02492614749915493</v>
+        <v>1.326215123079677</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T4">
-        <v>0.6373752912759435</v>
+        <v>-0.8738735230020797</v>
       </c>
       <c r="U4">
-        <v>0.6367709655424278</v>
+        <v>0.7925867707208032</v>
       </c>
       <c r="V4" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W4" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9998083378730133</v>
+        <v>0.9973747414794695</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>0.3315673733474611</v>
       </c>
       <c r="Z4">
-        <v>-87.12506249802411</v>
+        <v>136.2972034583038</v>
       </c>
       <c r="AA4">
-        <v>-17</v>
+        <v>-53</v>
       </c>
       <c r="AB4">
-        <v>0.05015607232391142</v>
+        <v>-0.7229334238653541</v>
       </c>
       <c r="AC4">
-        <v>-0.9987413921576689</v>
+        <v>0.6909176974563007</v>
       </c>
       <c r="AD4" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AF4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AH4">
-        <v>0.02507322965220426</v>
+        <v>-0.4800536978699176</v>
       </c>
       <c r="AI4">
-        <v>0.4781089601370971</v>
+        <v>0.7770164922437377</v>
       </c>
       <c r="AJ4">
-        <v>0.1122588171426417</v>
+        <v>-1.179377254172649</v>
       </c>
       <c r="AK4">
-        <v>-1.152165940047503</v>
+        <v>0.9629161850976939</v>
       </c>
       <c r="AL4">
-        <v>-0.2881312433733745</v>
+        <v>-0.9306409438947538</v>
       </c>
       <c r="AM4">
-        <v>-0.4037334404284169</v>
+        <v>4.69785617985081</v>
       </c>
       <c r="AN4">
-        <v>0.2766360853880414</v>
+        <v>0.8121045632290568</v>
       </c>
       <c r="AO4">
-        <v>0.2458051987708726</v>
+        <v>0.03505446068783412</v>
       </c>
       <c r="AP4">
-        <v>4349.870000000001</v>
+        <v>157.8075</v>
       </c>
       <c r="AQ4">
-        <v>4426.432037046988</v>
+        <v>158.6323664546501</v>
       </c>
       <c r="AR4">
-        <v>4949.543456823289</v>
+        <v>160.4987977089423</v>
       </c>
       <c r="AS4">
-        <v>4349.870000000001</v>
+        <v>157.8075</v>
       </c>
       <c r="AT4">
-        <v>4091.520000000002</v>
+        <v>156.6035</v>
       </c>
       <c r="AU4">
-        <v>4426.432037046988</v>
+        <v>158.6323664546501</v>
       </c>
       <c r="AV4">
-        <v>4216.232500000001</v>
+        <v>156.309375</v>
       </c>
       <c r="AW4">
-        <v>0.01760099429338967</v>
+        <v>0.005227042153574035</v>
       </c>
       <c r="AX4">
-        <v>0.5729083307229395</v>
+        <v>0.5505992187902383</v>
       </c>
       <c r="AY4">
-        <v>0.01760099429338967</v>
+        <v>0.005227042153574035</v>
       </c>
       <c r="AZ4">
-        <v>0.3</v>
+        <v>0.4590320402328539</v>
       </c>
       <c r="BA4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.4</v>
+        <v>0.3409679597671461</v>
       </c>
       <c r="BC4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1643,58 +1643,58 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.03072218250200584</v>
+        <v>0.009493370086973154</v>
       </c>
       <c r="BH4">
-        <v>16274.88541764099</v>
+        <v>52668.33541927354</v>
       </c>
       <c r="BI4">
-        <v>12206.16406323074</v>
+        <v>52668.33541927354</v>
       </c>
       <c r="BJ4">
-        <v>2.806098587597041</v>
+        <v>333.7505214851863</v>
       </c>
       <c r="BK4">
-        <v>122.0616406323074</v>
+        <v>526.6833541927354</v>
       </c>
       <c r="BL4">
-        <v>0.001220616406323074</v>
+        <v>0.005266833541927353</v>
       </c>
       <c r="BM4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BN4">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>287.9188629709716</v>
+        <v>5.261235000446435</v>
       </c>
       <c r="BP4">
-        <v>29.21205878589468</v>
+        <v>2.411632002337638</v>
       </c>
       <c r="BQ4">
-        <v>93.51594663334197</v>
+        <v>4.31033664890454</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW4" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1702,7 +1702,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1717,151 +1717,151 @@
         <v>89</v>
       </c>
       <c r="G5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" t="s">
         <v>92</v>
       </c>
-      <c r="H5" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" t="s">
-        <v>94</v>
-      </c>
       <c r="J5" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.8577256191889026</v>
+        <v>0.6920440496369997</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T5">
-        <v>0.6159994718469458</v>
+        <v>0.5846718301826457</v>
       </c>
       <c r="U5">
-        <v>0.677076930841619</v>
+        <v>0.6630150633925173</v>
       </c>
       <c r="V5" t="s">
+        <v>92</v>
+      </c>
+      <c r="W5" t="s">
         <v>94</v>
       </c>
-      <c r="W5" t="s">
-        <v>95</v>
-      </c>
       <c r="X5">
-        <v>0.9995086740419734</v>
+        <v>0.9996509592413069</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-69.10406610064956</v>
+        <v>-72.2883097669946</v>
       </c>
       <c r="AA5">
-        <v>-21.99999999999999</v>
+        <v>-16</v>
       </c>
       <c r="AB5">
-        <v>0.3566717008781201</v>
+        <v>0.3042274290293818</v>
       </c>
       <c r="AC5">
-        <v>-0.9342297885385098</v>
+        <v>-0.9525994286299843</v>
       </c>
       <c r="AD5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AG5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AH5">
-        <v>0.3564964588129852</v>
+        <v>0.3041212412567381</v>
       </c>
       <c r="AI5">
-        <v>0.7966078738714228</v>
+        <v>0.7795386901863116</v>
       </c>
       <c r="AJ5">
-        <v>0.9181959811564773</v>
+        <v>0.7833795217544304</v>
       </c>
       <c r="AK5">
-        <v>-2.142791983416557</v>
+        <v>-2.206654414137842</v>
       </c>
       <c r="AL5">
-        <v>0.4198628180733306</v>
+        <v>0.3515149772265023</v>
       </c>
       <c r="AM5">
-        <v>-3.418587270096519</v>
+        <v>-2.62818533186247</v>
       </c>
       <c r="AN5">
-        <v>0.5071495902468289</v>
+        <v>0.4103625275900591</v>
       </c>
       <c r="AO5">
-        <v>0.06814448204469208</v>
+        <v>0.07738249504640238</v>
       </c>
       <c r="AP5">
-        <v>0.7112700000000001</v>
+        <v>0.712165</v>
       </c>
       <c r="AQ5">
-        <v>0.7091669558493195</v>
+        <v>0.7104751389840841</v>
       </c>
       <c r="AR5">
-        <v>0.7103173493284834</v>
+        <v>0.7114041807059742</v>
       </c>
       <c r="AS5">
-        <v>0.7112700000000001</v>
+        <v>0.712165</v>
       </c>
       <c r="AT5">
-        <v>0.7066150000000002</v>
+        <v>0.7084050000000002</v>
       </c>
       <c r="AU5">
-        <v>0.7091669558493195</v>
+        <v>0.7104751389840841</v>
       </c>
       <c r="AV5">
-        <v>0.7184787500000001</v>
+        <v>0.7193737499999999</v>
       </c>
       <c r="AW5">
-        <v>-0.002956745189141285</v>
+        <v>-0.002372850415164955</v>
       </c>
       <c r="AX5">
-        <v>0.2917349263992429</v>
+        <v>0.2344180358475417</v>
       </c>
       <c r="AY5">
-        <v>0.002956745189141285</v>
+        <v>0.002372850415164955</v>
       </c>
       <c r="AZ5">
-        <v>0.4378181812420854</v>
+        <v>0.4394996878508224</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3621818187579146</v>
+        <v>0.3605003121491778</v>
       </c>
       <c r="BC5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1873,22 +1873,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.01013504013946874</v>
+        <v>0.01012230311795712</v>
       </c>
       <c r="BH5">
-        <v>49333.7957343511</v>
+        <v>49395.87307092123</v>
       </c>
       <c r="BI5">
-        <v>49333.7957343511</v>
+        <v>49395.87307092123</v>
       </c>
       <c r="BJ5">
-        <v>69360.15259233638</v>
+        <v>69360.15259233637</v>
       </c>
       <c r="BK5">
-        <v>493.337957343511</v>
+        <v>493.9587307092123</v>
       </c>
       <c r="BL5">
-        <v>0.00493337957343511</v>
+        <v>0.004939587307092123</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1897,31 +1897,31 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.01644435989176263</v>
+        <v>0.01576179974764567</v>
       </c>
       <c r="BP5">
-        <v>0.003673898616329937</v>
+        <v>0.003185466977036815</v>
       </c>
       <c r="BQ5">
-        <v>0.008291365289813231</v>
+        <v>0.007782323746711127</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW5" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1929,7 +1929,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1944,73 +1944,73 @@
         <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K6">
-        <v>0.6838933934311553</v>
+        <v>0.7348033142862079</v>
       </c>
       <c r="L6">
-        <v>3.312044073047681</v>
+        <v>3.387701679821335</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q6">
-        <v>0.9209733483577889</v>
+        <v>0.933700828571552</v>
       </c>
       <c r="R6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="T6">
-        <v>-0.9776490232765577</v>
+        <v>-0.9942167738971054</v>
       </c>
       <c r="U6">
-        <v>0.9425015538993265</v>
+        <v>0.9575949453430195</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
       </c>
       <c r="W6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X6">
-        <v>0.9999019376408095</v>
+        <v>0.9999075997855635</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>0.9405409251419504</v>
       </c>
       <c r="Z6">
-        <v>163.2541632768595</v>
+        <v>171.3857006022782</v>
       </c>
       <c r="AA6">
-        <v>-3.999999999999993</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AB6">
-        <v>-0.9575922994502618</v>
+        <v>-0.9887190304839409</v>
       </c>
       <c r="AC6">
-        <v>0.2881266874719525</v>
+        <v>0.149782104267819</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -2019,76 +2019,76 @@
         <v>112</v>
       </c>
       <c r="AF6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AH6">
-        <v>-0.9574983956902351</v>
+        <v>-0.9592362292365794</v>
       </c>
       <c r="AI6">
-        <v>0.982465254189971</v>
+        <v>0.9794401315396966</v>
       </c>
       <c r="AJ6">
-        <v>-2.532529145371306</v>
+        <v>-2.551143661676161</v>
       </c>
       <c r="AK6">
-        <v>0.7407625272065881</v>
+        <v>0.4162330582870611</v>
       </c>
       <c r="AL6">
-        <v>-4.057636880023013</v>
+        <v>-4.312108478118331</v>
       </c>
       <c r="AM6">
-        <v>4.020113645045003</v>
+        <v>3.358595373306814</v>
       </c>
       <c r="AN6">
-        <v>3.718235628769614</v>
+        <v>4.024164510598976</v>
       </c>
       <c r="AO6">
-        <v>0.03185409212927249</v>
+        <v>0.03500948372548682</v>
       </c>
       <c r="AP6">
-        <v>6.705825</v>
+        <v>6.69815</v>
       </c>
       <c r="AQ6">
-        <v>6.681239077143534</v>
+        <v>6.670773706514162</v>
       </c>
       <c r="AR6">
-        <v>6.665022738036885</v>
+        <v>6.653197876779366</v>
       </c>
       <c r="AS6">
-        <v>6.705825</v>
+        <v>6.69815</v>
       </c>
       <c r="AT6">
-        <v>6.690849999999998</v>
+        <v>6.675499999999999</v>
       </c>
       <c r="AU6">
-        <v>6.681239077143534</v>
+        <v>6.670773706514162</v>
       </c>
       <c r="AV6">
-        <v>6.72933125</v>
+        <v>6.72165625</v>
       </c>
       <c r="AW6">
-        <v>-0.003666353186441041</v>
+        <v>-0.004087142492455036</v>
       </c>
       <c r="AX6">
-        <v>1.045931310033136</v>
+        <v>1.164638914579661</v>
       </c>
       <c r="AY6">
-        <v>0.003666353186441041</v>
+        <v>0.004087142492455036</v>
       </c>
       <c r="AZ6">
-        <v>0.4880859176814781</v>
+        <v>0.4150409086285581</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3119140823185219</v>
+        <v>0.384959091371442</v>
       </c>
       <c r="BC6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2097,58 +2097,58 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>460.4866741788944</v>
+        <v>466.850414285776</v>
       </c>
       <c r="BG6">
-        <v>0.003505347962405762</v>
+        <v>0.003509364526025786</v>
       </c>
       <c r="BH6">
-        <v>142639.1917043363</v>
+        <v>142475.9372507335</v>
       </c>
       <c r="BI6">
-        <v>131366.8939909911</v>
+        <v>133029.9006625183</v>
       </c>
       <c r="BJ6">
-        <v>19589.96752688762</v>
+        <v>19860.69297679483</v>
       </c>
       <c r="BK6">
-        <v>1313.668939909911</v>
+        <v>1330.299006625183</v>
       </c>
       <c r="BL6">
-        <v>0.01313668939909911</v>
+        <v>0.01330299006625183</v>
       </c>
       <c r="BM6">
-        <v>460.4866741788945</v>
+        <v>466.850414285776</v>
       </c>
       <c r="BN6">
-        <v>0.004604866741788944</v>
+        <v>0.00466850414285776</v>
       </c>
       <c r="BO6">
-        <v>0.02928839371334552</v>
+        <v>0.03181803714854159</v>
       </c>
       <c r="BP6">
-        <v>0.001133733140364289</v>
+        <v>0.005634126674882603</v>
       </c>
       <c r="BQ6">
-        <v>0.01374960726467883</v>
+        <v>0.01081231929545353</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW6" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2156,7 +2156,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2168,154 +2168,154 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.3223109922322406</v>
+        <v>0.924936610197405</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T7">
-        <v>-0.4848709250354737</v>
+        <v>-0.5561168204200569</v>
       </c>
       <c r="U7">
-        <v>0.6181497420822262</v>
+        <v>0.6502308918462194</v>
       </c>
       <c r="V7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W7" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9998313032650523</v>
+        <v>0.999913290628775</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-97.88007791281441</v>
+        <v>-104.8606887688172</v>
       </c>
       <c r="AA7">
-        <v>-11</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB7">
-        <v>-0.1371001316370621</v>
+        <v>-0.2564696919894996</v>
       </c>
       <c r="AC7">
-        <v>-0.9905571936567319</v>
+        <v>-0.9665522733359077</v>
       </c>
       <c r="AD7" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AF7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH7">
-        <v>-0.137077003292494</v>
+        <v>-0.256447453663769</v>
       </c>
       <c r="AI7">
-        <v>0.7112252278539652</v>
+        <v>0.7577298228538096</v>
       </c>
       <c r="AJ7">
-        <v>-0.2247172167165957</v>
+        <v>-0.6151802809032</v>
       </c>
       <c r="AK7">
-        <v>-1.855469446779309</v>
+        <v>-2.441849635587668</v>
       </c>
       <c r="AL7">
-        <v>-1.054361149087296</v>
+        <v>-1.80377892824894</v>
       </c>
       <c r="AM7">
-        <v>-1.453125711083343</v>
+        <v>-1.023166154625297</v>
       </c>
       <c r="AN7">
-        <v>1.134914451439164</v>
+        <v>1.822018625129852</v>
       </c>
       <c r="AO7">
-        <v>0.1989717851994777</v>
+        <v>0.1278715764207432</v>
       </c>
       <c r="AP7">
-        <v>1.337245</v>
+        <v>1.334515</v>
       </c>
       <c r="AQ7">
-        <v>1.332331332521422</v>
+        <v>1.328517802332784</v>
       </c>
       <c r="AR7">
-        <v>1.345615160085486</v>
+        <v>1.342263208340746</v>
       </c>
       <c r="AS7">
-        <v>1.337245</v>
+        <v>1.334515</v>
       </c>
       <c r="AT7">
-        <v>1.311795</v>
+        <v>1.306335</v>
       </c>
       <c r="AU7">
-        <v>1.332331332521422</v>
+        <v>1.328517802332784</v>
       </c>
       <c r="AV7">
-        <v>1.348895</v>
+        <v>1.346165</v>
       </c>
       <c r="AW7">
-        <v>-0.003674470630720722</v>
+        <v>-0.0044939155177845</v>
       </c>
       <c r="AX7">
-        <v>0.4217740324959772</v>
+        <v>0.5147809156408741</v>
       </c>
       <c r="AY7">
-        <v>0.003674470630720722</v>
+        <v>0.0044939155177845</v>
       </c>
       <c r="AZ7">
-        <v>0.4567196749624623</v>
+        <v>0.4605518364804801</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3432803250375378</v>
+        <v>0.3394481635195199</v>
       </c>
       <c r="BC7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2327,55 +2327,55 @@
         <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.008711941342087645</v>
+        <v>0.008729763247322057</v>
       </c>
       <c r="BH7">
-        <v>57392.4892703863</v>
+        <v>57275.32188841204</v>
       </c>
       <c r="BI7">
-        <v>43044.36695278973</v>
+        <v>42956.49141630903</v>
       </c>
       <c r="BJ7">
-        <v>32188.84120171676</v>
+        <v>32188.84120171675</v>
       </c>
       <c r="BK7">
-        <v>430.4436695278973</v>
+        <v>429.5649141630903</v>
       </c>
       <c r="BL7">
-        <v>0.004304436695278973</v>
+        <v>0.004295649141630903</v>
       </c>
       <c r="BM7">
-        <v>375.0000000000001</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN7">
-        <v>0.003750000000000001</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO7">
-        <v>0.01178681730397356</v>
+        <v>0.0130841668709418</v>
       </c>
       <c r="BP7">
-        <v>0.008941883202846395</v>
+        <v>0.01054613888732201</v>
       </c>
       <c r="BQ7">
-        <v>0.01030111114841202</v>
+        <v>0.01202828386400293</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW7" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2383,7 +2383,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2395,154 +2395,154 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" t="s">
         <v>92</v>
       </c>
-      <c r="H8" t="s">
-        <v>92</v>
-      </c>
-      <c r="I8" t="s">
-        <v>94</v>
-      </c>
       <c r="J8" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.06524719674745511</v>
+        <v>0.01655556595978891</v>
       </c>
       <c r="M8">
         <v>4</v>
       </c>
       <c r="N8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T8">
-        <v>0.4344034749202256</v>
+        <v>0.3807338069966937</v>
       </c>
       <c r="U8">
-        <v>0.545387314894983</v>
+        <v>0.5212641397611941</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X8">
-        <v>0.9996230047235263</v>
+        <v>0.9997357064507278</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-83.46685860511681</v>
+        <v>-88.29671643254534</v>
       </c>
       <c r="AA8">
-        <v>-21.99999999999999</v>
+        <v>-20</v>
       </c>
       <c r="AB8">
-        <v>0.1137779030489081</v>
+        <v>0.02972352787565342</v>
       </c>
       <c r="AC8">
-        <v>-0.99350620973288</v>
+        <v>-0.9995581583332834</v>
       </c>
       <c r="AD8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE8" t="s">
         <v>111</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AF8" t="s">
         <v>114</v>
       </c>
-      <c r="AF8" t="s">
-        <v>117</v>
-      </c>
       <c r="AG8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="AH8">
-        <v>0.1137350093168916</v>
+        <v>0.02971567213897427</v>
       </c>
       <c r="AI8">
-        <v>0.7051261272952865</v>
+        <v>0.6640602090769308</v>
       </c>
       <c r="AJ8">
-        <v>0.1910823272299699</v>
+        <v>0.08430824290988428</v>
       </c>
       <c r="AK8">
-        <v>-1.28837034492356</v>
+        <v>-1.27747310797807</v>
       </c>
       <c r="AL8">
-        <v>-0.3878254263067406</v>
+        <v>-0.480242505338311</v>
       </c>
       <c r="AM8">
-        <v>-1.709134775113346</v>
+        <v>-1.185912524583119</v>
       </c>
       <c r="AN8">
-        <v>0.5484235748821181</v>
+        <v>0.5444737846546214</v>
       </c>
       <c r="AO8">
-        <v>0.1925019684841343</v>
+        <v>0.2984289769568</v>
       </c>
       <c r="AP8">
-        <v>4.75648</v>
+        <v>4.76573</v>
       </c>
       <c r="AQ8">
-        <v>4.727469534237068</v>
+        <v>4.741796488360759</v>
       </c>
       <c r="AR8">
-        <v>4.740797338810489</v>
+        <v>4.753933844001596</v>
       </c>
       <c r="AS8">
-        <v>4.75648</v>
+        <v>4.76573</v>
       </c>
       <c r="AT8">
-        <v>4.695889999999999</v>
+        <v>4.714389999999999</v>
       </c>
       <c r="AU8">
-        <v>4.727469534237068</v>
+        <v>4.741796488360759</v>
       </c>
       <c r="AV8">
-        <v>4.805215</v>
+        <v>4.8075275</v>
       </c>
       <c r="AW8">
-        <v>-0.006099145957290214</v>
+        <v>-0.005022003269014555</v>
       </c>
       <c r="AX8">
-        <v>0.5952696370766754</v>
+        <v>0.5726062955736742</v>
       </c>
       <c r="AY8">
-        <v>0.006099145957290214</v>
+        <v>0.005022003269014555</v>
       </c>
       <c r="AZ8">
-        <v>0.4333709089108385</v>
+        <v>0.4334047130083725</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3666290910891615</v>
+        <v>0.3665952869916275</v>
       </c>
       <c r="BC8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2554,22 +2554,22 @@
         <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.01024602226856835</v>
+        <v>0.008770429713810928</v>
       </c>
       <c r="BH8">
-        <v>48799.42546424543</v>
+        <v>57009.74938692484</v>
       </c>
       <c r="BI8">
-        <v>48799.42546424543</v>
+        <v>57009.74938692484</v>
       </c>
       <c r="BJ8">
-        <v>10259.56704627065</v>
+        <v>11962.43794485312</v>
       </c>
       <c r="BK8">
-        <v>487.9942546424543</v>
+        <v>570.0974938692484</v>
       </c>
       <c r="BL8">
-        <v>0.004879942546424543</v>
+        <v>0.005700974938692484</v>
       </c>
       <c r="BM8">
         <v>500</v>
@@ -2578,31 +2578,31 @@
         <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.1014184106043558</v>
+        <v>0.09425802443622699</v>
       </c>
       <c r="BP8">
-        <v>0.03383798261114321</v>
+        <v>0.02857531660759011</v>
       </c>
       <c r="BQ8">
-        <v>0.05618473652729796</v>
+        <v>0.05056710655796827</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW8" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2610,7 +2610,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2622,76 +2622,76 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K9">
-        <v>0.01880191757619046</v>
+        <v>0.5795383327517757</v>
       </c>
       <c r="L9">
-        <v>0.6964939566289734</v>
+        <v>0.9852090534858458</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q9">
-        <v>0.7547004793940476</v>
+        <v>0.8948845831879439</v>
       </c>
       <c r="R9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T9">
-        <v>-0.7794743312517826</v>
+        <v>-0.750971043846107</v>
       </c>
       <c r="U9">
-        <v>0.7535444680721862</v>
+        <v>0.8248566478294365</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
       </c>
       <c r="W9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X9">
-        <v>0.9998429254898222</v>
+        <v>0.9999557127436877</v>
       </c>
       <c r="Y9">
-        <v>0.4370428318113841</v>
+        <v>1</v>
       </c>
       <c r="Z9">
-        <v>-122.8576661840473</v>
+        <v>-122.4092014101674</v>
       </c>
       <c r="AA9">
-        <v>-5.999999999999996</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB9">
-        <v>-0.5425539364530436</v>
+        <v>-0.5359623828302383</v>
       </c>
       <c r="AC9">
-        <v>-0.8400209676188486</v>
+        <v>-0.8442418635621743</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
@@ -2700,76 +2700,76 @@
         <v>112</v>
       </c>
       <c r="AF9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AH9">
-        <v>-0.3897753892288995</v>
+        <v>-0.5359386465268161</v>
       </c>
       <c r="AI9">
-        <v>0.7390183193719653</v>
+        <v>0.8497017684473732</v>
       </c>
       <c r="AJ9">
-        <v>-0.4755050419453364</v>
+        <v>-0.678926070549545</v>
       </c>
       <c r="AK9">
-        <v>-0.7517380353983013</v>
+        <v>-1.080325044912384</v>
       </c>
       <c r="AL9">
-        <v>-1.093101510666785</v>
+        <v>-1.518876694813364</v>
       </c>
       <c r="AM9">
-        <v>-0.07158285209649816</v>
+        <v>0.01055656208299138</v>
       </c>
       <c r="AN9">
-        <v>1.078841554071325</v>
+        <v>1.486091757780796</v>
       </c>
       <c r="AO9">
-        <v>0.07400967898441663</v>
+        <v>0.07380963907992617</v>
       </c>
       <c r="AP9">
-        <v>8.981999999999999</v>
+        <v>8.95293</v>
       </c>
       <c r="AQ9">
-        <v>8.927056110058018</v>
+        <v>8.885451127902957</v>
       </c>
       <c r="AR9">
-        <v>9.026107434366153</v>
+        <v>8.990241951268386</v>
       </c>
       <c r="AS9">
-        <v>8.981999999999999</v>
+        <v>8.95293</v>
       </c>
       <c r="AT9">
-        <v>8.803579999999998</v>
+        <v>8.74544</v>
       </c>
       <c r="AU9">
-        <v>8.927056110058018</v>
+        <v>8.885451127902957</v>
       </c>
       <c r="AV9">
-        <v>9.063067499999999</v>
+        <v>9.0339975</v>
       </c>
       <c r="AW9">
-        <v>-0.0061171108819841</v>
+        <v>-0.007537071338326442</v>
       </c>
       <c r="AX9">
-        <v>0.6777548332189982</v>
+        <v>0.8323788459868985</v>
       </c>
       <c r="AY9">
-        <v>0.0061171108819841</v>
+        <v>0.007537071338326442</v>
       </c>
       <c r="AZ9">
-        <v>0.3945226363126192</v>
+        <v>0.4024197004661634</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.4054773636873809</v>
+        <v>0.3975802995338366</v>
       </c>
       <c r="BC9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2778,58 +2778,58 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>377.3502396970238</v>
+        <v>447.442291593972</v>
       </c>
       <c r="BG9">
-        <v>0.009025551102204417</v>
+        <v>0.00905485690159535</v>
       </c>
       <c r="BH9">
-        <v>55398.27921176793</v>
+        <v>55218.98417985009</v>
       </c>
       <c r="BI9">
-        <v>41809.10787872656</v>
+        <v>49414.61764184682</v>
       </c>
       <c r="BJ9">
-        <v>4654.765962895409</v>
+        <v>5519.379425712791</v>
       </c>
       <c r="BK9">
-        <v>418.0910787872656</v>
+        <v>494.1461764184681</v>
       </c>
       <c r="BL9">
-        <v>0.004180910787872655</v>
+        <v>0.004941461764184681</v>
       </c>
       <c r="BM9">
-        <v>377.3502396970238</v>
+        <v>447.442291593972</v>
       </c>
       <c r="BN9">
-        <v>0.003773502396970238</v>
+        <v>0.00447442291593972</v>
       </c>
       <c r="BO9">
-        <v>0.131666544532077</v>
+        <v>0.1561384069969589</v>
       </c>
       <c r="BP9">
-        <v>0.05015578782799125</v>
+        <v>0.0672426384105443</v>
       </c>
       <c r="BQ9">
-        <v>0.04862684645879806</v>
+        <v>0.06575906580641799</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV9" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW9" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2837,7 +2837,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2849,76 +2849,76 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.070761368424196</v>
+        <v>1.44161677324608</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q10">
         <v>0.75</v>
       </c>
       <c r="R10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="S10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T10">
-        <v>-0.714030007035483</v>
+        <v>-0.6609764876253195</v>
       </c>
       <c r="U10">
-        <v>0.7212776062636812</v>
+        <v>0.6974245382524717</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X10">
-        <v>0.9998564123908554</v>
+        <v>0.999940475284312</v>
       </c>
       <c r="Y10">
-        <v>0.4451120696948463</v>
+        <v>1</v>
       </c>
       <c r="Z10">
-        <v>-114.3341943260237</v>
+        <v>-115.6023027918092</v>
       </c>
       <c r="AA10">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="AB10">
-        <v>-0.4120582140207711</v>
+        <v>-0.4321219942737594</v>
       </c>
       <c r="AC10">
-        <v>-0.9111575211005023</v>
+        <v>-0.901815159589186</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
@@ -2927,76 +2927,76 @@
         <v>112</v>
       </c>
       <c r="AF10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AH10">
-        <v>-0.2976923981709202</v>
+        <v>-0.4320962723349077</v>
       </c>
       <c r="AI10">
-        <v>0.6982067874420025</v>
+        <v>0.8168070767963024</v>
       </c>
       <c r="AJ10">
-        <v>-0.663143586345423</v>
+        <v>-0.9432442515215841</v>
       </c>
       <c r="AK10">
-        <v>-1.535824737971604</v>
+        <v>-2.039730927594273</v>
       </c>
       <c r="AL10">
-        <v>-1.983768835891844</v>
+        <v>-2.45604809939681</v>
       </c>
       <c r="AM10">
-        <v>-0.943282125898916</v>
+        <v>-0.3859727635142868</v>
       </c>
       <c r="AN10">
-        <v>2.010883721962682</v>
+        <v>2.416353699652829</v>
       </c>
       <c r="AO10">
-        <v>0.09588556693331662</v>
+        <v>0.08539125223556419</v>
       </c>
       <c r="AP10">
-        <v>7.6952</v>
+        <v>7.6919</v>
       </c>
       <c r="AQ10">
-        <v>7.620994286062185</v>
+        <v>7.616003538069489</v>
       </c>
       <c r="AR10">
-        <v>7.661168106456968</v>
+        <v>7.656616654614982</v>
       </c>
       <c r="AS10">
-        <v>7.6952</v>
+        <v>7.6919</v>
       </c>
       <c r="AT10">
-        <v>7.542999999999999</v>
+        <v>7.5364</v>
       </c>
       <c r="AU10">
-        <v>7.620994286062185</v>
+        <v>7.616003538069489</v>
       </c>
       <c r="AV10">
-        <v>7.744875</v>
+        <v>7.742497641287009</v>
       </c>
       <c r="AW10">
-        <v>-0.009643116999923942</v>
+        <v>-0.009867063005305815</v>
       </c>
       <c r="AX10">
-        <v>1.493824135637924</v>
+        <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.009643116999923942</v>
+        <v>0.009867063005305815</v>
       </c>
       <c r="AZ10">
-        <v>0.4024291112721</v>
+        <v>0.4034677077384222</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3975708887279</v>
+        <v>0.3965322922615778</v>
       </c>
       <c r="BC10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -3008,55 +3008,55 @@
         <v>375</v>
       </c>
       <c r="BG10">
-        <v>0.006455322798627792</v>
+        <v>0.00657804200353721</v>
       </c>
       <c r="BH10">
-        <v>77455.46049320493</v>
+        <v>76010.46021462543</v>
       </c>
       <c r="BI10">
-        <v>58091.59536990369</v>
+        <v>57007.84516096907</v>
       </c>
       <c r="BJ10">
-        <v>7549.068948162971</v>
+        <v>7411.412675797797</v>
       </c>
       <c r="BK10">
-        <v>580.9159536990369</v>
+        <v>570.0784516096908</v>
       </c>
       <c r="BL10">
-        <v>0.005809159536990369</v>
+        <v>0.005700784516096908</v>
       </c>
       <c r="BM10">
-        <v>374.9999999999999</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN10">
-        <v>0.003749999999999999</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO10">
-        <v>0.1342660224642186</v>
+        <v>0.1367617082927783</v>
       </c>
       <c r="BP10">
-        <v>0.05067553755355485</v>
+        <v>0.05261061385391377</v>
       </c>
       <c r="BQ10">
-        <v>0.05415077402845746</v>
+        <v>0.05618363261382904</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW10" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3064,7 +3064,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3076,40 +3076,40 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.2823585839149488</v>
+        <v>0.7772118913444507</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O11" t="s">
+        <v>94</v>
+      </c>
+      <c r="P11" t="s">
         <v>96</v>
       </c>
-      <c r="P11" t="s">
-        <v>99</v>
-      </c>
       <c r="Q11">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R11" t="s">
         <v>102</v>
@@ -3118,112 +3118,112 @@
         <v>107</v>
       </c>
       <c r="T11">
-        <v>0.2673946141720625</v>
+        <v>-0.5121842826309468</v>
       </c>
       <c r="U11">
-        <v>0.420269735781742</v>
+        <v>0.6304485710096058</v>
       </c>
       <c r="V11" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W11" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="X11">
-        <v>0.9997686376172555</v>
+        <v>0.999862575302719</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-93.92557157819374</v>
+        <v>-100.5365903501272</v>
       </c>
       <c r="AA11">
-        <v>-17</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AB11">
-        <v>-0.06846055858543516</v>
+        <v>-0.1828634165865115</v>
       </c>
       <c r="AC11">
-        <v>-0.9976538236874403</v>
+        <v>-0.9831383274363318</v>
       </c>
       <c r="AD11" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AF11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH11">
-        <v>-0.06844471938747682</v>
+        <v>-0.1828382866368433</v>
       </c>
       <c r="AI11">
-        <v>0.6812703624360725</v>
+        <v>0.7300549854365139</v>
       </c>
       <c r="AJ11">
-        <v>-0.09177323229322928</v>
+        <v>-0.4403540916387163</v>
       </c>
       <c r="AK11">
-        <v>-2.185662763802843</v>
+        <v>-2.713880578029307</v>
       </c>
       <c r="AL11">
-        <v>-1.226663472154302</v>
+        <v>-1.842430185426691</v>
       </c>
       <c r="AM11">
-        <v>-2.187890960935691</v>
+        <v>-1.588397178922474</v>
       </c>
       <c r="AN11">
-        <v>1.346423448110695</v>
+        <v>1.886683180913546</v>
       </c>
       <c r="AO11">
-        <v>0.2612455220373168</v>
+        <v>0.1650396059692746</v>
       </c>
       <c r="AP11">
-        <v>1.14728</v>
+        <v>1.146005</v>
       </c>
       <c r="AQ11">
-        <v>1.119843012655404</v>
+        <v>1.117494777145027</v>
       </c>
       <c r="AR11">
-        <v>1.100156089037617</v>
+        <v>1.097565759249131</v>
       </c>
       <c r="AS11">
-        <v>1.14728</v>
+        <v>1.146005</v>
       </c>
       <c r="AT11">
-        <v>1.127065</v>
+        <v>1.124515</v>
       </c>
       <c r="AU11">
-        <v>1.119843012655404</v>
+        <v>1.117494777145027</v>
       </c>
       <c r="AV11">
-        <v>1.165571324896397</v>
+        <v>1.165011815236649</v>
       </c>
       <c r="AW11">
-        <v>-0.02391481359789753</v>
+        <v>-0.02487792187204522</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.02391481359789753</v>
+        <v>0.02487792187204522</v>
       </c>
       <c r="AZ11">
-        <v>0.4186340859480997</v>
+        <v>0.419982995424765</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3813659140519003</v>
+        <v>0.380017004575235</v>
       </c>
       <c r="BC11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3232,58 +3232,58 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.01594320906526502</v>
+        <v>0.01658528124803014</v>
       </c>
       <c r="BH11">
-        <v>31361.31489922783</v>
+        <v>30147.21261114494</v>
       </c>
       <c r="BI11">
-        <v>31361.31489922783</v>
+        <v>22610.40945835871</v>
       </c>
       <c r="BJ11">
-        <v>27335.36268324021</v>
+        <v>19729.7651043047</v>
       </c>
       <c r="BK11">
-        <v>313.6131489922784</v>
+        <v>226.1040945835871</v>
       </c>
       <c r="BL11">
-        <v>0.003136131489922784</v>
+        <v>0.002261040945835871</v>
       </c>
       <c r="BM11">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BN11">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>0.02186621370010488</v>
+        <v>0.02290103539180109</v>
       </c>
       <c r="BP11">
-        <v>0.007607723167977256</v>
+        <v>0.008355882246582373</v>
       </c>
       <c r="BQ11">
-        <v>0.01033844380630339</v>
+        <v>0.01117504901080117</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04494889380443722</v>
+        <v>0.05086952202688542</v>
       </c>
       <c r="BT11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="BU11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="BW11" s="2">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="141">
   <si>
     <t>Pair</t>
   </si>
@@ -262,12 +262,12 @@
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
@@ -277,15 +277,18 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
+    <t>FLAT</t>
+  </si>
+  <si>
     <t>LONG</t>
   </si>
   <si>
@@ -304,6 +307,9 @@
     <t>CONFLICT</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
@@ -391,37 +397,43 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.008401,naive=0.006561,drift4=0.008057; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=299,naive=29.49,drift4=90.52; naive_cap_applied; model_divergence_guard(abs=725.7,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=5.261,naive=2.412,drift4=4.31; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01576,naive=0.003185,drift4=0.007782; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03182,naive=0.005634,drift4=0.01081; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01308,naive=0.01055,drift4=0.01203; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.09426,naive=0.02858,drift4=0.05057; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1561,naive=0.06724,drift4=0.06576; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1368,naive=0.05261,drift4=0.05618; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.0229,naive=0.008356,drift4=0.01118; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.008493,naive=0.00625,drift4=0.007761; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=295,naive=26.72,drift4=83.64; naive_cap_applied; model_divergence_guard(abs=664.1,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=5.047,naive=2.403,drift4=4.339; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01504,naive=0.003004,drift4=0.007262; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02978,naive=0.005571,drift4=0.01033; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.0134,naive=0.01042,drift4=0.01198; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.09642,naive=0.02816,drift4=0.0486; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1366,naive=0.05358,drift4=0.05797; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1484,naive=0.0588,drift4=0.0583; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.0235,naive=0.008205,drift4=0.011; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -1021,7 +1033,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1042,7 +1054,7 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2">
         <v>46282</v>
@@ -1060,19 +1072,19 @@
         <v>11</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T2">
         <v>0.8080428531121724</v>
@@ -1081,10 +1093,10 @@
         <v>0.913616507569292</v>
       </c>
       <c r="V2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X2">
         <v>0.9999888946752581</v>
@@ -1105,16 +1117,16 @@
         <v>0.7876807914934287</v>
       </c>
       <c r="AD2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AF2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AG2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AH2">
         <v>0.6160767326460553</v>
@@ -1144,10 +1156,10 @@
         <v>0.8256600000000001</v>
       </c>
       <c r="AQ2">
-        <v>0.8448130489169474</v>
+        <v>0.8259160265513088</v>
       </c>
       <c r="AR2">
-        <v>0.8495986504576727</v>
+        <v>0.8086212372676598</v>
       </c>
       <c r="AS2">
         <v>0.8256600000000001</v>
@@ -1155,32 +1167,23 @@
       <c r="AT2">
         <v>0.8496050000000002</v>
       </c>
-      <c r="AU2">
-        <v>0.8448130489169474</v>
-      </c>
-      <c r="AV2">
-        <v>0.8128913007220352</v>
-      </c>
       <c r="AW2">
-        <v>0.02319725906177767</v>
-      </c>
-      <c r="AX2">
-        <v>1.5</v>
+        <v>0.0003100871439923712</v>
       </c>
       <c r="AY2">
-        <v>0.02319725906177767</v>
+        <v>0.0003100871439923712</v>
       </c>
       <c r="AZ2">
-        <v>0.4647709867175697</v>
+        <v>0.4611575948290714</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3352290132824303</v>
+        <v>0.3388424051709287</v>
       </c>
       <c r="BC2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1189,58 +1192,55 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>500</v>
-      </c>
-      <c r="BG2">
-        <v>0.01546483937451845</v>
+        <v>0</v>
       </c>
       <c r="BH2">
-        <v>32331.40596493064</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>32331.40596493064</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>39158.25638268856</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>323.3140596493064</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>0.003233140596493064</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.00840071228868911</v>
+        <v>0.00849251380034065</v>
       </c>
       <c r="BP2">
-        <v>0.006561205526185899</v>
+        <v>0.00624971563382879</v>
       </c>
       <c r="BQ2">
-        <v>0.008057314406635653</v>
+        <v>0.007760596961408234</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="BW2" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1260,16 +1260,16 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
         <v>46282</v>
@@ -1287,19 +1287,19 @@
         <v>27</v>
       </c>
       <c r="O3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q3">
         <v>0.75</v>
       </c>
       <c r="R3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T3">
         <v>0.7023511159933751</v>
@@ -1308,10 +1308,10 @@
         <v>0.7158272077718091</v>
       </c>
       <c r="V3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="X3">
         <v>0.9990768222991612</v>
@@ -1332,16 +1332,16 @@
         <v>-0.9918020786305632</v>
       </c>
       <c r="AD3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AE3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AH3">
         <v>0.06383279383179137</v>
@@ -1371,10 +1371,10 @@
         <v>4372.83</v>
       </c>
       <c r="AQ3">
-        <v>4461.07432301373</v>
+        <v>4442.595498755885</v>
       </c>
       <c r="AR3">
-        <v>4980.831076712437</v>
+        <v>4919.234995852948</v>
       </c>
       <c r="AS3">
         <v>4372.83</v>
@@ -1383,19 +1383,19 @@
         <v>4137.440000000001</v>
       </c>
       <c r="AU3">
-        <v>4461.07432301373</v>
+        <v>4442.595498755885</v>
       </c>
       <c r="AV3">
         <v>4239.1925</v>
       </c>
       <c r="AW3">
-        <v>0.02018014032416777</v>
+        <v>0.01595431305490617</v>
       </c>
       <c r="AX3">
-        <v>0.6603260537927635</v>
+        <v>0.5220503133917146</v>
       </c>
       <c r="AY3">
-        <v>0.02018014032416777</v>
+        <v>0.01595431305490617</v>
       </c>
       <c r="AZ3">
         <v>0.3</v>
@@ -1407,7 +1407,7 @@
         <v>0.4</v>
       </c>
       <c r="BC3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1443,31 +1443,31 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="BO3">
-        <v>298.9793015788462</v>
+        <v>295.0167031240425</v>
       </c>
       <c r="BP3">
-        <v>29.49056249664705</v>
+        <v>26.7186593225043</v>
       </c>
       <c r="BQ3">
-        <v>90.51925756513735</v>
+        <v>83.64233219288127</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW3" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1475,7 +1475,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1487,16 +1487,16 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J4" s="2">
         <v>46282</v>
@@ -1514,19 +1514,19 @@
         <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="T4">
         <v>-0.8738735230020797</v>
@@ -1535,10 +1535,10 @@
         <v>0.7925867707208032</v>
       </c>
       <c r="V4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X4">
         <v>0.9973747414794695</v>
@@ -1559,16 +1559,16 @@
         <v>0.6909176974563007</v>
       </c>
       <c r="AD4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AH4">
         <v>-0.4800536978699176</v>
@@ -1598,10 +1598,10 @@
         <v>157.8075</v>
       </c>
       <c r="AQ4">
-        <v>158.6323664546501</v>
+        <v>158.8413317956887</v>
       </c>
       <c r="AR4">
-        <v>160.4987977089423</v>
+        <v>160.9223365232886</v>
       </c>
       <c r="AS4">
         <v>157.8075</v>
@@ -1610,31 +1610,31 @@
         <v>156.6035</v>
       </c>
       <c r="AU4">
-        <v>158.6323664546501</v>
+        <v>158.8413317956887</v>
       </c>
       <c r="AV4">
         <v>156.309375</v>
       </c>
       <c r="AW4">
-        <v>0.005227042153574035</v>
+        <v>0.006551220922254364</v>
       </c>
       <c r="AX4">
-        <v>0.5505992187902383</v>
+        <v>0.6900838018781107</v>
       </c>
       <c r="AY4">
-        <v>0.005227042153574035</v>
+        <v>0.006551220922254364</v>
       </c>
       <c r="AZ4">
-        <v>0.4590320402328539</v>
+        <v>0.4624004138429429</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3409679597671461</v>
+        <v>0.3375995861570571</v>
       </c>
       <c r="BC4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1670,31 +1670,31 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>5.261235000446435</v>
+        <v>5.046718404865242</v>
       </c>
       <c r="BP4">
-        <v>2.411632002337638</v>
+        <v>2.40344946873723</v>
       </c>
       <c r="BQ4">
-        <v>4.31033664890454</v>
+        <v>4.339337297104737</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW4" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1702,7 +1702,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1717,13 +1717,13 @@
         <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2">
         <v>46282</v>
@@ -1741,19 +1741,19 @@
         <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T5">
         <v>0.5846718301826457</v>
@@ -1762,10 +1762,10 @@
         <v>0.6630150633925173</v>
       </c>
       <c r="V5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X5">
         <v>0.9996509592413069</v>
@@ -1786,16 +1786,16 @@
         <v>-0.9525994286299843</v>
       </c>
       <c r="AD5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AF5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AH5">
         <v>0.3041212412567381</v>
@@ -1825,10 +1825,10 @@
         <v>0.712165</v>
       </c>
       <c r="AQ5">
-        <v>0.7104751389840841</v>
+        <v>0.7109713897329846</v>
       </c>
       <c r="AR5">
-        <v>0.7114041807059742</v>
+        <v>0.7125456472398568</v>
       </c>
       <c r="AS5">
         <v>0.712165</v>
@@ -1837,31 +1837,31 @@
         <v>0.7084050000000002</v>
       </c>
       <c r="AU5">
-        <v>0.7104751389840841</v>
+        <v>0.7109713897329846</v>
       </c>
       <c r="AV5">
         <v>0.7193737499999999</v>
       </c>
       <c r="AW5">
-        <v>-0.002372850415164955</v>
+        <v>-0.001676030508401111</v>
       </c>
       <c r="AX5">
-        <v>0.2344180358475417</v>
+        <v>0.1655779805119457</v>
       </c>
       <c r="AY5">
-        <v>0.002372850415164955</v>
+        <v>0.001676030508401111</v>
       </c>
       <c r="AZ5">
-        <v>0.4394996878508224</v>
+        <v>0.4381898838229265</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3605003121491778</v>
+        <v>0.3618101161770735</v>
       </c>
       <c r="BC5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1897,31 +1897,31 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.01576179974764567</v>
+        <v>0.01503514053222917</v>
       </c>
       <c r="BP5">
-        <v>0.003185466977036815</v>
+        <v>0.003004205577708955</v>
       </c>
       <c r="BQ5">
-        <v>0.007782323746711127</v>
+        <v>0.007262303960698764</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW5" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1929,7 +1929,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1944,13 +1944,13 @@
         <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2">
         <v>46282</v>
@@ -1968,19 +1968,19 @@
         <v>46</v>
       </c>
       <c r="O6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>0.933700828571552</v>
       </c>
       <c r="R6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="T6">
         <v>-0.9942167738971054</v>
@@ -1989,10 +1989,10 @@
         <v>0.9575949453430195</v>
       </c>
       <c r="V6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X6">
         <v>0.9999075997855635</v>
@@ -2013,16 +2013,16 @@
         <v>0.149782104267819</v>
       </c>
       <c r="AD6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AH6">
         <v>-0.9592362292365794</v>
@@ -2052,10 +2052,10 @@
         <v>6.69815</v>
       </c>
       <c r="AQ6">
-        <v>6.670773706514162</v>
+        <v>6.680408283089646</v>
       </c>
       <c r="AR6">
-        <v>6.653197876779366</v>
+        <v>6.676412763335501</v>
       </c>
       <c r="AS6">
         <v>6.69815</v>
@@ -2064,31 +2064,31 @@
         <v>6.675499999999999</v>
       </c>
       <c r="AU6">
-        <v>6.670773706514162</v>
+        <v>6.680408283089646</v>
       </c>
       <c r="AV6">
         <v>6.72165625</v>
       </c>
       <c r="AW6">
-        <v>-0.004087142492455036</v>
+        <v>-0.002648748820249502</v>
       </c>
       <c r="AX6">
-        <v>1.164638914579661</v>
+        <v>0.7547659414136448</v>
       </c>
       <c r="AY6">
-        <v>0.004087142492455036</v>
+        <v>0.002648748820249502</v>
       </c>
       <c r="AZ6">
-        <v>0.4150409086285581</v>
+        <v>0.4144372094423198</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.384959091371442</v>
+        <v>0.3855627905576802</v>
       </c>
       <c r="BC6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2124,31 +2124,31 @@
         <v>0.00466850414285776</v>
       </c>
       <c r="BO6">
-        <v>0.03181803714854159</v>
+        <v>0.02978151977148156</v>
       </c>
       <c r="BP6">
-        <v>0.005634126674882603</v>
+        <v>0.005570663578087322</v>
       </c>
       <c r="BQ6">
-        <v>0.01081231929545353</v>
+        <v>0.01032568948596116</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW6" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2156,7 +2156,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2168,16 +2168,16 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J7" s="2">
         <v>46282</v>
@@ -2195,19 +2195,19 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T7">
         <v>-0.5561168204200569</v>
@@ -2216,10 +2216,10 @@
         <v>0.6502308918462194</v>
       </c>
       <c r="V7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X7">
         <v>0.999913290628775</v>
@@ -2240,16 +2240,16 @@
         <v>-0.9665522733359077</v>
       </c>
       <c r="AD7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AH7">
         <v>-0.256447453663769</v>
@@ -2279,10 +2279,10 @@
         <v>1.334515</v>
       </c>
       <c r="AQ7">
-        <v>1.328517802332784</v>
+        <v>1.328534843175083</v>
       </c>
       <c r="AR7">
-        <v>1.342263208340746</v>
+        <v>1.342465527843608</v>
       </c>
       <c r="AS7">
         <v>1.334515</v>
@@ -2291,31 +2291,31 @@
         <v>1.306335</v>
       </c>
       <c r="AU7">
-        <v>1.328517802332784</v>
+        <v>1.328534843175083</v>
       </c>
       <c r="AV7">
         <v>1.346165</v>
       </c>
       <c r="AW7">
-        <v>-0.0044939155177845</v>
+        <v>-0.004481146202865406</v>
       </c>
       <c r="AX7">
-        <v>0.5147809156408741</v>
+        <v>0.513318182396303</v>
       </c>
       <c r="AY7">
-        <v>0.0044939155177845</v>
+        <v>0.004481146202865406</v>
       </c>
       <c r="AZ7">
-        <v>0.4605518364804801</v>
+        <v>0.4584445388337488</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3394481635195199</v>
+        <v>0.3415554611662512</v>
       </c>
       <c r="BC7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2351,31 +2351,31 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="BO7">
-        <v>0.0130841668709418</v>
+        <v>0.01339814033893879</v>
       </c>
       <c r="BP7">
-        <v>0.01054613888732201</v>
+        <v>0.01042364378005856</v>
       </c>
       <c r="BQ7">
-        <v>0.01202828386400293</v>
+        <v>0.01197670571143663</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW7" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2383,7 +2383,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2398,151 +2398,151 @@
         <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.01655556595978891</v>
+        <v>0.08554759762750143</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T8">
-        <v>0.3807338069966937</v>
+        <v>0.3142695571397605</v>
       </c>
       <c r="U8">
-        <v>0.5212641397611941</v>
+        <v>0.4663733985142371</v>
       </c>
       <c r="V8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="W8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="X8">
-        <v>0.9997357064507278</v>
+        <v>0.9998083912053797</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-88.29671643254534</v>
+        <v>-92.13388134388816</v>
       </c>
       <c r="AA8">
-        <v>-20</v>
+        <v>-17</v>
       </c>
       <c r="AB8">
-        <v>0.02972352787565342</v>
+        <v>-0.03723464612280344</v>
       </c>
       <c r="AC8">
-        <v>-0.9995581583332834</v>
+        <v>-0.9993065501276921</v>
       </c>
       <c r="AD8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AE8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AH8">
-        <v>0.02971567213897427</v>
+        <v>-0.03722751163714174</v>
       </c>
       <c r="AI8">
-        <v>0.6640602090769308</v>
+        <v>0.6615956465052489</v>
       </c>
       <c r="AJ8">
-        <v>0.08430824290988428</v>
+        <v>-0.00491775251390192</v>
       </c>
       <c r="AK8">
-        <v>-1.27747310797807</v>
+        <v>-1.272933951822895</v>
       </c>
       <c r="AL8">
-        <v>-0.480242505338311</v>
+        <v>-0.51507400972078</v>
       </c>
       <c r="AM8">
-        <v>-1.185912524583119</v>
+        <v>-0.6963759476103385</v>
       </c>
       <c r="AN8">
-        <v>0.5444737846546214</v>
+        <v>0.522262883478808</v>
       </c>
       <c r="AO8">
-        <v>0.2984289769568</v>
+        <v>0.3300512283564994</v>
       </c>
       <c r="AP8">
-        <v>4.76573</v>
+        <v>4.7644</v>
       </c>
       <c r="AQ8">
-        <v>4.741796488360759</v>
+        <v>4.734844457863074</v>
       </c>
       <c r="AR8">
-        <v>4.753933844001596</v>
+        <v>4.741032800027971</v>
       </c>
       <c r="AS8">
-        <v>4.76573</v>
+        <v>4.7644</v>
       </c>
       <c r="AT8">
-        <v>4.714389999999999</v>
+        <v>4.71173</v>
       </c>
       <c r="AU8">
-        <v>4.741796488360759</v>
+        <v>4.734844457863074</v>
       </c>
       <c r="AV8">
-        <v>4.8075275</v>
+        <v>4.807195</v>
       </c>
       <c r="AW8">
-        <v>-0.005022003269014555</v>
+        <v>-0.006203413260206068</v>
       </c>
       <c r="AX8">
-        <v>0.5726062955736742</v>
+        <v>0.6906307310883516</v>
       </c>
       <c r="AY8">
-        <v>0.005022003269014555</v>
+        <v>0.006203413260206068</v>
       </c>
       <c r="AZ8">
-        <v>0.4334047130083725</v>
+        <v>0.4293261343989481</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3665952869916275</v>
+        <v>0.3706738656010519</v>
       </c>
       <c r="BC8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2554,22 +2554,22 @@
         <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.008770429713810928</v>
+        <v>0.008982243304508373</v>
       </c>
       <c r="BH8">
-        <v>57009.74938692484</v>
+        <v>55665.38146979827</v>
       </c>
       <c r="BI8">
-        <v>57009.74938692484</v>
+        <v>55665.38146979827</v>
       </c>
       <c r="BJ8">
-        <v>11962.43794485312</v>
+        <v>11683.60789811902</v>
       </c>
       <c r="BK8">
-        <v>570.0974938692484</v>
+        <v>556.6538146979827</v>
       </c>
       <c r="BL8">
-        <v>0.005700974938692484</v>
+        <v>0.005566538146979827</v>
       </c>
       <c r="BM8">
         <v>500</v>
@@ -2578,31 +2578,31 @@
         <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.09425802443622699</v>
+        <v>0.09641636474626521</v>
       </c>
       <c r="BP8">
-        <v>0.02857531660759011</v>
+        <v>0.02816002974822946</v>
       </c>
       <c r="BQ8">
-        <v>0.05056710655796827</v>
+        <v>0.04860057523681428</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW8" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2610,7 +2610,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2622,154 +2622,154 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K9">
-        <v>0.5795383327517757</v>
+        <v>0.07896167182858867</v>
       </c>
       <c r="L9">
-        <v>0.9852090534858458</v>
+        <v>1.664419904478783</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O9" t="s">
+        <v>95</v>
+      </c>
+      <c r="P9" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9">
+        <v>0.7697404179571472</v>
+      </c>
+      <c r="R9" t="s">
+        <v>104</v>
+      </c>
+      <c r="S9" t="s">
+        <v>109</v>
+      </c>
+      <c r="T9">
+        <v>-0.684818444315218</v>
+      </c>
+      <c r="U9">
+        <v>0.7200068284780117</v>
+      </c>
+      <c r="V9" t="s">
         <v>94</v>
       </c>
-      <c r="P9" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q9">
-        <v>0.8948845831879439</v>
-      </c>
-      <c r="R9" t="s">
-        <v>102</v>
-      </c>
-      <c r="S9" t="s">
-        <v>107</v>
-      </c>
-      <c r="T9">
-        <v>-0.750971043846107</v>
-      </c>
-      <c r="U9">
-        <v>0.8248566478294365</v>
-      </c>
-      <c r="V9" t="s">
-        <v>93</v>
-      </c>
       <c r="W9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9999557127436877</v>
+        <v>0.9999771110475011</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-122.4092014101674</v>
+        <v>-117.644066305188</v>
       </c>
       <c r="AA9">
-        <v>-3.000000000000004</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB9">
-        <v>-0.5359623828302383</v>
+        <v>-0.4639774790755453</v>
       </c>
       <c r="AC9">
-        <v>-0.8442418635621743</v>
+        <v>-0.8858469952032925</v>
       </c>
       <c r="AD9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AH9">
-        <v>-0.5359386465268161</v>
+        <v>-0.4639668591170661</v>
       </c>
       <c r="AI9">
-        <v>0.8497017684473732</v>
+        <v>0.8278743507134645</v>
       </c>
       <c r="AJ9">
-        <v>-0.678926070549545</v>
+        <v>-1.13585558544477</v>
       </c>
       <c r="AK9">
-        <v>-1.080325044912384</v>
+        <v>-2.241244700868494</v>
       </c>
       <c r="AL9">
-        <v>-1.518876694813364</v>
+        <v>-2.638569280296996</v>
       </c>
       <c r="AM9">
-        <v>0.01055656208299138</v>
+        <v>0.412048627952475</v>
       </c>
       <c r="AN9">
-        <v>1.486091757780796</v>
+        <v>2.52065545207872</v>
       </c>
       <c r="AO9">
-        <v>0.07380963907992617</v>
+        <v>0.0754058791721629</v>
       </c>
       <c r="AP9">
-        <v>8.95293</v>
+        <v>7.6885</v>
       </c>
       <c r="AQ9">
-        <v>8.885451127902957</v>
+        <v>7.635252006639986</v>
       </c>
       <c r="AR9">
-        <v>8.990241951268386</v>
+        <v>7.711677210042067</v>
       </c>
       <c r="AS9">
-        <v>8.95293</v>
+        <v>7.6885</v>
       </c>
       <c r="AT9">
-        <v>8.74544</v>
+        <v>7.5296</v>
       </c>
       <c r="AU9">
-        <v>8.885451127902957</v>
+        <v>7.635252006639986</v>
       </c>
       <c r="AV9">
-        <v>9.0339975</v>
+        <v>7.738175000000001</v>
       </c>
       <c r="AW9">
-        <v>-0.007537071338326442</v>
+        <v>-0.006925667342136244</v>
       </c>
       <c r="AX9">
-        <v>0.8323788459868985</v>
+        <v>1.07192739526953</v>
       </c>
       <c r="AY9">
-        <v>0.007537071338326442</v>
+        <v>0.006925667342136244</v>
       </c>
       <c r="AZ9">
-        <v>0.4024197004661634</v>
+        <v>0.4057180282085678</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3975802995338366</v>
+        <v>0.3942819717914322</v>
       </c>
       <c r="BC9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2778,58 +2778,58 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>447.442291593972</v>
+        <v>384.8702089785736</v>
       </c>
       <c r="BG9">
-        <v>0.00905485690159535</v>
+        <v>0.0064609481693439</v>
       </c>
       <c r="BH9">
-        <v>55218.98417985009</v>
+        <v>77388.02214393468</v>
       </c>
       <c r="BI9">
-        <v>49414.61764184682</v>
+        <v>59568.68850994924</v>
       </c>
       <c r="BJ9">
-        <v>5519.379425712791</v>
+        <v>7747.76464979505</v>
       </c>
       <c r="BK9">
-        <v>494.1461764184681</v>
+        <v>595.6868850994924</v>
       </c>
       <c r="BL9">
-        <v>0.004941461764184681</v>
+        <v>0.005956868850994924</v>
       </c>
       <c r="BM9">
-        <v>447.442291593972</v>
+        <v>384.8702089785736</v>
       </c>
       <c r="BN9">
-        <v>0.00447442291593972</v>
+        <v>0.003848702089785736</v>
       </c>
       <c r="BO9">
-        <v>0.1561384069969589</v>
+        <v>0.1366404359942915</v>
       </c>
       <c r="BP9">
-        <v>0.0672426384105443</v>
+        <v>0.05357706800275999</v>
       </c>
       <c r="BQ9">
-        <v>0.06575906580641799</v>
+        <v>0.05796994776484156</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW9" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2837,7 +2837,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2849,154 +2849,154 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.7961295937276529</v>
       </c>
       <c r="L10">
-        <v>1.44161677324608</v>
+        <v>1.099162256042905</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O10" t="s">
+        <v>95</v>
+      </c>
+      <c r="P10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q10">
+        <v>0.9490323984319132</v>
+      </c>
+      <c r="R10" t="s">
+        <v>104</v>
+      </c>
+      <c r="S10" t="s">
+        <v>109</v>
+      </c>
+      <c r="T10">
+        <v>-0.7634159909761071</v>
+      </c>
+      <c r="U10">
+        <v>0.8629527559013159</v>
+      </c>
+      <c r="V10" t="s">
         <v>94</v>
       </c>
-      <c r="P10" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q10">
-        <v>0.75</v>
-      </c>
-      <c r="R10" t="s">
-        <v>102</v>
-      </c>
-      <c r="S10" t="s">
-        <v>107</v>
-      </c>
-      <c r="T10">
-        <v>-0.6609764876253195</v>
-      </c>
-      <c r="U10">
-        <v>0.6974245382524717</v>
-      </c>
-      <c r="V10" t="s">
-        <v>93</v>
-      </c>
       <c r="W10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X10">
-        <v>0.999940475284312</v>
+        <v>0.9999844836116794</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-115.6023027918092</v>
+        <v>-122.8542676783943</v>
       </c>
       <c r="AA10">
-        <v>-9</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AB10">
-        <v>-0.4321219942737594</v>
+        <v>-0.5425041095597809</v>
       </c>
       <c r="AC10">
-        <v>-0.901815159589186</v>
+        <v>-0.8400531477893224</v>
       </c>
       <c r="AD10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AH10">
-        <v>-0.4320962723349077</v>
+        <v>-0.5424956918553514</v>
       </c>
       <c r="AI10">
-        <v>0.8168070767963024</v>
+        <v>0.8527255077304319</v>
       </c>
       <c r="AJ10">
-        <v>-0.9432442515215841</v>
+        <v>-0.782626422887848</v>
       </c>
       <c r="AK10">
-        <v>-2.039730927594273</v>
+        <v>-1.2207549222003</v>
       </c>
       <c r="AL10">
-        <v>-2.45604809939681</v>
+        <v>-1.592488924166868</v>
       </c>
       <c r="AM10">
-        <v>-0.3859727635142868</v>
+        <v>0.5709083704187535</v>
       </c>
       <c r="AN10">
-        <v>2.416353699652829</v>
+        <v>1.502624010295105</v>
       </c>
       <c r="AO10">
-        <v>0.08539125223556419</v>
+        <v>0.06680196267726835</v>
       </c>
       <c r="AP10">
-        <v>7.6919</v>
+        <v>8.965809999999999</v>
       </c>
       <c r="AQ10">
-        <v>7.616003538069489</v>
+        <v>8.901719650525836</v>
       </c>
       <c r="AR10">
-        <v>7.656616654614982</v>
+        <v>9.000936870462997</v>
       </c>
       <c r="AS10">
-        <v>7.6919</v>
+        <v>8.965809999999999</v>
       </c>
       <c r="AT10">
-        <v>7.5364</v>
+        <v>8.771199999999999</v>
       </c>
       <c r="AU10">
-        <v>7.616003538069489</v>
+        <v>8.901719650525836</v>
       </c>
       <c r="AV10">
-        <v>7.742497641287009</v>
+        <v>9.046877499999999</v>
       </c>
       <c r="AW10">
-        <v>-0.009867063005305815</v>
+        <v>-0.007148305560140533</v>
       </c>
       <c r="AX10">
-        <v>1.5</v>
+        <v>0.7905800656756843</v>
       </c>
       <c r="AY10">
-        <v>0.009867063005305815</v>
+        <v>0.007148305560140533</v>
       </c>
       <c r="AZ10">
-        <v>0.4034677077384222</v>
+        <v>0.3987067915621768</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3965322922615778</v>
+        <v>0.4012932084378233</v>
       </c>
       <c r="BC10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -3005,58 +3005,58 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>375</v>
+        <v>474.5161992159566</v>
       </c>
       <c r="BG10">
-        <v>0.00657804200353721</v>
+        <v>0.009041848979623712</v>
       </c>
       <c r="BH10">
-        <v>76010.46021462543</v>
+        <v>55298.4241527122</v>
       </c>
       <c r="BI10">
-        <v>57007.84516096907</v>
+        <v>52479.9961031537</v>
       </c>
       <c r="BJ10">
-        <v>7411.412675797797</v>
+        <v>5853.346892601304</v>
       </c>
       <c r="BK10">
-        <v>570.0784516096908</v>
+        <v>524.7999610315369</v>
       </c>
       <c r="BL10">
-        <v>0.005700784516096908</v>
+        <v>0.005247999610315369</v>
       </c>
       <c r="BM10">
-        <v>375.0000000000001</v>
+        <v>474.5161992159566</v>
       </c>
       <c r="BN10">
-        <v>0.003750000000000001</v>
+        <v>0.004745161992159566</v>
       </c>
       <c r="BO10">
-        <v>0.1367617082927783</v>
+        <v>0.1484031022727679</v>
       </c>
       <c r="BP10">
-        <v>0.05261061385391377</v>
+        <v>0.05880028035087533</v>
       </c>
       <c r="BQ10">
-        <v>0.05618363261382904</v>
+        <v>0.05830081718320743</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW10" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3064,7 +3064,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3079,13 +3079,13 @@
         <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="2">
         <v>46282</v>
@@ -3103,19 +3103,19 @@
         <v>31</v>
       </c>
       <c r="O11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="T11">
         <v>-0.5121842826309468</v>
@@ -3124,10 +3124,10 @@
         <v>0.6304485710096058</v>
       </c>
       <c r="V11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X11">
         <v>0.999862575302719</v>
@@ -3148,16 +3148,16 @@
         <v>-0.9831383274363318</v>
       </c>
       <c r="AD11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AH11">
         <v>-0.1828382866368433</v>
@@ -3187,10 +3187,10 @@
         <v>1.146005</v>
       </c>
       <c r="AQ11">
-        <v>1.117494777145027</v>
+        <v>1.122807662760497</v>
       </c>
       <c r="AR11">
-        <v>1.097565759249131</v>
+        <v>1.110136540588327</v>
       </c>
       <c r="AS11">
         <v>1.146005</v>
@@ -3199,31 +3199,31 @@
         <v>1.124515</v>
       </c>
       <c r="AU11">
-        <v>1.117494777145027</v>
+        <v>1.122807662760497</v>
       </c>
       <c r="AV11">
-        <v>1.165011815236649</v>
+        <v>1.161469891493002</v>
       </c>
       <c r="AW11">
-        <v>-0.02487792187204522</v>
+        <v>-0.02024191625647649</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.02487792187204522</v>
+        <v>0.02024191625647649</v>
       </c>
       <c r="AZ11">
-        <v>0.419982995424765</v>
+        <v>0.4176620782215197</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.380017004575235</v>
+        <v>0.3823379217784803</v>
       </c>
       <c r="BC11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3235,22 +3235,22 @@
         <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.01658528124803014</v>
+        <v>0.013494610837651</v>
       </c>
       <c r="BH11">
-        <v>30147.21261114494</v>
+        <v>37051.82802344783</v>
       </c>
       <c r="BI11">
-        <v>22610.40945835871</v>
+        <v>27788.87101758587</v>
       </c>
       <c r="BJ11">
-        <v>19729.7651043047</v>
+        <v>24248.47275324791</v>
       </c>
       <c r="BK11">
-        <v>226.1040945835871</v>
+        <v>277.8887101758587</v>
       </c>
       <c r="BL11">
-        <v>0.002261040945835871</v>
+        <v>0.002778887101758587</v>
       </c>
       <c r="BM11">
         <v>375</v>
@@ -3259,31 +3259,31 @@
         <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>0.02290103539180109</v>
+        <v>0.02350406743712772</v>
       </c>
       <c r="BP11">
-        <v>0.008355882246582373</v>
+        <v>0.008205487520676506</v>
       </c>
       <c r="BQ11">
-        <v>0.01117504901080117</v>
+        <v>0.01100111553355954</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05086952202688542</v>
+        <v>0.04858241297563112</v>
       </c>
       <c r="BT11" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="BU11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="BW11" s="2">
-        <v>46311</v>
+        <v>46312</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -301,13 +301,13 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
-  </si>
-  <si>
-    <t>NO_SIGNAL</t>
+    <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -355,76 +355,76 @@
     <t>上涨</t>
   </si>
   <si>
+    <t>下跌</t>
+  </si>
+  <si>
     <t>转换</t>
   </si>
   <si>
-    <t>下跌</t>
-  </si>
-  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
-  </si>
-  <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
-    <t>DOWN_SLOPE</t>
-  </si>
-  <si>
-    <t>DOWN_STEEPENING</t>
-  </si>
-  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
     <t>地形转换区</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
-  </si>
-  <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>下降坡延续</t>
-  </si>
-  <si>
-    <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.008493,naive=0.00625,drift4=0.007761; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=295,naive=26.72,drift4=83.64; naive_cap_applied; model_divergence_guard(abs=664.1,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=5.047,naive=2.403,drift4=4.339; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01504,naive=0.003004,drift4=0.007262; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02978,naive=0.005571,drift4=0.01033; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.0134,naive=0.01042,drift4=0.01198; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.09642,naive=0.02816,drift4=0.0486; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1366,naive=0.05358,drift4=0.05797; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1484,naive=0.0588,drift4=0.0583; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.0235,naive=0.008205,drift4=0.011; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.007419,naive=0.003997,drift4=0.005587; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=291.8,naive=25.94,drift4=76.28; naive_cap_applied; model_divergence_guard(abs=662,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=4.456,naive=1.876,drift4=3.835; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01414,naive=0.002597,drift4=0.006469; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02845,naive=0.006386,drift4=0.009433; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01123,naive=0.007682,drift4=0.0091; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.09736,naive=0.02687,drift4=0.04558; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1337,naive=0.05236,drift4=0.0576; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1527,naive=0.05772,drift4=0.05854; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02187,naive=0.006585,drift4=0.009173; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1033,7 +1033,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1051,28 +1051,28 @@
         <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I2" t="s">
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2.219972358040653</v>
+        <v>2.204458390183103</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P2" t="s">
         <v>97</v>
@@ -1087,34 +1087,34 @@
         <v>105</v>
       </c>
       <c r="T2">
-        <v>0.8080428531121724</v>
+        <v>0.8401908892389828</v>
       </c>
       <c r="U2">
-        <v>0.913616507569292</v>
+        <v>0.9280799837310828</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
       </c>
       <c r="W2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X2">
-        <v>0.9999888946752581</v>
+        <v>0.9999763342941623</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>51.96930300464032</v>
+        <v>47.12681191947653</v>
       </c>
       <c r="AA2">
-        <v>-6.999999999999997</v>
+        <v>-11</v>
       </c>
       <c r="AB2">
-        <v>0.6160835744542178</v>
+        <v>0.6803779963930544</v>
       </c>
       <c r="AC2">
-        <v>0.7876807914934287</v>
+        <v>0.7328613661697366</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1129,58 +1129,58 @@
         <v>121</v>
       </c>
       <c r="AH2">
-        <v>0.6160767326460553</v>
+        <v>0.6803618947675334</v>
       </c>
       <c r="AI2">
-        <v>0.8753104062886309</v>
+        <v>0.8959369865154437</v>
       </c>
       <c r="AJ2">
-        <v>1.556851134476295</v>
+        <v>1.60140670467573</v>
       </c>
       <c r="AK2">
-        <v>2.039565441109928</v>
+        <v>1.799634869832472</v>
       </c>
       <c r="AL2">
-        <v>3.338512226818299</v>
+        <v>3.088340235516783</v>
       </c>
       <c r="AM2">
-        <v>-1.112094145329638</v>
+        <v>-2.258449850764255</v>
       </c>
       <c r="AN2">
-        <v>3.157360108686769</v>
+        <v>2.806959672095708</v>
       </c>
       <c r="AO2">
-        <v>0.06340519455983201</v>
+        <v>0.05445419603619626</v>
       </c>
       <c r="AP2">
-        <v>0.8256600000000001</v>
+        <v>0.82211</v>
       </c>
       <c r="AQ2">
-        <v>0.8259160265513088</v>
+        <v>0.8212087303337301</v>
       </c>
       <c r="AR2">
-        <v>0.8086212372676598</v>
+        <v>0.8041434384556025</v>
       </c>
       <c r="AS2">
-        <v>0.8256600000000001</v>
+        <v>0.82211</v>
       </c>
       <c r="AT2">
-        <v>0.8496050000000002</v>
+        <v>0.8425050000000001</v>
       </c>
       <c r="AW2">
-        <v>0.0003100871439923712</v>
+        <v>-0.001096288411854752</v>
       </c>
       <c r="AY2">
-        <v>0.0003100871439923712</v>
+        <v>0.001096288411854752</v>
       </c>
       <c r="AZ2">
-        <v>0.4611575948290714</v>
+        <v>0.448815662687341</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3388424051709287</v>
+        <v>0.3511843373126591</v>
       </c>
       <c r="BC2" t="s">
         <v>127</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.00849251380034065</v>
+        <v>0.007418921024817762</v>
       </c>
       <c r="BP2">
-        <v>0.00624971563382879</v>
+        <v>0.003996946251392814</v>
       </c>
       <c r="BQ2">
-        <v>0.007760596961408234</v>
+        <v>0.005586992505074495</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT2" t="s">
         <v>137</v>
@@ -1240,7 +1240,7 @@
         <v>139</v>
       </c>
       <c r="BW2" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1272,22 +1272,22 @@
         <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.04969460202241648</v>
+        <v>0.1315860881573243</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P3" t="s">
         <v>98</v>
@@ -1302,40 +1302,40 @@
         <v>106</v>
       </c>
       <c r="T3">
-        <v>0.7023511159933751</v>
+        <v>0.8263005543277491</v>
       </c>
       <c r="U3">
-        <v>0.7158272077718091</v>
+        <v>0.7633635218447925</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W3" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="X3">
-        <v>0.9990768222991612</v>
+        <v>0.9661130895892217</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>-82.65846887999095</v>
+        <v>-61.34341222524586</v>
       </c>
       <c r="AA3">
-        <v>-7.999999999999998</v>
+        <v>56</v>
       </c>
       <c r="AB3">
-        <v>0.1277835545917157</v>
+        <v>0.4795587580597446</v>
       </c>
       <c r="AC3">
-        <v>-0.9918020786305632</v>
+        <v>-0.8775097706397321</v>
       </c>
       <c r="AD3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF3" t="s">
         <v>116</v>
@@ -1344,58 +1344,58 @@
         <v>122</v>
       </c>
       <c r="AH3">
-        <v>0.06383279383179137</v>
+        <v>0.231653996694335</v>
       </c>
       <c r="AI3">
-        <v>0.5135323923098526</v>
+        <v>0.6198718889289074</v>
       </c>
       <c r="AJ3">
-        <v>0.1318101331374104</v>
+        <v>0.1653357313260205</v>
       </c>
       <c r="AK3">
-        <v>-0.836292051867517</v>
+        <v>-0.6024835080623392</v>
       </c>
       <c r="AL3">
-        <v>-0.08946860949674705</v>
+        <v>0.08968126878286138</v>
       </c>
       <c r="AM3">
-        <v>-0.05403530635355595</v>
+        <v>0.09596656650477405</v>
       </c>
       <c r="AN3">
-        <v>0.1139465447500654</v>
+        <v>0.1290642195994172</v>
       </c>
       <c r="AO3">
-        <v>0.1631970791491234</v>
+        <v>0.08090213230162374</v>
       </c>
       <c r="AP3">
-        <v>4372.83</v>
+        <v>4380.92</v>
       </c>
       <c r="AQ3">
-        <v>4442.595498755885</v>
+        <v>4454.513880473512</v>
       </c>
       <c r="AR3">
-        <v>4919.234995852948</v>
+        <v>4929.299601578374</v>
       </c>
       <c r="AS3">
-        <v>4372.83</v>
+        <v>4380.92</v>
       </c>
       <c r="AT3">
-        <v>4137.440000000001</v>
+        <v>4153.620000000001</v>
       </c>
       <c r="AU3">
-        <v>4442.595498755885</v>
+        <v>4454.513880473512</v>
       </c>
       <c r="AV3">
-        <v>4239.1925</v>
+        <v>4247.2825</v>
       </c>
       <c r="AW3">
-        <v>0.01595431305490617</v>
+        <v>0.01679872731606886</v>
       </c>
       <c r="AX3">
-        <v>0.5220503133917146</v>
+        <v>0.5506978241400229</v>
       </c>
       <c r="AY3">
-        <v>0.01595431305490617</v>
+        <v>0.01679872731606886</v>
       </c>
       <c r="AZ3">
         <v>0.3</v>
@@ -1419,43 +1419,43 @@
         <v>375</v>
       </c>
       <c r="BG3">
-        <v>0.03056087247846364</v>
+        <v>0.03050443742410273</v>
       </c>
       <c r="BH3">
-        <v>16360.78944906929</v>
+        <v>16391.05789916751</v>
       </c>
       <c r="BI3">
-        <v>12270.59208680197</v>
+        <v>12293.29342437563</v>
       </c>
       <c r="BJ3">
         <v>2.806098587597041</v>
       </c>
       <c r="BK3">
-        <v>122.7059208680197</v>
+        <v>122.9329342437563</v>
       </c>
       <c r="BL3">
-        <v>0.001227059208680197</v>
+        <v>0.001229329342437563</v>
       </c>
       <c r="BM3">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="BN3">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="BO3">
-        <v>295.0167031240425</v>
+        <v>291.817262661377</v>
       </c>
       <c r="BP3">
-        <v>26.7186593225043</v>
+        <v>25.94410124064647</v>
       </c>
       <c r="BQ3">
-        <v>83.64233219288127</v>
+        <v>76.28207155433719</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT3" t="s">
         <v>138</v>
@@ -1467,7 +1467,7 @@
         <v>140</v>
       </c>
       <c r="BW3" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1475,7 +1475,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1499,22 +1499,22 @@
         <v>94</v>
       </c>
       <c r="J4" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.326215123079677</v>
+        <v>1.129510121686975</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P4" t="s">
         <v>99</v>
@@ -1529,40 +1529,40 @@
         <v>107</v>
       </c>
       <c r="T4">
-        <v>-0.8738735230020797</v>
+        <v>-0.7604381919198788</v>
       </c>
       <c r="U4">
-        <v>0.7925867707208032</v>
+        <v>0.7418676067757343</v>
       </c>
       <c r="V4" t="s">
         <v>94</v>
       </c>
       <c r="W4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X4">
-        <v>0.9973747414794695</v>
+        <v>0.9986816816471552</v>
       </c>
       <c r="Y4">
-        <v>0.3315673733474611</v>
+        <v>0.5832446989296391</v>
       </c>
       <c r="Z4">
-        <v>136.2972034583038</v>
+        <v>122.5722102741784</v>
       </c>
       <c r="AA4">
-        <v>-53</v>
+        <v>-37</v>
       </c>
       <c r="AB4">
-        <v>-0.7229334238653541</v>
+        <v>-0.538362113524273</v>
       </c>
       <c r="AC4">
-        <v>0.6909176974563007</v>
+        <v>0.8427136137037765</v>
       </c>
       <c r="AD4" t="s">
         <v>94</v>
       </c>
       <c r="AE4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF4" t="s">
         <v>117</v>
@@ -1571,67 +1571,67 @@
         <v>123</v>
       </c>
       <c r="AH4">
-        <v>-0.4800536978699176</v>
+        <v>-0.4256176409392974</v>
       </c>
       <c r="AI4">
-        <v>0.7770164922437377</v>
+        <v>0.7710242745176157</v>
       </c>
       <c r="AJ4">
-        <v>-1.179377254172649</v>
+        <v>-1.012783771105633</v>
       </c>
       <c r="AK4">
-        <v>0.9629161850976939</v>
+        <v>1.41591866015502</v>
       </c>
       <c r="AL4">
-        <v>-0.9306409438947538</v>
+        <v>-0.7463860614320315</v>
       </c>
       <c r="AM4">
-        <v>4.69785617985081</v>
+        <v>3.819793183395782</v>
       </c>
       <c r="AN4">
-        <v>0.8121045632290568</v>
+        <v>0.6643473352406452</v>
       </c>
       <c r="AO4">
-        <v>0.03505446068783412</v>
+        <v>0.04447925268065549</v>
       </c>
       <c r="AP4">
-        <v>157.8075</v>
+        <v>156.87</v>
       </c>
       <c r="AQ4">
-        <v>158.8413317956887</v>
+        <v>157.613335761856</v>
       </c>
       <c r="AR4">
-        <v>160.9223365232886</v>
+        <v>160.0157751104429</v>
       </c>
       <c r="AS4">
-        <v>157.8075</v>
+        <v>156.87</v>
       </c>
       <c r="AT4">
-        <v>156.6035</v>
+        <v>154.7285</v>
       </c>
       <c r="AU4">
-        <v>158.8413317956887</v>
+        <v>157.613335761856</v>
       </c>
       <c r="AV4">
-        <v>156.309375</v>
+        <v>155.371875</v>
       </c>
       <c r="AW4">
-        <v>0.006551220922254364</v>
+        <v>0.004738546324064345</v>
       </c>
       <c r="AX4">
-        <v>0.6900838018781107</v>
+        <v>0.4961773963160391</v>
       </c>
       <c r="AY4">
-        <v>0.006551220922254364</v>
+        <v>0.004738546324064345</v>
       </c>
       <c r="AZ4">
-        <v>0.4624004138429429</v>
+        <v>0.4646128129410264</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3375995861570571</v>
+        <v>0.3353871870589737</v>
       </c>
       <c r="BC4" t="s">
         <v>129</v>
@@ -1646,22 +1646,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.009493370086973154</v>
+        <v>0.009550105182635405</v>
       </c>
       <c r="BH4">
-        <v>52668.33541927354</v>
+        <v>52355.44430538117</v>
       </c>
       <c r="BI4">
-        <v>52668.33541927354</v>
+        <v>52355.44430538117</v>
       </c>
       <c r="BJ4">
         <v>333.7505214851863</v>
       </c>
       <c r="BK4">
-        <v>526.6833541927354</v>
+        <v>523.5544430538117</v>
       </c>
       <c r="BL4">
-        <v>0.005266833541927353</v>
+        <v>0.005235544430538117</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1670,19 +1670,19 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>5.046718404865242</v>
+        <v>4.456351763382687</v>
       </c>
       <c r="BP4">
-        <v>2.40344946873723</v>
+        <v>1.876082400225948</v>
       </c>
       <c r="BQ4">
-        <v>4.339337297104737</v>
+        <v>3.834702388521879</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT4" t="s">
         <v>138</v>
@@ -1694,7 +1694,7 @@
         <v>140</v>
       </c>
       <c r="BW4" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1702,7 +1702,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1726,22 +1726,22 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.6920440496369997</v>
+        <v>0.6714888821016466</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P5" t="s">
         <v>99</v>
@@ -1756,34 +1756,34 @@
         <v>106</v>
       </c>
       <c r="T5">
-        <v>0.5846718301826457</v>
+        <v>0.5721566250061204</v>
       </c>
       <c r="U5">
-        <v>0.6630150633925173</v>
+        <v>0.6574023218762785</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
       </c>
       <c r="W5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X5">
-        <v>0.9996509592413069</v>
+        <v>0.9997273624940969</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-72.2883097669946</v>
+        <v>-73.54372225878554</v>
       </c>
       <c r="AA5">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="AB5">
-        <v>0.3042274290293818</v>
+        <v>0.2832835892612633</v>
       </c>
       <c r="AC5">
-        <v>-0.9525994286299843</v>
+        <v>-0.9590361870415818</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1792,73 +1792,73 @@
         <v>112</v>
       </c>
       <c r="AF5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AG5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AH5">
-        <v>0.3041212412567381</v>
+        <v>0.2832063555300239</v>
       </c>
       <c r="AI5">
-        <v>0.7795386901863116</v>
+        <v>0.7731312137537724</v>
       </c>
       <c r="AJ5">
-        <v>0.7833795217544304</v>
+        <v>0.7340186446384928</v>
       </c>
       <c r="AK5">
-        <v>-2.206654414137842</v>
+        <v>-2.281072888774191</v>
       </c>
       <c r="AL5">
-        <v>0.3515149772265023</v>
+        <v>0.405411182059805</v>
       </c>
       <c r="AM5">
-        <v>-2.62818533186247</v>
+        <v>-2.033462601656284</v>
       </c>
       <c r="AN5">
-        <v>0.4103625275900591</v>
+        <v>0.3800632544046766</v>
       </c>
       <c r="AO5">
-        <v>0.07738249504640238</v>
+        <v>0.07838959931693661</v>
       </c>
       <c r="AP5">
-        <v>0.712165</v>
+        <v>0.712555</v>
       </c>
       <c r="AQ5">
-        <v>0.7109713897329846</v>
+        <v>0.711560469940694</v>
       </c>
       <c r="AR5">
-        <v>0.7125456472398568</v>
+        <v>0.7130789806241633</v>
       </c>
       <c r="AS5">
-        <v>0.712165</v>
+        <v>0.712555</v>
       </c>
       <c r="AT5">
-        <v>0.7084050000000002</v>
+        <v>0.7091850000000002</v>
       </c>
       <c r="AU5">
-        <v>0.7109713897329846</v>
+        <v>0.7114861675</v>
       </c>
       <c r="AV5">
-        <v>0.7193737499999999</v>
+        <v>0.71976375</v>
       </c>
       <c r="AW5">
-        <v>-0.001676030508401111</v>
+        <v>-0.001395723922091703</v>
       </c>
       <c r="AX5">
-        <v>0.1655779805119457</v>
+        <v>0.1482687705912968</v>
       </c>
       <c r="AY5">
-        <v>0.001676030508401111</v>
+        <v>0.001395723922091703</v>
       </c>
       <c r="AZ5">
-        <v>0.4381898838229265</v>
+        <v>0.4369487434364187</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3618101161770735</v>
+        <v>0.3630512565635813</v>
       </c>
       <c r="BC5" t="s">
         <v>130</v>
@@ -1873,22 +1873,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.01012230311795712</v>
+        <v>0.01011676291654669</v>
       </c>
       <c r="BH5">
-        <v>49395.87307092123</v>
+        <v>49422.92353043225</v>
       </c>
       <c r="BI5">
-        <v>49395.87307092123</v>
+        <v>49422.92353043225</v>
       </c>
       <c r="BJ5">
-        <v>69360.15259233637</v>
+        <v>69360.15259233638</v>
       </c>
       <c r="BK5">
-        <v>493.9587307092123</v>
+        <v>494.2292353043225</v>
       </c>
       <c r="BL5">
-        <v>0.004939587307092123</v>
+        <v>0.004942292353043225</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1897,19 +1897,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.01503514053222917</v>
+        <v>0.01413791946286085</v>
       </c>
       <c r="BP5">
-        <v>0.003004205577708955</v>
+        <v>0.002596815505138828</v>
       </c>
       <c r="BQ5">
-        <v>0.007262303960698764</v>
+        <v>0.006468556960569494</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT5" t="s">
         <v>138</v>
@@ -1921,7 +1921,7 @@
         <v>140</v>
       </c>
       <c r="BW5" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1929,7 +1929,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1953,28 +1953,28 @@
         <v>94</v>
       </c>
       <c r="J6" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K6">
-        <v>0.7348033142862079</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>3.387701679821335</v>
+        <v>3.810434383610249</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P6" t="s">
         <v>98</v>
       </c>
       <c r="Q6">
-        <v>0.933700828571552</v>
+        <v>1</v>
       </c>
       <c r="R6" t="s">
         <v>103</v>
@@ -1983,109 +1983,109 @@
         <v>108</v>
       </c>
       <c r="T6">
-        <v>-0.9942167738971054</v>
+        <v>-0.9994010773607538</v>
       </c>
       <c r="U6">
-        <v>0.9575949453430195</v>
+        <v>0.9997053321694902</v>
       </c>
       <c r="V6" t="s">
         <v>94</v>
       </c>
       <c r="W6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X6">
-        <v>0.9999075997855635</v>
+        <v>0.9998993894286041</v>
       </c>
       <c r="Y6">
-        <v>0.9405409251419504</v>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>171.3857006022782</v>
+        <v>177.1952621162782</v>
       </c>
       <c r="AA6">
-        <v>6.000000000000009</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>-0.9887190304839409</v>
+        <v>-0.9988020944574952</v>
       </c>
       <c r="AC6">
-        <v>0.149782104267819</v>
+        <v>0.0489323625765286</v>
       </c>
       <c r="AD6" t="s">
         <v>94</v>
       </c>
       <c r="AE6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AH6">
-        <v>-0.9592362292365794</v>
+        <v>-0.9987016044080604</v>
       </c>
       <c r="AI6">
-        <v>0.9794401315396966</v>
+        <v>0.9941049421684818</v>
       </c>
       <c r="AJ6">
-        <v>-2.551143661676161</v>
+        <v>-2.852760448391738</v>
       </c>
       <c r="AK6">
-        <v>0.4162330582870611</v>
+        <v>0.1928992565970481</v>
       </c>
       <c r="AL6">
-        <v>-4.312108478118331</v>
+        <v>-4.923376570422746</v>
       </c>
       <c r="AM6">
-        <v>3.358595373306814</v>
+        <v>3.583576937470743</v>
       </c>
       <c r="AN6">
-        <v>4.024164510598976</v>
+        <v>4.603722682386502</v>
       </c>
       <c r="AO6">
-        <v>0.03500948372548682</v>
+        <v>0.03666981645852199</v>
       </c>
       <c r="AP6">
-        <v>6.69815</v>
+        <v>6.696575</v>
       </c>
       <c r="AQ6">
-        <v>6.680408283089646</v>
+        <v>6.677913127374381</v>
       </c>
       <c r="AR6">
-        <v>6.676412763335501</v>
+        <v>6.674129200139214</v>
       </c>
       <c r="AS6">
-        <v>6.69815</v>
+        <v>6.696575</v>
       </c>
       <c r="AT6">
-        <v>6.675499999999999</v>
+        <v>6.672349999999999</v>
       </c>
       <c r="AU6">
-        <v>6.680408283089646</v>
+        <v>6.677913127374381</v>
       </c>
       <c r="AV6">
-        <v>6.72165625</v>
+        <v>6.72008125</v>
       </c>
       <c r="AW6">
-        <v>-0.002648748820249502</v>
+        <v>-0.002786778707864779</v>
       </c>
       <c r="AX6">
-        <v>0.7547659414136448</v>
+        <v>0.7939110928208406</v>
       </c>
       <c r="AY6">
-        <v>0.002648748820249502</v>
+        <v>0.002786778707864779</v>
       </c>
       <c r="AZ6">
-        <v>0.4144372094423198</v>
+        <v>0.4036237175087319</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3855627905576802</v>
+        <v>0.3963762824912681</v>
       </c>
       <c r="BC6" t="s">
         <v>131</v>
@@ -2097,46 +2097,46 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>466.850414285776</v>
+        <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.003509364526025786</v>
+        <v>0.003510189910513899</v>
       </c>
       <c r="BH6">
-        <v>142475.9372507335</v>
+        <v>142442.4355224698</v>
       </c>
       <c r="BI6">
-        <v>133029.9006625183</v>
+        <v>142442.4355224698</v>
       </c>
       <c r="BJ6">
-        <v>19860.69297679483</v>
+        <v>21270.9385801652</v>
       </c>
       <c r="BK6">
-        <v>1330.299006625183</v>
+        <v>1424.424355224698</v>
       </c>
       <c r="BL6">
-        <v>0.01330299006625183</v>
+        <v>0.01424424355224698</v>
       </c>
       <c r="BM6">
-        <v>466.850414285776</v>
+        <v>500</v>
       </c>
       <c r="BN6">
-        <v>0.00466850414285776</v>
+        <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.02978151977148156</v>
+        <v>0.0284522153009786</v>
       </c>
       <c r="BP6">
-        <v>0.005570663578087322</v>
+        <v>0.006385723239760613</v>
       </c>
       <c r="BQ6">
-        <v>0.01032568948596116</v>
+        <v>0.009432605409580814</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT6" t="s">
         <v>138</v>
@@ -2148,7 +2148,7 @@
         <v>140</v>
       </c>
       <c r="BW6" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2156,7 +2156,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2180,22 +2180,22 @@
         <v>94</v>
       </c>
       <c r="J7" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.924936610197405</v>
+        <v>1.061797745320032</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
         <v>98</v>
@@ -2210,109 +2210,109 @@
         <v>109</v>
       </c>
       <c r="T7">
-        <v>-0.5561168204200569</v>
+        <v>-0.5731410801839203</v>
       </c>
       <c r="U7">
-        <v>0.6502308918462194</v>
+        <v>0.6579014605262827</v>
       </c>
       <c r="V7" t="s">
         <v>94</v>
       </c>
       <c r="W7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X7">
-        <v>0.999913290628775</v>
+        <v>0.9999518977740743</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-104.8606887688172</v>
+        <v>-106.558696098558</v>
       </c>
       <c r="AA7">
-        <v>-7.999999999999998</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB7">
-        <v>-0.2564696919894996</v>
+        <v>-0.2849974489580183</v>
       </c>
       <c r="AC7">
-        <v>-0.9665522733359077</v>
+        <v>-0.9585282750589165</v>
       </c>
       <c r="AD7" t="s">
         <v>94</v>
       </c>
       <c r="AE7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AH7">
-        <v>-0.256447453663769</v>
+        <v>-0.2849837399463402</v>
       </c>
       <c r="AI7">
-        <v>0.7577298228538096</v>
+        <v>0.7703955525319746</v>
       </c>
       <c r="AJ7">
-        <v>-0.6151802809032</v>
+        <v>-0.7312207942320805</v>
       </c>
       <c r="AK7">
-        <v>-2.441849635587668</v>
+        <v>-2.54029940353815</v>
       </c>
       <c r="AL7">
-        <v>-1.80377892824894</v>
+        <v>-1.646490000985853</v>
       </c>
       <c r="AM7">
-        <v>-1.023166154625297</v>
+        <v>0.4093169905058616</v>
       </c>
       <c r="AN7">
-        <v>1.822018625129852</v>
+        <v>1.531132693320519</v>
       </c>
       <c r="AO7">
-        <v>0.1278715764207432</v>
+        <v>0.1005789758423803</v>
       </c>
       <c r="AP7">
-        <v>1.334515</v>
+        <v>1.339045</v>
       </c>
       <c r="AQ7">
-        <v>1.328534843175083</v>
+        <v>1.334764335329399</v>
       </c>
       <c r="AR7">
-        <v>1.342465527843608</v>
+        <v>1.347832446283538</v>
       </c>
       <c r="AS7">
-        <v>1.334515</v>
+        <v>1.339045</v>
       </c>
       <c r="AT7">
-        <v>1.306335</v>
+        <v>1.315395</v>
       </c>
       <c r="AU7">
-        <v>1.328534843175083</v>
+        <v>1.334764335329399</v>
       </c>
       <c r="AV7">
-        <v>1.346165</v>
+        <v>1.350695</v>
       </c>
       <c r="AW7">
-        <v>-0.004481146202865406</v>
+        <v>-0.003196804192989247</v>
       </c>
       <c r="AX7">
-        <v>0.513318182396303</v>
+        <v>0.3674390275194239</v>
       </c>
       <c r="AY7">
-        <v>0.004481146202865406</v>
+        <v>0.003196804192989247</v>
       </c>
       <c r="AZ7">
-        <v>0.4584445388337488</v>
+        <v>0.4513097363286572</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3415554611662512</v>
+        <v>0.3486902636713428</v>
       </c>
       <c r="BC7" t="s">
         <v>132</v>
@@ -2327,43 +2327,43 @@
         <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.008729763247322057</v>
+        <v>0.008700230388075079</v>
       </c>
       <c r="BH7">
-        <v>57275.32188841204</v>
+        <v>57469.74248927041</v>
       </c>
       <c r="BI7">
-        <v>42956.49141630903</v>
+        <v>43102.30686695281</v>
       </c>
       <c r="BJ7">
-        <v>32188.84120171675</v>
+        <v>32188.84120171676</v>
       </c>
       <c r="BK7">
-        <v>429.5649141630903</v>
+        <v>431.0230686695281</v>
       </c>
       <c r="BL7">
-        <v>0.004295649141630903</v>
+        <v>0.00431023068669528</v>
       </c>
       <c r="BM7">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="BN7">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="BO7">
-        <v>0.01339814033893879</v>
+        <v>0.0112339535712858</v>
       </c>
       <c r="BP7">
-        <v>0.01042364378005856</v>
+        <v>0.007682229735743873</v>
       </c>
       <c r="BQ7">
-        <v>0.01197670571143663</v>
+        <v>0.009099993243846579</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT7" t="s">
         <v>138</v>
@@ -2375,7 +2375,7 @@
         <v>140</v>
       </c>
       <c r="BW7" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2383,7 +2383,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2422,7 +2422,7 @@
         <v>28</v>
       </c>
       <c r="O8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P8" t="s">
         <v>99</v>
@@ -2470,13 +2470,13 @@
         <v>111</v>
       </c>
       <c r="AE8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AF8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AH8">
         <v>-0.03722751163714174</v>
@@ -2506,10 +2506,10 @@
         <v>4.7644</v>
       </c>
       <c r="AQ8">
-        <v>4.734844457863074</v>
+        <v>4.734678829967018</v>
       </c>
       <c r="AR8">
-        <v>4.741032800027971</v>
+        <v>4.740945124093886</v>
       </c>
       <c r="AS8">
         <v>4.7644</v>
@@ -2518,28 +2518,28 @@
         <v>4.71173</v>
       </c>
       <c r="AU8">
-        <v>4.734844457863074</v>
+        <v>4.734678829967018</v>
       </c>
       <c r="AV8">
         <v>4.807195</v>
       </c>
       <c r="AW8">
-        <v>-0.006203413260206068</v>
+        <v>-0.00623817690222941</v>
       </c>
       <c r="AX8">
-        <v>0.6906307310883516</v>
+        <v>0.6945009938773692</v>
       </c>
       <c r="AY8">
-        <v>0.006203413260206068</v>
+        <v>0.00623817690222941</v>
       </c>
       <c r="AZ8">
-        <v>0.4293261343989481</v>
+        <v>0.4249453100771195</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3706738656010519</v>
+        <v>0.3750546899228805</v>
       </c>
       <c r="BC8" t="s">
         <v>133</v>
@@ -2578,19 +2578,19 @@
         <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.09641636474626521</v>
+        <v>0.09735801866583019</v>
       </c>
       <c r="BP8">
-        <v>0.02816002974822946</v>
+        <v>0.02686696080771658</v>
       </c>
       <c r="BQ8">
-        <v>0.04860057523681428</v>
+        <v>0.04557881133168997</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT8" t="s">
         <v>138</v>
@@ -2602,7 +2602,7 @@
         <v>140</v>
       </c>
       <c r="BW8" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2610,7 +2610,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2649,7 +2649,7 @@
         <v>3</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P9" t="s">
         <v>98</v>
@@ -2673,7 +2673,7 @@
         <v>94</v>
       </c>
       <c r="W9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X9">
         <v>0.9999771110475011</v>
@@ -2697,13 +2697,13 @@
         <v>94</v>
       </c>
       <c r="AE9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AH9">
         <v>-0.4639668591170661</v>
@@ -2733,10 +2733,10 @@
         <v>7.6885</v>
       </c>
       <c r="AQ9">
-        <v>7.635252006639986</v>
+        <v>7.635383874457526</v>
       </c>
       <c r="AR9">
-        <v>7.711677210042067</v>
+        <v>7.71137845410894</v>
       </c>
       <c r="AS9">
         <v>7.6885</v>
@@ -2745,28 +2745,28 @@
         <v>7.5296</v>
       </c>
       <c r="AU9">
-        <v>7.635252006639986</v>
+        <v>7.635383874457526</v>
       </c>
       <c r="AV9">
         <v>7.738175000000001</v>
       </c>
       <c r="AW9">
-        <v>-0.006925667342136244</v>
+        <v>-0.006908516035959466</v>
       </c>
       <c r="AX9">
-        <v>1.07192739526953</v>
+        <v>1.069272783945118</v>
       </c>
       <c r="AY9">
-        <v>0.006925667342136244</v>
+        <v>0.006908516035959466</v>
       </c>
       <c r="AZ9">
-        <v>0.4057180282085678</v>
+        <v>0.4071102640865034</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3942819717914322</v>
+        <v>0.3928897359134966</v>
       </c>
       <c r="BC9" t="s">
         <v>134</v>
@@ -2805,19 +2805,19 @@
         <v>0.003848702089785736</v>
       </c>
       <c r="BO9">
-        <v>0.1366404359942915</v>
+        <v>0.1336838121244475</v>
       </c>
       <c r="BP9">
-        <v>0.05357706800275999</v>
+        <v>0.05235804556986372</v>
       </c>
       <c r="BQ9">
-        <v>0.05796994776484156</v>
+        <v>0.05760459172660702</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT9" t="s">
         <v>138</v>
@@ -2829,7 +2829,7 @@
         <v>140</v>
       </c>
       <c r="BW9" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2837,7 +2837,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2876,7 +2876,7 @@
         <v>7</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P10" t="s">
         <v>98</v>
@@ -2900,7 +2900,7 @@
         <v>94</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X10">
         <v>0.9999844836116794</v>
@@ -2924,13 +2924,13 @@
         <v>94</v>
       </c>
       <c r="AE10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AH10">
         <v>-0.5424956918553514</v>
@@ -2960,10 +2960,10 @@
         <v>8.965809999999999</v>
       </c>
       <c r="AQ10">
-        <v>8.901719650525836</v>
+        <v>8.901450099842762</v>
       </c>
       <c r="AR10">
-        <v>9.000936870462997</v>
+        <v>9.000670851267415</v>
       </c>
       <c r="AS10">
         <v>8.965809999999999</v>
@@ -2972,28 +2972,28 @@
         <v>8.771199999999999</v>
       </c>
       <c r="AU10">
-        <v>8.901719650525836</v>
+        <v>8.901450099842762</v>
       </c>
       <c r="AV10">
         <v>9.046877499999999</v>
       </c>
       <c r="AW10">
-        <v>-0.007148305560140533</v>
+        <v>-0.007178369846922615</v>
       </c>
       <c r="AX10">
-        <v>0.7905800656756843</v>
+        <v>0.793905081040333</v>
       </c>
       <c r="AY10">
-        <v>0.007148305560140533</v>
+        <v>0.007178369846922615</v>
       </c>
       <c r="AZ10">
-        <v>0.3987067915621768</v>
+        <v>0.3979943393173396</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.4012932084378233</v>
+        <v>0.4020056606826605</v>
       </c>
       <c r="BC10" t="s">
         <v>135</v>
@@ -3032,19 +3032,19 @@
         <v>0.004745161992159566</v>
       </c>
       <c r="BO10">
-        <v>0.1484031022727679</v>
+        <v>0.1526783475810659</v>
       </c>
       <c r="BP10">
-        <v>0.05880028035087533</v>
+        <v>0.05772225361712255</v>
       </c>
       <c r="BQ10">
-        <v>0.05830081718320743</v>
+        <v>0.0585421692784223</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT10" t="s">
         <v>138</v>
@@ -3056,7 +3056,7 @@
         <v>140</v>
       </c>
       <c r="BW10" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3064,7 +3064,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3088,22 +3088,22 @@
         <v>94</v>
       </c>
       <c r="J11" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.7772118913444507</v>
+        <v>1.000167377653249</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P11" t="s">
         <v>98</v>
@@ -3118,109 +3118,109 @@
         <v>109</v>
       </c>
       <c r="T11">
-        <v>-0.5121842826309468</v>
+        <v>-0.5386034294224616</v>
       </c>
       <c r="U11">
-        <v>0.6304485710096058</v>
+        <v>0.6423493220989157</v>
       </c>
       <c r="V11" t="s">
         <v>94</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X11">
-        <v>0.999862575302719</v>
+        <v>0.9999111154352319</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-100.5365903501272</v>
+        <v>-103.1283415028481</v>
       </c>
       <c r="AA11">
-        <v>-13.99999999999999</v>
+        <v>-11</v>
       </c>
       <c r="AB11">
-        <v>-0.1828634165865115</v>
+        <v>-0.2271330593743433</v>
       </c>
       <c r="AC11">
-        <v>-0.9831383274363318</v>
+        <v>-0.9738637344820121</v>
       </c>
       <c r="AD11" t="s">
         <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AH11">
-        <v>-0.1828382866368433</v>
+        <v>-0.2271128707512164</v>
       </c>
       <c r="AI11">
-        <v>0.7300549854365139</v>
+        <v>0.7491375611531098</v>
       </c>
       <c r="AJ11">
-        <v>-0.4403540916387163</v>
+        <v>-0.622650177525401</v>
       </c>
       <c r="AK11">
-        <v>-2.713880578029307</v>
+        <v>-2.933263767620166</v>
       </c>
       <c r="AL11">
-        <v>-1.842430185426691</v>
+        <v>-1.853504669552984</v>
       </c>
       <c r="AM11">
-        <v>-1.588397178922474</v>
+        <v>-0.2526973252355096</v>
       </c>
       <c r="AN11">
-        <v>1.886683180913546</v>
+        <v>1.770934123438676</v>
       </c>
       <c r="AO11">
-        <v>0.1650396059692746</v>
+        <v>0.1264749804101626</v>
       </c>
       <c r="AP11">
-        <v>1.146005</v>
+        <v>1.148535</v>
       </c>
       <c r="AQ11">
-        <v>1.122807662760497</v>
+        <v>1.126706762882134</v>
       </c>
       <c r="AR11">
-        <v>1.110136540588327</v>
+        <v>1.113443311146264</v>
       </c>
       <c r="AS11">
-        <v>1.146005</v>
+        <v>1.148535</v>
       </c>
       <c r="AT11">
-        <v>1.124515</v>
+        <v>1.129575</v>
       </c>
       <c r="AU11">
-        <v>1.122807662760497</v>
+        <v>1.126706762882134</v>
       </c>
       <c r="AV11">
-        <v>1.161469891493002</v>
+        <v>1.163087158078578</v>
       </c>
       <c r="AW11">
-        <v>-0.02024191625647649</v>
+        <v>-0.01900528683746354</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.02024191625647649</v>
+        <v>0.01900528683746354</v>
       </c>
       <c r="AZ11">
-        <v>0.4176620782215197</v>
+        <v>0.4128666984748956</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3823379217784803</v>
+        <v>0.3871333015251043</v>
       </c>
       <c r="BC11" t="s">
         <v>136</v>
@@ -3235,22 +3235,22 @@
         <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.013494610837651</v>
+        <v>0.01267019122497569</v>
       </c>
       <c r="BH11">
-        <v>37051.82802344783</v>
+        <v>39462.70353160824</v>
       </c>
       <c r="BI11">
-        <v>27788.87101758587</v>
+        <v>29597.02764870618</v>
       </c>
       <c r="BJ11">
-        <v>24248.47275324791</v>
+        <v>25769.37372279136</v>
       </c>
       <c r="BK11">
-        <v>277.8887101758587</v>
+        <v>295.9702764870618</v>
       </c>
       <c r="BL11">
-        <v>0.002778887101758587</v>
+        <v>0.002959702764870618</v>
       </c>
       <c r="BM11">
         <v>375</v>
@@ -3259,19 +3259,19 @@
         <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>0.02350406743712772</v>
+        <v>0.02186794851788672</v>
       </c>
       <c r="BP11">
-        <v>0.008205487520676506</v>
+        <v>0.006584927501496216</v>
       </c>
       <c r="BQ11">
-        <v>0.01100111553355954</v>
+        <v>0.009172553563114066</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04858241297563112</v>
+        <v>0.04969274973812191</v>
       </c>
       <c r="BT11" t="s">
         <v>138</v>
@@ -3283,7 +3283,7 @@
         <v>140</v>
       </c>
       <c r="BW11" s="2">
-        <v>46312</v>
+        <v>46314</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -241,15 +241,15 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
@@ -262,27 +262,27 @@
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
@@ -295,19 +295,19 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
+    <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>ALIGNED</t>
-  </si>
-  <si>
-    <t>BLOCK_STRONG_CONFLICT</t>
+    <t>NO_SIGNAL</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -316,30 +316,30 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>多头减速</t>
+  </si>
+  <si>
     <t>多头加速</t>
   </si>
   <si>
-    <t>多头减速</t>
-  </si>
-  <si>
-    <t>空头减速</t>
-  </si>
-  <si>
     <t>空头稳态</t>
   </si>
   <si>
@@ -352,24 +352,24 @@
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>下跌</t>
+  </si>
+  <si>
     <t>上涨</t>
   </si>
   <si>
-    <t>下跌</t>
-  </si>
-  <si>
     <t>转换</t>
   </si>
   <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
-  </si>
-  <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
@@ -379,15 +379,15 @@
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>下降谷底收敛</t>
-  </si>
-  <si>
     <t>下降坡延续</t>
   </si>
   <si>
@@ -397,34 +397,34 @@
     <t>地形转换区</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.007419,naive=0.003997,drift4=0.005587; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=291.8,naive=25.94,drift4=76.28; naive_cap_applied; model_divergence_guard(abs=662,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=4.456,naive=1.876,drift4=3.835; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01414,naive=0.002597,drift4=0.006469; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02845,naive=0.006386,drift4=0.009433; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01123,naive=0.007682,drift4=0.0091; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.09736,naive=0.02687,drift4=0.04558; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1337,naive=0.05236,drift4=0.0576; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1527,naive=0.05772,drift4=0.05854; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02187,naive=0.006585,drift4=0.009173; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=4.039,naive=1.791,drift4=4.119; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=305.2,naive=34.96,drift4=63.31; naive_cap_applied; model_divergence_guard(abs=539.1,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01576,naive=0.003151,drift4=0.007918; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01103,naive=0.002702,drift4=0.006164; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03364,naive=0.005506,drift4=0.01288; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01501,naive=0.008033,drift4=0.009993; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0815,naive=0.02459,drift4=0.04367; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1537,naive=0.06071,drift4=0.06733; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02189,naive=0.006656,drift4=0.009643; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1543,naive=0.05371,drift4=0.0635; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1033,7 +1033,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1051,28 +1051,28 @@
         <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>2.204458390183103</v>
+        <v>0.9655620847251117</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="O2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
         <v>97</v>
@@ -1087,34 +1087,34 @@
         <v>105</v>
       </c>
       <c r="T2">
-        <v>0.8401908892389828</v>
+        <v>-0.7109343538734294</v>
       </c>
       <c r="U2">
-        <v>0.9280799837310828</v>
+        <v>0.7197202381217118</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
       </c>
       <c r="W2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9999763342941623</v>
+        <v>0.9991991155146743</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0.6144610582570272</v>
       </c>
       <c r="Z2">
-        <v>47.12681191947653</v>
+        <v>116.7666666385041</v>
       </c>
       <c r="AA2">
-        <v>-11</v>
+        <v>-28</v>
       </c>
       <c r="AB2">
-        <v>0.6803779963930544</v>
+        <v>-0.4503581785973821</v>
       </c>
       <c r="AC2">
-        <v>0.7328613661697366</v>
+        <v>0.8928479775249807</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1129,58 +1129,58 @@
         <v>121</v>
       </c>
       <c r="AH2">
-        <v>0.6803618947675334</v>
+        <v>-0.3632517149615387</v>
       </c>
       <c r="AI2">
-        <v>0.8959369865154437</v>
+        <v>0.7497097212193088</v>
       </c>
       <c r="AJ2">
-        <v>1.60140670467573</v>
+        <v>-0.8754817607296135</v>
       </c>
       <c r="AK2">
-        <v>1.799634869832472</v>
+        <v>1.554069485227286</v>
       </c>
       <c r="AL2">
-        <v>3.088340235516783</v>
+        <v>-0.5886128695847785</v>
       </c>
       <c r="AM2">
-        <v>-2.258449850764255</v>
+        <v>3.189245913176564</v>
       </c>
       <c r="AN2">
-        <v>2.806959672095708</v>
+        <v>0.5463548806730636</v>
       </c>
       <c r="AO2">
-        <v>0.05445419603619626</v>
+        <v>0.05339756294298168</v>
       </c>
       <c r="AP2">
-        <v>0.82211</v>
+        <v>157.1105</v>
       </c>
       <c r="AQ2">
-        <v>0.8212087303337301</v>
+        <v>157.2010186173688</v>
       </c>
       <c r="AR2">
-        <v>0.8041434384556025</v>
+        <v>159.3054585008209</v>
       </c>
       <c r="AS2">
-        <v>0.82211</v>
+        <v>157.1105</v>
       </c>
       <c r="AT2">
-        <v>0.8425050000000001</v>
+        <v>154.1445</v>
       </c>
       <c r="AW2">
-        <v>-0.001096288411854752</v>
+        <v>0.0005761461988141254</v>
       </c>
       <c r="AY2">
-        <v>0.001096288411854752</v>
+        <v>0.0005761461988141254</v>
       </c>
       <c r="AZ2">
-        <v>0.448815662687341</v>
+        <v>0.4772986678689559</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3511843373126591</v>
+        <v>0.3227013321310441</v>
       </c>
       <c r="BC2" t="s">
         <v>127</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.007418921024817762</v>
+        <v>4.038634026021696</v>
       </c>
       <c r="BP2">
-        <v>0.003996946251392814</v>
+        <v>1.790667288627491</v>
       </c>
       <c r="BQ2">
-        <v>0.005586992505074495</v>
+        <v>4.119102819322602</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT2" t="s">
         <v>137</v>
@@ -1240,7 +1240,7 @@
         <v>139</v>
       </c>
       <c r="BW2" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1248,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1260,7 +1260,7 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
         <v>91</v>
@@ -1269,25 +1269,25 @@
         <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.1315860881573243</v>
+        <v>0.01093802734210199</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P3" t="s">
         <v>98</v>
@@ -1302,40 +1302,40 @@
         <v>106</v>
       </c>
       <c r="T3">
-        <v>0.8263005543277491</v>
+        <v>0.8747428227636473</v>
       </c>
       <c r="U3">
-        <v>0.7633635218447925</v>
+        <v>0.7044609170831502</v>
       </c>
       <c r="V3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9661130895892217</v>
+        <v>0.8433065873580352</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>-61.34341222524586</v>
+        <v>-50.63457834155941</v>
       </c>
       <c r="AA3">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="AB3">
-        <v>0.4795587580597446</v>
+        <v>0.6342640483614705</v>
       </c>
       <c r="AC3">
-        <v>-0.8775097706397321</v>
+        <v>-0.7731164963678618</v>
       </c>
       <c r="AD3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF3" t="s">
         <v>116</v>
@@ -1344,58 +1344,58 @@
         <v>122</v>
       </c>
       <c r="AH3">
-        <v>0.231653996694335</v>
+        <v>0.2674395250538018</v>
       </c>
       <c r="AI3">
-        <v>0.6198718889289074</v>
+        <v>0.6070657455659292</v>
       </c>
       <c r="AJ3">
-        <v>0.1653357313260205</v>
+        <v>0.0627906675128186</v>
       </c>
       <c r="AK3">
-        <v>-0.6024835080623392</v>
+        <v>-0.3385811013406831</v>
       </c>
       <c r="AL3">
-        <v>0.08968126878286138</v>
+        <v>-0.1469459846318279</v>
       </c>
       <c r="AM3">
-        <v>0.09596656650477405</v>
+        <v>-0.2679331550601287</v>
       </c>
       <c r="AN3">
-        <v>0.1290642195994172</v>
+        <v>0.151127139077636</v>
       </c>
       <c r="AO3">
-        <v>0.08090213230162374</v>
+        <v>0.189138496785495</v>
       </c>
       <c r="AP3">
-        <v>4380.92</v>
+        <v>4323.049999999999</v>
       </c>
       <c r="AQ3">
-        <v>4454.513880473512</v>
+        <v>4410.992589082751</v>
       </c>
       <c r="AR3">
-        <v>4929.299601578374</v>
+        <v>4795.085296942508</v>
       </c>
       <c r="AS3">
-        <v>4380.92</v>
+        <v>4323.049999999999</v>
       </c>
       <c r="AT3">
-        <v>4153.620000000001</v>
+        <v>4188.879999999998</v>
       </c>
       <c r="AU3">
-        <v>4454.513880473512</v>
+        <v>4410.992589082751</v>
       </c>
       <c r="AV3">
-        <v>4247.2825</v>
+        <v>4189.412499999999</v>
       </c>
       <c r="AW3">
-        <v>0.01679872731606886</v>
+        <v>0.02034271847023549</v>
       </c>
       <c r="AX3">
-        <v>0.5506978241400229</v>
+        <v>0.6580682000392959</v>
       </c>
       <c r="AY3">
-        <v>0.01679872731606886</v>
+        <v>0.02034271847023549</v>
       </c>
       <c r="AZ3">
         <v>0.3</v>
@@ -1419,43 +1419,43 @@
         <v>375</v>
       </c>
       <c r="BG3">
-        <v>0.03050443742410273</v>
+        <v>0.03091278148529399</v>
       </c>
       <c r="BH3">
-        <v>16391.05789916751</v>
+        <v>16174.53933214851</v>
       </c>
       <c r="BI3">
-        <v>12293.29342437563</v>
+        <v>12130.90449911138</v>
       </c>
       <c r="BJ3">
         <v>2.806098587597041</v>
       </c>
       <c r="BK3">
-        <v>122.9329342437563</v>
+        <v>121.3090449911138</v>
       </c>
       <c r="BL3">
-        <v>0.001229329342437563</v>
+        <v>0.001213090449911138</v>
       </c>
       <c r="BM3">
-        <v>375</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN3">
-        <v>0.00375</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO3">
-        <v>291.817262661377</v>
+        <v>305.1584185642193</v>
       </c>
       <c r="BP3">
-        <v>25.94410124064647</v>
+        <v>34.95586911447518</v>
       </c>
       <c r="BQ3">
-        <v>76.28207155433719</v>
+        <v>63.31322884344615</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT3" t="s">
         <v>138</v>
@@ -1467,7 +1467,7 @@
         <v>140</v>
       </c>
       <c r="BW3" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1475,7 +1475,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1487,7 +1487,7 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
@@ -1499,25 +1499,25 @@
         <v>94</v>
       </c>
       <c r="J4" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>1.129510121686975</v>
+        <v>2.05651322737015</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1529,34 +1529,34 @@
         <v>107</v>
       </c>
       <c r="T4">
-        <v>-0.7604381919198788</v>
+        <v>0.8988917203478006</v>
       </c>
       <c r="U4">
-        <v>0.7418676067757343</v>
+        <v>0.9544023477634401</v>
       </c>
       <c r="V4" t="s">
         <v>94</v>
       </c>
       <c r="W4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9986816816471552</v>
+        <v>0.9996042944277196</v>
       </c>
       <c r="Y4">
-        <v>0.5832446989296391</v>
+        <v>1</v>
       </c>
       <c r="Z4">
-        <v>122.5722102741784</v>
+        <v>37.08484846736302</v>
       </c>
       <c r="AA4">
-        <v>-37</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AB4">
-        <v>-0.538362113524273</v>
+        <v>0.7977434157478444</v>
       </c>
       <c r="AC4">
-        <v>0.8427136137037765</v>
+        <v>0.6029970502672148</v>
       </c>
       <c r="AD4" t="s">
         <v>94</v>
@@ -1571,67 +1571,67 @@
         <v>123</v>
       </c>
       <c r="AH4">
-        <v>-0.4256176409392974</v>
+        <v>0.7974277442329829</v>
       </c>
       <c r="AI4">
-        <v>0.7710242745176157</v>
+        <v>0.9327697977437558</v>
       </c>
       <c r="AJ4">
-        <v>-1.012783771105633</v>
+        <v>1.553909865259229</v>
       </c>
       <c r="AK4">
-        <v>1.41591866015502</v>
+        <v>1.303144291215953</v>
       </c>
       <c r="AL4">
-        <v>-0.7463860614320315</v>
+        <v>2.634002089849427</v>
       </c>
       <c r="AM4">
-        <v>3.819793183395782</v>
+        <v>-3.278751439118282</v>
       </c>
       <c r="AN4">
-        <v>0.6643473352406452</v>
+        <v>2.277861118416645</v>
       </c>
       <c r="AO4">
-        <v>0.04447925268065549</v>
+        <v>0.04276486686866134</v>
       </c>
       <c r="AP4">
-        <v>156.87</v>
+        <v>0.8189949999999999</v>
       </c>
       <c r="AQ4">
-        <v>157.613335761856</v>
+        <v>0.8232367053758801</v>
       </c>
       <c r="AR4">
-        <v>160.0157751104429</v>
+        <v>0.8204808100574377</v>
       </c>
       <c r="AS4">
-        <v>156.87</v>
+        <v>0.8189949999999999</v>
       </c>
       <c r="AT4">
-        <v>154.7285</v>
+        <v>0.8289899999999999</v>
       </c>
       <c r="AU4">
-        <v>157.613335761856</v>
+        <v>0.8232367053758801</v>
       </c>
       <c r="AV4">
-        <v>155.371875</v>
+        <v>0.811415</v>
       </c>
       <c r="AW4">
-        <v>0.004738546324064345</v>
+        <v>0.005179159061874859</v>
       </c>
       <c r="AX4">
-        <v>0.4961773963160391</v>
+        <v>0.5595917382427764</v>
       </c>
       <c r="AY4">
-        <v>0.004738546324064345</v>
+        <v>0.005179159061874859</v>
       </c>
       <c r="AZ4">
-        <v>0.4646128129410264</v>
+        <v>0.4412047033221271</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3353871870589737</v>
+        <v>0.3587952966778729</v>
       </c>
       <c r="BC4" t="s">
         <v>129</v>
@@ -1646,22 +1646,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.009550105182635405</v>
+        <v>0.009255245758521017</v>
       </c>
       <c r="BH4">
-        <v>52355.44430538117</v>
+        <v>54023.4168865441</v>
       </c>
       <c r="BI4">
-        <v>52355.44430538117</v>
+        <v>54023.4168865441</v>
       </c>
       <c r="BJ4">
-        <v>333.7505214851863</v>
+        <v>65963.06068601653</v>
       </c>
       <c r="BK4">
-        <v>523.5544430538117</v>
+        <v>540.234168865441</v>
       </c>
       <c r="BL4">
-        <v>0.005235544430538117</v>
+        <v>0.00540234168865441</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1670,19 +1670,19 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>4.456351763382687</v>
+        <v>0.01575794787707602</v>
       </c>
       <c r="BP4">
-        <v>1.876082400225948</v>
+        <v>0.003150743528682279</v>
       </c>
       <c r="BQ4">
-        <v>3.834702388521879</v>
+        <v>0.007918107439097462</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT4" t="s">
         <v>138</v>
@@ -1694,7 +1694,7 @@
         <v>140</v>
       </c>
       <c r="BW4" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1702,7 +1702,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1723,25 +1723,25 @@
         <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.6714888821016466</v>
+        <v>0.4181638738972803</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P5" t="s">
         <v>99</v>
@@ -1756,40 +1756,40 @@
         <v>106</v>
       </c>
       <c r="T5">
-        <v>0.5721566250061204</v>
+        <v>0.5558378967449604</v>
       </c>
       <c r="U5">
-        <v>0.6574023218762785</v>
+        <v>0.6500641347383993</v>
       </c>
       <c r="V5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9997273624940969</v>
+        <v>0.9997483248126688</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-73.54372225878554</v>
+        <v>-75.16993758728142</v>
       </c>
       <c r="AA5">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="AB5">
-        <v>0.2832835892612633</v>
+        <v>0.2559530034611136</v>
       </c>
       <c r="AC5">
-        <v>-0.9590361870415818</v>
+        <v>-0.9666892261834903</v>
       </c>
       <c r="AD5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AF5" t="s">
         <v>116</v>
@@ -1798,67 +1798,67 @@
         <v>122</v>
       </c>
       <c r="AH5">
-        <v>0.2832063555300239</v>
+        <v>0.2558885864410196</v>
       </c>
       <c r="AI5">
-        <v>0.7731312137537724</v>
+        <v>0.7628201312597849</v>
       </c>
       <c r="AJ5">
-        <v>0.7340186446384928</v>
+        <v>0.5644088449907517</v>
       </c>
       <c r="AK5">
-        <v>-2.281072888774191</v>
+        <v>-1.955200417359916</v>
       </c>
       <c r="AL5">
-        <v>0.405411182059805</v>
+        <v>0.238370532503597</v>
       </c>
       <c r="AM5">
-        <v>-2.033462601656284</v>
+        <v>-1.590173488013066</v>
       </c>
       <c r="AN5">
-        <v>0.3800632544046766</v>
+        <v>0.2705967320131298</v>
       </c>
       <c r="AO5">
-        <v>0.07838959931693661</v>
+        <v>0.09251788975322217</v>
       </c>
       <c r="AP5">
-        <v>0.712555</v>
+        <v>0.711165</v>
       </c>
       <c r="AQ5">
-        <v>0.711560469940694</v>
+        <v>0.7100532994112216</v>
       </c>
       <c r="AR5">
-        <v>0.7130789806241633</v>
+        <v>0.7122287991984426</v>
       </c>
       <c r="AS5">
-        <v>0.712555</v>
+        <v>0.711165</v>
       </c>
       <c r="AT5">
-        <v>0.7091850000000002</v>
+        <v>0.7067300000000001</v>
       </c>
       <c r="AU5">
-        <v>0.7114861675</v>
+        <v>0.7100532994112216</v>
       </c>
       <c r="AV5">
-        <v>0.71976375</v>
+        <v>0.7169650000000001</v>
       </c>
       <c r="AW5">
-        <v>-0.001395723922091703</v>
+        <v>-0.001563210490924621</v>
       </c>
       <c r="AX5">
-        <v>0.1482687705912968</v>
+        <v>0.1916725153066212</v>
       </c>
       <c r="AY5">
-        <v>0.001395723922091703</v>
+        <v>0.001563210490924621</v>
       </c>
       <c r="AZ5">
-        <v>0.4369487434364187</v>
+        <v>0.4430602615770424</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3630512565635813</v>
+        <v>0.3569397384229576</v>
       </c>
       <c r="BC5" t="s">
         <v>130</v>
@@ -1873,22 +1873,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.01011676291654669</v>
+        <v>0.008155631956015871</v>
       </c>
       <c r="BH5">
-        <v>49422.92353043225</v>
+        <v>61307.32758620661</v>
       </c>
       <c r="BI5">
-        <v>49422.92353043225</v>
+        <v>61307.32758620661</v>
       </c>
       <c r="BJ5">
-        <v>69360.15259233638</v>
+        <v>86206.89655172374</v>
       </c>
       <c r="BK5">
-        <v>494.2292353043225</v>
+        <v>613.0732758620661</v>
       </c>
       <c r="BL5">
-        <v>0.004942292353043225</v>
+        <v>0.006130732758620661</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1897,19 +1897,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.01413791946286085</v>
+        <v>0.01102501651430631</v>
       </c>
       <c r="BP5">
-        <v>0.002596815505138828</v>
+        <v>0.002701688092989758</v>
       </c>
       <c r="BQ5">
-        <v>0.006468556960569494</v>
+        <v>0.006164112042829227</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT5" t="s">
         <v>138</v>
@@ -1921,7 +1921,7 @@
         <v>140</v>
       </c>
       <c r="BW5" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1929,7 +1929,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1950,31 +1950,31 @@
         <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0.8246640972210072</v>
       </c>
       <c r="L6">
-        <v>3.810434383610249</v>
+        <v>3.528177455506283</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
         <v>98</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.9561660243052518</v>
       </c>
       <c r="R6" t="s">
         <v>103</v>
@@ -1983,40 +1983,40 @@
         <v>108</v>
       </c>
       <c r="T6">
-        <v>-0.9994010773607538</v>
+        <v>-0.998965934647524</v>
       </c>
       <c r="U6">
-        <v>0.9997053321694902</v>
+        <v>0.9731981751687198</v>
       </c>
       <c r="V6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9998993894286041</v>
+        <v>0.9998555599767319</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>0.9928258762532932</v>
       </c>
       <c r="Z6">
-        <v>177.1952621162782</v>
+        <v>-176.3631016843742</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="AB6">
-        <v>-0.9988020944574952</v>
+        <v>-0.9979860845618934</v>
       </c>
       <c r="AC6">
-        <v>0.0489323625765286</v>
+        <v>-0.06343323277920872</v>
       </c>
       <c r="AD6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF6" t="s">
         <v>118</v>
@@ -2025,67 +2025,67 @@
         <v>124</v>
       </c>
       <c r="AH6">
-        <v>-0.9987016044080604</v>
+        <v>-0.994262614666409</v>
       </c>
       <c r="AI6">
-        <v>0.9941049421684818</v>
+        <v>0.9925208284367179</v>
       </c>
       <c r="AJ6">
-        <v>-2.852760448391738</v>
+        <v>-2.651323782891174</v>
       </c>
       <c r="AK6">
-        <v>0.1928992565970481</v>
+        <v>-0.1048145629032953</v>
       </c>
       <c r="AL6">
-        <v>-4.923376570422746</v>
+        <v>-4.52315797129816</v>
       </c>
       <c r="AM6">
-        <v>3.583576937470743</v>
+        <v>3.65213557072818</v>
       </c>
       <c r="AN6">
-        <v>4.603722682386502</v>
+        <v>4.189749352804028</v>
       </c>
       <c r="AO6">
-        <v>0.03666981645852199</v>
+        <v>0.03593078782909975</v>
       </c>
       <c r="AP6">
-        <v>6.696575</v>
+        <v>6.69862</v>
       </c>
       <c r="AQ6">
-        <v>6.677913127374381</v>
+        <v>6.680820535554128</v>
       </c>
       <c r="AR6">
-        <v>6.674129200139214</v>
+        <v>6.685390072392268</v>
       </c>
       <c r="AS6">
-        <v>6.696575</v>
+        <v>6.69862</v>
       </c>
       <c r="AT6">
-        <v>6.672349999999999</v>
+        <v>6.666015</v>
       </c>
       <c r="AU6">
-        <v>6.677913127374381</v>
+        <v>6.680820535554128</v>
       </c>
       <c r="AV6">
-        <v>6.72008125</v>
+        <v>6.72212625</v>
       </c>
       <c r="AW6">
-        <v>-0.002786778707864779</v>
+        <v>-0.002657183784999314</v>
       </c>
       <c r="AX6">
-        <v>0.7939110928208406</v>
+        <v>0.7572226299759593</v>
       </c>
       <c r="AY6">
-        <v>0.002786778707864779</v>
+        <v>0.002657183784999314</v>
       </c>
       <c r="AZ6">
-        <v>0.4036237175087319</v>
+        <v>0.4275873341992818</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3963762824912681</v>
+        <v>0.3724126658007182</v>
       </c>
       <c r="BC6" t="s">
         <v>131</v>
@@ -2097,46 +2097,46 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>500</v>
+        <v>478.0830121526259</v>
       </c>
       <c r="BG6">
-        <v>0.003510189910513899</v>
+        <v>0.00350911829600718</v>
       </c>
       <c r="BH6">
-        <v>142442.4355224698</v>
+        <v>142485.9345918662</v>
       </c>
       <c r="BI6">
-        <v>142442.4355224698</v>
+        <v>136240.2095981228</v>
       </c>
       <c r="BJ6">
-        <v>21270.9385801652</v>
+        <v>20338.54877543775</v>
       </c>
       <c r="BK6">
-        <v>1424.424355224698</v>
+        <v>1362.402095981228</v>
       </c>
       <c r="BL6">
-        <v>0.01424424355224698</v>
+        <v>0.01362402095981228</v>
       </c>
       <c r="BM6">
-        <v>500</v>
+        <v>478.0830121526259</v>
       </c>
       <c r="BN6">
-        <v>0.005</v>
+        <v>0.004780830121526258</v>
       </c>
       <c r="BO6">
-        <v>0.0284522153009786</v>
+        <v>0.03363824918266327</v>
       </c>
       <c r="BP6">
-        <v>0.006385723239760613</v>
+        <v>0.005506382826467952</v>
       </c>
       <c r="BQ6">
-        <v>0.009432605409580814</v>
+        <v>0.01288254832241725</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT6" t="s">
         <v>138</v>
@@ -2148,7 +2148,7 @@
         <v>140</v>
       </c>
       <c r="BW6" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2156,7 +2156,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2168,7 +2168,7 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
         <v>92</v>
@@ -2177,31 +2177,31 @@
         <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.1910502009538229</v>
       </c>
       <c r="L7">
-        <v>1.061797745320032</v>
+        <v>1.251921697359182</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
         <v>98</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>0.7977625502384558</v>
       </c>
       <c r="R7" t="s">
         <v>104</v>
@@ -2210,40 +2210,40 @@
         <v>109</v>
       </c>
       <c r="T7">
-        <v>-0.5731410801839203</v>
+        <v>-0.6225277707030407</v>
       </c>
       <c r="U7">
-        <v>0.6579014605262827</v>
+        <v>0.7087856933245674</v>
       </c>
       <c r="V7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9999518977740743</v>
+        <v>0.9999626654605028</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-106.558696098558</v>
+        <v>-110.1382093721169</v>
       </c>
       <c r="AA7">
         <v>-4.999999999999995</v>
       </c>
       <c r="AB7">
-        <v>-0.2849974489580183</v>
+        <v>-0.3442858806847173</v>
       </c>
       <c r="AC7">
-        <v>-0.9585282750589165</v>
+        <v>-0.9388648637376673</v>
       </c>
       <c r="AD7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF7" t="s">
         <v>119</v>
@@ -2252,67 +2252,67 @@
         <v>125</v>
       </c>
       <c r="AH7">
-        <v>-0.2849837399463402</v>
+        <v>-0.3442730269299066</v>
       </c>
       <c r="AI7">
-        <v>0.7703955525319746</v>
+        <v>0.7910621921093854</v>
       </c>
       <c r="AJ7">
-        <v>-0.7312207942320805</v>
+        <v>-0.9019855763860494</v>
       </c>
       <c r="AK7">
-        <v>-2.54029940353815</v>
+        <v>-2.533901608832344</v>
       </c>
       <c r="AL7">
-        <v>-1.646490000985853</v>
+        <v>-1.772215587384921</v>
       </c>
       <c r="AM7">
-        <v>0.4093169905058616</v>
+        <v>1.10061735100406</v>
       </c>
       <c r="AN7">
-        <v>1.531132693320519</v>
+        <v>1.599572967380154</v>
       </c>
       <c r="AO7">
-        <v>0.1005789758423803</v>
+        <v>0.08140336671470533</v>
       </c>
       <c r="AP7">
-        <v>1.339045</v>
+        <v>1.33622</v>
       </c>
       <c r="AQ7">
-        <v>1.334764335329399</v>
+        <v>1.331247259914613</v>
       </c>
       <c r="AR7">
-        <v>1.347832446283538</v>
+        <v>1.339103574728014</v>
       </c>
       <c r="AS7">
-        <v>1.339045</v>
+        <v>1.33622</v>
       </c>
       <c r="AT7">
-        <v>1.315395</v>
+        <v>1.318995</v>
       </c>
       <c r="AU7">
-        <v>1.334764335329399</v>
+        <v>1.331247259914613</v>
       </c>
       <c r="AV7">
-        <v>1.350695</v>
+        <v>1.34787</v>
       </c>
       <c r="AW7">
-        <v>-0.003196804192989247</v>
+        <v>-0.003721498020825459</v>
       </c>
       <c r="AX7">
-        <v>0.3674390275194239</v>
+        <v>0.4268446425225234</v>
       </c>
       <c r="AY7">
-        <v>0.003196804192989247</v>
+        <v>0.003721498020825459</v>
       </c>
       <c r="AZ7">
-        <v>0.4513097363286572</v>
+        <v>0.4379852890490062</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3486902636713428</v>
+        <v>0.3620147109509938</v>
       </c>
       <c r="BC7" t="s">
         <v>132</v>
@@ -2324,46 +2324,46 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>375</v>
+        <v>398.8812751192279</v>
       </c>
       <c r="BG7">
-        <v>0.008700230388075079</v>
+        <v>0.008718624178653211</v>
       </c>
       <c r="BH7">
-        <v>57469.74248927041</v>
+        <v>57348.49785407728</v>
       </c>
       <c r="BI7">
-        <v>43102.30686695281</v>
+        <v>45750.4839004133</v>
       </c>
       <c r="BJ7">
-        <v>32188.84120171676</v>
+        <v>34238.73606173632</v>
       </c>
       <c r="BK7">
-        <v>431.0230686695281</v>
+        <v>457.504839004133</v>
       </c>
       <c r="BL7">
-        <v>0.00431023068669528</v>
+        <v>0.00457504839004133</v>
       </c>
       <c r="BM7">
-        <v>375</v>
+        <v>398.8812751192278</v>
       </c>
       <c r="BN7">
-        <v>0.00375</v>
+        <v>0.003988812751192278</v>
       </c>
       <c r="BO7">
-        <v>0.0112339535712858</v>
+        <v>0.01501276607022105</v>
       </c>
       <c r="BP7">
-        <v>0.007682229735743873</v>
+        <v>0.008032774085598299</v>
       </c>
       <c r="BQ7">
-        <v>0.009099993243846579</v>
+        <v>0.009992883116811912</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT7" t="s">
         <v>138</v>
@@ -2375,7 +2375,7 @@
         <v>140</v>
       </c>
       <c r="BW7" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2383,7 +2383,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2395,7 +2395,7 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
         <v>92</v>
@@ -2404,25 +2404,25 @@
         <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J8" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.08554759762750143</v>
+        <v>0.1526537623190971</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
         <v>99</v>
@@ -2437,10 +2437,10 @@
         <v>106</v>
       </c>
       <c r="T8">
-        <v>0.3142695571397605</v>
+        <v>0.2186794537827037</v>
       </c>
       <c r="U8">
-        <v>0.4663733985142371</v>
+        <v>0.3733611123269195</v>
       </c>
       <c r="V8" t="s">
         <v>110</v>
@@ -2449,22 +2449,22 @@
         <v>110</v>
       </c>
       <c r="X8">
-        <v>0.9998083912053797</v>
+        <v>0.9998214324988115</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0.9400710092179918</v>
       </c>
       <c r="Z8">
-        <v>-92.13388134388816</v>
+        <v>-96.31315585318613</v>
       </c>
       <c r="AA8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="AB8">
-        <v>-0.03723464612280344</v>
+        <v>-0.1099625345074773</v>
       </c>
       <c r="AC8">
-        <v>-0.9993065501276921</v>
+        <v>-0.993935732834217</v>
       </c>
       <c r="AD8" t="s">
         <v>111</v>
@@ -2479,67 +2479,67 @@
         <v>126</v>
       </c>
       <c r="AH8">
-        <v>-0.03722751163714174</v>
+        <v>-0.1066485152889248</v>
       </c>
       <c r="AI8">
-        <v>0.6615956465052489</v>
+        <v>0.6844906202511921</v>
       </c>
       <c r="AJ8">
-        <v>-0.00491775251390192</v>
+        <v>-0.08259994564590215</v>
       </c>
       <c r="AK8">
-        <v>-1.272933951822895</v>
+        <v>-1.166748508274195</v>
       </c>
       <c r="AL8">
-        <v>-0.51507400972078</v>
+        <v>-0.5497611236473408</v>
       </c>
       <c r="AM8">
-        <v>-0.6963759476103385</v>
+        <v>-0.3231161013929401</v>
       </c>
       <c r="AN8">
-        <v>0.522262883478808</v>
+        <v>0.5269346290651268</v>
       </c>
       <c r="AO8">
-        <v>0.3300512283564994</v>
+        <v>0.2429989554615568</v>
       </c>
       <c r="AP8">
-        <v>4.7644</v>
+        <v>4.76171</v>
       </c>
       <c r="AQ8">
-        <v>4.734678829967018</v>
+        <v>4.734970451972385</v>
       </c>
       <c r="AR8">
-        <v>4.740945124093886</v>
+        <v>4.747750251247417</v>
       </c>
       <c r="AS8">
-        <v>4.7644</v>
+        <v>4.76171</v>
       </c>
       <c r="AT8">
-        <v>4.71173</v>
+        <v>4.70527</v>
       </c>
       <c r="AU8">
-        <v>4.734678829967018</v>
+        <v>4.734970451972385</v>
       </c>
       <c r="AV8">
-        <v>4.807195</v>
+        <v>4.80151</v>
       </c>
       <c r="AW8">
-        <v>-0.00623817690222941</v>
+        <v>-0.005615534761170771</v>
       </c>
       <c r="AX8">
-        <v>0.6945009938773692</v>
+        <v>0.6718479403923223</v>
       </c>
       <c r="AY8">
-        <v>0.00623817690222941</v>
+        <v>0.005615534761170771</v>
       </c>
       <c r="AZ8">
-        <v>0.4249453100771195</v>
+        <v>0.4334355713940182</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3750546899228805</v>
+        <v>0.3665644286059819</v>
       </c>
       <c r="BC8" t="s">
         <v>133</v>
@@ -2554,22 +2554,22 @@
         <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.008982243304508373</v>
+        <v>0.008358341856181931</v>
       </c>
       <c r="BH8">
-        <v>55665.38146979827</v>
+        <v>59820.47738693458</v>
       </c>
       <c r="BI8">
-        <v>55665.38146979827</v>
+        <v>59820.47738693458</v>
       </c>
       <c r="BJ8">
-        <v>11683.60789811902</v>
+        <v>12562.81407035174</v>
       </c>
       <c r="BK8">
-        <v>556.6538146979827</v>
+        <v>598.2047738693458</v>
       </c>
       <c r="BL8">
-        <v>0.005566538146979827</v>
+        <v>0.005982047738693458</v>
       </c>
       <c r="BM8">
         <v>500</v>
@@ -2578,19 +2578,19 @@
         <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.09735801866583019</v>
+        <v>0.08149556763383116</v>
       </c>
       <c r="BP8">
-        <v>0.02686696080771658</v>
+        <v>0.02459226358824925</v>
       </c>
       <c r="BQ8">
-        <v>0.04557881133168997</v>
+        <v>0.04366570536165922</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT8" t="s">
         <v>138</v>
@@ -2602,7 +2602,7 @@
         <v>140</v>
       </c>
       <c r="BW8" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2610,7 +2610,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2622,7 +2622,7 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
         <v>92</v>
@@ -2631,31 +2631,31 @@
         <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K9">
-        <v>0.07896167182858867</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>1.664419904478783</v>
+        <v>1.284619702940228</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P9" t="s">
         <v>98</v>
       </c>
       <c r="Q9">
-        <v>0.7697404179571472</v>
+        <v>1</v>
       </c>
       <c r="R9" t="s">
         <v>104</v>
@@ -2664,40 +2664,40 @@
         <v>109</v>
       </c>
       <c r="T9">
-        <v>-0.684818444315218</v>
+        <v>-0.7787999376878065</v>
       </c>
       <c r="U9">
-        <v>0.7200068284780117</v>
+        <v>0.9004588682205338</v>
       </c>
       <c r="V9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9999771110475011</v>
+        <v>0.9999955850440831</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-117.644066305188</v>
+        <v>-123.8899077017919</v>
       </c>
       <c r="AA9">
-        <v>-7.999999999999998</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AB9">
-        <v>-0.4639774790755453</v>
+        <v>-0.5575988987827774</v>
       </c>
       <c r="AC9">
-        <v>-0.8858469952032925</v>
+        <v>-0.8301105155798437</v>
       </c>
       <c r="AD9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF9" t="s">
         <v>119</v>
@@ -2706,67 +2706,67 @@
         <v>125</v>
       </c>
       <c r="AH9">
-        <v>-0.4639668591170661</v>
+        <v>-0.5575964370082199</v>
       </c>
       <c r="AI9">
-        <v>0.8278743507134645</v>
+        <v>0.8579998559087119</v>
       </c>
       <c r="AJ9">
-        <v>-1.13585558544477</v>
+        <v>-0.9304608564918229</v>
       </c>
       <c r="AK9">
-        <v>-2.241244700868494</v>
+        <v>-1.395684904895981</v>
       </c>
       <c r="AL9">
-        <v>-2.638569280296996</v>
+        <v>-1.794984205749615</v>
       </c>
       <c r="AM9">
-        <v>0.412048627952475</v>
+        <v>0.9515974066848344</v>
       </c>
       <c r="AN9">
-        <v>2.52065545207872</v>
+        <v>1.667567034891542</v>
       </c>
       <c r="AO9">
-        <v>0.0754058791721629</v>
+        <v>0.06185512327700235</v>
       </c>
       <c r="AP9">
-        <v>7.6885</v>
+        <v>8.94319</v>
       </c>
       <c r="AQ9">
-        <v>7.635383874457526</v>
+        <v>8.885011687385264</v>
       </c>
       <c r="AR9">
-        <v>7.71137845410894</v>
+        <v>8.959432026461487</v>
       </c>
       <c r="AS9">
-        <v>7.6885</v>
+        <v>8.94319</v>
       </c>
       <c r="AT9">
-        <v>7.5296</v>
+        <v>8.777729999999998</v>
       </c>
       <c r="AU9">
-        <v>7.635383874457526</v>
+        <v>8.885011687385264</v>
       </c>
       <c r="AV9">
-        <v>7.738175000000001</v>
+        <v>9.024257499999999</v>
       </c>
       <c r="AW9">
-        <v>-0.006908516035959466</v>
+        <v>-0.006505319982549372</v>
       </c>
       <c r="AX9">
-        <v>1.069272783945118</v>
+        <v>0.7176527290805276</v>
       </c>
       <c r="AY9">
-        <v>0.006908516035959466</v>
+        <v>0.006505319982549372</v>
       </c>
       <c r="AZ9">
-        <v>0.4071102640865034</v>
+        <v>0.4083041275326151</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3928897359134966</v>
+        <v>0.3916958724673847</v>
       </c>
       <c r="BC9" t="s">
         <v>134</v>
@@ -2778,46 +2778,46 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>384.8702089785736</v>
+        <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.0064609481693439</v>
+        <v>0.009064718517665405</v>
       </c>
       <c r="BH9">
-        <v>77388.02214393468</v>
+        <v>55158.91078422298</v>
       </c>
       <c r="BI9">
-        <v>59568.68850994924</v>
+        <v>55158.91078422298</v>
       </c>
       <c r="BJ9">
-        <v>7747.76464979505</v>
+        <v>6167.699756375855</v>
       </c>
       <c r="BK9">
-        <v>595.6868850994924</v>
+        <v>551.5891078422297</v>
       </c>
       <c r="BL9">
-        <v>0.005956868850994924</v>
+        <v>0.005515891078422297</v>
       </c>
       <c r="BM9">
-        <v>384.8702089785736</v>
+        <v>500</v>
       </c>
       <c r="BN9">
-        <v>0.003848702089785736</v>
+        <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.1336838121244475</v>
+        <v>0.1537018033695721</v>
       </c>
       <c r="BP9">
-        <v>0.05235804556986372</v>
+        <v>0.0607115022994875</v>
       </c>
       <c r="BQ9">
-        <v>0.05760459172660702</v>
+        <v>0.06732802787784554</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT9" t="s">
         <v>138</v>
@@ -2829,7 +2829,7 @@
         <v>140</v>
       </c>
       <c r="BW9" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2837,7 +2837,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2849,7 +2849,7 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
         <v>92</v>
@@ -2858,31 +2858,31 @@
         <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K10">
-        <v>0.7961295937276529</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1.099162256042905</v>
+        <v>1.16554786331072</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P10" t="s">
         <v>98</v>
       </c>
       <c r="Q10">
-        <v>0.9490323984319132</v>
+        <v>0.75</v>
       </c>
       <c r="R10" t="s">
         <v>104</v>
@@ -2891,40 +2891,40 @@
         <v>109</v>
       </c>
       <c r="T10">
-        <v>-0.7634159909761071</v>
+        <v>-0.58775016694939</v>
       </c>
       <c r="U10">
-        <v>0.8629527559013159</v>
+        <v>0.6644663500040134</v>
       </c>
       <c r="V10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9999844836116794</v>
+        <v>0.9999150995071521</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-122.8542676783943</v>
+        <v>-108.0265642236214</v>
       </c>
       <c r="AA10">
-        <v>-2.000000000000003</v>
+        <v>-12</v>
       </c>
       <c r="AB10">
-        <v>-0.5425041095597809</v>
+        <v>-0.3094579024898199</v>
       </c>
       <c r="AC10">
-        <v>-0.8400531477893224</v>
+        <v>-0.9509131435554991</v>
       </c>
       <c r="AD10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF10" t="s">
         <v>119</v>
@@ -2933,67 +2933,67 @@
         <v>125</v>
       </c>
       <c r="AH10">
-        <v>-0.5424956918553514</v>
+        <v>-0.3094316293613829</v>
       </c>
       <c r="AI10">
-        <v>0.8527255077304319</v>
+        <v>0.7781174576414135</v>
       </c>
       <c r="AJ10">
-        <v>-0.782626422887848</v>
+        <v>-0.7843640309727368</v>
       </c>
       <c r="AK10">
-        <v>-1.2207549222003</v>
+        <v>-2.625449121050811</v>
       </c>
       <c r="AL10">
-        <v>-1.592488924166868</v>
+        <v>-1.904919545246617</v>
       </c>
       <c r="AM10">
-        <v>0.5709083704187535</v>
+        <v>0.516566091981597</v>
       </c>
       <c r="AN10">
-        <v>1.502624010295105</v>
+        <v>1.764158597753124</v>
       </c>
       <c r="AO10">
-        <v>0.06680196267726835</v>
+        <v>0.09793465288690467</v>
       </c>
       <c r="AP10">
-        <v>8.965809999999999</v>
+        <v>1.14658</v>
       </c>
       <c r="AQ10">
-        <v>8.901450099842762</v>
+        <v>1.131002667508531</v>
       </c>
       <c r="AR10">
-        <v>9.000670851267415</v>
+        <v>1.11988618075938</v>
       </c>
       <c r="AS10">
-        <v>8.965809999999999</v>
+        <v>1.14658</v>
       </c>
       <c r="AT10">
-        <v>8.771199999999999</v>
+        <v>1.13496</v>
       </c>
       <c r="AU10">
-        <v>8.901450099842762</v>
+        <v>1.131002667508531</v>
       </c>
       <c r="AV10">
-        <v>9.046877499999999</v>
+        <v>1.156964888327646</v>
       </c>
       <c r="AW10">
-        <v>-0.007178369846922615</v>
+        <v>-0.01358590982876795</v>
       </c>
       <c r="AX10">
-        <v>0.793905081040333</v>
+        <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.007178369846922615</v>
+        <v>0.01358590982876795</v>
       </c>
       <c r="AZ10">
-        <v>0.3979943393173396</v>
+        <v>0.4167047774158125</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.4020056606826605</v>
+        <v>0.3832952225841875</v>
       </c>
       <c r="BC10" t="s">
         <v>135</v>
@@ -3005,46 +3005,46 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>474.5161992159566</v>
+        <v>375</v>
       </c>
       <c r="BG10">
-        <v>0.009041848979623712</v>
+        <v>0.009057273219178633</v>
       </c>
       <c r="BH10">
-        <v>55298.4241527122</v>
+        <v>55204.25274808514</v>
       </c>
       <c r="BI10">
-        <v>52479.9961031537</v>
+        <v>41403.18956106386</v>
       </c>
       <c r="BJ10">
-        <v>5853.346892601304</v>
+        <v>36110.16201317297</v>
       </c>
       <c r="BK10">
-        <v>524.7999610315369</v>
+        <v>414.0318956106386</v>
       </c>
       <c r="BL10">
-        <v>0.005247999610315369</v>
+        <v>0.004140318956106386</v>
       </c>
       <c r="BM10">
-        <v>474.5161992159566</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN10">
-        <v>0.004745161992159566</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO10">
-        <v>0.1526783475810659</v>
+        <v>0.02189429102257438</v>
       </c>
       <c r="BP10">
-        <v>0.05772225361712255</v>
+        <v>0.006655835153010404</v>
       </c>
       <c r="BQ10">
-        <v>0.0585421692784223</v>
+        <v>0.009642679235864244</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT10" t="s">
         <v>138</v>
@@ -3056,7 +3056,7 @@
         <v>140</v>
       </c>
       <c r="BW10" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3064,7 +3064,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3076,7 +3076,7 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
         <v>92</v>
@@ -3085,31 +3085,31 @@
         <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.3438626324877645</v>
       </c>
       <c r="L11">
-        <v>1.000167377653249</v>
+        <v>1.926125894897982</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P11" t="s">
         <v>98</v>
       </c>
       <c r="Q11">
-        <v>0.75</v>
+        <v>0.8359656581219411</v>
       </c>
       <c r="R11" t="s">
         <v>104</v>
@@ -3118,40 +3118,40 @@
         <v>109</v>
       </c>
       <c r="T11">
-        <v>-0.5386034294224616</v>
+        <v>-0.7355337437864559</v>
       </c>
       <c r="U11">
-        <v>0.6423493220989157</v>
+        <v>0.7825647886622367</v>
       </c>
       <c r="V11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="X11">
-        <v>0.9999111154352319</v>
+        <v>0.9999808363406676</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-103.1283415028481</v>
+        <v>-121.8339645075535</v>
       </c>
       <c r="AA11">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="AB11">
-        <v>-0.2271330593743433</v>
+        <v>-0.5274595128822603</v>
       </c>
       <c r="AC11">
-        <v>-0.9738637344820121</v>
+        <v>-0.8495801682419433</v>
       </c>
       <c r="AD11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF11" t="s">
         <v>119</v>
@@ -3160,67 +3160,67 @@
         <v>125</v>
       </c>
       <c r="AH11">
-        <v>-0.2271128707512164</v>
+        <v>-0.5274494048278439</v>
       </c>
       <c r="AI11">
-        <v>0.7491375611531098</v>
+        <v>0.8480274956895379</v>
       </c>
       <c r="AJ11">
-        <v>-0.622650177525401</v>
+        <v>-1.349191485165129</v>
       </c>
       <c r="AK11">
-        <v>-2.933263767620166</v>
+        <v>-2.263978158998908</v>
       </c>
       <c r="AL11">
-        <v>-1.853504669552984</v>
+        <v>-2.903115257756255</v>
       </c>
       <c r="AM11">
-        <v>-0.2526973252355096</v>
+        <v>0.9980947323278444</v>
       </c>
       <c r="AN11">
-        <v>1.770934123438676</v>
+        <v>2.731178806381457</v>
       </c>
       <c r="AO11">
-        <v>0.1264749804101626</v>
+        <v>0.06802433929582494</v>
       </c>
       <c r="AP11">
-        <v>1.148535</v>
+        <v>7.6709</v>
       </c>
       <c r="AQ11">
-        <v>1.126706762882134</v>
+        <v>7.521435017599883</v>
       </c>
       <c r="AR11">
-        <v>1.113443311146264</v>
+        <v>7.424645922574383</v>
       </c>
       <c r="AS11">
-        <v>1.148535</v>
+        <v>7.6709</v>
       </c>
       <c r="AT11">
-        <v>1.129575</v>
+        <v>7.5455</v>
       </c>
       <c r="AU11">
-        <v>1.126706762882134</v>
+        <v>7.521435017599883</v>
       </c>
       <c r="AV11">
-        <v>1.163087158078578</v>
+        <v>7.770543321600077</v>
       </c>
       <c r="AW11">
-        <v>-0.01900528683746354</v>
+        <v>-0.01948467355852858</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.01900528683746354</v>
+        <v>0.01948467355852858</v>
       </c>
       <c r="AZ11">
-        <v>0.4128666984748956</v>
+        <v>0.406647284452319</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3871333015251043</v>
+        <v>0.393352715547681</v>
       </c>
       <c r="BC11" t="s">
         <v>136</v>
@@ -3232,46 +3232,46 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>375</v>
+        <v>417.9828290609706</v>
       </c>
       <c r="BG11">
-        <v>0.01267019122497569</v>
+        <v>0.01298978237235238</v>
       </c>
       <c r="BH11">
-        <v>39462.70353160824</v>
+        <v>38491.79190747693</v>
       </c>
       <c r="BI11">
-        <v>29597.02764870618</v>
+        <v>32177.81615422676</v>
       </c>
       <c r="BJ11">
-        <v>25769.37372279136</v>
+        <v>4194.790201179361</v>
       </c>
       <c r="BK11">
-        <v>295.9702764870618</v>
+        <v>321.7781615422676</v>
       </c>
       <c r="BL11">
-        <v>0.002959702764870618</v>
+        <v>0.003217781615422676</v>
       </c>
       <c r="BM11">
-        <v>375</v>
+        <v>417.9828290609705</v>
       </c>
       <c r="BN11">
-        <v>0.00375</v>
+        <v>0.004179828290609706</v>
       </c>
       <c r="BO11">
-        <v>0.02186794851788672</v>
+        <v>0.154278444585355</v>
       </c>
       <c r="BP11">
-        <v>0.006584927501496216</v>
+        <v>0.05370867568048682</v>
       </c>
       <c r="BQ11">
-        <v>0.009172553563114066</v>
+        <v>0.06350246369542772</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04969274973812191</v>
+        <v>0.04980127363568463</v>
       </c>
       <c r="BT11" t="s">
         <v>138</v>
@@ -3283,7 +3283,7 @@
         <v>140</v>
       </c>
       <c r="BW11" s="2">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="139">
   <si>
     <t>Pair</t>
   </si>
@@ -241,30 +241,30 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
+    <t>USDCNH</t>
   </si>
   <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>USDCNH</t>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
   </si>
   <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
@@ -277,72 +277,72 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>UP_REVERSAL_WATCH</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>UP_ACCELERATING</t>
-  </si>
-  <si>
-    <t>DOWN_STEADY</t>
-  </si>
-  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
+    <t>多头反转预警</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
     <t>空头减速</t>
   </si>
   <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
     <t>多头减速</t>
   </si>
   <si>
-    <t>多头加速</t>
-  </si>
-  <si>
-    <t>空头稳态</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
@@ -361,79 +361,73 @@
     <t>转换</t>
   </si>
   <si>
+    <t>TURNING_DOWN</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
-    <t>UP_CREST_FLATTENING</t>
-  </si>
-  <si>
-    <t>UP_STEEPENING</t>
-  </si>
-  <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
+    <t>向下转折带</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
   </si>
   <si>
     <t>下降谷底收敛</t>
   </si>
   <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>上升陡坡形成</t>
-  </si>
-  <si>
     <t>下降坡延续</t>
   </si>
   <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>地形转换区</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=4.039,naive=1.791,drift4=4.119; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=305.2,naive=34.96,drift4=63.31; naive_cap_applied; model_divergence_guard(abs=539.1,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01576,naive=0.003151,drift4=0.007918; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01103,naive=0.002702,drift4=0.006164; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03364,naive=0.005506,drift4=0.01288; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01501,naive=0.008033,drift4=0.009993; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0815,naive=0.02459,drift4=0.04367; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1537,naive=0.06071,drift4=0.06733; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02189,naive=0.006656,drift4=0.009643; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1543,naive=0.05371,drift4=0.0635; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=300.7,naive=38.66,drift4=54.44; naive_cap_applied; model_divergence_guard(abs=537.1,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01327,naive=0.003205,drift4=0.006509; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=3.637,naive=2.027,drift4=4.336; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.03813,naive=0.006512,drift4=0.01684; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01033,naive=0.004649,drift4=0.007287; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0807,naive=0.0221,drift4=0.04007; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1583,naive=0.06107,drift4=0.06662; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.0204,naive=0.01161,drift4=0.01113; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02127,naive=0.008709,drift4=0.0101; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1501,naive=0.05223,drift4=0.06234; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -1033,7 +1027,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1054,43 +1048,43 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.9655620847251117</v>
+        <v>0.05907275545969401</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T2">
-        <v>-0.7109343538734294</v>
+        <v>0.3792715393973716</v>
       </c>
       <c r="U2">
-        <v>0.7197202381217118</v>
+        <v>0.4424306633820686</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1099,22 +1093,22 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9991991155146743</v>
+        <v>0.9870338826130057</v>
       </c>
       <c r="Y2">
-        <v>0.6144610582570272</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>116.7666666385041</v>
+        <v>-110.3001532599342</v>
       </c>
       <c r="AA2">
-        <v>-28</v>
+        <v>-69</v>
       </c>
       <c r="AB2">
-        <v>-0.4503581785973821</v>
+        <v>-0.3469381603221821</v>
       </c>
       <c r="AC2">
-        <v>0.8928479775249807</v>
+        <v>-0.9378880065936763</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1129,58 +1123,67 @@
         <v>121</v>
       </c>
       <c r="AH2">
-        <v>-0.3632517149615387</v>
+        <v>-0.1712198597047084</v>
       </c>
       <c r="AI2">
-        <v>0.7497097212193088</v>
+        <v>0.5657747095271159</v>
       </c>
       <c r="AJ2">
-        <v>-0.8754817607296135</v>
+        <v>-0.03360509406946684</v>
       </c>
       <c r="AK2">
-        <v>1.554069485227286</v>
+        <v>-0.4212699702445057</v>
       </c>
       <c r="AL2">
-        <v>-0.5886128695847785</v>
+        <v>-0.3247500522790193</v>
       </c>
       <c r="AM2">
-        <v>3.189245913176564</v>
+        <v>-0.3386557400517989</v>
       </c>
       <c r="AN2">
-        <v>0.5463548806730636</v>
+        <v>0.3371940299437112</v>
       </c>
       <c r="AO2">
-        <v>0.05339756294298168</v>
+        <v>0.2251239832272708</v>
       </c>
       <c r="AP2">
-        <v>157.1105</v>
+        <v>4313.549999999999</v>
       </c>
       <c r="AQ2">
-        <v>157.2010186173688</v>
+        <v>4395.661892463767</v>
       </c>
       <c r="AR2">
-        <v>159.3054585008209</v>
+        <v>4778.816308212558</v>
       </c>
       <c r="AS2">
-        <v>157.1105</v>
+        <v>4313.549999999999</v>
       </c>
       <c r="AT2">
-        <v>154.1445</v>
+        <v>4169.879999999998</v>
+      </c>
+      <c r="AU2">
+        <v>4395.661892463767</v>
+      </c>
+      <c r="AV2">
+        <v>4179.912499999999</v>
       </c>
       <c r="AW2">
-        <v>0.0005761461988141254</v>
+        <v>0.01903580402771908</v>
+      </c>
+      <c r="AX2">
+        <v>0.6144375079133291</v>
       </c>
       <c r="AY2">
-        <v>0.0005761461988141254</v>
+        <v>0.01903580402771908</v>
       </c>
       <c r="AZ2">
-        <v>0.4772986678689559</v>
+        <v>0.3</v>
       </c>
       <c r="BA2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="BB2">
-        <v>0.3227013321310441</v>
+        <v>0.4</v>
       </c>
       <c r="BC2" t="s">
         <v>127</v>
@@ -1192,43 +1195,46 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="BG2">
+        <v>0.03098086263054797</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>16138.99541670562</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>12104.24656252921</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>2.806098587597041</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>121.0424656252921</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>0.001210424656252921</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="BO2">
-        <v>4.038634026021696</v>
+        <v>300.7180060746317</v>
       </c>
       <c r="BP2">
-        <v>1.790667288627491</v>
+        <v>38.66278786334527</v>
       </c>
       <c r="BQ2">
-        <v>4.119102819322602</v>
+        <v>54.43780650617621</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT2" t="s">
         <v>137</v>
@@ -1237,10 +1243,10 @@
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BW2" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1248,7 +1254,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1263,76 +1269,76 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" s="2">
+        <v>46287</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2.192273573372067</v>
+      </c>
+      <c r="M3">
+        <v>6</v>
+      </c>
+      <c r="N3">
+        <v>14</v>
+      </c>
+      <c r="O3" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="2">
-        <v>46286</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0.01093802734210199</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-      <c r="N3">
-        <v>29</v>
-      </c>
-      <c r="O3" t="s">
-        <v>95</v>
-      </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T3">
-        <v>0.8747428227636473</v>
+        <v>0.9242740106740395</v>
       </c>
       <c r="U3">
-        <v>0.7044609170831502</v>
+        <v>0.9658409170466475</v>
       </c>
       <c r="V3" t="s">
+        <v>92</v>
+      </c>
+      <c r="W3" t="s">
         <v>94</v>
       </c>
-      <c r="W3" t="s">
-        <v>95</v>
-      </c>
       <c r="X3">
-        <v>0.8433065873580352</v>
+        <v>0.999670448973319</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>-50.63457834155941</v>
+        <v>31.94860947065497</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>-24</v>
       </c>
       <c r="AB3">
-        <v>0.6342640483614705</v>
+        <v>0.8485230575437027</v>
       </c>
       <c r="AC3">
-        <v>-0.7731164963678618</v>
+        <v>0.5291584080563081</v>
       </c>
       <c r="AD3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AE3" t="s">
         <v>113</v>
@@ -1344,67 +1350,67 @@
         <v>122</v>
       </c>
       <c r="AH3">
-        <v>0.2674395250538018</v>
+        <v>0.8482434258989268</v>
       </c>
       <c r="AI3">
-        <v>0.6070657455659292</v>
+        <v>0.9483751407441491</v>
       </c>
       <c r="AJ3">
-        <v>0.0627906675128186</v>
+        <v>1.659969719740997</v>
       </c>
       <c r="AK3">
-        <v>-0.3385811013406831</v>
+        <v>1.159505413854145</v>
       </c>
       <c r="AL3">
-        <v>-0.1469459846318279</v>
+        <v>2.781852845213402</v>
       </c>
       <c r="AM3">
-        <v>-0.2679331550601287</v>
+        <v>-3.240957977731926</v>
       </c>
       <c r="AN3">
-        <v>0.151127139077636</v>
+        <v>2.446842755826611</v>
       </c>
       <c r="AO3">
-        <v>0.189138496785495</v>
+        <v>0.040442891064156</v>
       </c>
       <c r="AP3">
-        <v>4323.049999999999</v>
+        <v>0.82284</v>
       </c>
       <c r="AQ3">
-        <v>4410.992589082751</v>
+        <v>0.8299803311530252</v>
       </c>
       <c r="AR3">
-        <v>4795.085296942508</v>
+        <v>0.8276015698644621</v>
       </c>
       <c r="AS3">
-        <v>4323.049999999999</v>
+        <v>0.82284</v>
       </c>
       <c r="AT3">
-        <v>4188.879999999998</v>
+        <v>0.8366800000000001</v>
       </c>
       <c r="AU3">
-        <v>4410.992589082751</v>
+        <v>0.8299803311530252</v>
       </c>
       <c r="AV3">
-        <v>4189.412499999999</v>
+        <v>0.8152600000000001</v>
       </c>
       <c r="AW3">
-        <v>0.02034271847023549</v>
+        <v>0.008677666560965859</v>
       </c>
       <c r="AX3">
-        <v>0.6580682000392959</v>
+        <v>0.9419961943305044</v>
       </c>
       <c r="AY3">
-        <v>0.02034271847023549</v>
+        <v>0.008677666560965859</v>
       </c>
       <c r="AZ3">
-        <v>0.3</v>
+        <v>0.4330780529537038</v>
       </c>
       <c r="BA3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.4</v>
+        <v>0.3669219470462963</v>
       </c>
       <c r="BC3" t="s">
         <v>128</v>
@@ -1416,58 +1422,58 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.03091278148529399</v>
+        <v>0.009211997472169461</v>
       </c>
       <c r="BH3">
-        <v>16174.53933214851</v>
+        <v>54277.04485488185</v>
       </c>
       <c r="BI3">
-        <v>12130.90449911138</v>
+        <v>54277.04485488185</v>
       </c>
       <c r="BJ3">
-        <v>2.806098587597041</v>
+        <v>65963.06068601653</v>
       </c>
       <c r="BK3">
-        <v>121.3090449911138</v>
+        <v>542.7704485488184</v>
       </c>
       <c r="BL3">
-        <v>0.001213090449911138</v>
+        <v>0.005427704485488185</v>
       </c>
       <c r="BM3">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="BN3">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>305.1584185642193</v>
+        <v>0.0132718649523491</v>
       </c>
       <c r="BP3">
-        <v>34.95586911447518</v>
+        <v>0.003205192906976022</v>
       </c>
       <c r="BQ3">
-        <v>63.31322884344615</v>
+        <v>0.006509169235105735</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV3" t="s">
         <v>138</v>
       </c>
-      <c r="BU3" t="s">
-        <v>91</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>140</v>
-      </c>
       <c r="BW3" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1475,7 +1481,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1487,82 +1493,82 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2.05651322737015</v>
+        <v>0.7689035290244188</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T4">
-        <v>0.8988917203478006</v>
+        <v>-0.5978205059167399</v>
       </c>
       <c r="U4">
-        <v>0.9544023477634401</v>
+        <v>0.6688986334359897</v>
       </c>
       <c r="V4" t="s">
+        <v>93</v>
+      </c>
+      <c r="W4" t="s">
         <v>94</v>
       </c>
-      <c r="W4" t="s">
-        <v>95</v>
-      </c>
       <c r="X4">
-        <v>0.9996042944277196</v>
+        <v>0.9995176230938265</v>
       </c>
       <c r="Y4">
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>37.08484846736302</v>
+        <v>109.0394036561722</v>
       </c>
       <c r="AA4">
-        <v>-22.99999999999999</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AB4">
-        <v>0.7977434157478444</v>
+        <v>-0.3262183327945586</v>
       </c>
       <c r="AC4">
-        <v>0.6029970502672148</v>
+        <v>0.9452944511361201</v>
       </c>
       <c r="AD4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF4" t="s">
         <v>117</v>
@@ -1571,67 +1577,67 @@
         <v>123</v>
       </c>
       <c r="AH4">
-        <v>0.7974277442329829</v>
+        <v>-0.3260609726044481</v>
       </c>
       <c r="AI4">
-        <v>0.9327697977437558</v>
+        <v>0.7868040498795141</v>
       </c>
       <c r="AJ4">
-        <v>1.553909865259229</v>
+        <v>-0.8089699437799314</v>
       </c>
       <c r="AK4">
-        <v>1.303144291215953</v>
+        <v>2.083598681709422</v>
       </c>
       <c r="AL4">
-        <v>2.634002089849427</v>
+        <v>-0.3346738025946434</v>
       </c>
       <c r="AM4">
-        <v>-3.278751439118282</v>
+        <v>3.278481602830913</v>
       </c>
       <c r="AN4">
-        <v>2.277861118416645</v>
+        <v>0.4572595628691817</v>
       </c>
       <c r="AO4">
-        <v>0.04276486686866134</v>
+        <v>0.07261745361128483</v>
       </c>
       <c r="AP4">
-        <v>0.8189949999999999</v>
+        <v>157.9215</v>
       </c>
       <c r="AQ4">
-        <v>0.8232367053758801</v>
+        <v>158.6881286629266</v>
       </c>
       <c r="AR4">
-        <v>0.8204808100574377</v>
+        <v>160.8825000340996</v>
       </c>
       <c r="AS4">
-        <v>0.8189949999999999</v>
+        <v>157.9215</v>
       </c>
       <c r="AT4">
-        <v>0.8289899999999999</v>
+        <v>155.7665</v>
       </c>
       <c r="AU4">
-        <v>0.8232367053758801</v>
+        <v>158.6881286629266</v>
       </c>
       <c r="AV4">
-        <v>0.811415</v>
+        <v>156.423375</v>
       </c>
       <c r="AW4">
-        <v>0.005179159061874859</v>
+        <v>0.004854492028802871</v>
       </c>
       <c r="AX4">
-        <v>0.5595917382427764</v>
+        <v>0.5117254320744827</v>
       </c>
       <c r="AY4">
-        <v>0.005179159061874859</v>
+        <v>0.004854492028802871</v>
       </c>
       <c r="AZ4">
-        <v>0.4412047033221271</v>
+        <v>0.486831244395201</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3587952966778729</v>
+        <v>0.3131687556047991</v>
       </c>
       <c r="BC4" t="s">
         <v>129</v>
@@ -1646,22 +1652,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.009255245758521017</v>
+        <v>0.009486517035362607</v>
       </c>
       <c r="BH4">
-        <v>54023.4168865441</v>
+        <v>52706.38297872285</v>
       </c>
       <c r="BI4">
-        <v>54023.4168865441</v>
+        <v>52706.38297872285</v>
       </c>
       <c r="BJ4">
-        <v>65963.06068601653</v>
+        <v>333.7505214851863</v>
       </c>
       <c r="BK4">
-        <v>540.234168865441</v>
+        <v>527.0638297872284</v>
       </c>
       <c r="BL4">
-        <v>0.00540234168865441</v>
+        <v>0.005270638297872284</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1670,31 +1676,31 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.01575794787707602</v>
+        <v>3.636527797113456</v>
       </c>
       <c r="BP4">
-        <v>0.003150743528682279</v>
+        <v>2.027489551955681</v>
       </c>
       <c r="BQ4">
-        <v>0.007918107439097462</v>
+        <v>4.335841383866189</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT4" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV4" t="s">
         <v>138</v>
       </c>
-      <c r="BU4" t="s">
-        <v>91</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>140</v>
-      </c>
       <c r="BW4" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1702,7 +1708,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1717,148 +1723,148 @@
         <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.4030843275967169</v>
       </c>
       <c r="L5">
-        <v>0.4181638738972803</v>
+        <v>2.977543930371167</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="O5" t="s">
+        <v>94</v>
+      </c>
+      <c r="P5" t="s">
         <v>96</v>
       </c>
-      <c r="P5" t="s">
-        <v>99</v>
-      </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.8507710818991793</v>
       </c>
       <c r="R5" t="s">
         <v>101</v>
       </c>
       <c r="S5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="T5">
-        <v>0.5558378967449604</v>
+        <v>-0.999306556385563</v>
       </c>
       <c r="U5">
-        <v>0.6500641347383993</v>
+        <v>0.9101417880330798</v>
       </c>
       <c r="V5" t="s">
+        <v>93</v>
+      </c>
+      <c r="W5" t="s">
         <v>94</v>
       </c>
-      <c r="W5" t="s">
-        <v>95</v>
-      </c>
       <c r="X5">
-        <v>0.9997483248126688</v>
+        <v>0.9999647540802756</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0.5735485146995495</v>
       </c>
       <c r="Z5">
-        <v>-75.16993758728142</v>
+        <v>176.8963988010664</v>
       </c>
       <c r="AA5">
-        <v>-9</v>
+        <v>4.000000000000005</v>
       </c>
       <c r="AB5">
-        <v>0.2559530034611136</v>
+        <v>-0.9985332693502192</v>
       </c>
       <c r="AC5">
-        <v>-0.9666892261834903</v>
+        <v>0.05414157368199048</v>
       </c>
       <c r="AD5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AH5">
-        <v>0.2558885864410196</v>
+        <v>-0.7855925815230406</v>
       </c>
       <c r="AI5">
-        <v>0.7628201312597849</v>
+        <v>0.9095452538029476</v>
       </c>
       <c r="AJ5">
-        <v>0.5644088449907517</v>
+        <v>-2.277041399063659</v>
       </c>
       <c r="AK5">
-        <v>-1.955200417359916</v>
+        <v>0.14124748482445</v>
       </c>
       <c r="AL5">
-        <v>0.238370532503597</v>
+        <v>-3.659126875043988</v>
       </c>
       <c r="AM5">
-        <v>-1.590173488013066</v>
+        <v>3.946624535019657</v>
       </c>
       <c r="AN5">
-        <v>0.2705967320131298</v>
+        <v>3.304175784760246</v>
       </c>
       <c r="AO5">
-        <v>0.09251788975322217</v>
+        <v>0.03141395913416333</v>
       </c>
       <c r="AP5">
-        <v>0.711165</v>
+        <v>6.706895</v>
       </c>
       <c r="AQ5">
-        <v>0.7100532994112216</v>
+        <v>6.694730672031935</v>
       </c>
       <c r="AR5">
-        <v>0.7122287991984426</v>
+        <v>6.699273149849925</v>
       </c>
       <c r="AS5">
-        <v>0.711165</v>
+        <v>6.706895</v>
       </c>
       <c r="AT5">
-        <v>0.7067300000000001</v>
+        <v>6.682565</v>
       </c>
       <c r="AU5">
-        <v>0.7100532994112216</v>
+        <v>6.694730672031935</v>
       </c>
       <c r="AV5">
-        <v>0.7169650000000001</v>
+        <v>6.73040125</v>
       </c>
       <c r="AW5">
-        <v>-0.001563210490924621</v>
+        <v>-0.001813704846738384</v>
       </c>
       <c r="AX5">
-        <v>0.1916725153066212</v>
+        <v>0.5174933461554112</v>
       </c>
       <c r="AY5">
-        <v>0.001563210490924621</v>
+        <v>0.001813704846738384</v>
       </c>
       <c r="AZ5">
-        <v>0.4430602615770424</v>
+        <v>0.4368928994233587</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3569397384229576</v>
+        <v>0.3631071005766412</v>
       </c>
       <c r="BC5" t="s">
         <v>130</v>
@@ -1870,58 +1876,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>500</v>
+        <v>425.3855409495897</v>
       </c>
       <c r="BG5">
-        <v>0.008155631956015871</v>
+        <v>0.003504788728614302</v>
       </c>
       <c r="BH5">
-        <v>61307.32758620661</v>
+        <v>142661.9516086171</v>
       </c>
       <c r="BI5">
-        <v>61307.32758620661</v>
+        <v>121372.6629159115</v>
       </c>
       <c r="BJ5">
-        <v>86206.89655172374</v>
+        <v>18096.69942885814</v>
       </c>
       <c r="BK5">
-        <v>613.0732758620661</v>
+        <v>1213.726629159115</v>
       </c>
       <c r="BL5">
-        <v>0.006130732758620661</v>
+        <v>0.01213726629159115</v>
       </c>
       <c r="BM5">
-        <v>500</v>
+        <v>425.3855409495897</v>
       </c>
       <c r="BN5">
-        <v>0.005</v>
+        <v>0.004253855409495897</v>
       </c>
       <c r="BO5">
-        <v>0.01102501651430631</v>
+        <v>0.03813256662767046</v>
       </c>
       <c r="BP5">
-        <v>0.002701688092989758</v>
+        <v>0.00651249792009968</v>
       </c>
       <c r="BQ5">
-        <v>0.006164112042829227</v>
+        <v>0.01684423659943875</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT5" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV5" t="s">
         <v>138</v>
       </c>
-      <c r="BU5" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>140</v>
-      </c>
       <c r="BW5" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1929,7 +1935,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1941,151 +1947,151 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" t="s">
         <v>92</v>
       </c>
-      <c r="H6" t="s">
-        <v>92</v>
-      </c>
-      <c r="I6" t="s">
-        <v>93</v>
-      </c>
       <c r="J6" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K6">
-        <v>0.8246640972210072</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>3.528177455506283</v>
+        <v>0.04694163332292873</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q6">
-        <v>0.9561660243052518</v>
+        <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S6" t="s">
         <v>108</v>
       </c>
       <c r="T6">
-        <v>-0.998965934647524</v>
+        <v>0.4129561684468722</v>
       </c>
       <c r="U6">
-        <v>0.9731981751687198</v>
+        <v>0.5357659834023484</v>
       </c>
       <c r="V6" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="W6" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="X6">
-        <v>0.9998555599767319</v>
+        <v>0.9997428304050235</v>
       </c>
       <c r="Y6">
-        <v>0.9928258762532932</v>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>-176.3631016843742</v>
+        <v>-85.39922393047949</v>
       </c>
       <c r="AA6">
-        <v>13.00000000000001</v>
+        <v>-15</v>
       </c>
       <c r="AB6">
-        <v>-0.9979860845618934</v>
+        <v>0.08021242565986955</v>
       </c>
       <c r="AC6">
-        <v>-0.06343323277920872</v>
+        <v>-0.9967777920729173</v>
       </c>
       <c r="AD6" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="AE6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AF6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AH6">
-        <v>-0.994262614666409</v>
+        <v>0.08019179746285052</v>
       </c>
       <c r="AI6">
-        <v>0.9925208284367179</v>
+        <v>0.6883379886469313</v>
       </c>
       <c r="AJ6">
-        <v>-2.651323782891174</v>
+        <v>0.240984797672557</v>
       </c>
       <c r="AK6">
-        <v>-0.1048145629032953</v>
+        <v>-2.091845367565583</v>
       </c>
       <c r="AL6">
-        <v>-4.52315797129816</v>
+        <v>-0.3948136949341936</v>
       </c>
       <c r="AM6">
-        <v>3.65213557072818</v>
+        <v>-1.616098126748459</v>
       </c>
       <c r="AN6">
-        <v>4.189749352804028</v>
+        <v>0.5286548680489591</v>
       </c>
       <c r="AO6">
-        <v>0.03593078782909975</v>
+        <v>0.2375715312852523</v>
       </c>
       <c r="AP6">
-        <v>6.69862</v>
+        <v>0.70695</v>
       </c>
       <c r="AQ6">
-        <v>6.680820535554128</v>
+        <v>0.7037613355257435</v>
       </c>
       <c r="AR6">
-        <v>6.685390072392268</v>
+        <v>0.7066531181252356</v>
       </c>
       <c r="AS6">
-        <v>6.69862</v>
+        <v>0.70695</v>
       </c>
       <c r="AT6">
-        <v>6.666015</v>
+        <v>0.6982999999999999</v>
       </c>
       <c r="AU6">
-        <v>6.680820535554128</v>
+        <v>0.7037613355257435</v>
       </c>
       <c r="AV6">
-        <v>6.72212625</v>
+        <v>0.71277625</v>
       </c>
       <c r="AW6">
-        <v>-0.002657183784999314</v>
+        <v>-0.004510452612287255</v>
       </c>
       <c r="AX6">
-        <v>0.7572226299759593</v>
+        <v>0.547292765373346</v>
       </c>
       <c r="AY6">
-        <v>0.002657183784999314</v>
+        <v>0.004510452612287255</v>
       </c>
       <c r="AZ6">
-        <v>0.4275873341992818</v>
+        <v>0.4466997197694126</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3724126658007182</v>
+        <v>0.3533002802305875</v>
       </c>
       <c r="BC6" t="s">
         <v>131</v>
@@ -2097,58 +2103,58 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>478.0830121526259</v>
+        <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.00350911829600718</v>
+        <v>0.008241389065704836</v>
       </c>
       <c r="BH6">
-        <v>142485.9345918662</v>
+        <v>60669.38425230602</v>
       </c>
       <c r="BI6">
-        <v>136240.2095981228</v>
+        <v>60669.38425230602</v>
       </c>
       <c r="BJ6">
-        <v>20338.54877543775</v>
+        <v>85818.49388543182</v>
       </c>
       <c r="BK6">
-        <v>1362.402095981228</v>
+        <v>606.6938425230602</v>
       </c>
       <c r="BL6">
-        <v>0.01362402095981228</v>
+        <v>0.006066938425230602</v>
       </c>
       <c r="BM6">
-        <v>478.0830121526259</v>
+        <v>500</v>
       </c>
       <c r="BN6">
-        <v>0.004780830121526258</v>
+        <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.03363824918266327</v>
+        <v>0.01032603868544872</v>
       </c>
       <c r="BP6">
-        <v>0.005506382826467952</v>
+        <v>0.004649363264761622</v>
       </c>
       <c r="BQ6">
-        <v>0.01288254832241725</v>
+        <v>0.007286988782996478</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT6" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV6" t="s">
         <v>138</v>
       </c>
-      <c r="BU6" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>140</v>
-      </c>
       <c r="BW6" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2156,7 +2162,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2168,76 +2174,76 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K7">
-        <v>0.1910502009538229</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.251921697359182</v>
+        <v>0.2093737509907309</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q7">
-        <v>0.7977625502384558</v>
+        <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S7" t="s">
         <v>109</v>
       </c>
       <c r="T7">
-        <v>-0.6225277707030407</v>
+        <v>-0.5472059317582344</v>
       </c>
       <c r="U7">
-        <v>0.7087856933245674</v>
+        <v>0.6461936102511192</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
       </c>
       <c r="W7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9999626654605028</v>
+        <v>0.999803763839655</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0.7115228263201009</v>
       </c>
       <c r="Z7">
-        <v>-110.1382093721169</v>
+        <v>-99.84364096212249</v>
       </c>
       <c r="AA7">
-        <v>-4.999999999999995</v>
+        <v>-18</v>
       </c>
       <c r="AB7">
-        <v>-0.3442858806847173</v>
+        <v>-0.1709600137076963</v>
       </c>
       <c r="AC7">
-        <v>-0.9388648637376673</v>
+        <v>-0.985277967739594</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
@@ -2246,73 +2252,73 @@
         <v>112</v>
       </c>
       <c r="AF7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH7">
-        <v>-0.3442730269299066</v>
+        <v>-0.146272273381216</v>
       </c>
       <c r="AI7">
-        <v>0.7910621921093854</v>
+        <v>0.6674818814331507</v>
       </c>
       <c r="AJ7">
-        <v>-0.9019855763860494</v>
+        <v>-0.1369034983993388</v>
       </c>
       <c r="AK7">
-        <v>-2.533901608832344</v>
+        <v>-1.058472612049463</v>
       </c>
       <c r="AL7">
-        <v>-1.772215587384921</v>
+        <v>-0.5346054176647519</v>
       </c>
       <c r="AM7">
-        <v>1.10061735100406</v>
+        <v>0.0283605067527304</v>
       </c>
       <c r="AN7">
-        <v>1.599572967380154</v>
+        <v>0.4856165403755571</v>
       </c>
       <c r="AO7">
-        <v>0.08140336671470533</v>
+        <v>0.173613368580384</v>
       </c>
       <c r="AP7">
-        <v>1.33622</v>
+        <v>4.76404</v>
       </c>
       <c r="AQ7">
-        <v>1.331247259914613</v>
+        <v>4.737892869277369</v>
       </c>
       <c r="AR7">
-        <v>1.339103574728014</v>
+        <v>4.749786792158678</v>
       </c>
       <c r="AS7">
-        <v>1.33622</v>
+        <v>4.76404</v>
       </c>
       <c r="AT7">
-        <v>1.318995</v>
+        <v>4.709929999999999</v>
       </c>
       <c r="AU7">
-        <v>1.331247259914613</v>
+        <v>4.737892869277369</v>
       </c>
       <c r="AV7">
-        <v>1.34787</v>
+        <v>4.803839999999999</v>
       </c>
       <c r="AW7">
-        <v>-0.003721498020825459</v>
+        <v>-0.005488436436854196</v>
       </c>
       <c r="AX7">
-        <v>0.4268446425225234</v>
+        <v>0.6569630834831865</v>
       </c>
       <c r="AY7">
-        <v>0.003721498020825459</v>
+        <v>0.005488436436854196</v>
       </c>
       <c r="AZ7">
-        <v>0.4379852890490062</v>
+        <v>0.430061436181992</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3620147109509938</v>
+        <v>0.369938563818008</v>
       </c>
       <c r="BC7" t="s">
         <v>132</v>
@@ -2324,58 +2330,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>398.8812751192279</v>
+        <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.008718624178653211</v>
+        <v>0.0083542539525277</v>
       </c>
       <c r="BH7">
-        <v>57348.49785407728</v>
+        <v>59849.7487437185</v>
       </c>
       <c r="BI7">
-        <v>45750.4839004133</v>
+        <v>44887.31155778887</v>
       </c>
       <c r="BJ7">
-        <v>34238.73606173632</v>
+        <v>9422.110552763805</v>
       </c>
       <c r="BK7">
-        <v>457.504839004133</v>
+        <v>448.8731155778888</v>
       </c>
       <c r="BL7">
-        <v>0.00457504839004133</v>
+        <v>0.004488731155778888</v>
       </c>
       <c r="BM7">
-        <v>398.8812751192278</v>
+        <v>375</v>
       </c>
       <c r="BN7">
-        <v>0.003988812751192278</v>
+        <v>0.00375</v>
       </c>
       <c r="BO7">
-        <v>0.01501276607022105</v>
+        <v>0.08069579517435506</v>
       </c>
       <c r="BP7">
-        <v>0.008032774085598299</v>
+        <v>0.02210163493867729</v>
       </c>
       <c r="BQ7">
-        <v>0.009992883116811912</v>
+        <v>0.0400675116276946</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT7" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV7" t="s">
         <v>138</v>
       </c>
-      <c r="BU7" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>140</v>
-      </c>
       <c r="BW7" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2383,7 +2389,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2395,82 +2401,82 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="2">
+        <v>46287</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1.381248909600365</v>
+      </c>
+      <c r="M8">
+        <v>6</v>
+      </c>
+      <c r="N8">
+        <v>9</v>
+      </c>
+      <c r="O8" t="s">
         <v>94</v>
       </c>
-      <c r="J8" s="2">
-        <v>46286</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0.1526537623190971</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>29</v>
-      </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>96</v>
-      </c>
-      <c r="P8" t="s">
-        <v>99</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T8">
-        <v>0.2186794537827037</v>
+        <v>-0.789229280077872</v>
       </c>
       <c r="U8">
-        <v>0.3733611123269195</v>
+        <v>0.9051524404477519</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9998214324988115</v>
+        <v>0.9999970576508379</v>
       </c>
       <c r="Y8">
-        <v>0.9400710092179918</v>
+        <v>1</v>
       </c>
       <c r="Z8">
-        <v>-96.31315585318613</v>
+        <v>-125.3421552880807</v>
       </c>
       <c r="AA8">
-        <v>-18</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB8">
-        <v>-0.1099625345074773</v>
+        <v>-0.5784579399928681</v>
       </c>
       <c r="AC8">
-        <v>-0.993935732834217</v>
+        <v>-0.8157122112971017</v>
       </c>
       <c r="AD8" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AF8" t="s">
         <v>120</v>
@@ -2479,67 +2485,67 @@
         <v>126</v>
       </c>
       <c r="AH8">
-        <v>-0.1066485152889248</v>
+        <v>-0.578456237967633</v>
       </c>
       <c r="AI8">
-        <v>0.6844906202511921</v>
+        <v>0.8650299022740746</v>
       </c>
       <c r="AJ8">
-        <v>-0.08259994564590215</v>
+        <v>-1.017783425722924</v>
       </c>
       <c r="AK8">
-        <v>-1.166748508274195</v>
+        <v>-1.452100818022269</v>
       </c>
       <c r="AL8">
-        <v>-0.5497611236473408</v>
+        <v>-1.857171237747023</v>
       </c>
       <c r="AM8">
-        <v>-0.3231161013929401</v>
+        <v>1.329157897606892</v>
       </c>
       <c r="AN8">
-        <v>0.5269346290651268</v>
+        <v>1.697031421034574</v>
       </c>
       <c r="AO8">
-        <v>0.2429989554615568</v>
+        <v>0.05670966601052702</v>
       </c>
       <c r="AP8">
-        <v>4.76171</v>
+        <v>8.93526</v>
       </c>
       <c r="AQ8">
-        <v>4.734970451972385</v>
+        <v>8.869639589787214</v>
       </c>
       <c r="AR8">
-        <v>4.747750251247417</v>
+        <v>8.942123479366558</v>
       </c>
       <c r="AS8">
-        <v>4.76171</v>
+        <v>8.93526</v>
       </c>
       <c r="AT8">
-        <v>4.70527</v>
+        <v>8.761869999999998</v>
       </c>
       <c r="AU8">
-        <v>4.734970451972385</v>
+        <v>8.869639589787214</v>
       </c>
       <c r="AV8">
-        <v>4.80151</v>
+        <v>9.016327499999999</v>
       </c>
       <c r="AW8">
-        <v>-0.005615534761170771</v>
+        <v>-0.007343984418224599</v>
       </c>
       <c r="AX8">
-        <v>0.6718479403923223</v>
+        <v>0.8094539761653619</v>
       </c>
       <c r="AY8">
-        <v>0.005615534761170771</v>
+        <v>0.007343984418224599</v>
       </c>
       <c r="AZ8">
-        <v>0.4334355713940182</v>
+        <v>0.4054933643670589</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3665644286059819</v>
+        <v>0.3945066356329412</v>
       </c>
       <c r="BC8" t="s">
         <v>133</v>
@@ -2554,22 +2560,22 @@
         <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.008358341856181931</v>
+        <v>0.009072763411473206</v>
       </c>
       <c r="BH8">
-        <v>59820.47738693458</v>
+        <v>55110.00092515491</v>
       </c>
       <c r="BI8">
-        <v>59820.47738693458</v>
+        <v>55110.00092515491</v>
       </c>
       <c r="BJ8">
-        <v>12562.81407035174</v>
+        <v>6167.699756375854</v>
       </c>
       <c r="BK8">
-        <v>598.2047738693458</v>
+        <v>551.1000092515492</v>
       </c>
       <c r="BL8">
-        <v>0.005982047738693458</v>
+        <v>0.005511000092515492</v>
       </c>
       <c r="BM8">
         <v>500</v>
@@ -2578,31 +2584,31 @@
         <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.08149556763383116</v>
+        <v>0.1582691445982495</v>
       </c>
       <c r="BP8">
-        <v>0.02459226358824925</v>
+        <v>0.06106743776347189</v>
       </c>
       <c r="BQ8">
-        <v>0.04366570536165922</v>
+        <v>0.06661519919811368</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT8" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV8" t="s">
         <v>138</v>
       </c>
-      <c r="BU8" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>140</v>
-      </c>
       <c r="BW8" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2610,7 +2616,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2622,76 +2628,76 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0.6832713888004702</v>
       </c>
       <c r="L9">
-        <v>1.284619702940228</v>
+        <v>1.619095300778423</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.9208178472001176</v>
       </c>
       <c r="R9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S9" t="s">
         <v>109</v>
       </c>
       <c r="T9">
-        <v>-0.7787999376878065</v>
+        <v>-0.6904655038694207</v>
       </c>
       <c r="U9">
-        <v>0.9004588682205338</v>
+        <v>0.8131919886960746</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
       </c>
       <c r="W9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X9">
-        <v>0.9999955850440831</v>
+        <v>0.999967214539059</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-123.8899077017919</v>
+        <v>-114.3798665051813</v>
       </c>
       <c r="AA9">
-        <v>-2.000000000000003</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB9">
-        <v>-0.5575988987827774</v>
+        <v>-0.4127843939359378</v>
       </c>
       <c r="AC9">
-        <v>-0.8301105155798437</v>
+        <v>-0.9108287677291164</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
@@ -2700,73 +2706,73 @@
         <v>112</v>
       </c>
       <c r="AF9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH9">
-        <v>-0.5575964370082199</v>
+        <v>-0.4127708606093133</v>
       </c>
       <c r="AI9">
-        <v>0.8579998559087119</v>
+        <v>0.8126213546059401</v>
       </c>
       <c r="AJ9">
-        <v>-0.9304608564918229</v>
+        <v>-1.161244345024767</v>
       </c>
       <c r="AK9">
-        <v>-1.395684904895981</v>
+        <v>-2.626630382371999</v>
       </c>
       <c r="AL9">
-        <v>-1.794984205749615</v>
+        <v>-2.304505260688903</v>
       </c>
       <c r="AM9">
-        <v>0.9515974066848344</v>
+        <v>0.9905931590872408</v>
       </c>
       <c r="AN9">
-        <v>1.667567034891542</v>
+        <v>2.146520531148934</v>
       </c>
       <c r="AO9">
-        <v>0.06185512327700235</v>
+        <v>0.07468325775674514</v>
       </c>
       <c r="AP9">
-        <v>8.94319</v>
+        <v>1.327755</v>
       </c>
       <c r="AQ9">
-        <v>8.885011687385264</v>
+        <v>1.31706311983565</v>
       </c>
       <c r="AR9">
-        <v>8.959432026461487</v>
+        <v>1.325613475393128</v>
       </c>
       <c r="AS9">
-        <v>8.94319</v>
+        <v>1.327755</v>
       </c>
       <c r="AT9">
-        <v>8.777729999999998</v>
+        <v>1.302065</v>
       </c>
       <c r="AU9">
-        <v>8.885011687385264</v>
+        <v>1.31706311983565</v>
       </c>
       <c r="AV9">
-        <v>9.024257499999999</v>
+        <v>1.3395775</v>
       </c>
       <c r="AW9">
-        <v>-0.006505319982549372</v>
+        <v>-0.008052600189304225</v>
       </c>
       <c r="AX9">
-        <v>0.7176527290805276</v>
+        <v>0.9043671105391938</v>
       </c>
       <c r="AY9">
-        <v>0.006505319982549372</v>
+        <v>0.008052600189304225</v>
       </c>
       <c r="AZ9">
-        <v>0.4083041275326151</v>
+        <v>0.4187158476734184</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3916958724673847</v>
+        <v>0.3812841523265816</v>
       </c>
       <c r="BC9" t="s">
         <v>134</v>
@@ -2778,58 +2784,58 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>500</v>
+        <v>460.4089236000588</v>
       </c>
       <c r="BG9">
-        <v>0.009064718517665405</v>
+        <v>0.008904127644030724</v>
       </c>
       <c r="BH9">
-        <v>55158.91078422298</v>
+        <v>56153.7322901247</v>
       </c>
       <c r="BI9">
-        <v>55158.91078422298</v>
+        <v>51707.35887964435</v>
       </c>
       <c r="BJ9">
-        <v>6167.699756375855</v>
+        <v>38943.44881370761</v>
       </c>
       <c r="BK9">
-        <v>551.5891078422297</v>
+        <v>517.0735887964435</v>
       </c>
       <c r="BL9">
-        <v>0.005515891078422297</v>
+        <v>0.005170735887964435</v>
       </c>
       <c r="BM9">
-        <v>500</v>
+        <v>460.4089236000588</v>
       </c>
       <c r="BN9">
-        <v>0.005</v>
+        <v>0.004604089236000588</v>
       </c>
       <c r="BO9">
-        <v>0.1537018033695721</v>
+        <v>0.02039708598916613</v>
       </c>
       <c r="BP9">
-        <v>0.0607115022994875</v>
+        <v>0.01161186370203634</v>
       </c>
       <c r="BQ9">
-        <v>0.06732802787784554</v>
+        <v>0.01113274835472322</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT9" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV9" t="s">
         <v>138</v>
       </c>
-      <c r="BU9" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>140</v>
-      </c>
       <c r="BW9" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2837,7 +2843,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2849,76 +2855,76 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.5129785038932553</v>
       </c>
       <c r="L10">
-        <v>1.16554786331072</v>
+        <v>1.531323994638813</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>0.8782446259733139</v>
       </c>
       <c r="R10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S10" t="s">
         <v>109</v>
       </c>
       <c r="T10">
-        <v>-0.58775016694939</v>
+        <v>-0.6666080153865663</v>
       </c>
       <c r="U10">
-        <v>0.6644663500040134</v>
+        <v>0.7769005430959033</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X10">
-        <v>0.9999150995071521</v>
+        <v>0.9999206423518406</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-108.0265642236214</v>
+        <v>-112.7035812855123</v>
       </c>
       <c r="AA10">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="AB10">
-        <v>-0.3094579024898199</v>
+        <v>-0.3859637050200329</v>
       </c>
       <c r="AC10">
-        <v>-0.9509131435554991</v>
+        <v>-0.9225139665106481</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
@@ -2927,73 +2933,73 @@
         <v>112</v>
       </c>
       <c r="AF10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH10">
-        <v>-0.3094316293613829</v>
+        <v>-0.3859330758481276</v>
       </c>
       <c r="AI10">
-        <v>0.7781174576414135</v>
+        <v>0.8033281115250186</v>
       </c>
       <c r="AJ10">
-        <v>-0.7843640309727368</v>
+        <v>-1.057722188765269</v>
       </c>
       <c r="AK10">
-        <v>-2.625449121050811</v>
+        <v>-2.690737151312734</v>
       </c>
       <c r="AL10">
-        <v>-1.904919545246617</v>
+        <v>-2.370579042741876</v>
       </c>
       <c r="AM10">
-        <v>0.516566091981597</v>
+        <v>0.6611776113723781</v>
       </c>
       <c r="AN10">
-        <v>1.764158597753124</v>
+        <v>2.224121156604697</v>
       </c>
       <c r="AO10">
-        <v>0.09793465288690467</v>
+        <v>0.0828881653609035</v>
       </c>
       <c r="AP10">
-        <v>1.14658</v>
+        <v>1.14114</v>
       </c>
       <c r="AQ10">
-        <v>1.131002667508531</v>
+        <v>1.122202637295434</v>
       </c>
       <c r="AR10">
-        <v>1.11988618075938</v>
+        <v>1.111314343296532</v>
       </c>
       <c r="AS10">
-        <v>1.14658</v>
+        <v>1.14114</v>
       </c>
       <c r="AT10">
-        <v>1.13496</v>
+        <v>1.12408</v>
       </c>
       <c r="AU10">
-        <v>1.131002667508531</v>
+        <v>1.122202637295434</v>
       </c>
       <c r="AV10">
-        <v>1.156964888327646</v>
+        <v>1.153764908469711</v>
       </c>
       <c r="AW10">
-        <v>-0.01358590982876795</v>
+        <v>-0.01659512654412773</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01358590982876795</v>
+        <v>0.01659512654412773</v>
       </c>
       <c r="AZ10">
-        <v>0.4167047774158125</v>
+        <v>0.4143431730487508</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3832952225841875</v>
+        <v>0.3856568269512493</v>
       </c>
       <c r="BC10" t="s">
         <v>135</v>
@@ -3005,58 +3011,58 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>375</v>
+        <v>439.1223129866569</v>
       </c>
       <c r="BG10">
-        <v>0.009057273219178633</v>
+        <v>0.01106341769608515</v>
       </c>
       <c r="BH10">
-        <v>55204.25274808514</v>
+        <v>45193.9910193328</v>
       </c>
       <c r="BI10">
-        <v>41403.18956106386</v>
+        <v>39691.37973901524</v>
       </c>
       <c r="BJ10">
-        <v>36110.16201317297</v>
+        <v>34782.21755351248</v>
       </c>
       <c r="BK10">
-        <v>414.0318956106386</v>
+        <v>396.9137973901524</v>
       </c>
       <c r="BL10">
-        <v>0.004140318956106386</v>
+        <v>0.003969137973901524</v>
       </c>
       <c r="BM10">
-        <v>375.0000000000001</v>
+        <v>439.1223129866569</v>
       </c>
       <c r="BN10">
-        <v>0.003750000000000001</v>
+        <v>0.004391223129866569</v>
       </c>
       <c r="BO10">
-        <v>0.02189429102257438</v>
+        <v>0.02126756895753121</v>
       </c>
       <c r="BP10">
-        <v>0.006655835153010404</v>
+        <v>0.008708714180085814</v>
       </c>
       <c r="BQ10">
-        <v>0.009642679235864244</v>
+        <v>0.01009533797842482</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT10" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV10" t="s">
         <v>138</v>
       </c>
-      <c r="BU10" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV10" t="s">
-        <v>140</v>
-      </c>
       <c r="BW10" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3064,7 +3070,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3076,76 +3082,76 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="K11">
-        <v>0.3438626324877645</v>
+        <v>0.4926462336262687</v>
       </c>
       <c r="L11">
-        <v>1.926125894897982</v>
+        <v>2.073088797280267</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q11">
-        <v>0.8359656581219411</v>
+        <v>0.8731615584065672</v>
       </c>
       <c r="R11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S11" t="s">
         <v>109</v>
       </c>
       <c r="T11">
-        <v>-0.7355337437864559</v>
+        <v>-0.7642070699045426</v>
       </c>
       <c r="U11">
-        <v>0.7825647886622367</v>
+        <v>0.8177839062277842</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X11">
-        <v>0.9999808363406676</v>
+        <v>0.9999751589071989</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-121.8339645075535</v>
+        <v>-124.5614046355496</v>
       </c>
       <c r="AA11">
         <v>-10</v>
       </c>
       <c r="AB11">
-        <v>-0.5274595128822603</v>
+        <v>-0.5672891382821459</v>
       </c>
       <c r="AC11">
-        <v>-0.8495801682419433</v>
+        <v>-0.8235186904904468</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
@@ -3154,73 +3160,73 @@
         <v>112</v>
       </c>
       <c r="AF11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AH11">
-        <v>-0.5274494048278439</v>
+        <v>-0.5672750462000168</v>
       </c>
       <c r="AI11">
-        <v>0.8480274956895379</v>
+        <v>0.8610512426607231</v>
       </c>
       <c r="AJ11">
-        <v>-1.349191485165129</v>
+        <v>-1.488663435624243</v>
       </c>
       <c r="AK11">
-        <v>-2.263978158998908</v>
+        <v>-2.252073862699043</v>
       </c>
       <c r="AL11">
-        <v>-2.903115257756255</v>
+        <v>-2.96861681290742</v>
       </c>
       <c r="AM11">
-        <v>0.9980947323278444</v>
+        <v>1.667210972507485</v>
       </c>
       <c r="AN11">
-        <v>2.731178806381457</v>
+        <v>2.740950933643604</v>
       </c>
       <c r="AO11">
-        <v>0.06802433929582494</v>
+        <v>0.0608453629429361</v>
       </c>
       <c r="AP11">
-        <v>7.6709</v>
+        <v>7.6677</v>
       </c>
       <c r="AQ11">
-        <v>7.521435017599883</v>
+        <v>7.516384688921528</v>
       </c>
       <c r="AR11">
-        <v>7.424645922574383</v>
+        <v>7.420222364312545</v>
       </c>
       <c r="AS11">
-        <v>7.6709</v>
+        <v>7.6677</v>
       </c>
       <c r="AT11">
-        <v>7.5455</v>
+        <v>7.5391</v>
       </c>
       <c r="AU11">
-        <v>7.521435017599883</v>
+        <v>7.516384688921528</v>
       </c>
       <c r="AV11">
-        <v>7.770543321600077</v>
+        <v>7.768576874052314</v>
       </c>
       <c r="AW11">
-        <v>-0.01948467355852858</v>
+        <v>-0.01973411988972857</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.01948467355852858</v>
+        <v>0.01973411988972857</v>
       </c>
       <c r="AZ11">
-        <v>0.406647284452319</v>
+        <v>0.4074383781135761</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.393352715547681</v>
+        <v>0.3925616218864239</v>
       </c>
       <c r="BC11" t="s">
         <v>136</v>
@@ -3232,58 +3238,58 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>417.9828290609706</v>
+        <v>436.5807792032836</v>
       </c>
       <c r="BG11">
-        <v>0.01298978237235238</v>
+        <v>0.01315607992648571</v>
       </c>
       <c r="BH11">
-        <v>38491.79190747693</v>
+        <v>38005.24189530075</v>
       </c>
       <c r="BI11">
-        <v>32177.81615422676</v>
+        <v>33184.71624091936</v>
       </c>
       <c r="BJ11">
-        <v>4194.790201179361</v>
+        <v>4327.857928833857</v>
       </c>
       <c r="BK11">
-        <v>321.7781615422676</v>
+        <v>331.8471624091936</v>
       </c>
       <c r="BL11">
-        <v>0.003217781615422676</v>
+        <v>0.003318471624091936</v>
       </c>
       <c r="BM11">
-        <v>417.9828290609705</v>
+        <v>436.5807792032836</v>
       </c>
       <c r="BN11">
-        <v>0.004179828290609706</v>
+        <v>0.004365807792032836</v>
       </c>
       <c r="BO11">
-        <v>0.154278444585355</v>
+        <v>0.1501029427918794</v>
       </c>
       <c r="BP11">
-        <v>0.05370867568048682</v>
+        <v>0.05222630260760249</v>
       </c>
       <c r="BQ11">
-        <v>0.06350246369542772</v>
+        <v>0.06234010440010179</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04980127363568463</v>
+        <v>0.05257104889068741</v>
       </c>
       <c r="BT11" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV11" t="s">
         <v>138</v>
       </c>
-      <c r="BU11" t="s">
-        <v>92</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>140</v>
-      </c>
       <c r="BW11" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="135">
   <si>
     <t>Pair</t>
   </si>
@@ -241,18 +241,18 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
@@ -277,13 +277,16 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>HIGH</t>
+    <t>FLAT</t>
   </si>
   <si>
     <t>LONG</t>
@@ -292,60 +295,51 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>UP_REVERSAL_WATCH</t>
+    <t>DOWN_DECELERATING</t>
   </si>
   <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
-    <t>DOWN_STEADY</t>
+    <t>DOWN_ACCELERATING</t>
   </si>
   <si>
     <t>UP_DECELERATING</t>
   </si>
   <si>
-    <t>DOWN_ACCELERATING</t>
-  </si>
-  <si>
-    <t>多头反转预警</t>
+    <t>空头减速</t>
   </si>
   <si>
     <t>多头加速</t>
   </si>
   <si>
-    <t>空头减速</t>
-  </si>
-  <si>
-    <t>空头稳态</t>
+    <t>空头加速</t>
   </si>
   <si>
     <t>多头减速</t>
   </si>
   <si>
-    <t>空头加速</t>
-  </si>
-  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
@@ -361,73 +355,67 @@
     <t>转换</t>
   </si>
   <si>
-    <t>TURNING_DOWN</t>
+    <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
-  </si>
-  <si>
-    <t>DOWN_SLOPE</t>
+    <t>DOWN_STEEPENING</t>
   </si>
   <si>
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
-    <t>DOWN_STEEPENING</t>
-  </si>
-  <si>
-    <t>向下转折带</t>
+    <t>下降谷底收敛</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
-  </si>
-  <si>
-    <t>下降坡延续</t>
+    <t>下降陡坡形成</t>
   </si>
   <si>
     <t>地形转换区</t>
   </si>
   <si>
-    <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=300.7,naive=38.66,drift4=54.44; naive_cap_applied; model_divergence_guard(abs=537.1,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01327,naive=0.003205,drift4=0.006509; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=3.637,naive=2.027,drift4=4.336; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.03813,naive=0.006512,drift4=0.01684; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01033,naive=0.004649,drift4=0.007287; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0807,naive=0.0221,drift4=0.04007; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1583,naive=0.06107,drift4=0.06662; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.0204,naive=0.01161,drift4=0.01113; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02127,naive=0.008709,drift4=0.0101; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1501,naive=0.05223,drift4=0.06234; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04431,naive=0.01045,drift4=0.02156; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01096,naive=0.005197,drift4=0.005871; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=drift4; scores=model=320.2,naive=67.44,drift4=51.44; naive_cap_applied; model_divergence_guard(abs=498,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=3.415,naive=2.348,drift4=4.57; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01102,naive=0.007031,drift4=0.009134; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0829,naive=0.03921,drift4=0.04852; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.1888,naive=0.08253,drift4=0.07069; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.02531,naive=0.01445,drift4=0.01313; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02118,naive=0.01054,drift4=0.01097; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1546,naive=0.06267,drift4=0.06294; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -1027,7 +1015,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1048,43 +1036,43 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K2">
+        <v>0.03357562127703215</v>
+      </c>
+      <c r="L2">
+        <v>2.49205161606413</v>
+      </c>
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="N2">
+        <v>50</v>
+      </c>
+      <c r="O2" t="s">
+        <v>90</v>
+      </c>
+      <c r="P2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>0.05907275545969401</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>30</v>
-      </c>
-      <c r="O2" t="s">
-        <v>94</v>
-      </c>
-      <c r="P2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q2">
-        <v>0.75</v>
-      </c>
       <c r="R2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S2" t="s">
         <v>104</v>
       </c>
       <c r="T2">
-        <v>0.3792715393973716</v>
+        <v>-0.9752996702053002</v>
       </c>
       <c r="U2">
-        <v>0.4424306633820686</v>
+        <v>0.8438188640126402</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1093,100 +1081,91 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9870338826130057</v>
+        <v>0.999590676914801</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>0.3195501221615862</v>
       </c>
       <c r="Z2">
-        <v>-110.3001532599342</v>
+        <v>160.8929859153165</v>
       </c>
       <c r="AA2">
-        <v>-69</v>
+        <v>-11</v>
       </c>
       <c r="AB2">
-        <v>-0.3469381603221821</v>
+        <v>-0.9449088474309428</v>
       </c>
       <c r="AC2">
-        <v>-0.9378880065936763</v>
+        <v>0.3273335761065877</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
       </c>
       <c r="AE2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH2">
+        <v>-0.6231721093467566</v>
+      </c>
+      <c r="AI2">
+        <v>0.8433063414120239</v>
+      </c>
+      <c r="AJ2">
+        <v>-1.953534880719627</v>
+      </c>
+      <c r="AK2">
+        <v>0.6295166517535071</v>
+      </c>
+      <c r="AL2">
+        <v>-2.867520626012551</v>
+      </c>
+      <c r="AM2">
+        <v>4.217005378068214</v>
+      </c>
+      <c r="AN2">
+        <v>2.504716256557524</v>
+      </c>
+      <c r="AO2">
+        <v>0.02622049446504374</v>
+      </c>
+      <c r="AP2">
+        <v>6.71509</v>
+      </c>
+      <c r="AQ2">
+        <v>6.709027401616966</v>
+      </c>
+      <c r="AR2">
+        <v>6.714757009237212</v>
+      </c>
+      <c r="AS2">
+        <v>6.71509</v>
+      </c>
+      <c r="AT2">
+        <v>6.698955</v>
+      </c>
+      <c r="AW2">
+        <v>-0.0009028320369546502</v>
+      </c>
+      <c r="AY2">
+        <v>0.0009028320369546502</v>
+      </c>
+      <c r="AZ2">
+        <v>0.4331981784218614</v>
+      </c>
+      <c r="BA2">
+        <v>0.2</v>
+      </c>
+      <c r="BB2">
+        <v>0.3668018215781387</v>
+      </c>
+      <c r="BC2" t="s">
         <v>121</v>
-      </c>
-      <c r="AH2">
-        <v>-0.1712198597047084</v>
-      </c>
-      <c r="AI2">
-        <v>0.5657747095271159</v>
-      </c>
-      <c r="AJ2">
-        <v>-0.03360509406946684</v>
-      </c>
-      <c r="AK2">
-        <v>-0.4212699702445057</v>
-      </c>
-      <c r="AL2">
-        <v>-0.3247500522790193</v>
-      </c>
-      <c r="AM2">
-        <v>-0.3386557400517989</v>
-      </c>
-      <c r="AN2">
-        <v>0.3371940299437112</v>
-      </c>
-      <c r="AO2">
-        <v>0.2251239832272708</v>
-      </c>
-      <c r="AP2">
-        <v>4313.549999999999</v>
-      </c>
-      <c r="AQ2">
-        <v>4395.661892463767</v>
-      </c>
-      <c r="AR2">
-        <v>4778.816308212558</v>
-      </c>
-      <c r="AS2">
-        <v>4313.549999999999</v>
-      </c>
-      <c r="AT2">
-        <v>4169.879999999998</v>
-      </c>
-      <c r="AU2">
-        <v>4395.661892463767</v>
-      </c>
-      <c r="AV2">
-        <v>4179.912499999999</v>
-      </c>
-      <c r="AW2">
-        <v>0.01903580402771908</v>
-      </c>
-      <c r="AX2">
-        <v>0.6144375079133291</v>
-      </c>
-      <c r="AY2">
-        <v>0.01903580402771908</v>
-      </c>
-      <c r="AZ2">
-        <v>0.3</v>
-      </c>
-      <c r="BA2">
-        <v>0.3</v>
-      </c>
-      <c r="BB2">
-        <v>0.4</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>127</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1195,58 +1174,55 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>375</v>
-      </c>
-      <c r="BG2">
-        <v>0.03098086263054797</v>
+        <v>0</v>
       </c>
       <c r="BH2">
-        <v>16138.99541670562</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>12104.24656252921</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>2.806098587597041</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>121.0424656252921</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>0.001210424656252921</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>0.00375</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>300.7180060746317</v>
+        <v>0.04430805903653775</v>
       </c>
       <c r="BP2">
-        <v>38.66278786334527</v>
+        <v>0.01045205229836684</v>
       </c>
       <c r="BQ2">
-        <v>54.43780650617621</v>
+        <v>0.021556263798919</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="BW2" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1254,7 +1230,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1269,151 +1245,151 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2.192273573372067</v>
+        <v>2.376780171594311</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S3" t="s">
         <v>105</v>
       </c>
       <c r="T3">
-        <v>0.9242740106740395</v>
+        <v>0.9572287493821052</v>
       </c>
       <c r="U3">
-        <v>0.9658409170466475</v>
+        <v>0.9806592389820111</v>
       </c>
       <c r="V3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X3">
-        <v>0.999670448973319</v>
+        <v>0.999625207040255</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>31.94860947065497</v>
+        <v>23.87346857120675</v>
       </c>
       <c r="AA3">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="AB3">
-        <v>0.8485230575437027</v>
+        <v>0.9144414623902793</v>
       </c>
       <c r="AC3">
-        <v>0.5291584080563081</v>
+        <v>0.4047181882020221</v>
       </c>
       <c r="AD3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AE3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AF3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AG3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="AH3">
-        <v>0.8482434258989268</v>
+        <v>0.9140987361680766</v>
       </c>
       <c r="AI3">
-        <v>0.9483751407441491</v>
+        <v>0.9675472119477917</v>
       </c>
       <c r="AJ3">
-        <v>1.659969719740997</v>
+        <v>1.770806310825148</v>
       </c>
       <c r="AK3">
-        <v>1.159505413854145</v>
+        <v>0.8942736127801956</v>
       </c>
       <c r="AL3">
-        <v>2.781852845213402</v>
+        <v>3.122413841577219</v>
       </c>
       <c r="AM3">
-        <v>-3.240957977731926</v>
+        <v>-2.63079051722874</v>
       </c>
       <c r="AN3">
-        <v>2.446842755826611</v>
+        <v>2.850120757434095</v>
       </c>
       <c r="AO3">
-        <v>0.040442891064156</v>
+        <v>0.04436032822254267</v>
       </c>
       <c r="AP3">
-        <v>0.82284</v>
+        <v>0.827825</v>
       </c>
       <c r="AQ3">
-        <v>0.8299803311530252</v>
+        <v>0.8401659895214915</v>
       </c>
       <c r="AR3">
-        <v>0.8276015698644621</v>
+        <v>0.8401956382214166</v>
       </c>
       <c r="AS3">
-        <v>0.82284</v>
+        <v>0.827825</v>
       </c>
       <c r="AT3">
-        <v>0.8366800000000001</v>
+        <v>0.8466500000000001</v>
       </c>
       <c r="AU3">
-        <v>0.8299803311530252</v>
+        <v>0.8401659895214915</v>
       </c>
       <c r="AV3">
-        <v>0.8152600000000001</v>
+        <v>0.819597673652339</v>
       </c>
       <c r="AW3">
-        <v>0.008677666560965859</v>
+        <v>0.01490772750459509</v>
       </c>
       <c r="AX3">
-        <v>0.9419961943305044</v>
+        <v>1.5</v>
       </c>
       <c r="AY3">
-        <v>0.008677666560965859</v>
+        <v>0.01490772750459509</v>
       </c>
       <c r="AZ3">
-        <v>0.4330780529537038</v>
+        <v>0.4212671324887197</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3669219470462963</v>
+        <v>0.3787328675112803</v>
       </c>
       <c r="BC3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1425,22 +1401,22 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009211997472169461</v>
+        <v>0.009938485003063394</v>
       </c>
       <c r="BH3">
-        <v>54277.04485488185</v>
+        <v>50309.47874307626</v>
       </c>
       <c r="BI3">
-        <v>54277.04485488185</v>
+        <v>50309.47874307626</v>
       </c>
       <c r="BJ3">
-        <v>65963.06068601653</v>
+        <v>60773.0845807704</v>
       </c>
       <c r="BK3">
-        <v>542.7704485488184</v>
+        <v>503.0947874307626</v>
       </c>
       <c r="BL3">
-        <v>0.005427704485488185</v>
+        <v>0.005030947874307626</v>
       </c>
       <c r="BM3">
         <v>500</v>
@@ -1449,31 +1425,31 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>0.0132718649523491</v>
+        <v>0.01095694989739418</v>
       </c>
       <c r="BP3">
-        <v>0.003205192906976022</v>
+        <v>0.005197309855101563</v>
       </c>
       <c r="BQ3">
-        <v>0.006509169235105735</v>
+        <v>0.005870508671643774</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW3" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1481,7 +1457,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1493,154 +1469,154 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.7689035290244188</v>
+        <v>0.313230502143933</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S4" t="s">
         <v>106</v>
       </c>
       <c r="T4">
-        <v>-0.5978205059167399</v>
+        <v>-0.7779212152637645</v>
       </c>
       <c r="U4">
-        <v>0.6688986334359897</v>
+        <v>0.7498208223188599</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
       </c>
       <c r="W4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9995176230938265</v>
+        <v>0.9990251018006636</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>109.0394036561722</v>
+        <v>-110.4389089368781</v>
       </c>
       <c r="AA4">
-        <v>-21.99999999999999</v>
+        <v>-27</v>
       </c>
       <c r="AB4">
-        <v>-0.3262183327945586</v>
+        <v>-0.3492084648411762</v>
       </c>
       <c r="AC4">
-        <v>0.9452944511361201</v>
+        <v>-0.937045061927797</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH4">
+        <v>-0.1744340110688048</v>
+      </c>
+      <c r="AI4">
+        <v>0.585867111841665</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.2059344731686537</v>
+      </c>
+      <c r="AK4">
+        <v>-0.6807757311370635</v>
+      </c>
+      <c r="AL4">
+        <v>-0.6926233149025872</v>
+      </c>
+      <c r="AM4">
+        <v>-0.482024643841854</v>
+      </c>
+      <c r="AN4">
+        <v>0.7153250269384762</v>
+      </c>
+      <c r="AO4">
+        <v>0.1236947549394671</v>
+      </c>
+      <c r="AP4">
+        <v>4262.719999999999</v>
+      </c>
+      <c r="AQ4">
+        <v>4305.138982475778</v>
+      </c>
+      <c r="AR4">
+        <v>4663.44994158593</v>
+      </c>
+      <c r="AS4">
+        <v>4262.719999999999</v>
+      </c>
+      <c r="AT4">
+        <v>4068.219999999998</v>
+      </c>
+      <c r="AU4">
+        <v>4305.138982475778</v>
+      </c>
+      <c r="AV4">
+        <v>4129.0825</v>
+      </c>
+      <c r="AW4">
+        <v>0.009951153835058051</v>
+      </c>
+      <c r="AX4">
+        <v>0.3174182581668962</v>
+      </c>
+      <c r="AY4">
+        <v>0.009951153835058051</v>
+      </c>
+      <c r="AZ4">
+        <v>0.3</v>
+      </c>
+      <c r="BA4">
+        <v>0.3</v>
+      </c>
+      <c r="BB4">
+        <v>0.4</v>
+      </c>
+      <c r="BC4" t="s">
         <v>123</v>
-      </c>
-      <c r="AH4">
-        <v>-0.3260609726044481</v>
-      </c>
-      <c r="AI4">
-        <v>0.7868040498795141</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.8089699437799314</v>
-      </c>
-      <c r="AK4">
-        <v>2.083598681709422</v>
-      </c>
-      <c r="AL4">
-        <v>-0.3346738025946434</v>
-      </c>
-      <c r="AM4">
-        <v>3.278481602830913</v>
-      </c>
-      <c r="AN4">
-        <v>0.4572595628691817</v>
-      </c>
-      <c r="AO4">
-        <v>0.07261745361128483</v>
-      </c>
-      <c r="AP4">
-        <v>157.9215</v>
-      </c>
-      <c r="AQ4">
-        <v>158.6881286629266</v>
-      </c>
-      <c r="AR4">
-        <v>160.8825000340996</v>
-      </c>
-      <c r="AS4">
-        <v>157.9215</v>
-      </c>
-      <c r="AT4">
-        <v>155.7665</v>
-      </c>
-      <c r="AU4">
-        <v>158.6881286629266</v>
-      </c>
-      <c r="AV4">
-        <v>156.423375</v>
-      </c>
-      <c r="AW4">
-        <v>0.004854492028802871</v>
-      </c>
-      <c r="AX4">
-        <v>0.5117254320744827</v>
-      </c>
-      <c r="AY4">
-        <v>0.004854492028802871</v>
-      </c>
-      <c r="AZ4">
-        <v>0.486831244395201</v>
-      </c>
-      <c r="BA4">
-        <v>0.2</v>
-      </c>
-      <c r="BB4">
-        <v>0.3131687556047991</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>129</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1652,22 +1628,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.009486517035362607</v>
+        <v>0.03135028807897309</v>
       </c>
       <c r="BH4">
-        <v>52706.38297872285</v>
+        <v>15948.81676176221</v>
       </c>
       <c r="BI4">
-        <v>52706.38297872285</v>
+        <v>15948.81676176221</v>
       </c>
       <c r="BJ4">
-        <v>333.7505214851863</v>
+        <v>3.741464783462721</v>
       </c>
       <c r="BK4">
-        <v>527.0638297872284</v>
+        <v>159.4881676176221</v>
       </c>
       <c r="BL4">
-        <v>0.005270638297872284</v>
+        <v>0.001594881676176221</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1676,31 +1652,31 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>3.636527797113456</v>
+        <v>320.1622584956892</v>
       </c>
       <c r="BP4">
-        <v>2.027489551955681</v>
+        <v>67.44203602450197</v>
       </c>
       <c r="BQ4">
-        <v>4.335841383866189</v>
+        <v>51.43661626901583</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW4" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1708,7 +1684,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1720,7 +1696,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1732,142 +1708,142 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K5">
-        <v>0.4030843275967169</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>2.977543930371167</v>
+        <v>0.2376599206115991</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="O5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q5">
-        <v>0.8507710818991793</v>
+        <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T5">
-        <v>-0.999306556385563</v>
+        <v>-0.5202907831583916</v>
       </c>
       <c r="U5">
-        <v>0.9101417880330798</v>
+        <v>0.6340495393606566</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
       </c>
       <c r="W5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9999647540802756</v>
+        <v>0.9996747477575215</v>
       </c>
       <c r="Y5">
-        <v>0.5735485146995495</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>176.8963988010664</v>
+        <v>101.3254505345612</v>
       </c>
       <c r="AA5">
-        <v>4.000000000000005</v>
+        <v>-19</v>
       </c>
       <c r="AB5">
-        <v>-0.9985332693502192</v>
+        <v>-0.1963817096377843</v>
       </c>
       <c r="AC5">
-        <v>0.05414157368199048</v>
+        <v>0.9805275233871515</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="AG5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="AH5">
-        <v>-0.7855925815230406</v>
+        <v>-0.1963178360463429</v>
       </c>
       <c r="AI5">
-        <v>0.9095452538029476</v>
+        <v>0.7405993536458721</v>
       </c>
       <c r="AJ5">
-        <v>-2.277041399063659</v>
+        <v>-0.5496875005070285</v>
       </c>
       <c r="AK5">
-        <v>0.14124748482445</v>
+        <v>2.325902149472054</v>
       </c>
       <c r="AL5">
-        <v>-3.659126875043988</v>
+        <v>0.132020877264693</v>
       </c>
       <c r="AM5">
-        <v>3.946624535019657</v>
+        <v>2.911735307341218</v>
       </c>
       <c r="AN5">
-        <v>3.304175784760246</v>
+        <v>0.5490395199594185</v>
       </c>
       <c r="AO5">
-        <v>0.03141395913416333</v>
+        <v>0.1213421397373044</v>
       </c>
       <c r="AP5">
-        <v>6.706895</v>
+        <v>158.8345</v>
       </c>
       <c r="AQ5">
-        <v>6.694730672031935</v>
+        <v>159.933285388434</v>
       </c>
       <c r="AR5">
-        <v>6.699273149849925</v>
+        <v>161.8257466085711</v>
       </c>
       <c r="AS5">
-        <v>6.706895</v>
+        <v>158.8345</v>
       </c>
       <c r="AT5">
-        <v>6.682565</v>
+        <v>157.5925</v>
       </c>
       <c r="AU5">
-        <v>6.694730672031935</v>
+        <v>159.933285388434</v>
       </c>
       <c r="AV5">
-        <v>6.73040125</v>
+        <v>156.96075</v>
       </c>
       <c r="AW5">
-        <v>-0.001813704846738384</v>
+        <v>0.006917800530955059</v>
       </c>
       <c r="AX5">
-        <v>0.5174933461554112</v>
+        <v>0.5864098137072634</v>
       </c>
       <c r="AY5">
-        <v>0.001813704846738384</v>
+        <v>0.006917800530955059</v>
       </c>
       <c r="AZ5">
-        <v>0.4368928994233587</v>
+        <v>0.4942743907707793</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3631071005766412</v>
+        <v>0.3057256092292207</v>
       </c>
       <c r="BC5" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1876,58 +1852,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>425.3855409495897</v>
+        <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.003504788728614302</v>
+        <v>0.01179687032729032</v>
       </c>
       <c r="BH5">
-        <v>142661.9516086171</v>
+        <v>42384.12274849913</v>
       </c>
       <c r="BI5">
-        <v>121372.6629159115</v>
+        <v>42384.12274849913</v>
       </c>
       <c r="BJ5">
-        <v>18096.69942885814</v>
+        <v>266.8445630420289</v>
       </c>
       <c r="BK5">
-        <v>1213.726629159115</v>
+        <v>423.8412274849914</v>
       </c>
       <c r="BL5">
-        <v>0.01213726629159115</v>
+        <v>0.004238412274849914</v>
       </c>
       <c r="BM5">
-        <v>425.3855409495897</v>
+        <v>500</v>
       </c>
       <c r="BN5">
-        <v>0.004253855409495897</v>
+        <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.03813256662767046</v>
+        <v>3.41472060012922</v>
       </c>
       <c r="BP5">
-        <v>0.00651249792009968</v>
+        <v>2.347726812158319</v>
       </c>
       <c r="BQ5">
-        <v>0.01684423659943875</v>
+        <v>4.56988287492687</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW5" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1935,7 +1911,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1950,151 +1926,151 @@
         <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.04694163332292873</v>
+        <v>0.2689586953865793</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S6" t="s">
+        <v>107</v>
+      </c>
+      <c r="T6">
+        <v>0.2070180677677997</v>
+      </c>
+      <c r="U6">
+        <v>0.3680812380767515</v>
+      </c>
+      <c r="V6" t="s">
         <v>108</v>
       </c>
-      <c r="T6">
-        <v>0.4129561684468722</v>
-      </c>
-      <c r="U6">
-        <v>0.5357659834023484</v>
-      </c>
-      <c r="V6" t="s">
-        <v>110</v>
-      </c>
       <c r="W6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X6">
-        <v>0.9997428304050235</v>
+        <v>0.9996924303249665</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-85.39922393047949</v>
+        <v>-96.5215785744879</v>
       </c>
       <c r="AA6">
-        <v>-15</v>
+        <v>-17</v>
       </c>
       <c r="AB6">
-        <v>0.08021242565986955</v>
+        <v>-0.1135774019538207</v>
       </c>
       <c r="AC6">
-        <v>-0.9967777920729173</v>
+        <v>-0.9935291509389245</v>
       </c>
       <c r="AD6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AF6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="AH6">
-        <v>0.08019179746285052</v>
+        <v>-0.1135424689892106</v>
       </c>
       <c r="AI6">
-        <v>0.6883379886469313</v>
+        <v>0.6959674270694126</v>
       </c>
       <c r="AJ6">
-        <v>0.240984797672557</v>
+        <v>-0.1784819731560597</v>
       </c>
       <c r="AK6">
-        <v>-2.091845367565583</v>
+        <v>-2.255471694803508</v>
       </c>
       <c r="AL6">
-        <v>-0.3948136949341936</v>
+        <v>-1.192907343146901</v>
       </c>
       <c r="AM6">
-        <v>-1.616098126748459</v>
+        <v>-1.471257199994455</v>
       </c>
       <c r="AN6">
-        <v>0.5286548680489591</v>
+        <v>1.236629001477036</v>
       </c>
       <c r="AO6">
-        <v>0.2375715312852523</v>
+        <v>0.2533209608698126</v>
       </c>
       <c r="AP6">
-        <v>0.70695</v>
+        <v>0.7025399999999999</v>
       </c>
       <c r="AQ6">
-        <v>0.7037613355257435</v>
+        <v>0.6983141942360814</v>
       </c>
       <c r="AR6">
-        <v>0.7066531181252356</v>
+        <v>0.7031721391760661</v>
       </c>
       <c r="AS6">
-        <v>0.70695</v>
+        <v>0.7025399999999999</v>
       </c>
       <c r="AT6">
-        <v>0.6982999999999999</v>
+        <v>0.6894799999999999</v>
       </c>
       <c r="AU6">
-        <v>0.7037613355257435</v>
+        <v>0.6983141942360814</v>
       </c>
       <c r="AV6">
-        <v>0.71277625</v>
+        <v>0.7097487499999999</v>
       </c>
       <c r="AW6">
-        <v>-0.004510452612287255</v>
+        <v>-0.006015039377001326</v>
       </c>
       <c r="AX6">
-        <v>0.547292765373346</v>
+        <v>0.5862050652219249</v>
       </c>
       <c r="AY6">
-        <v>0.004510452612287255</v>
+        <v>0.006015039377001326</v>
       </c>
       <c r="AZ6">
-        <v>0.4466997197694126</v>
+        <v>0.4544355090224217</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3533002802305875</v>
+        <v>0.3455644909775782</v>
       </c>
       <c r="BC6" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2106,55 +2082,55 @@
         <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.008241389065704836</v>
+        <v>0.01026098158111984</v>
       </c>
       <c r="BH6">
-        <v>60669.38425230602</v>
+        <v>48728.28160221999</v>
       </c>
       <c r="BI6">
-        <v>60669.38425230602</v>
+        <v>48728.28160221999</v>
       </c>
       <c r="BJ6">
-        <v>85818.49388543182</v>
+        <v>69360.15259233637</v>
       </c>
       <c r="BK6">
-        <v>606.6938425230602</v>
+        <v>487.2828160221999</v>
       </c>
       <c r="BL6">
-        <v>0.006066938425230602</v>
+        <v>0.004872828160221999</v>
       </c>
       <c r="BM6">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN6">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO6">
-        <v>0.01032603868544872</v>
+        <v>0.01102162549689513</v>
       </c>
       <c r="BP6">
-        <v>0.004649363264761622</v>
+        <v>0.007030650633555798</v>
       </c>
       <c r="BQ6">
-        <v>0.007286988782996478</v>
+        <v>0.009133833196351204</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW6" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2162,7 +2138,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2174,154 +2150,154 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.2093737509907309</v>
+        <v>0.4830108028346309</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T7">
-        <v>-0.5472059317582344</v>
+        <v>-0.6570892863706981</v>
       </c>
       <c r="U7">
-        <v>0.6461936102511192</v>
+        <v>0.6955935713688013</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
       </c>
       <c r="W7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X7">
-        <v>0.999803763839655</v>
+        <v>0.9996135700079486</v>
       </c>
       <c r="Y7">
-        <v>0.7115228263201009</v>
+        <v>0.6133263391396896</v>
       </c>
       <c r="Z7">
-        <v>-99.84364096212249</v>
+        <v>-110.3527274422077</v>
       </c>
       <c r="AA7">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="AB7">
-        <v>-0.1709600137076963</v>
+        <v>-0.3477986132223966</v>
       </c>
       <c r="AC7">
-        <v>-0.985277967739594</v>
+        <v>-0.9375692639163135</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AH7">
-        <v>-0.146272273381216</v>
+        <v>-0.2804479163329407</v>
       </c>
       <c r="AI7">
-        <v>0.6674818814331507</v>
+        <v>0.7099677896516908</v>
       </c>
       <c r="AJ7">
-        <v>-0.1369034983993388</v>
+        <v>-0.30306000469083</v>
       </c>
       <c r="AK7">
-        <v>-1.058472612049463</v>
+        <v>-0.9757644934454882</v>
       </c>
       <c r="AL7">
-        <v>-0.5346054176647519</v>
+        <v>-0.8842826585876883</v>
       </c>
       <c r="AM7">
-        <v>0.0283605067527304</v>
+        <v>-0.1393141209674965</v>
       </c>
       <c r="AN7">
-        <v>0.4856165403755571</v>
+        <v>0.8553251341179611</v>
       </c>
       <c r="AO7">
-        <v>0.173613368580384</v>
+        <v>0.1126787443049873</v>
       </c>
       <c r="AP7">
-        <v>4.76404</v>
+        <v>4.72165</v>
       </c>
       <c r="AQ7">
-        <v>4.737892869277369</v>
+        <v>4.68273362221265</v>
       </c>
       <c r="AR7">
-        <v>4.749786792158678</v>
+        <v>4.714347275326612</v>
       </c>
       <c r="AS7">
-        <v>4.76404</v>
+        <v>4.72165</v>
       </c>
       <c r="AT7">
-        <v>4.709929999999999</v>
+        <v>4.625150000000001</v>
       </c>
       <c r="AU7">
-        <v>4.737892869277369</v>
+        <v>4.68273362221265</v>
       </c>
       <c r="AV7">
-        <v>4.803839999999999</v>
+        <v>4.76407</v>
       </c>
       <c r="AW7">
-        <v>-0.005488436436854196</v>
+        <v>-0.00824211404643509</v>
       </c>
       <c r="AX7">
-        <v>0.6569630834831865</v>
+        <v>0.9174063599092488</v>
       </c>
       <c r="AY7">
-        <v>0.005488436436854196</v>
+        <v>0.00824211404643509</v>
       </c>
       <c r="AZ7">
-        <v>0.430061436181992</v>
+        <v>0.4292017000795932</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.369938563818008</v>
+        <v>0.3707982999204068</v>
       </c>
       <c r="BC7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2333,55 +2309,55 @@
         <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.0083542539525277</v>
+        <v>0.008984147490813572</v>
       </c>
       <c r="BH7">
-        <v>59849.7487437185</v>
+        <v>55653.58321546453</v>
       </c>
       <c r="BI7">
-        <v>44887.31155778887</v>
+        <v>41740.1874115984</v>
       </c>
       <c r="BJ7">
-        <v>9422.110552763805</v>
+        <v>8840.169731258859</v>
       </c>
       <c r="BK7">
-        <v>448.8731155778888</v>
+        <v>417.401874115984</v>
       </c>
       <c r="BL7">
-        <v>0.004488731155778888</v>
+        <v>0.00417401874115984</v>
       </c>
       <c r="BM7">
-        <v>375</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN7">
-        <v>0.00375</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO7">
-        <v>0.08069579517435506</v>
+        <v>0.08290391528818435</v>
       </c>
       <c r="BP7">
-        <v>0.02210163493867729</v>
+        <v>0.03920552985362548</v>
       </c>
       <c r="BQ7">
-        <v>0.0400675116276946</v>
+        <v>0.04851631004207464</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW7" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2389,7 +2365,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2404,151 +2380,151 @@
         <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1.381248909600365</v>
+        <v>1.53164505827551</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T8">
-        <v>-0.789229280077872</v>
+        <v>-0.8223711890740208</v>
       </c>
       <c r="U8">
-        <v>0.9051524404477519</v>
+        <v>0.9200612304297192</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
       </c>
       <c r="W8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9999970576508379</v>
+        <v>0.9999767813856395</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-125.3421552880807</v>
+        <v>-130.1460534722882</v>
       </c>
       <c r="AA8">
-        <v>-3.000000000000004</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB8">
-        <v>-0.5784579399928681</v>
+        <v>-0.6447382537574189</v>
       </c>
       <c r="AC8">
-        <v>-0.8157122112971017</v>
+        <v>-0.7644034171442682</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF8" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AH8">
-        <v>-0.578456237967633</v>
+        <v>-0.6447232838285414</v>
       </c>
       <c r="AI8">
-        <v>0.8650299022740746</v>
+        <v>0.8849205896684339</v>
       </c>
       <c r="AJ8">
-        <v>-1.017783425722924</v>
+        <v>-1.124696659556274</v>
       </c>
       <c r="AK8">
-        <v>-1.452100818022269</v>
+        <v>-1.364512082778895</v>
       </c>
       <c r="AL8">
-        <v>-1.857171237747023</v>
+        <v>-2.072038687377193</v>
       </c>
       <c r="AM8">
-        <v>1.329157897606892</v>
+        <v>1.298911310092194</v>
       </c>
       <c r="AN8">
-        <v>1.697031421034574</v>
+        <v>1.916109695271846</v>
       </c>
       <c r="AO8">
-        <v>0.05670966601052702</v>
+        <v>0.05661839962510434</v>
       </c>
       <c r="AP8">
-        <v>8.93526</v>
+        <v>8.882949999999999</v>
       </c>
       <c r="AQ8">
-        <v>8.869639589787214</v>
+        <v>8.800607958564148</v>
       </c>
       <c r="AR8">
-        <v>8.942123479366558</v>
+        <v>8.908004968866212</v>
       </c>
       <c r="AS8">
-        <v>8.93526</v>
+        <v>8.882949999999999</v>
       </c>
       <c r="AT8">
-        <v>8.761869999999998</v>
+        <v>8.657249999999998</v>
       </c>
       <c r="AU8">
-        <v>8.869639589787214</v>
+        <v>8.800607958564148</v>
       </c>
       <c r="AV8">
-        <v>9.016327499999999</v>
+        <v>8.966125</v>
       </c>
       <c r="AW8">
-        <v>-0.007343984418224599</v>
+        <v>-0.009269672961780816</v>
       </c>
       <c r="AX8">
-        <v>0.8094539761653619</v>
+        <v>0.9899854696224908</v>
       </c>
       <c r="AY8">
-        <v>0.007343984418224599</v>
+        <v>0.009269672961780816</v>
       </c>
       <c r="AZ8">
-        <v>0.4054933643670589</v>
+        <v>0.391688982309069</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3945066356329412</v>
+        <v>0.408311017690931</v>
       </c>
       <c r="BC8" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2560,55 +2536,55 @@
         <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.009072763411473206</v>
+        <v>0.009363443450655495</v>
       </c>
       <c r="BH8">
-        <v>55110.00092515491</v>
+        <v>53399.15840096169</v>
       </c>
       <c r="BI8">
-        <v>55110.00092515491</v>
+        <v>53399.15840096169</v>
       </c>
       <c r="BJ8">
-        <v>6167.699756375854</v>
+        <v>6011.421701232326</v>
       </c>
       <c r="BK8">
-        <v>551.1000092515492</v>
+        <v>533.9915840096169</v>
       </c>
       <c r="BL8">
-        <v>0.005511000092515492</v>
+        <v>0.005339915840096169</v>
       </c>
       <c r="BM8">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN8">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO8">
-        <v>0.1582691445982495</v>
+        <v>0.1888477955742677</v>
       </c>
       <c r="BP8">
-        <v>0.06106743776347189</v>
+        <v>0.08253188420158984</v>
       </c>
       <c r="BQ8">
-        <v>0.06661519919811368</v>
+        <v>0.0706913560646502</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT8" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW8" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2616,7 +2592,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2631,151 +2607,151 @@
         <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K9">
-        <v>0.6832713888004702</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>1.619095300778423</v>
+        <v>2.095946280581374</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q9">
-        <v>0.9208178472001176</v>
+        <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T9">
-        <v>-0.6904655038694207</v>
+        <v>-0.754933602569243</v>
       </c>
       <c r="U9">
-        <v>0.8131919886960746</v>
+        <v>0.889705343267465</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
       </c>
       <c r="W9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X9">
-        <v>0.999967214539059</v>
+        <v>0.9999408884452222</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-114.3798665051813</v>
+        <v>-120.6540198628737</v>
       </c>
       <c r="AA9">
-        <v>-4.999999999999995</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB9">
-        <v>-0.4127843939359378</v>
+        <v>-0.5098527180263543</v>
       </c>
       <c r="AC9">
-        <v>-0.9108287677291164</v>
+        <v>-0.8602617078082336</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
       </c>
       <c r="AE9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AH9">
-        <v>-0.4127708606093133</v>
+        <v>-0.5098225798394841</v>
       </c>
       <c r="AI9">
-        <v>0.8126213546059401</v>
+        <v>0.8423133093768236</v>
       </c>
       <c r="AJ9">
-        <v>-1.161244345024767</v>
+        <v>-1.505982560345274</v>
       </c>
       <c r="AK9">
-        <v>-2.626630382371999</v>
+        <v>-2.619424373215611</v>
       </c>
       <c r="AL9">
-        <v>-2.304505260688903</v>
+        <v>-2.968284586879674</v>
       </c>
       <c r="AM9">
-        <v>0.9905931590872408</v>
+        <v>1.18822526655318</v>
       </c>
       <c r="AN9">
-        <v>2.146520531148934</v>
+        <v>2.785106010718397</v>
       </c>
       <c r="AO9">
-        <v>0.07468325775674514</v>
+        <v>0.07081211324606963</v>
       </c>
       <c r="AP9">
-        <v>1.327755</v>
+        <v>1.321695</v>
       </c>
       <c r="AQ9">
-        <v>1.31706311983565</v>
+        <v>1.308638105134802</v>
       </c>
       <c r="AR9">
-        <v>1.325613475393128</v>
+        <v>1.319759361373311</v>
       </c>
       <c r="AS9">
-        <v>1.327755</v>
+        <v>1.321695</v>
       </c>
       <c r="AT9">
-        <v>1.302065</v>
+        <v>1.289945</v>
       </c>
       <c r="AU9">
-        <v>1.31706311983565</v>
+        <v>1.308638105134802</v>
       </c>
       <c r="AV9">
-        <v>1.3395775</v>
+        <v>1.3348575</v>
       </c>
       <c r="AW9">
-        <v>-0.008052600189304225</v>
+        <v>-0.009878901611338226</v>
       </c>
       <c r="AX9">
-        <v>0.9043671105391938</v>
+        <v>0.9919768178687719</v>
       </c>
       <c r="AY9">
-        <v>0.008052600189304225</v>
+        <v>0.009878901611338226</v>
       </c>
       <c r="AZ9">
-        <v>0.4187158476734184</v>
+        <v>0.4139986424747509</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3812841523265816</v>
+        <v>0.3860013575252492</v>
       </c>
       <c r="BC9" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2784,58 +2760,58 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>460.4089236000588</v>
+        <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.008904127644030724</v>
+        <v>0.009958802900820511</v>
       </c>
       <c r="BH9">
-        <v>56153.7322901247</v>
+        <v>50206.83760683774</v>
       </c>
       <c r="BI9">
-        <v>51707.35887964435</v>
+        <v>50206.83760683774</v>
       </c>
       <c r="BJ9">
-        <v>38943.44881370761</v>
+        <v>37986.70465337142</v>
       </c>
       <c r="BK9">
-        <v>517.0735887964435</v>
+        <v>502.0683760683774</v>
       </c>
       <c r="BL9">
-        <v>0.005170735887964435</v>
+        <v>0.005020683760683774</v>
       </c>
       <c r="BM9">
-        <v>460.4089236000588</v>
+        <v>500</v>
       </c>
       <c r="BN9">
-        <v>0.004604089236000588</v>
+        <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.02039708598916613</v>
+        <v>0.02531051245703349</v>
       </c>
       <c r="BP9">
-        <v>0.01161186370203634</v>
+        <v>0.01444960636967392</v>
       </c>
       <c r="BQ9">
-        <v>0.01113274835472322</v>
+        <v>0.01312590211303527</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW9" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2843,7 +2819,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2858,151 +2834,151 @@
         <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K10">
-        <v>0.5129785038932553</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>1.531323994638813</v>
+        <v>1.909240718243277</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q10">
-        <v>0.8782446259733139</v>
+        <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T10">
-        <v>-0.6666080153865663</v>
+        <v>-0.7471010554355209</v>
       </c>
       <c r="U10">
-        <v>0.7769005430959033</v>
+        <v>0.8861648483533932</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
       </c>
       <c r="W10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9999206423518406</v>
+        <v>0.9998774936296352</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-112.7035812855123</v>
+        <v>-119.6151082460876</v>
       </c>
       <c r="AA10">
-        <v>-11</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB10">
-        <v>-0.3859637050200329</v>
+        <v>-0.4941711253433494</v>
       </c>
       <c r="AC10">
-        <v>-0.9225139665106481</v>
+        <v>-0.8693646524197356</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
       </c>
       <c r="AE10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG10" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AH10">
-        <v>-0.3859330758481276</v>
+        <v>-0.4941105862324445</v>
       </c>
       <c r="AI10">
-        <v>0.8033281115250186</v>
+        <v>0.8369653791787706</v>
       </c>
       <c r="AJ10">
-        <v>-1.057722188765269</v>
+        <v>-1.341166100762454</v>
       </c>
       <c r="AK10">
-        <v>-2.690737151312734</v>
+        <v>-2.50942208627491</v>
       </c>
       <c r="AL10">
-        <v>-2.370579042741876</v>
+        <v>-2.850159455517604</v>
       </c>
       <c r="AM10">
-        <v>0.6611776113723781</v>
+        <v>0.9111780842076089</v>
       </c>
       <c r="AN10">
-        <v>2.224121156604697</v>
+        <v>2.682292018941203</v>
       </c>
       <c r="AO10">
-        <v>0.0828881653609035</v>
+        <v>0.07495387463071046</v>
       </c>
       <c r="AP10">
-        <v>1.14114</v>
+        <v>1.136865</v>
       </c>
       <c r="AQ10">
-        <v>1.122202637295434</v>
+        <v>1.116328890809298</v>
       </c>
       <c r="AR10">
-        <v>1.111314343296532</v>
+        <v>1.107215933432272</v>
       </c>
       <c r="AS10">
-        <v>1.14114</v>
+        <v>1.136865</v>
       </c>
       <c r="AT10">
-        <v>1.12408</v>
+        <v>1.11553</v>
       </c>
       <c r="AU10">
-        <v>1.122202637295434</v>
+        <v>1.116328890809298</v>
       </c>
       <c r="AV10">
-        <v>1.153764908469711</v>
+        <v>1.150555739460468</v>
       </c>
       <c r="AW10">
-        <v>-0.01659512654412773</v>
+        <v>-0.01806380633646244</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01659512654412773</v>
+        <v>0.01806380633646244</v>
       </c>
       <c r="AZ10">
-        <v>0.4143431730487508</v>
+        <v>0.4171375298057224</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3856568269512493</v>
+        <v>0.3828624701942777</v>
       </c>
       <c r="BC10" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -3011,58 +2987,58 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>439.1223129866569</v>
+        <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01106341769608515</v>
+        <v>0.01204253755764162</v>
       </c>
       <c r="BH10">
-        <v>45193.9910193328</v>
+        <v>41519.4885302827</v>
       </c>
       <c r="BI10">
-        <v>39691.37973901524</v>
+        <v>41519.4885302827</v>
       </c>
       <c r="BJ10">
-        <v>34782.21755351248</v>
+        <v>36521.0368252015</v>
       </c>
       <c r="BK10">
-        <v>396.9137973901524</v>
+        <v>415.1948853028269</v>
       </c>
       <c r="BL10">
-        <v>0.003969137973901524</v>
+        <v>0.004151948853028269</v>
       </c>
       <c r="BM10">
-        <v>439.1223129866569</v>
+        <v>500</v>
       </c>
       <c r="BN10">
-        <v>0.004391223129866569</v>
+        <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.02126756895753121</v>
+        <v>0.02117500617395042</v>
       </c>
       <c r="BP10">
-        <v>0.008708714180085814</v>
+        <v>0.01053520678721724</v>
       </c>
       <c r="BQ10">
-        <v>0.01009533797842482</v>
+        <v>0.01097458477039072</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW10" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3070,7 +3046,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3085,151 +3061,151 @@
         <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="K11">
-        <v>0.4926462336262687</v>
+        <v>0.7983977380112539</v>
       </c>
       <c r="L11">
-        <v>2.073088797280267</v>
+        <v>2.375811432323905</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q11">
-        <v>0.8731615584065672</v>
+        <v>0.9495994345028135</v>
       </c>
       <c r="R11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T11">
-        <v>-0.7642070699045426</v>
+        <v>-0.8243571875466386</v>
       </c>
       <c r="U11">
-        <v>0.8177839062277842</v>
+        <v>0.8906962567325648</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
       </c>
       <c r="W11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X11">
-        <v>0.9999751589071989</v>
+        <v>0.9999034465395575</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-124.5614046355496</v>
+        <v>-131.3156443052732</v>
       </c>
       <c r="AA11">
-        <v>-10</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AB11">
-        <v>-0.5672891382821459</v>
+        <v>-0.6602067719977383</v>
       </c>
       <c r="AC11">
-        <v>-0.8235186904904468</v>
+        <v>-0.7510838955857904</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
       </c>
       <c r="AE11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AF11" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AG11" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AH11">
-        <v>-0.5672750462000168</v>
+        <v>-0.6601430267492944</v>
       </c>
       <c r="AI11">
-        <v>0.8610512426607231</v>
+        <v>0.8893433459388245</v>
       </c>
       <c r="AJ11">
-        <v>-1.488663435624243</v>
+        <v>-1.719822012607482</v>
       </c>
       <c r="AK11">
-        <v>-2.252073862699043</v>
+        <v>-2.070348970910865</v>
       </c>
       <c r="AL11">
-        <v>-2.96861681290742</v>
+        <v>-3.335704082077868</v>
       </c>
       <c r="AM11">
-        <v>1.667210972507485</v>
+        <v>1.940600048762417</v>
       </c>
       <c r="AN11">
-        <v>2.740950933643604</v>
+        <v>3.086665026183349</v>
       </c>
       <c r="AO11">
-        <v>0.0608453629429361</v>
+        <v>0.05789927966228124</v>
       </c>
       <c r="AP11">
-        <v>7.6677</v>
+        <v>7.6368</v>
       </c>
       <c r="AQ11">
-        <v>7.516384688921528</v>
+        <v>7.469763581265449</v>
       </c>
       <c r="AR11">
-        <v>7.420222364312545</v>
+        <v>7.378993192574002</v>
       </c>
       <c r="AS11">
-        <v>7.6677</v>
+        <v>7.6368</v>
       </c>
       <c r="AT11">
-        <v>7.5391</v>
+        <v>7.477300000000001</v>
       </c>
       <c r="AU11">
-        <v>7.516384688921528</v>
+        <v>7.469763581265449</v>
       </c>
       <c r="AV11">
-        <v>7.768576874052314</v>
+        <v>7.748157612489701</v>
       </c>
       <c r="AW11">
-        <v>-0.01973411988972857</v>
+        <v>-0.02187256687808394</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.01973411988972857</v>
+        <v>0.02187256687808394</v>
       </c>
       <c r="AZ11">
-        <v>0.4074383781135761</v>
+        <v>0.4011565400924744</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3925616218864239</v>
+        <v>0.3988434599075256</v>
       </c>
       <c r="BC11" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3238,58 +3214,58 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>436.5807792032836</v>
+        <v>474.7997172514067</v>
       </c>
       <c r="BG11">
-        <v>0.01315607992648571</v>
+        <v>0.01458171125205596</v>
       </c>
       <c r="BH11">
-        <v>38005.24189530075</v>
+        <v>34289.52825612303</v>
       </c>
       <c r="BI11">
-        <v>33184.71624091936</v>
+        <v>32561.31664138268</v>
       </c>
       <c r="BJ11">
-        <v>4327.857928833857</v>
+        <v>4263.738298944934</v>
       </c>
       <c r="BK11">
-        <v>331.8471624091936</v>
+        <v>325.6131664138268</v>
       </c>
       <c r="BL11">
-        <v>0.003318471624091936</v>
+        <v>0.003256131664138268</v>
       </c>
       <c r="BM11">
-        <v>436.5807792032836</v>
+        <v>474.7997172514068</v>
       </c>
       <c r="BN11">
-        <v>0.004365807792032836</v>
+        <v>0.004747997172514068</v>
       </c>
       <c r="BO11">
-        <v>0.1501029427918794</v>
+        <v>0.1546083954209371</v>
       </c>
       <c r="BP11">
-        <v>0.05222630260760249</v>
+        <v>0.06266540545624545</v>
       </c>
       <c r="BQ11">
-        <v>0.06234010440010179</v>
+        <v>0.06294276564810321</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05257104889068741</v>
+        <v>0.03767976884466208</v>
       </c>
       <c r="BT11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="BU11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="BW11" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -379,34 +379,34 @@
     <t>地形转换区</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04431,naive=0.01045,drift4=0.02156; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01096,naive=0.005197,drift4=0.005871; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=drift4; scores=model=320.2,naive=67.44,drift4=51.44; naive_cap_applied; model_divergence_guard(abs=498,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=3.415,naive=2.348,drift4=4.57; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01102,naive=0.007031,drift4=0.009134; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0829,naive=0.03921,drift4=0.04852; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.1888,naive=0.08253,drift4=0.07069; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.02531,naive=0.01445,drift4=0.01313; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02118,naive=0.01054,drift4=0.01097; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1546,naive=0.06267,drift4=0.06294; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04497,naive=0.01521,drift4=0.02406; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01088,naive=0.01142,drift4=0.009938; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=305.5,naive=116.1,drift4=130.8; naive_cap_applied; model_divergence_guard(abs=496.7,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.52,naive=0.20,drift4=0.28); metric_best=model; scores=model=3.093,naive=4.089,drift4=5.911; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=0.01008,naive=0.01261,drift4=0.0161; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=model; scores=model=0.0752,naive=0.07741,drift4=0.09203; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.1798,naive=0.1525,drift4=0.1153; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.02455,naive=0.02534,drift4=0.02217; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.02019,naive=0.01933,drift4=0.01908; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.1411,naive=0.1215,drift4=0.1017; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1015,7 +1015,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1138,10 +1138,10 @@
         <v>6.71509</v>
       </c>
       <c r="AQ2">
-        <v>6.709027401616966</v>
+        <v>6.709012637539413</v>
       </c>
       <c r="AR2">
-        <v>6.714757009237212</v>
+        <v>6.71483882001394</v>
       </c>
       <c r="AS2">
         <v>6.71509</v>
@@ -1150,19 +1150,19 @@
         <v>6.698955</v>
       </c>
       <c r="AW2">
-        <v>-0.0009028320369546502</v>
+        <v>-0.0009050306787529594</v>
       </c>
       <c r="AY2">
-        <v>0.0009028320369546502</v>
+        <v>0.0009050306787529594</v>
       </c>
       <c r="AZ2">
-        <v>0.4331981784218614</v>
+        <v>0.4300374553110444</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3668018215781387</v>
+        <v>0.3699625446889556</v>
       </c>
       <c r="BC2" t="s">
         <v>121</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.04430805903653775</v>
+        <v>0.04496546289982566</v>
       </c>
       <c r="BP2">
-        <v>0.01045205229836684</v>
+        <v>0.0152110084154809</v>
       </c>
       <c r="BQ2">
-        <v>0.021556263798919</v>
+        <v>0.02405827726993014</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT2" t="s">
         <v>131</v>
@@ -1222,7 +1222,7 @@
         <v>133</v>
       </c>
       <c r="BW2" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1230,7 +1230,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1353,10 +1353,10 @@
         <v>0.827825</v>
       </c>
       <c r="AQ3">
-        <v>0.8401659895214915</v>
+        <v>0.8399007993466148</v>
       </c>
       <c r="AR3">
-        <v>0.8401956382214166</v>
+        <v>0.8401192461457658</v>
       </c>
       <c r="AS3">
         <v>0.827825</v>
@@ -1365,28 +1365,28 @@
         <v>0.8466500000000001</v>
       </c>
       <c r="AU3">
-        <v>0.8401659895214915</v>
+        <v>0.8399007993466148</v>
       </c>
       <c r="AV3">
-        <v>0.819597673652339</v>
+        <v>0.8197744671022569</v>
       </c>
       <c r="AW3">
-        <v>0.01490772750459509</v>
+        <v>0.0145873818096998</v>
       </c>
       <c r="AX3">
         <v>1.5</v>
       </c>
       <c r="AY3">
-        <v>0.01490772750459509</v>
+        <v>0.0145873818096998</v>
       </c>
       <c r="AZ3">
-        <v>0.4212671324887197</v>
+        <v>0.4569458166687104</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3787328675112803</v>
+        <v>0.3430541833312897</v>
       </c>
       <c r="BC3" t="s">
         <v>122</v>
@@ -1401,22 +1401,22 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009938485003063394</v>
+        <v>0.009724921206466531</v>
       </c>
       <c r="BH3">
-        <v>50309.47874307626</v>
+        <v>51414.29831508844</v>
       </c>
       <c r="BI3">
-        <v>50309.47874307626</v>
+        <v>51414.29831508844</v>
       </c>
       <c r="BJ3">
-        <v>60773.0845807704</v>
+        <v>62107.68980773525</v>
       </c>
       <c r="BK3">
-        <v>503.0947874307626</v>
+        <v>514.1429831508844</v>
       </c>
       <c r="BL3">
-        <v>0.005030947874307626</v>
+        <v>0.005141429831508845</v>
       </c>
       <c r="BM3">
         <v>500</v>
@@ -1425,19 +1425,19 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>0.01095694989739418</v>
+        <v>0.01088091363525142</v>
       </c>
       <c r="BP3">
-        <v>0.005197309855101563</v>
+        <v>0.01141976670902999</v>
       </c>
       <c r="BQ3">
-        <v>0.005870508671643774</v>
+        <v>0.009937944182096871</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT3" t="s">
         <v>132</v>
@@ -1449,7 +1449,7 @@
         <v>134</v>
       </c>
       <c r="BW3" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1457,7 +1457,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1580,10 +1580,10 @@
         <v>4262.719999999999</v>
       </c>
       <c r="AQ4">
-        <v>4305.138982475778</v>
+        <v>4304.768330617102</v>
       </c>
       <c r="AR4">
-        <v>4663.44994158593</v>
+        <v>4662.214435390344</v>
       </c>
       <c r="AS4">
         <v>4262.719999999999</v>
@@ -1592,19 +1592,19 @@
         <v>4068.219999999998</v>
       </c>
       <c r="AU4">
-        <v>4305.138982475778</v>
+        <v>4304.768330617102</v>
       </c>
       <c r="AV4">
         <v>4129.0825</v>
       </c>
       <c r="AW4">
-        <v>0.009951153835058051</v>
+        <v>0.009864201875117929</v>
       </c>
       <c r="AX4">
-        <v>0.3174182581668962</v>
+        <v>0.314644696414574</v>
       </c>
       <c r="AY4">
-        <v>0.009951153835058051</v>
+        <v>0.009864201875117929</v>
       </c>
       <c r="AZ4">
         <v>0.3</v>
@@ -1652,19 +1652,19 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>320.1622584956892</v>
+        <v>305.5169508484249</v>
       </c>
       <c r="BP4">
-        <v>67.44203602450197</v>
+        <v>116.1268631192649</v>
       </c>
       <c r="BQ4">
-        <v>51.43661626901583</v>
+        <v>130.8395447036675</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT4" t="s">
         <v>132</v>
@@ -1676,7 +1676,7 @@
         <v>134</v>
       </c>
       <c r="BW4" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1684,7 +1684,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1807,10 +1807,10 @@
         <v>158.8345</v>
       </c>
       <c r="AQ5">
-        <v>159.933285388434</v>
+        <v>160.0434672698141</v>
       </c>
       <c r="AR5">
-        <v>161.8257466085711</v>
+        <v>161.8203770121322</v>
       </c>
       <c r="AS5">
         <v>158.8345</v>
@@ -1819,28 +1819,28 @@
         <v>157.5925</v>
       </c>
       <c r="AU5">
-        <v>159.933285388434</v>
+        <v>160.0434672698141</v>
       </c>
       <c r="AV5">
         <v>156.96075</v>
       </c>
       <c r="AW5">
-        <v>0.006917800530955059</v>
+        <v>0.007611490386623247</v>
       </c>
       <c r="AX5">
-        <v>0.5864098137072634</v>
+        <v>0.6452126856913216</v>
       </c>
       <c r="AY5">
-        <v>0.006917800530955059</v>
+        <v>0.007611490386623247</v>
       </c>
       <c r="AZ5">
-        <v>0.4942743907707793</v>
+        <v>0.5209629474778172</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3057256092292207</v>
+        <v>0.2790370525221827</v>
       </c>
       <c r="BC5" t="s">
         <v>124</v>
@@ -1879,19 +1879,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>3.41472060012922</v>
+        <v>3.093341245208128</v>
       </c>
       <c r="BP5">
-        <v>2.347726812158319</v>
+        <v>4.089290112093337</v>
       </c>
       <c r="BQ5">
-        <v>4.56988287492687</v>
+        <v>5.911399607745481</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT5" t="s">
         <v>132</v>
@@ -1903,7 +1903,7 @@
         <v>134</v>
       </c>
       <c r="BW5" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1911,7 +1911,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -2034,10 +2034,10 @@
         <v>0.7025399999999999</v>
       </c>
       <c r="AQ6">
-        <v>0.6983141942360814</v>
+        <v>0.6990881268516193</v>
       </c>
       <c r="AR6">
-        <v>0.7031721391760661</v>
+        <v>0.7032958382939281</v>
       </c>
       <c r="AS6">
         <v>0.7025399999999999</v>
@@ -2046,28 +2046,28 @@
         <v>0.6894799999999999</v>
       </c>
       <c r="AU6">
-        <v>0.6983141942360814</v>
+        <v>0.6990881268516193</v>
       </c>
       <c r="AV6">
         <v>0.7097487499999999</v>
       </c>
       <c r="AW6">
-        <v>-0.006015039377001326</v>
+        <v>-0.004913418664247859</v>
       </c>
       <c r="AX6">
-        <v>0.5862050652219249</v>
+        <v>0.4788448966021466</v>
       </c>
       <c r="AY6">
-        <v>0.006015039377001326</v>
+        <v>0.004913418664247859</v>
       </c>
       <c r="AZ6">
-        <v>0.4544355090224217</v>
+        <v>0.506384535109537</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3455644909775782</v>
+        <v>0.293615464890463</v>
       </c>
       <c r="BC6" t="s">
         <v>125</v>
@@ -2106,19 +2106,19 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO6">
-        <v>0.01102162549689513</v>
+        <v>0.01007628104207423</v>
       </c>
       <c r="BP6">
-        <v>0.007030650633555798</v>
+        <v>0.01261362464852814</v>
       </c>
       <c r="BQ6">
-        <v>0.009133833196351204</v>
+        <v>0.01610499004676101</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT6" t="s">
         <v>132</v>
@@ -2130,7 +2130,7 @@
         <v>134</v>
       </c>
       <c r="BW6" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2138,7 +2138,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2261,10 +2261,10 @@
         <v>4.72165</v>
       </c>
       <c r="AQ7">
-        <v>4.68273362221265</v>
+        <v>4.688249181472372</v>
       </c>
       <c r="AR7">
-        <v>4.714347275326612</v>
+        <v>4.715631365816517</v>
       </c>
       <c r="AS7">
         <v>4.72165</v>
@@ -2273,28 +2273,28 @@
         <v>4.625150000000001</v>
       </c>
       <c r="AU7">
-        <v>4.68273362221265</v>
+        <v>4.688249181472372</v>
       </c>
       <c r="AV7">
         <v>4.76407</v>
       </c>
       <c r="AW7">
-        <v>-0.00824211404643509</v>
+        <v>-0.007073971710657973</v>
       </c>
       <c r="AX7">
-        <v>0.9174063599092488</v>
+        <v>0.7873837465258909</v>
       </c>
       <c r="AY7">
-        <v>0.00824211404643509</v>
+        <v>0.007073971710657973</v>
       </c>
       <c r="AZ7">
-        <v>0.4292017000795932</v>
+        <v>0.4840685270068787</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3707982999204068</v>
+        <v>0.3159314729931212</v>
       </c>
       <c r="BC7" t="s">
         <v>126</v>
@@ -2333,19 +2333,19 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="BO7">
-        <v>0.08290391528818435</v>
+        <v>0.07519595145155746</v>
       </c>
       <c r="BP7">
-        <v>0.03920552985362548</v>
+        <v>0.07741028249471793</v>
       </c>
       <c r="BQ7">
-        <v>0.04851631004207464</v>
+        <v>0.0920309079316083</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT7" t="s">
         <v>132</v>
@@ -2357,7 +2357,7 @@
         <v>134</v>
       </c>
       <c r="BW7" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2365,7 +2365,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2488,10 +2488,10 @@
         <v>8.882949999999999</v>
       </c>
       <c r="AQ8">
-        <v>8.800607958564148</v>
+        <v>8.809164071008837</v>
       </c>
       <c r="AR8">
-        <v>8.908004968866212</v>
+        <v>8.907786700165374</v>
       </c>
       <c r="AS8">
         <v>8.882949999999999</v>
@@ -2500,28 +2500,28 @@
         <v>8.657249999999998</v>
       </c>
       <c r="AU8">
-        <v>8.800607958564148</v>
+        <v>8.809164071008837</v>
       </c>
       <c r="AV8">
         <v>8.966125</v>
       </c>
       <c r="AW8">
-        <v>-0.009269672961780816</v>
+        <v>-0.008306466769616199</v>
       </c>
       <c r="AX8">
-        <v>0.9899854696224908</v>
+        <v>0.8871166695661198</v>
       </c>
       <c r="AY8">
-        <v>0.009269672961780816</v>
+        <v>0.008306466769616199</v>
       </c>
       <c r="AZ8">
-        <v>0.391688982309069</v>
+        <v>0.4261813576149057</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.408311017690931</v>
+        <v>0.3738186423850944</v>
       </c>
       <c r="BC8" t="s">
         <v>127</v>
@@ -2560,19 +2560,19 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO8">
-        <v>0.1888477955742677</v>
+        <v>0.1798180798935454</v>
       </c>
       <c r="BP8">
-        <v>0.08253188420158984</v>
+        <v>0.1524718721761815</v>
       </c>
       <c r="BQ8">
-        <v>0.0706913560646502</v>
+        <v>0.1153327476188802</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT8" t="s">
         <v>132</v>
@@ -2584,7 +2584,7 @@
         <v>134</v>
       </c>
       <c r="BW8" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2592,7 +2592,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2715,10 +2715,10 @@
         <v>1.321695</v>
       </c>
       <c r="AQ9">
-        <v>1.308638105134802</v>
+        <v>1.309876720296334</v>
       </c>
       <c r="AR9">
-        <v>1.319759361373311</v>
+        <v>1.319725828260172</v>
       </c>
       <c r="AS9">
         <v>1.321695</v>
@@ -2727,28 +2727,28 @@
         <v>1.289945</v>
       </c>
       <c r="AU9">
-        <v>1.308638105134802</v>
+        <v>1.309876720296334</v>
       </c>
       <c r="AV9">
         <v>1.3348575</v>
       </c>
       <c r="AW9">
-        <v>-0.009878901611338226</v>
+        <v>-0.008941760166805588</v>
       </c>
       <c r="AX9">
-        <v>0.9919768178687719</v>
+        <v>0.897875001228197</v>
       </c>
       <c r="AY9">
-        <v>0.009878901611338226</v>
+        <v>0.008941760166805588</v>
       </c>
       <c r="AZ9">
-        <v>0.4139986424747509</v>
+        <v>0.4560558281885464</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3860013575252492</v>
+        <v>0.3439441718114536</v>
       </c>
       <c r="BC9" t="s">
         <v>128</v>
@@ -2787,19 +2787,19 @@
         <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.02531051245703349</v>
+        <v>0.02454799163954378</v>
       </c>
       <c r="BP9">
-        <v>0.01444960636967392</v>
+        <v>0.02533765547909182</v>
       </c>
       <c r="BQ9">
-        <v>0.01312590211303527</v>
+        <v>0.02216938074301786</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT9" t="s">
         <v>132</v>
@@ -2811,7 +2811,7 @@
         <v>134</v>
       </c>
       <c r="BW9" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2819,7 +2819,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2942,10 +2942,10 @@
         <v>1.136865</v>
       </c>
       <c r="AQ10">
-        <v>1.116328890809298</v>
+        <v>1.116006329931233</v>
       </c>
       <c r="AR10">
-        <v>1.107215933432272</v>
+        <v>1.107309279688594</v>
       </c>
       <c r="AS10">
         <v>1.136865</v>
@@ -2954,28 +2954,28 @@
         <v>1.11553</v>
       </c>
       <c r="AU10">
-        <v>1.116328890809298</v>
+        <v>1.116006329931233</v>
       </c>
       <c r="AV10">
-        <v>1.150555739460468</v>
+        <v>1.150770780045844</v>
       </c>
       <c r="AW10">
-        <v>-0.01806380633646244</v>
+        <v>-0.01834753472819265</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01806380633646244</v>
+        <v>0.01834753472819265</v>
       </c>
       <c r="AZ10">
-        <v>0.4171375298057224</v>
+        <v>0.4611116696802749</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3828624701942777</v>
+        <v>0.338888330319725</v>
       </c>
       <c r="BC10" t="s">
         <v>129</v>
@@ -2990,22 +2990,22 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01204253755764162</v>
+        <v>0.0122316898187951</v>
       </c>
       <c r="BH10">
-        <v>41519.4885302827</v>
+        <v>40877.42637421239</v>
       </c>
       <c r="BI10">
-        <v>41519.4885302827</v>
+        <v>40877.42637421239</v>
       </c>
       <c r="BJ10">
-        <v>36521.0368252015</v>
+        <v>35956.27130240828</v>
       </c>
       <c r="BK10">
-        <v>415.1948853028269</v>
+        <v>408.7742637421239</v>
       </c>
       <c r="BL10">
-        <v>0.004151948853028269</v>
+        <v>0.004087742637421239</v>
       </c>
       <c r="BM10">
         <v>500</v>
@@ -3014,19 +3014,19 @@
         <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.02117500617395042</v>
+        <v>0.02018746237398035</v>
       </c>
       <c r="BP10">
-        <v>0.01053520678721724</v>
+        <v>0.01933487885535643</v>
       </c>
       <c r="BQ10">
-        <v>0.01097458477039072</v>
+        <v>0.01907625328524329</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT10" t="s">
         <v>132</v>
@@ -3038,7 +3038,7 @@
         <v>134</v>
       </c>
       <c r="BW10" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3046,7 +3046,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3169,10 +3169,10 @@
         <v>7.6368</v>
       </c>
       <c r="AQ11">
-        <v>7.469763581265449</v>
+        <v>7.467011684903857</v>
       </c>
       <c r="AR11">
-        <v>7.378993192574002</v>
+        <v>7.380758517932839</v>
       </c>
       <c r="AS11">
         <v>7.6368</v>
@@ -3181,28 +3181,28 @@
         <v>7.477300000000001</v>
       </c>
       <c r="AU11">
-        <v>7.469763581265449</v>
+        <v>7.467011684903857</v>
       </c>
       <c r="AV11">
-        <v>7.748157612489701</v>
+        <v>7.749992210064096</v>
       </c>
       <c r="AW11">
-        <v>-0.02187256687808394</v>
+        <v>-0.0222329136675235</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.02187256687808394</v>
+        <v>0.0222329136675235</v>
       </c>
       <c r="AZ11">
-        <v>0.4011565400924744</v>
+        <v>0.4369967623533516</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3988434599075256</v>
+        <v>0.3630032376466484</v>
       </c>
       <c r="BC11" t="s">
         <v>130</v>
@@ -3217,43 +3217,43 @@
         <v>474.7997172514067</v>
       </c>
       <c r="BG11">
-        <v>0.01458171125205596</v>
+        <v>0.01482194244501567</v>
       </c>
       <c r="BH11">
-        <v>34289.52825612303</v>
+        <v>33733.77017586115</v>
       </c>
       <c r="BI11">
-        <v>32561.31664138268</v>
+        <v>32033.56908264562</v>
       </c>
       <c r="BJ11">
-        <v>4263.738298944934</v>
+        <v>4194.632448492251</v>
       </c>
       <c r="BK11">
-        <v>325.6131664138268</v>
+        <v>320.3356908264562</v>
       </c>
       <c r="BL11">
-        <v>0.003256131664138268</v>
+        <v>0.003203356908264562</v>
       </c>
       <c r="BM11">
-        <v>474.7997172514068</v>
+        <v>474.7997172514067</v>
       </c>
       <c r="BN11">
         <v>0.004747997172514068</v>
       </c>
       <c r="BO11">
-        <v>0.1546083954209371</v>
+        <v>0.1411157968947358</v>
       </c>
       <c r="BP11">
-        <v>0.06266540545624545</v>
+        <v>0.1214848986263434</v>
       </c>
       <c r="BQ11">
-        <v>0.06294276564810321</v>
+        <v>0.1017110072039362</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.03767976884466208</v>
+        <v>0.03767326983038256</v>
       </c>
       <c r="BT11" t="s">
         <v>132</v>
@@ -3265,7 +3265,7 @@
         <v>134</v>
       </c>
       <c r="BW11" s="2">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="128">
   <si>
     <t>Pair</t>
   </si>
@@ -256,15 +256,15 @@
     <t>AUDUSD</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
@@ -325,9 +325,6 @@
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
     <t>空头减速</t>
   </si>
   <si>
@@ -337,24 +334,12 @@
     <t>空头加速</t>
   </si>
   <si>
-    <t>多头减速</t>
-  </si>
-  <si>
-    <t>NEUTRAL</t>
-  </si>
-  <si>
-    <t>TRANSITION</t>
-  </si>
-  <si>
     <t>下跌</t>
   </si>
   <si>
     <t>上涨</t>
   </si>
   <si>
-    <t>转换</t>
-  </si>
-  <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
@@ -364,9 +349,6 @@
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
     <t>下降谷底收敛</t>
   </si>
   <si>
@@ -376,37 +358,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>地形转换区</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04497,naive=0.01521,drift4=0.02406; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01088,naive=0.01142,drift4=0.009938; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=305.5,naive=116.1,drift4=130.8; naive_cap_applied; model_divergence_guard(abs=496.7,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.52,naive=0.20,drift4=0.28); metric_best=model; scores=model=3.093,naive=4.089,drift4=5.911; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=0.01008,naive=0.01261,drift4=0.0161; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=model; scores=model=0.0752,naive=0.07741,drift4=0.09203; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.1798,naive=0.1525,drift4=0.1153; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.02455,naive=0.02534,drift4=0.02217; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.02019,naive=0.01933,drift4=0.01908; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.1411,naive=0.1215,drift4=0.1017; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.05213,naive=0.02158,drift4=0.03061; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01073,naive=0.01163,drift4=0.009811; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=276.1,naive=80.13,drift4=99.93; naive_cap_applied; model_divergence_guard(abs=499,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=2.973,naive=3.263,drift4=5.117; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=0.009241,naive=0.012,drift4=0.01517; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.02237,naive=0.02261,drift4=0.01962; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=model; scores=model=0.0762,naive=0.08789,drift4=0.09885; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.1851,naive=0.1588,drift4=0.1198; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.02039,naive=0.01655,drift4=0.01643; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.1323,naive=0.1173,drift4=0.09759; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1039,19 +1018,19 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K2">
-        <v>0.03357562127703215</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>2.49205161606413</v>
+        <v>1.857568777251797</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O2" t="s">
         <v>90</v>
@@ -1066,13 +1045,13 @@
         <v>100</v>
       </c>
       <c r="S2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T2">
-        <v>-0.9752996702053002</v>
+        <v>-0.8754554507866911</v>
       </c>
       <c r="U2">
-        <v>0.8438188640126402</v>
+        <v>0.7937111193351427</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1081,91 +1060,91 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.999590676914801</v>
+        <v>0.9990246659245268</v>
       </c>
       <c r="Y2">
-        <v>0.3195501221615862</v>
+        <v>0.2831373626789613</v>
       </c>
       <c r="Z2">
-        <v>160.8929859153165</v>
+        <v>135.8800085737004</v>
       </c>
       <c r="AA2">
-        <v>-11</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AB2">
-        <v>-0.9449088474309428</v>
+        <v>-0.7178834387986207</v>
       </c>
       <c r="AC2">
-        <v>0.3273335761065877</v>
+        <v>0.6961633201330468</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
       </c>
       <c r="AE2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AF2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AG2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="AH2">
-        <v>-0.6231721093467566</v>
+        <v>-0.4601223200769247</v>
       </c>
       <c r="AI2">
-        <v>0.8433063414120239</v>
+        <v>0.7676310761284897</v>
       </c>
       <c r="AJ2">
-        <v>-1.953534880719627</v>
+        <v>-1.499617419309893</v>
       </c>
       <c r="AK2">
-        <v>0.6295166517535071</v>
+        <v>1.348309231129061</v>
       </c>
       <c r="AL2">
-        <v>-2.867520626012551</v>
+        <v>-1.95746081059966</v>
       </c>
       <c r="AM2">
-        <v>4.217005378068214</v>
+        <v>3.872641928994977</v>
       </c>
       <c r="AN2">
-        <v>2.504716256557524</v>
+        <v>1.646006478955865</v>
       </c>
       <c r="AO2">
-        <v>0.02622049446504374</v>
+        <v>0.02680040746982128</v>
       </c>
       <c r="AP2">
-        <v>6.71509</v>
+        <v>6.722295</v>
       </c>
       <c r="AQ2">
-        <v>6.709012637539413</v>
+        <v>6.720241318443436</v>
       </c>
       <c r="AR2">
-        <v>6.71483882001394</v>
+        <v>6.725128981574848</v>
       </c>
       <c r="AS2">
-        <v>6.71509</v>
+        <v>6.722295</v>
       </c>
       <c r="AT2">
-        <v>6.698955</v>
+        <v>6.713365</v>
       </c>
       <c r="AW2">
-        <v>-0.0009050306787529594</v>
+        <v>-0.0003055030397452295</v>
       </c>
       <c r="AY2">
-        <v>0.0009050306787529594</v>
+        <v>0.0003055030397452295</v>
       </c>
       <c r="AZ2">
-        <v>0.4300374553110444</v>
+        <v>0.432703707588168</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3699625446889556</v>
+        <v>0.367296292411832</v>
       </c>
       <c r="BC2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1198,28 +1177,28 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.04496546289982566</v>
+        <v>0.05212607627081053</v>
       </c>
       <c r="BP2">
-        <v>0.0152110084154809</v>
+        <v>0.02158252790607651</v>
       </c>
       <c r="BQ2">
-        <v>0.02405827726993014</v>
+        <v>0.0306111139410063</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="BW2" s="2">
         <v>46318</v>
@@ -1254,19 +1233,19 @@
         <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2.376780171594311</v>
+        <v>2.488771664565861</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1281,13 +1260,13 @@
         <v>101</v>
       </c>
       <c r="S3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T3">
-        <v>0.9572287493821052</v>
+        <v>0.9753638670405722</v>
       </c>
       <c r="U3">
-        <v>0.9806592389820111</v>
+        <v>0.9888294149974884</v>
       </c>
       <c r="V3" t="s">
         <v>94</v>
@@ -1296,100 +1275,100 @@
         <v>95</v>
       </c>
       <c r="X3">
-        <v>0.999625207040255</v>
+        <v>0.9996626993169238</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>23.87346857120675</v>
+        <v>18.06239721480294</v>
       </c>
       <c r="AA3">
-        <v>-25</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AB3">
-        <v>0.9144414623902793</v>
+        <v>0.9507194214928271</v>
       </c>
       <c r="AC3">
-        <v>0.4047181882020221</v>
+        <v>0.3100525465084012</v>
       </c>
       <c r="AD3" t="s">
         <v>94</v>
       </c>
       <c r="AE3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AF3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="AG3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="AH3">
-        <v>0.9140987361680766</v>
+        <v>0.9503987431825437</v>
       </c>
       <c r="AI3">
-        <v>0.9675472119477917</v>
+        <v>0.9783500314562832</v>
       </c>
       <c r="AJ3">
-        <v>1.770806310825148</v>
+        <v>1.85546613991107</v>
       </c>
       <c r="AK3">
-        <v>0.8942736127801956</v>
+        <v>0.699775371572142</v>
       </c>
       <c r="AL3">
-        <v>3.122413841577219</v>
+        <v>3.25965202062125</v>
       </c>
       <c r="AM3">
-        <v>-2.63079051722874</v>
+        <v>-2.679407041876462</v>
       </c>
       <c r="AN3">
-        <v>2.850120757434095</v>
+        <v>2.98272762231678</v>
       </c>
       <c r="AO3">
-        <v>0.04436032822254267</v>
+        <v>0.04498493168325392</v>
       </c>
       <c r="AP3">
-        <v>0.827825</v>
+        <v>0.8285</v>
       </c>
       <c r="AQ3">
-        <v>0.8399007993466148</v>
+        <v>0.8430604394689205</v>
       </c>
       <c r="AR3">
-        <v>0.8401192461457658</v>
+        <v>0.8457239108482708</v>
       </c>
       <c r="AS3">
-        <v>0.827825</v>
+        <v>0.8285</v>
       </c>
       <c r="AT3">
-        <v>0.8466500000000001</v>
+        <v>0.8480000000000001</v>
       </c>
       <c r="AU3">
-        <v>0.8399007993466148</v>
+        <v>0.8430604394689205</v>
       </c>
       <c r="AV3">
-        <v>0.8197744671022569</v>
+        <v>0.818793040354053</v>
       </c>
       <c r="AW3">
-        <v>0.0145873818096998</v>
+        <v>0.01757445922621665</v>
       </c>
       <c r="AX3">
         <v>1.5</v>
       </c>
       <c r="AY3">
-        <v>0.0145873818096998</v>
+        <v>0.01757445922621665</v>
       </c>
       <c r="AZ3">
-        <v>0.4569458166687104</v>
+        <v>0.4567310249204258</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3430541833312897</v>
+        <v>0.3432689750795742</v>
       </c>
       <c r="BC3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1401,22 +1380,22 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009724921206466531</v>
+        <v>0.0117163061508111</v>
       </c>
       <c r="BH3">
-        <v>51414.29831508844</v>
+        <v>42675.56630597143</v>
       </c>
       <c r="BI3">
-        <v>51414.29831508844</v>
+        <v>42675.56630597143</v>
       </c>
       <c r="BJ3">
-        <v>62107.68980773525</v>
+        <v>51509.43428602465</v>
       </c>
       <c r="BK3">
-        <v>514.1429831508844</v>
+        <v>426.7556630597143</v>
       </c>
       <c r="BL3">
-        <v>0.005141429831508845</v>
+        <v>0.004267556630597144</v>
       </c>
       <c r="BM3">
         <v>500</v>
@@ -1425,28 +1404,28 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>0.01088091363525142</v>
+        <v>0.0107281469549552</v>
       </c>
       <c r="BP3">
-        <v>0.01141976670902999</v>
+        <v>0.01162693307989298</v>
       </c>
       <c r="BQ3">
-        <v>0.009937944182096871</v>
+        <v>0.009810652487100925</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU3" t="s">
         <v>91</v>
       </c>
       <c r="BV3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW3" s="2">
         <v>46318</v>
@@ -1481,19 +1460,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.313230502143933</v>
+        <v>0.3506227820907868</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>96</v>
@@ -1508,13 +1487,13 @@
         <v>102</v>
       </c>
       <c r="S4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T4">
-        <v>-0.7779212152637645</v>
+        <v>-0.7708715311066867</v>
       </c>
       <c r="U4">
-        <v>0.7498208223188599</v>
+        <v>0.7467909939190269</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1523,88 +1502,88 @@
         <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9990251018006636</v>
+        <v>0.9995952196840717</v>
       </c>
       <c r="Y4">
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>-110.4389089368781</v>
+        <v>-109.1960761664299</v>
       </c>
       <c r="AA4">
-        <v>-27</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AB4">
-        <v>-0.3492084648411762</v>
+        <v>-0.3288019714707134</v>
       </c>
       <c r="AC4">
-        <v>-0.937045061927797</v>
+        <v>-0.9443988900655126</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
       </c>
       <c r="AE4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF4" t="s">
         <v>110</v>
       </c>
-      <c r="AF4" t="s">
-        <v>115</v>
-      </c>
       <c r="AG4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AH4">
-        <v>-0.1744340110688048</v>
+        <v>-0.1643344394524118</v>
       </c>
       <c r="AI4">
-        <v>0.585867111841665</v>
+        <v>0.5838487033228706</v>
       </c>
       <c r="AJ4">
-        <v>-0.2059344731686537</v>
+        <v>-0.2435543012591954</v>
       </c>
       <c r="AK4">
-        <v>-0.6807757311370635</v>
+        <v>-0.7745960668631813</v>
       </c>
       <c r="AL4">
-        <v>-0.6926233149025872</v>
+        <v>-0.5990815336725037</v>
       </c>
       <c r="AM4">
-        <v>-0.482024643841854</v>
+        <v>0.03399497494145383</v>
       </c>
       <c r="AN4">
-        <v>0.7153250269384762</v>
+        <v>0.5748397811172627</v>
       </c>
       <c r="AO4">
-        <v>0.1236947549394671</v>
+        <v>0.09766810005178962</v>
       </c>
       <c r="AP4">
-        <v>4262.719999999999</v>
+        <v>4304.280000000001</v>
       </c>
       <c r="AQ4">
-        <v>4304.768330617102</v>
+        <v>4369.851759244538</v>
       </c>
       <c r="AR4">
-        <v>4662.214435390344</v>
+        <v>4726.772530815125</v>
       </c>
       <c r="AS4">
-        <v>4262.719999999999</v>
+        <v>4304.280000000001</v>
       </c>
       <c r="AT4">
-        <v>4068.219999999998</v>
+        <v>4151.340000000001</v>
       </c>
       <c r="AU4">
-        <v>4304.768330617102</v>
+        <v>4369.851759244538</v>
       </c>
       <c r="AV4">
-        <v>4129.0825</v>
+        <v>4170.642500000001</v>
       </c>
       <c r="AW4">
-        <v>0.009864201875117929</v>
+        <v>0.01523408310903034</v>
       </c>
       <c r="AX4">
-        <v>0.314644696414574</v>
+        <v>0.4906688560062636</v>
       </c>
       <c r="AY4">
-        <v>0.009864201875117929</v>
+        <v>0.01523408310903034</v>
       </c>
       <c r="AZ4">
         <v>0.3</v>
@@ -1616,7 +1595,7 @@
         <v>0.4</v>
       </c>
       <c r="BC4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1628,22 +1607,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.03135028807897309</v>
+        <v>0.03104758519427178</v>
       </c>
       <c r="BH4">
-        <v>15948.81676176221</v>
+        <v>16104.31203816292</v>
       </c>
       <c r="BI4">
-        <v>15948.81676176221</v>
+        <v>16104.31203816292</v>
       </c>
       <c r="BJ4">
         <v>3.741464783462721</v>
       </c>
       <c r="BK4">
-        <v>159.4881676176221</v>
+        <v>161.0431203816292</v>
       </c>
       <c r="BL4">
-        <v>0.001594881676176221</v>
+        <v>0.001610431203816292</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1652,28 +1631,28 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>305.5169508484249</v>
+        <v>276.110614441147</v>
       </c>
       <c r="BP4">
-        <v>116.1268631192649</v>
+        <v>80.13314278191893</v>
       </c>
       <c r="BQ4">
-        <v>130.8395447036675</v>
+        <v>99.92928043991822</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT4" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU4" t="s">
         <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW4" s="2">
         <v>46318</v>
@@ -1708,19 +1687,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.2376599206115991</v>
+        <v>0.2841135154704187</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O5" t="s">
         <v>96</v>
@@ -1735,13 +1714,13 @@
         <v>100</v>
       </c>
       <c r="S5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T5">
-        <v>-0.5202907831583916</v>
+        <v>-0.614006259335212</v>
       </c>
       <c r="U5">
-        <v>0.6340495393606566</v>
+        <v>0.6762239512074667</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1750,100 +1729,100 @@
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9996747477575215</v>
+        <v>0.999684538026485</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0.4977826390295005</v>
       </c>
       <c r="Z5">
-        <v>101.3254505345612</v>
+        <v>103.1243080525524</v>
       </c>
       <c r="AA5">
-        <v>-19</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AB5">
-        <v>-0.1963817096377843</v>
+        <v>-0.2270645017380868</v>
       </c>
       <c r="AC5">
-        <v>0.9805275233871515</v>
+        <v>0.9738797215521198</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AF5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="AH5">
-        <v>-0.1963178360463429</v>
+        <v>-0.1699929910747425</v>
       </c>
       <c r="AI5">
-        <v>0.7405993536458721</v>
+        <v>0.6501038832630816</v>
       </c>
       <c r="AJ5">
-        <v>-0.5496875005070285</v>
+        <v>-0.4469555849811924</v>
       </c>
       <c r="AK5">
-        <v>2.325902149472054</v>
+        <v>1.667747666634527</v>
       </c>
       <c r="AL5">
-        <v>0.132020877264693</v>
+        <v>-0.04342638805186327</v>
       </c>
       <c r="AM5">
-        <v>2.911735307341218</v>
+        <v>1.64989536827254</v>
       </c>
       <c r="AN5">
-        <v>0.5490395199594185</v>
+        <v>0.2156359868502796</v>
       </c>
       <c r="AO5">
-        <v>0.1213421397373044</v>
+        <v>0.1164105558234287</v>
       </c>
       <c r="AP5">
-        <v>158.8345</v>
+        <v>157.572</v>
       </c>
       <c r="AQ5">
-        <v>160.0434672698141</v>
+        <v>158.2600477851997</v>
       </c>
       <c r="AR5">
-        <v>161.8203770121322</v>
+        <v>160.3176687971889</v>
       </c>
       <c r="AS5">
-        <v>158.8345</v>
+        <v>157.572</v>
       </c>
       <c r="AT5">
-        <v>157.5925</v>
+        <v>155.0675</v>
       </c>
       <c r="AU5">
-        <v>160.0434672698141</v>
+        <v>158.2600477851997</v>
       </c>
       <c r="AV5">
-        <v>156.96075</v>
+        <v>156.073875</v>
       </c>
       <c r="AW5">
-        <v>0.007611490386623247</v>
+        <v>0.004366561224073439</v>
       </c>
       <c r="AX5">
-        <v>0.6452126856913216</v>
+        <v>0.4592726142342546</v>
       </c>
       <c r="AY5">
-        <v>0.007611490386623247</v>
+        <v>0.004366561224073439</v>
       </c>
       <c r="AZ5">
-        <v>0.5209629474778172</v>
+        <v>0.5126783326739646</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.2790370525221827</v>
+        <v>0.2873216673260355</v>
       </c>
       <c r="BC5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1855,22 +1834,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.01179687032729032</v>
+        <v>0.009507558449470819</v>
       </c>
       <c r="BH5">
-        <v>42384.12274849913</v>
+        <v>52589.73717146377</v>
       </c>
       <c r="BI5">
-        <v>42384.12274849913</v>
+        <v>52589.73717146377</v>
       </c>
       <c r="BJ5">
-        <v>266.8445630420289</v>
+        <v>333.7505214851863</v>
       </c>
       <c r="BK5">
-        <v>423.8412274849914</v>
+        <v>525.8973717146378</v>
       </c>
       <c r="BL5">
-        <v>0.004238412274849914</v>
+        <v>0.005258973717146378</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1879,28 +1858,28 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>3.093341245208128</v>
+        <v>2.972561820729688</v>
       </c>
       <c r="BP5">
-        <v>4.089290112093337</v>
+        <v>3.26335193352986</v>
       </c>
       <c r="BQ5">
-        <v>5.911399607745481</v>
+        <v>5.116634297740439</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW5" s="2">
         <v>46318</v>
@@ -1932,145 +1911,145 @@
         <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.2689586953865793</v>
+        <v>0.566725038997936</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T6">
-        <v>0.2070180677677997</v>
+        <v>-0.5250351037526458</v>
       </c>
       <c r="U6">
-        <v>0.3680812380767515</v>
+        <v>0.6362120452480466</v>
       </c>
       <c r="V6" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="W6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9996924303249665</v>
+        <v>0.999784994237424</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-96.5215785744879</v>
+        <v>-101.7923206715223</v>
       </c>
       <c r="AA6">
-        <v>-17</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB6">
-        <v>-0.1135774019538207</v>
+        <v>-0.2043648528338475</v>
       </c>
       <c r="AC6">
-        <v>-0.9935291509389245</v>
+        <v>-0.978894788486587</v>
       </c>
       <c r="AD6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="AE6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="AF6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="AG6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="AH6">
-        <v>-0.1135424689892106</v>
+        <v>-0.2043209132128203</v>
       </c>
       <c r="AI6">
-        <v>0.6959674270694126</v>
+        <v>0.7374858102473283</v>
       </c>
       <c r="AJ6">
-        <v>-0.1784819731560597</v>
+        <v>-0.4230599295764431</v>
       </c>
       <c r="AK6">
-        <v>-2.255471694803508</v>
+        <v>-2.325626394417131</v>
       </c>
       <c r="AL6">
-        <v>-1.192907343146901</v>
+        <v>-1.404634614757629</v>
       </c>
       <c r="AM6">
-        <v>-1.471257199994455</v>
+        <v>-0.5117315277336331</v>
       </c>
       <c r="AN6">
-        <v>1.236629001477036</v>
+        <v>1.360152190851854</v>
       </c>
       <c r="AO6">
-        <v>0.2533209608698126</v>
+        <v>0.1583226239061616</v>
       </c>
       <c r="AP6">
-        <v>0.7025399999999999</v>
+        <v>0.70316</v>
       </c>
       <c r="AQ6">
-        <v>0.6990881268516193</v>
+        <v>0.7000953935816343</v>
       </c>
       <c r="AR6">
-        <v>0.7032958382939281</v>
+        <v>0.7042626552707765</v>
       </c>
       <c r="AS6">
-        <v>0.7025399999999999</v>
+        <v>0.70316</v>
       </c>
       <c r="AT6">
-        <v>0.6894799999999999</v>
+        <v>0.69072</v>
       </c>
       <c r="AU6">
-        <v>0.6990881268516193</v>
+        <v>0.7000953935816343</v>
       </c>
       <c r="AV6">
-        <v>0.7097487499999999</v>
+        <v>0.71036875</v>
       </c>
       <c r="AW6">
-        <v>-0.004913418664247859</v>
+        <v>-0.00435833440236319</v>
       </c>
       <c r="AX6">
-        <v>0.4788448966021466</v>
+        <v>0.4251231376265969</v>
       </c>
       <c r="AY6">
-        <v>0.004913418664247859</v>
+        <v>0.00435833440236319</v>
       </c>
       <c r="AZ6">
-        <v>0.506384535109537</v>
+        <v>0.5085703980442011</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.293615464890463</v>
+        <v>0.2914296019557989</v>
       </c>
       <c r="BC6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2079,55 +2058,55 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG6">
-        <v>0.01026098158111984</v>
+        <v>0.01025193412594563</v>
       </c>
       <c r="BH6">
-        <v>48728.28160221999</v>
+        <v>48771.28489682724</v>
       </c>
       <c r="BI6">
-        <v>48728.28160221999</v>
+        <v>36578.46367262043</v>
       </c>
       <c r="BJ6">
-        <v>69360.15259233637</v>
+        <v>52020.11444425228</v>
       </c>
       <c r="BK6">
-        <v>487.2828160221999</v>
+        <v>365.7846367262043</v>
       </c>
       <c r="BL6">
-        <v>0.004872828160221999</v>
+        <v>0.003657846367262043</v>
       </c>
       <c r="BM6">
-        <v>500.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="BN6">
-        <v>0.005000000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="BO6">
-        <v>0.01007628104207423</v>
+        <v>0.009240600538895163</v>
       </c>
       <c r="BP6">
-        <v>0.01261362464852814</v>
+        <v>0.01200096255836485</v>
       </c>
       <c r="BQ6">
-        <v>0.01610499004676101</v>
+        <v>0.01517019156202318</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT6" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU6" t="s">
         <v>92</v>
       </c>
       <c r="BV6" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW6" s="2">
         <v>46318</v>
@@ -2162,19 +2141,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0.4830108028346309</v>
+        <v>2.204056462375657</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O7" t="s">
         <v>95</v>
@@ -2183,19 +2162,19 @@
         <v>98</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R7" t="s">
         <v>102</v>
       </c>
       <c r="S7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T7">
-        <v>-0.6570892863706981</v>
+        <v>-0.8002262984732403</v>
       </c>
       <c r="U7">
-        <v>0.6955935713688013</v>
+        <v>0.9100712051909596</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2204,100 +2183,100 @@
         <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9996135700079486</v>
+        <v>0.9998774835120062</v>
       </c>
       <c r="Y7">
-        <v>0.6133263391396896</v>
+        <v>1</v>
       </c>
       <c r="Z7">
-        <v>-110.3527274422077</v>
+        <v>-126.9005655230236</v>
       </c>
       <c r="AA7">
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="AB7">
-        <v>-0.3477986132223966</v>
+        <v>-0.6004281183751474</v>
       </c>
       <c r="AC7">
-        <v>-0.9375692639163135</v>
+        <v>-0.7996787321571581</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
       </c>
       <c r="AE7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF7" t="s">
         <v>110</v>
       </c>
-      <c r="AF7" t="s">
-        <v>115</v>
-      </c>
       <c r="AG7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AH7">
-        <v>-0.2804479163329407</v>
+        <v>-0.6003545560307914</v>
       </c>
       <c r="AI7">
-        <v>0.7099677896516908</v>
+        <v>0.8707782775731258</v>
       </c>
       <c r="AJ7">
-        <v>-0.30306000469083</v>
+        <v>-1.633709510762142</v>
       </c>
       <c r="AK7">
-        <v>-0.9757644934454882</v>
+        <v>-2.271893086854237</v>
       </c>
       <c r="AL7">
-        <v>-0.8842826585876883</v>
+        <v>-2.916394408212985</v>
       </c>
       <c r="AM7">
-        <v>-0.1393141209674965</v>
+        <v>2.274414857222687</v>
       </c>
       <c r="AN7">
-        <v>0.8553251341179611</v>
+        <v>2.63505261990162</v>
       </c>
       <c r="AO7">
-        <v>0.1126787443049873</v>
+        <v>0.06204851445747073</v>
       </c>
       <c r="AP7">
-        <v>4.72165</v>
+        <v>1.325005</v>
       </c>
       <c r="AQ7">
-        <v>4.688249181472372</v>
+        <v>1.314338015591842</v>
       </c>
       <c r="AR7">
-        <v>4.715631365816517</v>
+        <v>1.323212619205391</v>
       </c>
       <c r="AS7">
-        <v>4.72165</v>
+        <v>1.325005</v>
       </c>
       <c r="AT7">
-        <v>4.625150000000001</v>
+        <v>1.296565</v>
       </c>
       <c r="AU7">
-        <v>4.688249181472372</v>
+        <v>1.314338015591842</v>
       </c>
       <c r="AV7">
-        <v>4.76407</v>
+        <v>1.3381675</v>
       </c>
       <c r="AW7">
-        <v>-0.007073971710657973</v>
+        <v>-0.008050523890972779</v>
       </c>
       <c r="AX7">
-        <v>0.7873837465258909</v>
+        <v>0.8104071725096611</v>
       </c>
       <c r="AY7">
-        <v>0.007073971710657973</v>
+        <v>0.008050523890972779</v>
       </c>
       <c r="AZ7">
-        <v>0.4840685270068787</v>
+        <v>0.4535120191674236</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3159314729931212</v>
+        <v>0.3464879808325765</v>
       </c>
       <c r="BC7" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2306,55 +2285,55 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG7">
-        <v>0.008984147490813572</v>
+        <v>0.009933924777642322</v>
       </c>
       <c r="BH7">
-        <v>55653.58321546453</v>
+        <v>50332.5735992404</v>
       </c>
       <c r="BI7">
-        <v>41740.1874115984</v>
+        <v>50332.5735992404</v>
       </c>
       <c r="BJ7">
-        <v>8840.169731258859</v>
+        <v>37986.70465337142</v>
       </c>
       <c r="BK7">
-        <v>417.401874115984</v>
+        <v>503.325735992404</v>
       </c>
       <c r="BL7">
-        <v>0.00417401874115984</v>
+        <v>0.00503325735992404</v>
       </c>
       <c r="BM7">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="BN7">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="BO7">
-        <v>0.07519595145155746</v>
+        <v>0.02236906780713557</v>
       </c>
       <c r="BP7">
-        <v>0.07741028249471793</v>
+        <v>0.02261119110357151</v>
       </c>
       <c r="BQ7">
-        <v>0.0920309079316083</v>
+        <v>0.01961867037225893</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT7" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU7" t="s">
         <v>92</v>
       </c>
       <c r="BV7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW7" s="2">
         <v>46318</v>
@@ -2389,19 +2368,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1.53164505827551</v>
+        <v>0.72159686465018</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O8" t="s">
         <v>95</v>
@@ -2410,19 +2389,19 @@
         <v>98</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R8" t="s">
         <v>102</v>
       </c>
       <c r="S8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T8">
-        <v>-0.8223711890740208</v>
+        <v>-0.6576729416402983</v>
       </c>
       <c r="U8">
-        <v>0.9200612304297192</v>
+        <v>0.6958944975982615</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2431,100 +2410,100 @@
         <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9999767813856395</v>
+        <v>0.9997666954405091</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-130.1460534722882</v>
+        <v>-115.2487023089534</v>
       </c>
       <c r="AA8">
-        <v>-5.999999999999996</v>
+        <v>-18</v>
       </c>
       <c r="AB8">
-        <v>-0.6447382537574189</v>
+        <v>-0.4265482548042499</v>
       </c>
       <c r="AC8">
-        <v>-0.7644034171442682</v>
+        <v>-0.9044648065698569</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
       </c>
       <c r="AE8" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF8" t="s">
         <v>110</v>
       </c>
-      <c r="AF8" t="s">
-        <v>115</v>
-      </c>
       <c r="AG8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AH8">
-        <v>-0.6447232838285414</v>
+        <v>-0.4264487391515612</v>
       </c>
       <c r="AI8">
-        <v>0.8849205896684339</v>
+        <v>0.8139638137495891</v>
       </c>
       <c r="AJ8">
-        <v>-1.124696659556274</v>
+        <v>-0.4786861000143117</v>
       </c>
       <c r="AK8">
-        <v>-1.364512082778895</v>
+        <v>-1.118584792062444</v>
       </c>
       <c r="AL8">
-        <v>-2.072038687377193</v>
+        <v>-1.202583453339989</v>
       </c>
       <c r="AM8">
-        <v>1.298911310092194</v>
+        <v>0.009187576265506802</v>
       </c>
       <c r="AN8">
-        <v>1.916109695271846</v>
+        <v>1.156643411261429</v>
       </c>
       <c r="AO8">
-        <v>0.05661839962510434</v>
+        <v>0.09279337397242693</v>
       </c>
       <c r="AP8">
-        <v>8.882949999999999</v>
+        <v>4.70771</v>
       </c>
       <c r="AQ8">
-        <v>8.809164071008837</v>
+        <v>4.669328787732332</v>
       </c>
       <c r="AR8">
-        <v>8.907786700165374</v>
+        <v>4.699547965008261</v>
       </c>
       <c r="AS8">
-        <v>8.882949999999999</v>
+        <v>4.70771</v>
       </c>
       <c r="AT8">
-        <v>8.657249999999998</v>
+        <v>4.597269999999999</v>
       </c>
       <c r="AU8">
-        <v>8.809164071008837</v>
+        <v>4.669328787732332</v>
       </c>
       <c r="AV8">
-        <v>8.966125</v>
+        <v>4.750505</v>
       </c>
       <c r="AW8">
-        <v>-0.008306466769616199</v>
+        <v>-0.008152841247160014</v>
       </c>
       <c r="AX8">
-        <v>0.8871166695661198</v>
+        <v>0.8968620695798093</v>
       </c>
       <c r="AY8">
-        <v>0.008306466769616199</v>
+        <v>0.008152841247160014</v>
       </c>
       <c r="AZ8">
-        <v>0.4261813576149057</v>
+        <v>0.4885782360677241</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3738186423850944</v>
+        <v>0.3114217639322759</v>
       </c>
       <c r="BC8" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2533,55 +2512,55 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG8">
-        <v>0.009363443450655495</v>
+        <v>0.009090407013176193</v>
       </c>
       <c r="BH8">
-        <v>53399.15840096169</v>
+        <v>55003.03773805391</v>
       </c>
       <c r="BI8">
-        <v>53399.15840096169</v>
+        <v>41252.27830354043</v>
       </c>
       <c r="BJ8">
-        <v>6011.421701232326</v>
+        <v>8762.705923589268</v>
       </c>
       <c r="BK8">
-        <v>533.9915840096169</v>
+        <v>412.5227830354043</v>
       </c>
       <c r="BL8">
-        <v>0.005339915840096169</v>
+        <v>0.004125227830354043</v>
       </c>
       <c r="BM8">
-        <v>500.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="BN8">
-        <v>0.005000000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="BO8">
-        <v>0.1798180798935454</v>
+        <v>0.07619732523477254</v>
       </c>
       <c r="BP8">
-        <v>0.1524718721761815</v>
+        <v>0.08788523224742868</v>
       </c>
       <c r="BQ8">
-        <v>0.1153327476188802</v>
+        <v>0.09885431363449866</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT8" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU8" t="s">
         <v>92</v>
       </c>
       <c r="BV8" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW8" s="2">
         <v>46318</v>
@@ -2616,19 +2595,19 @@
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>2.095946280581374</v>
+        <v>1.731094300173867</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
@@ -2643,13 +2622,13 @@
         <v>102</v>
       </c>
       <c r="S9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T9">
-        <v>-0.754933602569243</v>
+        <v>-0.8581893648443246</v>
       </c>
       <c r="U9">
-        <v>0.889705343267465</v>
+        <v>0.9361672199703406</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
@@ -2658,100 +2637,100 @@
         <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9999408884452222</v>
+        <v>0.9999280231615781</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-120.6540198628737</v>
+        <v>-135.7554670436737</v>
       </c>
       <c r="AA9">
-        <v>-6.999999999999997</v>
+        <v>-9</v>
       </c>
       <c r="AB9">
-        <v>-0.5098527180263543</v>
+        <v>-0.7163685218727499</v>
       </c>
       <c r="AC9">
-        <v>-0.8602617078082336</v>
+        <v>-0.6977221086291099</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
       </c>
       <c r="AE9" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF9" t="s">
         <v>110</v>
       </c>
-      <c r="AF9" t="s">
-        <v>115</v>
-      </c>
       <c r="AG9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AH9">
-        <v>-0.5098225798394841</v>
+        <v>-0.7163169599314005</v>
       </c>
       <c r="AI9">
-        <v>0.8423133093768236</v>
+        <v>0.9067913366807934</v>
       </c>
       <c r="AJ9">
-        <v>-1.505982560345274</v>
+        <v>-1.283492045000352</v>
       </c>
       <c r="AK9">
-        <v>-2.619424373215611</v>
+        <v>-1.295307354814334</v>
       </c>
       <c r="AL9">
-        <v>-2.968284586879674</v>
+        <v>-2.289981742105469</v>
       </c>
       <c r="AM9">
-        <v>1.18822526655318</v>
+        <v>1.687538655759319</v>
       </c>
       <c r="AN9">
-        <v>2.785106010718397</v>
+        <v>2.096552420224453</v>
       </c>
       <c r="AO9">
-        <v>0.07081211324606963</v>
+        <v>0.05396018658389255</v>
       </c>
       <c r="AP9">
-        <v>1.321695</v>
+        <v>8.8748</v>
       </c>
       <c r="AQ9">
-        <v>1.309876720296334</v>
+        <v>8.79753233725579</v>
       </c>
       <c r="AR9">
-        <v>1.319725828260172</v>
+        <v>8.898234443552214</v>
       </c>
       <c r="AS9">
-        <v>1.321695</v>
+        <v>8.8748</v>
       </c>
       <c r="AT9">
-        <v>1.289945</v>
+        <v>8.64095</v>
       </c>
       <c r="AU9">
-        <v>1.309876720296334</v>
+        <v>8.79753233725579</v>
       </c>
       <c r="AV9">
-        <v>1.3348575</v>
+        <v>8.9626325</v>
       </c>
       <c r="AW9">
-        <v>-0.008941760166805588</v>
+        <v>-0.008706411721301955</v>
       </c>
       <c r="AX9">
-        <v>0.897875001228197</v>
+        <v>0.8797160816805945</v>
       </c>
       <c r="AY9">
-        <v>0.008941760166805588</v>
+        <v>0.008706411721301955</v>
       </c>
       <c r="AZ9">
-        <v>0.4560558281885464</v>
+        <v>0.4268129691001081</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3439441718114536</v>
+        <v>0.3731870308998919</v>
       </c>
       <c r="BC9" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2763,52 +2742,52 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.009958802900820511</v>
+        <v>0.009896842745751989</v>
       </c>
       <c r="BH9">
-        <v>50206.83760683774</v>
+        <v>50521.16243987148</v>
       </c>
       <c r="BI9">
-        <v>50206.83760683774</v>
+        <v>50521.16243987148</v>
       </c>
       <c r="BJ9">
-        <v>37986.70465337142</v>
+        <v>5692.653630489868</v>
       </c>
       <c r="BK9">
-        <v>502.0683760683774</v>
+        <v>505.2116243987148</v>
       </c>
       <c r="BL9">
-        <v>0.005020683760683774</v>
+        <v>0.005052116243987148</v>
       </c>
       <c r="BM9">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN9">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO9">
-        <v>0.02454799163954378</v>
+        <v>0.1851482706392628</v>
       </c>
       <c r="BP9">
-        <v>0.02533765547909182</v>
+        <v>0.1587713910494239</v>
       </c>
       <c r="BQ9">
-        <v>0.02216938074301786</v>
+        <v>0.1197719571831242</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT9" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU9" t="s">
         <v>92</v>
       </c>
       <c r="BV9" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW9" s="2">
         <v>46318</v>
@@ -2843,19 +2822,19 @@
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>1.909240718243277</v>
+        <v>1.937886361804994</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="s">
         <v>95</v>
@@ -2870,13 +2849,13 @@
         <v>102</v>
       </c>
       <c r="S10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T10">
-        <v>-0.7471010554355209</v>
+        <v>-0.7961588187096806</v>
       </c>
       <c r="U10">
-        <v>0.8861648483533932</v>
+        <v>0.9082160858493072</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
@@ -2885,100 +2864,100 @@
         <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9998774936296352</v>
+        <v>0.9997784697198041</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-119.6151082460876</v>
+        <v>-126.3184359725715</v>
       </c>
       <c r="AA10">
-        <v>-12.99999999999999</v>
+        <v>-17</v>
       </c>
       <c r="AB10">
-        <v>-0.4941711253433494</v>
+        <v>-0.5922724704194963</v>
       </c>
       <c r="AC10">
-        <v>-0.8693646524197356</v>
+        <v>-0.8057377493844923</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
       </c>
       <c r="AE10" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF10" t="s">
         <v>110</v>
       </c>
-      <c r="AF10" t="s">
-        <v>115</v>
-      </c>
       <c r="AG10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AH10">
-        <v>-0.4941105862324445</v>
+        <v>-0.5921412641331719</v>
       </c>
       <c r="AI10">
-        <v>0.8369653791787706</v>
+        <v>0.8680458577953514</v>
       </c>
       <c r="AJ10">
-        <v>-1.341166100762454</v>
+        <v>-1.417510206787846</v>
       </c>
       <c r="AK10">
-        <v>-2.50942208627491</v>
+        <v>-2.085903665482049</v>
       </c>
       <c r="AL10">
-        <v>-2.850159455517604</v>
+        <v>-2.658809421329499</v>
       </c>
       <c r="AM10">
-        <v>0.9111780842076089</v>
+        <v>1.988827958919698</v>
       </c>
       <c r="AN10">
-        <v>2.682292018941203</v>
+        <v>2.400354864997008</v>
       </c>
       <c r="AO10">
-        <v>0.07495387463071046</v>
+        <v>0.06372231821619306</v>
       </c>
       <c r="AP10">
-        <v>1.136865</v>
+        <v>1.14024</v>
       </c>
       <c r="AQ10">
-        <v>1.116006329931233</v>
+        <v>1.121620090410704</v>
       </c>
       <c r="AR10">
-        <v>1.107309279688594</v>
+        <v>1.112795216466475</v>
       </c>
       <c r="AS10">
-        <v>1.136865</v>
+        <v>1.14024</v>
       </c>
       <c r="AT10">
-        <v>1.11553</v>
+        <v>1.12228</v>
       </c>
       <c r="AU10">
-        <v>1.116006329931233</v>
+        <v>1.121620090410704</v>
       </c>
       <c r="AV10">
-        <v>1.150770780045844</v>
+        <v>1.15265327305953</v>
       </c>
       <c r="AW10">
-        <v>-0.01834753472819265</v>
+        <v>-0.01632981616966218</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01834753472819265</v>
+        <v>0.01632981616966218</v>
       </c>
       <c r="AZ10">
-        <v>0.4611116696802749</v>
+        <v>0.4482874674226232</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.338888330319725</v>
+        <v>0.3517125325773768</v>
       </c>
       <c r="BC10" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2990,22 +2969,22 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.0122316898187951</v>
+        <v>0.01088654411310812</v>
       </c>
       <c r="BH10">
-        <v>40877.42637421239</v>
+        <v>45928.25737948987</v>
       </c>
       <c r="BI10">
-        <v>40877.42637421239</v>
+        <v>45928.25737948987</v>
       </c>
       <c r="BJ10">
-        <v>35956.27130240828</v>
+        <v>40279.46518232115</v>
       </c>
       <c r="BK10">
-        <v>408.7742637421239</v>
+        <v>459.2825737948987</v>
       </c>
       <c r="BL10">
-        <v>0.004087742637421239</v>
+        <v>0.004592825737948988</v>
       </c>
       <c r="BM10">
         <v>500</v>
@@ -3014,28 +2993,28 @@
         <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.02018746237398035</v>
+        <v>0.02039035488453229</v>
       </c>
       <c r="BP10">
-        <v>0.01933487885535643</v>
+        <v>0.01654747555605129</v>
       </c>
       <c r="BQ10">
-        <v>0.01907625328524329</v>
+        <v>0.01642533051830474</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT10" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU10" t="s">
         <v>92</v>
       </c>
       <c r="BV10" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW10" s="2">
         <v>46318</v>
@@ -3070,19 +3049,19 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K11">
-        <v>0.7983977380112539</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>2.375811432323905</v>
+        <v>2.606939258271708</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11" t="s">
         <v>95</v>
@@ -3091,19 +3070,19 @@
         <v>98</v>
       </c>
       <c r="Q11">
-        <v>0.9495994345028135</v>
+        <v>1</v>
       </c>
       <c r="R11" t="s">
         <v>102</v>
       </c>
       <c r="S11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T11">
-        <v>-0.8243571875466386</v>
+        <v>-0.8650041178133678</v>
       </c>
       <c r="U11">
-        <v>0.8906962567325648</v>
+        <v>0.9392125146723864</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
@@ -3112,100 +3091,100 @@
         <v>95</v>
       </c>
       <c r="X11">
-        <v>0.9999034465395575</v>
+        <v>0.9998426466254836</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-131.3156443052732</v>
+        <v>-136.8853034100549</v>
       </c>
       <c r="AA11">
-        <v>-13.99999999999999</v>
+        <v>-16</v>
       </c>
       <c r="AB11">
-        <v>-0.6602067719977383</v>
+        <v>-0.7299869902260921</v>
       </c>
       <c r="AC11">
-        <v>-0.7510838955857904</v>
+        <v>-0.6834610406604398</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
       </c>
       <c r="AE11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF11" t="s">
         <v>110</v>
       </c>
-      <c r="AF11" t="s">
-        <v>115</v>
-      </c>
       <c r="AG11" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AH11">
-        <v>-0.6601430267492944</v>
+        <v>-0.7298721243098271</v>
       </c>
       <c r="AI11">
-        <v>0.8893433459388245</v>
+        <v>0.9110237886549594</v>
       </c>
       <c r="AJ11">
-        <v>-1.719822012607482</v>
+        <v>-1.92260762015714</v>
       </c>
       <c r="AK11">
-        <v>-2.070348970910865</v>
+        <v>-1.923421855165394</v>
       </c>
       <c r="AL11">
-        <v>-3.335704082077868</v>
+        <v>-3.50897594146149</v>
       </c>
       <c r="AM11">
-        <v>1.940600048762417</v>
+        <v>2.711789877950863</v>
       </c>
       <c r="AN11">
-        <v>3.086665026183349</v>
+        <v>3.193175629649289</v>
       </c>
       <c r="AO11">
-        <v>0.05789927966228124</v>
+        <v>0.0527815648785832</v>
       </c>
       <c r="AP11">
-        <v>7.6368</v>
+        <v>7.6411</v>
       </c>
       <c r="AQ11">
-        <v>7.467011684903857</v>
+        <v>7.474334395423858</v>
       </c>
       <c r="AR11">
-        <v>7.380758517932839</v>
+        <v>7.388796722350728</v>
       </c>
       <c r="AS11">
-        <v>7.6368</v>
+        <v>7.6411</v>
       </c>
       <c r="AT11">
-        <v>7.477300000000001</v>
+        <v>7.4859</v>
       </c>
       <c r="AU11">
-        <v>7.467011684903857</v>
+        <v>7.474334395423858</v>
       </c>
       <c r="AV11">
-        <v>7.749992210064096</v>
+        <v>7.752277069717428</v>
       </c>
       <c r="AW11">
-        <v>-0.0222329136675235</v>
+        <v>-0.02182481639765765</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.0222329136675235</v>
+        <v>0.02182481639765765</v>
       </c>
       <c r="AZ11">
-        <v>0.4369967623533516</v>
+        <v>0.4387658749278224</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3630032376466484</v>
+        <v>0.3612341250721777</v>
       </c>
       <c r="BC11" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3214,55 +3193,55 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>474.7997172514067</v>
+        <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.01482194244501567</v>
+        <v>0.01454987759843843</v>
       </c>
       <c r="BH11">
-        <v>33733.77017586115</v>
+        <v>34364.55025942366</v>
       </c>
       <c r="BI11">
-        <v>32033.56908264562</v>
+        <v>34364.55025942366</v>
       </c>
       <c r="BJ11">
-        <v>4194.632448492251</v>
+        <v>4497.330261274379</v>
       </c>
       <c r="BK11">
-        <v>320.3356908264562</v>
+        <v>343.6455025942366</v>
       </c>
       <c r="BL11">
-        <v>0.003203356908264562</v>
+        <v>0.003436455025942366</v>
       </c>
       <c r="BM11">
-        <v>474.7997172514067</v>
+        <v>500</v>
       </c>
       <c r="BN11">
-        <v>0.004747997172514068</v>
+        <v>0.005</v>
       </c>
       <c r="BO11">
-        <v>0.1411157968947358</v>
+        <v>0.1322861075944443</v>
       </c>
       <c r="BP11">
-        <v>0.1214848986263434</v>
+        <v>0.1173279859843811</v>
       </c>
       <c r="BQ11">
-        <v>0.1017110072039362</v>
+        <v>0.09758862813742765</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.03767326983038256</v>
+        <v>0.03703469011697844</v>
       </c>
       <c r="BT11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="BU11" t="s">
         <v>92</v>
       </c>
       <c r="BV11" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="BW11" s="2">
         <v>46318</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -994,7 +994,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1201,7 +1201,7 @@
         <v>126</v>
       </c>
       <c r="BW2" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1209,7 +1209,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1428,7 +1428,7 @@
         <v>127</v>
       </c>
       <c r="BW3" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1436,7 +1436,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1655,7 +1655,7 @@
         <v>127</v>
       </c>
       <c r="BW4" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1663,7 +1663,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1882,7 +1882,7 @@
         <v>127</v>
       </c>
       <c r="BW5" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1890,7 +1890,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -2109,7 +2109,7 @@
         <v>127</v>
       </c>
       <c r="BW6" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2117,7 +2117,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2336,7 +2336,7 @@
         <v>127</v>
       </c>
       <c r="BW7" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2344,7 +2344,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2368,19 +2368,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.72159686465018</v>
+        <v>0.7854436532796554</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="s">
         <v>95</v>
@@ -2398,10 +2398,10 @@
         <v>105</v>
       </c>
       <c r="T8">
-        <v>-0.6576729416402983</v>
+        <v>-0.6883344829636022</v>
       </c>
       <c r="U8">
-        <v>0.6958944975982615</v>
+        <v>0.7097055200273884</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2410,22 +2410,22 @@
         <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9997666954405091</v>
+        <v>0.9998200107750694</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-115.2487023089534</v>
+        <v>-118.5497975325826</v>
       </c>
       <c r="AA8">
-        <v>-18</v>
+        <v>-15</v>
       </c>
       <c r="AB8">
-        <v>-0.4265482548042499</v>
+        <v>-0.4779223870539749</v>
       </c>
       <c r="AC8">
-        <v>-0.9044648065698569</v>
+        <v>-0.8784020673658678</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
@@ -2440,28 +2440,28 @@
         <v>113</v>
       </c>
       <c r="AH8">
-        <v>-0.4264487391515612</v>
+        <v>-0.4778363661739521</v>
       </c>
       <c r="AI8">
-        <v>0.8139638137495891</v>
+        <v>0.8317376753168102</v>
       </c>
       <c r="AJ8">
-        <v>-0.4786861000143117</v>
+        <v>-0.5516853420326328</v>
       </c>
       <c r="AK8">
-        <v>-1.118584792062444</v>
+        <v>-1.093985872863719</v>
       </c>
       <c r="AL8">
-        <v>-1.202583453339989</v>
+        <v>-1.18034673663606</v>
       </c>
       <c r="AM8">
-        <v>0.009187576265506802</v>
+        <v>0.5677450671431065</v>
       </c>
       <c r="AN8">
-        <v>1.156643411261429</v>
+        <v>1.084772897096356</v>
       </c>
       <c r="AO8">
-        <v>0.09279337397242693</v>
+        <v>0.07717363047104363</v>
       </c>
       <c r="AP8">
         <v>4.70771</v>
@@ -2563,7 +2563,7 @@
         <v>127</v>
       </c>
       <c r="BW8" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2571,7 +2571,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2790,7 +2790,7 @@
         <v>127</v>
       </c>
       <c r="BW9" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2798,7 +2798,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -3017,7 +3017,7 @@
         <v>127</v>
       </c>
       <c r="BW10" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3025,7 +3025,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3244,7 +3244,7 @@
         <v>127</v>
       </c>
       <c r="BW11" s="2">
-        <v>46318</v>
+        <v>46319</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -256,15 +256,15 @@
     <t>AUDUSD</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
@@ -358,34 +358,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.05213,naive=0.02158,drift4=0.03061; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01073,naive=0.01163,drift4=0.009811; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=276.1,naive=80.13,drift4=99.93; naive_cap_applied; model_divergence_guard(abs=499,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=2.973,naive=3.263,drift4=5.117; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=0.009241,naive=0.012,drift4=0.01517; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.02237,naive=0.02261,drift4=0.01962; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=model; scores=model=0.0762,naive=0.08789,drift4=0.09885; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.1851,naive=0.1588,drift4=0.1198; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.02039,naive=0.01655,drift4=0.01643; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.1323,naive=0.1173,drift4=0.09759; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.05349,naive=0.02231,drift4=0.03101; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.01082,naive=0.01141,drift4=0.009323; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=293.8,naive=95.04,drift4=99.22; naive_cap_applied; model_divergence_guard(abs=491.1,thr=400.9)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=3.073,naive=3.085,drift4=4.964; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=0.009391,naive=0.01397,drift4=0.01647; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=model; scores=model=0.06572,naive=0.07539,drift4=0.08554; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.1632,naive=0.1315,drift4=0.09657; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.02398,naive=0.02407,drift4=0.02069; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01994,naive=0.01845,drift4=0.01776; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.1189,naive=0.104,drift4=0.08769; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -994,7 +994,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1018,19 +1018,19 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.857568777251797</v>
+        <v>1.553656358261324</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" t="s">
         <v>90</v>
@@ -1048,10 +1048,10 @@
         <v>103</v>
       </c>
       <c r="T2">
-        <v>-0.8754554507866911</v>
+        <v>-0.7441634316464502</v>
       </c>
       <c r="U2">
-        <v>0.7937111193351427</v>
+        <v>0.7347092904436736</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
@@ -1060,22 +1060,22 @@
         <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9990246659245268</v>
+        <v>0.9993429848110841</v>
       </c>
       <c r="Y2">
-        <v>0.2831373626789613</v>
+        <v>0.6314948200763472</v>
       </c>
       <c r="Z2">
-        <v>135.8800085737004</v>
+        <v>121.1266661180417</v>
       </c>
       <c r="AA2">
-        <v>-21.99999999999999</v>
+        <v>-18</v>
       </c>
       <c r="AB2">
-        <v>-0.7178834387986207</v>
+        <v>-0.516931789508032</v>
       </c>
       <c r="AC2">
-        <v>0.6961633201330468</v>
+        <v>0.856026591290261</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
@@ -1090,58 +1090,58 @@
         <v>111</v>
       </c>
       <c r="AH2">
-        <v>-0.4601223200769247</v>
+        <v>-0.4214087145027491</v>
       </c>
       <c r="AI2">
-        <v>0.7676310761284897</v>
+        <v>0.7760809504182696</v>
       </c>
       <c r="AJ2">
-        <v>-1.499617419309893</v>
+        <v>-1.271926308750624</v>
       </c>
       <c r="AK2">
-        <v>1.348309231129061</v>
+        <v>1.976159184924614</v>
       </c>
       <c r="AL2">
-        <v>-1.95746081059966</v>
+        <v>-1.59135535249199</v>
       </c>
       <c r="AM2">
-        <v>3.872641928994977</v>
+        <v>3.276585817871569</v>
       </c>
       <c r="AN2">
-        <v>1.646006478955865</v>
+        <v>1.352819908812047</v>
       </c>
       <c r="AO2">
-        <v>0.02680040746982128</v>
+        <v>0.03378396755525835</v>
       </c>
       <c r="AP2">
-        <v>6.722295</v>
+        <v>6.722455</v>
       </c>
       <c r="AQ2">
-        <v>6.720241318443436</v>
+        <v>6.720578808223988</v>
       </c>
       <c r="AR2">
-        <v>6.725128981574848</v>
+        <v>6.725598777192802</v>
       </c>
       <c r="AS2">
-        <v>6.722295</v>
+        <v>6.722455</v>
       </c>
       <c r="AT2">
-        <v>6.713365</v>
+        <v>6.713685</v>
       </c>
       <c r="AW2">
-        <v>-0.0003055030397452295</v>
+        <v>-0.0002790932443597124</v>
       </c>
       <c r="AY2">
-        <v>0.0003055030397452295</v>
+        <v>0.0002790932443597124</v>
       </c>
       <c r="AZ2">
-        <v>0.432703707588168</v>
+        <v>0.4314171853988076</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.367296292411832</v>
+        <v>0.3685828146011924</v>
       </c>
       <c r="BC2" t="s">
         <v>114</v>
@@ -1177,19 +1177,19 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.05212607627081053</v>
+        <v>0.05348874741949559</v>
       </c>
       <c r="BP2">
-        <v>0.02158252790607651</v>
+        <v>0.02230689060362511</v>
       </c>
       <c r="BQ2">
-        <v>0.0306111139410063</v>
+        <v>0.03101449469704753</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT2" t="s">
         <v>124</v>
@@ -1201,7 +1201,7 @@
         <v>126</v>
       </c>
       <c r="BW2" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1209,7 +1209,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1233,19 +1233,19 @@
         <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2.488771664565861</v>
+        <v>2.771955978776556</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1263,10 +1263,10 @@
         <v>104</v>
       </c>
       <c r="T3">
-        <v>0.9753638670405722</v>
+        <v>0.966604633832096</v>
       </c>
       <c r="U3">
-        <v>0.9888294149974884</v>
+        <v>0.9849232799787089</v>
       </c>
       <c r="V3" t="s">
         <v>94</v>
@@ -1275,22 +1275,22 @@
         <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9996626993169238</v>
+        <v>0.9998047790170624</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>18.06239721480294</v>
+        <v>21.06030066615424</v>
       </c>
       <c r="AA3">
-        <v>-22.99999999999999</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB3">
-        <v>0.9507194214928271</v>
+        <v>0.9332027469149962</v>
       </c>
       <c r="AC3">
-        <v>0.3100525465084012</v>
+        <v>0.3593502930989561</v>
       </c>
       <c r="AD3" t="s">
         <v>94</v>
@@ -1305,67 +1305,67 @@
         <v>112</v>
       </c>
       <c r="AH3">
-        <v>0.9503987431825437</v>
+        <v>0.9330205661574634</v>
       </c>
       <c r="AI3">
-        <v>0.9783500314562832</v>
+        <v>0.9733599994677484</v>
       </c>
       <c r="AJ3">
-        <v>1.85546613991107</v>
+        <v>2.083345892564772</v>
       </c>
       <c r="AK3">
-        <v>0.699775371572142</v>
+        <v>0.8638397659875174</v>
       </c>
       <c r="AL3">
-        <v>3.25965202062125</v>
+        <v>3.558600649852225</v>
       </c>
       <c r="AM3">
-        <v>-2.679407041876462</v>
+        <v>-3.261242385719994</v>
       </c>
       <c r="AN3">
-        <v>2.98272762231678</v>
+        <v>3.226954040271941</v>
       </c>
       <c r="AO3">
-        <v>0.04498493168325392</v>
+        <v>0.04354998175148109</v>
       </c>
       <c r="AP3">
-        <v>0.8285</v>
+        <v>0.8286450000000001</v>
       </c>
       <c r="AQ3">
-        <v>0.8430604394689205</v>
+        <v>0.840778383137571</v>
       </c>
       <c r="AR3">
-        <v>0.8457239108482708</v>
+        <v>0.8403531016693058</v>
       </c>
       <c r="AS3">
-        <v>0.8285</v>
+        <v>0.8286450000000001</v>
       </c>
       <c r="AT3">
-        <v>0.8480000000000001</v>
+        <v>0.8482900000000002</v>
       </c>
       <c r="AU3">
-        <v>0.8430604394689205</v>
+        <v>0.840778383137571</v>
       </c>
       <c r="AV3">
-        <v>0.818793040354053</v>
+        <v>0.8205560779082861</v>
       </c>
       <c r="AW3">
-        <v>0.01757445922621665</v>
+        <v>0.01464243812195928</v>
       </c>
       <c r="AX3">
         <v>1.5</v>
       </c>
       <c r="AY3">
-        <v>0.01757445922621665</v>
+        <v>0.01464243812195928</v>
       </c>
       <c r="AZ3">
-        <v>0.4567310249204258</v>
+        <v>0.4513875210640012</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3432689750795742</v>
+        <v>0.3486124789359988</v>
       </c>
       <c r="BC3" t="s">
         <v>115</v>
@@ -1380,22 +1380,22 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.0117163061508111</v>
+        <v>0.009761625414639524</v>
       </c>
       <c r="BH3">
-        <v>42675.56630597143</v>
+        <v>51220.97793776734</v>
       </c>
       <c r="BI3">
-        <v>42675.56630597143</v>
+        <v>51220.97793776734</v>
       </c>
       <c r="BJ3">
-        <v>51509.43428602465</v>
+        <v>61812.93308686752</v>
       </c>
       <c r="BK3">
-        <v>426.7556630597143</v>
+        <v>512.2097793776734</v>
       </c>
       <c r="BL3">
-        <v>0.004267556630597144</v>
+        <v>0.005122097793776734</v>
       </c>
       <c r="BM3">
         <v>500</v>
@@ -1404,19 +1404,19 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>0.0107281469549552</v>
+        <v>0.01081640700663146</v>
       </c>
       <c r="BP3">
-        <v>0.01162693307989298</v>
+        <v>0.01140536508399152</v>
       </c>
       <c r="BQ3">
-        <v>0.009810652487100925</v>
+        <v>0.009323110491309244</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT3" t="s">
         <v>125</v>
@@ -1428,7 +1428,7 @@
         <v>127</v>
       </c>
       <c r="BW3" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1436,7 +1436,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1460,19 +1460,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.3506227820907868</v>
+        <v>0.461376602456803</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="s">
         <v>96</v>
@@ -1490,10 +1490,10 @@
         <v>105</v>
       </c>
       <c r="T4">
-        <v>-0.7708715311066867</v>
+        <v>-0.76950823222412</v>
       </c>
       <c r="U4">
-        <v>0.7467909939190269</v>
+        <v>0.7462381362649918</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1502,22 +1502,22 @@
         <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9995952196840717</v>
+        <v>0.9998377270565512</v>
       </c>
       <c r="Y4">
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>-109.1960761664299</v>
+        <v>-108.9605010459745</v>
       </c>
       <c r="AA4">
-        <v>-13.99999999999999</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB4">
-        <v>-0.3288019714707134</v>
+        <v>-0.3249162491209054</v>
       </c>
       <c r="AC4">
-        <v>-0.9443988900655126</v>
+        <v>-0.9457427932885356</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
@@ -1532,58 +1532,58 @@
         <v>113</v>
       </c>
       <c r="AH4">
-        <v>-0.1643344394524118</v>
+        <v>-0.1624317620023931</v>
       </c>
       <c r="AI4">
-        <v>0.5838487033228706</v>
+        <v>0.5854529060921151</v>
       </c>
       <c r="AJ4">
-        <v>-0.2435543012591954</v>
+        <v>-0.325902664262283</v>
       </c>
       <c r="AK4">
-        <v>-0.7745960668631813</v>
+        <v>-0.9932626463738097</v>
       </c>
       <c r="AL4">
-        <v>-0.5990815336725037</v>
+        <v>-0.6796074969203546</v>
       </c>
       <c r="AM4">
-        <v>0.03399497494145383</v>
+        <v>0.2419988380794569</v>
       </c>
       <c r="AN4">
-        <v>0.5748397811172627</v>
+        <v>0.6383726808067267</v>
       </c>
       <c r="AO4">
-        <v>0.09766810005178962</v>
+        <v>0.07976782075966257</v>
       </c>
       <c r="AP4">
-        <v>4304.280000000001</v>
+        <v>4284.91</v>
       </c>
       <c r="AQ4">
-        <v>4369.851759244538</v>
+        <v>4337.465758670276</v>
       </c>
       <c r="AR4">
-        <v>4726.772530815125</v>
+        <v>4689.842528900921</v>
       </c>
       <c r="AS4">
-        <v>4304.280000000001</v>
+        <v>4284.91</v>
       </c>
       <c r="AT4">
-        <v>4151.340000000001</v>
+        <v>4112.599999999999</v>
       </c>
       <c r="AU4">
-        <v>4369.851759244538</v>
+        <v>4337.465758670276</v>
       </c>
       <c r="AV4">
-        <v>4170.642500000001</v>
+        <v>4151.2725</v>
       </c>
       <c r="AW4">
-        <v>0.01523408310903034</v>
+        <v>0.01226531214664396</v>
       </c>
       <c r="AX4">
-        <v>0.4906688560062636</v>
+        <v>0.3932710404660079</v>
       </c>
       <c r="AY4">
-        <v>0.01523408310903034</v>
+        <v>0.01226531214664396</v>
       </c>
       <c r="AZ4">
         <v>0.3</v>
@@ -1607,22 +1607,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.03104758519427178</v>
+        <v>0.03118793626937326</v>
       </c>
       <c r="BH4">
-        <v>16104.31203816292</v>
+        <v>16031.83986530725</v>
       </c>
       <c r="BI4">
-        <v>16104.31203816292</v>
+        <v>16031.83986530725</v>
       </c>
       <c r="BJ4">
         <v>3.741464783462721</v>
       </c>
       <c r="BK4">
-        <v>161.0431203816292</v>
+        <v>160.3183986530725</v>
       </c>
       <c r="BL4">
-        <v>0.001610431203816292</v>
+        <v>0.001603183986530725</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1631,19 +1631,19 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>276.110614441147</v>
+        <v>293.8362333155085</v>
       </c>
       <c r="BP4">
-        <v>80.13314278191893</v>
+        <v>95.0449793786315</v>
       </c>
       <c r="BQ4">
-        <v>99.92928043991822</v>
+        <v>99.21532252031129</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT4" t="s">
         <v>125</v>
@@ -1655,7 +1655,7 @@
         <v>127</v>
       </c>
       <c r="BW4" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1663,7 +1663,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1687,19 +1687,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.2841135154704187</v>
+        <v>0.4656618797617593</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O5" t="s">
         <v>96</v>
@@ -1717,10 +1717,10 @@
         <v>103</v>
       </c>
       <c r="T5">
-        <v>-0.614006259335212</v>
+        <v>-0.6372822385028896</v>
       </c>
       <c r="U5">
-        <v>0.6762239512074667</v>
+        <v>0.6866487673838128</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1729,22 +1729,22 @@
         <v>95</v>
       </c>
       <c r="X5">
-        <v>0.999684538026485</v>
+        <v>0.9994870402300498</v>
       </c>
       <c r="Y5">
-        <v>0.4977826390295005</v>
+        <v>0.4989245714908739</v>
       </c>
       <c r="Z5">
-        <v>103.1243080525524</v>
+        <v>105.9025552549323</v>
       </c>
       <c r="AA5">
-        <v>-13.99999999999999</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB5">
-        <v>-0.2270645017380868</v>
+        <v>-0.2740021097855445</v>
       </c>
       <c r="AC5">
-        <v>0.9738797215521198</v>
+        <v>0.961729090665906</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1759,67 +1759,67 @@
         <v>111</v>
       </c>
       <c r="AH5">
-        <v>-0.1699929910747425</v>
+        <v>-0.205248909031391</v>
       </c>
       <c r="AI5">
-        <v>0.6501038832630816</v>
+        <v>0.6680714303987534</v>
       </c>
       <c r="AJ5">
-        <v>-0.4469555849811924</v>
+        <v>-0.4969293061111932</v>
       </c>
       <c r="AK5">
-        <v>1.667747666634527</v>
+        <v>1.662264372548948</v>
       </c>
       <c r="AL5">
-        <v>-0.04342638805186327</v>
+        <v>-0.2879211642521388</v>
       </c>
       <c r="AM5">
-        <v>1.64989536827254</v>
+        <v>1.0851574638904</v>
       </c>
       <c r="AN5">
-        <v>0.2156359868502796</v>
+        <v>0.2744702378443663</v>
       </c>
       <c r="AO5">
-        <v>0.1164105558234287</v>
+        <v>0.09156387277068113</v>
       </c>
       <c r="AP5">
-        <v>157.572</v>
+        <v>157.2345</v>
       </c>
       <c r="AQ5">
-        <v>158.2600477851997</v>
+        <v>157.7350547722465</v>
       </c>
       <c r="AR5">
-        <v>160.3176687971889</v>
+        <v>159.8563858250094</v>
       </c>
       <c r="AS5">
-        <v>157.572</v>
+        <v>157.2345</v>
       </c>
       <c r="AT5">
-        <v>155.0675</v>
+        <v>154.3925</v>
       </c>
       <c r="AU5">
-        <v>158.2600477851997</v>
+        <v>157.7350547722465</v>
       </c>
       <c r="AV5">
-        <v>156.073875</v>
+        <v>155.736375</v>
       </c>
       <c r="AW5">
-        <v>0.004366561224073439</v>
+        <v>0.00318349199600889</v>
       </c>
       <c r="AX5">
-        <v>0.4592726142342546</v>
+        <v>0.3341208325383092</v>
       </c>
       <c r="AY5">
-        <v>0.004366561224073439</v>
+        <v>0.00318349199600889</v>
       </c>
       <c r="AZ5">
-        <v>0.5126783326739646</v>
+        <v>0.5077256116056714</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.2873216673260355</v>
+        <v>0.2922743883943285</v>
       </c>
       <c r="BC5" t="s">
         <v>117</v>
@@ -1834,22 +1834,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.009507558449470819</v>
+        <v>0.009527966190626205</v>
       </c>
       <c r="BH5">
-        <v>52589.73717146377</v>
+        <v>52477.09637046252</v>
       </c>
       <c r="BI5">
-        <v>52589.73717146377</v>
+        <v>52477.09637046252</v>
       </c>
       <c r="BJ5">
         <v>333.7505214851863</v>
       </c>
       <c r="BK5">
-        <v>525.8973717146378</v>
+        <v>524.7709637046252</v>
       </c>
       <c r="BL5">
-        <v>0.005258973717146378</v>
+        <v>0.005247709637046251</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1858,19 +1858,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>2.972561820729688</v>
+        <v>3.072926972048653</v>
       </c>
       <c r="BP5">
-        <v>3.26335193352986</v>
+        <v>3.085441892668619</v>
       </c>
       <c r="BQ5">
-        <v>5.116634297740439</v>
+        <v>4.963623601441139</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT5" t="s">
         <v>125</v>
@@ -1882,7 +1882,7 @@
         <v>127</v>
       </c>
       <c r="BW5" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1890,7 +1890,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1914,19 +1914,19 @@
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.566725038997936</v>
+        <v>0.9932868956067169</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
         <v>95</v>
@@ -1944,10 +1944,10 @@
         <v>105</v>
       </c>
       <c r="T6">
-        <v>-0.5250351037526458</v>
+        <v>-0.5645177567596933</v>
       </c>
       <c r="U6">
-        <v>0.6362120452480466</v>
+        <v>0.6539994770128366</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1956,22 +1956,22 @@
         <v>95</v>
       </c>
       <c r="X6">
-        <v>0.999784994237424</v>
+        <v>0.9998659458838982</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-101.7923206715223</v>
+        <v>-105.6956783367861</v>
       </c>
       <c r="AA6">
-        <v>-12.99999999999999</v>
+        <v>-9</v>
       </c>
       <c r="AB6">
-        <v>-0.2043648528338475</v>
+        <v>-0.2705278320129815</v>
       </c>
       <c r="AC6">
-        <v>-0.978894788486587</v>
+        <v>-0.9627121543360487</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -1986,67 +1986,67 @@
         <v>113</v>
       </c>
       <c r="AH6">
-        <v>-0.2043209132128203</v>
+        <v>-0.27049156664358</v>
       </c>
       <c r="AI6">
-        <v>0.7374858102473283</v>
+        <v>0.7641073423462377</v>
       </c>
       <c r="AJ6">
-        <v>-0.4230599295764431</v>
+        <v>-0.6965267282036537</v>
       </c>
       <c r="AK6">
-        <v>-2.325626394417131</v>
+        <v>-2.653163019204379</v>
       </c>
       <c r="AL6">
-        <v>-1.404634614757629</v>
+        <v>-1.758527870195961</v>
       </c>
       <c r="AM6">
-        <v>-0.5117315277336331</v>
+        <v>0.1702143361458303</v>
       </c>
       <c r="AN6">
-        <v>1.360152190851854</v>
+        <v>1.650793431524987</v>
       </c>
       <c r="AO6">
-        <v>0.1583226239061616</v>
+        <v>0.1133605887801404</v>
       </c>
       <c r="AP6">
-        <v>0.70316</v>
+        <v>0.70094</v>
       </c>
       <c r="AQ6">
-        <v>0.7000953935816343</v>
+        <v>0.6971472480782931</v>
       </c>
       <c r="AR6">
-        <v>0.7042626552707765</v>
+        <v>0.7017196448747367</v>
       </c>
       <c r="AS6">
-        <v>0.70316</v>
+        <v>0.70094</v>
       </c>
       <c r="AT6">
-        <v>0.69072</v>
+        <v>0.68628</v>
       </c>
       <c r="AU6">
-        <v>0.7000953935816343</v>
+        <v>0.6971472480782931</v>
       </c>
       <c r="AV6">
-        <v>0.71036875</v>
+        <v>0.7081487499999999</v>
       </c>
       <c r="AW6">
-        <v>-0.00435833440236319</v>
+        <v>-0.005410950896948264</v>
       </c>
       <c r="AX6">
-        <v>0.4251231376265969</v>
+        <v>0.5261317040689374</v>
       </c>
       <c r="AY6">
-        <v>0.00435833440236319</v>
+        <v>0.005410950896948264</v>
       </c>
       <c r="AZ6">
-        <v>0.5085703980442011</v>
+        <v>0.5139527588019327</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.2914296019557989</v>
+        <v>0.2860472411980673</v>
       </c>
       <c r="BC6" t="s">
         <v>118</v>
@@ -2061,22 +2061,22 @@
         <v>375</v>
       </c>
       <c r="BG6">
-        <v>0.01025193412594563</v>
+        <v>0.01028440380061051</v>
       </c>
       <c r="BH6">
-        <v>48771.28489682724</v>
+        <v>48617.30535807226</v>
       </c>
       <c r="BI6">
-        <v>36578.46367262043</v>
+        <v>36462.97901855419</v>
       </c>
       <c r="BJ6">
         <v>52020.11444425228</v>
       </c>
       <c r="BK6">
-        <v>365.7846367262043</v>
+        <v>364.6297901855419</v>
       </c>
       <c r="BL6">
-        <v>0.003657846367262043</v>
+        <v>0.003646297901855419</v>
       </c>
       <c r="BM6">
         <v>375</v>
@@ -2085,19 +2085,19 @@
         <v>0.00375</v>
       </c>
       <c r="BO6">
-        <v>0.009240600538895163</v>
+        <v>0.009390655634912228</v>
       </c>
       <c r="BP6">
-        <v>0.01200096255836485</v>
+        <v>0.013969378924017</v>
       </c>
       <c r="BQ6">
-        <v>0.01517019156202318</v>
+        <v>0.01646719235472326</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT6" t="s">
         <v>125</v>
@@ -2109,7 +2109,7 @@
         <v>127</v>
       </c>
       <c r="BW6" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2117,7 +2117,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2141,19 +2141,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>2.204056462375657</v>
+        <v>0.7854436532796554</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O7" t="s">
         <v>95</v>
@@ -2162,7 +2162,7 @@
         <v>98</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R7" t="s">
         <v>102</v>
@@ -2171,10 +2171,10 @@
         <v>105</v>
       </c>
       <c r="T7">
-        <v>-0.8002262984732403</v>
+        <v>-0.6883344829636022</v>
       </c>
       <c r="U7">
-        <v>0.9100712051909596</v>
+        <v>0.7097055200273884</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2183,22 +2183,22 @@
         <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9998774835120062</v>
+        <v>0.9998200107750694</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-126.9005655230236</v>
+        <v>-118.5497975325826</v>
       </c>
       <c r="AA7">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="AB7">
-        <v>-0.6004281183751474</v>
+        <v>-0.4779223870539749</v>
       </c>
       <c r="AC7">
-        <v>-0.7996787321571581</v>
+        <v>-0.8784020673658678</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
@@ -2213,67 +2213,67 @@
         <v>113</v>
       </c>
       <c r="AH7">
-        <v>-0.6003545560307914</v>
+        <v>-0.4778363661739521</v>
       </c>
       <c r="AI7">
-        <v>0.8707782775731258</v>
+        <v>0.8317376753168102</v>
       </c>
       <c r="AJ7">
-        <v>-1.633709510762142</v>
+        <v>-0.5516853420326328</v>
       </c>
       <c r="AK7">
-        <v>-2.271893086854237</v>
+        <v>-1.093985872863719</v>
       </c>
       <c r="AL7">
-        <v>-2.916394408212985</v>
+        <v>-1.18034673663606</v>
       </c>
       <c r="AM7">
-        <v>2.274414857222687</v>
+        <v>0.5677450671431065</v>
       </c>
       <c r="AN7">
-        <v>2.63505261990162</v>
+        <v>1.084772897096356</v>
       </c>
       <c r="AO7">
-        <v>0.06204851445747073</v>
+        <v>0.07717363047104363</v>
       </c>
       <c r="AP7">
-        <v>1.325005</v>
+        <v>4.72135</v>
       </c>
       <c r="AQ7">
-        <v>1.314338015591842</v>
+        <v>4.690199290006634</v>
       </c>
       <c r="AR7">
-        <v>1.323212619205391</v>
+        <v>4.719232681557525</v>
       </c>
       <c r="AS7">
-        <v>1.325005</v>
+        <v>4.72135</v>
       </c>
       <c r="AT7">
-        <v>1.296565</v>
+        <v>4.62455</v>
       </c>
       <c r="AU7">
-        <v>1.314338015591842</v>
+        <v>4.690199290006634</v>
       </c>
       <c r="AV7">
-        <v>1.3381675</v>
+        <v>4.763995</v>
       </c>
       <c r="AW7">
-        <v>-0.008050523890972779</v>
+        <v>-0.0065978395995566</v>
       </c>
       <c r="AX7">
-        <v>0.8104071725096611</v>
+        <v>0.7304657050853915</v>
       </c>
       <c r="AY7">
-        <v>0.008050523890972779</v>
+        <v>0.0065978395995566</v>
       </c>
       <c r="AZ7">
-        <v>0.4535120191674236</v>
+        <v>0.4888886673378569</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3464879808325765</v>
+        <v>0.3111113326621431</v>
       </c>
       <c r="BC7" t="s">
         <v>119</v>
@@ -2285,46 +2285,46 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.009933924777642322</v>
+        <v>0.009032374215002074</v>
       </c>
       <c r="BH7">
-        <v>50332.5735992404</v>
+        <v>55356.43100011719</v>
       </c>
       <c r="BI7">
-        <v>50332.5735992404</v>
+        <v>41517.32325008789</v>
       </c>
       <c r="BJ7">
-        <v>37986.70465337142</v>
+        <v>8793.527963418916</v>
       </c>
       <c r="BK7">
-        <v>503.325735992404</v>
+        <v>415.173232500879</v>
       </c>
       <c r="BL7">
-        <v>0.00503325735992404</v>
+        <v>0.00415173232500879</v>
       </c>
       <c r="BM7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BN7">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="BO7">
-        <v>0.02236906780713557</v>
+        <v>0.06572396496462461</v>
       </c>
       <c r="BP7">
-        <v>0.02261119110357151</v>
+        <v>0.07539459805921911</v>
       </c>
       <c r="BQ7">
-        <v>0.01961867037225893</v>
+        <v>0.08553679890027988</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT7" t="s">
         <v>125</v>
@@ -2336,7 +2336,7 @@
         <v>127</v>
       </c>
       <c r="BW7" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2344,7 +2344,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2371,16 +2371,16 @@
         <v>46290</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0.7854436532796554</v>
+        <v>1.680550403729014</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O8" t="s">
         <v>95</v>
@@ -2389,7 +2389,7 @@
         <v>98</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
         <v>102</v>
@@ -2398,10 +2398,10 @@
         <v>105</v>
       </c>
       <c r="T8">
-        <v>-0.6883344829636022</v>
+        <v>-0.8855271921817665</v>
       </c>
       <c r="U8">
-        <v>0.7097055200273884</v>
+        <v>0.9484558051191534</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2410,22 +2410,22 @@
         <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9998200107750694</v>
+        <v>0.9998742745494339</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-118.5497975325826</v>
+        <v>-140.4473711516528</v>
       </c>
       <c r="AA8">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="AB8">
-        <v>-0.4779223870539749</v>
+        <v>-0.7710399904085061</v>
       </c>
       <c r="AC8">
-        <v>-0.8784020673658678</v>
+        <v>-0.6367867250428912</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
@@ -2440,67 +2440,67 @@
         <v>113</v>
       </c>
       <c r="AH8">
-        <v>-0.4778363661739521</v>
+        <v>-0.7709430510583075</v>
       </c>
       <c r="AI8">
-        <v>0.8317376753168102</v>
+        <v>0.9242730690792125</v>
       </c>
       <c r="AJ8">
-        <v>-0.5516853420326328</v>
+        <v>-1.281459118945528</v>
       </c>
       <c r="AK8">
-        <v>-1.093985872863719</v>
+        <v>-1.109466462516039</v>
       </c>
       <c r="AL8">
-        <v>-1.18034673663606</v>
+        <v>-2.07682591302683</v>
       </c>
       <c r="AM8">
-        <v>0.5677450671431065</v>
+        <v>2.337058766020589</v>
       </c>
       <c r="AN8">
-        <v>1.084772897096356</v>
+        <v>1.830539036054295</v>
       </c>
       <c r="AO8">
-        <v>0.07717363047104363</v>
+        <v>0.0466328275709414</v>
       </c>
       <c r="AP8">
-        <v>4.70771</v>
+        <v>8.908250000000001</v>
       </c>
       <c r="AQ8">
-        <v>4.669328787732332</v>
+        <v>8.843319243234429</v>
       </c>
       <c r="AR8">
-        <v>4.699547965008261</v>
+        <v>8.935269980348812</v>
       </c>
       <c r="AS8">
-        <v>4.70771</v>
+        <v>8.908250000000001</v>
       </c>
       <c r="AT8">
-        <v>4.597269999999999</v>
+        <v>8.707850000000001</v>
       </c>
       <c r="AU8">
-        <v>4.669328787732332</v>
+        <v>8.843319243234429</v>
       </c>
       <c r="AV8">
-        <v>4.750505</v>
+        <v>8.9893175</v>
       </c>
       <c r="AW8">
-        <v>-0.008152841247160014</v>
+        <v>-0.007288834144256332</v>
       </c>
       <c r="AX8">
-        <v>0.8968620695798093</v>
+        <v>0.80094682536863</v>
       </c>
       <c r="AY8">
-        <v>0.008152841247160014</v>
+        <v>0.007288834144256332</v>
       </c>
       <c r="AZ8">
-        <v>0.4885782360677241</v>
+        <v>0.4194409087896486</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3114217639322759</v>
+        <v>0.3805590912103514</v>
       </c>
       <c r="BC8" t="s">
         <v>120</v>
@@ -2512,46 +2512,46 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.009090407013176193</v>
+        <v>0.009100272219571753</v>
       </c>
       <c r="BH8">
-        <v>55003.03773805391</v>
+        <v>54943.41135473521</v>
       </c>
       <c r="BI8">
-        <v>41252.27830354043</v>
+        <v>54943.41135473521</v>
       </c>
       <c r="BJ8">
-        <v>8762.705923589268</v>
+        <v>6167.699756375854</v>
       </c>
       <c r="BK8">
-        <v>412.5227830354043</v>
+        <v>549.4341135473521</v>
       </c>
       <c r="BL8">
-        <v>0.004125227830354043</v>
+        <v>0.005494341135473521</v>
       </c>
       <c r="BM8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BN8">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.07619732523477254</v>
+        <v>0.163156079899769</v>
       </c>
       <c r="BP8">
-        <v>0.08788523224742868</v>
+        <v>0.1314544086006516</v>
       </c>
       <c r="BQ8">
-        <v>0.09885431363449866</v>
+        <v>0.09656612302088997</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT8" t="s">
         <v>125</v>
@@ -2563,7 +2563,7 @@
         <v>127</v>
       </c>
       <c r="BW8" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2571,7 +2571,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2595,19 +2595,19 @@
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1.731094300173867</v>
+        <v>2.433491918712662</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
@@ -2625,10 +2625,10 @@
         <v>105</v>
       </c>
       <c r="T9">
-        <v>-0.8581893648443246</v>
+        <v>-0.8071098751366853</v>
       </c>
       <c r="U9">
-        <v>0.9361672199703406</v>
+        <v>0.9131857171886492</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
@@ -2637,22 +2637,22 @@
         <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9999280231615781</v>
+        <v>0.9999450935085634</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-135.7554670436737</v>
+        <v>-127.894478809305</v>
       </c>
       <c r="AA9">
-        <v>-9</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB9">
-        <v>-0.7163685218727499</v>
+        <v>-0.6142091587718395</v>
       </c>
       <c r="AC9">
-        <v>-0.6977221086291099</v>
+        <v>-0.7891432755088199</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
@@ -2667,67 +2667,67 @@
         <v>113</v>
       </c>
       <c r="AH9">
-        <v>-0.7163169599314005</v>
+        <v>-0.614175434701923</v>
       </c>
       <c r="AI9">
-        <v>0.9067913366807934</v>
+        <v>0.8759707461057231</v>
       </c>
       <c r="AJ9">
-        <v>-1.283492045000352</v>
+        <v>-1.840866142847872</v>
       </c>
       <c r="AK9">
-        <v>-1.295307354814334</v>
+        <v>-2.426251652530377</v>
       </c>
       <c r="AL9">
-        <v>-2.289981742105469</v>
+        <v>-3.063933652710714</v>
       </c>
       <c r="AM9">
-        <v>1.687538655759319</v>
+        <v>3.14378323842924</v>
       </c>
       <c r="AN9">
-        <v>2.096552420224453</v>
+        <v>2.709019752958548</v>
       </c>
       <c r="AO9">
-        <v>0.05396018658389255</v>
+        <v>0.05515189502550502</v>
       </c>
       <c r="AP9">
-        <v>8.8748</v>
+        <v>1.323345</v>
       </c>
       <c r="AQ9">
-        <v>8.79753233725579</v>
+        <v>1.311698859235281</v>
       </c>
       <c r="AR9">
-        <v>8.898234443552214</v>
+        <v>1.32075178303796</v>
       </c>
       <c r="AS9">
-        <v>8.8748</v>
+        <v>1.323345</v>
       </c>
       <c r="AT9">
-        <v>8.64095</v>
+        <v>1.293245</v>
       </c>
       <c r="AU9">
-        <v>8.79753233725579</v>
+        <v>1.311698859235281</v>
       </c>
       <c r="AV9">
-        <v>8.9626325</v>
+        <v>1.3365075</v>
       </c>
       <c r="AW9">
-        <v>-0.008706411721301955</v>
+        <v>-0.008800532563102285</v>
       </c>
       <c r="AX9">
-        <v>0.8797160816805945</v>
+        <v>0.8847970191619087</v>
       </c>
       <c r="AY9">
-        <v>0.008706411721301955</v>
+        <v>0.008800532563102285</v>
       </c>
       <c r="AZ9">
-        <v>0.4268129691001081</v>
+        <v>0.4520288402363377</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3731870308998919</v>
+        <v>0.3479711597636623</v>
       </c>
       <c r="BC9" t="s">
         <v>121</v>
@@ -2742,22 +2742,22 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.009896842745751989</v>
+        <v>0.0099463858630969</v>
       </c>
       <c r="BH9">
-        <v>50521.16243987148</v>
+        <v>50269.51566951579</v>
       </c>
       <c r="BI9">
-        <v>50521.16243987148</v>
+        <v>50269.51566951579</v>
       </c>
       <c r="BJ9">
-        <v>5692.653630489868</v>
+        <v>37986.70465337142</v>
       </c>
       <c r="BK9">
-        <v>505.2116243987148</v>
+        <v>502.6951566951579</v>
       </c>
       <c r="BL9">
-        <v>0.005052116243987148</v>
+        <v>0.005026951566951579</v>
       </c>
       <c r="BM9">
         <v>499.9999999999999</v>
@@ -2766,19 +2766,19 @@
         <v>0.004999999999999999</v>
       </c>
       <c r="BO9">
-        <v>0.1851482706392628</v>
+        <v>0.02397734359525433</v>
       </c>
       <c r="BP9">
-        <v>0.1587713910494239</v>
+        <v>0.0240683090367852</v>
       </c>
       <c r="BQ9">
-        <v>0.1197719571831242</v>
+        <v>0.02068553988895863</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT9" t="s">
         <v>125</v>
@@ -2790,7 +2790,7 @@
         <v>127</v>
       </c>
       <c r="BW9" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2798,7 +2798,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2822,19 +2822,19 @@
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>1.937886361804994</v>
+        <v>2.129473063872976</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" t="s">
         <v>95</v>
@@ -2852,10 +2852,10 @@
         <v>105</v>
       </c>
       <c r="T10">
-        <v>-0.7961588187096806</v>
+        <v>-0.8077528568583739</v>
       </c>
       <c r="U10">
-        <v>0.9082160858493072</v>
+        <v>0.9134586544216092</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
@@ -2864,22 +2864,22 @@
         <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9997784697198041</v>
+        <v>0.9998794753413637</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-126.3184359725715</v>
+        <v>-127.9869909050153</v>
       </c>
       <c r="AA10">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="AB10">
-        <v>-0.5922724704194963</v>
+        <v>-0.6154825404024911</v>
       </c>
       <c r="AC10">
-        <v>-0.8057377493844923</v>
+        <v>-0.7881505201798042</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
@@ -2894,67 +2894,67 @@
         <v>113</v>
       </c>
       <c r="AH10">
-        <v>-0.5921412641331719</v>
+        <v>-0.6154083595794124</v>
       </c>
       <c r="AI10">
-        <v>0.8680458577953514</v>
+        <v>0.8760997784776414</v>
       </c>
       <c r="AJ10">
-        <v>-1.417510206787846</v>
+        <v>-1.588081467671415</v>
       </c>
       <c r="AK10">
-        <v>-2.085903665482049</v>
+        <v>-2.144495083360733</v>
       </c>
       <c r="AL10">
-        <v>-2.658809421329499</v>
+        <v>-2.788446245796797</v>
       </c>
       <c r="AM10">
-        <v>1.988827958919698</v>
+        <v>2.57285487600075</v>
       </c>
       <c r="AN10">
-        <v>2.400354864997008</v>
+        <v>2.486618874765054</v>
       </c>
       <c r="AO10">
-        <v>0.06372231821619306</v>
+        <v>0.05668533341722131</v>
       </c>
       <c r="AP10">
-        <v>1.14024</v>
+        <v>1.13777</v>
       </c>
       <c r="AQ10">
-        <v>1.121620090410704</v>
+        <v>1.116260279152847</v>
       </c>
       <c r="AR10">
-        <v>1.112795216466475</v>
+        <v>1.106010509926755</v>
       </c>
       <c r="AS10">
-        <v>1.14024</v>
+        <v>1.13777</v>
       </c>
       <c r="AT10">
-        <v>1.12228</v>
+        <v>1.11734</v>
       </c>
       <c r="AU10">
-        <v>1.121620090410704</v>
+        <v>1.116260279152847</v>
       </c>
       <c r="AV10">
-        <v>1.15265327305953</v>
+        <v>1.152109813898102</v>
       </c>
       <c r="AW10">
-        <v>-0.01632981616966218</v>
+        <v>-0.01890515732279183</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01632981616966218</v>
+        <v>0.01890515732279183</v>
       </c>
       <c r="AZ10">
-        <v>0.4482874674226232</v>
+        <v>0.4559535172153993</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3517125325773768</v>
+        <v>0.3440464827846007</v>
       </c>
       <c r="BC10" t="s">
         <v>122</v>
@@ -2969,22 +2969,22 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01088654411310812</v>
+        <v>0.01260343821519455</v>
       </c>
       <c r="BH10">
-        <v>45928.25737948987</v>
+        <v>39671.71429437453</v>
       </c>
       <c r="BI10">
-        <v>45928.25737948987</v>
+        <v>39671.71429437453</v>
       </c>
       <c r="BJ10">
-        <v>40279.46518232115</v>
+        <v>34867.95599670806</v>
       </c>
       <c r="BK10">
-        <v>459.2825737948987</v>
+        <v>396.7171429437453</v>
       </c>
       <c r="BL10">
-        <v>0.004592825737948988</v>
+        <v>0.003967171429437453</v>
       </c>
       <c r="BM10">
         <v>500</v>
@@ -2993,19 +2993,19 @@
         <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.02039035488453229</v>
+        <v>0.01994012827347854</v>
       </c>
       <c r="BP10">
-        <v>0.01654747555605129</v>
+        <v>0.01845179818392216</v>
       </c>
       <c r="BQ10">
-        <v>0.01642533051830474</v>
+        <v>0.01775576961076967</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT10" t="s">
         <v>125</v>
@@ -3017,7 +3017,7 @@
         <v>127</v>
       </c>
       <c r="BW10" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3025,7 +3025,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3049,19 +3049,19 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0.9148333723278068</v>
       </c>
       <c r="L11">
-        <v>2.606939258271708</v>
+        <v>2.493281471206344</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O11" t="s">
         <v>95</v>
@@ -3070,7 +3070,7 @@
         <v>98</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>0.9787083430819516</v>
       </c>
       <c r="R11" t="s">
         <v>102</v>
@@ -3079,10 +3079,10 @@
         <v>105</v>
       </c>
       <c r="T11">
-        <v>-0.8650041178133678</v>
+        <v>-0.9005834154530278</v>
       </c>
       <c r="U11">
-        <v>0.9392125146723864</v>
+        <v>0.9424138742155972</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
@@ -3091,22 +3091,22 @@
         <v>95</v>
       </c>
       <c r="X11">
-        <v>0.9998426466254836</v>
+        <v>0.9997053256502548</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-136.8853034100549</v>
+        <v>-143.5032023394873</v>
       </c>
       <c r="AA11">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="AB11">
-        <v>-0.7299869902260921</v>
+        <v>-0.8038901048208</v>
       </c>
       <c r="AC11">
-        <v>-0.6834610406604398</v>
+        <v>-0.5947778571628261</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
@@ -3121,67 +3121,67 @@
         <v>113</v>
       </c>
       <c r="AH11">
-        <v>-0.7298721243098271</v>
+        <v>-0.8036532190268953</v>
       </c>
       <c r="AI11">
-        <v>0.9110237886549594</v>
+        <v>0.9342438322494659</v>
       </c>
       <c r="AJ11">
-        <v>-1.92260762015714</v>
+        <v>-1.887874379105325</v>
       </c>
       <c r="AK11">
-        <v>-1.923421855165394</v>
+        <v>-1.529025323777559</v>
       </c>
       <c r="AL11">
-        <v>-3.50897594146149</v>
+        <v>-3.149732462578228</v>
       </c>
       <c r="AM11">
-        <v>2.711789877950863</v>
+        <v>3.462882975329206</v>
       </c>
       <c r="AN11">
-        <v>3.193175629649289</v>
+        <v>2.781737744488757</v>
       </c>
       <c r="AO11">
-        <v>0.0527815648785832</v>
+        <v>0.04546708782908851</v>
       </c>
       <c r="AP11">
-        <v>7.6411</v>
+        <v>7.6578</v>
       </c>
       <c r="AQ11">
-        <v>7.474334395423858</v>
+        <v>7.505453189223388</v>
       </c>
       <c r="AR11">
-        <v>7.388796722350728</v>
+        <v>7.424652347025853</v>
       </c>
       <c r="AS11">
-        <v>7.6411</v>
+        <v>7.6578</v>
       </c>
       <c r="AT11">
-        <v>7.4859</v>
+        <v>7.5193</v>
       </c>
       <c r="AU11">
-        <v>7.474334395423858</v>
+        <v>7.505453189223388</v>
       </c>
       <c r="AV11">
-        <v>7.752277069717428</v>
+        <v>7.759364540517741</v>
       </c>
       <c r="AW11">
-        <v>-0.02182481639765765</v>
+        <v>-0.01989433137149204</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.02182481639765765</v>
+        <v>0.01989433137149204</v>
       </c>
       <c r="AZ11">
-        <v>0.4387658749278224</v>
+        <v>0.4389629269302664</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3612341250721777</v>
+        <v>0.3610370730697336</v>
       </c>
       <c r="BC11" t="s">
         <v>123</v>
@@ -3193,46 +3193,46 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>500</v>
+        <v>489.3541715409758</v>
       </c>
       <c r="BG11">
-        <v>0.01454987759843843</v>
+        <v>0.01326288758099469</v>
       </c>
       <c r="BH11">
-        <v>34364.55025942366</v>
+        <v>37699.18103780692</v>
       </c>
       <c r="BI11">
-        <v>34364.55025942366</v>
+        <v>36896.50300905854</v>
       </c>
       <c r="BJ11">
-        <v>4497.330261274379</v>
+        <v>4818.159655391698</v>
       </c>
       <c r="BK11">
-        <v>343.6455025942366</v>
+        <v>368.9650300905854</v>
       </c>
       <c r="BL11">
-        <v>0.003436455025942366</v>
+        <v>0.003689650300905854</v>
       </c>
       <c r="BM11">
-        <v>500</v>
+        <v>489.3541715409759</v>
       </c>
       <c r="BN11">
-        <v>0.005</v>
+        <v>0.00489354171540976</v>
       </c>
       <c r="BO11">
-        <v>0.1322861075944443</v>
+        <v>0.1188689254895395</v>
       </c>
       <c r="BP11">
-        <v>0.1173279859843811</v>
+        <v>0.1039987737545497</v>
       </c>
       <c r="BQ11">
-        <v>0.09758862813742765</v>
+        <v>0.08769261655424945</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.03703469011697844</v>
+        <v>0.03794913607698633</v>
       </c>
       <c r="BT11" t="s">
         <v>125</v>
@@ -3244,7 +3244,7 @@
         <v>127</v>
       </c>
       <c r="BW11" s="2">
-        <v>46319</v>
+        <v>46321</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="124">
   <si>
     <t>Pair</t>
   </si>
@@ -241,160 +241,148 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>USDCHF</t>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
   </si>
   <si>
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
-    <t>UP_ACCELERATING</t>
-  </si>
-  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
+    <t>多头加速</t>
+  </si>
+  <si>
     <t>空头减速</t>
   </si>
   <si>
-    <t>多头加速</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
+    <t>上涨</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
-    <t>上涨</t>
+    <t>UP_STEEPENING</t>
   </si>
   <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
-    <t>UP_STEEPENING</t>
-  </si>
-  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
     <t>下降谷底收敛</t>
   </si>
   <si>
-    <t>上升陡坡形成</t>
-  </si>
-  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.05349,naive=0.02231,drift4=0.03101; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.01082,naive=0.01141,drift4=0.009323; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=293.8,naive=95.04,drift4=99.22; naive_cap_applied; model_divergence_guard(abs=491.1,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=3.073,naive=3.085,drift4=4.964; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=0.009391,naive=0.01397,drift4=0.01647; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=model; scores=model=0.06572,naive=0.07539,drift4=0.08554; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.1632,naive=0.1315,drift4=0.09657; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.02398,naive=0.02407,drift4=0.02069; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01994,naive=0.01845,drift4=0.01776; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.1189,naive=0.104,drift4=0.08769; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.01458,naive=0.01196,drift4=0.00835; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=naive; scores=model=2.938,naive=2.411,drift4=4.341; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04442,naive=0.01955,drift4=0.02586; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1505,naive=0.1161,drift4=0.08421; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=model; scores=model=0.05543,naive=0.07071,drift4=0.07489; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.009356,naive=0.01274,drift4=0.0147; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02238,naive=0.017,drift4=0.01538; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02587,naive=0.02063,drift4=0.01792; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1395,naive=0.09655,drift4=0.07629; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=583.1,naive=174.2,drift4=129.2; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -994,7 +982,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1015,136 +1003,145 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1.553656358261324</v>
+        <v>2.932167664138002</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="O2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T2">
-        <v>-0.7441634316464502</v>
+        <v>0.9218538591375706</v>
       </c>
       <c r="U2">
-        <v>0.7347092904436736</v>
+        <v>0.9647819294336638</v>
       </c>
       <c r="V2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9993429848110841</v>
+        <v>0.9997907712870285</v>
       </c>
       <c r="Y2">
-        <v>0.6314948200763472</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>121.1266661180417</v>
+        <v>32.46800368571632</v>
       </c>
       <c r="AA2">
-        <v>-18</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="AB2">
-        <v>-0.516931789508032</v>
+        <v>0.8436913644369721</v>
       </c>
       <c r="AC2">
-        <v>0.856026591290261</v>
+        <v>0.5368285402011337</v>
       </c>
       <c r="AD2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AF2" t="s">
         <v>106</v>
       </c>
-      <c r="AF2" t="s">
-        <v>108</v>
-      </c>
       <c r="AG2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH2">
-        <v>-0.4214087145027491</v>
+        <v>0.8435148399786458</v>
       </c>
       <c r="AI2">
-        <v>0.7760809504182696</v>
+        <v>0.9462415230111136</v>
       </c>
       <c r="AJ2">
-        <v>-1.271926308750624</v>
+        <v>2.192111888492398</v>
       </c>
       <c r="AK2">
-        <v>1.976159184924614</v>
+        <v>1.389207911484684</v>
       </c>
       <c r="AL2">
-        <v>-1.59135535249199</v>
+        <v>3.807126716510738</v>
       </c>
       <c r="AM2">
-        <v>3.276585817871569</v>
+        <v>-3.104391978020509</v>
       </c>
       <c r="AN2">
-        <v>1.352819908812047</v>
+        <v>3.489051630129082</v>
       </c>
       <c r="AO2">
-        <v>0.03378396755525835</v>
+        <v>0.04528437513625278</v>
       </c>
       <c r="AP2">
-        <v>6.722455</v>
+        <v>0.8329800000000001</v>
       </c>
       <c r="AQ2">
-        <v>6.720578808223988</v>
+        <v>0.8468376486247797</v>
       </c>
       <c r="AR2">
-        <v>6.725598777192802</v>
+        <v>0.8450935075735262</v>
       </c>
       <c r="AS2">
-        <v>6.722455</v>
+        <v>0.8329800000000001</v>
       </c>
       <c r="AT2">
-        <v>6.713685</v>
+        <v>0.8559450000000002</v>
+      </c>
+      <c r="AU2">
+        <v>0.8468376486247797</v>
+      </c>
+      <c r="AV2">
+        <v>0.8237415675834803</v>
       </c>
       <c r="AW2">
-        <v>-0.0002790932443597124</v>
+        <v>0.01663623211215116</v>
+      </c>
+      <c r="AX2">
+        <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.0002790932443597124</v>
+        <v>0.01663623211215116</v>
       </c>
       <c r="AZ2">
-        <v>0.4314171853988076</v>
+        <v>0.4160120283738065</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3685828146011924</v>
+        <v>0.3839879716261935</v>
       </c>
       <c r="BC2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1153,55 +1150,58 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="BG2">
+        <v>0.01109082140810077</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>45082.32362616518</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>45082.32362616518</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>54121.7359674484</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>450.8232362616517</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>0.004508232362616517</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="BO2">
-        <v>0.05348874741949559</v>
+        <v>0.01458490297650403</v>
       </c>
       <c r="BP2">
-        <v>0.02230689060362511</v>
+        <v>0.01196134736379736</v>
       </c>
       <c r="BQ2">
-        <v>0.03101449469704753</v>
+        <v>0.008350487428316263</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="BW2" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1209,7 +1209,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1224,151 +1224,151 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>2.771955978776556</v>
+        <v>0.6027559670788827</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T3">
-        <v>0.966604633832096</v>
+        <v>-0.7533042661490058</v>
       </c>
       <c r="U3">
-        <v>0.9849232799787089</v>
+        <v>0.7385549057734455</v>
       </c>
       <c r="V3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W3" t="s">
         <v>94</v>
       </c>
-      <c r="W3" t="s">
-        <v>95</v>
-      </c>
       <c r="X3">
-        <v>0.9998047790170624</v>
+        <v>0.9982719440255712</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0.1322712175335533</v>
       </c>
       <c r="Z3">
-        <v>21.06030066615424</v>
+        <v>111.7585844870444</v>
       </c>
       <c r="AA3">
-        <v>-12.99999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB3">
-        <v>0.9332027469149962</v>
+        <v>-0.370696594622404</v>
       </c>
       <c r="AC3">
-        <v>0.3593502930989561</v>
+        <v>0.9287540227290286</v>
       </c>
       <c r="AD3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF3" t="s">
         <v>107</v>
       </c>
-      <c r="AF3" t="s">
-        <v>109</v>
-      </c>
       <c r="AG3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AH3">
-        <v>0.9330205661574634</v>
+        <v>-0.2095018845882451</v>
       </c>
       <c r="AI3">
-        <v>0.9733599994677484</v>
+        <v>0.6274303558378602</v>
       </c>
       <c r="AJ3">
-        <v>2.083345892564772</v>
+        <v>-0.5068419590390092</v>
       </c>
       <c r="AK3">
-        <v>0.8638397659875174</v>
+        <v>1.371187588717483</v>
       </c>
       <c r="AL3">
-        <v>3.558600649852225</v>
+        <v>-0.5107035571324423</v>
       </c>
       <c r="AM3">
-        <v>-3.261242385719994</v>
+        <v>0.6156979308825091</v>
       </c>
       <c r="AN3">
-        <v>3.226954040271941</v>
+        <v>0.5221834591978205</v>
       </c>
       <c r="AO3">
-        <v>0.04354998175148109</v>
+        <v>0.06418697643014314</v>
       </c>
       <c r="AP3">
-        <v>0.8286450000000001</v>
+        <v>157.035</v>
       </c>
       <c r="AQ3">
-        <v>0.840778383137571</v>
+        <v>158.1763837352517</v>
       </c>
       <c r="AR3">
-        <v>0.8403531016693058</v>
+        <v>158.7035878012672</v>
       </c>
       <c r="AS3">
-        <v>0.8286450000000001</v>
+        <v>157.035</v>
       </c>
       <c r="AT3">
-        <v>0.8482900000000002</v>
+        <v>158.056</v>
       </c>
       <c r="AU3">
-        <v>0.840778383137571</v>
+        <v>158.1763837352517</v>
       </c>
       <c r="AV3">
-        <v>0.8205560779082861</v>
+        <v>155.536875</v>
       </c>
       <c r="AW3">
-        <v>0.01464243812195928</v>
+        <v>0.007268339766623595</v>
       </c>
       <c r="AX3">
-        <v>1.5</v>
+        <v>0.7618748337099535</v>
       </c>
       <c r="AY3">
-        <v>0.01464243812195928</v>
+        <v>0.007268339766623595</v>
       </c>
       <c r="AZ3">
-        <v>0.4513875210640012</v>
+        <v>0.5012196564181495</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3486124789359988</v>
+        <v>0.2987803435818505</v>
       </c>
       <c r="BC3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1380,22 +1380,22 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009761625414639524</v>
+        <v>0.009540070684879269</v>
       </c>
       <c r="BH3">
-        <v>51220.97793776734</v>
+        <v>52410.51314142622</v>
       </c>
       <c r="BI3">
-        <v>51220.97793776734</v>
+        <v>52410.51314142622</v>
       </c>
       <c r="BJ3">
-        <v>61812.93308686752</v>
+        <v>333.7505214851863</v>
       </c>
       <c r="BK3">
-        <v>512.2097793776734</v>
+        <v>524.1051314142622</v>
       </c>
       <c r="BL3">
-        <v>0.005122097793776734</v>
+        <v>0.005241051314142623</v>
       </c>
       <c r="BM3">
         <v>500</v>
@@ -1404,31 +1404,31 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>0.01081640700663146</v>
+        <v>2.937820126934294</v>
       </c>
       <c r="BP3">
-        <v>0.01140536508399152</v>
+        <v>2.41064466159896</v>
       </c>
       <c r="BQ3">
-        <v>0.009323110491309244</v>
+        <v>4.340942912653166</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW3" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1436,7 +1436,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1448,154 +1448,154 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.461376602456803</v>
+        <v>1.59972298782819</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" t="s">
         <v>102</v>
       </c>
-      <c r="S4" t="s">
-        <v>105</v>
-      </c>
       <c r="T4">
-        <v>-0.76950823222412</v>
+        <v>-0.8233824537727303</v>
       </c>
       <c r="U4">
-        <v>0.7462381362649918</v>
+        <v>0.7704458387086559</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
       </c>
       <c r="W4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9998377270565512</v>
+        <v>0.9996949380437088</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>0.2643328411100709</v>
       </c>
       <c r="Z4">
-        <v>-108.9605010459745</v>
+        <v>126.5017684982347</v>
       </c>
       <c r="AA4">
-        <v>-6.999999999999997</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AB4">
-        <v>-0.3249162491209054</v>
+        <v>-0.594847598407908</v>
       </c>
       <c r="AC4">
-        <v>-0.9457427932885356</v>
+        <v>0.8038385003645597</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF4" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG4" t="s">
         <v>110</v>
       </c>
-      <c r="AG4" t="s">
-        <v>113</v>
-      </c>
       <c r="AH4">
-        <v>-0.1624317620023931</v>
+        <v>-0.3759279607465731</v>
       </c>
       <c r="AI4">
-        <v>0.5854529060921151</v>
+        <v>0.7267869082306386</v>
       </c>
       <c r="AJ4">
-        <v>-0.325902664262283</v>
+        <v>-1.215020172870769</v>
       </c>
       <c r="AK4">
-        <v>-0.9932626463738097</v>
+        <v>1.617118747976555</v>
       </c>
       <c r="AL4">
-        <v>-0.6796074969203546</v>
+        <v>-1.990772269975929</v>
       </c>
       <c r="AM4">
-        <v>0.2419988380794569</v>
+        <v>1.494423962202693</v>
       </c>
       <c r="AN4">
-        <v>0.6383726808067267</v>
+        <v>1.904882111597325</v>
       </c>
       <c r="AO4">
-        <v>0.07976782075966257</v>
+        <v>0.0295144521936399</v>
       </c>
       <c r="AP4">
-        <v>4284.91</v>
+        <v>6.70401</v>
       </c>
       <c r="AQ4">
-        <v>4337.465758670276</v>
+        <v>6.723505385672373</v>
       </c>
       <c r="AR4">
-        <v>4689.842528900921</v>
+        <v>6.752111735273507</v>
       </c>
       <c r="AS4">
-        <v>4284.91</v>
+        <v>6.70401</v>
       </c>
       <c r="AT4">
-        <v>4112.599999999999</v>
+        <v>6.700735</v>
       </c>
       <c r="AU4">
-        <v>4337.465758670276</v>
+        <v>6.723505385672373</v>
       </c>
       <c r="AV4">
-        <v>4151.2725</v>
+        <v>6.680503750000001</v>
       </c>
       <c r="AW4">
-        <v>0.01226531214664396</v>
+        <v>0.002908018584753482</v>
       </c>
       <c r="AX4">
-        <v>0.3932710404660079</v>
+        <v>0.8293703024673653</v>
       </c>
       <c r="AY4">
-        <v>0.01226531214664396</v>
+        <v>0.002908018584753482</v>
       </c>
       <c r="AZ4">
-        <v>0.3</v>
+        <v>0.4304552547888046</v>
       </c>
       <c r="BA4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.4</v>
+        <v>0.3695447452111953</v>
       </c>
       <c r="BC4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1607,55 +1607,55 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.03118793626937326</v>
+        <v>0.003506296977480585</v>
       </c>
       <c r="BH4">
-        <v>16031.83986530725</v>
+        <v>142600.5849508133</v>
       </c>
       <c r="BI4">
-        <v>16031.83986530725</v>
+        <v>142600.5849508133</v>
       </c>
       <c r="BJ4">
-        <v>3.741464783462721</v>
+        <v>21270.9385801652</v>
       </c>
       <c r="BK4">
-        <v>160.3183986530725</v>
+        <v>1426.005849508133</v>
       </c>
       <c r="BL4">
-        <v>0.001603183986530725</v>
+        <v>0.01426005849508133</v>
       </c>
       <c r="BM4">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN4">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO4">
-        <v>293.8362333155085</v>
+        <v>0.04441568089305444</v>
       </c>
       <c r="BP4">
-        <v>95.0449793786315</v>
+        <v>0.01954760957488873</v>
       </c>
       <c r="BQ4">
-        <v>99.21532252031129</v>
+        <v>0.02585904693129224</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV4" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW4" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1663,7 +1663,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1675,7 +1675,7 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1687,25 +1687,25 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0.4656618797617593</v>
+        <v>1.650686963337997</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="O5" t="s">
+        <v>94</v>
+      </c>
+      <c r="P5" t="s">
         <v>96</v>
-      </c>
-      <c r="P5" t="s">
-        <v>99</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -1717,40 +1717,40 @@
         <v>103</v>
       </c>
       <c r="T5">
-        <v>-0.6372822385028896</v>
+        <v>-0.9156846880096801</v>
       </c>
       <c r="U5">
-        <v>0.6866487673838128</v>
+        <v>0.9620062704350962</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
       </c>
       <c r="W5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X5">
-        <v>0.9994870402300498</v>
+        <v>0.9997926433229609</v>
       </c>
       <c r="Y5">
-        <v>0.4989245714908739</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>105.9025552549323</v>
+        <v>-146.2378611632244</v>
       </c>
       <c r="AA5">
-        <v>-4.999999999999995</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AB5">
-        <v>-0.2740021097855445</v>
+        <v>-0.8313518890504025</v>
       </c>
       <c r="AC5">
-        <v>0.961729090665906</v>
+        <v>-0.5557463779210147</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF5" t="s">
         <v>108</v>
@@ -1759,70 +1759,70 @@
         <v>111</v>
       </c>
       <c r="AH5">
-        <v>-0.205248909031391</v>
+        <v>-0.8311795026852388</v>
       </c>
       <c r="AI5">
-        <v>0.6680714303987534</v>
+        <v>0.9429933139314797</v>
       </c>
       <c r="AJ5">
-        <v>-0.4969293061111932</v>
+        <v>-1.276388143369669</v>
       </c>
       <c r="AK5">
-        <v>1.662264372548948</v>
+        <v>-0.9110023757400542</v>
       </c>
       <c r="AL5">
-        <v>-0.2879211642521388</v>
+        <v>-1.963456515348875</v>
       </c>
       <c r="AM5">
-        <v>1.0851574638904</v>
+        <v>2.544165157925495</v>
       </c>
       <c r="AN5">
-        <v>0.2744702378443663</v>
+        <v>1.708720613577435</v>
       </c>
       <c r="AO5">
-        <v>0.09156387277068113</v>
+        <v>0.04226451964451648</v>
       </c>
       <c r="AP5">
-        <v>157.2345</v>
+        <v>8.89554</v>
       </c>
       <c r="AQ5">
-        <v>157.7350547722465</v>
+        <v>8.829778631827244</v>
       </c>
       <c r="AR5">
-        <v>159.8563858250094</v>
+        <v>8.89872953157983</v>
       </c>
       <c r="AS5">
-        <v>157.2345</v>
+        <v>8.89554</v>
       </c>
       <c r="AT5">
-        <v>154.3925</v>
+        <v>8.72133</v>
       </c>
       <c r="AU5">
-        <v>157.7350547722465</v>
+        <v>8.829778631827244</v>
       </c>
       <c r="AV5">
-        <v>155.736375</v>
+        <v>8.965752500000001</v>
       </c>
       <c r="AW5">
-        <v>0.00318349199600889</v>
+        <v>-0.007392622389731985</v>
       </c>
       <c r="AX5">
-        <v>0.3341208325383092</v>
+        <v>0.936604852024313</v>
       </c>
       <c r="AY5">
-        <v>0.00318349199600889</v>
+        <v>0.007392622389731985</v>
       </c>
       <c r="AZ5">
-        <v>0.5077256116056714</v>
+        <v>0.4149201025038798</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.2922743883943285</v>
+        <v>0.3850798974961202</v>
       </c>
       <c r="BC5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1834,22 +1834,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.009527966190626205</v>
+        <v>0.007893000312516085</v>
       </c>
       <c r="BH5">
-        <v>52477.09637046252</v>
+        <v>63347.26722449766</v>
       </c>
       <c r="BI5">
-        <v>52477.09637046252</v>
+        <v>63347.26722449766</v>
       </c>
       <c r="BJ5">
-        <v>333.7505214851863</v>
+        <v>7121.239095602702</v>
       </c>
       <c r="BK5">
-        <v>524.7709637046252</v>
+        <v>633.4726722449766</v>
       </c>
       <c r="BL5">
-        <v>0.005247709637046251</v>
+        <v>0.006334726722449766</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1858,31 +1858,31 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>3.072926972048653</v>
+        <v>0.1505374517041939</v>
       </c>
       <c r="BP5">
-        <v>3.085441892668619</v>
+        <v>0.1160585727127575</v>
       </c>
       <c r="BQ5">
-        <v>4.963623601441139</v>
+        <v>0.08420706933258511</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW5" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1890,7 +1890,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1902,154 +1902,154 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.1139093758378123</v>
       </c>
       <c r="L6">
-        <v>0.9932868956067169</v>
+        <v>0.8812195371627741</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>0.7784773439594531</v>
       </c>
       <c r="R6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T6">
-        <v>-0.5645177567596933</v>
+        <v>-0.7168960933814398</v>
       </c>
       <c r="U6">
-        <v>0.6539994770128366</v>
+        <v>0.7396580646989981</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
       </c>
       <c r="W6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X6">
-        <v>0.9998659458838982</v>
+        <v>0.9998736652067134</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-105.6956783367861</v>
+        <v>-121.0171635773847</v>
       </c>
       <c r="AA6">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="AB6">
-        <v>-0.2705278320129815</v>
+        <v>-0.5152948256368708</v>
       </c>
       <c r="AC6">
-        <v>-0.9627121543360487</v>
+        <v>-0.8570129769565143</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
       </c>
       <c r="AE6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AH6">
-        <v>-0.27049156664358</v>
+        <v>-0.5152297259715923</v>
       </c>
       <c r="AI6">
-        <v>0.7641073423462377</v>
+        <v>0.844495057941078</v>
       </c>
       <c r="AJ6">
-        <v>-0.6965267282036537</v>
+        <v>-0.6365195457344136</v>
       </c>
       <c r="AK6">
-        <v>-2.653163019204379</v>
+        <v>-1.120271831010521</v>
       </c>
       <c r="AL6">
-        <v>-1.758527870195961</v>
+        <v>-1.246666538707811</v>
       </c>
       <c r="AM6">
-        <v>0.1702143361458303</v>
+        <v>0.8468396378540953</v>
       </c>
       <c r="AN6">
-        <v>1.650793431524987</v>
+        <v>1.13024247798072</v>
       </c>
       <c r="AO6">
-        <v>0.1133605887801404</v>
+        <v>0.06699448381555198</v>
       </c>
       <c r="AP6">
-        <v>0.70094</v>
+        <v>4.70822</v>
       </c>
       <c r="AQ6">
-        <v>0.6971472480782931</v>
+        <v>4.670264561368022</v>
       </c>
       <c r="AR6">
-        <v>0.7017196448747367</v>
+        <v>4.708030255836245</v>
       </c>
       <c r="AS6">
-        <v>0.70094</v>
+        <v>4.70822</v>
       </c>
       <c r="AT6">
-        <v>0.68628</v>
+        <v>4.58541</v>
       </c>
       <c r="AU6">
-        <v>0.6971472480782931</v>
+        <v>4.670264561368022</v>
       </c>
       <c r="AV6">
-        <v>0.7081487499999999</v>
+        <v>4.750865</v>
       </c>
       <c r="AW6">
-        <v>-0.005410950896948264</v>
+        <v>-0.008061526146182217</v>
       </c>
       <c r="AX6">
-        <v>0.5261317040689374</v>
+        <v>0.8900325625976784</v>
       </c>
       <c r="AY6">
-        <v>0.005410950896948264</v>
+        <v>0.008061526146182217</v>
       </c>
       <c r="AZ6">
-        <v>0.5139527588019327</v>
+        <v>0.4917014807776953</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.2860472411980673</v>
+        <v>0.3082985192223047</v>
       </c>
       <c r="BC6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2058,58 +2058,58 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>375</v>
+        <v>389.2386719797266</v>
       </c>
       <c r="BG6">
-        <v>0.01028440380061051</v>
+        <v>0.009057563155502513</v>
       </c>
       <c r="BH6">
-        <v>48617.30535807226</v>
+        <v>55202.48563723761</v>
       </c>
       <c r="BI6">
-        <v>36462.97901855419</v>
+        <v>42973.88439883659</v>
       </c>
       <c r="BJ6">
-        <v>52020.11444425228</v>
+        <v>9127.416390660715</v>
       </c>
       <c r="BK6">
-        <v>364.6297901855419</v>
+        <v>429.7388439883659</v>
       </c>
       <c r="BL6">
-        <v>0.003646297901855419</v>
+        <v>0.004297388439883659</v>
       </c>
       <c r="BM6">
-        <v>375</v>
+        <v>389.2386719797266</v>
       </c>
       <c r="BN6">
-        <v>0.00375</v>
+        <v>0.003892386719797266</v>
       </c>
       <c r="BO6">
-        <v>0.009390655634912228</v>
+        <v>0.05543408485399783</v>
       </c>
       <c r="BP6">
-        <v>0.013969378924017</v>
+        <v>0.07071449030372613</v>
       </c>
       <c r="BQ6">
-        <v>0.01646719235472326</v>
+        <v>0.0748891245846756</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW6" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2117,7 +2117,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2129,154 +2129,154 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.7854436532796554</v>
+        <v>1.231225676064555</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q7">
         <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T7">
-        <v>-0.6883344829636022</v>
+        <v>-0.595924863504193</v>
       </c>
       <c r="U7">
-        <v>0.7097055200273884</v>
+        <v>0.6681437470584861</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
       </c>
       <c r="W7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9998200107750694</v>
+        <v>0.9999102339263967</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-118.5497975325826</v>
+        <v>-108.8535103508429</v>
       </c>
       <c r="AA7">
-        <v>-15</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB7">
-        <v>-0.4779223870539749</v>
+        <v>-0.3231496604105653</v>
       </c>
       <c r="AC7">
-        <v>-0.8784020673658678</v>
+        <v>-0.9463478731293986</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AH7">
-        <v>-0.4778363661739521</v>
+        <v>-0.323120652534364</v>
       </c>
       <c r="AI7">
-        <v>0.8317376753168102</v>
+        <v>0.7834993593713424</v>
       </c>
       <c r="AJ7">
-        <v>-0.5516853420326328</v>
+        <v>-0.8666558135598412</v>
       </c>
       <c r="AK7">
-        <v>-1.093985872863719</v>
+        <v>-2.656708430055078</v>
       </c>
       <c r="AL7">
-        <v>-1.18034673663606</v>
+        <v>-1.837967646475184</v>
       </c>
       <c r="AM7">
-        <v>0.5677450671431065</v>
+        <v>0.9485436712745416</v>
       </c>
       <c r="AN7">
-        <v>1.084772897096356</v>
+        <v>1.667661908120894</v>
       </c>
       <c r="AO7">
-        <v>0.07717363047104363</v>
+        <v>0.08942747084043955</v>
       </c>
       <c r="AP7">
-        <v>4.72135</v>
+        <v>0.700515</v>
       </c>
       <c r="AQ7">
-        <v>4.690199290006634</v>
+        <v>0.6939588303130619</v>
       </c>
       <c r="AR7">
-        <v>4.719232681557525</v>
+        <v>0.6990084940198391</v>
       </c>
       <c r="AS7">
-        <v>4.72135</v>
+        <v>0.700515</v>
       </c>
       <c r="AT7">
-        <v>4.62455</v>
+        <v>0.680885</v>
       </c>
       <c r="AU7">
-        <v>4.690199290006634</v>
+        <v>0.6939588303130619</v>
       </c>
       <c r="AV7">
-        <v>4.763995</v>
+        <v>0.70772375</v>
       </c>
       <c r="AW7">
-        <v>-0.0065978395995566</v>
+        <v>-0.009359071093321432</v>
       </c>
       <c r="AX7">
-        <v>0.7304657050853915</v>
+        <v>0.9094738598145484</v>
       </c>
       <c r="AY7">
-        <v>0.0065978395995566</v>
+        <v>0.009359071093321432</v>
       </c>
       <c r="AZ7">
-        <v>0.4888886673378569</v>
+        <v>0.504749818277214</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3111113326621431</v>
+        <v>0.295250181722786</v>
       </c>
       <c r="BC7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2288,55 +2288,55 @@
         <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.009032374215002074</v>
+        <v>0.01029064331242005</v>
       </c>
       <c r="BH7">
-        <v>55356.43100011719</v>
+        <v>48587.82729322051</v>
       </c>
       <c r="BI7">
-        <v>41517.32325008789</v>
+        <v>36440.87046991539</v>
       </c>
       <c r="BJ7">
-        <v>8793.527963418916</v>
+        <v>52020.11444425229</v>
       </c>
       <c r="BK7">
-        <v>415.173232500879</v>
+        <v>364.4087046991539</v>
       </c>
       <c r="BL7">
-        <v>0.00415173232500879</v>
+        <v>0.003644087046991539</v>
       </c>
       <c r="BM7">
-        <v>375</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN7">
-        <v>0.00375</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO7">
-        <v>0.06572396496462461</v>
+        <v>0.009356290313371035</v>
       </c>
       <c r="BP7">
-        <v>0.07539459805921911</v>
+        <v>0.01274452855590083</v>
       </c>
       <c r="BQ7">
-        <v>0.08553679890027988</v>
+        <v>0.01470120815420496</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW7" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2344,7 +2344,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2356,154 +2356,154 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1.680550403729014</v>
+        <v>2.319262127002522</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T8">
-        <v>-0.8855271921817665</v>
+        <v>-0.8233672241928232</v>
       </c>
       <c r="U8">
-        <v>0.9484558051191534</v>
+        <v>0.9204933629019073</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
       </c>
       <c r="W8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9998742745494339</v>
+        <v>0.9999124480605475</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-140.4473711516528</v>
+        <v>-130.2946815533073</v>
       </c>
       <c r="AA8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="AB8">
-        <v>-0.7710399904085061</v>
+        <v>-0.6467189824894843</v>
       </c>
       <c r="AC8">
-        <v>-0.6367867250428912</v>
+        <v>-0.7627283642868974</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AH8">
-        <v>-0.7709430510583075</v>
+        <v>-0.6466623609882867</v>
       </c>
       <c r="AI8">
-        <v>0.9242730690792125</v>
+        <v>0.8861291279153403</v>
       </c>
       <c r="AJ8">
-        <v>-1.281459118945528</v>
+        <v>-1.748288201739388</v>
       </c>
       <c r="AK8">
-        <v>-1.109466462516039</v>
+        <v>-2.152294668115119</v>
       </c>
       <c r="AL8">
-        <v>-2.07682591302683</v>
+        <v>-2.951780375378513</v>
       </c>
       <c r="AM8">
-        <v>2.337058766020589</v>
+        <v>2.943748028975494</v>
       </c>
       <c r="AN8">
-        <v>1.830539036054295</v>
+        <v>2.626531266664112</v>
       </c>
       <c r="AO8">
-        <v>0.0466328275709414</v>
+        <v>0.05237282435131042</v>
       </c>
       <c r="AP8">
-        <v>8.908250000000001</v>
+        <v>1.135555</v>
       </c>
       <c r="AQ8">
-        <v>8.843319243234429</v>
+        <v>1.124658252520412</v>
       </c>
       <c r="AR8">
-        <v>8.935269980348812</v>
+        <v>1.132172341597065</v>
       </c>
       <c r="AS8">
-        <v>8.908250000000001</v>
+        <v>1.135555</v>
       </c>
       <c r="AT8">
-        <v>8.707850000000001</v>
+        <v>1.109765</v>
       </c>
       <c r="AU8">
-        <v>8.843319243234429</v>
+        <v>1.124658252520412</v>
       </c>
       <c r="AV8">
-        <v>8.9893175</v>
+        <v>1.145915</v>
       </c>
       <c r="AW8">
-        <v>-0.007288834144256332</v>
+        <v>-0.009595966271636745</v>
       </c>
       <c r="AX8">
-        <v>0.80094682536863</v>
+        <v>1.051809602276875</v>
       </c>
       <c r="AY8">
-        <v>0.007288834144256332</v>
+        <v>0.009595966271636745</v>
       </c>
       <c r="AZ8">
-        <v>0.4194409087896486</v>
+        <v>0.4344670909862309</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3805590912103514</v>
+        <v>0.3655329090137691</v>
       </c>
       <c r="BC8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2515,22 +2515,22 @@
         <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.009100272219571753</v>
+        <v>0.009123292134683072</v>
       </c>
       <c r="BH8">
-        <v>54943.41135473521</v>
+        <v>54804.77799227781</v>
       </c>
       <c r="BI8">
-        <v>54943.41135473521</v>
+        <v>54804.77799227781</v>
       </c>
       <c r="BJ8">
-        <v>6167.699756375854</v>
+        <v>48262.54826254809</v>
       </c>
       <c r="BK8">
-        <v>549.4341135473521</v>
+        <v>548.0477799227781</v>
       </c>
       <c r="BL8">
-        <v>0.005494341135473521</v>
+        <v>0.005480477799227781</v>
       </c>
       <c r="BM8">
         <v>500</v>
@@ -2539,31 +2539,31 @@
         <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.163156079899769</v>
+        <v>0.02237877538157037</v>
       </c>
       <c r="BP8">
-        <v>0.1314544086006516</v>
+        <v>0.01699771817582816</v>
       </c>
       <c r="BQ8">
-        <v>0.09656612302088997</v>
+        <v>0.01537929770192019</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW8" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2571,7 +2571,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2583,154 +2583,154 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>2.433491918712662</v>
+        <v>2.466913398925232</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T9">
-        <v>-0.8071098751366853</v>
+        <v>-0.8287815975951317</v>
       </c>
       <c r="U9">
-        <v>0.9131857171886492</v>
+        <v>0.9229361870932464</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
       </c>
       <c r="W9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X9">
-        <v>0.9999450935085634</v>
+        <v>0.9999378727017488</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-127.894478809305</v>
+        <v>-131.1134829237438</v>
       </c>
       <c r="AA9">
-        <v>-5.999999999999996</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB9">
-        <v>-0.6142091587718395</v>
+        <v>-0.657552557192601</v>
       </c>
       <c r="AC9">
-        <v>-0.7891432755088199</v>
+        <v>-0.7534086769672029</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
       </c>
       <c r="AE9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AH9">
-        <v>-0.614175434701923</v>
+        <v>-0.6575117052287645</v>
       </c>
       <c r="AI9">
-        <v>0.8759707461057231</v>
+        <v>0.8900777640785847</v>
       </c>
       <c r="AJ9">
-        <v>-1.840866142847872</v>
+        <v>-1.911796185433251</v>
       </c>
       <c r="AK9">
-        <v>-2.426251652530377</v>
+        <v>-2.258467911996093</v>
       </c>
       <c r="AL9">
-        <v>-3.063933652710714</v>
+        <v>-2.913296091257616</v>
       </c>
       <c r="AM9">
-        <v>3.14378323842924</v>
+        <v>3.95866498724083</v>
       </c>
       <c r="AN9">
-        <v>2.709019752958548</v>
+        <v>2.499134567504587</v>
       </c>
       <c r="AO9">
-        <v>0.05515189502550502</v>
+        <v>0.04777505683205054</v>
       </c>
       <c r="AP9">
-        <v>1.323345</v>
+        <v>1.32477</v>
       </c>
       <c r="AQ9">
-        <v>1.311698859235281</v>
+        <v>1.311168234181072</v>
       </c>
       <c r="AR9">
-        <v>1.32075178303796</v>
+        <v>1.316181811869156</v>
       </c>
       <c r="AS9">
-        <v>1.323345</v>
+        <v>1.32477</v>
       </c>
       <c r="AT9">
-        <v>1.293245</v>
+        <v>1.29777</v>
       </c>
       <c r="AU9">
-        <v>1.311698859235281</v>
+        <v>1.311168234181072</v>
       </c>
       <c r="AV9">
-        <v>1.3365075</v>
+        <v>1.3379325</v>
       </c>
       <c r="AW9">
-        <v>-0.008800532563102285</v>
+        <v>-0.01026726587930586</v>
       </c>
       <c r="AX9">
-        <v>0.8847970191619087</v>
+        <v>1.033372521855883</v>
       </c>
       <c r="AY9">
-        <v>0.008800532563102285</v>
+        <v>0.01026726587930586</v>
       </c>
       <c r="AZ9">
-        <v>0.4520288402363377</v>
+        <v>0.434407772462125</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3479711597636623</v>
+        <v>0.3655922275378751</v>
       </c>
       <c r="BC9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2742,55 +2742,55 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.0099463858630969</v>
+        <v>0.009935686949432705</v>
       </c>
       <c r="BH9">
-        <v>50269.51566951579</v>
+        <v>50323.64672364686</v>
       </c>
       <c r="BI9">
-        <v>50269.51566951579</v>
+        <v>50323.64672364686</v>
       </c>
       <c r="BJ9">
         <v>37986.70465337142</v>
       </c>
       <c r="BK9">
-        <v>502.6951566951579</v>
+        <v>503.2364672364686</v>
       </c>
       <c r="BL9">
-        <v>0.005026951566951579</v>
+        <v>0.005032364672364687</v>
       </c>
       <c r="BM9">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="BN9">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.02397734359525433</v>
+        <v>0.02587249420031677</v>
       </c>
       <c r="BP9">
-        <v>0.0240683090367852</v>
+        <v>0.02062747324503312</v>
       </c>
       <c r="BQ9">
-        <v>0.02068553988895863</v>
+        <v>0.01791816760719848</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV9" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW9" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2798,7 +2798,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2810,154 +2810,154 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0.9516467148497846</v>
       </c>
       <c r="L10">
-        <v>2.129473063872976</v>
+        <v>2.531869505183189</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0.9879116787124461</v>
       </c>
       <c r="R10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T10">
-        <v>-0.8077528568583739</v>
+        <v>-0.9269663208517464</v>
       </c>
       <c r="U10">
-        <v>0.9134586544216092</v>
+        <v>0.9598096798408658</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X10">
-        <v>0.9998794753413637</v>
+        <v>0.9997113129204496</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-127.9869909050153</v>
+        <v>-148.7663191074937</v>
       </c>
       <c r="AA10">
-        <v>-12</v>
+        <v>-20</v>
       </c>
       <c r="AB10">
-        <v>-0.6154825404024911</v>
+        <v>-0.8550595941124134</v>
       </c>
       <c r="AC10">
-        <v>-0.7881505201798042</v>
+        <v>-0.5185297392785827</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
       </c>
       <c r="AE10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AH10">
-        <v>-0.6154083595794124</v>
+        <v>-0.8548127494553475</v>
       </c>
       <c r="AI10">
-        <v>0.8760997784776414</v>
+        <v>0.949901971502339</v>
       </c>
       <c r="AJ10">
-        <v>-1.588081467671415</v>
+        <v>-1.925842983037204</v>
       </c>
       <c r="AK10">
-        <v>-2.144495083360733</v>
+        <v>-1.2851741782499</v>
       </c>
       <c r="AL10">
-        <v>-2.788446245796797</v>
+        <v>-3.153265573276221</v>
       </c>
       <c r="AM10">
-        <v>2.57285487600075</v>
+        <v>3.442020031094641</v>
       </c>
       <c r="AN10">
-        <v>2.486618874765054</v>
+        <v>2.802616292963461</v>
       </c>
       <c r="AO10">
-        <v>0.05668533341722131</v>
+        <v>0.04343244169028213</v>
       </c>
       <c r="AP10">
-        <v>1.13777</v>
+        <v>7.6322</v>
       </c>
       <c r="AQ10">
-        <v>1.116260279152847</v>
+        <v>7.526086211634818</v>
       </c>
       <c r="AR10">
-        <v>1.106010509926755</v>
+        <v>7.522822315224786</v>
       </c>
       <c r="AS10">
-        <v>1.13777</v>
+        <v>7.6322</v>
       </c>
       <c r="AT10">
-        <v>1.11734</v>
+        <v>7.4745</v>
       </c>
       <c r="AU10">
-        <v>1.116260279152847</v>
+        <v>7.526086211634818</v>
       </c>
       <c r="AV10">
-        <v>1.152109813898102</v>
+        <v>7.702942525576788</v>
       </c>
       <c r="AW10">
-        <v>-0.01890515732279183</v>
+        <v>-0.0139034339201256</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01890515732279183</v>
+        <v>0.0139034339201256</v>
       </c>
       <c r="AZ10">
-        <v>0.4559535172153993</v>
+        <v>0.41484377438388</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3440464827846007</v>
+        <v>0.38515622561612</v>
       </c>
       <c r="BC10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2966,58 +2966,58 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>500</v>
+        <v>493.9558393562231</v>
       </c>
       <c r="BG10">
-        <v>0.01260343821519455</v>
+        <v>0.009268955946750399</v>
       </c>
       <c r="BH10">
-        <v>39671.71429437453</v>
+        <v>53943.50807927778</v>
       </c>
       <c r="BI10">
-        <v>39671.71429437453</v>
+        <v>53291.42162223771</v>
       </c>
       <c r="BJ10">
-        <v>34867.95599670806</v>
+        <v>6982.445641130698</v>
       </c>
       <c r="BK10">
-        <v>396.7171429437453</v>
+        <v>532.9142162223771</v>
       </c>
       <c r="BL10">
-        <v>0.003967171429437453</v>
+        <v>0.005329142162223771</v>
       </c>
       <c r="BM10">
-        <v>500</v>
+        <v>493.9558393562231</v>
       </c>
       <c r="BN10">
-        <v>0.005</v>
+        <v>0.004939558393562232</v>
       </c>
       <c r="BO10">
-        <v>0.01994012827347854</v>
+        <v>0.1395008072086692</v>
       </c>
       <c r="BP10">
-        <v>0.01845179818392216</v>
+        <v>0.09655266359281418</v>
       </c>
       <c r="BQ10">
-        <v>0.01775576961076967</v>
+        <v>0.0762888347081721</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW10" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3025,7 +3025,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3037,154 +3037,154 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K11">
-        <v>0.9148333723278068</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2.493281471206344</v>
+        <v>0.8442669667037336</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q11">
-        <v>0.9787083430819516</v>
+        <v>0.75</v>
       </c>
       <c r="R11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T11">
-        <v>-0.9005834154530278</v>
+        <v>-0.799413457057678</v>
       </c>
       <c r="U11">
-        <v>0.9424138742155972</v>
+        <v>0.7597236630877668</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X11">
-        <v>0.9997053256502548</v>
+        <v>0.9999504296472475</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <v>0.01423705444324133</v>
       </c>
       <c r="Z11">
-        <v>-143.5032023394873</v>
+        <v>-114.9934161293111</v>
       </c>
       <c r="AA11">
-        <v>-20</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB11">
-        <v>-0.8038901048208</v>
+        <v>-0.4225141149225828</v>
       </c>
       <c r="AC11">
-        <v>-0.5947778571628261</v>
+        <v>-0.9063563442108112</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
       </c>
       <c r="AE11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AH11">
-        <v>-0.8036532190268953</v>
+        <v>-0.2142541145113562</v>
       </c>
       <c r="AI11">
-        <v>0.9342438322494659</v>
+        <v>0.6172400075338201</v>
       </c>
       <c r="AJ11">
-        <v>-1.887874379105325</v>
+        <v>-0.5744807373974551</v>
       </c>
       <c r="AK11">
-        <v>-1.529025323777559</v>
+        <v>-1.265489614079226</v>
       </c>
       <c r="AL11">
-        <v>-3.149732462578228</v>
+        <v>-1.325059533461581</v>
       </c>
       <c r="AM11">
-        <v>3.462882975329206</v>
+        <v>-0.2605068332565275</v>
       </c>
       <c r="AN11">
-        <v>2.781737744488757</v>
+        <v>1.324012771455588</v>
       </c>
       <c r="AO11">
-        <v>0.04546708782908851</v>
+        <v>0.08229525472093058</v>
       </c>
       <c r="AP11">
-        <v>7.6578</v>
+        <v>4156.379999999999</v>
       </c>
       <c r="AQ11">
-        <v>7.505453189223388</v>
+        <v>4039.33707274071</v>
       </c>
       <c r="AR11">
-        <v>7.424652347025853</v>
+        <v>4165.880380238179</v>
       </c>
       <c r="AS11">
-        <v>7.6578</v>
+        <v>4156.379999999999</v>
       </c>
       <c r="AT11">
-        <v>7.5193</v>
+        <v>3882.459999999999</v>
       </c>
       <c r="AU11">
-        <v>7.505453189223388</v>
+        <v>4039.33707274071</v>
       </c>
       <c r="AV11">
-        <v>7.759364540517741</v>
+        <v>4288.0825</v>
       </c>
       <c r="AW11">
-        <v>-0.01989433137149204</v>
+        <v>-0.02815982351452206</v>
       </c>
       <c r="AX11">
-        <v>1.5</v>
+        <v>0.8886917656026969</v>
       </c>
       <c r="AY11">
-        <v>0.01989433137149204</v>
+        <v>0.02815982351452206</v>
       </c>
       <c r="AZ11">
-        <v>0.4389629269302664</v>
+        <v>0.3602178243318779</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3610370730697336</v>
+        <v>0.4397821756681222</v>
       </c>
       <c r="BC11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3193,58 +3193,58 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>489.3541715409758</v>
+        <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.01326288758099469</v>
+        <v>0.03168682844205775</v>
       </c>
       <c r="BH11">
-        <v>37699.18103780692</v>
+        <v>15779.42711793626</v>
       </c>
       <c r="BI11">
-        <v>36896.50300905854</v>
+        <v>11834.57033845219</v>
       </c>
       <c r="BJ11">
-        <v>4818.159655391698</v>
+        <v>2.847326360547447</v>
       </c>
       <c r="BK11">
-        <v>368.9650300905854</v>
+        <v>118.345703384522</v>
       </c>
       <c r="BL11">
-        <v>0.003689650300905854</v>
+        <v>0.00118345703384522</v>
       </c>
       <c r="BM11">
-        <v>489.3541715409759</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN11">
-        <v>0.00489354171540976</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO11">
-        <v>0.1188689254895395</v>
+        <v>583.1344784013556</v>
       </c>
       <c r="BP11">
-        <v>0.1039987737545497</v>
+        <v>174.2098723928191</v>
       </c>
       <c r="BQ11">
-        <v>0.08769261655424945</v>
+        <v>129.242491806396</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.03794913607698633</v>
+        <v>0.05531098604882689</v>
       </c>
       <c r="BT11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BU11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="BW11" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -253,18 +253,18 @@
     <t>GBPCNH</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -352,34 +352,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.01458,naive=0.01196,drift4=0.00835; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=naive; scores=model=2.938,naive=2.411,drift4=4.341; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04442,naive=0.01955,drift4=0.02586; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1505,naive=0.1161,drift4=0.08421; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=model; scores=model=0.05543,naive=0.07071,drift4=0.07489; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.009356,naive=0.01274,drift4=0.0147; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02238,naive=0.017,drift4=0.01538; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02587,naive=0.02063,drift4=0.01792; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1395,naive=0.09655,drift4=0.07629; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=583.1,naive=174.2,drift4=129.2; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.01456,naive=0.01274,drift4=0.008193; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=naive; scores=model=2.947,naive=2.348,drift4=4.238; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04485,naive=0.01898,drift4=0.02591; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1496,naive=0.1238,drift4=0.08089; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.02444,naive=0.01909,drift4=0.01752; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02212,naive=0.01662,drift4=0.01468; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.05242,naive=0.08356,drift4=0.0793; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.009956,naive=0.01464,drift4=0.0153; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.128,naive=0.1087,drift4=0.07824; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=571.7,naive=149.7,drift4=98.14; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -982,7 +982,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1006,19 +1006,19 @@
         <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2.932167664138002</v>
+        <v>3.293394736705306</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="s">
         <v>94</v>
@@ -1036,10 +1036,10 @@
         <v>101</v>
       </c>
       <c r="T2">
-        <v>0.9218538591375706</v>
+        <v>0.9106606642624933</v>
       </c>
       <c r="U2">
-        <v>0.9647819294336638</v>
+        <v>0.9597737270081802</v>
       </c>
       <c r="V2" t="s">
         <v>92</v>
@@ -1048,22 +1048,22 @@
         <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9997907712870285</v>
+        <v>0.9999057123602327</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>32.46800368571632</v>
+        <v>34.78356273707708</v>
       </c>
       <c r="AA2">
         <v>1.000000000000001</v>
       </c>
       <c r="AB2">
-        <v>0.8436913644369721</v>
+        <v>0.8213129041355656</v>
       </c>
       <c r="AC2">
-        <v>0.5368285402011337</v>
+        <v>0.5704779693383464</v>
       </c>
       <c r="AD2" t="s">
         <v>92</v>
@@ -1078,67 +1078,67 @@
         <v>109</v>
       </c>
       <c r="AH2">
-        <v>0.8435148399786458</v>
+        <v>0.8212354644803243</v>
       </c>
       <c r="AI2">
-        <v>0.9462415230111136</v>
+        <v>0.9395174548097359</v>
       </c>
       <c r="AJ2">
-        <v>2.192111888492398</v>
+        <v>2.464555010315478</v>
       </c>
       <c r="AK2">
-        <v>1.389207911484684</v>
+        <v>1.705231389955091</v>
       </c>
       <c r="AL2">
-        <v>3.807126716510738</v>
+        <v>4.2639503565686</v>
       </c>
       <c r="AM2">
-        <v>-3.104391978020509</v>
+        <v>-3.495735030421925</v>
       </c>
       <c r="AN2">
-        <v>3.489051630129082</v>
+        <v>3.904446306804026</v>
       </c>
       <c r="AO2">
-        <v>0.04528437513625278</v>
+        <v>0.04562277171343429</v>
       </c>
       <c r="AP2">
-        <v>0.8329800000000001</v>
+        <v>0.83474</v>
       </c>
       <c r="AQ2">
-        <v>0.8468376486247797</v>
+        <v>0.8530467649169398</v>
       </c>
       <c r="AR2">
-        <v>0.8450935075735262</v>
+        <v>0.8559002336739718</v>
       </c>
       <c r="AS2">
-        <v>0.8329800000000001</v>
+        <v>0.83474</v>
       </c>
       <c r="AT2">
-        <v>0.8559450000000002</v>
+        <v>0.8594650000000001</v>
       </c>
       <c r="AU2">
-        <v>0.8468376486247797</v>
+        <v>0.8530467649169398</v>
       </c>
       <c r="AV2">
-        <v>0.8237415675834803</v>
+        <v>0.8225354900553735</v>
       </c>
       <c r="AW2">
-        <v>0.01663623211215116</v>
+        <v>0.021931098206555</v>
       </c>
       <c r="AX2">
         <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.01663623211215116</v>
+        <v>0.021931098206555</v>
       </c>
       <c r="AZ2">
-        <v>0.4160120283738065</v>
+        <v>0.4132767615940288</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3839879716261935</v>
+        <v>0.3867232384059712</v>
       </c>
       <c r="BC2" t="s">
         <v>112</v>
@@ -1153,22 +1153,22 @@
         <v>500</v>
       </c>
       <c r="BG2">
-        <v>0.01109082140810077</v>
+        <v>0.01462073213770333</v>
       </c>
       <c r="BH2">
-        <v>45082.32362616518</v>
+        <v>34198.01384026596</v>
       </c>
       <c r="BI2">
-        <v>45082.32362616518</v>
+        <v>34198.01384026596</v>
       </c>
       <c r="BJ2">
-        <v>54121.7359674484</v>
+        <v>40968.46184472526</v>
       </c>
       <c r="BK2">
-        <v>450.8232362616517</v>
+        <v>341.9801384026596</v>
       </c>
       <c r="BL2">
-        <v>0.004508232362616517</v>
+        <v>0.003419801384026596</v>
       </c>
       <c r="BM2">
         <v>500</v>
@@ -1177,19 +1177,19 @@
         <v>0.005</v>
       </c>
       <c r="BO2">
-        <v>0.01458490297650403</v>
+        <v>0.01456074222371069</v>
       </c>
       <c r="BP2">
-        <v>0.01196134736379736</v>
+        <v>0.01273817779929987</v>
       </c>
       <c r="BQ2">
-        <v>0.008350487428316263</v>
+        <v>0.008192592366240389</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT2" t="s">
         <v>122</v>
@@ -1201,7 +1201,7 @@
         <v>123</v>
       </c>
       <c r="BW2" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1209,7 +1209,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1233,19 +1233,19 @@
         <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.6027559670788827</v>
+        <v>0.6064542638378875</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1263,10 +1263,10 @@
         <v>102</v>
       </c>
       <c r="T3">
-        <v>-0.7533042661490058</v>
+        <v>-0.8683317575861065</v>
       </c>
       <c r="U3">
-        <v>0.7385549057734455</v>
+        <v>0.7877528177119205</v>
       </c>
       <c r="V3" t="s">
         <v>93</v>
@@ -1275,22 +1275,22 @@
         <v>94</v>
       </c>
       <c r="X3">
-        <v>0.9982719440255712</v>
+        <v>0.9880141071926903</v>
       </c>
       <c r="Y3">
-        <v>0.1322712175335533</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>111.7585844870444</v>
+        <v>127.6849818985768</v>
       </c>
       <c r="AA3">
-        <v>9</v>
+        <v>47.99999999999999</v>
       </c>
       <c r="AB3">
-        <v>-0.370696594622404</v>
+        <v>-0.6113196273735488</v>
       </c>
       <c r="AC3">
-        <v>0.9287540227290286</v>
+        <v>0.791383796389505</v>
       </c>
       <c r="AD3" t="s">
         <v>93</v>
@@ -1305,67 +1305,67 @@
         <v>110</v>
       </c>
       <c r="AH3">
-        <v>-0.2095018845882451</v>
+        <v>-0.3019962079244225</v>
       </c>
       <c r="AI3">
-        <v>0.6274303558378602</v>
+        <v>0.6722534140912019</v>
       </c>
       <c r="AJ3">
-        <v>-0.5068419590390092</v>
+        <v>-0.4863212653666539</v>
       </c>
       <c r="AK3">
-        <v>1.371187588717483</v>
+        <v>0.8876675396272942</v>
       </c>
       <c r="AL3">
-        <v>-0.5107035571324423</v>
+        <v>-0.6207243804159661</v>
       </c>
       <c r="AM3">
-        <v>0.6156979308825091</v>
+        <v>0.4121811549329377</v>
       </c>
       <c r="AN3">
-        <v>0.5221834591978205</v>
+        <v>0.6299719581735045</v>
       </c>
       <c r="AO3">
-        <v>0.06418697643014314</v>
+        <v>0.0463160775886956</v>
       </c>
       <c r="AP3">
-        <v>157.035</v>
+        <v>157.031</v>
       </c>
       <c r="AQ3">
-        <v>158.1763837352517</v>
+        <v>157.9508558258993</v>
       </c>
       <c r="AR3">
-        <v>158.7035878012672</v>
+        <v>158.2608615494896</v>
       </c>
       <c r="AS3">
-        <v>157.035</v>
+        <v>157.031</v>
       </c>
       <c r="AT3">
-        <v>158.056</v>
+        <v>158.048</v>
       </c>
       <c r="AU3">
-        <v>158.1763837352517</v>
+        <v>157.9508558258993</v>
       </c>
       <c r="AV3">
-        <v>155.536875</v>
+        <v>155.532875</v>
       </c>
       <c r="AW3">
-        <v>0.007268339766623595</v>
+        <v>0.005857797669882409</v>
       </c>
       <c r="AX3">
-        <v>0.7618748337099535</v>
+        <v>0.6140047231701592</v>
       </c>
       <c r="AY3">
-        <v>0.007268339766623595</v>
+        <v>0.005857797669882409</v>
       </c>
       <c r="AZ3">
-        <v>0.5012196564181495</v>
+        <v>0.4991781096869681</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.2987803435818505</v>
+        <v>0.3008218903130319</v>
       </c>
       <c r="BC3" t="s">
         <v>113</v>
@@ -1380,22 +1380,22 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009540070684879269</v>
+        <v>0.009540313696021905</v>
       </c>
       <c r="BH3">
-        <v>52410.51314142622</v>
+        <v>52409.17813934029</v>
       </c>
       <c r="BI3">
-        <v>52410.51314142622</v>
+        <v>52409.17813934029</v>
       </c>
       <c r="BJ3">
         <v>333.7505214851863</v>
       </c>
       <c r="BK3">
-        <v>524.1051314142622</v>
+        <v>524.0917813934029</v>
       </c>
       <c r="BL3">
-        <v>0.005241051314142623</v>
+        <v>0.005240917813934029</v>
       </c>
       <c r="BM3">
         <v>500</v>
@@ -1404,19 +1404,19 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>2.937820126934294</v>
+        <v>2.947401273681342</v>
       </c>
       <c r="BP3">
-        <v>2.41064466159896</v>
+        <v>2.348390588129686</v>
       </c>
       <c r="BQ3">
-        <v>4.340942912653166</v>
+        <v>4.238277691428006</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT3" t="s">
         <v>122</v>
@@ -1428,7 +1428,7 @@
         <v>123</v>
       </c>
       <c r="BW3" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1436,7 +1436,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1460,19 +1460,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.59972298782819</v>
+        <v>1.601962707376349</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1490,10 +1490,10 @@
         <v>102</v>
       </c>
       <c r="T4">
-        <v>-0.8233824537727303</v>
+        <v>-0.8875092570303886</v>
       </c>
       <c r="U4">
-        <v>0.7704458387086559</v>
+        <v>0.799294106389153</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1502,22 +1502,22 @@
         <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9996949380437088</v>
+        <v>0.9996597629019126</v>
       </c>
       <c r="Y4">
-        <v>0.2643328411100709</v>
+        <v>0.01427563709587434</v>
       </c>
       <c r="Z4">
-        <v>126.5017684982347</v>
+        <v>132.5391637230116</v>
       </c>
       <c r="AA4">
-        <v>-3.999999999999993</v>
+        <v>7.999999999999998</v>
       </c>
       <c r="AB4">
-        <v>-0.594847598407908</v>
+        <v>-0.6760940052895485</v>
       </c>
       <c r="AC4">
-        <v>0.8038385003645597</v>
+        <v>0.7368153744402568</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
@@ -1532,67 +1532,67 @@
         <v>110</v>
       </c>
       <c r="AH4">
-        <v>-0.3759279607465731</v>
+        <v>-0.342756180916133</v>
       </c>
       <c r="AI4">
-        <v>0.7267869082306386</v>
+        <v>0.7010553573831118</v>
       </c>
       <c r="AJ4">
-        <v>-1.215020172870769</v>
+        <v>-1.191355127502856</v>
       </c>
       <c r="AK4">
-        <v>1.617118747976555</v>
+        <v>1.340860156058459</v>
       </c>
       <c r="AL4">
-        <v>-1.990772269975929</v>
+        <v>-2.101978656319525</v>
       </c>
       <c r="AM4">
-        <v>1.494423962202693</v>
+        <v>1.119580104648711</v>
       </c>
       <c r="AN4">
-        <v>1.904882111597325</v>
+        <v>2.035641485288978</v>
       </c>
       <c r="AO4">
-        <v>0.0295144521936399</v>
+        <v>0.03005925759064645</v>
       </c>
       <c r="AP4">
-        <v>6.70401</v>
+        <v>6.707165</v>
       </c>
       <c r="AQ4">
-        <v>6.723505385672373</v>
+        <v>6.728333176464895</v>
       </c>
       <c r="AR4">
-        <v>6.752111735273507</v>
+        <v>6.756412033806345</v>
       </c>
       <c r="AS4">
-        <v>6.70401</v>
+        <v>6.707165</v>
       </c>
       <c r="AT4">
-        <v>6.700735</v>
+        <v>6.707044999999999</v>
       </c>
       <c r="AU4">
-        <v>6.723505385672373</v>
+        <v>6.728333176464895</v>
       </c>
       <c r="AV4">
-        <v>6.680503750000001</v>
+        <v>6.68365875</v>
       </c>
       <c r="AW4">
-        <v>0.002908018584753482</v>
+        <v>0.003156054229304846</v>
       </c>
       <c r="AX4">
-        <v>0.8293703024673653</v>
+        <v>0.9005339628777785</v>
       </c>
       <c r="AY4">
-        <v>0.002908018584753482</v>
+        <v>0.003156054229304846</v>
       </c>
       <c r="AZ4">
-        <v>0.4304552547888046</v>
+        <v>0.4307363603879871</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3695447452111953</v>
+        <v>0.3692636396120129</v>
       </c>
       <c r="BC4" t="s">
         <v>114</v>
@@ -1607,22 +1607,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.003506296977480585</v>
+        <v>0.003504647641738293</v>
       </c>
       <c r="BH4">
-        <v>142600.5849508133</v>
+        <v>142667.6947620337</v>
       </c>
       <c r="BI4">
-        <v>142600.5849508133</v>
+        <v>142667.6947620337</v>
       </c>
       <c r="BJ4">
-        <v>21270.9385801652</v>
+        <v>21270.93858016519</v>
       </c>
       <c r="BK4">
-        <v>1426.005849508133</v>
+        <v>1426.676947620337</v>
       </c>
       <c r="BL4">
-        <v>0.01426005849508133</v>
+        <v>0.01426676947620337</v>
       </c>
       <c r="BM4">
         <v>499.9999999999999</v>
@@ -1631,19 +1631,19 @@
         <v>0.004999999999999999</v>
       </c>
       <c r="BO4">
-        <v>0.04441568089305444</v>
+        <v>0.04484503479508233</v>
       </c>
       <c r="BP4">
-        <v>0.01954760957488873</v>
+        <v>0.01897532214029101</v>
       </c>
       <c r="BQ4">
-        <v>0.02585904693129224</v>
+        <v>0.02590707952162591</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT4" t="s">
         <v>122</v>
@@ -1655,7 +1655,7 @@
         <v>123</v>
       </c>
       <c r="BW4" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1663,7 +1663,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1687,19 +1687,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1.650686963337997</v>
+        <v>1.686218320861796</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O5" t="s">
         <v>94</v>
@@ -1717,10 +1717,10 @@
         <v>103</v>
       </c>
       <c r="T5">
-        <v>-0.9156846880096801</v>
+        <v>-0.9310160695900964</v>
       </c>
       <c r="U5">
-        <v>0.9620062704350962</v>
+        <v>0.9689184193132682</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1729,22 +1729,22 @@
         <v>94</v>
       </c>
       <c r="X5">
-        <v>0.9997926433229609</v>
+        <v>0.9998447519908988</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-146.2378611632244</v>
+        <v>-149.5443119926976</v>
       </c>
       <c r="AA5">
-        <v>-13.99999999999999</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB5">
-        <v>-0.8313518890504025</v>
+        <v>-0.8620214278994317</v>
       </c>
       <c r="AC5">
-        <v>-0.5557463779210147</v>
+        <v>-0.5068718357161155</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1759,67 +1759,67 @@
         <v>111</v>
       </c>
       <c r="AH5">
-        <v>-0.8311795026852388</v>
+        <v>-0.8618876007889478</v>
       </c>
       <c r="AI5">
-        <v>0.9429933139314797</v>
+        <v>0.9524285422341819</v>
       </c>
       <c r="AJ5">
-        <v>-1.276388143369669</v>
+        <v>-1.307642339867632</v>
       </c>
       <c r="AK5">
-        <v>-0.9110023757400542</v>
+        <v>-0.8193903906115763</v>
       </c>
       <c r="AL5">
-        <v>-1.963456515348875</v>
+        <v>-1.985887170759058</v>
       </c>
       <c r="AM5">
-        <v>2.544165157925495</v>
+        <v>2.55210889701048</v>
       </c>
       <c r="AN5">
-        <v>1.708720613577435</v>
+        <v>1.738626987625601</v>
       </c>
       <c r="AO5">
-        <v>0.04226451964451648</v>
+        <v>0.04082366221641366</v>
       </c>
       <c r="AP5">
-        <v>8.89554</v>
+        <v>8.87401</v>
       </c>
       <c r="AQ5">
-        <v>8.829778631827244</v>
+        <v>8.8001122694613</v>
       </c>
       <c r="AR5">
-        <v>8.89872953157983</v>
+        <v>8.879740452396382</v>
       </c>
       <c r="AS5">
-        <v>8.89554</v>
+        <v>8.87401</v>
       </c>
       <c r="AT5">
-        <v>8.72133</v>
+        <v>8.678269999999999</v>
       </c>
       <c r="AU5">
-        <v>8.829778631827244</v>
+        <v>8.8001122694613</v>
       </c>
       <c r="AV5">
-        <v>8.965752500000001</v>
+        <v>8.944222499999999</v>
       </c>
       <c r="AW5">
-        <v>-0.007392622389731985</v>
+        <v>-0.00832743376880354</v>
       </c>
       <c r="AX5">
-        <v>0.936604852024313</v>
+        <v>1.052486815577012</v>
       </c>
       <c r="AY5">
-        <v>0.007392622389731985</v>
+        <v>0.00832743376880354</v>
       </c>
       <c r="AZ5">
-        <v>0.4149201025038798</v>
+        <v>0.41045358501803</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3850798974961202</v>
+        <v>0.38954641498197</v>
       </c>
       <c r="BC5" t="s">
         <v>115</v>
@@ -1834,22 +1834,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.007893000312516085</v>
+        <v>0.007912150200416648</v>
       </c>
       <c r="BH5">
-        <v>63347.26722449766</v>
+        <v>63193.94694676933</v>
       </c>
       <c r="BI5">
-        <v>63347.26722449766</v>
+        <v>63193.94694676933</v>
       </c>
       <c r="BJ5">
         <v>7121.239095602702</v>
       </c>
       <c r="BK5">
-        <v>633.4726722449766</v>
+        <v>631.9394694676934</v>
       </c>
       <c r="BL5">
-        <v>0.006334726722449766</v>
+        <v>0.006319394694676934</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1858,19 +1858,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.1505374517041939</v>
+        <v>0.149646943954001</v>
       </c>
       <c r="BP5">
-        <v>0.1160585727127575</v>
+        <v>0.1238062648997809</v>
       </c>
       <c r="BQ5">
-        <v>0.08420706933258511</v>
+        <v>0.08088815701195276</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT5" t="s">
         <v>122</v>
@@ -1882,7 +1882,7 @@
         <v>123</v>
       </c>
       <c r="BW5" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1890,7 +1890,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1914,19 +1914,19 @@
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K6">
-        <v>0.1139093758378123</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0.8812195371627741</v>
+        <v>2.191816852613451</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O6" t="s">
         <v>94</v>
@@ -1935,7 +1935,7 @@
         <v>96</v>
       </c>
       <c r="Q6">
-        <v>0.7784773439594531</v>
+        <v>1</v>
       </c>
       <c r="R6" t="s">
         <v>100</v>
@@ -1944,10 +1944,10 @@
         <v>103</v>
       </c>
       <c r="T6">
-        <v>-0.7168960933814398</v>
+        <v>-0.9047095565525618</v>
       </c>
       <c r="U6">
-        <v>0.7396580646989981</v>
+        <v>0.9569307161286699</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1956,22 +1956,22 @@
         <v>94</v>
       </c>
       <c r="X6">
-        <v>0.9998736652067134</v>
+        <v>0.9992456627200683</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-121.0171635773847</v>
+        <v>-144.032197867296</v>
       </c>
       <c r="AA6">
-        <v>-12</v>
+        <v>-21.99999999999999</v>
       </c>
       <c r="AB6">
-        <v>-0.5152948256368708</v>
+        <v>-0.8093471777076577</v>
       </c>
       <c r="AC6">
-        <v>-0.8570129769565143</v>
+        <v>-0.5873305252893375</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -1986,67 +1986,67 @@
         <v>111</v>
       </c>
       <c r="AH6">
-        <v>-0.5152297259715923</v>
+        <v>-0.8087366569591053</v>
       </c>
       <c r="AI6">
-        <v>0.844495057941078</v>
+        <v>0.9366725589471102</v>
       </c>
       <c r="AJ6">
-        <v>-0.6365195457344136</v>
+        <v>-1.756786577883378</v>
       </c>
       <c r="AK6">
-        <v>-1.120271831010521</v>
+        <v>-1.426204797739647</v>
       </c>
       <c r="AL6">
-        <v>-1.246666538707811</v>
+        <v>-2.342231527080917</v>
       </c>
       <c r="AM6">
-        <v>0.8468396378540953</v>
+        <v>4.49810636208657</v>
       </c>
       <c r="AN6">
-        <v>1.13024247798072</v>
+        <v>1.904298802940368</v>
       </c>
       <c r="AO6">
-        <v>0.06699448381555198</v>
+        <v>0.03911717544807258</v>
       </c>
       <c r="AP6">
-        <v>4.70822</v>
+        <v>1.328665</v>
       </c>
       <c r="AQ6">
-        <v>4.670264561368022</v>
+        <v>1.315672296868062</v>
       </c>
       <c r="AR6">
-        <v>4.708030255836245</v>
+        <v>1.318097453520323</v>
       </c>
       <c r="AS6">
-        <v>4.70822</v>
+        <v>1.328665</v>
       </c>
       <c r="AT6">
-        <v>4.58541</v>
+        <v>1.30556</v>
       </c>
       <c r="AU6">
-        <v>4.670264561368022</v>
+        <v>1.315672296868062</v>
       </c>
       <c r="AV6">
-        <v>4.750865</v>
+        <v>1.3418275</v>
       </c>
       <c r="AW6">
-        <v>-0.008061526146182217</v>
+        <v>-0.009778765250787578</v>
       </c>
       <c r="AX6">
-        <v>0.8900325625976784</v>
+        <v>0.9870999530437008</v>
       </c>
       <c r="AY6">
-        <v>0.008061526146182217</v>
+        <v>0.009778765250787578</v>
       </c>
       <c r="AZ6">
-        <v>0.4917014807776953</v>
+        <v>0.4379914038493627</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3082985192223047</v>
+        <v>0.3620085961506372</v>
       </c>
       <c r="BC6" t="s">
         <v>116</v>
@@ -2058,46 +2058,46 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>389.2386719797266</v>
+        <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.009057563155502513</v>
+        <v>0.009906560344405825</v>
       </c>
       <c r="BH6">
-        <v>55202.48563723761</v>
+        <v>50471.60493827174</v>
       </c>
       <c r="BI6">
-        <v>42973.88439883659</v>
+        <v>50471.60493827174</v>
       </c>
       <c r="BJ6">
-        <v>9127.416390660715</v>
+        <v>37986.70465337142</v>
       </c>
       <c r="BK6">
-        <v>429.7388439883659</v>
+        <v>504.7160493827174</v>
       </c>
       <c r="BL6">
-        <v>0.004297388439883659</v>
+        <v>0.005047160493827174</v>
       </c>
       <c r="BM6">
-        <v>389.2386719797266</v>
+        <v>500</v>
       </c>
       <c r="BN6">
-        <v>0.003892386719797266</v>
+        <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.05543408485399783</v>
+        <v>0.024435639524581</v>
       </c>
       <c r="BP6">
-        <v>0.07071449030372613</v>
+        <v>0.01908638583115809</v>
       </c>
       <c r="BQ6">
-        <v>0.0748891245846756</v>
+        <v>0.01752157685838423</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT6" t="s">
         <v>122</v>
@@ -2109,7 +2109,7 @@
         <v>123</v>
       </c>
       <c r="BW6" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2117,7 +2117,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2141,19 +2141,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>1.231225676064555</v>
+        <v>2.448355559158069</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O7" t="s">
         <v>94</v>
@@ -2162,7 +2162,7 @@
         <v>96</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R7" t="s">
         <v>100</v>
@@ -2171,10 +2171,10 @@
         <v>103</v>
       </c>
       <c r="T7">
-        <v>-0.595924863504193</v>
+        <v>-0.8679424902676787</v>
       </c>
       <c r="U7">
-        <v>0.6681437470584861</v>
+        <v>0.9405322076889344</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2183,22 +2183,22 @@
         <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9999102339263967</v>
+        <v>0.999832348273916</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-108.8535103508429</v>
+        <v>-137.3801750828664</v>
       </c>
       <c r="AA7">
-        <v>-6.999999999999997</v>
+        <v>-15</v>
       </c>
       <c r="AB7">
-        <v>-0.3231496604105653</v>
+        <v>-0.7358628371535323</v>
       </c>
       <c r="AC7">
-        <v>-0.9463478731293986</v>
+        <v>-0.6771306261692451</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
@@ -2213,67 +2213,67 @@
         <v>111</v>
       </c>
       <c r="AH7">
-        <v>-0.323120652534364</v>
+        <v>-0.7357394684787224</v>
       </c>
       <c r="AI7">
-        <v>0.7834993593713424</v>
+        <v>0.9135148954568622</v>
       </c>
       <c r="AJ7">
-        <v>-0.8666558135598412</v>
+        <v>-1.872197956013963</v>
       </c>
       <c r="AK7">
-        <v>-2.656708430055078</v>
+        <v>-1.841178257824594</v>
       </c>
       <c r="AL7">
-        <v>-1.837967646475184</v>
+        <v>-2.999864441677517</v>
       </c>
       <c r="AM7">
-        <v>0.9485436712745416</v>
+        <v>3.456865937544864</v>
       </c>
       <c r="AN7">
-        <v>1.667661908120894</v>
+        <v>2.638502559097331</v>
       </c>
       <c r="AO7">
-        <v>0.08942747084043955</v>
+        <v>0.04790185056712054</v>
       </c>
       <c r="AP7">
-        <v>0.700515</v>
+        <v>1.13531</v>
       </c>
       <c r="AQ7">
-        <v>0.6939588303130619</v>
+        <v>1.124110358715052</v>
       </c>
       <c r="AR7">
-        <v>0.6990084940198391</v>
+        <v>1.131594211210355</v>
       </c>
       <c r="AS7">
-        <v>0.700515</v>
+        <v>1.13531</v>
       </c>
       <c r="AT7">
-        <v>0.680885</v>
+        <v>1.109275</v>
       </c>
       <c r="AU7">
-        <v>0.6939588303130619</v>
+        <v>1.124110358715052</v>
       </c>
       <c r="AV7">
-        <v>0.70772375</v>
+        <v>1.14567</v>
       </c>
       <c r="AW7">
-        <v>-0.009359071093321432</v>
+        <v>-0.009864831002058951</v>
       </c>
       <c r="AX7">
-        <v>0.9094738598145484</v>
+        <v>1.081046456076014</v>
       </c>
       <c r="AY7">
-        <v>0.009359071093321432</v>
+        <v>0.009864831002058951</v>
       </c>
       <c r="AZ7">
-        <v>0.504749818277214</v>
+        <v>0.4313933240877914</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.295250181722786</v>
+        <v>0.3686066759122087</v>
       </c>
       <c r="BC7" t="s">
         <v>117</v>
@@ -2285,46 +2285,46 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG7">
-        <v>0.01029064331242005</v>
+        <v>0.009125260941945403</v>
       </c>
       <c r="BH7">
-        <v>48587.82729322051</v>
+        <v>54792.95366795348</v>
       </c>
       <c r="BI7">
-        <v>36440.87046991539</v>
+        <v>54792.95366795348</v>
       </c>
       <c r="BJ7">
-        <v>52020.11444425229</v>
+        <v>48262.54826254809</v>
       </c>
       <c r="BK7">
-        <v>364.4087046991539</v>
+        <v>547.9295366795347</v>
       </c>
       <c r="BL7">
-        <v>0.003644087046991539</v>
+        <v>0.005479295366795348</v>
       </c>
       <c r="BM7">
-        <v>375.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN7">
-        <v>0.003750000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO7">
-        <v>0.009356290313371035</v>
+        <v>0.02211827353786557</v>
       </c>
       <c r="BP7">
-        <v>0.01274452855590083</v>
+        <v>0.01662269000308126</v>
       </c>
       <c r="BQ7">
-        <v>0.01470120815420496</v>
+        <v>0.01468100294008004</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT7" t="s">
         <v>122</v>
@@ -2336,7 +2336,7 @@
         <v>123</v>
       </c>
       <c r="BW7" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2344,7 +2344,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2368,19 +2368,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.3875237439433573</v>
       </c>
       <c r="L8">
-        <v>2.319262127002522</v>
+        <v>1.023507931409482</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O8" t="s">
         <v>94</v>
@@ -2389,7 +2389,7 @@
         <v>96</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.8468809359858394</v>
       </c>
       <c r="R8" t="s">
         <v>100</v>
@@ -2398,10 +2398,10 @@
         <v>103</v>
       </c>
       <c r="T8">
-        <v>-0.8233672241928232</v>
+        <v>-0.734687963719556</v>
       </c>
       <c r="U8">
-        <v>0.9204933629019073</v>
+        <v>0.7887195394723627</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2410,22 +2410,22 @@
         <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9999124480605475</v>
+        <v>0.9999255768282354</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-130.2946815533073</v>
+        <v>-121.4780406646686</v>
       </c>
       <c r="AA8">
-        <v>-10</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB8">
-        <v>-0.6467189824894843</v>
+        <v>-0.5221717411748173</v>
       </c>
       <c r="AC8">
-        <v>-0.7627283642868974</v>
+        <v>-0.8528403559391755</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
@@ -2440,67 +2440,67 @@
         <v>111</v>
       </c>
       <c r="AH8">
-        <v>-0.6466623609882867</v>
+        <v>-0.5221328794976332</v>
       </c>
       <c r="AI8">
-        <v>0.8861291279153403</v>
+        <v>0.8471886320641755</v>
       </c>
       <c r="AJ8">
-        <v>-1.748288201739388</v>
+        <v>-0.7440078990797057</v>
       </c>
       <c r="AK8">
-        <v>-2.152294668115119</v>
+        <v>-1.252768306779863</v>
       </c>
       <c r="AL8">
-        <v>-2.951780375378513</v>
+        <v>-1.422315781665723</v>
       </c>
       <c r="AM8">
-        <v>2.943748028975494</v>
+        <v>0.9086215531623327</v>
       </c>
       <c r="AN8">
-        <v>2.626531266664112</v>
+        <v>1.303750748746877</v>
       </c>
       <c r="AO8">
-        <v>0.05237282435131042</v>
+        <v>0.0629122811876793</v>
       </c>
       <c r="AP8">
-        <v>1.135555</v>
+        <v>4.6842</v>
       </c>
       <c r="AQ8">
-        <v>1.124658252520412</v>
+        <v>4.636802163338683</v>
       </c>
       <c r="AR8">
-        <v>1.132172341597065</v>
+        <v>4.677205999868868</v>
       </c>
       <c r="AS8">
-        <v>1.135555</v>
+        <v>4.6842</v>
       </c>
       <c r="AT8">
-        <v>1.109765</v>
+        <v>4.537369999999999</v>
       </c>
       <c r="AU8">
-        <v>1.124658252520412</v>
+        <v>4.636802163338683</v>
       </c>
       <c r="AV8">
-        <v>1.145915</v>
+        <v>4.726845</v>
       </c>
       <c r="AW8">
-        <v>-0.009595966271636745</v>
+        <v>-0.01011866202581366</v>
       </c>
       <c r="AX8">
-        <v>1.051809602276875</v>
+        <v>1.111451205564927</v>
       </c>
       <c r="AY8">
-        <v>0.009595966271636745</v>
+        <v>0.01011866202581366</v>
       </c>
       <c r="AZ8">
-        <v>0.4344670909862309</v>
+        <v>0.5010595512199196</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3655329090137691</v>
+        <v>0.2989404487800804</v>
       </c>
       <c r="BC8" t="s">
         <v>118</v>
@@ -2512,46 +2512,46 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>500</v>
+        <v>423.4404679929197</v>
       </c>
       <c r="BG8">
-        <v>0.009123292134683072</v>
+        <v>0.009104009222492646</v>
       </c>
       <c r="BH8">
-        <v>54804.77799227781</v>
+        <v>54920.85824832917</v>
       </c>
       <c r="BI8">
-        <v>54804.77799227781</v>
+        <v>46511.42783849061</v>
       </c>
       <c r="BJ8">
-        <v>48262.54826254809</v>
+        <v>9929.428256370484</v>
       </c>
       <c r="BK8">
-        <v>548.0477799227781</v>
+        <v>465.1142783849061</v>
       </c>
       <c r="BL8">
-        <v>0.005480477799227781</v>
+        <v>0.004651142783849061</v>
       </c>
       <c r="BM8">
-        <v>500</v>
+        <v>423.4404679929197</v>
       </c>
       <c r="BN8">
-        <v>0.005</v>
+        <v>0.004234404679929197</v>
       </c>
       <c r="BO8">
-        <v>0.02237877538157037</v>
+        <v>0.05242005318528788</v>
       </c>
       <c r="BP8">
-        <v>0.01699771817582816</v>
+        <v>0.08356103671521799</v>
       </c>
       <c r="BQ8">
-        <v>0.01537929770192019</v>
+        <v>0.07930316151635283</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT8" t="s">
         <v>122</v>
@@ -2563,7 +2563,7 @@
         <v>123</v>
       </c>
       <c r="BW8" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2571,7 +2571,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2595,19 +2595,19 @@
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2.466913398925232</v>
+        <v>1.580657490691484</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O9" t="s">
         <v>94</v>
@@ -2616,7 +2616,7 @@
         <v>96</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R9" t="s">
         <v>100</v>
@@ -2625,10 +2625,10 @@
         <v>103</v>
       </c>
       <c r="T9">
-        <v>-0.8287815975951317</v>
+        <v>-0.6458738715279175</v>
       </c>
       <c r="U9">
-        <v>0.9229361870932464</v>
+        <v>0.6906240438363735</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
@@ -2637,22 +2637,22 @@
         <v>94</v>
       </c>
       <c r="X9">
-        <v>0.9999378727017488</v>
+        <v>0.9999232065952424</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-131.1134829237438</v>
+        <v>-114.0052517395412</v>
       </c>
       <c r="AA9">
-        <v>-6.999999999999997</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB9">
-        <v>-0.657552557192601</v>
+        <v>-0.4068203770775038</v>
       </c>
       <c r="AC9">
-        <v>-0.7534086769672029</v>
+        <v>-0.9135081722647683</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
@@ -2667,67 +2667,67 @@
         <v>111</v>
       </c>
       <c r="AH9">
-        <v>-0.6575117052287645</v>
+        <v>-0.4067891359556232</v>
       </c>
       <c r="AI9">
-        <v>0.8900777640785847</v>
+        <v>0.8105194080324716</v>
       </c>
       <c r="AJ9">
-        <v>-1.911796185433251</v>
+        <v>-1.135727345137667</v>
       </c>
       <c r="AK9">
-        <v>-2.258467911996093</v>
+        <v>-2.664484724449971</v>
       </c>
       <c r="AL9">
-        <v>-2.913296091257616</v>
+        <v>-2.252117691376024</v>
       </c>
       <c r="AM9">
-        <v>3.95866498724083</v>
+        <v>1.300479567144253</v>
       </c>
       <c r="AN9">
-        <v>2.499134567504587</v>
+        <v>2.054119478603557</v>
       </c>
       <c r="AO9">
-        <v>0.04777505683205054</v>
+        <v>0.07666551599409556</v>
       </c>
       <c r="AP9">
-        <v>1.32477</v>
+        <v>0.696725</v>
       </c>
       <c r="AQ9">
-        <v>1.311168234181072</v>
+        <v>0.6879503817910337</v>
       </c>
       <c r="AR9">
-        <v>1.316181811869156</v>
+        <v>0.6931225707547108</v>
       </c>
       <c r="AS9">
-        <v>1.32477</v>
+        <v>0.696725</v>
       </c>
       <c r="AT9">
-        <v>1.29777</v>
+        <v>0.673305</v>
       </c>
       <c r="AU9">
-        <v>1.311168234181072</v>
+        <v>0.6879503817910337</v>
       </c>
       <c r="AV9">
-        <v>1.3379325</v>
+        <v>0.70393375</v>
       </c>
       <c r="AW9">
-        <v>-0.01026726587930586</v>
+        <v>-0.0125940912253275</v>
       </c>
       <c r="AX9">
-        <v>1.033372521855883</v>
+        <v>1.217217715826792</v>
       </c>
       <c r="AY9">
-        <v>0.01026726587930586</v>
+        <v>0.0125940912253275</v>
       </c>
       <c r="AZ9">
-        <v>0.434407772462125</v>
+        <v>0.5026540293121369</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3655922275378751</v>
+        <v>0.2973459706878631</v>
       </c>
       <c r="BC9" t="s">
         <v>119</v>
@@ -2739,46 +2739,46 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG9">
-        <v>0.009935686949432705</v>
+        <v>0.01034662169435564</v>
       </c>
       <c r="BH9">
-        <v>50323.64672364686</v>
+        <v>48324.95231489556</v>
       </c>
       <c r="BI9">
-        <v>50323.64672364686</v>
+        <v>36243.71423617167</v>
       </c>
       <c r="BJ9">
-        <v>37986.70465337142</v>
+        <v>52020.11444425228</v>
       </c>
       <c r="BK9">
-        <v>503.2364672364686</v>
+        <v>362.4371423617167</v>
       </c>
       <c r="BL9">
-        <v>0.005032364672364687</v>
+        <v>0.003624371423617167</v>
       </c>
       <c r="BM9">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BN9">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="BO9">
-        <v>0.02587249420031677</v>
+        <v>0.009956424853519674</v>
       </c>
       <c r="BP9">
-        <v>0.02062747324503312</v>
+        <v>0.0146373971021013</v>
       </c>
       <c r="BQ9">
-        <v>0.01791816760719848</v>
+        <v>0.01530233622789463</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT9" t="s">
         <v>122</v>
@@ -2790,7 +2790,7 @@
         <v>123</v>
       </c>
       <c r="BW9" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2798,7 +2798,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2822,19 +2822,19 @@
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K10">
-        <v>0.9516467148497846</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>2.531869505183189</v>
+        <v>2.608829370559007</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O10" t="s">
         <v>94</v>
@@ -2843,7 +2843,7 @@
         <v>96</v>
       </c>
       <c r="Q10">
-        <v>0.9879116787124461</v>
+        <v>1</v>
       </c>
       <c r="R10" t="s">
         <v>100</v>
@@ -2852,10 +2852,10 @@
         <v>103</v>
       </c>
       <c r="T10">
-        <v>-0.9269663208517464</v>
+        <v>-0.9312250164575222</v>
       </c>
       <c r="U10">
-        <v>0.9598096798408658</v>
+        <v>0.969012578960153</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
@@ -2864,22 +2864,22 @@
         <v>94</v>
       </c>
       <c r="X10">
-        <v>0.9997113129204496</v>
+        <v>0.9998452862170725</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-148.7663191074937</v>
+        <v>-149.5915908669479</v>
       </c>
       <c r="AA10">
-        <v>-20</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AB10">
-        <v>-0.8550595941124134</v>
+        <v>-0.8624393908306924</v>
       </c>
       <c r="AC10">
-        <v>-0.5185297392785827</v>
+        <v>-0.5061603472651568</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
@@ -2894,67 +2894,67 @@
         <v>111</v>
       </c>
       <c r="AH10">
-        <v>-0.8548127494553475</v>
+        <v>-0.8623059595699913</v>
       </c>
       <c r="AI10">
-        <v>0.949901971502339</v>
+        <v>0.9520876357080611</v>
       </c>
       <c r="AJ10">
-        <v>-1.925842983037204</v>
+        <v>-1.977952480195611</v>
       </c>
       <c r="AK10">
-        <v>-1.2851741782499</v>
+        <v>-1.239678744082058</v>
       </c>
       <c r="AL10">
-        <v>-3.153265573276221</v>
+        <v>-3.267881377329152</v>
       </c>
       <c r="AM10">
-        <v>3.442020031094641</v>
+        <v>3.219450918109771</v>
       </c>
       <c r="AN10">
-        <v>2.802616292963461</v>
+        <v>2.945769017765066</v>
       </c>
       <c r="AO10">
-        <v>0.04343244169028213</v>
+        <v>0.04393354478081245</v>
       </c>
       <c r="AP10">
-        <v>7.6322</v>
+        <v>7.6069</v>
       </c>
       <c r="AQ10">
-        <v>7.526086211634818</v>
+        <v>7.483772994207849</v>
       </c>
       <c r="AR10">
-        <v>7.522822315224786</v>
+        <v>7.479103262088698</v>
       </c>
       <c r="AS10">
-        <v>7.6322</v>
+        <v>7.6069</v>
       </c>
       <c r="AT10">
-        <v>7.4745</v>
+        <v>7.423900000000001</v>
       </c>
       <c r="AU10">
-        <v>7.526086211634818</v>
+        <v>7.483772994207849</v>
       </c>
       <c r="AV10">
-        <v>7.702942525576788</v>
+        <v>7.688984670528102</v>
       </c>
       <c r="AW10">
-        <v>-0.0139034339201256</v>
+        <v>-0.01618622642497625</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.0139034339201256</v>
+        <v>0.01618622642497625</v>
       </c>
       <c r="AZ10">
-        <v>0.41484377438388</v>
+        <v>0.4215872998674224</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.38515622561612</v>
+        <v>0.3784127001325776</v>
       </c>
       <c r="BC10" t="s">
         <v>120</v>
@@ -2966,46 +2966,46 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>493.9558393562231</v>
+        <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.009268955946750399</v>
+        <v>0.01079081761665084</v>
       </c>
       <c r="BH10">
-        <v>53943.50807927778</v>
+        <v>46335.69185975973</v>
       </c>
       <c r="BI10">
-        <v>53291.42162223771</v>
+        <v>46335.69185975973</v>
       </c>
       <c r="BJ10">
-        <v>6982.445641130698</v>
+        <v>6091.271327315953</v>
       </c>
       <c r="BK10">
-        <v>532.9142162223771</v>
+        <v>463.3569185975973</v>
       </c>
       <c r="BL10">
-        <v>0.005329142162223771</v>
+        <v>0.004633569185975973</v>
       </c>
       <c r="BM10">
-        <v>493.9558393562231</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN10">
-        <v>0.004939558393562232</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO10">
-        <v>0.1395008072086692</v>
+        <v>0.1280042126183581</v>
       </c>
       <c r="BP10">
-        <v>0.09655266359281418</v>
+        <v>0.1087448547103897</v>
       </c>
       <c r="BQ10">
-        <v>0.0762888347081721</v>
+        <v>0.07823669613789609</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT10" t="s">
         <v>122</v>
@@ -3017,7 +3017,7 @@
         <v>123</v>
       </c>
       <c r="BW10" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3025,7 +3025,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3049,19 +3049,19 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.8442669667037336</v>
+        <v>1.041925313923938</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" t="s">
         <v>94</v>
@@ -3079,10 +3079,10 @@
         <v>103</v>
       </c>
       <c r="T11">
-        <v>-0.799413457057678</v>
+        <v>-0.7672334316389841</v>
       </c>
       <c r="U11">
-        <v>0.7597236630877668</v>
+        <v>0.7452492951360262</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
@@ -3091,22 +3091,22 @@
         <v>94</v>
       </c>
       <c r="X11">
-        <v>0.9999504296472475</v>
+        <v>0.9999770035939334</v>
       </c>
       <c r="Y11">
-        <v>0.01423705444324133</v>
+        <v>0.2757833170547879</v>
       </c>
       <c r="Z11">
-        <v>-114.9934161293111</v>
+        <v>-118.0579048274395</v>
       </c>
       <c r="AA11">
-        <v>-5.999999999999996</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB11">
-        <v>-0.4225141149225828</v>
+        <v>-0.4703636561113492</v>
       </c>
       <c r="AC11">
-        <v>-0.9063563442108112</v>
+        <v>-0.8824726800357984</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
@@ -3121,67 +3121,67 @@
         <v>111</v>
       </c>
       <c r="AH11">
-        <v>-0.2142541145113562</v>
+        <v>-0.3000341528419926</v>
       </c>
       <c r="AI11">
-        <v>0.6172400075338201</v>
+        <v>0.6851678841211011</v>
       </c>
       <c r="AJ11">
-        <v>-0.5744807373974551</v>
+        <v>-0.736119286372471</v>
       </c>
       <c r="AK11">
-        <v>-1.265489614079226</v>
+        <v>-1.411213946911632</v>
       </c>
       <c r="AL11">
-        <v>-1.325059533461581</v>
+        <v>-1.524934214595735</v>
       </c>
       <c r="AM11">
-        <v>-0.2605068332565275</v>
+        <v>0.2709319473538737</v>
       </c>
       <c r="AN11">
-        <v>1.324012771455588</v>
+        <v>1.466348748653392</v>
       </c>
       <c r="AO11">
-        <v>0.08229525472093058</v>
+        <v>0.0739321825409195</v>
       </c>
       <c r="AP11">
-        <v>4156.379999999999</v>
+        <v>4185.83</v>
       </c>
       <c r="AQ11">
-        <v>4039.33707274071</v>
+        <v>4073.817921899701</v>
       </c>
       <c r="AR11">
-        <v>4165.880380238179</v>
+        <v>4183.246489108134</v>
       </c>
       <c r="AS11">
-        <v>4156.379999999999</v>
+        <v>4185.83</v>
       </c>
       <c r="AT11">
-        <v>3882.459999999999</v>
+        <v>3941.360000000001</v>
       </c>
       <c r="AU11">
-        <v>4039.33707274071</v>
+        <v>4073.817921899701</v>
       </c>
       <c r="AV11">
-        <v>4288.0825</v>
+        <v>4315.695</v>
       </c>
       <c r="AW11">
-        <v>-0.02815982351452206</v>
+        <v>-0.02675982495712889</v>
       </c>
       <c r="AX11">
-        <v>0.8886917656026969</v>
+        <v>0.8625270711916136</v>
       </c>
       <c r="AY11">
-        <v>0.02815982351452206</v>
+        <v>0.02675982495712889</v>
       </c>
       <c r="AZ11">
-        <v>0.3602178243318779</v>
+        <v>0.345467505059135</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4397821756681222</v>
+        <v>0.454532494940865</v>
       </c>
       <c r="BC11" t="s">
         <v>121</v>
@@ -3196,43 +3196,43 @@
         <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.03168682844205775</v>
+        <v>0.03102491023285702</v>
       </c>
       <c r="BH11">
-        <v>15779.42711793626</v>
+        <v>16116.08208524238</v>
       </c>
       <c r="BI11">
-        <v>11834.57033845219</v>
+        <v>12087.06156393178</v>
       </c>
       <c r="BJ11">
-        <v>2.847326360547447</v>
+        <v>2.887614060755402</v>
       </c>
       <c r="BK11">
-        <v>118.345703384522</v>
+        <v>120.8706156393178</v>
       </c>
       <c r="BL11">
-        <v>0.00118345703384522</v>
+        <v>0.001208706156393178</v>
       </c>
       <c r="BM11">
-        <v>375.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="BN11">
-        <v>0.003750000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>583.1344784013556</v>
+        <v>571.6803372881661</v>
       </c>
       <c r="BP11">
-        <v>174.2098723928191</v>
+        <v>149.6829062744359</v>
       </c>
       <c r="BQ11">
-        <v>129.242491806396</v>
+        <v>98.14238034003415</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05531098604882689</v>
+        <v>0.05389112877929883</v>
       </c>
       <c r="BT11" t="s">
         <v>122</v>
@@ -3244,7 +3244,7 @@
         <v>123</v>
       </c>
       <c r="BW11" s="2">
-        <v>46322</v>
+        <v>46324</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -256,15 +256,15 @@
     <t>GBPUSD</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -352,34 +352,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.01456,naive=0.01274,drift4=0.008193; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=naive; scores=model=2.947,naive=2.348,drift4=4.238; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04485,naive=0.01898,drift4=0.02591; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1496,naive=0.1238,drift4=0.08089; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.02444,naive=0.01909,drift4=0.01752; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02212,naive=0.01662,drift4=0.01468; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.05242,naive=0.08356,drift4=0.0793; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.009956,naive=0.01464,drift4=0.0153; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.128,naive=0.1087,drift4=0.07824; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=571.7,naive=149.7,drift4=98.14; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.01476,naive=0.01244,drift4=0.007456; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.52,naive=0.20,drift4=0.28); metric_best=naive; scores=model=2.642,naive=2.583,drift4=4.703; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04778,naive=0.01896,drift4=0.02793; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1427,naive=0.1056,drift4=0.0772; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02556,naive=0.0197,drift4=0.01664; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.05988,naive=0.1016,drift4=0.08991; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.01012,naive=0.01519,drift4=0.01519; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.02056,naive=0.01891,drift4=0.01537; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.1174,naive=0.1103,drift4=0.07662; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=583.6,naive=151.9,drift4=88.85; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -1006,19 +1006,19 @@
         <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>3.293394736705306</v>
+        <v>3.378740912970246</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O2" t="s">
         <v>94</v>
@@ -1036,10 +1036,10 @@
         <v>101</v>
       </c>
       <c r="T2">
-        <v>0.9106606642624933</v>
+        <v>0.9306934926262588</v>
       </c>
       <c r="U2">
-        <v>0.9597737270081802</v>
+        <v>0.9688101444556124</v>
       </c>
       <c r="V2" t="s">
         <v>92</v>
@@ -1048,22 +1048,22 @@
         <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9999057123602327</v>
+        <v>0.9999922910951836</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>34.78356273707708</v>
+        <v>30.52738825204341</v>
       </c>
       <c r="AA2">
-        <v>1.000000000000001</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AB2">
-        <v>0.8213129041355656</v>
+        <v>0.8613864509711305</v>
       </c>
       <c r="AC2">
-        <v>0.5704779693383464</v>
+        <v>0.5079501767726439</v>
       </c>
       <c r="AD2" t="s">
         <v>92</v>
@@ -1078,67 +1078,67 @@
         <v>109</v>
       </c>
       <c r="AH2">
-        <v>0.8212354644803243</v>
+        <v>0.8613798106249698</v>
       </c>
       <c r="AI2">
-        <v>0.9395174548097359</v>
+        <v>0.9518200568779011</v>
       </c>
       <c r="AJ2">
-        <v>2.464555010315478</v>
+        <v>2.549126527825603</v>
       </c>
       <c r="AK2">
-        <v>1.705231389955091</v>
+        <v>1.529719679925059</v>
       </c>
       <c r="AL2">
-        <v>4.2639503565686</v>
+        <v>4.288121635869815</v>
       </c>
       <c r="AM2">
-        <v>-3.495735030421925</v>
+        <v>-3.984759872388338</v>
       </c>
       <c r="AN2">
-        <v>3.904446306804026</v>
+        <v>3.884106796188359</v>
       </c>
       <c r="AO2">
-        <v>0.04562277171343429</v>
+        <v>0.04395453531168182</v>
       </c>
       <c r="AP2">
-        <v>0.83474</v>
+        <v>0.8349</v>
       </c>
       <c r="AQ2">
-        <v>0.8530467649169398</v>
+        <v>0.8544212093530574</v>
       </c>
       <c r="AR2">
-        <v>0.8559002336739718</v>
+        <v>0.858827151047561</v>
       </c>
       <c r="AS2">
-        <v>0.83474</v>
+        <v>0.8349</v>
       </c>
       <c r="AT2">
-        <v>0.8594650000000001</v>
+        <v>0.859785</v>
       </c>
       <c r="AU2">
-        <v>0.8530467649169398</v>
+        <v>0.8544212093530574</v>
       </c>
       <c r="AV2">
-        <v>0.8225354900553735</v>
+        <v>0.821885860431295</v>
       </c>
       <c r="AW2">
-        <v>0.021931098206555</v>
+        <v>0.0233814940149209</v>
       </c>
       <c r="AX2">
         <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.021931098206555</v>
+        <v>0.0233814940149209</v>
       </c>
       <c r="AZ2">
-        <v>0.4132767615940288</v>
+        <v>0.4038117345723198</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3867232384059712</v>
+        <v>0.3961882654276802</v>
       </c>
       <c r="BC2" t="s">
         <v>112</v>
@@ -1153,22 +1153,22 @@
         <v>500</v>
       </c>
       <c r="BG2">
-        <v>0.01462073213770333</v>
+        <v>0.01558766267661393</v>
       </c>
       <c r="BH2">
-        <v>34198.01384026596</v>
+        <v>32076.65000026891</v>
       </c>
       <c r="BI2">
-        <v>34198.01384026596</v>
+        <v>32076.65000026891</v>
       </c>
       <c r="BJ2">
-        <v>40968.46184472526</v>
+        <v>38419.75086868956</v>
       </c>
       <c r="BK2">
-        <v>341.9801384026596</v>
+        <v>320.7665000026892</v>
       </c>
       <c r="BL2">
-        <v>0.003419801384026596</v>
+        <v>0.003207665000026892</v>
       </c>
       <c r="BM2">
         <v>500</v>
@@ -1177,19 +1177,19 @@
         <v>0.005</v>
       </c>
       <c r="BO2">
-        <v>0.01456074222371069</v>
+        <v>0.01475731303085191</v>
       </c>
       <c r="BP2">
-        <v>0.01273817779929987</v>
+        <v>0.01244369052452963</v>
       </c>
       <c r="BQ2">
-        <v>0.008192592366240389</v>
+        <v>0.007456422959561114</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT2" t="s">
         <v>122</v>
@@ -1221,7 +1221,7 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
         <v>90</v>
@@ -1233,19 +1233,19 @@
         <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.6064542638378875</v>
+        <v>0.3424523408692119</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1263,10 +1263,10 @@
         <v>102</v>
       </c>
       <c r="T3">
-        <v>-0.8683317575861065</v>
+        <v>-0.9353001500868481</v>
       </c>
       <c r="U3">
-        <v>0.7877528177119205</v>
+        <v>0.8131384431632092</v>
       </c>
       <c r="V3" t="s">
         <v>93</v>
@@ -1275,22 +1275,22 @@
         <v>94</v>
       </c>
       <c r="X3">
-        <v>0.9880141071926903</v>
+        <v>0.96901350249651</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>127.6849818985768</v>
+        <v>143.7584485979793</v>
       </c>
       <c r="AA3">
-        <v>47.99999999999999</v>
+        <v>90</v>
       </c>
       <c r="AB3">
-        <v>-0.6113196273735488</v>
+        <v>-0.8065317875677571</v>
       </c>
       <c r="AC3">
-        <v>0.791383796389505</v>
+        <v>0.5911907269593784</v>
       </c>
       <c r="AD3" t="s">
         <v>93</v>
@@ -1305,67 +1305,67 @@
         <v>110</v>
       </c>
       <c r="AH3">
-        <v>-0.3019962079244225</v>
+        <v>-0.3907700961729017</v>
       </c>
       <c r="AI3">
-        <v>0.6722534140912019</v>
+        <v>0.7233679184644034</v>
       </c>
       <c r="AJ3">
-        <v>-0.4863212653666539</v>
+        <v>-0.3468659020247033</v>
       </c>
       <c r="AK3">
-        <v>0.8876675396272942</v>
+        <v>0.4993964211198217</v>
       </c>
       <c r="AL3">
-        <v>-0.6207243804159661</v>
+        <v>-0.3497518955610466</v>
       </c>
       <c r="AM3">
-        <v>0.4121811549329377</v>
+        <v>0.6296139460443165</v>
       </c>
       <c r="AN3">
-        <v>0.6299719581735045</v>
+        <v>0.3260613169725994</v>
       </c>
       <c r="AO3">
-        <v>0.0463160775886956</v>
+        <v>0.05164229119801473</v>
       </c>
       <c r="AP3">
-        <v>157.031</v>
+        <v>157.903</v>
       </c>
       <c r="AQ3">
-        <v>157.9508558258993</v>
+        <v>159.1723297834252</v>
       </c>
       <c r="AR3">
-        <v>158.2608615494896</v>
+        <v>159.3227157069123</v>
       </c>
       <c r="AS3">
-        <v>157.031</v>
+        <v>157.903</v>
       </c>
       <c r="AT3">
-        <v>158.048</v>
+        <v>159.792</v>
       </c>
       <c r="AU3">
-        <v>157.9508558258993</v>
+        <v>159.1723297834252</v>
       </c>
       <c r="AV3">
-        <v>155.532875</v>
+        <v>156.404875</v>
       </c>
       <c r="AW3">
-        <v>0.005857797669882409</v>
+        <v>0.008038667938070882</v>
       </c>
       <c r="AX3">
-        <v>0.6140047231701592</v>
+        <v>0.8472789543096824</v>
       </c>
       <c r="AY3">
-        <v>0.005857797669882409</v>
+        <v>0.008038667938070882</v>
       </c>
       <c r="AZ3">
-        <v>0.4991781096869681</v>
+        <v>0.5154023267716845</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3008218903130319</v>
+        <v>0.2845976732283155</v>
       </c>
       <c r="BC3" t="s">
         <v>113</v>
@@ -1380,43 +1380,43 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009540313696021905</v>
+        <v>0.009487628480776274</v>
       </c>
       <c r="BH3">
-        <v>52409.17813934029</v>
+        <v>52700.20859407536</v>
       </c>
       <c r="BI3">
-        <v>52409.17813934029</v>
+        <v>52700.20859407536</v>
       </c>
       <c r="BJ3">
         <v>333.7505214851863</v>
       </c>
       <c r="BK3">
-        <v>524.0917813934029</v>
+        <v>527.0020859407537</v>
       </c>
       <c r="BL3">
-        <v>0.005240917813934029</v>
+        <v>0.005270020859407537</v>
       </c>
       <c r="BM3">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN3">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO3">
-        <v>2.947401273681342</v>
+        <v>2.642118395805356</v>
       </c>
       <c r="BP3">
-        <v>2.348390588129686</v>
+        <v>2.582630166408372</v>
       </c>
       <c r="BQ3">
-        <v>4.238277691428006</v>
+        <v>4.703333983201522</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT3" t="s">
         <v>122</v>
@@ -1460,19 +1460,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.601962707376349</v>
+        <v>1.305286412125909</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1490,10 +1490,10 @@
         <v>102</v>
       </c>
       <c r="T4">
-        <v>-0.8875092570303886</v>
+        <v>-0.8922180012993804</v>
       </c>
       <c r="U4">
-        <v>0.799294106389153</v>
+        <v>0.8014244115365977</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1502,22 +1502,22 @@
         <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9996597629019126</v>
+        <v>0.9997052438075062</v>
       </c>
       <c r="Y4">
-        <v>0.01427563709587434</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>132.5391637230116</v>
+        <v>133.1799076199624</v>
       </c>
       <c r="AA4">
-        <v>7.999999999999998</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.6760940052895485</v>
+        <v>-0.6842914304466994</v>
       </c>
       <c r="AC4">
-        <v>0.7368153744402568</v>
+        <v>0.7292086383314518</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
@@ -1532,67 +1532,67 @@
         <v>110</v>
       </c>
       <c r="AH4">
-        <v>-0.342756180916133</v>
+        <v>-0.3420448656550524</v>
       </c>
       <c r="AI4">
-        <v>0.7010553573831118</v>
+        <v>0.7012332975526965</v>
       </c>
       <c r="AJ4">
-        <v>-1.191355127502856</v>
+        <v>-0.983698823497191</v>
       </c>
       <c r="AK4">
-        <v>1.340860156058459</v>
+        <v>1.108692421264028</v>
       </c>
       <c r="AL4">
-        <v>-2.101978656319525</v>
+        <v>-1.66527450442444</v>
       </c>
       <c r="AM4">
-        <v>1.119580104648711</v>
+        <v>1.289303196796456</v>
       </c>
       <c r="AN4">
-        <v>2.035641485288978</v>
+        <v>1.574602384132876</v>
       </c>
       <c r="AO4">
-        <v>0.03005925759064645</v>
+        <v>0.02633977942627003</v>
       </c>
       <c r="AP4">
-        <v>6.707165</v>
+        <v>6.71654</v>
       </c>
       <c r="AQ4">
-        <v>6.728333176464895</v>
+        <v>6.739294005909224</v>
       </c>
       <c r="AR4">
-        <v>6.756412033806345</v>
+        <v>6.761215724863414</v>
       </c>
       <c r="AS4">
-        <v>6.707165</v>
+        <v>6.71654</v>
       </c>
       <c r="AT4">
-        <v>6.707044999999999</v>
+        <v>6.725795</v>
       </c>
       <c r="AU4">
-        <v>6.728333176464895</v>
+        <v>6.739294005909224</v>
       </c>
       <c r="AV4">
-        <v>6.68365875</v>
+        <v>6.693033750000001</v>
       </c>
       <c r="AW4">
-        <v>0.003156054229304846</v>
+        <v>0.00338775707570031</v>
       </c>
       <c r="AX4">
-        <v>0.9005339628777785</v>
+        <v>0.9679981242956461</v>
       </c>
       <c r="AY4">
-        <v>0.003156054229304846</v>
+        <v>0.00338775707570031</v>
       </c>
       <c r="AZ4">
-        <v>0.4307363603879871</v>
+        <v>0.4333622750075093</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3692636396120129</v>
+        <v>0.3666377249924908</v>
       </c>
       <c r="BC4" t="s">
         <v>114</v>
@@ -1607,43 +1607,43 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.003504647641738293</v>
+        <v>0.003499755826660694</v>
       </c>
       <c r="BH4">
-        <v>142667.6947620337</v>
+        <v>142867.1098112227</v>
       </c>
       <c r="BI4">
-        <v>142667.6947620337</v>
+        <v>142867.1098112227</v>
       </c>
       <c r="BJ4">
-        <v>21270.93858016519</v>
+        <v>21270.9385801652</v>
       </c>
       <c r="BK4">
-        <v>1426.676947620337</v>
+        <v>1428.671098112227</v>
       </c>
       <c r="BL4">
-        <v>0.01426676947620337</v>
+        <v>0.01428671098112227</v>
       </c>
       <c r="BM4">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="BN4">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.04484503479508233</v>
+        <v>0.04778196205526292</v>
       </c>
       <c r="BP4">
-        <v>0.01897532214029101</v>
+        <v>0.01895998129063894</v>
       </c>
       <c r="BQ4">
-        <v>0.02590707952162591</v>
+        <v>0.02792971513026282</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT4" t="s">
         <v>122</v>
@@ -1687,19 +1687,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1.686218320861796</v>
+        <v>1.616572460132184</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O5" t="s">
         <v>94</v>
@@ -1717,10 +1717,10 @@
         <v>103</v>
       </c>
       <c r="T5">
-        <v>-0.9310160695900964</v>
+        <v>-0.9818373332182917</v>
       </c>
       <c r="U5">
-        <v>0.9689184193132682</v>
+        <v>0.9916260459944204</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1729,22 +1729,22 @@
         <v>94</v>
       </c>
       <c r="X5">
-        <v>0.9998447519908988</v>
+        <v>0.9991969841847563</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-149.5443119926976</v>
+        <v>-164.5063510536556</v>
       </c>
       <c r="AA5">
-        <v>-12.99999999999999</v>
+        <v>-27</v>
       </c>
       <c r="AB5">
-        <v>-0.8620214278994317</v>
+        <v>-0.9636600698065861</v>
       </c>
       <c r="AC5">
-        <v>-0.5068718357161155</v>
+        <v>-0.2671315590872138</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1759,67 +1759,67 @@
         <v>111</v>
       </c>
       <c r="AH5">
-        <v>-0.8618876007889478</v>
+        <v>-0.9628862355300126</v>
       </c>
       <c r="AI5">
-        <v>0.9524285422341819</v>
+        <v>0.9833178748673881</v>
       </c>
       <c r="AJ5">
-        <v>-1.307642339867632</v>
+        <v>-1.276534132260322</v>
       </c>
       <c r="AK5">
-        <v>-0.8193903906115763</v>
+        <v>-0.4390378921614405</v>
       </c>
       <c r="AL5">
-        <v>-1.985887170759058</v>
+        <v>-1.806419332275516</v>
       </c>
       <c r="AM5">
-        <v>2.55210889701048</v>
+        <v>2.816401832666294</v>
       </c>
       <c r="AN5">
-        <v>1.738626987625601</v>
+        <v>1.544142849550404</v>
       </c>
       <c r="AO5">
-        <v>0.04082366221641366</v>
+        <v>0.03666060359501535</v>
       </c>
       <c r="AP5">
-        <v>8.87401</v>
+        <v>8.898960000000001</v>
       </c>
       <c r="AQ5">
-        <v>8.8001122694613</v>
+        <v>8.846756456552766</v>
       </c>
       <c r="AR5">
-        <v>8.879740452396382</v>
+        <v>8.932807549047284</v>
       </c>
       <c r="AS5">
-        <v>8.87401</v>
+        <v>8.898960000000001</v>
       </c>
       <c r="AT5">
-        <v>8.678269999999999</v>
+        <v>8.72817</v>
       </c>
       <c r="AU5">
-        <v>8.8001122694613</v>
+        <v>8.846756456552766</v>
       </c>
       <c r="AV5">
-        <v>8.944222499999999</v>
+        <v>8.969172499999999</v>
       </c>
       <c r="AW5">
-        <v>-0.00832743376880354</v>
+        <v>-0.005866252174100605</v>
       </c>
       <c r="AX5">
-        <v>1.052486815577012</v>
+        <v>0.7435078290508785</v>
       </c>
       <c r="AY5">
-        <v>0.00832743376880354</v>
+        <v>0.005866252174100605</v>
       </c>
       <c r="AZ5">
-        <v>0.41045358501803</v>
+        <v>0.4125755852033638</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.38954641498197</v>
+        <v>0.3874244147966362</v>
       </c>
       <c r="BC5" t="s">
         <v>115</v>
@@ -1834,22 +1834,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.007912150200416648</v>
+        <v>0.007889966917482418</v>
       </c>
       <c r="BH5">
-        <v>63193.94694676933</v>
+        <v>63371.62186220462</v>
       </c>
       <c r="BI5">
-        <v>63193.94694676933</v>
+        <v>63371.62186220462</v>
       </c>
       <c r="BJ5">
-        <v>7121.239095602702</v>
+        <v>7121.239095602701</v>
       </c>
       <c r="BK5">
-        <v>631.9394694676934</v>
+        <v>633.7162186220462</v>
       </c>
       <c r="BL5">
-        <v>0.006319394694676934</v>
+        <v>0.006337162186220462</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1858,19 +1858,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.149646943954001</v>
+        <v>0.1426684623581498</v>
       </c>
       <c r="BP5">
-        <v>0.1238062648997809</v>
+        <v>0.1056234889380684</v>
       </c>
       <c r="BQ5">
-        <v>0.08088815701195276</v>
+        <v>0.07720462843616414</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT5" t="s">
         <v>122</v>
@@ -1914,19 +1914,19 @@
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2.191816852613451</v>
+        <v>2.088257853924038</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" t="s">
         <v>94</v>
@@ -1944,10 +1944,10 @@
         <v>103</v>
       </c>
       <c r="T6">
-        <v>-0.9047095565525618</v>
+        <v>-0.9721408351059729</v>
       </c>
       <c r="U6">
-        <v>0.9569307161286699</v>
+        <v>0.9869858172170075</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1956,22 +1956,22 @@
         <v>94</v>
       </c>
       <c r="X6">
-        <v>0.9992456627200683</v>
+        <v>0.9980897656772786</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-144.032197867296</v>
+        <v>-160.7742284166306</v>
       </c>
       <c r="AA6">
-        <v>-21.99999999999999</v>
+        <v>-37.99999999999999</v>
       </c>
       <c r="AB6">
-        <v>-0.8093471777076577</v>
+        <v>-0.9442283508264429</v>
       </c>
       <c r="AC6">
-        <v>-0.5873305252893375</v>
+        <v>-0.3292913929873902</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -1986,67 +1986,67 @@
         <v>111</v>
       </c>
       <c r="AH6">
-        <v>-0.8087366569591053</v>
+        <v>-0.9424246534222075</v>
       </c>
       <c r="AI6">
-        <v>0.9366725589471102</v>
+        <v>0.9769265843431376</v>
       </c>
       <c r="AJ6">
-        <v>-1.756786577883378</v>
+        <v>-1.675686243201328</v>
       </c>
       <c r="AK6">
-        <v>-1.426204797739647</v>
+        <v>-0.7646194488281861</v>
       </c>
       <c r="AL6">
-        <v>-2.342231527080917</v>
+        <v>-2.214383829346423</v>
       </c>
       <c r="AM6">
-        <v>4.49810636208657</v>
+        <v>4.050922111619149</v>
       </c>
       <c r="AN6">
-        <v>1.904298802940368</v>
+        <v>1.837490612426009</v>
       </c>
       <c r="AO6">
-        <v>0.03911717544807258</v>
+        <v>0.03782225927895106</v>
       </c>
       <c r="AP6">
-        <v>1.328665</v>
+        <v>1.324045</v>
       </c>
       <c r="AQ6">
-        <v>1.315672296868062</v>
+        <v>1.312148149745882</v>
       </c>
       <c r="AR6">
-        <v>1.318097453520323</v>
+        <v>1.320281026760314</v>
       </c>
       <c r="AS6">
-        <v>1.328665</v>
+        <v>1.324045</v>
       </c>
       <c r="AT6">
-        <v>1.30556</v>
+        <v>1.29632</v>
       </c>
       <c r="AU6">
-        <v>1.315672296868062</v>
+        <v>1.312148149745882</v>
       </c>
       <c r="AV6">
-        <v>1.3418275</v>
+        <v>1.3372075</v>
       </c>
       <c r="AW6">
-        <v>-0.009778765250787578</v>
+        <v>-0.008985231056434988</v>
       </c>
       <c r="AX6">
-        <v>0.9870999530437008</v>
+        <v>0.9038442738170936</v>
       </c>
       <c r="AY6">
-        <v>0.009778765250787578</v>
+        <v>0.008985231056434988</v>
       </c>
       <c r="AZ6">
-        <v>0.4379914038493627</v>
+        <v>0.4291614816320815</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3620085961506372</v>
+        <v>0.3708385183679184</v>
       </c>
       <c r="BC6" t="s">
         <v>116</v>
@@ -2061,22 +2061,22 @@
         <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.009906560344405825</v>
+        <v>0.009941127378601155</v>
       </c>
       <c r="BH6">
-        <v>50471.60493827174</v>
+        <v>50296.10636277316</v>
       </c>
       <c r="BI6">
-        <v>50471.60493827174</v>
+        <v>50296.10636277316</v>
       </c>
       <c r="BJ6">
         <v>37986.70465337142</v>
       </c>
       <c r="BK6">
-        <v>504.7160493827174</v>
+        <v>502.9610636277316</v>
       </c>
       <c r="BL6">
-        <v>0.005047160493827174</v>
+        <v>0.005029610636277316</v>
       </c>
       <c r="BM6">
         <v>500</v>
@@ -2085,19 +2085,19 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.024435639524581</v>
+        <v>0.02555824879767395</v>
       </c>
       <c r="BP6">
-        <v>0.01908638583115809</v>
+        <v>0.01969673358501425</v>
       </c>
       <c r="BQ6">
-        <v>0.01752157685838423</v>
+        <v>0.01664006164345863</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT6" t="s">
         <v>122</v>
@@ -2129,7 +2129,7 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
@@ -2141,19 +2141,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.9039271599898244</v>
       </c>
       <c r="L7">
-        <v>2.448355559158069</v>
+        <v>1.292937086363888</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7" t="s">
         <v>94</v>
@@ -2162,7 +2162,7 @@
         <v>96</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.9759817899974561</v>
       </c>
       <c r="R7" t="s">
         <v>100</v>
@@ -2171,10 +2171,10 @@
         <v>103</v>
       </c>
       <c r="T7">
-        <v>-0.8679424902676787</v>
+        <v>-0.795840700863802</v>
       </c>
       <c r="U7">
-        <v>0.9405322076889344</v>
+        <v>0.893703816089003</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2183,22 +2183,22 @@
         <v>94</v>
       </c>
       <c r="X7">
-        <v>0.999832348273916</v>
+        <v>0.9999457068072733</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-137.3801750828664</v>
+        <v>-126.7300280378528</v>
       </c>
       <c r="AA7">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="AB7">
-        <v>-0.7358628371535323</v>
+        <v>-0.5980452659787504</v>
       </c>
       <c r="AC7">
-        <v>-0.6771306261692451</v>
+        <v>-0.8014623259021011</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
@@ -2213,67 +2213,67 @@
         <v>111</v>
       </c>
       <c r="AH7">
-        <v>-0.7357394684787224</v>
+        <v>-0.5980127961918653</v>
       </c>
       <c r="AI7">
-        <v>0.9135148954568622</v>
+        <v>0.870165774698108</v>
       </c>
       <c r="AJ7">
-        <v>-1.872197956013963</v>
+        <v>-0.940598851906124</v>
       </c>
       <c r="AK7">
-        <v>-1.841178257824594</v>
+        <v>-1.307650064117717</v>
       </c>
       <c r="AL7">
-        <v>-2.999864441677517</v>
+        <v>-1.788621567071688</v>
       </c>
       <c r="AM7">
-        <v>3.456865937544864</v>
+        <v>1.027296053135507</v>
       </c>
       <c r="AN7">
-        <v>2.638502559097331</v>
+        <v>1.656572150677154</v>
       </c>
       <c r="AO7">
-        <v>0.04790185056712054</v>
+        <v>0.06152534985375147</v>
       </c>
       <c r="AP7">
-        <v>1.13531</v>
+        <v>4.65778</v>
       </c>
       <c r="AQ7">
-        <v>1.124110358715052</v>
+        <v>4.609806829669798</v>
       </c>
       <c r="AR7">
-        <v>1.131594211210355</v>
+        <v>4.66570004075639</v>
       </c>
       <c r="AS7">
-        <v>1.13531</v>
+        <v>4.65778</v>
       </c>
       <c r="AT7">
-        <v>1.109275</v>
+        <v>4.484529999999999</v>
       </c>
       <c r="AU7">
-        <v>1.124110358715052</v>
+        <v>4.609806829669798</v>
       </c>
       <c r="AV7">
-        <v>1.14567</v>
+        <v>4.700979999999999</v>
       </c>
       <c r="AW7">
-        <v>-0.009864831002058951</v>
+        <v>-0.01029957841078845</v>
       </c>
       <c r="AX7">
-        <v>1.081046456076014</v>
+        <v>1.110490053939874</v>
       </c>
       <c r="AY7">
-        <v>0.009864831002058951</v>
+        <v>0.01029957841078845</v>
       </c>
       <c r="AZ7">
-        <v>0.4313933240877914</v>
+        <v>0.5002307737605444</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3686066759122087</v>
+        <v>0.2997692262394557</v>
       </c>
       <c r="BC7" t="s">
         <v>117</v>
@@ -2285,46 +2285,46 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>500</v>
+        <v>487.990894998728</v>
       </c>
       <c r="BG7">
-        <v>0.009125260941945403</v>
+        <v>0.009274804735303017</v>
       </c>
       <c r="BH7">
-        <v>54792.95366795348</v>
+        <v>53909.49074074113</v>
       </c>
       <c r="BI7">
-        <v>54792.95366795348</v>
+        <v>52614.68127099981</v>
       </c>
       <c r="BJ7">
-        <v>48262.54826254809</v>
+        <v>11296.08553237805</v>
       </c>
       <c r="BK7">
-        <v>547.9295366795347</v>
+        <v>526.1468127099981</v>
       </c>
       <c r="BL7">
-        <v>0.005479295366795348</v>
+        <v>0.005261468127099982</v>
       </c>
       <c r="BM7">
-        <v>500</v>
+        <v>487.990894998728</v>
       </c>
       <c r="BN7">
-        <v>0.005</v>
+        <v>0.004879908949987279</v>
       </c>
       <c r="BO7">
-        <v>0.02211827353786557</v>
+        <v>0.05987976413099401</v>
       </c>
       <c r="BP7">
-        <v>0.01662269000308126</v>
+        <v>0.1015978607547848</v>
       </c>
       <c r="BQ7">
-        <v>0.01468100294008004</v>
+        <v>0.08990849250503109</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT7" t="s">
         <v>122</v>
@@ -2356,7 +2356,7 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
         <v>91</v>
@@ -2368,19 +2368,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K8">
-        <v>0.3875237439433573</v>
+        <v>0.2855066308341941</v>
       </c>
       <c r="L8">
-        <v>1.023507931409482</v>
+        <v>1.880633460185654</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O8" t="s">
         <v>94</v>
@@ -2389,7 +2389,7 @@
         <v>96</v>
       </c>
       <c r="Q8">
-        <v>0.8468809359858394</v>
+        <v>0.8213766577085485</v>
       </c>
       <c r="R8" t="s">
         <v>100</v>
@@ -2398,10 +2398,10 @@
         <v>103</v>
       </c>
       <c r="T8">
-        <v>-0.734687963719556</v>
+        <v>-0.7235236151413669</v>
       </c>
       <c r="U8">
-        <v>0.7887195394723627</v>
+        <v>0.7683804230674002</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2410,22 +2410,22 @@
         <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9999255768282354</v>
+        <v>0.9998752065146239</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-121.4780406646686</v>
+        <v>-120.7452217488702</v>
       </c>
       <c r="AA8">
-        <v>-6.999999999999997</v>
+        <v>-11</v>
       </c>
       <c r="AB8">
-        <v>-0.5221717411748173</v>
+        <v>-0.5112214130575213</v>
       </c>
       <c r="AC8">
-        <v>-0.8528403559391755</v>
+        <v>-0.8594490484208306</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
@@ -2440,67 +2440,67 @@
         <v>111</v>
       </c>
       <c r="AH8">
-        <v>-0.5221328794976332</v>
+        <v>-0.511157615955587</v>
       </c>
       <c r="AI8">
-        <v>0.8471886320641755</v>
+        <v>0.8431946044942086</v>
       </c>
       <c r="AJ8">
-        <v>-0.7440078990797057</v>
+        <v>-1.380707035153005</v>
       </c>
       <c r="AK8">
-        <v>-1.252768306779863</v>
+        <v>-2.449850074260372</v>
       </c>
       <c r="AL8">
-        <v>-1.422315781665723</v>
+        <v>-2.550765209518937</v>
       </c>
       <c r="AM8">
-        <v>0.9086215531623327</v>
+        <v>1.908526650114289</v>
       </c>
       <c r="AN8">
-        <v>1.303750748746877</v>
+        <v>2.300377809545366</v>
       </c>
       <c r="AO8">
-        <v>0.0629122811876793</v>
+        <v>0.06752094468777455</v>
       </c>
       <c r="AP8">
-        <v>4.6842</v>
+        <v>0.69546</v>
       </c>
       <c r="AQ8">
-        <v>4.636802163338683</v>
+        <v>0.6878222039864111</v>
       </c>
       <c r="AR8">
-        <v>4.677205999868868</v>
+        <v>0.6949712620086721</v>
       </c>
       <c r="AS8">
-        <v>4.6842</v>
+        <v>0.69546</v>
       </c>
       <c r="AT8">
-        <v>4.537369999999999</v>
+        <v>0.6707749999999999</v>
       </c>
       <c r="AU8">
-        <v>4.636802163338683</v>
+        <v>0.6878222039864111</v>
       </c>
       <c r="AV8">
-        <v>4.726845</v>
+        <v>0.70266875</v>
       </c>
       <c r="AW8">
-        <v>-0.01011866202581366</v>
+        <v>-0.01098236564804421</v>
       </c>
       <c r="AX8">
-        <v>1.111451205564927</v>
+        <v>1.059517393943319</v>
       </c>
       <c r="AY8">
-        <v>0.01011866202581366</v>
+        <v>0.01098236564804421</v>
       </c>
       <c r="AZ8">
-        <v>0.5010595512199196</v>
+        <v>0.5004989606275069</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.2989404487800804</v>
+        <v>0.2995010393724932</v>
       </c>
       <c r="BC8" t="s">
         <v>118</v>
@@ -2512,46 +2512,46 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>423.4404679929197</v>
+        <v>410.6883288542742</v>
       </c>
       <c r="BG8">
-        <v>0.009104009222492646</v>
+        <v>0.01036544157823589</v>
       </c>
       <c r="BH8">
-        <v>54920.85824832917</v>
+        <v>48237.21172186625</v>
       </c>
       <c r="BI8">
-        <v>46511.42783849061</v>
+        <v>39620.91974128612</v>
       </c>
       <c r="BJ8">
-        <v>9929.428256370484</v>
+        <v>56970.81031444817</v>
       </c>
       <c r="BK8">
-        <v>465.1142783849061</v>
+        <v>396.2091974128613</v>
       </c>
       <c r="BL8">
-        <v>0.004651142783849061</v>
+        <v>0.003962091974128613</v>
       </c>
       <c r="BM8">
-        <v>423.4404679929197</v>
+        <v>410.6883288542743</v>
       </c>
       <c r="BN8">
-        <v>0.004234404679929197</v>
+        <v>0.004106883288542743</v>
       </c>
       <c r="BO8">
-        <v>0.05242005318528788</v>
+        <v>0.01012146669265816</v>
       </c>
       <c r="BP8">
-        <v>0.08356103671521799</v>
+        <v>0.01519203330548107</v>
       </c>
       <c r="BQ8">
-        <v>0.07930316151635283</v>
+        <v>0.01518974121666016</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT8" t="s">
         <v>122</v>
@@ -2595,19 +2595,19 @@
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>1.580657490691484</v>
+        <v>2.48292018664256</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O9" t="s">
         <v>94</v>
@@ -2616,7 +2616,7 @@
         <v>96</v>
       </c>
       <c r="Q9">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R9" t="s">
         <v>100</v>
@@ -2625,10 +2625,10 @@
         <v>103</v>
       </c>
       <c r="T9">
-        <v>-0.6458738715279175</v>
+        <v>-0.9063526665320979</v>
       </c>
       <c r="U9">
-        <v>0.6906240438363735</v>
+        <v>0.9578006969677269</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
@@ -2637,22 +2637,22 @@
         <v>94</v>
       </c>
       <c r="X9">
-        <v>0.9999232065952424</v>
+        <v>0.9997679881131314</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-114.0052517395412</v>
+        <v>-144.3589612871395</v>
       </c>
       <c r="AA9">
-        <v>-7.999999999999998</v>
+        <v>-17</v>
       </c>
       <c r="AB9">
-        <v>-0.4068203770775038</v>
+        <v>-0.8126836007274972</v>
       </c>
       <c r="AC9">
-        <v>-0.9135081722647683</v>
+        <v>-0.5827052128723321</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
@@ -2667,67 +2667,67 @@
         <v>111</v>
       </c>
       <c r="AH9">
-        <v>-0.4067891359556232</v>
+        <v>-0.8124950484718653</v>
       </c>
       <c r="AI9">
-        <v>0.8105194080324716</v>
+        <v>0.9365796182124053</v>
       </c>
       <c r="AJ9">
-        <v>-1.135727345137667</v>
+        <v>-1.893505965617223</v>
       </c>
       <c r="AK9">
-        <v>-2.664484724449971</v>
+        <v>-1.467101241271337</v>
       </c>
       <c r="AL9">
-        <v>-2.252117691376024</v>
+        <v>-3.056251015761235</v>
       </c>
       <c r="AM9">
-        <v>1.300479567144253</v>
+        <v>3.205348086151252</v>
       </c>
       <c r="AN9">
-        <v>2.054119478603557</v>
+        <v>2.728059091268482</v>
       </c>
       <c r="AO9">
-        <v>0.07666551599409556</v>
+        <v>0.04762838563626552</v>
       </c>
       <c r="AP9">
-        <v>0.696725</v>
+        <v>1.130685</v>
       </c>
       <c r="AQ9">
-        <v>0.6879503817910337</v>
+        <v>1.118047963187125</v>
       </c>
       <c r="AR9">
-        <v>0.6931225707547108</v>
+        <v>1.12707850403741</v>
       </c>
       <c r="AS9">
-        <v>0.696725</v>
+        <v>1.130685</v>
       </c>
       <c r="AT9">
-        <v>0.673305</v>
+        <v>1.100025</v>
       </c>
       <c r="AU9">
-        <v>0.6879503817910337</v>
+        <v>1.118047963187125</v>
       </c>
       <c r="AV9">
-        <v>0.70393375</v>
+        <v>1.141045</v>
       </c>
       <c r="AW9">
-        <v>-0.0125940912253275</v>
+        <v>-0.01117644331787769</v>
       </c>
       <c r="AX9">
-        <v>1.217217715826792</v>
+        <v>1.219791198153908</v>
       </c>
       <c r="AY9">
-        <v>0.0125940912253275</v>
+        <v>0.01117644331787769</v>
       </c>
       <c r="AZ9">
-        <v>0.5026540293121369</v>
+        <v>0.4395350476848701</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.2973459706878631</v>
+        <v>0.3604649523151299</v>
       </c>
       <c r="BC9" t="s">
         <v>119</v>
@@ -2739,46 +2739,46 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.01034662169435564</v>
+        <v>0.009162587281161452</v>
       </c>
       <c r="BH9">
-        <v>48324.95231489556</v>
+        <v>54569.7393822392</v>
       </c>
       <c r="BI9">
-        <v>36243.71423617167</v>
+        <v>54569.7393822392</v>
       </c>
       <c r="BJ9">
-        <v>52020.11444425228</v>
+        <v>48262.5482625481</v>
       </c>
       <c r="BK9">
-        <v>362.4371423617167</v>
+        <v>545.697393822392</v>
       </c>
       <c r="BL9">
-        <v>0.003624371423617167</v>
+        <v>0.00545697393822392</v>
       </c>
       <c r="BM9">
-        <v>375</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN9">
-        <v>0.00375</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO9">
-        <v>0.009956424853519674</v>
+        <v>0.02055850205318315</v>
       </c>
       <c r="BP9">
-        <v>0.0146373971021013</v>
+        <v>0.01891201963655544</v>
       </c>
       <c r="BQ9">
-        <v>0.01530233622789463</v>
+        <v>0.01537203738301346</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT9" t="s">
         <v>122</v>
@@ -2822,19 +2822,19 @@
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>2.608829370559007</v>
+        <v>2.705070514113462</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O10" t="s">
         <v>94</v>
@@ -2852,10 +2852,10 @@
         <v>103</v>
       </c>
       <c r="T10">
-        <v>-0.9312250164575222</v>
+        <v>-0.9537670107020406</v>
       </c>
       <c r="U10">
-        <v>0.969012578960153</v>
+        <v>0.9791527777605064</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
@@ -2864,22 +2864,22 @@
         <v>94</v>
       </c>
       <c r="X10">
-        <v>0.9998452862170725</v>
+        <v>0.999830491778352</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-149.5915908669479</v>
+        <v>-155.1656961041744</v>
       </c>
       <c r="AA10">
-        <v>-13.99999999999999</v>
+        <v>-16</v>
       </c>
       <c r="AB10">
-        <v>-0.8624393908306924</v>
+        <v>-0.9075261832036445</v>
       </c>
       <c r="AC10">
-        <v>-0.5061603472651568</v>
+        <v>-0.419995508071009</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
@@ -2894,67 +2894,67 @@
         <v>111</v>
       </c>
       <c r="AH10">
-        <v>-0.8623059595699913</v>
+        <v>-0.9073723500542307</v>
       </c>
       <c r="AI10">
-        <v>0.9520876357080611</v>
+        <v>0.9657125306530133</v>
       </c>
       <c r="AJ10">
-        <v>-1.977952480195611</v>
+        <v>-2.057925361683973</v>
       </c>
       <c r="AK10">
-        <v>-1.239678744082058</v>
+        <v>-1.036690202182976</v>
       </c>
       <c r="AL10">
-        <v>-3.267881377329152</v>
+        <v>-3.355195142784461</v>
       </c>
       <c r="AM10">
-        <v>3.219450918109771</v>
+        <v>3.372322007769957</v>
       </c>
       <c r="AN10">
-        <v>2.945769017765066</v>
+        <v>3.022937930816534</v>
       </c>
       <c r="AO10">
-        <v>0.04393354478081245</v>
+        <v>0.04323997620335489</v>
       </c>
       <c r="AP10">
-        <v>7.6069</v>
+        <v>7.5995</v>
       </c>
       <c r="AQ10">
-        <v>7.483772994207849</v>
+        <v>7.479529156217189</v>
       </c>
       <c r="AR10">
-        <v>7.479103262088698</v>
+        <v>7.484993193572257</v>
       </c>
       <c r="AS10">
-        <v>7.6069</v>
+        <v>7.5995</v>
       </c>
       <c r="AT10">
-        <v>7.423900000000001</v>
+        <v>7.4091</v>
       </c>
       <c r="AU10">
-        <v>7.483772994207849</v>
+        <v>7.479529156217189</v>
       </c>
       <c r="AV10">
-        <v>7.688984670528102</v>
+        <v>7.679480562521874</v>
       </c>
       <c r="AW10">
-        <v>-0.01618622642497625</v>
+        <v>-0.01578667593694468</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01618622642497625</v>
+        <v>0.01578667593694468</v>
       </c>
       <c r="AZ10">
-        <v>0.4215872998674224</v>
+        <v>0.4262458159227343</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3784127001325776</v>
+        <v>0.3737541840772657</v>
       </c>
       <c r="BC10" t="s">
         <v>120</v>
@@ -2969,43 +2969,43 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01079081761665084</v>
+        <v>0.01052445062462979</v>
       </c>
       <c r="BH10">
-        <v>46335.69185975973</v>
+        <v>47508.41804795757</v>
       </c>
       <c r="BI10">
-        <v>46335.69185975973</v>
+        <v>47508.41804795757</v>
       </c>
       <c r="BJ10">
-        <v>6091.271327315953</v>
+        <v>6251.51892202876</v>
       </c>
       <c r="BK10">
-        <v>463.3569185975973</v>
+        <v>475.0841804795757</v>
       </c>
       <c r="BL10">
-        <v>0.004633569185975973</v>
+        <v>0.004750841804795757</v>
       </c>
       <c r="BM10">
-        <v>499.9999999999999</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN10">
-        <v>0.004999999999999999</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO10">
-        <v>0.1280042126183581</v>
+        <v>0.1174122215908453</v>
       </c>
       <c r="BP10">
-        <v>0.1087448547103897</v>
+        <v>0.1103279690110938</v>
       </c>
       <c r="BQ10">
-        <v>0.07823669613789609</v>
+        <v>0.07661988462949135</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT10" t="s">
         <v>122</v>
@@ -3049,19 +3049,19 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.041925313923938</v>
+        <v>1.184094117988854</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" t="s">
         <v>94</v>
@@ -3079,10 +3079,10 @@
         <v>103</v>
       </c>
       <c r="T11">
-        <v>-0.7672334316389841</v>
+        <v>-0.8035130852316634</v>
       </c>
       <c r="U11">
-        <v>0.7452492951360262</v>
+        <v>0.7615723161265613</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
@@ -3091,22 +3091,22 @@
         <v>94</v>
       </c>
       <c r="X11">
-        <v>0.9999770035939334</v>
+        <v>0.9999657110892508</v>
       </c>
       <c r="Y11">
-        <v>0.2757833170547879</v>
+        <v>0.2858700109977305</v>
       </c>
       <c r="Z11">
-        <v>-118.0579048274395</v>
+        <v>-123.778093395207</v>
       </c>
       <c r="AA11">
-        <v>-4.999999999999995</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB11">
-        <v>-0.4703636561113492</v>
+        <v>-0.5559778542657846</v>
       </c>
       <c r="AC11">
-        <v>-0.8824726800357984</v>
+        <v>-0.8311971039206127</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
@@ -3121,67 +3121,67 @@
         <v>111</v>
       </c>
       <c r="AH11">
-        <v>-0.3000341528419926</v>
+        <v>-0.3574453679570265</v>
       </c>
       <c r="AI11">
-        <v>0.6851678841211011</v>
+        <v>0.7141599891641723</v>
       </c>
       <c r="AJ11">
-        <v>-0.736119286372471</v>
+        <v>-0.863648980598598</v>
       </c>
       <c r="AK11">
-        <v>-1.411213946911632</v>
+        <v>-1.336363537718617</v>
       </c>
       <c r="AL11">
-        <v>-1.524934214595735</v>
+        <v>-1.621296341443538</v>
       </c>
       <c r="AM11">
-        <v>0.2709319473538737</v>
+        <v>0.8466860714347184</v>
       </c>
       <c r="AN11">
-        <v>1.466348748653392</v>
+        <v>1.50767916435789</v>
       </c>
       <c r="AO11">
-        <v>0.0739321825409195</v>
+        <v>0.06530245464231241</v>
       </c>
       <c r="AP11">
-        <v>4185.83</v>
+        <v>4182.79</v>
       </c>
       <c r="AQ11">
-        <v>4073.817921899701</v>
+        <v>4083.666873774167</v>
       </c>
       <c r="AR11">
-        <v>4183.246489108134</v>
+        <v>4228.628324825712</v>
       </c>
       <c r="AS11">
-        <v>4185.83</v>
+        <v>4182.79</v>
       </c>
       <c r="AT11">
-        <v>3941.360000000001</v>
+        <v>3935.280000000001</v>
       </c>
       <c r="AU11">
-        <v>4073.817921899701</v>
+        <v>4083.666873774167</v>
       </c>
       <c r="AV11">
-        <v>4315.695</v>
+        <v>4312.655</v>
       </c>
       <c r="AW11">
-        <v>-0.02675982495712889</v>
+        <v>-0.02369784909733276</v>
       </c>
       <c r="AX11">
-        <v>0.8625270711916136</v>
+        <v>0.7632782214286572</v>
       </c>
       <c r="AY11">
-        <v>0.02675982495712889</v>
+        <v>0.02369784909733276</v>
       </c>
       <c r="AZ11">
-        <v>0.345467505059135</v>
+        <v>0.3370902964348517</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.454532494940865</v>
+        <v>0.4629097035651483</v>
       </c>
       <c r="BC11" t="s">
         <v>121</v>
@@ -3196,22 +3196,22 @@
         <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.03102491023285702</v>
+        <v>0.03104745875360702</v>
       </c>
       <c r="BH11">
-        <v>16116.08208524238</v>
+        <v>16104.37762291612</v>
       </c>
       <c r="BI11">
-        <v>12087.06156393178</v>
+        <v>12078.28321718709</v>
       </c>
       <c r="BJ11">
         <v>2.887614060755402</v>
       </c>
       <c r="BK11">
-        <v>120.8706156393178</v>
+        <v>120.7828321718709</v>
       </c>
       <c r="BL11">
-        <v>0.001208706156393178</v>
+        <v>0.001207828321718709</v>
       </c>
       <c r="BM11">
         <v>375</v>
@@ -3220,19 +3220,19 @@
         <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>571.6803372881661</v>
+        <v>583.6159500412928</v>
       </c>
       <c r="BP11">
-        <v>149.6829062744359</v>
+        <v>151.9030217894891</v>
       </c>
       <c r="BQ11">
-        <v>98.14238034003415</v>
+        <v>88.85490573226802</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05389112877929883</v>
+        <v>0.05477037382902145</v>
       </c>
       <c r="BT11" t="s">
         <v>122</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="128">
   <si>
     <t>Pair</t>
   </si>
@@ -316,6 +316,9 @@
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
@@ -325,6 +328,9 @@
     <t>空头减速</t>
   </si>
   <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
     <t>空头加速</t>
   </si>
   <si>
@@ -340,6 +346,9 @@
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
@@ -349,37 +358,40 @@
     <t>下降谷底收敛</t>
   </si>
   <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.01476,naive=0.01244,drift4=0.007456; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.52,naive=0.20,drift4=0.28); metric_best=naive; scores=model=2.642,naive=2.583,drift4=4.703; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04778,naive=0.01896,drift4=0.02793; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1427,naive=0.1056,drift4=0.0772; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02556,naive=0.0197,drift4=0.01664; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.05988,naive=0.1016,drift4=0.08991; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.01012,naive=0.01519,drift4=0.01519; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.02056,naive=0.01891,drift4=0.01537; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.1174,naive=0.1103,drift4=0.07662; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=583.6,naive=151.9,drift4=88.85; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.01549,naive=0.007894,drift4=0.007732; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=2.714,naive=2.464,drift4=4.569; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04491,naive=0.01891,drift4=0.02598; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1478,naive=0.1277,drift4=0.07807; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.0266,naive=0.02144,drift4=0.01703; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.06393,naive=0.1067,drift4=0.09407; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.01103,naive=0.01624,drift4=0.01602; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01997,naive=0.02468,drift4=0.01987; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.1128,naive=0.1523,drift4=0.1087; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=585.4,naive=153.9,drift4=90.59; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -982,7 +994,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1006,19 +1018,19 @@
         <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>3.378740912970246</v>
+        <v>2.608637289688342</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
         <v>94</v>
@@ -1033,13 +1045,13 @@
         <v>98</v>
       </c>
       <c r="S2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T2">
-        <v>0.9306934926262588</v>
+        <v>0.9796349403972437</v>
       </c>
       <c r="U2">
-        <v>0.9688101444556124</v>
+        <v>0.9907448616739116</v>
       </c>
       <c r="V2" t="s">
         <v>92</v>
@@ -1048,100 +1060,100 @@
         <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9999922910951836</v>
+        <v>0.9996365539806078</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>30.52738825204341</v>
+        <v>16.41044730187966</v>
       </c>
       <c r="AA2">
-        <v>-3.999999999999993</v>
+        <v>-19</v>
       </c>
       <c r="AB2">
-        <v>0.8613864509711305</v>
+        <v>0.95926247650358</v>
       </c>
       <c r="AC2">
-        <v>0.5079501767726439</v>
+        <v>0.2825163732816537</v>
       </c>
       <c r="AD2" t="s">
         <v>92</v>
       </c>
       <c r="AE2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AF2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AG2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AH2">
-        <v>0.8613798106249698</v>
+        <v>0.9589138363749424</v>
       </c>
       <c r="AI2">
-        <v>0.9518200568779011</v>
+        <v>0.9825022639046214</v>
       </c>
       <c r="AJ2">
-        <v>2.549126527825603</v>
+        <v>2.05009011765739</v>
       </c>
       <c r="AK2">
-        <v>1.529719679925059</v>
+        <v>0.6972104431422118</v>
       </c>
       <c r="AL2">
-        <v>4.288121635869815</v>
+        <v>2.973943519718391</v>
       </c>
       <c r="AM2">
-        <v>-3.984759872388338</v>
+        <v>-4.716551146444409</v>
       </c>
       <c r="AN2">
-        <v>3.884106796188359</v>
+        <v>2.52479207909921</v>
       </c>
       <c r="AO2">
-        <v>0.04395453531168182</v>
+        <v>0.03432848626443592</v>
       </c>
       <c r="AP2">
-        <v>0.8349</v>
+        <v>0.826435</v>
       </c>
       <c r="AQ2">
-        <v>0.8544212093530574</v>
+        <v>0.8349696568410131</v>
       </c>
       <c r="AR2">
-        <v>0.858827151047561</v>
+        <v>0.8317190033401873</v>
       </c>
       <c r="AS2">
-        <v>0.8349</v>
+        <v>0.826435</v>
       </c>
       <c r="AT2">
-        <v>0.859785</v>
+        <v>0.8428550000000001</v>
       </c>
       <c r="AU2">
-        <v>0.8544212093530574</v>
+        <v>0.8349696568410131</v>
       </c>
       <c r="AV2">
-        <v>0.821885860431295</v>
+        <v>0.8188550000000001</v>
       </c>
       <c r="AW2">
-        <v>0.0233814940149209</v>
+        <v>0.01032707574220969</v>
       </c>
       <c r="AX2">
-        <v>1.5</v>
+        <v>1.125944174276142</v>
       </c>
       <c r="AY2">
-        <v>0.0233814940149209</v>
+        <v>0.01032707574220969</v>
       </c>
       <c r="AZ2">
-        <v>0.4038117345723198</v>
+        <v>0.4131954507127501</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3961882654276802</v>
+        <v>0.3868045492872498</v>
       </c>
       <c r="BC2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1153,22 +1165,22 @@
         <v>500</v>
       </c>
       <c r="BG2">
-        <v>0.01558766267661393</v>
+        <v>0.009171925196778839</v>
       </c>
       <c r="BH2">
-        <v>32076.65000026891</v>
+        <v>54514.18205804807</v>
       </c>
       <c r="BI2">
-        <v>32076.65000026891</v>
+        <v>54514.18205804807</v>
       </c>
       <c r="BJ2">
-        <v>38419.75086868956</v>
+        <v>65963.06068601653</v>
       </c>
       <c r="BK2">
-        <v>320.7665000026892</v>
+        <v>545.1418205804807</v>
       </c>
       <c r="BL2">
-        <v>0.003207665000026892</v>
+        <v>0.005451418205804808</v>
       </c>
       <c r="BM2">
         <v>500</v>
@@ -1177,31 +1189,31 @@
         <v>0.005</v>
       </c>
       <c r="BO2">
-        <v>0.01475731303085191</v>
+        <v>0.01548532872769406</v>
       </c>
       <c r="BP2">
-        <v>0.01244369052452963</v>
+        <v>0.007894167149506309</v>
       </c>
       <c r="BQ2">
-        <v>0.007456422959561114</v>
+        <v>0.007731639913840072</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW2" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1209,7 +1221,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1221,7 +1233,7 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
         <v>90</v>
@@ -1233,19 +1245,19 @@
         <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.3424523408692119</v>
+        <v>0.2618113337995194</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1260,13 +1272,13 @@
         <v>99</v>
       </c>
       <c r="S3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T3">
-        <v>-0.9353001500868481</v>
+        <v>-0.9040330999209918</v>
       </c>
       <c r="U3">
-        <v>0.8131384431632092</v>
+        <v>0.8034816978108861</v>
       </c>
       <c r="V3" t="s">
         <v>93</v>
@@ -1275,100 +1287,100 @@
         <v>94</v>
       </c>
       <c r="X3">
-        <v>0.96901350249651</v>
+        <v>0.9866672113857586</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>143.7584485979793</v>
+        <v>135.7624140442337</v>
       </c>
       <c r="AA3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AB3">
-        <v>-0.8065317875677571</v>
+        <v>-0.7164531140400342</v>
       </c>
       <c r="AC3">
-        <v>0.5911907269593784</v>
+        <v>0.6976352452265708</v>
       </c>
       <c r="AD3" t="s">
         <v>93</v>
       </c>
       <c r="AE3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AG3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AH3">
-        <v>-0.3907700961729017</v>
+        <v>-0.3534503980592617</v>
       </c>
       <c r="AI3">
-        <v>0.7233679184644034</v>
+        <v>0.7027950690557376</v>
       </c>
       <c r="AJ3">
-        <v>-0.3468659020247033</v>
+        <v>-0.2799160452746512</v>
       </c>
       <c r="AK3">
-        <v>0.4993964211198217</v>
+        <v>0.4588162104022177</v>
       </c>
       <c r="AL3">
-        <v>-0.3497518955610466</v>
+        <v>-0.3114098830211929</v>
       </c>
       <c r="AM3">
-        <v>0.6296139460443165</v>
+        <v>0.4534600500415369</v>
       </c>
       <c r="AN3">
-        <v>0.3260613169725994</v>
+        <v>0.296562298165182</v>
       </c>
       <c r="AO3">
-        <v>0.05164229119801473</v>
+        <v>0.04982926094192065</v>
       </c>
       <c r="AP3">
-        <v>157.903</v>
+        <v>157.6555</v>
       </c>
       <c r="AQ3">
-        <v>159.1723297834252</v>
+        <v>158.8684935872391</v>
       </c>
       <c r="AR3">
-        <v>159.3227157069123</v>
+        <v>159.1009716676874</v>
       </c>
       <c r="AS3">
-        <v>157.903</v>
+        <v>157.6555</v>
       </c>
       <c r="AT3">
-        <v>159.792</v>
+        <v>159.297</v>
       </c>
       <c r="AU3">
-        <v>159.1723297834252</v>
+        <v>158.8684935872391</v>
       </c>
       <c r="AV3">
-        <v>156.404875</v>
+        <v>156.157375</v>
       </c>
       <c r="AW3">
-        <v>0.008038667938070882</v>
+        <v>0.007693950336265719</v>
       </c>
       <c r="AX3">
-        <v>0.8472789543096824</v>
+        <v>0.8096744845984996</v>
       </c>
       <c r="AY3">
-        <v>0.008038667938070882</v>
+        <v>0.007693950336265719</v>
       </c>
       <c r="AZ3">
-        <v>0.5154023267716845</v>
+        <v>0.5111833150786086</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.2845976732283155</v>
+        <v>0.2888166849213915</v>
       </c>
       <c r="BC3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1380,55 +1392,55 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009487628480776274</v>
+        <v>0.009502522905956443</v>
       </c>
       <c r="BH3">
-        <v>52700.20859407536</v>
+        <v>52617.60534000778</v>
       </c>
       <c r="BI3">
-        <v>52700.20859407536</v>
+        <v>52617.60534000778</v>
       </c>
       <c r="BJ3">
         <v>333.7505214851863</v>
       </c>
       <c r="BK3">
-        <v>527.0020859407537</v>
+        <v>526.1760534000778</v>
       </c>
       <c r="BL3">
-        <v>0.005270020859407537</v>
+        <v>0.005261760534000777</v>
       </c>
       <c r="BM3">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="BN3">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>2.642118395805356</v>
+        <v>2.714003218867912</v>
       </c>
       <c r="BP3">
-        <v>2.582630166408372</v>
+        <v>2.463672355706823</v>
       </c>
       <c r="BQ3">
-        <v>4.703333983201522</v>
+        <v>4.569272956396243</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU3" t="s">
         <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW3" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1436,7 +1448,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1460,19 +1472,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.305286412125909</v>
+        <v>1.19362427702495</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1487,13 +1499,13 @@
         <v>99</v>
       </c>
       <c r="S4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T4">
-        <v>-0.8922180012993804</v>
+        <v>-0.9664049471866771</v>
       </c>
       <c r="U4">
-        <v>0.8014244115365977</v>
+        <v>0.8343774977760345</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1502,100 +1514,100 @@
         <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9997052438075062</v>
+        <v>0.9979810861681192</v>
       </c>
       <c r="Y4">
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>133.1799076199624</v>
+        <v>154.3537461065839</v>
       </c>
       <c r="AA4">
-        <v>13.00000000000001</v>
+        <v>42.00000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.6842914304466994</v>
+        <v>-0.9014834172147076</v>
       </c>
       <c r="AC4">
-        <v>0.7292086383314518</v>
+        <v>0.4328136417523059</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AG4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="AH4">
-        <v>-0.3420448656550524</v>
+        <v>-0.4498316999372408</v>
       </c>
       <c r="AI4">
-        <v>0.7012332975526965</v>
+        <v>0.7653579103828585</v>
       </c>
       <c r="AJ4">
-        <v>-0.983698823497191</v>
+        <v>-0.875977160782628</v>
       </c>
       <c r="AK4">
-        <v>1.108692421264028</v>
+        <v>0.5233042074103007</v>
       </c>
       <c r="AL4">
-        <v>-1.66527450442444</v>
+        <v>-1.621531224814846</v>
       </c>
       <c r="AM4">
-        <v>1.289303196796456</v>
+        <v>0.7595991782462008</v>
       </c>
       <c r="AN4">
-        <v>1.574602384132876</v>
+        <v>1.57002796163998</v>
       </c>
       <c r="AO4">
-        <v>0.02633977942627003</v>
+        <v>0.0292032996026361</v>
       </c>
       <c r="AP4">
-        <v>6.71654</v>
+        <v>6.707825</v>
       </c>
       <c r="AQ4">
-        <v>6.739294005909224</v>
+        <v>6.727488694656001</v>
       </c>
       <c r="AR4">
-        <v>6.761215724863414</v>
+        <v>6.752987456069103</v>
       </c>
       <c r="AS4">
-        <v>6.71654</v>
+        <v>6.707825</v>
       </c>
       <c r="AT4">
-        <v>6.725795</v>
+        <v>6.708364999999999</v>
       </c>
       <c r="AU4">
-        <v>6.739294005909224</v>
+        <v>6.727488694656001</v>
       </c>
       <c r="AV4">
-        <v>6.693033750000001</v>
+        <v>6.68431875</v>
       </c>
       <c r="AW4">
-        <v>0.00338775707570031</v>
+        <v>0.002931456121172153</v>
       </c>
       <c r="AX4">
-        <v>0.9679981242956461</v>
+        <v>0.8365304825738651</v>
       </c>
       <c r="AY4">
-        <v>0.00338775707570031</v>
+        <v>0.002931456121172153</v>
       </c>
       <c r="AZ4">
-        <v>0.4333622750075093</v>
+        <v>0.4309869144409747</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3666377249924908</v>
+        <v>0.3690130855590253</v>
       </c>
       <c r="BC4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1607,22 +1619,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.003499755826660694</v>
+        <v>0.003504302810523473</v>
       </c>
       <c r="BH4">
-        <v>142867.1098112227</v>
+        <v>142681.7335814966</v>
       </c>
       <c r="BI4">
-        <v>142867.1098112227</v>
+        <v>142681.7335814966</v>
       </c>
       <c r="BJ4">
         <v>21270.9385801652</v>
       </c>
       <c r="BK4">
-        <v>1428.671098112227</v>
+        <v>1426.817335814966</v>
       </c>
       <c r="BL4">
-        <v>0.01428671098112227</v>
+        <v>0.01426817335814966</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1631,31 +1643,31 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.04778196205526292</v>
+        <v>0.04490838928174511</v>
       </c>
       <c r="BP4">
-        <v>0.01895998129063894</v>
+        <v>0.0189131590017995</v>
       </c>
       <c r="BQ4">
-        <v>0.02792971513026282</v>
+        <v>0.025983599551301</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU4" t="s">
         <v>90</v>
       </c>
       <c r="BV4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW4" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1663,7 +1675,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1687,19 +1699,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1.616572460132184</v>
+        <v>1.627240488486849</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O5" t="s">
         <v>94</v>
@@ -1714,13 +1726,13 @@
         <v>100</v>
       </c>
       <c r="S5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T5">
-        <v>-0.9818373332182917</v>
+        <v>-0.9940211326421459</v>
       </c>
       <c r="U5">
-        <v>0.9916260459944204</v>
+        <v>0.9971626583140305</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1729,100 +1741,100 @@
         <v>94</v>
       </c>
       <c r="X5">
-        <v>0.9991969841847563</v>
+        <v>0.9994125945002593</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-164.5063510536556</v>
+        <v>-171.1292623209555</v>
       </c>
       <c r="AA5">
-        <v>-27</v>
+        <v>-25</v>
       </c>
       <c r="AB5">
-        <v>-0.9636600698065861</v>
+        <v>-0.9880387512005313</v>
       </c>
       <c r="AC5">
-        <v>-0.2671315590872138</v>
+        <v>-0.1542057914803935</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AH5">
-        <v>-0.9628862355300126</v>
+        <v>-0.9874583718041192</v>
       </c>
       <c r="AI5">
-        <v>0.9833178748673881</v>
+        <v>0.9905963388632689</v>
       </c>
       <c r="AJ5">
-        <v>-1.276534132260322</v>
+        <v>-1.277873527068895</v>
       </c>
       <c r="AK5">
-        <v>-0.4390378921614405</v>
+        <v>-0.2709725081015805</v>
       </c>
       <c r="AL5">
-        <v>-1.806419332275516</v>
+        <v>-1.843404713991136</v>
       </c>
       <c r="AM5">
-        <v>2.816401832666294</v>
+        <v>2.5773153998553</v>
       </c>
       <c r="AN5">
-        <v>1.544142849550404</v>
+        <v>1.609260271222911</v>
       </c>
       <c r="AO5">
-        <v>0.03666060359501535</v>
+        <v>0.03739796381320831</v>
       </c>
       <c r="AP5">
-        <v>8.898960000000001</v>
+        <v>8.860749999999999</v>
       </c>
       <c r="AQ5">
-        <v>8.846756456552766</v>
+        <v>8.790977784891592</v>
       </c>
       <c r="AR5">
-        <v>8.932807549047284</v>
+        <v>8.890809715407702</v>
       </c>
       <c r="AS5">
-        <v>8.898960000000001</v>
+        <v>8.860749999999999</v>
       </c>
       <c r="AT5">
-        <v>8.72817</v>
+        <v>8.651749999999998</v>
       </c>
       <c r="AU5">
-        <v>8.846756456552766</v>
+        <v>8.790977784891592</v>
       </c>
       <c r="AV5">
-        <v>8.969172499999999</v>
+        <v>8.9309625</v>
       </c>
       <c r="AW5">
-        <v>-0.005866252174100605</v>
+        <v>-0.007874301284700271</v>
       </c>
       <c r="AX5">
-        <v>0.7435078290508785</v>
+        <v>0.9937292520335919</v>
       </c>
       <c r="AY5">
-        <v>0.005866252174100605</v>
+        <v>0.007874301284700271</v>
       </c>
       <c r="AZ5">
-        <v>0.4125755852033638</v>
+        <v>0.4075458080648772</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3874244147966362</v>
+        <v>0.3924541919351229</v>
       </c>
       <c r="BC5" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1834,22 +1846,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.007889966917482418</v>
+        <v>0.007923990632847034</v>
       </c>
       <c r="BH5">
-        <v>63371.62186220462</v>
+        <v>63099.51931636163</v>
       </c>
       <c r="BI5">
-        <v>63371.62186220462</v>
+        <v>63099.51931636163</v>
       </c>
       <c r="BJ5">
         <v>7121.239095602701</v>
       </c>
       <c r="BK5">
-        <v>633.7162186220462</v>
+        <v>630.9951931636162</v>
       </c>
       <c r="BL5">
-        <v>0.006337162186220462</v>
+        <v>0.006309951931636163</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1858,31 +1870,31 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.1426684623581498</v>
+        <v>0.1477755314743206</v>
       </c>
       <c r="BP5">
-        <v>0.1056234889380684</v>
+        <v>0.1277296930196652</v>
       </c>
       <c r="BQ5">
-        <v>0.07720462843616414</v>
+        <v>0.07806579320859676</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW5" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1890,7 +1902,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1914,19 +1926,19 @@
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2.088257853924038</v>
+        <v>2.137214015356746</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O6" t="s">
         <v>94</v>
@@ -1938,16 +1950,16 @@
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T6">
-        <v>-0.9721408351059729</v>
+        <v>-0.9795687248641783</v>
       </c>
       <c r="U6">
-        <v>0.9869858172170075</v>
+        <v>0.9906040627503265</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1956,100 +1968,100 @@
         <v>94</v>
       </c>
       <c r="X6">
-        <v>0.9980897656772786</v>
+        <v>0.9991925462457855</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-160.7742284166306</v>
+        <v>-163.5608725506031</v>
       </c>
       <c r="AA6">
-        <v>-37.99999999999999</v>
+        <v>-27</v>
       </c>
       <c r="AB6">
-        <v>-0.9442283508264429</v>
+        <v>-0.9591209390869654</v>
       </c>
       <c r="AC6">
-        <v>-0.3292913929873902</v>
+        <v>-0.2829965091744729</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
       </c>
       <c r="AE6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AH6">
-        <v>-0.9424246534222075</v>
+        <v>-0.9583464932839538</v>
       </c>
       <c r="AI6">
-        <v>0.9769265843431376</v>
+        <v>0.9816195552636744</v>
       </c>
       <c r="AJ6">
-        <v>-1.675686243201328</v>
+        <v>-1.700671729753976</v>
       </c>
       <c r="AK6">
-        <v>-0.7646194488281861</v>
+        <v>-0.6196399847827141</v>
       </c>
       <c r="AL6">
-        <v>-2.214383829346423</v>
+        <v>-2.319054224479197</v>
       </c>
       <c r="AM6">
-        <v>4.050922111619149</v>
+        <v>3.681947944800657</v>
       </c>
       <c r="AN6">
-        <v>1.837490612426009</v>
+        <v>1.985039928428203</v>
       </c>
       <c r="AO6">
-        <v>0.03782225927895106</v>
+        <v>0.0388941176562674</v>
       </c>
       <c r="AP6">
-        <v>1.324045</v>
+        <v>1.32041</v>
       </c>
       <c r="AQ6">
-        <v>1.312148149745882</v>
+        <v>1.307555618164289</v>
       </c>
       <c r="AR6">
-        <v>1.320281026760314</v>
+        <v>1.317711914353102</v>
       </c>
       <c r="AS6">
-        <v>1.324045</v>
+        <v>1.32041</v>
       </c>
       <c r="AT6">
-        <v>1.29632</v>
+        <v>1.28905</v>
       </c>
       <c r="AU6">
-        <v>1.312148149745882</v>
+        <v>1.307555618164289</v>
       </c>
       <c r="AV6">
-        <v>1.3372075</v>
+        <v>1.3335725</v>
       </c>
       <c r="AW6">
-        <v>-0.008985231056434988</v>
+        <v>-0.009735144262547806</v>
       </c>
       <c r="AX6">
-        <v>0.9038442738170936</v>
+        <v>0.976591212589613</v>
       </c>
       <c r="AY6">
-        <v>0.008985231056434988</v>
+        <v>0.009735144262547806</v>
       </c>
       <c r="AZ6">
-        <v>0.4291614816320815</v>
+        <v>0.4268248803473757</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3708385183679184</v>
+        <v>0.3731751196526242</v>
       </c>
       <c r="BC6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2061,22 +2073,22 @@
         <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.009941127378601155</v>
+        <v>0.009968494634242368</v>
       </c>
       <c r="BH6">
-        <v>50296.10636277316</v>
+        <v>50158.02469135816</v>
       </c>
       <c r="BI6">
-        <v>50296.10636277316</v>
+        <v>50158.02469135816</v>
       </c>
       <c r="BJ6">
         <v>37986.70465337142</v>
       </c>
       <c r="BK6">
-        <v>502.9610636277316</v>
+        <v>501.5802469135816</v>
       </c>
       <c r="BL6">
-        <v>0.005029610636277316</v>
+        <v>0.005015802469135816</v>
       </c>
       <c r="BM6">
         <v>500</v>
@@ -2085,31 +2097,31 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.02555824879767395</v>
+        <v>0.02660213945007981</v>
       </c>
       <c r="BP6">
-        <v>0.01969673358501425</v>
+        <v>0.02143610497483248</v>
       </c>
       <c r="BQ6">
-        <v>0.01664006164345863</v>
+        <v>0.0170288967832171</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU6" t="s">
         <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW6" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2117,7 +2129,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2141,19 +2153,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K7">
-        <v>0.9039271599898244</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>1.292937086363888</v>
+        <v>1.436117214086973</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O7" t="s">
         <v>94</v>
@@ -2162,19 +2174,19 @@
         <v>96</v>
       </c>
       <c r="Q7">
-        <v>0.9759817899974561</v>
+        <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T7">
-        <v>-0.795840700863802</v>
+        <v>-0.8324927566148754</v>
       </c>
       <c r="U7">
-        <v>0.893703816089003</v>
+        <v>0.9246058751830176</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2183,100 +2195,100 @@
         <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9999457068072733</v>
+        <v>0.9999365388252949</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-126.7300280378528</v>
+        <v>-131.6803984646848</v>
       </c>
       <c r="AA7">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="AB7">
-        <v>-0.5980452659787504</v>
+        <v>-0.6649748823486659</v>
       </c>
       <c r="AC7">
-        <v>-0.8014623259021011</v>
+        <v>-0.7468657214288108</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AH7">
-        <v>-0.5980127961918653</v>
+        <v>-0.6649326822614826</v>
       </c>
       <c r="AI7">
-        <v>0.870165774698108</v>
+        <v>0.8907932093356834</v>
       </c>
       <c r="AJ7">
-        <v>-0.940598851906124</v>
+        <v>-1.058581563827818</v>
       </c>
       <c r="AK7">
-        <v>-1.307650064117717</v>
+        <v>-1.237913132438912</v>
       </c>
       <c r="AL7">
-        <v>-1.788621567071688</v>
+        <v>-1.927592862822559</v>
       </c>
       <c r="AM7">
-        <v>1.027296053135507</v>
+        <v>1.362787785936421</v>
       </c>
       <c r="AN7">
-        <v>1.656572150677154</v>
+        <v>1.764276295525329</v>
       </c>
       <c r="AO7">
-        <v>0.06152534985375147</v>
+        <v>0.05784695971846391</v>
       </c>
       <c r="AP7">
-        <v>4.65778</v>
+        <v>4.65158</v>
       </c>
       <c r="AQ7">
-        <v>4.609806829669798</v>
+        <v>4.600494737305521</v>
       </c>
       <c r="AR7">
-        <v>4.66570004075639</v>
+        <v>4.657655485483788</v>
       </c>
       <c r="AS7">
-        <v>4.65778</v>
+        <v>4.65158</v>
       </c>
       <c r="AT7">
-        <v>4.484529999999999</v>
+        <v>4.47213</v>
       </c>
       <c r="AU7">
-        <v>4.609806829669798</v>
+        <v>4.600494737305521</v>
       </c>
       <c r="AV7">
-        <v>4.700979999999999</v>
+        <v>4.69478</v>
       </c>
       <c r="AW7">
-        <v>-0.01029957841078845</v>
+        <v>-0.01098234636284426</v>
       </c>
       <c r="AX7">
-        <v>1.110490053939874</v>
+        <v>1.182529229038877</v>
       </c>
       <c r="AY7">
-        <v>0.01029957841078845</v>
+        <v>0.01098234636284426</v>
       </c>
       <c r="AZ7">
-        <v>0.5002307737605444</v>
+        <v>0.4984476233245135</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.2997692262394557</v>
+        <v>0.3015523766754865</v>
       </c>
       <c r="BC7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2285,58 +2297,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>487.990894998728</v>
+        <v>500</v>
       </c>
       <c r="BG7">
-        <v>0.009274804735303017</v>
+        <v>0.009287166941125313</v>
       </c>
       <c r="BH7">
-        <v>53909.49074074113</v>
+        <v>53837.73148148188</v>
       </c>
       <c r="BI7">
-        <v>52614.68127099981</v>
+        <v>53837.73148148188</v>
       </c>
       <c r="BJ7">
-        <v>11296.08553237805</v>
+        <v>11574.07407407416</v>
       </c>
       <c r="BK7">
-        <v>526.1468127099981</v>
+        <v>538.3773148148189</v>
       </c>
       <c r="BL7">
-        <v>0.005261468127099982</v>
+        <v>0.005383773148148189</v>
       </c>
       <c r="BM7">
-        <v>487.990894998728</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN7">
-        <v>0.004879908949987279</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO7">
-        <v>0.05987976413099401</v>
+        <v>0.06392813720795297</v>
       </c>
       <c r="BP7">
-        <v>0.1015978607547848</v>
+        <v>0.1066584905580932</v>
       </c>
       <c r="BQ7">
-        <v>0.08990849250503109</v>
+        <v>0.09406755710042691</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU7" t="s">
         <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW7" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2344,7 +2356,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2368,19 +2380,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K8">
-        <v>0.2855066308341941</v>
+        <v>0.4559350349948318</v>
       </c>
       <c r="L8">
-        <v>1.880633460185654</v>
+        <v>2.039962344502193</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="s">
         <v>94</v>
@@ -2389,19 +2401,19 @@
         <v>96</v>
       </c>
       <c r="Q8">
-        <v>0.8213766577085485</v>
+        <v>0.8639837587487079</v>
       </c>
       <c r="R8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T8">
-        <v>-0.7235236151413669</v>
+        <v>-0.7640048563958072</v>
       </c>
       <c r="U8">
-        <v>0.7683804230674002</v>
+        <v>0.8121651451941891</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2410,100 +2422,100 @@
         <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9998752065146239</v>
+        <v>0.9998908182674044</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-120.7452217488702</v>
+        <v>-124.7305232386064</v>
       </c>
       <c r="AA8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="AB8">
-        <v>-0.5112214130575213</v>
+        <v>-0.5697174242557334</v>
       </c>
       <c r="AC8">
-        <v>-0.8594490484208306</v>
+        <v>-0.8218406515252289</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AH8">
-        <v>-0.511157615955587</v>
+        <v>-0.5696552215202633</v>
       </c>
       <c r="AI8">
-        <v>0.8431946044942086</v>
+        <v>0.8617887040323801</v>
       </c>
       <c r="AJ8">
-        <v>-1.380707035153005</v>
+        <v>-1.523950601975966</v>
       </c>
       <c r="AK8">
-        <v>-2.449850074260372</v>
+        <v>-2.301406853944384</v>
       </c>
       <c r="AL8">
-        <v>-2.550765209518937</v>
+        <v>-2.652459802625317</v>
       </c>
       <c r="AM8">
-        <v>1.908526650114289</v>
+        <v>2.408154409026348</v>
       </c>
       <c r="AN8">
-        <v>2.300377809545366</v>
+        <v>2.365246036986357</v>
       </c>
       <c r="AO8">
-        <v>0.06752094468777455</v>
+        <v>0.06058873091954324</v>
       </c>
       <c r="AP8">
-        <v>0.69546</v>
+        <v>0.693995</v>
       </c>
       <c r="AQ8">
-        <v>0.6878222039864111</v>
+        <v>0.6852026673757073</v>
       </c>
       <c r="AR8">
-        <v>0.6949712620086721</v>
+        <v>0.6922166340055864</v>
       </c>
       <c r="AS8">
-        <v>0.69546</v>
+        <v>0.693995</v>
       </c>
       <c r="AT8">
-        <v>0.6707749999999999</v>
+        <v>0.667845</v>
       </c>
       <c r="AU8">
-        <v>0.6878222039864111</v>
+        <v>0.6852026673757073</v>
       </c>
       <c r="AV8">
-        <v>0.70266875</v>
+        <v>0.701465</v>
       </c>
       <c r="AW8">
-        <v>-0.01098236564804421</v>
+        <v>-0.0126691584583357</v>
       </c>
       <c r="AX8">
-        <v>1.059517393943319</v>
+        <v>1.177019092944147</v>
       </c>
       <c r="AY8">
-        <v>0.01098236564804421</v>
+        <v>0.0126691584583357</v>
       </c>
       <c r="AZ8">
-        <v>0.5004989606275069</v>
+        <v>0.497614044791887</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.2995010393724932</v>
+        <v>0.302385955208113</v>
       </c>
       <c r="BC8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2512,58 +2524,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>410.6883288542742</v>
+        <v>431.991879374354</v>
       </c>
       <c r="BG8">
-        <v>0.01036544157823589</v>
+        <v>0.01076376630955543</v>
       </c>
       <c r="BH8">
-        <v>48237.21172186625</v>
+        <v>46452.14190093757</v>
       </c>
       <c r="BI8">
-        <v>39620.91974128612</v>
+        <v>40133.89616150039</v>
       </c>
       <c r="BJ8">
-        <v>56970.81031444817</v>
+        <v>57830.23820272536</v>
       </c>
       <c r="BK8">
-        <v>396.2091974128613</v>
+        <v>401.3389616150039</v>
       </c>
       <c r="BL8">
-        <v>0.003962091974128613</v>
+        <v>0.004013389616150039</v>
       </c>
       <c r="BM8">
-        <v>410.6883288542743</v>
+        <v>431.9918793743539</v>
       </c>
       <c r="BN8">
-        <v>0.004106883288542743</v>
+        <v>0.004319918793743539</v>
       </c>
       <c r="BO8">
-        <v>0.01012146669265816</v>
+        <v>0.01103123257524498</v>
       </c>
       <c r="BP8">
-        <v>0.01519203330548107</v>
+        <v>0.01623739133446996</v>
       </c>
       <c r="BQ8">
-        <v>0.01518974121666016</v>
+        <v>0.01601733385130864</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU8" t="s">
         <v>91</v>
       </c>
       <c r="BV8" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW8" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2571,7 +2583,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2595,19 +2607,19 @@
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>2.48292018664256</v>
+        <v>2.679185503841806</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" t="s">
         <v>94</v>
@@ -2619,16 +2631,16 @@
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T9">
-        <v>-0.9063526665320979</v>
+        <v>-0.8835016086238986</v>
       </c>
       <c r="U9">
-        <v>0.9578006969677269</v>
+        <v>0.9475566658037164</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
@@ -2637,100 +2649,100 @@
         <v>94</v>
       </c>
       <c r="X9">
-        <v>0.9997679881131314</v>
+        <v>0.9999237676918484</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-144.3589612871395</v>
+        <v>-140.0847447279974</v>
       </c>
       <c r="AA9">
-        <v>-17</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB9">
-        <v>-0.8126836007274972</v>
+        <v>-0.7669943356294604</v>
       </c>
       <c r="AC9">
-        <v>-0.5827052128723321</v>
+        <v>-0.6416538701763769</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
       </c>
       <c r="AE9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AH9">
-        <v>-0.8124950484718653</v>
+        <v>-0.7669358658809162</v>
       </c>
       <c r="AI9">
-        <v>0.9365796182124053</v>
+        <v>0.9224527554252537</v>
       </c>
       <c r="AJ9">
-        <v>-1.893505965617223</v>
+        <v>-2.012734723500569</v>
       </c>
       <c r="AK9">
-        <v>-1.467101241271337</v>
+        <v>-1.717633643535347</v>
       </c>
       <c r="AL9">
-        <v>-3.056251015761235</v>
+        <v>-3.419068369064508</v>
       </c>
       <c r="AM9">
-        <v>3.205348086151252</v>
+        <v>2.732463485735718</v>
       </c>
       <c r="AN9">
-        <v>2.728059091268482</v>
+        <v>3.1331921734011</v>
       </c>
       <c r="AO9">
-        <v>0.04762838563626552</v>
+        <v>0.05079242637154264</v>
       </c>
       <c r="AP9">
-        <v>1.130685</v>
+        <v>1.12296</v>
       </c>
       <c r="AQ9">
-        <v>1.118047963187125</v>
+        <v>1.104321861676361</v>
       </c>
       <c r="AR9">
-        <v>1.12707850403741</v>
+        <v>1.110612651799884</v>
       </c>
       <c r="AS9">
-        <v>1.130685</v>
+        <v>1.12296</v>
       </c>
       <c r="AT9">
-        <v>1.100025</v>
+        <v>1.084575</v>
       </c>
       <c r="AU9">
-        <v>1.118047963187125</v>
+        <v>1.104321861676361</v>
       </c>
       <c r="AV9">
-        <v>1.141045</v>
+        <v>1.135385425549093</v>
       </c>
       <c r="AW9">
-        <v>-0.01117644331787769</v>
+        <v>-0.01659733055820276</v>
       </c>
       <c r="AX9">
-        <v>1.219791198153908</v>
+        <v>1.5</v>
       </c>
       <c r="AY9">
-        <v>0.01117644331787769</v>
+        <v>0.01659733055820276</v>
       </c>
       <c r="AZ9">
-        <v>0.4395350476848701</v>
+        <v>0.4635541549263026</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3604649523151299</v>
+        <v>0.3364458450736974</v>
       </c>
       <c r="BC9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2742,55 +2754,55 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.009162587281161452</v>
+        <v>0.01106488703880184</v>
       </c>
       <c r="BH9">
-        <v>54569.7393822392</v>
+        <v>45187.98956072692</v>
       </c>
       <c r="BI9">
-        <v>54569.7393822392</v>
+        <v>45187.98956072692</v>
       </c>
       <c r="BJ9">
-        <v>48262.5482625481</v>
+        <v>40240.07049291775</v>
       </c>
       <c r="BK9">
-        <v>545.697393822392</v>
+        <v>451.8798956072692</v>
       </c>
       <c r="BL9">
-        <v>0.00545697393822392</v>
+        <v>0.004518798956072692</v>
       </c>
       <c r="BM9">
-        <v>500.0000000000001</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN9">
-        <v>0.005000000000000001</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO9">
-        <v>0.02055850205318315</v>
+        <v>0.01996590170568829</v>
       </c>
       <c r="BP9">
-        <v>0.01891201963655544</v>
+        <v>0.02468023571794847</v>
       </c>
       <c r="BQ9">
-        <v>0.01537203738301346</v>
+        <v>0.01986855853101914</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU9" t="s">
         <v>91</v>
       </c>
       <c r="BV9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW9" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2798,7 +2810,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2822,19 +2834,19 @@
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>2.705070514113462</v>
+        <v>2.857204220469094</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O10" t="s">
         <v>94</v>
@@ -2846,16 +2858,16 @@
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T10">
-        <v>-0.9537670107020406</v>
+        <v>-0.9372718221868184</v>
       </c>
       <c r="U10">
-        <v>0.9791527777605064</v>
+        <v>0.9717498527387396</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
@@ -2864,100 +2876,100 @@
         <v>94</v>
       </c>
       <c r="X10">
-        <v>0.999830491778352</v>
+        <v>0.9999101310186854</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-155.1656961041744</v>
+        <v>-150.990345926623</v>
       </c>
       <c r="AA10">
-        <v>-16</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB10">
-        <v>-0.9075261832036445</v>
+        <v>-0.8745380065495315</v>
       </c>
       <c r="AC10">
-        <v>-0.419995508071009</v>
+        <v>-0.4849569827318414</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
       </c>
       <c r="AE10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AH10">
-        <v>-0.9073723500542307</v>
+        <v>-0.874459412709762</v>
       </c>
       <c r="AI10">
-        <v>0.9657125306530133</v>
+        <v>0.9553502360627675</v>
       </c>
       <c r="AJ10">
-        <v>-2.057925361683973</v>
+        <v>-2.145904883336818</v>
       </c>
       <c r="AK10">
-        <v>-1.036690202182976</v>
+        <v>-1.222741549119324</v>
       </c>
       <c r="AL10">
-        <v>-3.355195142784461</v>
+        <v>-3.654036973284544</v>
       </c>
       <c r="AM10">
-        <v>3.372322007769957</v>
+        <v>2.911302453698565</v>
       </c>
       <c r="AN10">
-        <v>3.022937930816534</v>
+        <v>3.361581629454079</v>
       </c>
       <c r="AO10">
-        <v>0.04323997620335489</v>
+        <v>0.04653141172421118</v>
       </c>
       <c r="AP10">
-        <v>7.5995</v>
+        <v>7.5463</v>
       </c>
       <c r="AQ10">
-        <v>7.479529156217189</v>
+        <v>7.406232341919727</v>
       </c>
       <c r="AR10">
-        <v>7.484993193572257</v>
+        <v>7.421931817818645</v>
       </c>
       <c r="AS10">
-        <v>7.5995</v>
+        <v>7.5463</v>
       </c>
       <c r="AT10">
-        <v>7.4091</v>
+        <v>7.302699999999999</v>
       </c>
       <c r="AU10">
-        <v>7.479529156217189</v>
+        <v>7.406232341919727</v>
       </c>
       <c r="AV10">
-        <v>7.679480562521874</v>
+        <v>7.639678438720181</v>
       </c>
       <c r="AW10">
-        <v>-0.01578667593694468</v>
+        <v>-0.01856110386285626</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01578667593694468</v>
+        <v>0.01856110386285626</v>
       </c>
       <c r="AZ10">
-        <v>0.4262458159227343</v>
+        <v>0.4597123731108294</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3737541840772657</v>
+        <v>0.3402876268891706</v>
       </c>
       <c r="BC10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2969,55 +2981,55 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01052445062462979</v>
+        <v>0.01237406924190418</v>
       </c>
       <c r="BH10">
-        <v>47508.41804795757</v>
+        <v>40407.07953263868</v>
       </c>
       <c r="BI10">
-        <v>47508.41804795757</v>
+        <v>40407.07953263868</v>
       </c>
       <c r="BJ10">
-        <v>6251.51892202876</v>
+        <v>5354.555150555727</v>
       </c>
       <c r="BK10">
-        <v>475.0841804795757</v>
+        <v>404.0707953263868</v>
       </c>
       <c r="BL10">
-        <v>0.004750841804795757</v>
+        <v>0.004040707953263868</v>
       </c>
       <c r="BM10">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN10">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.1174122215908453</v>
+        <v>0.1127723470934458</v>
       </c>
       <c r="BP10">
-        <v>0.1103279690110938</v>
+        <v>0.1522875669610324</v>
       </c>
       <c r="BQ10">
-        <v>0.07661988462949135</v>
+        <v>0.1086609465292724</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU10" t="s">
         <v>91</v>
       </c>
       <c r="BV10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW10" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3025,7 +3037,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3049,19 +3061,19 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.184094117988854</v>
+        <v>1.199086584005827</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" t="s">
         <v>94</v>
@@ -3073,16 +3085,16 @@
         <v>0.75</v>
       </c>
       <c r="R11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T11">
-        <v>-0.8035130852316634</v>
+        <v>-0.8009341781493173</v>
       </c>
       <c r="U11">
-        <v>0.7615723161265613</v>
+        <v>0.7604161503618175</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
@@ -3091,100 +3103,100 @@
         <v>94</v>
       </c>
       <c r="X11">
-        <v>0.9999657110892508</v>
+        <v>0.999983080778499</v>
       </c>
       <c r="Y11">
-        <v>0.2858700109977305</v>
+        <v>0.329685621292421</v>
       </c>
       <c r="Z11">
-        <v>-123.778093395207</v>
+        <v>-124.2504419493343</v>
       </c>
       <c r="AA11">
-        <v>-7.999999999999998</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB11">
-        <v>-0.5559778542657846</v>
+        <v>-0.5628113035543927</v>
       </c>
       <c r="AC11">
-        <v>-0.8311971039206127</v>
+        <v>-0.8265854079231045</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
       </c>
       <c r="AE11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AH11">
-        <v>-0.3574453679570265</v>
+        <v>-0.3741747180665119</v>
       </c>
       <c r="AI11">
-        <v>0.7141599891641723</v>
+        <v>0.7261714516087068</v>
       </c>
       <c r="AJ11">
-        <v>-0.863648980598598</v>
+        <v>-0.8978914120511587</v>
       </c>
       <c r="AK11">
-        <v>-1.336363537718617</v>
+        <v>-1.347389051822805</v>
       </c>
       <c r="AL11">
-        <v>-1.621296341443538</v>
+        <v>-1.544103667012919</v>
       </c>
       <c r="AM11">
-        <v>0.8466860714347184</v>
+        <v>1.272710087346403</v>
       </c>
       <c r="AN11">
-        <v>1.50767916435789</v>
+        <v>1.396927745736445</v>
       </c>
       <c r="AO11">
-        <v>0.06530245464231241</v>
+        <v>0.05735427992379936</v>
       </c>
       <c r="AP11">
-        <v>4182.79</v>
+        <v>4180.43</v>
       </c>
       <c r="AQ11">
-        <v>4083.666873774167</v>
+        <v>4080.404562058218</v>
       </c>
       <c r="AR11">
-        <v>4228.628324825712</v>
+        <v>4226.132137089084</v>
       </c>
       <c r="AS11">
-        <v>4182.79</v>
+        <v>4180.43</v>
       </c>
       <c r="AT11">
-        <v>3935.280000000001</v>
+        <v>3930.560000000001</v>
       </c>
       <c r="AU11">
-        <v>4083.666873774167</v>
+        <v>4080.404562058218</v>
       </c>
       <c r="AV11">
-        <v>4312.655</v>
+        <v>4310.295</v>
       </c>
       <c r="AW11">
-        <v>-0.02369784909733276</v>
+        <v>-0.02392706921100987</v>
       </c>
       <c r="AX11">
-        <v>0.7632782214286572</v>
+        <v>0.7702262960904176</v>
       </c>
       <c r="AY11">
-        <v>0.02369784909733276</v>
+        <v>0.02392706921100987</v>
       </c>
       <c r="AZ11">
-        <v>0.3370902964348517</v>
+        <v>0.3378889601766373</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4629097035651483</v>
+        <v>0.4621110398233628</v>
       </c>
       <c r="BC11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3196,22 +3208,22 @@
         <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.03104745875360702</v>
+        <v>0.03106498613778963</v>
       </c>
       <c r="BH11">
-        <v>16104.37762291612</v>
+        <v>16095.29126400494</v>
       </c>
       <c r="BI11">
-        <v>12078.28321718709</v>
+        <v>12071.46844800371</v>
       </c>
       <c r="BJ11">
         <v>2.887614060755402</v>
       </c>
       <c r="BK11">
-        <v>120.7828321718709</v>
+        <v>120.7146844800371</v>
       </c>
       <c r="BL11">
-        <v>0.001207828321718709</v>
+        <v>0.001207146844800371</v>
       </c>
       <c r="BM11">
         <v>375</v>
@@ -3220,31 +3232,31 @@
         <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>583.6159500412928</v>
+        <v>585.4463833422634</v>
       </c>
       <c r="BP11">
-        <v>151.9030217894891</v>
+        <v>153.8863138746162</v>
       </c>
       <c r="BQ11">
-        <v>88.85490573226802</v>
+        <v>90.58950203340144</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05477037382902145</v>
+        <v>0.05547092301716239</v>
       </c>
       <c r="BT11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BU11" t="s">
         <v>91</v>
       </c>
       <c r="BV11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BW11" s="2">
-        <v>46324</v>
+        <v>46325</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -364,34 +364,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.01549,naive=0.007894,drift4=0.007732; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=2.714,naive=2.464,drift4=4.569; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04491,naive=0.01891,drift4=0.02598; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.1478,naive=0.1277,drift4=0.07807; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.0266,naive=0.02144,drift4=0.01703; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.06393,naive=0.1067,drift4=0.09407; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.01103,naive=0.01624,drift4=0.01602; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01997,naive=0.02468,drift4=0.01987; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.1128,naive=0.1523,drift4=0.1087; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=585.4,naive=153.9,drift4=90.59; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.01542,naive=0.007423,drift4=0.007414; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=2.707,naive=2.331,drift4=4.35; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04377,naive=0.01924,drift4=0.02565; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1411,naive=0.1227,drift4=0.0722; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.02592,naive=0.02066,drift4=0.01607; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.06014,naive=0.1049,drift4=0.08954; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.01052,naive=0.01596,drift4=0.01529; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01952,naive=0.02424,drift4=0.019; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.1052,naive=0.1497,drift4=0.1043; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=593.4,naive=154.1,drift4=82.34; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -994,7 +994,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1117,10 +1117,10 @@
         <v>0.826435</v>
       </c>
       <c r="AQ2">
-        <v>0.8349696568410131</v>
+        <v>0.8350334122308836</v>
       </c>
       <c r="AR2">
-        <v>0.8317190033401873</v>
+        <v>0.8318201893627784</v>
       </c>
       <c r="AS2">
         <v>0.826435</v>
@@ -1129,28 +1129,28 @@
         <v>0.8428550000000001</v>
       </c>
       <c r="AU2">
-        <v>0.8349696568410131</v>
+        <v>0.8350334122308836</v>
       </c>
       <c r="AV2">
         <v>0.8188550000000001</v>
       </c>
       <c r="AW2">
-        <v>0.01032707574220969</v>
+        <v>0.01040422081698323</v>
       </c>
       <c r="AX2">
-        <v>1.125944174276142</v>
+        <v>1.134355175578315</v>
       </c>
       <c r="AY2">
-        <v>0.01032707574220969</v>
+        <v>0.01040422081698323</v>
       </c>
       <c r="AZ2">
-        <v>0.4131954507127501</v>
+        <v>0.4112066729818429</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3868045492872498</v>
+        <v>0.388793327018157</v>
       </c>
       <c r="BC2" t="s">
         <v>116</v>
@@ -1189,19 +1189,19 @@
         <v>0.005</v>
       </c>
       <c r="BO2">
-        <v>0.01548532872769406</v>
+        <v>0.01542405003386405</v>
       </c>
       <c r="BP2">
-        <v>0.007894167149506309</v>
+        <v>0.007423250344803028</v>
       </c>
       <c r="BQ2">
-        <v>0.007731639913840072</v>
+        <v>0.007413939653829339</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT2" t="s">
         <v>126</v>
@@ -1213,7 +1213,7 @@
         <v>127</v>
       </c>
       <c r="BW2" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1221,7 +1221,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1344,10 +1344,10 @@
         <v>157.6555</v>
       </c>
       <c r="AQ3">
-        <v>158.8684935872391</v>
+        <v>158.8452398268254</v>
       </c>
       <c r="AR3">
-        <v>159.1009716676874</v>
+        <v>159.0538086512412</v>
       </c>
       <c r="AS3">
         <v>157.6555</v>
@@ -1356,28 +1356,28 @@
         <v>159.297</v>
       </c>
       <c r="AU3">
-        <v>158.8684935872391</v>
+        <v>158.8452398268254</v>
       </c>
       <c r="AV3">
         <v>156.157375</v>
       </c>
       <c r="AW3">
-        <v>0.007693950336265719</v>
+        <v>0.007546453037321533</v>
       </c>
       <c r="AX3">
-        <v>0.8096744845984996</v>
+        <v>0.7941525752693749</v>
       </c>
       <c r="AY3">
-        <v>0.007693950336265719</v>
+        <v>0.007546453037321533</v>
       </c>
       <c r="AZ3">
-        <v>0.5111833150786086</v>
+        <v>0.5076667973785483</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.2888166849213915</v>
+        <v>0.2923332026214518</v>
       </c>
       <c r="BC3" t="s">
         <v>117</v>
@@ -1416,19 +1416,19 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>2.714003218867912</v>
+        <v>2.707473145983308</v>
       </c>
       <c r="BP3">
-        <v>2.463672355706823</v>
+        <v>2.331411422452795</v>
       </c>
       <c r="BQ3">
-        <v>4.569272956396243</v>
+        <v>4.350387180020063</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT3" t="s">
         <v>126</v>
@@ -1440,7 +1440,7 @@
         <v>127</v>
       </c>
       <c r="BW3" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1448,7 +1448,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1571,10 +1571,10 @@
         <v>6.707825</v>
       </c>
       <c r="AQ4">
-        <v>6.727488694656001</v>
+        <v>6.727381246380099</v>
       </c>
       <c r="AR4">
-        <v>6.752987456069103</v>
+        <v>6.752733249971111</v>
       </c>
       <c r="AS4">
         <v>6.707825</v>
@@ -1583,28 +1583,28 @@
         <v>6.708364999999999</v>
       </c>
       <c r="AU4">
-        <v>6.727488694656001</v>
+        <v>6.727381246380099</v>
       </c>
       <c r="AV4">
         <v>6.68431875</v>
       </c>
       <c r="AW4">
-        <v>0.002931456121172153</v>
+        <v>0.002915437773063417</v>
       </c>
       <c r="AX4">
-        <v>0.8365304825738651</v>
+        <v>0.8319594312193326</v>
       </c>
       <c r="AY4">
-        <v>0.002931456121172153</v>
+        <v>0.002915437773063417</v>
       </c>
       <c r="AZ4">
-        <v>0.4309869144409747</v>
+        <v>0.4310344986009579</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3690130855590253</v>
+        <v>0.3689655013990421</v>
       </c>
       <c r="BC4" t="s">
         <v>118</v>
@@ -1643,19 +1643,19 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.04490838928174511</v>
+        <v>0.04377480298376337</v>
       </c>
       <c r="BP4">
-        <v>0.0189131590017995</v>
+        <v>0.01924087341663613</v>
       </c>
       <c r="BQ4">
-        <v>0.025983599551301</v>
+        <v>0.02564535052303343</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT4" t="s">
         <v>126</v>
@@ -1667,7 +1667,7 @@
         <v>127</v>
       </c>
       <c r="BW4" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1675,7 +1675,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1699,19 +1699,19 @@
         <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1.627240488486849</v>
+        <v>1.570244421407061</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O5" t="s">
         <v>94</v>
@@ -1729,10 +1729,10 @@
         <v>104</v>
       </c>
       <c r="T5">
-        <v>-0.9940211326421459</v>
+        <v>-0.9962572872601604</v>
       </c>
       <c r="U5">
-        <v>0.9971626583140305</v>
+        <v>0.9982219692857099</v>
       </c>
       <c r="V5" t="s">
         <v>93</v>
@@ -1741,22 +1741,22 @@
         <v>94</v>
       </c>
       <c r="X5">
-        <v>0.9994125945002593</v>
+        <v>0.999624760074551</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-171.1292623209555</v>
+        <v>-172.9845108296907</v>
       </c>
       <c r="AA5">
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="AB5">
-        <v>-0.9880387512005313</v>
+        <v>-0.9925131695778808</v>
       </c>
       <c r="AC5">
-        <v>-0.1542057914803935</v>
+        <v>-0.122137660917789</v>
       </c>
       <c r="AD5" t="s">
         <v>93</v>
@@ -1771,37 +1771,37 @@
         <v>114</v>
       </c>
       <c r="AH5">
-        <v>-0.9874583718041192</v>
+        <v>-0.9921407390101213</v>
       </c>
       <c r="AI5">
-        <v>0.9905963388632689</v>
+        <v>0.9923127082335879</v>
       </c>
       <c r="AJ5">
-        <v>-1.277873527068895</v>
+        <v>-1.246160489784905</v>
       </c>
       <c r="AK5">
-        <v>-0.2709725081015805</v>
+        <v>-0.2061656177606775</v>
       </c>
       <c r="AL5">
-        <v>-1.843404713991136</v>
+        <v>-1.722603599910343</v>
       </c>
       <c r="AM5">
-        <v>2.5773153998553</v>
+        <v>2.679459988838541</v>
       </c>
       <c r="AN5">
-        <v>1.609260271222911</v>
+        <v>1.484448322388167</v>
       </c>
       <c r="AO5">
-        <v>0.03739796381320831</v>
+        <v>0.03539939110579538</v>
       </c>
       <c r="AP5">
         <v>8.860749999999999</v>
       </c>
       <c r="AQ5">
-        <v>8.790977784891592</v>
+        <v>8.790976546854722</v>
       </c>
       <c r="AR5">
-        <v>8.890809715407702</v>
+        <v>8.892627315578657</v>
       </c>
       <c r="AS5">
         <v>8.860749999999999</v>
@@ -1810,28 +1810,28 @@
         <v>8.651749999999998</v>
       </c>
       <c r="AU5">
-        <v>8.790977784891592</v>
+        <v>8.790976546854722</v>
       </c>
       <c r="AV5">
         <v>8.9309625</v>
       </c>
       <c r="AW5">
-        <v>-0.007874301284700271</v>
+        <v>-0.007874441006153813</v>
       </c>
       <c r="AX5">
-        <v>0.9937292520335919</v>
+        <v>0.9937468847467051</v>
       </c>
       <c r="AY5">
-        <v>0.007874301284700271</v>
+        <v>0.007874441006153813</v>
       </c>
       <c r="AZ5">
-        <v>0.4075458080648772</v>
+        <v>0.4044654293023725</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3924541919351229</v>
+        <v>0.3955345706976274</v>
       </c>
       <c r="BC5" t="s">
         <v>119</v>
@@ -1870,19 +1870,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.1477755314743206</v>
+        <v>0.141093140256222</v>
       </c>
       <c r="BP5">
-        <v>0.1277296930196652</v>
+        <v>0.1226892281164322</v>
       </c>
       <c r="BQ5">
-        <v>0.07806579320859676</v>
+        <v>0.07220346322129705</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT5" t="s">
         <v>126</v>
@@ -1894,7 +1894,7 @@
         <v>127</v>
       </c>
       <c r="BW5" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1902,7 +1902,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -2025,10 +2025,10 @@
         <v>1.32041</v>
       </c>
       <c r="AQ6">
-        <v>1.307555618164289</v>
+        <v>1.307494887574405</v>
       </c>
       <c r="AR6">
-        <v>1.317711914353102</v>
+        <v>1.317759401826194</v>
       </c>
       <c r="AS6">
         <v>1.32041</v>
@@ -2037,28 +2037,28 @@
         <v>1.28905</v>
       </c>
       <c r="AU6">
-        <v>1.307555618164289</v>
+        <v>1.307494887574405</v>
       </c>
       <c r="AV6">
         <v>1.3335725</v>
       </c>
       <c r="AW6">
-        <v>-0.009735144262547806</v>
+        <v>-0.009781137999253901</v>
       </c>
       <c r="AX6">
-        <v>0.976591212589613</v>
+        <v>0.9812051225523173</v>
       </c>
       <c r="AY6">
-        <v>0.009735144262547806</v>
+        <v>0.009781137999253901</v>
       </c>
       <c r="AZ6">
-        <v>0.4268248803473757</v>
+        <v>0.4240035249811095</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3731751196526242</v>
+        <v>0.3759964750188905</v>
       </c>
       <c r="BC6" t="s">
         <v>120</v>
@@ -2097,19 +2097,19 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.02660213945007981</v>
+        <v>0.0259177672501914</v>
       </c>
       <c r="BP6">
-        <v>0.02143610497483248</v>
+        <v>0.02065659645761009</v>
       </c>
       <c r="BQ6">
-        <v>0.0170288967832171</v>
+        <v>0.01606990663690898</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT6" t="s">
         <v>126</v>
@@ -2121,7 +2121,7 @@
         <v>127</v>
       </c>
       <c r="BW6" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2129,7 +2129,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2153,19 +2153,19 @@
         <v>93</v>
       </c>
       <c r="J7" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1.436117214086973</v>
+        <v>1.463615183089874</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O7" t="s">
         <v>94</v>
@@ -2183,10 +2183,10 @@
         <v>105</v>
       </c>
       <c r="T7">
-        <v>-0.8324927566148754</v>
+        <v>-0.8450594482724709</v>
       </c>
       <c r="U7">
-        <v>0.9246058751830176</v>
+        <v>0.9302633338376369</v>
       </c>
       <c r="V7" t="s">
         <v>93</v>
@@ -2195,22 +2195,22 @@
         <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9999365388252949</v>
+        <v>0.9999463284600998</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-131.6803984646848</v>
+        <v>-133.6388628858862</v>
       </c>
       <c r="AA7">
-        <v>-10</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB7">
-        <v>-0.6649748823486659</v>
+        <v>-0.6901105802005867</v>
       </c>
       <c r="AC7">
-        <v>-0.7468657214288108</v>
+        <v>-0.72370393607829</v>
       </c>
       <c r="AD7" t="s">
         <v>93</v>
@@ -2225,37 +2225,37 @@
         <v>115</v>
       </c>
       <c r="AH7">
-        <v>-0.6649326822614826</v>
+        <v>-0.6900735409030458</v>
       </c>
       <c r="AI7">
-        <v>0.8907932093356834</v>
+        <v>0.899352430585687</v>
       </c>
       <c r="AJ7">
-        <v>-1.058581563827818</v>
+        <v>-1.106432633112826</v>
       </c>
       <c r="AK7">
-        <v>-1.237913132438912</v>
+        <v>-1.199374953179614</v>
       </c>
       <c r="AL7">
-        <v>-1.927592862822559</v>
+        <v>-1.849504232112959</v>
       </c>
       <c r="AM7">
-        <v>1.362787785936421</v>
+        <v>1.904964899468453</v>
       </c>
       <c r="AN7">
-        <v>1.764276295525329</v>
+        <v>1.640925519332009</v>
       </c>
       <c r="AO7">
-        <v>0.05784695971846391</v>
+        <v>0.05107972290349189</v>
       </c>
       <c r="AP7">
         <v>4.65158</v>
       </c>
       <c r="AQ7">
-        <v>4.600494737305521</v>
+        <v>4.600515737072323</v>
       </c>
       <c r="AR7">
-        <v>4.657655485483788</v>
+        <v>4.657346242940257</v>
       </c>
       <c r="AS7">
         <v>4.65158</v>
@@ -2264,28 +2264,28 @@
         <v>4.47213</v>
       </c>
       <c r="AU7">
-        <v>4.600494737305521</v>
+        <v>4.600515737072323</v>
       </c>
       <c r="AV7">
         <v>4.69478</v>
       </c>
       <c r="AW7">
-        <v>-0.01098234636284426</v>
+        <v>-0.01097783181793653</v>
       </c>
       <c r="AX7">
-        <v>1.182529229038877</v>
+        <v>1.182043123325869</v>
       </c>
       <c r="AY7">
-        <v>0.01098234636284426</v>
+        <v>0.01097783181793653</v>
       </c>
       <c r="AZ7">
-        <v>0.4984476233245135</v>
+        <v>0.4993932260150525</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3015523766754865</v>
+        <v>0.3006067739849475</v>
       </c>
       <c r="BC7" t="s">
         <v>121</v>
@@ -2324,19 +2324,19 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO7">
-        <v>0.06392813720795297</v>
+        <v>0.06014176790331476</v>
       </c>
       <c r="BP7">
-        <v>0.1066584905580932</v>
+        <v>0.1049429184638299</v>
       </c>
       <c r="BQ7">
-        <v>0.09406755710042691</v>
+        <v>0.08953831221253236</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT7" t="s">
         <v>126</v>
@@ -2348,7 +2348,7 @@
         <v>127</v>
       </c>
       <c r="BW7" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2356,7 +2356,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2479,10 +2479,10 @@
         <v>0.693995</v>
       </c>
       <c r="AQ8">
-        <v>0.6852026673757073</v>
+        <v>0.68517058311831</v>
       </c>
       <c r="AR8">
-        <v>0.6922166340055864</v>
+        <v>0.6921517593755507</v>
       </c>
       <c r="AS8">
         <v>0.693995</v>
@@ -2491,28 +2491,28 @@
         <v>0.667845</v>
       </c>
       <c r="AU8">
-        <v>0.6852026673757073</v>
+        <v>0.68517058311831</v>
       </c>
       <c r="AV8">
         <v>0.701465</v>
       </c>
       <c r="AW8">
-        <v>-0.0126691584583357</v>
+        <v>-0.01271538970985382</v>
       </c>
       <c r="AX8">
-        <v>1.177019092944147</v>
+        <v>1.181314174255702</v>
       </c>
       <c r="AY8">
-        <v>0.0126691584583357</v>
+        <v>0.01271538970985382</v>
       </c>
       <c r="AZ8">
-        <v>0.497614044791887</v>
+        <v>0.4976222017681398</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.302385955208113</v>
+        <v>0.3023777982318603</v>
       </c>
       <c r="BC8" t="s">
         <v>122</v>
@@ -2551,19 +2551,19 @@
         <v>0.004319918793743539</v>
       </c>
       <c r="BO8">
-        <v>0.01103123257524498</v>
+        <v>0.01051673906935029</v>
       </c>
       <c r="BP8">
-        <v>0.01623739133446996</v>
+        <v>0.01595618770451222</v>
       </c>
       <c r="BQ8">
-        <v>0.01601733385130864</v>
+        <v>0.0152876209644398</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT8" t="s">
         <v>126</v>
@@ -2575,7 +2575,7 @@
         <v>127</v>
       </c>
       <c r="BW8" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2583,7 +2583,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2706,10 +2706,10 @@
         <v>1.12296</v>
       </c>
       <c r="AQ9">
-        <v>1.104321861676361</v>
+        <v>1.104386263084863</v>
       </c>
       <c r="AR9">
-        <v>1.110612651799884</v>
+        <v>1.110874523014808</v>
       </c>
       <c r="AS9">
         <v>1.12296</v>
@@ -2718,28 +2718,28 @@
         <v>1.084575</v>
       </c>
       <c r="AU9">
-        <v>1.104321861676361</v>
+        <v>1.104386263084863</v>
       </c>
       <c r="AV9">
-        <v>1.135385425549093</v>
+        <v>1.135342491276758</v>
       </c>
       <c r="AW9">
-        <v>-0.01659733055820276</v>
+        <v>-0.01653998086765095</v>
       </c>
       <c r="AX9">
         <v>1.5</v>
       </c>
       <c r="AY9">
-        <v>0.01659733055820276</v>
+        <v>0.01653998086765095</v>
       </c>
       <c r="AZ9">
-        <v>0.4635541549263026</v>
+        <v>0.4613871923848443</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3364458450736974</v>
+        <v>0.3386128076151557</v>
       </c>
       <c r="BC9" t="s">
         <v>123</v>
@@ -2754,43 +2754,43 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.01106488703880184</v>
+        <v>0.0110266539117673</v>
       </c>
       <c r="BH9">
-        <v>45187.98956072692</v>
+        <v>45344.671556837</v>
       </c>
       <c r="BI9">
-        <v>45187.98956072692</v>
+        <v>45344.671556837</v>
       </c>
       <c r="BJ9">
-        <v>40240.07049291775</v>
+        <v>40379.59638530046</v>
       </c>
       <c r="BK9">
-        <v>451.8798956072692</v>
+        <v>453.44671556837</v>
       </c>
       <c r="BL9">
-        <v>0.004518798956072692</v>
+        <v>0.0045344671556837</v>
       </c>
       <c r="BM9">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="BN9">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.01996590170568829</v>
+        <v>0.01952366480548363</v>
       </c>
       <c r="BP9">
-        <v>0.02468023571794847</v>
+        <v>0.02424060672985473</v>
       </c>
       <c r="BQ9">
-        <v>0.01986855853101914</v>
+        <v>0.01900069501469215</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT9" t="s">
         <v>126</v>
@@ -2802,7 +2802,7 @@
         <v>127</v>
       </c>
       <c r="BW9" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2810,7 +2810,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2834,19 +2834,19 @@
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>2.857204220469094</v>
+        <v>3.1134405973988</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O10" t="s">
         <v>94</v>
@@ -2864,10 +2864,10 @@
         <v>105</v>
       </c>
       <c r="T10">
-        <v>-0.9372718221868184</v>
+        <v>-0.9179262337987019</v>
       </c>
       <c r="U10">
-        <v>0.9717498527387396</v>
+        <v>0.9630490710525563</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
@@ -2876,22 +2876,22 @@
         <v>94</v>
       </c>
       <c r="X10">
-        <v>0.9999101310186854</v>
+        <v>0.9999290633725623</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-150.990345926623</v>
+        <v>-146.7040998612845</v>
       </c>
       <c r="AA10">
-        <v>-5.999999999999996</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>-0.8745380065495315</v>
+        <v>-0.8358466451482032</v>
       </c>
       <c r="AC10">
-        <v>-0.4849569827318414</v>
+        <v>-0.548963009495625</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
@@ -2906,37 +2906,37 @@
         <v>115</v>
       </c>
       <c r="AH10">
-        <v>-0.874459412709762</v>
+        <v>-0.8357873530061413</v>
       </c>
       <c r="AI10">
-        <v>0.9553502360627675</v>
+        <v>0.9438551948879159</v>
       </c>
       <c r="AJ10">
-        <v>-2.145904883336818</v>
+        <v>-2.350144667876241</v>
       </c>
       <c r="AK10">
-        <v>-1.222741549119324</v>
+        <v>-1.543515783805872</v>
       </c>
       <c r="AL10">
-        <v>-3.654036973284544</v>
+        <v>-3.933391754439335</v>
       </c>
       <c r="AM10">
-        <v>2.911302453698565</v>
+        <v>3.431344064360473</v>
       </c>
       <c r="AN10">
-        <v>3.361581629454079</v>
+        <v>3.588006011818242</v>
       </c>
       <c r="AO10">
-        <v>0.04653141172421118</v>
+        <v>0.04582647224627837</v>
       </c>
       <c r="AP10">
         <v>7.5463</v>
       </c>
       <c r="AQ10">
-        <v>7.406232341919727</v>
+        <v>7.406769729557718</v>
       </c>
       <c r="AR10">
-        <v>7.421931817818645</v>
+        <v>7.422469825340755</v>
       </c>
       <c r="AS10">
         <v>7.5463</v>
@@ -2945,28 +2945,28 @@
         <v>7.302699999999999</v>
       </c>
       <c r="AU10">
-        <v>7.406232341919727</v>
+        <v>7.406769729557718</v>
       </c>
       <c r="AV10">
-        <v>7.639678438720181</v>
+        <v>7.639320180294854</v>
       </c>
       <c r="AW10">
-        <v>-0.01856110386285626</v>
+        <v>-0.01848989179363153</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01856110386285626</v>
+        <v>0.01848989179363153</v>
       </c>
       <c r="AZ10">
-        <v>0.4597123731108294</v>
+        <v>0.4621341761186041</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3402876268891706</v>
+        <v>0.3378658238813958</v>
       </c>
       <c r="BC10" t="s">
         <v>124</v>
@@ -2981,43 +2981,43 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01237406924190418</v>
+        <v>0.01232659452908769</v>
       </c>
       <c r="BH10">
-        <v>40407.07953263868</v>
+        <v>40562.70357722278</v>
       </c>
       <c r="BI10">
-        <v>40407.07953263868</v>
+        <v>40562.70357722278</v>
       </c>
       <c r="BJ10">
-        <v>5354.555150555727</v>
+        <v>5375.177713213467</v>
       </c>
       <c r="BK10">
-        <v>404.0707953263868</v>
+        <v>405.6270357722278</v>
       </c>
       <c r="BL10">
-        <v>0.004040707953263868</v>
+        <v>0.004056270357722278</v>
       </c>
       <c r="BM10">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="BN10">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="BO10">
-        <v>0.1127723470934458</v>
+        <v>0.1051534679714189</v>
       </c>
       <c r="BP10">
-        <v>0.1522875669610324</v>
+        <v>0.1496901367766263</v>
       </c>
       <c r="BQ10">
-        <v>0.1086609465292724</v>
+        <v>0.1043361589865909</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT10" t="s">
         <v>126</v>
@@ -3029,7 +3029,7 @@
         <v>127</v>
       </c>
       <c r="BW10" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3037,7 +3037,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3160,7 +3160,7 @@
         <v>4180.43</v>
       </c>
       <c r="AQ11">
-        <v>4080.404562058218</v>
+        <v>4078.308584387067</v>
       </c>
       <c r="AR11">
         <v>4226.132137089084</v>
@@ -3172,28 +3172,28 @@
         <v>3930.560000000001</v>
       </c>
       <c r="AU11">
-        <v>4080.404562058218</v>
+        <v>4078.308584387067</v>
       </c>
       <c r="AV11">
         <v>4310.295</v>
       </c>
       <c r="AW11">
-        <v>-0.02392706921100987</v>
+        <v>-0.02442844769866582</v>
       </c>
       <c r="AX11">
-        <v>0.7702262960904176</v>
+        <v>0.7863659616750752</v>
       </c>
       <c r="AY11">
-        <v>0.02392706921100987</v>
+        <v>0.02442844769866582</v>
       </c>
       <c r="AZ11">
-        <v>0.3378889601766373</v>
+        <v>0.3307977042423221</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4621110398233628</v>
+        <v>0.4692022957576779</v>
       </c>
       <c r="BC11" t="s">
         <v>125</v>
@@ -3232,19 +3232,19 @@
         <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>585.4463833422634</v>
+        <v>593.3901592495364</v>
       </c>
       <c r="BP11">
-        <v>153.8863138746162</v>
+        <v>154.1478394600492</v>
       </c>
       <c r="BQ11">
-        <v>90.58950203340144</v>
+        <v>82.3367072127096</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05547092301716239</v>
+        <v>0.0555021536212318</v>
       </c>
       <c r="BT11" t="s">
         <v>126</v>
@@ -3256,7 +3256,7 @@
         <v>127</v>
       </c>
       <c r="BW11" s="2">
-        <v>46325</v>
+        <v>46326</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -310,7 +310,7 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>UP_ACCELERATING</t>
+    <t>UP_STEADY</t>
   </si>
   <si>
     <t>DOWN_DECELERATING</t>
@@ -322,7 +322,7 @@
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>多头加速</t>
+    <t>多头稳态</t>
   </si>
   <si>
     <t>空头减速</t>
@@ -340,7 +340,7 @@
     <t>下跌</t>
   </si>
   <si>
-    <t>UP_STEEPENING</t>
+    <t>UP_SLOPE</t>
   </si>
   <si>
     <t>DOWN_VALLEY_FLATTENING</t>
@@ -352,7 +352,7 @@
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>上升陡坡形成</t>
+    <t>上升坡延续</t>
   </si>
   <si>
     <t>下降谷底收敛</t>
@@ -364,34 +364,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.01542,naive=0.007423,drift4=0.007414; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=2.707,naive=2.331,drift4=4.35; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04377,naive=0.01924,drift4=0.02565; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1411,naive=0.1227,drift4=0.0722; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.02592,naive=0.02066,drift4=0.01607; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.06014,naive=0.1049,drift4=0.08954; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.01052,naive=0.01596,drift4=0.01529; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.01952,naive=0.02424,drift4=0.019; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.1052,naive=0.1497,drift4=0.1043; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=593.4,naive=154.1,drift4=82.34; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.01479,naive=0.007632,drift4=0.006113; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=2.634,naive=2.238,drift4=4.128; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04163,naive=0.02025,drift4=0.02512; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1295,naive=0.1043,drift4=0.06469; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02399,naive=0.01795,drift4=0.01487; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.05059,naive=0.09364,drift4=0.07769</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.008892,naive=0.01438,drift4=0.01365; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.01936,naive=0.02184,drift4=0.0165; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.1062,naive=0.1466,drift4=0.09965; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=632.7,naive=192.7,drift4=116.5; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -994,7 +994,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1018,19 +1018,19 @@
         <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2.608637289688342</v>
+        <v>2.465037919765153</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
         <v>94</v>
@@ -1048,10 +1048,10 @@
         <v>102</v>
       </c>
       <c r="T2">
-        <v>0.9796349403972437</v>
+        <v>0.9962834818469217</v>
       </c>
       <c r="U2">
-        <v>0.9907448616739116</v>
+        <v>0.9981878746310084</v>
       </c>
       <c r="V2" t="s">
         <v>92</v>
@@ -1060,22 +1060,22 @@
         <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9996365539806078</v>
+        <v>0.9994412311995745</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>16.41044730187966</v>
+        <v>6.991186755245489</v>
       </c>
       <c r="AA2">
-        <v>-19</v>
+        <v>-25</v>
       </c>
       <c r="AB2">
-        <v>0.95926247650358</v>
+        <v>0.992564885858424</v>
       </c>
       <c r="AC2">
-        <v>0.2825163732816537</v>
+        <v>0.1217166683772349</v>
       </c>
       <c r="AD2" t="s">
         <v>92</v>
@@ -1090,67 +1090,67 @@
         <v>112</v>
       </c>
       <c r="AH2">
-        <v>0.9589138363749424</v>
+        <v>0.9920102715678084</v>
       </c>
       <c r="AI2">
-        <v>0.9825022639046214</v>
+        <v>0.9928469825342465</v>
       </c>
       <c r="AJ2">
-        <v>2.05009011765739</v>
+        <v>1.960061041963213</v>
       </c>
       <c r="AK2">
-        <v>0.6972104431422118</v>
+        <v>0.3500288017584413</v>
       </c>
       <c r="AL2">
-        <v>2.973943519718391</v>
+        <v>2.708348477042971</v>
       </c>
       <c r="AM2">
-        <v>-4.716551146444409</v>
+        <v>-4.670177103758457</v>
       </c>
       <c r="AN2">
-        <v>2.52479207909921</v>
+        <v>2.285629500781877</v>
       </c>
       <c r="AO2">
-        <v>0.03432848626443592</v>
+        <v>0.03151276095421195</v>
       </c>
       <c r="AP2">
-        <v>0.826435</v>
+        <v>0.8287599999999999</v>
       </c>
       <c r="AQ2">
-        <v>0.8350334122308836</v>
+        <v>0.8413485859843923</v>
       </c>
       <c r="AR2">
-        <v>0.8318201893627784</v>
+        <v>0.8414250571719638</v>
       </c>
       <c r="AS2">
-        <v>0.826435</v>
+        <v>0.8287599999999999</v>
       </c>
       <c r="AT2">
-        <v>0.8428550000000001</v>
+        <v>0.847505</v>
       </c>
       <c r="AU2">
-        <v>0.8350334122308836</v>
+        <v>0.8413485859843923</v>
       </c>
       <c r="AV2">
-        <v>0.8188550000000001</v>
+        <v>0.8203676093437383</v>
       </c>
       <c r="AW2">
-        <v>0.01040422081698323</v>
+        <v>0.01518966405761908</v>
       </c>
       <c r="AX2">
-        <v>1.134355175578315</v>
+        <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.01040422081698323</v>
+        <v>0.01518966405761908</v>
       </c>
       <c r="AZ2">
-        <v>0.4112066729818429</v>
+        <v>0.3959599758909541</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.388793327018157</v>
+        <v>0.4040400241090458</v>
       </c>
       <c r="BC2" t="s">
         <v>116</v>
@@ -1165,43 +1165,43 @@
         <v>500</v>
       </c>
       <c r="BG2">
-        <v>0.009171925196778839</v>
+        <v>0.01012644270507939</v>
       </c>
       <c r="BH2">
-        <v>54514.18205804807</v>
+        <v>49375.68053875443</v>
       </c>
       <c r="BI2">
-        <v>54514.18205804807</v>
+        <v>49375.68053875443</v>
       </c>
       <c r="BJ2">
-        <v>65963.06068601653</v>
+        <v>59577.77950040354</v>
       </c>
       <c r="BK2">
-        <v>545.1418205804807</v>
+        <v>493.7568053875443</v>
       </c>
       <c r="BL2">
-        <v>0.005451418205804808</v>
+        <v>0.004937568053875443</v>
       </c>
       <c r="BM2">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN2">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO2">
-        <v>0.01542405003386405</v>
+        <v>0.01479440280903969</v>
       </c>
       <c r="BP2">
-        <v>0.007423250344803028</v>
+        <v>0.007631629170536013</v>
       </c>
       <c r="BQ2">
-        <v>0.007413939653829339</v>
+        <v>0.006112744410909562</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT2" t="s">
         <v>126</v>
@@ -1213,7 +1213,7 @@
         <v>127</v>
       </c>
       <c r="BW2" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1221,7 +1221,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1233,7 +1233,7 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
         <v>90</v>
@@ -1245,19 +1245,19 @@
         <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.2618113337995194</v>
+        <v>0.1759201018796525</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1275,10 +1275,10 @@
         <v>103</v>
       </c>
       <c r="T3">
-        <v>-0.9040330999209918</v>
+        <v>-0.7976630934848853</v>
       </c>
       <c r="U3">
-        <v>0.8034816978108861</v>
+        <v>0.7588861098037478</v>
       </c>
       <c r="V3" t="s">
         <v>93</v>
@@ -1287,22 +1287,22 @@
         <v>94</v>
       </c>
       <c r="X3">
-        <v>0.9866672113857586</v>
+        <v>0.9997508709421974</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>135.7624140442337</v>
+        <v>114.0381403485021</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="AB3">
-        <v>-0.7164531140400342</v>
+        <v>-0.407344676974959</v>
       </c>
       <c r="AC3">
-        <v>0.6976352452265708</v>
+        <v>0.9132745009799443</v>
       </c>
       <c r="AD3" t="s">
         <v>93</v>
@@ -1317,67 +1317,67 @@
         <v>113</v>
       </c>
       <c r="AH3">
-        <v>-0.3534503980592617</v>
+        <v>-0.2036215977896917</v>
       </c>
       <c r="AI3">
-        <v>0.7027950690557376</v>
+        <v>0.6134016422533884</v>
       </c>
       <c r="AJ3">
-        <v>-0.2799160452746512</v>
+        <v>-0.2296472657165816</v>
       </c>
       <c r="AK3">
-        <v>0.4588162104022177</v>
+        <v>0.6035889157375692</v>
       </c>
       <c r="AL3">
-        <v>-0.3114098830211929</v>
+        <v>-0.2556816737650891</v>
       </c>
       <c r="AM3">
-        <v>0.4534600500415369</v>
+        <v>0.3946921492060487</v>
       </c>
       <c r="AN3">
-        <v>0.296562298165182</v>
+        <v>0.2433294980053786</v>
       </c>
       <c r="AO3">
-        <v>0.04982926094192065</v>
+        <v>0.05809710445912196</v>
       </c>
       <c r="AP3">
-        <v>157.6555</v>
+        <v>157.859</v>
       </c>
       <c r="AQ3">
-        <v>158.8452398268254</v>
+        <v>159.1777276569718</v>
       </c>
       <c r="AR3">
-        <v>159.0538086512412</v>
+        <v>159.3930274166936</v>
       </c>
       <c r="AS3">
-        <v>157.6555</v>
+        <v>157.859</v>
       </c>
       <c r="AT3">
-        <v>159.297</v>
+        <v>159.704</v>
       </c>
       <c r="AU3">
-        <v>158.8452398268254</v>
+        <v>159.1777276569718</v>
       </c>
       <c r="AV3">
-        <v>156.157375</v>
+        <v>156.360875</v>
       </c>
       <c r="AW3">
-        <v>0.007546453037321533</v>
+        <v>0.008353832578261357</v>
       </c>
       <c r="AX3">
-        <v>0.7941525752693749</v>
+        <v>0.8802520864225253</v>
       </c>
       <c r="AY3">
-        <v>0.007546453037321533</v>
+        <v>0.008353832578261357</v>
       </c>
       <c r="AZ3">
-        <v>0.5076667973785483</v>
+        <v>0.5057434367879905</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.2923332026214518</v>
+        <v>0.2942565632120095</v>
       </c>
       <c r="BC3" t="s">
         <v>117</v>
@@ -1392,43 +1392,43 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009502522905956443</v>
+        <v>0.009490272965114538</v>
       </c>
       <c r="BH3">
-        <v>52617.60534000778</v>
+        <v>52685.52357113003</v>
       </c>
       <c r="BI3">
-        <v>52617.60534000778</v>
+        <v>52685.52357113003</v>
       </c>
       <c r="BJ3">
         <v>333.7505214851863</v>
       </c>
       <c r="BK3">
-        <v>526.1760534000778</v>
+        <v>526.8552357113002</v>
       </c>
       <c r="BL3">
-        <v>0.005261760534000777</v>
+        <v>0.005268552357113002</v>
       </c>
       <c r="BM3">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN3">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO3">
-        <v>2.707473145983308</v>
+        <v>2.63441354706161</v>
       </c>
       <c r="BP3">
-        <v>2.331411422452795</v>
+        <v>2.237827819188108</v>
       </c>
       <c r="BQ3">
-        <v>4.350387180020063</v>
+        <v>4.1281714346991</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT3" t="s">
         <v>126</v>
@@ -1440,7 +1440,7 @@
         <v>127</v>
       </c>
       <c r="BW3" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1448,7 +1448,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1472,19 +1472,19 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.19362427702495</v>
+        <v>1.285725995326295</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
@@ -1496,16 +1496,16 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T4">
-        <v>-0.9664049471866771</v>
+        <v>-0.9993283430045486</v>
       </c>
       <c r="U4">
-        <v>0.8343774977760345</v>
+        <v>0.8490288919884816</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
@@ -1514,22 +1514,22 @@
         <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9979810861681192</v>
+        <v>0.997324550545739</v>
       </c>
       <c r="Y4">
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>154.3537461065839</v>
+        <v>176.4025569540482</v>
       </c>
       <c r="AA4">
-        <v>42.00000000000001</v>
+        <v>53.00000000000001</v>
       </c>
       <c r="AB4">
-        <v>-0.9014834172147076</v>
+        <v>-0.9980295296037169</v>
       </c>
       <c r="AC4">
-        <v>0.4328136417523059</v>
+        <v>0.06274598026155627</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
@@ -1538,73 +1538,73 @@
         <v>107</v>
       </c>
       <c r="AF4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AH4">
-        <v>-0.4498316999372408</v>
+        <v>-0.4976796760217012</v>
       </c>
       <c r="AI4">
-        <v>0.7653579103828585</v>
+        <v>0.7935656771619158</v>
       </c>
       <c r="AJ4">
-        <v>-0.875977160782628</v>
+        <v>-0.927412727153209</v>
       </c>
       <c r="AK4">
-        <v>0.5233042074103007</v>
+        <v>0.1440315104885368</v>
       </c>
       <c r="AL4">
-        <v>-1.621531224814846</v>
+        <v>-1.816656800577983</v>
       </c>
       <c r="AM4">
-        <v>0.7595991782462008</v>
+        <v>0.6012046257110735</v>
       </c>
       <c r="AN4">
-        <v>1.57002796163998</v>
+        <v>1.771224108307004</v>
       </c>
       <c r="AO4">
-        <v>0.0292032996026361</v>
+        <v>0.03271182940138548</v>
       </c>
       <c r="AP4">
-        <v>6.707825</v>
+        <v>6.70615</v>
       </c>
       <c r="AQ4">
-        <v>6.727381246380099</v>
+        <v>6.720678763840674</v>
       </c>
       <c r="AR4">
-        <v>6.752733249971111</v>
+        <v>6.7408091081622</v>
       </c>
       <c r="AS4">
-        <v>6.707825</v>
+        <v>6.70615</v>
       </c>
       <c r="AT4">
-        <v>6.708364999999999</v>
+        <v>6.705015</v>
       </c>
       <c r="AU4">
-        <v>6.727381246380099</v>
+        <v>6.720678763840674</v>
       </c>
       <c r="AV4">
-        <v>6.68431875</v>
+        <v>6.68264375</v>
       </c>
       <c r="AW4">
-        <v>0.002915437773063417</v>
+        <v>0.002166483577115587</v>
       </c>
       <c r="AX4">
-        <v>0.8319594312193326</v>
+        <v>0.6180808866013904</v>
       </c>
       <c r="AY4">
-        <v>0.002915437773063417</v>
+        <v>0.002166483577115587</v>
       </c>
       <c r="AZ4">
-        <v>0.4310344986009579</v>
+        <v>0.4312654968444056</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3689655013990421</v>
+        <v>0.3687345031555944</v>
       </c>
       <c r="BC4" t="s">
         <v>118</v>
@@ -1619,22 +1619,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.003504302810523473</v>
+        <v>0.003505178082804533</v>
       </c>
       <c r="BH4">
-        <v>142681.7335814966</v>
+        <v>142646.1047593748</v>
       </c>
       <c r="BI4">
-        <v>142681.7335814966</v>
+        <v>142646.1047593748</v>
       </c>
       <c r="BJ4">
         <v>21270.9385801652</v>
       </c>
       <c r="BK4">
-        <v>1426.817335814966</v>
+        <v>1426.461047593748</v>
       </c>
       <c r="BL4">
-        <v>0.01426817335814966</v>
+        <v>0.01426461047593748</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1643,19 +1643,19 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.04377480298376337</v>
+        <v>0.04162844935503391</v>
       </c>
       <c r="BP4">
-        <v>0.01924087341663613</v>
+        <v>0.02024959669254959</v>
       </c>
       <c r="BQ4">
-        <v>0.02564535052303343</v>
+        <v>0.02511603358898713</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT4" t="s">
         <v>126</v>
@@ -1667,7 +1667,7 @@
         <v>127</v>
       </c>
       <c r="BW4" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1675,7 +1675,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1795,43 +1795,43 @@
         <v>0.03539939110579538</v>
       </c>
       <c r="AP5">
-        <v>8.860749999999999</v>
+        <v>8.87955</v>
       </c>
       <c r="AQ5">
-        <v>8.790976546854722</v>
+        <v>8.817659428743085</v>
       </c>
       <c r="AR5">
-        <v>8.892627315578657</v>
+        <v>8.913018329765272</v>
       </c>
       <c r="AS5">
-        <v>8.860749999999999</v>
+        <v>8.87955</v>
       </c>
       <c r="AT5">
-        <v>8.651749999999998</v>
+        <v>8.689349999999999</v>
       </c>
       <c r="AU5">
-        <v>8.790976546854722</v>
+        <v>8.817659428743085</v>
       </c>
       <c r="AV5">
-        <v>8.9309625</v>
+        <v>8.949762499999999</v>
       </c>
       <c r="AW5">
-        <v>-0.007874441006153813</v>
+        <v>-0.006970012135402757</v>
       </c>
       <c r="AX5">
-        <v>0.9937468847467051</v>
+        <v>0.8814751113678636</v>
       </c>
       <c r="AY5">
-        <v>0.007874441006153813</v>
+        <v>0.006970012135402757</v>
       </c>
       <c r="AZ5">
-        <v>0.4044654293023725</v>
+        <v>0.4035860992828934</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3955345706976274</v>
+        <v>0.3964139007171066</v>
       </c>
       <c r="BC5" t="s">
         <v>119</v>
@@ -1846,22 +1846,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.007923990632847034</v>
+        <v>0.007907213766463316</v>
       </c>
       <c r="BH5">
-        <v>63099.51931636163</v>
+        <v>63233.39861135897</v>
       </c>
       <c r="BI5">
-        <v>63099.51931636163</v>
+        <v>63233.39861135897</v>
       </c>
       <c r="BJ5">
-        <v>7121.239095602701</v>
+        <v>7121.239095602702</v>
       </c>
       <c r="BK5">
-        <v>630.9951931636162</v>
+        <v>632.3339861135897</v>
       </c>
       <c r="BL5">
-        <v>0.006309951931636163</v>
+        <v>0.006323339861135898</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1870,19 +1870,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.141093140256222</v>
+        <v>0.1294778174020023</v>
       </c>
       <c r="BP5">
-        <v>0.1226892281164322</v>
+        <v>0.1042955815612341</v>
       </c>
       <c r="BQ5">
-        <v>0.07220346322129705</v>
+        <v>0.06469059202743228</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT5" t="s">
         <v>126</v>
@@ -1894,7 +1894,7 @@
         <v>127</v>
       </c>
       <c r="BW5" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1902,7 +1902,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1926,19 +1926,19 @@
         <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2.137214015356746</v>
+        <v>2.146278781367343</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O6" t="s">
         <v>94</v>
@@ -1950,16 +1950,16 @@
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="T6">
-        <v>-0.9795687248641783</v>
+        <v>-0.9971076933219547</v>
       </c>
       <c r="U6">
-        <v>0.9906040627503265</v>
+        <v>0.9984662328369414</v>
       </c>
       <c r="V6" t="s">
         <v>93</v>
@@ -1968,22 +1968,22 @@
         <v>94</v>
       </c>
       <c r="X6">
-        <v>0.9991925462457855</v>
+        <v>0.9990710833682475</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-163.5608725506031</v>
+        <v>-173.8328374355906</v>
       </c>
       <c r="AA6">
-        <v>-27</v>
+        <v>-30.99999999999999</v>
       </c>
       <c r="AB6">
-        <v>-0.9591209390869654</v>
+        <v>-0.9942126974340801</v>
       </c>
       <c r="AC6">
-        <v>-0.2829965091744729</v>
+        <v>-0.1074295688386122</v>
       </c>
       <c r="AD6" t="s">
         <v>93</v>
@@ -1992,73 +1992,73 @@
         <v>107</v>
       </c>
       <c r="AF6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AH6">
-        <v>-0.9583464932839538</v>
+        <v>-0.993289156723934</v>
       </c>
       <c r="AI6">
-        <v>0.9816195552636744</v>
+        <v>0.9925145540429726</v>
       </c>
       <c r="AJ6">
-        <v>-1.700671729753976</v>
+        <v>-1.73512953719635</v>
       </c>
       <c r="AK6">
-        <v>-0.6196399847827141</v>
+        <v>-0.313789042006236</v>
       </c>
       <c r="AL6">
-        <v>-2.319054224479197</v>
+        <v>-2.212107403362016</v>
       </c>
       <c r="AM6">
-        <v>3.681947944800657</v>
+        <v>4.1232762300579</v>
       </c>
       <c r="AN6">
-        <v>1.985039928428203</v>
+        <v>1.846950093617659</v>
       </c>
       <c r="AO6">
-        <v>0.0388941176562674</v>
+        <v>0.03616089577425368</v>
       </c>
       <c r="AP6">
-        <v>1.32041</v>
+        <v>1.324035</v>
       </c>
       <c r="AQ6">
-        <v>1.307494887574405</v>
+        <v>1.312392729165544</v>
       </c>
       <c r="AR6">
-        <v>1.317759401826194</v>
+        <v>1.321111369719784</v>
       </c>
       <c r="AS6">
-        <v>1.32041</v>
+        <v>1.324035</v>
       </c>
       <c r="AT6">
-        <v>1.28905</v>
+        <v>1.2963</v>
       </c>
       <c r="AU6">
-        <v>1.307494887574405</v>
+        <v>1.312392729165544</v>
       </c>
       <c r="AV6">
-        <v>1.3335725</v>
+        <v>1.3371975</v>
       </c>
       <c r="AW6">
-        <v>-0.009781137999253901</v>
+        <v>-0.008793023473288775</v>
       </c>
       <c r="AX6">
-        <v>0.9812051225523173</v>
+        <v>0.8845030073660728</v>
       </c>
       <c r="AY6">
-        <v>0.009781137999253901</v>
+        <v>0.008793023473288775</v>
       </c>
       <c r="AZ6">
-        <v>0.4240035249811095</v>
+        <v>0.4250361541763325</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3759964750188905</v>
+        <v>0.3749638458236675</v>
       </c>
       <c r="BC6" t="s">
         <v>120</v>
@@ -2073,22 +2073,22 @@
         <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.009968494634242368</v>
+        <v>0.009941202460660001</v>
       </c>
       <c r="BH6">
-        <v>50158.02469135816</v>
+        <v>50295.72649572663</v>
       </c>
       <c r="BI6">
-        <v>50158.02469135816</v>
+        <v>50295.72649572663</v>
       </c>
       <c r="BJ6">
         <v>37986.70465337142</v>
       </c>
       <c r="BK6">
-        <v>501.5802469135816</v>
+        <v>502.9572649572663</v>
       </c>
       <c r="BL6">
-        <v>0.005015802469135816</v>
+        <v>0.005029572649572663</v>
       </c>
       <c r="BM6">
         <v>500</v>
@@ -2097,19 +2097,19 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.0259177672501914</v>
+        <v>0.02399064598623212</v>
       </c>
       <c r="BP6">
-        <v>0.02065659645761009</v>
+        <v>0.01795120680939846</v>
       </c>
       <c r="BQ6">
-        <v>0.01606990663690898</v>
+        <v>0.01486592917721869</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT6" t="s">
         <v>126</v>
@@ -2121,7 +2121,7 @@
         <v>127</v>
       </c>
       <c r="BW6" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2129,7 +2129,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2249,43 +2249,43 @@
         <v>0.05107972290349189</v>
       </c>
       <c r="AP7">
-        <v>4.65158</v>
+        <v>4.66275</v>
       </c>
       <c r="AQ7">
-        <v>4.600515737072323</v>
+        <v>4.616797495394381</v>
       </c>
       <c r="AR7">
-        <v>4.657346242940257</v>
+        <v>4.671278093138992</v>
       </c>
       <c r="AS7">
-        <v>4.65158</v>
+        <v>4.66275</v>
       </c>
       <c r="AT7">
-        <v>4.47213</v>
+        <v>4.49447</v>
       </c>
       <c r="AU7">
-        <v>4.600515737072323</v>
+        <v>4.616797495394381</v>
       </c>
       <c r="AV7">
-        <v>4.69478</v>
+        <v>4.70595</v>
       </c>
       <c r="AW7">
-        <v>-0.01097783181793653</v>
+        <v>-0.009855236631948804</v>
       </c>
       <c r="AX7">
-        <v>1.182043123325869</v>
+        <v>1.063715384389343</v>
       </c>
       <c r="AY7">
-        <v>0.01097783181793653</v>
+        <v>0.009855236631948804</v>
       </c>
       <c r="AZ7">
-        <v>0.4993932260150525</v>
+        <v>0.5031668899317518</v>
       </c>
       <c r="BA7">
-        <v>0.2</v>
+        <v>0.1982619268770551</v>
       </c>
       <c r="BB7">
-        <v>0.3006067739849475</v>
+        <v>0.2985711831911931</v>
       </c>
       <c r="BC7" t="s">
         <v>121</v>
@@ -2300,43 +2300,43 @@
         <v>500</v>
       </c>
       <c r="BG7">
-        <v>0.009287166941125313</v>
+        <v>0.009264918771111401</v>
       </c>
       <c r="BH7">
-        <v>53837.73148148188</v>
+        <v>53967.01388888928</v>
       </c>
       <c r="BI7">
-        <v>53837.73148148188</v>
+        <v>53967.01388888928</v>
       </c>
       <c r="BJ7">
         <v>11574.07407407416</v>
       </c>
       <c r="BK7">
-        <v>538.3773148148189</v>
+        <v>539.6701388888928</v>
       </c>
       <c r="BL7">
-        <v>0.005383773148148189</v>
+        <v>0.005396701388888927</v>
       </c>
       <c r="BM7">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN7">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO7">
-        <v>0.06014176790331476</v>
+        <v>0.05058586155879946</v>
       </c>
       <c r="BP7">
-        <v>0.1049429184638299</v>
+        <v>0.09363814925513671</v>
       </c>
       <c r="BQ7">
-        <v>0.08953831221253236</v>
+        <v>0.07768679267725995</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT7" t="s">
         <v>126</v>
@@ -2348,7 +2348,7 @@
         <v>127</v>
       </c>
       <c r="BW7" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2356,7 +2356,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2380,19 +2380,19 @@
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K8">
-        <v>0.4559350349948318</v>
+        <v>0.6476295876202839</v>
       </c>
       <c r="L8">
-        <v>2.039962344502193</v>
+        <v>2.221462233986172</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" t="s">
         <v>94</v>
@@ -2401,7 +2401,7 @@
         <v>96</v>
       </c>
       <c r="Q8">
-        <v>0.8639837587487079</v>
+        <v>0.9119073969050709</v>
       </c>
       <c r="R8" t="s">
         <v>101</v>
@@ -2410,10 +2410,10 @@
         <v>105</v>
       </c>
       <c r="T8">
-        <v>-0.7640048563958072</v>
+        <v>-0.8152999060570199</v>
       </c>
       <c r="U8">
-        <v>0.8121651451941891</v>
+        <v>0.8639857864506869</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
@@ -2422,22 +2422,22 @@
         <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9998908182674044</v>
+        <v>0.9998255623279414</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-124.7305232386064</v>
+        <v>-130.6716504042479</v>
       </c>
       <c r="AA8">
-        <v>-10</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB8">
-        <v>-0.5697174242557334</v>
+        <v>-0.6517232038624154</v>
       </c>
       <c r="AC8">
-        <v>-0.8218406515252289</v>
+        <v>-0.7584568976199693</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
@@ -2452,67 +2452,67 @@
         <v>115</v>
       </c>
       <c r="AH8">
-        <v>-0.5696552215202633</v>
+        <v>-0.6516095187839072</v>
       </c>
       <c r="AI8">
-        <v>0.8617887040323801</v>
+        <v>0.8876921592364666</v>
       </c>
       <c r="AJ8">
-        <v>-1.523950601975966</v>
+        <v>-1.709742231684434</v>
       </c>
       <c r="AK8">
-        <v>-2.301406853944384</v>
+        <v>-2.112879613523765</v>
       </c>
       <c r="AL8">
-        <v>-2.652459802625317</v>
+        <v>-2.676659359883749</v>
       </c>
       <c r="AM8">
-        <v>2.408154409026348</v>
+        <v>3.48691946774025</v>
       </c>
       <c r="AN8">
-        <v>2.365246036986357</v>
+        <v>2.299539616987486</v>
       </c>
       <c r="AO8">
-        <v>0.06058873091954324</v>
+        <v>0.05175832491358315</v>
       </c>
       <c r="AP8">
-        <v>0.693995</v>
+        <v>0.6957249999999999</v>
       </c>
       <c r="AQ8">
-        <v>0.68517058311831</v>
+        <v>0.6877136500981937</v>
       </c>
       <c r="AR8">
-        <v>0.6921517593755507</v>
+        <v>0.6942461558539956</v>
       </c>
       <c r="AS8">
-        <v>0.693995</v>
+        <v>0.6957249999999999</v>
       </c>
       <c r="AT8">
-        <v>0.667845</v>
+        <v>0.6713049999999998</v>
       </c>
       <c r="AU8">
-        <v>0.68517058311831</v>
+        <v>0.6877136500981937</v>
       </c>
       <c r="AV8">
-        <v>0.701465</v>
+        <v>0.7029337499999999</v>
       </c>
       <c r="AW8">
-        <v>-0.01271538970985382</v>
+        <v>-0.01151510999576871</v>
       </c>
       <c r="AX8">
-        <v>1.181314174255702</v>
+        <v>1.111336903319752</v>
       </c>
       <c r="AY8">
-        <v>0.01271538970985382</v>
+        <v>0.01151510999576871</v>
       </c>
       <c r="AZ8">
-        <v>0.4976222017681398</v>
+        <v>0.5023569941959377</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3023777982318603</v>
+        <v>0.2976430058040623</v>
       </c>
       <c r="BC8" t="s">
         <v>122</v>
@@ -2524,46 +2524,46 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>431.991879374354</v>
+        <v>455.9536984525355</v>
       </c>
       <c r="BG8">
-        <v>0.01076376630955543</v>
+        <v>0.01036149340615894</v>
       </c>
       <c r="BH8">
-        <v>46452.14190093757</v>
+        <v>48255.59216230321</v>
       </c>
       <c r="BI8">
-        <v>40133.89616150039</v>
+        <v>44004.63143483867</v>
       </c>
       <c r="BJ8">
-        <v>57830.23820272536</v>
+        <v>63250.03619941596</v>
       </c>
       <c r="BK8">
-        <v>401.3389616150039</v>
+        <v>440.0463143483867</v>
       </c>
       <c r="BL8">
-        <v>0.004013389616150039</v>
+        <v>0.004400463143483867</v>
       </c>
       <c r="BM8">
-        <v>431.9918793743539</v>
+        <v>455.9536984525354</v>
       </c>
       <c r="BN8">
-        <v>0.004319918793743539</v>
+        <v>0.004559536984525354</v>
       </c>
       <c r="BO8">
-        <v>0.01051673906935029</v>
+        <v>0.008891634072827208</v>
       </c>
       <c r="BP8">
-        <v>0.01595618770451222</v>
+        <v>0.01438092731696102</v>
       </c>
       <c r="BQ8">
-        <v>0.0152876209644398</v>
+        <v>0.0136540694814981</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT8" t="s">
         <v>126</v>
@@ -2575,7 +2575,7 @@
         <v>127</v>
       </c>
       <c r="BW8" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2583,7 +2583,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2607,19 +2607,19 @@
         <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>2.679185503841806</v>
+        <v>3.052787287013346</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O9" t="s">
         <v>94</v>
@@ -2637,10 +2637,10 @@
         <v>105</v>
       </c>
       <c r="T9">
-        <v>-0.8835016086238986</v>
+        <v>-0.891041205370296</v>
       </c>
       <c r="U9">
-        <v>0.9475566658037164</v>
+        <v>0.9509582065410651</v>
       </c>
       <c r="V9" t="s">
         <v>93</v>
@@ -2649,22 +2649,22 @@
         <v>94</v>
       </c>
       <c r="X9">
-        <v>0.9999237676918484</v>
+        <v>0.9999586564977279</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>-140.0847447279974</v>
+        <v>-141.4512221898441</v>
       </c>
       <c r="AA9">
-        <v>-4.999999999999995</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AB9">
-        <v>-0.7669943356294604</v>
+        <v>-0.7820779058161692</v>
       </c>
       <c r="AC9">
-        <v>-0.6416538701763769</v>
+        <v>-0.6231806714221768</v>
       </c>
       <c r="AD9" t="s">
         <v>93</v>
@@ -2679,67 +2679,67 @@
         <v>115</v>
       </c>
       <c r="AH9">
-        <v>-0.7669358658809162</v>
+        <v>-0.7820455719764932</v>
       </c>
       <c r="AI9">
-        <v>0.9224527554252537</v>
+        <v>0.9274205860666791</v>
       </c>
       <c r="AJ9">
-        <v>-2.012734723500569</v>
+        <v>-2.322853513699059</v>
       </c>
       <c r="AK9">
-        <v>-1.717633643535347</v>
+        <v>-1.88145753411371</v>
       </c>
       <c r="AL9">
-        <v>-3.419068369064508</v>
+        <v>-3.775023293907783</v>
       </c>
       <c r="AM9">
-        <v>2.732463485735718</v>
+        <v>3.724128517196357</v>
       </c>
       <c r="AN9">
-        <v>3.1331921734011</v>
+        <v>3.393437940830339</v>
       </c>
       <c r="AO9">
-        <v>0.05079242637154264</v>
+        <v>0.0479221030158419</v>
       </c>
       <c r="AP9">
-        <v>1.12296</v>
+        <v>1.125215</v>
       </c>
       <c r="AQ9">
-        <v>1.104386263084863</v>
+        <v>1.108365606871953</v>
       </c>
       <c r="AR9">
-        <v>1.110874523014808</v>
+        <v>1.115897827062754</v>
       </c>
       <c r="AS9">
-        <v>1.12296</v>
+        <v>1.125215</v>
       </c>
       <c r="AT9">
-        <v>1.084575</v>
+        <v>1.089085</v>
       </c>
       <c r="AU9">
-        <v>1.104386263084863</v>
+        <v>1.108365606871953</v>
       </c>
       <c r="AV9">
-        <v>1.135342491276758</v>
+        <v>1.136447928752032</v>
       </c>
       <c r="AW9">
-        <v>-0.01653998086765095</v>
+        <v>-0.0149743765662985</v>
       </c>
       <c r="AX9">
         <v>1.5</v>
       </c>
       <c r="AY9">
-        <v>0.01653998086765095</v>
+        <v>0.0149743765662985</v>
       </c>
       <c r="AZ9">
-        <v>0.4613871923848443</v>
+        <v>0.4495835833998097</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3386128076151557</v>
+        <v>0.3504164166001904</v>
       </c>
       <c r="BC9" t="s">
         <v>123</v>
@@ -2754,22 +2754,22 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.0110266539117673</v>
+        <v>0.009982917710865664</v>
       </c>
       <c r="BH9">
-        <v>45344.671556837</v>
+        <v>50085.55759763372</v>
       </c>
       <c r="BI9">
-        <v>45344.671556837</v>
+        <v>50085.55759763372</v>
       </c>
       <c r="BJ9">
-        <v>40379.59638530046</v>
+        <v>44511.98890668336</v>
       </c>
       <c r="BK9">
-        <v>453.44671556837</v>
+        <v>500.8555759763372</v>
       </c>
       <c r="BL9">
-        <v>0.0045344671556837</v>
+        <v>0.005008555759763372</v>
       </c>
       <c r="BM9">
         <v>500</v>
@@ -2778,19 +2778,19 @@
         <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.01952366480548363</v>
+        <v>0.01936187273214413</v>
       </c>
       <c r="BP9">
-        <v>0.02424060672985473</v>
+        <v>0.02184267473234254</v>
       </c>
       <c r="BQ9">
-        <v>0.01900069501469215</v>
+        <v>0.01650432232271824</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT9" t="s">
         <v>126</v>
@@ -2802,7 +2802,7 @@
         <v>127</v>
       </c>
       <c r="BW9" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2810,7 +2810,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2930,43 +2930,43 @@
         <v>0.04582647224627837</v>
       </c>
       <c r="AP10">
-        <v>7.5463</v>
+        <v>7.5464</v>
       </c>
       <c r="AQ10">
-        <v>7.406769729557718</v>
+        <v>7.40619827397423</v>
       </c>
       <c r="AR10">
-        <v>7.422469825340755</v>
+        <v>7.422379892101859</v>
       </c>
       <c r="AS10">
-        <v>7.5463</v>
+        <v>7.5464</v>
       </c>
       <c r="AT10">
-        <v>7.302699999999999</v>
+        <v>7.3029</v>
       </c>
       <c r="AU10">
-        <v>7.406769729557718</v>
+        <v>7.40619827397423</v>
       </c>
       <c r="AV10">
-        <v>7.639320180294854</v>
+        <v>7.639867817350514</v>
       </c>
       <c r="AW10">
-        <v>-0.01848989179363153</v>
+        <v>-0.01857862371803382</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01848989179363153</v>
+        <v>0.01857862371803382</v>
       </c>
       <c r="AZ10">
-        <v>0.4621341761186041</v>
+        <v>0.4569662142620839</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3378658238813958</v>
+        <v>0.3430337857379161</v>
       </c>
       <c r="BC10" t="s">
         <v>124</v>
@@ -2981,43 +2981,43 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01232659452908769</v>
+        <v>0.01238574914535588</v>
       </c>
       <c r="BH10">
-        <v>40562.70357722278</v>
+        <v>40368.97519335586</v>
       </c>
       <c r="BI10">
-        <v>40562.70357722278</v>
+        <v>40368.97519335586</v>
       </c>
       <c r="BJ10">
-        <v>5375.177713213467</v>
+        <v>5349.434855474909</v>
       </c>
       <c r="BK10">
-        <v>405.6270357722278</v>
+        <v>403.6897519335586</v>
       </c>
       <c r="BL10">
-        <v>0.004056270357722278</v>
+        <v>0.004036897519335586</v>
       </c>
       <c r="BM10">
-        <v>499.9999999999999</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN10">
-        <v>0.004999999999999999</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO10">
-        <v>0.1051534679714189</v>
+        <v>0.1061842727896242</v>
       </c>
       <c r="BP10">
-        <v>0.1496901367766263</v>
+        <v>0.1466303707363127</v>
       </c>
       <c r="BQ10">
-        <v>0.1043361589865909</v>
+        <v>0.09965132921432279</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT10" t="s">
         <v>126</v>
@@ -3029,7 +3029,7 @@
         <v>127</v>
       </c>
       <c r="BW10" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3037,7 +3037,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3061,19 +3061,19 @@
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.199086584005827</v>
+        <v>1.427443740981068</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" t="s">
         <v>94</v>
@@ -3091,10 +3091,10 @@
         <v>105</v>
       </c>
       <c r="T11">
-        <v>-0.8009341781493173</v>
+        <v>-0.771919016304465</v>
       </c>
       <c r="U11">
-        <v>0.7604161503618175</v>
+        <v>0.7473612893329706</v>
       </c>
       <c r="V11" t="s">
         <v>93</v>
@@ -3103,22 +3103,22 @@
         <v>94</v>
       </c>
       <c r="X11">
-        <v>0.999983080778499</v>
+        <v>0.9999909279838457</v>
       </c>
       <c r="Y11">
-        <v>0.329685621292421</v>
+        <v>0.6685907682296063</v>
       </c>
       <c r="Z11">
-        <v>-124.2504419493343</v>
+        <v>-125.1481539265188</v>
       </c>
       <c r="AA11">
-        <v>-4.999999999999995</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB11">
-        <v>-0.5628113035543927</v>
+        <v>-0.5756926583694939</v>
       </c>
       <c r="AC11">
-        <v>-0.8265854079231045</v>
+        <v>-0.8176661684938817</v>
       </c>
       <c r="AD11" t="s">
         <v>93</v>
@@ -3133,67 +3133,67 @@
         <v>115</v>
       </c>
       <c r="AH11">
-        <v>-0.3741747180665119</v>
+        <v>-0.4802933702777059</v>
       </c>
       <c r="AI11">
-        <v>0.7261714516087068</v>
+        <v>0.7982537553042506</v>
       </c>
       <c r="AJ11">
-        <v>-0.8978914120511587</v>
+        <v>-1.073416863306361</v>
       </c>
       <c r="AK11">
-        <v>-1.347389051822805</v>
+        <v>-1.543823420466639</v>
       </c>
       <c r="AL11">
-        <v>-1.544103667012919</v>
+        <v>-1.816192253452593</v>
       </c>
       <c r="AM11">
-        <v>1.272710087346403</v>
+        <v>1.501229997671825</v>
       </c>
       <c r="AN11">
-        <v>1.396927745736445</v>
+        <v>1.650245314925916</v>
       </c>
       <c r="AO11">
-        <v>0.05735427992379936</v>
+        <v>0.05446013764576514</v>
       </c>
       <c r="AP11">
-        <v>4180.43</v>
+        <v>4138.6</v>
       </c>
       <c r="AQ11">
-        <v>4078.308584387067</v>
+        <v>4020.928220352271</v>
       </c>
       <c r="AR11">
-        <v>4226.132137089084</v>
+        <v>4181.74220740396</v>
       </c>
       <c r="AS11">
-        <v>4180.43</v>
+        <v>4138.6</v>
       </c>
       <c r="AT11">
-        <v>3930.560000000001</v>
+        <v>3846.900000000001</v>
       </c>
       <c r="AU11">
-        <v>4078.308584387067</v>
+        <v>4020.928220352271</v>
       </c>
       <c r="AV11">
-        <v>4310.295</v>
+        <v>4272.2375</v>
       </c>
       <c r="AW11">
-        <v>-0.02442844769866582</v>
+        <v>-0.02843275012026522</v>
       </c>
       <c r="AX11">
-        <v>0.7863659616750752</v>
+        <v>0.8805296391187316</v>
       </c>
       <c r="AY11">
-        <v>0.02442844769866582</v>
+        <v>0.02843275012026522</v>
       </c>
       <c r="AZ11">
-        <v>0.3307977042423221</v>
+        <v>0.3455007098692947</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4692022957576779</v>
+        <v>0.4544992901307053</v>
       </c>
       <c r="BC11" t="s">
         <v>125</v>
@@ -3208,22 +3208,22 @@
         <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.03106498613778963</v>
+        <v>0.03229050886773308</v>
       </c>
       <c r="BH11">
-        <v>16095.29126400494</v>
+        <v>15484.42615283882</v>
       </c>
       <c r="BI11">
-        <v>12071.46844800371</v>
+        <v>11613.31961462912</v>
       </c>
       <c r="BJ11">
-        <v>2.887614060755402</v>
+        <v>2.806098587597041</v>
       </c>
       <c r="BK11">
-        <v>120.7146844800371</v>
+        <v>116.1331961462912</v>
       </c>
       <c r="BL11">
-        <v>0.001207146844800371</v>
+        <v>0.001161331961462912</v>
       </c>
       <c r="BM11">
         <v>375</v>
@@ -3232,19 +3232,19 @@
         <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>593.3901592495364</v>
+        <v>632.6821301217592</v>
       </c>
       <c r="BP11">
-        <v>154.1478394600492</v>
+        <v>192.676452588529</v>
       </c>
       <c r="BQ11">
-        <v>82.3367072127096</v>
+        <v>116.5403466124175</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.0555021536212318</v>
+        <v>0.05582759317056915</v>
       </c>
       <c r="BT11" t="s">
         <v>126</v>
@@ -3256,7 +3256,7 @@
         <v>127</v>
       </c>
       <c r="BW11" s="2">
-        <v>46326</v>
+        <v>46327</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -364,34 +364,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.01479,naive=0.007632,drift4=0.006113; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=2.634,naive=2.238,drift4=4.128; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04163,naive=0.02025,drift4=0.02512; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1295,naive=0.1043,drift4=0.06469; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02399,naive=0.01795,drift4=0.01487; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.05059,naive=0.09364,drift4=0.07769</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.008892,naive=0.01438,drift4=0.01365; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.01936,naive=0.02184,drift4=0.0165; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.1062,naive=0.1466,drift4=0.09965; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=632.7,naive=192.7,drift4=116.5; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.0146,naive=0.007165,drift4=0.005814; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=naive; scores=model=2.615,naive=2.015,drift4=3.742; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04016,naive=0.02057,drift4=0.02487; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1201,naive=0.09703,drift4=0.05787; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.02287,naive=0.01684,drift4=0.01379; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.04875,naive=0.09143,drift4=0.07293</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.00836,naive=0.01401,drift4=0.01291; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.01915,naive=0.0212,drift4=0.01537; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.107,naive=0.1434,drift4=0.09458; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=637.9,naive=194.4,drift4=116; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -994,7 +994,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1117,10 +1117,10 @@
         <v>0.8287599999999999</v>
       </c>
       <c r="AQ2">
-        <v>0.8413485859843923</v>
+        <v>0.8415008889738373</v>
       </c>
       <c r="AR2">
-        <v>0.8414250571719638</v>
+        <v>0.8417812234292146</v>
       </c>
       <c r="AS2">
         <v>0.8287599999999999</v>
@@ -1129,28 +1129,28 @@
         <v>0.847505</v>
       </c>
       <c r="AU2">
-        <v>0.8413485859843923</v>
+        <v>0.8415008889738373</v>
       </c>
       <c r="AV2">
-        <v>0.8203676093437383</v>
+        <v>0.8202660740174417</v>
       </c>
       <c r="AW2">
-        <v>0.01518966405761908</v>
+        <v>0.01537343618639583</v>
       </c>
       <c r="AX2">
         <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.01518966405761908</v>
+        <v>0.01537343618639583</v>
       </c>
       <c r="AZ2">
-        <v>0.3959599758909541</v>
+        <v>0.3939900515462004</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.4040400241090458</v>
+        <v>0.4060099484537996</v>
       </c>
       <c r="BC2" t="s">
         <v>116</v>
@@ -1165,43 +1165,43 @@
         <v>500</v>
       </c>
       <c r="BG2">
-        <v>0.01012644270507939</v>
+        <v>0.01024895745759722</v>
       </c>
       <c r="BH2">
-        <v>49375.68053875443</v>
+        <v>48785.4498439123</v>
       </c>
       <c r="BI2">
-        <v>49375.68053875443</v>
+        <v>48785.4498439123</v>
       </c>
       <c r="BJ2">
-        <v>59577.77950040354</v>
+        <v>58865.5941936294</v>
       </c>
       <c r="BK2">
-        <v>493.7568053875443</v>
+        <v>487.854498439123</v>
       </c>
       <c r="BL2">
-        <v>0.004937568053875443</v>
+        <v>0.00487854498439123</v>
       </c>
       <c r="BM2">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN2">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO2">
-        <v>0.01479440280903969</v>
+        <v>0.01459556389036138</v>
       </c>
       <c r="BP2">
-        <v>0.007631629170536013</v>
+        <v>0.007165162329135994</v>
       </c>
       <c r="BQ2">
-        <v>0.006112744410909562</v>
+        <v>0.005813896021069633</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT2" t="s">
         <v>126</v>
@@ -1213,7 +1213,7 @@
         <v>127</v>
       </c>
       <c r="BW2" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1221,7 +1221,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1344,10 +1344,10 @@
         <v>157.859</v>
       </c>
       <c r="AQ3">
-        <v>159.1777276569718</v>
+        <v>159.1796970605233</v>
       </c>
       <c r="AR3">
-        <v>159.3930274166936</v>
+        <v>159.3927457193804</v>
       </c>
       <c r="AS3">
         <v>157.859</v>
@@ -1356,28 +1356,28 @@
         <v>159.704</v>
       </c>
       <c r="AU3">
-        <v>159.1777276569718</v>
+        <v>159.1796970605233</v>
       </c>
       <c r="AV3">
         <v>156.360875</v>
       </c>
       <c r="AW3">
-        <v>0.008353832578261357</v>
+        <v>0.0083663082910907</v>
       </c>
       <c r="AX3">
-        <v>0.8802520864225253</v>
+        <v>0.8815666653471992</v>
       </c>
       <c r="AY3">
-        <v>0.008353832578261357</v>
+        <v>0.0083663082910907</v>
       </c>
       <c r="AZ3">
-        <v>0.5057434367879905</v>
+        <v>0.4989584052226753</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.2942565632120095</v>
+        <v>0.3010415947773247</v>
       </c>
       <c r="BC3" t="s">
         <v>117</v>
@@ -1416,19 +1416,19 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO3">
-        <v>2.63441354706161</v>
+        <v>2.614664625606945</v>
       </c>
       <c r="BP3">
-        <v>2.237827819188108</v>
+        <v>2.014834792026686</v>
       </c>
       <c r="BQ3">
-        <v>4.1281714346991</v>
+        <v>3.741981589974724</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT3" t="s">
         <v>126</v>
@@ -1440,7 +1440,7 @@
         <v>127</v>
       </c>
       <c r="BW3" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1448,7 +1448,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1571,10 +1571,10 @@
         <v>6.70615</v>
       </c>
       <c r="AQ4">
-        <v>6.720678763840674</v>
+        <v>6.720361301958777</v>
       </c>
       <c r="AR4">
-        <v>6.7408091081622</v>
+        <v>6.739977223397817</v>
       </c>
       <c r="AS4">
         <v>6.70615</v>
@@ -1583,28 +1583,28 @@
         <v>6.705015</v>
       </c>
       <c r="AU4">
-        <v>6.720678763840674</v>
+        <v>6.720361301958777</v>
       </c>
       <c r="AV4">
         <v>6.68264375</v>
       </c>
       <c r="AW4">
-        <v>0.002166483577115587</v>
+        <v>0.002119144659570189</v>
       </c>
       <c r="AX4">
-        <v>0.6180808866013904</v>
+        <v>0.6045754622186378</v>
       </c>
       <c r="AY4">
-        <v>0.002166483577115587</v>
+        <v>0.002119144659570189</v>
       </c>
       <c r="AZ4">
-        <v>0.4312654968444056</v>
+        <v>0.4324468094246091</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3687345031555944</v>
+        <v>0.3675531905753909</v>
       </c>
       <c r="BC4" t="s">
         <v>118</v>
@@ -1643,19 +1643,19 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.04162844935503391</v>
+        <v>0.04015775485452167</v>
       </c>
       <c r="BP4">
-        <v>0.02024959669254959</v>
+        <v>0.02057390409711823</v>
       </c>
       <c r="BQ4">
-        <v>0.02511603358898713</v>
+        <v>0.02487036417177179</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT4" t="s">
         <v>126</v>
@@ -1667,7 +1667,7 @@
         <v>127</v>
       </c>
       <c r="BW4" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1675,7 +1675,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1798,10 +1798,10 @@
         <v>8.87955</v>
       </c>
       <c r="AQ5">
-        <v>8.817659428743085</v>
+        <v>8.817942739119742</v>
       </c>
       <c r="AR5">
-        <v>8.913018329765272</v>
+        <v>8.91564090802841</v>
       </c>
       <c r="AS5">
         <v>8.87955</v>
@@ -1810,28 +1810,28 @@
         <v>8.689349999999999</v>
       </c>
       <c r="AU5">
-        <v>8.817659428743085</v>
+        <v>8.817942739119742</v>
       </c>
       <c r="AV5">
         <v>8.949762499999999</v>
       </c>
       <c r="AW5">
-        <v>-0.006970012135402757</v>
+        <v>-0.006938106196852121</v>
       </c>
       <c r="AX5">
-        <v>0.8814751113678636</v>
+        <v>0.8774400695069799</v>
       </c>
       <c r="AY5">
-        <v>0.006970012135402757</v>
+        <v>0.006938106196852121</v>
       </c>
       <c r="AZ5">
-        <v>0.4035860992828934</v>
+        <v>0.4001607484308423</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3964139007171066</v>
+        <v>0.3998392515691576</v>
       </c>
       <c r="BC5" t="s">
         <v>119</v>
@@ -1870,19 +1870,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.1294778174020023</v>
+        <v>0.120114845355222</v>
       </c>
       <c r="BP5">
-        <v>0.1042955815612341</v>
+        <v>0.09702696824003146</v>
       </c>
       <c r="BQ5">
-        <v>0.06469059202743228</v>
+        <v>0.0578670113369846</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT5" t="s">
         <v>126</v>
@@ -1894,7 +1894,7 @@
         <v>127</v>
       </c>
       <c r="BW5" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1902,7 +1902,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -2025,10 +2025,10 @@
         <v>1.324035</v>
       </c>
       <c r="AQ6">
-        <v>1.312392729165544</v>
+        <v>1.312377208472548</v>
       </c>
       <c r="AR6">
-        <v>1.321111369719784</v>
+        <v>1.321207108702315</v>
       </c>
       <c r="AS6">
         <v>1.324035</v>
@@ -2037,28 +2037,28 @@
         <v>1.2963</v>
       </c>
       <c r="AU6">
-        <v>1.312392729165544</v>
+        <v>1.312377208472548</v>
       </c>
       <c r="AV6">
         <v>1.3371975</v>
       </c>
       <c r="AW6">
-        <v>-0.008793023473288775</v>
+        <v>-0.008804745741202082</v>
       </c>
       <c r="AX6">
-        <v>0.8845030073660728</v>
+        <v>0.8856821673278275</v>
       </c>
       <c r="AY6">
-        <v>0.008793023473288775</v>
+        <v>0.008804745741202082</v>
       </c>
       <c r="AZ6">
-        <v>0.4250361541763325</v>
+        <v>0.422779239389148</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3749638458236675</v>
+        <v>0.377220760610852</v>
       </c>
       <c r="BC6" t="s">
         <v>120</v>
@@ -2097,19 +2097,19 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.02399064598623212</v>
+        <v>0.02287257793309682</v>
       </c>
       <c r="BP6">
-        <v>0.01795120680939846</v>
+        <v>0.01684359236907697</v>
       </c>
       <c r="BQ6">
-        <v>0.01486592917721869</v>
+        <v>0.01379312587301068</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT6" t="s">
         <v>126</v>
@@ -2121,7 +2121,7 @@
         <v>127</v>
       </c>
       <c r="BW6" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2129,7 +2129,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2252,10 +2252,10 @@
         <v>4.66275</v>
       </c>
       <c r="AQ7">
-        <v>4.616797495394381</v>
+        <v>4.616074054699095</v>
       </c>
       <c r="AR7">
-        <v>4.671278093138992</v>
+        <v>4.670937796084543</v>
       </c>
       <c r="AS7">
         <v>4.66275</v>
@@ -2264,28 +2264,28 @@
         <v>4.49447</v>
       </c>
       <c r="AU7">
-        <v>4.616797495394381</v>
+        <v>4.616074054699095</v>
       </c>
       <c r="AV7">
         <v>4.70595</v>
       </c>
       <c r="AW7">
-        <v>-0.009855236631948804</v>
+        <v>-0.01001038985596583</v>
       </c>
       <c r="AX7">
-        <v>1.063715384389343</v>
+        <v>1.080461696780209</v>
       </c>
       <c r="AY7">
-        <v>0.009855236631948804</v>
+        <v>0.01001038985596583</v>
       </c>
       <c r="AZ7">
-        <v>0.5031668899317518</v>
+        <v>0.5021108720930492</v>
       </c>
       <c r="BA7">
-        <v>0.1982619268770551</v>
+        <v>0.1960878043186793</v>
       </c>
       <c r="BB7">
-        <v>0.2985711831911931</v>
+        <v>0.3018013235882716</v>
       </c>
       <c r="BC7" t="s">
         <v>121</v>
@@ -2324,19 +2324,19 @@
         <v>0.005</v>
       </c>
       <c r="BO7">
-        <v>0.05058586155879946</v>
+        <v>0.04874551676730057</v>
       </c>
       <c r="BP7">
-        <v>0.09363814925513671</v>
+        <v>0.09142652215009396</v>
       </c>
       <c r="BQ7">
-        <v>0.07768679267725995</v>
+        <v>0.07292846045054716</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT7" t="s">
         <v>126</v>
@@ -2348,7 +2348,7 @@
         <v>127</v>
       </c>
       <c r="BW7" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2356,7 +2356,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2479,10 +2479,10 @@
         <v>0.6957249999999999</v>
       </c>
       <c r="AQ8">
-        <v>0.6877136500981937</v>
+        <v>0.6876951867292037</v>
       </c>
       <c r="AR8">
-        <v>0.6942461558539956</v>
+        <v>0.6941896408823138</v>
       </c>
       <c r="AS8">
         <v>0.6957249999999999</v>
@@ -2491,28 +2491,28 @@
         <v>0.6713049999999998</v>
       </c>
       <c r="AU8">
-        <v>0.6877136500981937</v>
+        <v>0.6876951867292037</v>
       </c>
       <c r="AV8">
         <v>0.7029337499999999</v>
       </c>
       <c r="AW8">
-        <v>-0.01151510999576871</v>
+        <v>-0.01154164831046206</v>
       </c>
       <c r="AX8">
-        <v>1.111336903319752</v>
+        <v>1.113898147500786</v>
       </c>
       <c r="AY8">
-        <v>0.01151510999576871</v>
+        <v>0.01154164831046206</v>
       </c>
       <c r="AZ8">
-        <v>0.5023569941959377</v>
+        <v>0.5027907926707393</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.2976430058040623</v>
+        <v>0.2972092073292606</v>
       </c>
       <c r="BC8" t="s">
         <v>122</v>
@@ -2551,19 +2551,19 @@
         <v>0.004559536984525354</v>
       </c>
       <c r="BO8">
-        <v>0.008891634072827208</v>
+        <v>0.008360260038126522</v>
       </c>
       <c r="BP8">
-        <v>0.01438092731696102</v>
+        <v>0.01400817312972545</v>
       </c>
       <c r="BQ8">
-        <v>0.0136540694814981</v>
+        <v>0.01291188476453448</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT8" t="s">
         <v>126</v>
@@ -2575,7 +2575,7 @@
         <v>127</v>
       </c>
       <c r="BW8" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2583,7 +2583,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2706,10 +2706,10 @@
         <v>1.125215</v>
       </c>
       <c r="AQ9">
-        <v>1.108365606871953</v>
+        <v>1.108208173798799</v>
       </c>
       <c r="AR9">
-        <v>1.115897827062754</v>
+        <v>1.115880044489722</v>
       </c>
       <c r="AS9">
         <v>1.125215</v>
@@ -2718,28 +2718,28 @@
         <v>1.089085</v>
       </c>
       <c r="AU9">
-        <v>1.108365606871953</v>
+        <v>1.108208173798799</v>
       </c>
       <c r="AV9">
-        <v>1.136447928752032</v>
+        <v>1.136552884134134</v>
       </c>
       <c r="AW9">
-        <v>-0.0149743765662985</v>
+        <v>-0.01511429033669237</v>
       </c>
       <c r="AX9">
         <v>1.5</v>
       </c>
       <c r="AY9">
-        <v>0.0149743765662985</v>
+        <v>0.01511429033669237</v>
       </c>
       <c r="AZ9">
-        <v>0.4495835833998097</v>
+        <v>0.4440064954309816</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3504164166001904</v>
+        <v>0.3559935045690184</v>
       </c>
       <c r="BC9" t="s">
         <v>123</v>
@@ -2754,22 +2754,22 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.009982917710865664</v>
+        <v>0.01007619355779491</v>
       </c>
       <c r="BH9">
-        <v>50085.55759763372</v>
+        <v>49621.91299046667</v>
       </c>
       <c r="BI9">
-        <v>50085.55759763372</v>
+        <v>49621.91299046667</v>
       </c>
       <c r="BJ9">
-        <v>44511.98890668336</v>
+        <v>44099.93911427297</v>
       </c>
       <c r="BK9">
-        <v>500.8555759763372</v>
+        <v>496.2191299046667</v>
       </c>
       <c r="BL9">
-        <v>0.005008555759763372</v>
+        <v>0.004962191299046667</v>
       </c>
       <c r="BM9">
         <v>500</v>
@@ -2778,19 +2778,19 @@
         <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.01936187273214413</v>
+        <v>0.01914590299958203</v>
       </c>
       <c r="BP9">
-        <v>0.02184267473234254</v>
+        <v>0.0211961669519198</v>
       </c>
       <c r="BQ9">
-        <v>0.01650432232271824</v>
+        <v>0.01536950092134931</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT9" t="s">
         <v>126</v>
@@ -2802,7 +2802,7 @@
         <v>127</v>
       </c>
       <c r="BW9" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2810,7 +2810,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2933,10 +2933,10 @@
         <v>7.5464</v>
       </c>
       <c r="AQ10">
-        <v>7.40619827397423</v>
+        <v>7.405995202757335</v>
       </c>
       <c r="AR10">
-        <v>7.422379892101859</v>
+        <v>7.423409137310402</v>
       </c>
       <c r="AS10">
         <v>7.5464</v>
@@ -2945,28 +2945,28 @@
         <v>7.3029</v>
       </c>
       <c r="AU10">
-        <v>7.40619827397423</v>
+        <v>7.405995202757335</v>
       </c>
       <c r="AV10">
-        <v>7.639867817350514</v>
+        <v>7.640003198161777</v>
       </c>
       <c r="AW10">
-        <v>-0.01857862371803382</v>
+        <v>-0.01860553339905981</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01857862371803382</v>
+        <v>0.01860553339905981</v>
       </c>
       <c r="AZ10">
-        <v>0.4569662142620839</v>
+        <v>0.4513782437694108</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3430337857379161</v>
+        <v>0.3486217562305892</v>
       </c>
       <c r="BC10" t="s">
         <v>124</v>
@@ -2981,43 +2981,43 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01238574914535588</v>
+        <v>0.01240368893270654</v>
       </c>
       <c r="BH10">
-        <v>40368.97519335586</v>
+        <v>40310.5884638545</v>
       </c>
       <c r="BI10">
-        <v>40368.97519335586</v>
+        <v>40310.5884638545</v>
       </c>
       <c r="BJ10">
-        <v>5349.434855474909</v>
+        <v>5341.697824638833</v>
       </c>
       <c r="BK10">
-        <v>403.6897519335586</v>
+        <v>403.105884638545</v>
       </c>
       <c r="BL10">
-        <v>0.004036897519335586</v>
+        <v>0.00403105884638545</v>
       </c>
       <c r="BM10">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN10">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.1061842727896242</v>
+        <v>0.1070123281722849</v>
       </c>
       <c r="BP10">
-        <v>0.1466303707363127</v>
+        <v>0.143425720531775</v>
       </c>
       <c r="BQ10">
-        <v>0.09965132921432279</v>
+        <v>0.0945800576534486</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT10" t="s">
         <v>126</v>
@@ -3029,7 +3029,7 @@
         <v>127</v>
       </c>
       <c r="BW10" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3037,7 +3037,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3160,7 +3160,7 @@
         <v>4138.6</v>
       </c>
       <c r="AQ11">
-        <v>4020.928220352271</v>
+        <v>4020.60298775407</v>
       </c>
       <c r="AR11">
         <v>4181.74220740396</v>
@@ -3172,28 +3172,28 @@
         <v>3846.900000000001</v>
       </c>
       <c r="AU11">
-        <v>4020.928220352271</v>
+        <v>4020.60298775407</v>
       </c>
       <c r="AV11">
         <v>4272.2375</v>
       </c>
       <c r="AW11">
-        <v>-0.02843275012026522</v>
+        <v>-0.02851133529356082</v>
       </c>
       <c r="AX11">
-        <v>0.8805296391187316</v>
+        <v>0.8829633317439393</v>
       </c>
       <c r="AY11">
-        <v>0.02843275012026522</v>
+        <v>0.02851133529356082</v>
       </c>
       <c r="AZ11">
-        <v>0.3455007098692947</v>
+        <v>0.3445294087877428</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4544992901307053</v>
+        <v>0.4554705912122572</v>
       </c>
       <c r="BC11" t="s">
         <v>125</v>
@@ -3232,19 +3232,19 @@
         <v>0.00375</v>
       </c>
       <c r="BO11">
-        <v>632.6821301217592</v>
+        <v>637.8668022490939</v>
       </c>
       <c r="BP11">
-        <v>192.676452588529</v>
+        <v>194.3750123445652</v>
       </c>
       <c r="BQ11">
-        <v>116.5403466124175</v>
+        <v>115.9837236719726</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05582759317056915</v>
+        <v>0.05571636696741809</v>
       </c>
       <c r="BT11" t="s">
         <v>126</v>
@@ -3256,7 +3256,7 @@
         <v>127</v>
       </c>
       <c r="BW11" s="2">
-        <v>46327</v>
+        <v>46328</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="134">
   <si>
     <t>Pair</t>
   </si>
@@ -241,30 +241,30 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
     <t>GBPCNH</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -277,13 +277,13 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>LOW</t>
+    <t>FLAT</t>
   </si>
   <si>
     <t>LONG</t>
@@ -292,109 +292,127 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
+    <t>CONFLICT</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
+    <t>REDUCE_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>REDUCE_CONFLICT</t>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_DECELERATING</t>
   </si>
   <si>
     <t>UP_STEADY</t>
   </si>
   <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
     <t>DOWN_STEADY</t>
   </si>
   <si>
-    <t>DOWN_ACCELERATING</t>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>空头减速</t>
   </si>
   <si>
     <t>多头稳态</t>
   </si>
   <si>
-    <t>空头减速</t>
-  </si>
-  <si>
     <t>空头稳态</t>
   </si>
   <si>
-    <t>空头加速</t>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>转换</t>
   </si>
   <si>
     <t>上涨</t>
   </si>
   <si>
-    <t>下跌</t>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
   </si>
   <si>
     <t>UP_SLOPE</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
-  </si>
-  <si>
     <t>DOWN_SLOPE</t>
   </si>
   <si>
-    <t>DOWN_STEEPENING</t>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
   </si>
   <si>
     <t>上升坡延续</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
-  </si>
-  <si>
     <t>下降坡延续</t>
   </si>
   <si>
-    <t>下降陡坡形成</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.0146,naive=0.007165,drift4=0.005814; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=naive; scores=model=2.615,naive=2.015,drift4=3.742; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.04016,naive=0.02057,drift4=0.02487; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1201,naive=0.09703,drift4=0.05787; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.02287,naive=0.01684,drift4=0.01379; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.04875,naive=0.09143,drift4=0.07293</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=model; scores=model=0.00836,naive=0.01401,drift4=0.01291; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.01915,naive=0.0212,drift4=0.01537; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.107,naive=0.1434,drift4=0.09458; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=637.9,naive=194.4,drift4=116; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.02074,naive=0.01739,drift4=0.0123; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=2.696,naive=1.58,drift4=3.013; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.01589,naive=0.006808,drift4=0.005304; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03712,naive=0.01719,drift4=0.01965; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.109,naive=0.06791,drift4=0.07211; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=model; scores=model=0.0532,naive=0.0715,drift4=0.06247; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.01013,naive=0.01055,drift4=0.01108; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02039,naive=0.01177,drift4=0.01463; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.1026,naive=0.1235,drift4=0.07793; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=608.6,naive=162.4,drift4=100.9; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -994,7 +1012,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1009,151 +1027,142 @@
         <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
         <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2.465037919765153</v>
+        <v>3.256613153033321</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="P2" t="s">
         <v>96</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T2">
-        <v>0.9962834818469217</v>
+        <v>-0.9199361538026168</v>
       </c>
       <c r="U2">
-        <v>0.9981878746310084</v>
+        <v>0.9639637521852494</v>
       </c>
       <c r="V2" t="s">
         <v>92</v>
       </c>
       <c r="W2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9994412311995745</v>
+        <v>0.9999699318962872</v>
       </c>
       <c r="Y2">
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>6.991186755245489</v>
+        <v>-147.1263839496164</v>
       </c>
       <c r="AA2">
-        <v>-25</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB2">
-        <v>0.992564885858424</v>
+        <v>-0.8398699001648156</v>
       </c>
       <c r="AC2">
-        <v>0.1217166683772349</v>
+        <v>-0.5427877585181364</v>
       </c>
       <c r="AD2" t="s">
         <v>92</v>
       </c>
       <c r="AE2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AF2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AG2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AH2">
-        <v>0.9920102715678084</v>
+        <v>-0.8398446468695522</v>
       </c>
       <c r="AI2">
-        <v>0.9928469825342465</v>
+        <v>0.9458517462217577</v>
       </c>
       <c r="AJ2">
-        <v>1.960061041963213</v>
+        <v>-2.547891424492321</v>
       </c>
       <c r="AK2">
-        <v>0.3500288017584413</v>
+        <v>-1.693309253773119</v>
       </c>
       <c r="AL2">
-        <v>2.708348477042971</v>
+        <v>-3.732074298369752</v>
       </c>
       <c r="AM2">
-        <v>-4.670177103758457</v>
+        <v>5.170479060669843</v>
       </c>
       <c r="AN2">
-        <v>2.285629500781877</v>
+        <v>3.236897597500552</v>
       </c>
       <c r="AO2">
-        <v>0.03151276095421195</v>
+        <v>0.04065799994258394</v>
       </c>
       <c r="AP2">
-        <v>0.8287599999999999</v>
+        <v>1.125345</v>
       </c>
       <c r="AQ2">
-        <v>0.8415008889738373</v>
+        <v>1.125134288537906</v>
       </c>
       <c r="AR2">
-        <v>0.8417812234292146</v>
+        <v>1.15626968011145</v>
       </c>
       <c r="AS2">
-        <v>0.8287599999999999</v>
+        <v>1.125345</v>
       </c>
       <c r="AT2">
-        <v>0.847505</v>
-      </c>
-      <c r="AU2">
-        <v>0.8415008889738373</v>
-      </c>
-      <c r="AV2">
-        <v>0.8202660740174417</v>
+        <v>1.090795</v>
       </c>
       <c r="AW2">
-        <v>0.01537343618639583</v>
-      </c>
-      <c r="AX2">
-        <v>1.5</v>
+        <v>-0.000187241656642337</v>
       </c>
       <c r="AY2">
-        <v>0.01537343618639583</v>
+        <v>0.000187241656642337</v>
       </c>
       <c r="AZ2">
-        <v>0.3939900515462004</v>
+        <v>0.4189297067387882</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.4060099484537996</v>
+        <v>0.3810702932612118</v>
       </c>
       <c r="BC2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1162,58 +1171,55 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>500</v>
-      </c>
-      <c r="BG2">
-        <v>0.01024895745759722</v>
+        <v>0</v>
       </c>
       <c r="BH2">
-        <v>48785.4498439123</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>48785.4498439123</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>58865.5941936294</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>487.854498439123</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>0.00487854498439123</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.01459556389036138</v>
+        <v>0.02074145600507162</v>
       </c>
       <c r="BP2">
-        <v>0.007165162329135994</v>
+        <v>0.01739231066546624</v>
       </c>
       <c r="BQ2">
-        <v>0.005813896021069633</v>
+        <v>0.01229772261637768</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="BU2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BV2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="BW2" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1221,7 +1227,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1233,7 +1239,7 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
         <v>90</v>
@@ -1242,25 +1248,25 @@
         <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J3" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.1759201018796525</v>
+        <v>0.002177776906038563</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P3" t="s">
         <v>97</v>
@@ -1269,118 +1275,118 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T3">
-        <v>-0.7976630934848853</v>
+        <v>-0.6507469057837999</v>
       </c>
       <c r="U3">
-        <v>0.7588861098037478</v>
+        <v>0.6678042029930771</v>
       </c>
       <c r="V3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="W3" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="X3">
-        <v>0.9997508709421974</v>
+        <v>0.9998723815614684</v>
       </c>
       <c r="Y3">
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>114.0381403485021</v>
+        <v>91.78558942711715</v>
       </c>
       <c r="AA3">
-        <v>18</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB3">
-        <v>-0.407344676974959</v>
+        <v>-0.03115937024934096</v>
       </c>
       <c r="AC3">
-        <v>0.9132745009799443</v>
+        <v>0.9995144289332017</v>
       </c>
       <c r="AD3" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AG3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AH3">
-        <v>-0.2036215977896917</v>
+        <v>-0.01557769686958205</v>
       </c>
       <c r="AI3">
-        <v>0.6134016422533884</v>
+        <v>0.4448547990031296</v>
       </c>
       <c r="AJ3">
-        <v>-0.2296472657165816</v>
+        <v>-0.03853955374076883</v>
       </c>
       <c r="AK3">
-        <v>0.6035889157375692</v>
+        <v>1.023611027881948</v>
       </c>
       <c r="AL3">
-        <v>-0.2556816737650891</v>
+        <v>0.02052277034608236</v>
       </c>
       <c r="AM3">
-        <v>0.3946921492060487</v>
+        <v>0.2014498284857335</v>
       </c>
       <c r="AN3">
-        <v>0.2433294980053786</v>
+        <v>0.08409136317548631</v>
       </c>
       <c r="AO3">
-        <v>0.05809710445912196</v>
+        <v>0.4296556374545773</v>
       </c>
       <c r="AP3">
-        <v>157.859</v>
+        <v>158.325</v>
       </c>
       <c r="AQ3">
-        <v>159.1796970605233</v>
+        <v>160.7458868424893</v>
       </c>
       <c r="AR3">
-        <v>159.3927457193804</v>
+        <v>160.1690033653171</v>
       </c>
       <c r="AS3">
-        <v>157.859</v>
+        <v>158.325</v>
       </c>
       <c r="AT3">
-        <v>159.704</v>
+        <v>163.135</v>
       </c>
       <c r="AU3">
-        <v>159.1796970605233</v>
+        <v>160.7458868424893</v>
       </c>
       <c r="AV3">
-        <v>156.360875</v>
+        <v>156.7110754383405</v>
       </c>
       <c r="AW3">
-        <v>0.0083663082910907</v>
+        <v>0.01529061640605903</v>
       </c>
       <c r="AX3">
-        <v>0.8815666653471992</v>
+        <v>1.5</v>
       </c>
       <c r="AY3">
-        <v>0.0083663082910907</v>
+        <v>0.01529061640605903</v>
       </c>
       <c r="AZ3">
-        <v>0.4989584052226753</v>
+        <v>0.4811580501551425</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3010415947773247</v>
+        <v>0.3188419498448576</v>
       </c>
       <c r="BC3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1392,55 +1398,55 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.009490272965114538</v>
+        <v>0.01019374427070602</v>
       </c>
       <c r="BH3">
-        <v>52685.52357113003</v>
+        <v>49049.69035145022</v>
       </c>
       <c r="BI3">
-        <v>52685.52357113003</v>
+        <v>49049.69035145022</v>
       </c>
       <c r="BJ3">
-        <v>333.7505214851863</v>
+        <v>309.8038234735527</v>
       </c>
       <c r="BK3">
-        <v>526.8552357113002</v>
+        <v>490.4969035145022</v>
       </c>
       <c r="BL3">
-        <v>0.005268552357113002</v>
+        <v>0.004904969035145022</v>
       </c>
       <c r="BM3">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN3">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>2.614664625606945</v>
+        <v>2.695770751454349</v>
       </c>
       <c r="BP3">
-        <v>2.014834792026686</v>
+        <v>1.579982334883066</v>
       </c>
       <c r="BQ3">
-        <v>3.741981589974724</v>
+        <v>3.012788336553901</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU3" t="s">
         <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW3" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1448,7 +1454,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1472,142 +1478,142 @@
         <v>93</v>
       </c>
       <c r="J4" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>1.285725995326295</v>
+        <v>2.696719377268863</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="O4" t="s">
         <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T4">
-        <v>-0.9993283430045486</v>
+        <v>0.9889860594949241</v>
       </c>
       <c r="U4">
-        <v>0.8490288919884816</v>
+        <v>0.994894244187264</v>
       </c>
       <c r="V4" t="s">
         <v>93</v>
       </c>
       <c r="W4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X4">
-        <v>0.997324550545739</v>
+        <v>0.9994020696581923</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4">
-        <v>176.4025569540482</v>
+        <v>-12.05007180912457</v>
       </c>
       <c r="AA4">
-        <v>53.00000000000001</v>
+        <v>-25</v>
       </c>
       <c r="AB4">
-        <v>-0.9980295296037169</v>
+        <v>0.97796552948057</v>
       </c>
       <c r="AC4">
-        <v>0.06274598026155627</v>
+        <v>-0.2087664320425777</v>
       </c>
       <c r="AD4" t="s">
         <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AF4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AG4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="AH4">
-        <v>-0.4976796760217012</v>
+        <v>0.9773807742172516</v>
       </c>
       <c r="AI4">
-        <v>0.7935656771619158</v>
+        <v>0.9881850231608122</v>
       </c>
       <c r="AJ4">
-        <v>-0.927412727153209</v>
+        <v>2.120294982223862</v>
       </c>
       <c r="AK4">
-        <v>0.1440315104885368</v>
+        <v>-0.3438991264746123</v>
       </c>
       <c r="AL4">
-        <v>-1.816656800577983</v>
+        <v>3.047661417731772</v>
       </c>
       <c r="AM4">
-        <v>0.6012046257110735</v>
+        <v>-4.240237424373629</v>
       </c>
       <c r="AN4">
-        <v>1.771224108307004</v>
+        <v>2.684528356714271</v>
       </c>
       <c r="AO4">
-        <v>0.03271182940138548</v>
+        <v>0.03330240042484071</v>
       </c>
       <c r="AP4">
-        <v>6.70615</v>
+        <v>0.832335</v>
       </c>
       <c r="AQ4">
-        <v>6.720361301958777</v>
+        <v>0.8412785922560549</v>
       </c>
       <c r="AR4">
-        <v>6.739977223397817</v>
+        <v>0.8383694593080617</v>
       </c>
       <c r="AS4">
-        <v>6.70615</v>
+        <v>0.832335</v>
       </c>
       <c r="AT4">
-        <v>6.705015</v>
+        <v>0.8482250000000001</v>
       </c>
       <c r="AU4">
-        <v>6.720361301958777</v>
+        <v>0.8412785922560549</v>
       </c>
       <c r="AV4">
-        <v>6.68264375</v>
+        <v>0.82496375</v>
       </c>
       <c r="AW4">
-        <v>0.002119144659570189</v>
+        <v>0.01074518343702343</v>
       </c>
       <c r="AX4">
-        <v>0.6045754622186378</v>
+        <v>1.213307411369149</v>
       </c>
       <c r="AY4">
-        <v>0.002119144659570189</v>
+        <v>0.01074518343702343</v>
       </c>
       <c r="AZ4">
-        <v>0.4324468094246091</v>
+        <v>0.382364383826005</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3675531905753909</v>
+        <v>0.417635616173995</v>
       </c>
       <c r="BC4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1619,22 +1625,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.003505178082804533</v>
+        <v>0.008856109619324011</v>
       </c>
       <c r="BH4">
-        <v>142646.1047593748</v>
+        <v>56458.19908427975</v>
       </c>
       <c r="BI4">
-        <v>142646.1047593748</v>
+        <v>56458.19908427975</v>
       </c>
       <c r="BJ4">
-        <v>21270.9385801652</v>
+        <v>67831.10055960611</v>
       </c>
       <c r="BK4">
-        <v>1426.461047593748</v>
+        <v>564.5819908427975</v>
       </c>
       <c r="BL4">
-        <v>0.01426461047593748</v>
+        <v>0.005645819908427975</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1643,31 +1649,31 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.04015775485452167</v>
+        <v>0.01589280173866453</v>
       </c>
       <c r="BP4">
-        <v>0.02057390409711823</v>
+        <v>0.006807506596170394</v>
       </c>
       <c r="BQ4">
-        <v>0.02487036417177179</v>
+        <v>0.005304479483922261</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU4" t="s">
         <v>90</v>
       </c>
       <c r="BV4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW4" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1675,7 +1681,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1687,154 +1693,154 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1.570244421407061</v>
+        <v>1.461090899523458</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="O5" t="s">
         <v>94</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T5">
-        <v>-0.9962572872601604</v>
+        <v>-0.9986655881761152</v>
       </c>
       <c r="U5">
-        <v>0.9982219692857099</v>
+        <v>0.8491583172689934</v>
       </c>
       <c r="V5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X5">
-        <v>0.999624760074551</v>
+        <v>0.9990352103589665</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>-172.9845108296907</v>
+        <v>174.9313750264995</v>
       </c>
       <c r="AA5">
-        <v>-19</v>
+        <v>25</v>
       </c>
       <c r="AB5">
-        <v>-0.9925131695778808</v>
+        <v>-0.99608959436648</v>
       </c>
       <c r="AC5">
-        <v>-0.122137660917789</v>
+        <v>0.0883488539530722</v>
       </c>
       <c r="AD5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AF5" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="AG5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AH5">
-        <v>-0.9921407390101213</v>
+        <v>-0.497564288722147</v>
       </c>
       <c r="AI5">
-        <v>0.9923127082335879</v>
+        <v>0.792502680820846</v>
       </c>
       <c r="AJ5">
-        <v>-1.246160489784905</v>
+        <v>-1.03560922134312</v>
       </c>
       <c r="AK5">
-        <v>-0.2061656177606775</v>
+        <v>0.1340434818816628</v>
       </c>
       <c r="AL5">
-        <v>-1.722603599910343</v>
+        <v>-2.148195515030185</v>
       </c>
       <c r="AM5">
-        <v>2.679459988838541</v>
+        <v>0.5831554618618305</v>
       </c>
       <c r="AN5">
-        <v>1.484448322388167</v>
+        <v>2.083980118395606</v>
       </c>
       <c r="AO5">
-        <v>0.03539939110579538</v>
+        <v>0.03991014076490834</v>
       </c>
       <c r="AP5">
-        <v>8.87955</v>
+        <v>6.702685000000001</v>
       </c>
       <c r="AQ5">
-        <v>8.817942739119742</v>
+        <v>6.743230552550399</v>
       </c>
       <c r="AR5">
-        <v>8.91564090802841</v>
+        <v>6.803670919197419</v>
       </c>
       <c r="AS5">
-        <v>8.87955</v>
+        <v>6.702685000000001</v>
       </c>
       <c r="AT5">
-        <v>8.689349999999999</v>
+        <v>6.697545000000002</v>
       </c>
       <c r="AU5">
-        <v>8.817942739119742</v>
+        <v>6.743230552550399</v>
       </c>
       <c r="AV5">
-        <v>8.949762499999999</v>
+        <v>6.675654631633068</v>
       </c>
       <c r="AW5">
-        <v>-0.006938106196852121</v>
+        <v>0.006049150832897287</v>
       </c>
       <c r="AX5">
-        <v>0.8774400695069799</v>
+        <v>1.5</v>
       </c>
       <c r="AY5">
-        <v>0.006938106196852121</v>
+        <v>0.006049150832897287</v>
       </c>
       <c r="AZ5">
-        <v>0.4001607484308423</v>
+        <v>0.4207977927364186</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3998392515691576</v>
+        <v>0.3792022072635814</v>
       </c>
       <c r="BC5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1846,22 +1852,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.007907213766463316</v>
+        <v>0.004032767221931525</v>
       </c>
       <c r="BH5">
-        <v>63233.39861135897</v>
+        <v>123984.3443680147</v>
       </c>
       <c r="BI5">
-        <v>63233.39861135897</v>
+        <v>123984.3443680147</v>
       </c>
       <c r="BJ5">
-        <v>7121.239095602702</v>
+        <v>18497.71313555905</v>
       </c>
       <c r="BK5">
-        <v>632.3339861135897</v>
+        <v>1239.843443680146</v>
       </c>
       <c r="BL5">
-        <v>0.006323339861135898</v>
+        <v>0.01239843443680146</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1870,31 +1876,31 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.120114845355222</v>
+        <v>0.03711910361811745</v>
       </c>
       <c r="BP5">
-        <v>0.09702696824003146</v>
+        <v>0.01719439126974981</v>
       </c>
       <c r="BQ5">
-        <v>0.0578670113369846</v>
+        <v>0.01965447369598544</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW5" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1902,7 +1908,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1914,7 +1920,7 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
         <v>91</v>
@@ -1923,145 +1929,145 @@
         <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>2.146278781367343</v>
+        <v>1.506347676435477</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="O6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T6">
-        <v>-0.9971076933219547</v>
+        <v>-0.9978536348105105</v>
       </c>
       <c r="U6">
-        <v>0.9984662328369414</v>
+        <v>0.9989361574110378</v>
       </c>
       <c r="V6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9990710833682475</v>
+        <v>0.9996080869852325</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>-173.8328374355906</v>
+        <v>174.6886794591638</v>
       </c>
       <c r="AA6">
-        <v>-30.99999999999999</v>
+        <v>-21</v>
       </c>
       <c r="AB6">
-        <v>-0.9942126974340801</v>
+        <v>-0.9957064281027668</v>
       </c>
       <c r="AC6">
-        <v>-0.1074295688386122</v>
+        <v>0.09256732163582181</v>
       </c>
       <c r="AD6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="AG6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AH6">
-        <v>-0.993289156723934</v>
+        <v>-0.9953161977947057</v>
       </c>
       <c r="AI6">
-        <v>0.9925145540429726</v>
+        <v>0.9936570242774376</v>
       </c>
       <c r="AJ6">
-        <v>-1.73512953719635</v>
+        <v>-1.216661059825341</v>
       </c>
       <c r="AK6">
-        <v>-0.313789042006236</v>
+        <v>0.05698617845660994</v>
       </c>
       <c r="AL6">
-        <v>-2.212107403362016</v>
+        <v>-1.560013788358898</v>
       </c>
       <c r="AM6">
-        <v>4.1232762300579</v>
+        <v>2.84983750976704</v>
       </c>
       <c r="AN6">
-        <v>1.846950093617659</v>
+        <v>1.31691237659644</v>
       </c>
       <c r="AO6">
-        <v>0.03616089577425368</v>
+        <v>0.0327848973214919</v>
       </c>
       <c r="AP6">
-        <v>1.324035</v>
+        <v>8.893829999999999</v>
       </c>
       <c r="AQ6">
-        <v>1.312377208472548</v>
+        <v>8.827935909289558</v>
       </c>
       <c r="AR6">
-        <v>1.321207108702315</v>
+        <v>8.887568777580498</v>
       </c>
       <c r="AS6">
-        <v>1.324035</v>
+        <v>8.893829999999999</v>
       </c>
       <c r="AT6">
-        <v>1.2963</v>
+        <v>8.720999999999998</v>
       </c>
       <c r="AU6">
-        <v>1.312377208472548</v>
+        <v>8.827935909289558</v>
       </c>
       <c r="AV6">
-        <v>1.3371975</v>
+        <v>8.949942499999999</v>
       </c>
       <c r="AW6">
-        <v>-0.008804745741202082</v>
+        <v>-0.007408966745535045</v>
       </c>
       <c r="AX6">
-        <v>0.8856821673278275</v>
+        <v>1.174321064120174</v>
       </c>
       <c r="AY6">
-        <v>0.008804745741202082</v>
+        <v>0.007408966745535045</v>
       </c>
       <c r="AZ6">
-        <v>0.422779239389148</v>
+        <v>0.4344746376888231</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.377220760610852</v>
+        <v>0.365525362311177</v>
       </c>
       <c r="BC6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2073,22 +2079,22 @@
         <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.009941202460660001</v>
+        <v>0.006309149151715166</v>
       </c>
       <c r="BH6">
-        <v>50295.72649572663</v>
+        <v>79249.9888616634</v>
       </c>
       <c r="BI6">
-        <v>50295.72649572663</v>
+        <v>79249.9888616634</v>
       </c>
       <c r="BJ6">
-        <v>37986.70465337142</v>
+        <v>8910.670527957405</v>
       </c>
       <c r="BK6">
-        <v>502.9572649572663</v>
+        <v>792.4998886166339</v>
       </c>
       <c r="BL6">
-        <v>0.005029572649572663</v>
+        <v>0.007924998886166339</v>
       </c>
       <c r="BM6">
         <v>500</v>
@@ -2097,31 +2103,31 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.02287257793309682</v>
+        <v>0.1089524077517103</v>
       </c>
       <c r="BP6">
-        <v>0.01684359236907697</v>
+        <v>0.06791435132412199</v>
       </c>
       <c r="BQ6">
-        <v>0.01379312587301068</v>
+        <v>0.07211022188834387</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU6" t="s">
         <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW6" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2129,7 +2135,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2141,7 +2147,7 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
@@ -2150,145 +2156,145 @@
         <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J7" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1.463615183089874</v>
+        <v>1.41384031359683</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T7">
-        <v>-0.8450594482724709</v>
+        <v>-0.9312053040770206</v>
       </c>
       <c r="U7">
-        <v>0.9302633338376369</v>
+        <v>0.9689152835989751</v>
       </c>
       <c r="V7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X7">
-        <v>0.9999463284600998</v>
+        <v>0.9994915870572633</v>
       </c>
       <c r="Y7">
         <v>1</v>
       </c>
       <c r="Z7">
-        <v>-133.6388628858862</v>
+        <v>-149.5843723307099</v>
       </c>
       <c r="AA7">
-        <v>-7.999999999999998</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AB7">
-        <v>-0.6901105802005867</v>
+        <v>-0.8623756142488881</v>
       </c>
       <c r="AC7">
-        <v>-0.72370393607829</v>
+        <v>-0.5062689995929565</v>
       </c>
       <c r="AD7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AF7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AH7">
-        <v>-0.6900735409030458</v>
+        <v>-0.8619371713251034</v>
       </c>
       <c r="AI7">
-        <v>0.899352430585687</v>
+        <v>0.9528918082725243</v>
       </c>
       <c r="AJ7">
-        <v>-1.106432633112826</v>
+        <v>-1.123718285723238</v>
       </c>
       <c r="AK7">
-        <v>-1.199374953179614</v>
+        <v>-0.7452867368265162</v>
       </c>
       <c r="AL7">
-        <v>-1.849504232112959</v>
+        <v>-1.552801375349311</v>
       </c>
       <c r="AM7">
-        <v>1.904964899468453</v>
+        <v>2.72310269088192</v>
       </c>
       <c r="AN7">
-        <v>1.640925519332009</v>
+        <v>1.291695185302931</v>
       </c>
       <c r="AO7">
-        <v>0.05107972290349189</v>
+        <v>0.03761954314789425</v>
       </c>
       <c r="AP7">
-        <v>4.66275</v>
+        <v>4.67878</v>
       </c>
       <c r="AQ7">
-        <v>4.616074054699095</v>
+        <v>4.634894458762735</v>
       </c>
       <c r="AR7">
-        <v>4.670937796084543</v>
+        <v>4.673628236402769</v>
       </c>
       <c r="AS7">
-        <v>4.66275</v>
+        <v>4.67878</v>
       </c>
       <c r="AT7">
-        <v>4.49447</v>
+        <v>4.54991</v>
       </c>
       <c r="AU7">
-        <v>4.616074054699095</v>
+        <v>4.634894458762735</v>
       </c>
       <c r="AV7">
-        <v>4.70595</v>
+        <v>4.721425</v>
       </c>
       <c r="AW7">
-        <v>-0.01001038985596583</v>
+        <v>-0.009379697535952598</v>
       </c>
       <c r="AX7">
-        <v>1.080461696780209</v>
+        <v>1.02908995749242</v>
       </c>
       <c r="AY7">
-        <v>0.01001038985596583</v>
+        <v>0.009379697535952598</v>
       </c>
       <c r="AZ7">
-        <v>0.5021108720930492</v>
+        <v>0.478591196288746</v>
       </c>
       <c r="BA7">
-        <v>0.1960878043186793</v>
+        <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3018013235882716</v>
+        <v>0.321408803711254</v>
       </c>
       <c r="BC7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2300,22 +2306,22 @@
         <v>500</v>
       </c>
       <c r="BG7">
-        <v>0.009264918771111401</v>
+        <v>0.009114555503785185</v>
       </c>
       <c r="BH7">
-        <v>53967.01388888928</v>
+        <v>54857.31035291353</v>
       </c>
       <c r="BI7">
-        <v>53967.01388888928</v>
+        <v>54857.31035291353</v>
       </c>
       <c r="BJ7">
-        <v>11574.07407407416</v>
+        <v>11724.70395122522</v>
       </c>
       <c r="BK7">
-        <v>539.6701388888928</v>
+        <v>548.5731035291352</v>
       </c>
       <c r="BL7">
-        <v>0.005396701388888927</v>
+        <v>0.005485731035291352</v>
       </c>
       <c r="BM7">
         <v>500</v>
@@ -2324,31 +2330,31 @@
         <v>0.005</v>
       </c>
       <c r="BO7">
-        <v>0.04874551676730057</v>
+        <v>0.05320166801388212</v>
       </c>
       <c r="BP7">
-        <v>0.09142652215009396</v>
+        <v>0.07150128445095107</v>
       </c>
       <c r="BQ7">
-        <v>0.07292846045054716</v>
+        <v>0.06247093602912388</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU7" t="s">
         <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW7" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2356,7 +2362,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2368,7 +2374,7 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
         <v>91</v>
@@ -2377,145 +2383,145 @@
         <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J8" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K8">
-        <v>0.6476295876202839</v>
+        <v>0.5206325096177565</v>
       </c>
       <c r="L8">
-        <v>2.221462233986172</v>
+        <v>2.114622406007593</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q8">
-        <v>0.9119073969050709</v>
+        <v>0.8801581274044391</v>
       </c>
       <c r="R8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T8">
-        <v>-0.8152999060570199</v>
+        <v>-0.9471943794584506</v>
       </c>
       <c r="U8">
-        <v>0.8639857864506869</v>
+        <v>0.9038615815922336</v>
       </c>
       <c r="V8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9998255623279414</v>
+        <v>0.9981169375730693</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0.9303371883403148</v>
       </c>
       <c r="Z8">
-        <v>-130.6716504042479</v>
+        <v>-154.212432023279</v>
       </c>
       <c r="AA8">
-        <v>-12.99999999999999</v>
+        <v>-37.99999999999999</v>
       </c>
       <c r="AB8">
-        <v>-0.6517232038624154</v>
+        <v>-0.90041318653816</v>
       </c>
       <c r="AC8">
-        <v>-0.7584568976199693</v>
+        <v>-0.4350357381965263</v>
       </c>
       <c r="AD8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AF8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AH8">
-        <v>-0.6516095187839072</v>
+        <v>-0.8674140530242463</v>
       </c>
       <c r="AI8">
-        <v>0.8876921592364666</v>
+        <v>0.9501034015349541</v>
       </c>
       <c r="AJ8">
-        <v>-1.709742231684434</v>
+        <v>-1.730949690210708</v>
       </c>
       <c r="AK8">
-        <v>-2.112879613523765</v>
+        <v>-1.059460664405853</v>
       </c>
       <c r="AL8">
-        <v>-2.676659359883749</v>
+        <v>-2.102664683571918</v>
       </c>
       <c r="AM8">
-        <v>3.48691946774025</v>
+        <v>4.863130987710345</v>
       </c>
       <c r="AN8">
-        <v>2.299539616987486</v>
+        <v>1.648412988117296</v>
       </c>
       <c r="AO8">
-        <v>0.05175832491358315</v>
+        <v>0.03619280163420795</v>
       </c>
       <c r="AP8">
-        <v>0.6957249999999999</v>
+        <v>0.69811</v>
       </c>
       <c r="AQ8">
-        <v>0.6876951867292037</v>
+        <v>0.6914529257505855</v>
       </c>
       <c r="AR8">
-        <v>0.6941896408823138</v>
+        <v>0.6966185852863654</v>
       </c>
       <c r="AS8">
-        <v>0.6957249999999999</v>
+        <v>0.69811</v>
       </c>
       <c r="AT8">
-        <v>0.6713049999999998</v>
+        <v>0.67987</v>
       </c>
       <c r="AU8">
-        <v>0.6876951867292037</v>
+        <v>0.6914529257505855</v>
       </c>
       <c r="AV8">
-        <v>0.7029337499999999</v>
+        <v>0.70391</v>
       </c>
       <c r="AW8">
-        <v>-0.01154164831046206</v>
+        <v>-0.00953585287335023</v>
       </c>
       <c r="AX8">
-        <v>1.113898147500786</v>
+        <v>1.147771422312845</v>
       </c>
       <c r="AY8">
-        <v>0.01154164831046206</v>
+        <v>0.00953585287335023</v>
       </c>
       <c r="AZ8">
-        <v>0.5027907926707393</v>
+        <v>0.4737669250814356</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.2972092073292606</v>
+        <v>0.3262330749185643</v>
       </c>
       <c r="BC8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2524,58 +2530,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>455.9536984525355</v>
+        <v>440.0790637022196</v>
       </c>
       <c r="BG8">
-        <v>0.01036149340615894</v>
+        <v>0.008308146280672139</v>
       </c>
       <c r="BH8">
-        <v>48255.59216230321</v>
+        <v>60181.89655172386</v>
       </c>
       <c r="BI8">
-        <v>44004.63143483867</v>
+        <v>52969.58537261294</v>
       </c>
       <c r="BJ8">
-        <v>63250.03619941596</v>
+        <v>75875.70063831337</v>
       </c>
       <c r="BK8">
-        <v>440.0463143483867</v>
+        <v>529.6958537261294</v>
       </c>
       <c r="BL8">
-        <v>0.004400463143483867</v>
+        <v>0.005296958537261294</v>
       </c>
       <c r="BM8">
-        <v>455.9536984525354</v>
+        <v>440.0790637022196</v>
       </c>
       <c r="BN8">
-        <v>0.004559536984525354</v>
+        <v>0.004400790637022196</v>
       </c>
       <c r="BO8">
-        <v>0.008360260038126522</v>
+        <v>0.01013385624181444</v>
       </c>
       <c r="BP8">
-        <v>0.01400817312972545</v>
+        <v>0.01055374653169943</v>
       </c>
       <c r="BQ8">
-        <v>0.01291188476453448</v>
+        <v>0.01107590721002824</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT8" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU8" t="s">
         <v>91</v>
       </c>
       <c r="BV8" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW8" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2583,7 +2589,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2595,7 +2601,7 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
         <v>91</v>
@@ -2604,145 +2610,145 @@
         <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>3.052787287013346</v>
+        <v>1.974934095296505</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T9">
-        <v>-0.891041205370296</v>
+        <v>-0.9971996562992052</v>
       </c>
       <c r="U9">
-        <v>0.9509582065410651</v>
+        <v>0.9985561363126866</v>
       </c>
       <c r="V9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X9">
-        <v>0.9999586564977279</v>
+        <v>0.9992651639121771</v>
       </c>
       <c r="Y9">
-        <v>1</v>
+        <v>0.8503939498892883</v>
       </c>
       <c r="Z9">
-        <v>-141.4512221898441</v>
+        <v>173.7705818678119</v>
       </c>
       <c r="AA9">
-        <v>-3.999999999999993</v>
+        <v>-25</v>
       </c>
       <c r="AB9">
-        <v>-0.7820779058161692</v>
+        <v>-0.9940953813917636</v>
       </c>
       <c r="AC9">
-        <v>-0.6231806714221768</v>
+        <v>0.1085097815662903</v>
       </c>
       <c r="AD9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AF9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="AH9">
-        <v>-0.7820455719764932</v>
+        <v>-0.9190581859065532</v>
       </c>
       <c r="AI9">
-        <v>0.9274205860666791</v>
+        <v>0.9630370270288057</v>
       </c>
       <c r="AJ9">
-        <v>-2.322853513699059</v>
+        <v>-1.656667388225915</v>
       </c>
       <c r="AK9">
-        <v>-1.88145753411371</v>
+        <v>0.08241201497533358</v>
       </c>
       <c r="AL9">
-        <v>-3.775023293907783</v>
+        <v>-1.77255413036166</v>
       </c>
       <c r="AM9">
-        <v>3.724128517196357</v>
+        <v>4.572304537091131</v>
       </c>
       <c r="AN9">
-        <v>3.393437940830339</v>
+        <v>1.397114876266881</v>
       </c>
       <c r="AO9">
-        <v>0.0479221030158419</v>
+        <v>0.03342123157228699</v>
       </c>
       <c r="AP9">
-        <v>1.125215</v>
+        <v>1.326815</v>
       </c>
       <c r="AQ9">
-        <v>1.108208173798799</v>
+        <v>1.313752245007693</v>
       </c>
       <c r="AR9">
-        <v>1.115880044489722</v>
+        <v>1.31809250107805</v>
       </c>
       <c r="AS9">
-        <v>1.125215</v>
+        <v>1.326815</v>
       </c>
       <c r="AT9">
-        <v>1.089085</v>
+        <v>1.301035</v>
       </c>
       <c r="AU9">
-        <v>1.108208173798799</v>
+        <v>1.313752245007693</v>
       </c>
       <c r="AV9">
-        <v>1.136552884134134</v>
+        <v>1.338465</v>
       </c>
       <c r="AW9">
-        <v>-0.01511429033669237</v>
+        <v>-0.009845196950823774</v>
       </c>
       <c r="AX9">
-        <v>1.5</v>
+        <v>1.121266522944829</v>
       </c>
       <c r="AY9">
-        <v>0.01511429033669237</v>
+        <v>0.009845196950823774</v>
       </c>
       <c r="AZ9">
-        <v>0.4440064954309816</v>
+        <v>0.4432797613844443</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3559935045690184</v>
+        <v>0.3567202386155557</v>
       </c>
       <c r="BC9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2754,22 +2760,22 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.01007619355779491</v>
+        <v>0.008780425304205931</v>
       </c>
       <c r="BH9">
-        <v>49621.91299046667</v>
+        <v>56944.84978540777</v>
       </c>
       <c r="BI9">
-        <v>49621.91299046667</v>
+        <v>56944.84978540777</v>
       </c>
       <c r="BJ9">
-        <v>44099.93911427297</v>
+        <v>42918.45493562234</v>
       </c>
       <c r="BK9">
-        <v>496.2191299046667</v>
+        <v>569.4484978540777</v>
       </c>
       <c r="BL9">
-        <v>0.004962191299046667</v>
+        <v>0.005694484978540777</v>
       </c>
       <c r="BM9">
         <v>500</v>
@@ -2778,31 +2784,31 @@
         <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.01914590299958203</v>
+        <v>0.02038591771463159</v>
       </c>
       <c r="BP9">
-        <v>0.0211961669519198</v>
+        <v>0.01176897456789048</v>
       </c>
       <c r="BQ9">
-        <v>0.01536950092134931</v>
+        <v>0.01463473880735201</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU9" t="s">
         <v>91</v>
       </c>
       <c r="BV9" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW9" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2810,7 +2816,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2822,7 +2828,7 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
         <v>91</v>
@@ -2831,145 +2837,145 @@
         <v>91</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>3.1134405973988</v>
+        <v>3.143653764222756</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T10">
-        <v>-0.9179262337987019</v>
+        <v>-0.9318473998340459</v>
       </c>
       <c r="U10">
-        <v>0.9630490710525563</v>
+        <v>0.9693302174354312</v>
       </c>
       <c r="V10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X10">
-        <v>0.9999290633725623</v>
+        <v>0.9999955500404425</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-146.7040998612845</v>
+        <v>-149.7339664761072</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AB10">
-        <v>-0.8358466451482032</v>
+        <v>-0.8636944963904277</v>
       </c>
       <c r="AC10">
-        <v>-0.548963009495625</v>
+        <v>-0.5040156911296367</v>
       </c>
       <c r="AD10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AF10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AH10">
-        <v>-0.8357873530061413</v>
+        <v>-0.8636906529848487</v>
       </c>
       <c r="AI10">
-        <v>0.9438551948879159</v>
+        <v>0.952854627449048</v>
       </c>
       <c r="AJ10">
-        <v>-2.350144667876241</v>
+        <v>-2.416449289337514</v>
       </c>
       <c r="AK10">
-        <v>-1.543515783805872</v>
+        <v>-1.436407037481282</v>
       </c>
       <c r="AL10">
-        <v>-3.933391754439335</v>
+        <v>-3.791539223637096</v>
       </c>
       <c r="AM10">
-        <v>3.431344064360473</v>
+        <v>4.317520847982976</v>
       </c>
       <c r="AN10">
-        <v>3.588006011818242</v>
+        <v>3.369330601403916</v>
       </c>
       <c r="AO10">
-        <v>0.04582647224627837</v>
+        <v>0.04168109321489994</v>
       </c>
       <c r="AP10">
-        <v>7.5464</v>
+        <v>7.5442</v>
       </c>
       <c r="AQ10">
-        <v>7.405995202757335</v>
+        <v>7.444494758812539</v>
       </c>
       <c r="AR10">
-        <v>7.423409137310402</v>
+        <v>7.510684976994754</v>
       </c>
       <c r="AS10">
-        <v>7.5464</v>
+        <v>7.5442</v>
       </c>
       <c r="AT10">
-        <v>7.3029</v>
+        <v>7.3095</v>
       </c>
       <c r="AU10">
-        <v>7.405995202757335</v>
+        <v>7.444494758812539</v>
       </c>
       <c r="AV10">
-        <v>7.640003198161777</v>
+        <v>7.610670160791641</v>
       </c>
       <c r="AW10">
-        <v>-0.01860553339905981</v>
+        <v>-0.01321614501040021</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01860553339905981</v>
+        <v>0.01321614501040021</v>
       </c>
       <c r="AZ10">
-        <v>0.4513782437694108</v>
+        <v>0.4376805869298792</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3486217562305892</v>
+        <v>0.3623194130701208</v>
       </c>
       <c r="BC10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2981,22 +2987,22 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.01240368893270654</v>
+        <v>0.008810763340266807</v>
       </c>
       <c r="BH10">
-        <v>40310.5884638545</v>
+        <v>56748.77200649666</v>
       </c>
       <c r="BI10">
-        <v>40310.5884638545</v>
+        <v>56748.77200649666</v>
       </c>
       <c r="BJ10">
-        <v>5341.697824638833</v>
+        <v>7522.17226564734</v>
       </c>
       <c r="BK10">
-        <v>403.105884638545</v>
+        <v>567.4877200649667</v>
       </c>
       <c r="BL10">
-        <v>0.00403105884638545</v>
+        <v>0.005674877200649666</v>
       </c>
       <c r="BM10">
         <v>500</v>
@@ -3005,31 +3011,31 @@
         <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.1070123281722849</v>
+        <v>0.1025947435030273</v>
       </c>
       <c r="BP10">
-        <v>0.143425720531775</v>
+        <v>0.1235147620335832</v>
       </c>
       <c r="BQ10">
-        <v>0.0945800576534486</v>
+        <v>0.07792545720117591</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT10" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU10" t="s">
         <v>91</v>
       </c>
       <c r="BV10" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW10" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3037,7 +3043,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3049,7 +3055,7 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
         <v>91</v>
@@ -3058,145 +3064,145 @@
         <v>91</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J11" s="2">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.427443740981068</v>
+        <v>1.599304465565033</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T11">
-        <v>-0.771919016304465</v>
+        <v>-0.9369233410214868</v>
       </c>
       <c r="U11">
-        <v>0.7473612893329706</v>
+        <v>0.8214132020955007</v>
       </c>
       <c r="V11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X11">
-        <v>0.9999909279838457</v>
+        <v>0.9991907945433268</v>
       </c>
       <c r="Y11">
-        <v>0.6685907682296063</v>
+        <v>0.2482464792281063</v>
       </c>
       <c r="Z11">
-        <v>-125.1481539265188</v>
+        <v>-148.6047692938305</v>
       </c>
       <c r="AA11">
-        <v>-3.000000000000004</v>
+        <v>-25</v>
       </c>
       <c r="AB11">
-        <v>-0.5756926583694939</v>
+        <v>-0.853594163097612</v>
       </c>
       <c r="AC11">
-        <v>-0.8176661684938817</v>
+        <v>-0.5209385805694251</v>
       </c>
       <c r="AD11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AF11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AH11">
-        <v>-0.4802933702777059</v>
+        <v>-0.5323168518364058</v>
       </c>
       <c r="AI11">
-        <v>0.7982537553042506</v>
+        <v>0.7990491246692972</v>
       </c>
       <c r="AJ11">
-        <v>-1.073416863306361</v>
+        <v>-1.255285529206324</v>
       </c>
       <c r="AK11">
-        <v>-1.543823420466639</v>
+        <v>-0.8723776306932588</v>
       </c>
       <c r="AL11">
-        <v>-1.816192253452593</v>
+        <v>-1.811219957742462</v>
       </c>
       <c r="AM11">
-        <v>1.501229997671825</v>
+        <v>2.541659773996094</v>
       </c>
       <c r="AN11">
-        <v>1.650245314925916</v>
+        <v>1.564963027451948</v>
       </c>
       <c r="AO11">
-        <v>0.05446013764576514</v>
+        <v>0.04263465463848008</v>
       </c>
       <c r="AP11">
-        <v>4138.6</v>
+        <v>4164.190000000001</v>
       </c>
       <c r="AQ11">
-        <v>4020.60298775407</v>
+        <v>4059.231636985722</v>
       </c>
       <c r="AR11">
-        <v>4181.74220740396</v>
+        <v>4101.572363305086</v>
       </c>
       <c r="AS11">
-        <v>4138.6</v>
+        <v>4164.190000000001</v>
       </c>
       <c r="AT11">
-        <v>3846.900000000001</v>
+        <v>3981.700000000003</v>
       </c>
       <c r="AU11">
-        <v>4020.60298775407</v>
+        <v>4059.231636985722</v>
       </c>
       <c r="AV11">
-        <v>4272.2375</v>
+        <v>4297.827500000001</v>
       </c>
       <c r="AW11">
-        <v>-0.02851133529356082</v>
+        <v>-0.02520498896887022</v>
       </c>
       <c r="AX11">
-        <v>0.8829633317439393</v>
+        <v>0.7853960378956475</v>
       </c>
       <c r="AY11">
-        <v>0.02851133529356082</v>
+        <v>0.02520498896887022</v>
       </c>
       <c r="AZ11">
-        <v>0.3445294087877428</v>
+        <v>0.3423110703280764</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4554705912122572</v>
+        <v>0.4576889296719236</v>
       </c>
       <c r="BC11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3208,55 +3214,55 @@
         <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.03229050886773308</v>
+        <v>0.03209207552969488</v>
       </c>
       <c r="BH11">
-        <v>15484.42615283882</v>
+        <v>15580.17023664763</v>
       </c>
       <c r="BI11">
-        <v>11613.31961462912</v>
+        <v>11685.12767748573</v>
       </c>
       <c r="BJ11">
         <v>2.806098587597041</v>
       </c>
       <c r="BK11">
-        <v>116.1331961462912</v>
+        <v>116.8512767748573</v>
       </c>
       <c r="BL11">
-        <v>0.001161331961462912</v>
+        <v>0.001168512767748573</v>
       </c>
       <c r="BM11">
-        <v>375</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN11">
-        <v>0.00375</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO11">
-        <v>637.8668022490939</v>
+        <v>608.5603399473235</v>
       </c>
       <c r="BP11">
-        <v>194.3750123445652</v>
+        <v>162.4205869871446</v>
       </c>
       <c r="BQ11">
-        <v>115.9837236719726</v>
+        <v>100.9496079619278</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05571636696741809</v>
+        <v>0.05419478678603245</v>
       </c>
       <c r="BT11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="BU11" t="s">
         <v>91</v>
       </c>
       <c r="BV11" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BW11" s="2">
-        <v>46328</v>
+        <v>46330</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="130">
   <si>
     <t>Pair</t>
   </si>
@@ -241,27 +241,27 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>GBPCNH</t>
   </si>
   <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>GBPUSD</t>
   </si>
   <si>
@@ -277,15 +277,12 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
@@ -304,115 +301,106 @@
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
-    <t>UP_STEADY</t>
-  </si>
-  <si>
-    <t>DOWN_STEADY</t>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
   </si>
   <si>
     <t>空头加速</t>
   </si>
   <si>
-    <t>空头减速</t>
-  </si>
-  <si>
-    <t>多头稳态</t>
-  </si>
-  <si>
-    <t>空头稳态</t>
-  </si>
-  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
     <t>下跌</t>
   </si>
   <si>
-    <t>转换</t>
-  </si>
-  <si>
-    <t>上涨</t>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
   </si>
   <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
-    <t>UP_SLOPE</t>
-  </si>
-  <si>
-    <t>DOWN_SLOPE</t>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>地形转换区</t>
-  </si>
-  <si>
-    <t>上升坡延续</t>
-  </si>
-  <si>
-    <t>下降坡延续</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.02074,naive=0.01739,drift4=0.0123; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=2.696,naive=1.58,drift4=3.013; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.01589,naive=0.006808,drift4=0.005304; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03712,naive=0.01719,drift4=0.01965; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.109,naive=0.06791,drift4=0.07211; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=model; scores=model=0.0532,naive=0.0715,drift4=0.06247; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.01013,naive=0.01055,drift4=0.01108; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02039,naive=0.01177,drift4=0.01463; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=0.1026,naive=0.1235,drift4=0.07793; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=608.6,naive=162.4,drift4=100.9; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.699,naive=1.356,drift4=2.593; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.0152,naive=0.006315,drift4=0.005002; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03592,naive=0.0172,drift4=0.01891; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.02052,naive=0.01638,drift4=0.01107; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.102,naive=0.05951,drift4=0.06966; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.009849,naive=0.009901,drift4=0.01032; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.05241,naive=0.06774,drift4=0.0581; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01927,naive=0.0105,drift4=0.01417; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.1008,naive=0.1181,drift4=0.07261; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=595.6,naive=159.1,drift4=99.76; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -1033,136 +1021,145 @@
         <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J2" s="2">
         <v>46301</v>
       </c>
       <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0.002177776906038563</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+      <c r="N2">
+        <v>46</v>
+      </c>
+      <c r="O2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q2">
         <v>1</v>
       </c>
-      <c r="L2">
-        <v>3.256613153033321</v>
-      </c>
-      <c r="M2">
-        <v>6</v>
-      </c>
-      <c r="N2">
-        <v>12</v>
-      </c>
-      <c r="O2" t="s">
-        <v>89</v>
-      </c>
-      <c r="P2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q2">
+      <c r="R2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S2" t="s">
+        <v>101</v>
+      </c>
+      <c r="T2">
+        <v>-0.6507469057837999</v>
+      </c>
+      <c r="U2">
+        <v>0.6678042029930771</v>
+      </c>
+      <c r="V2" t="s">
+        <v>105</v>
+      </c>
+      <c r="W2" t="s">
+        <v>105</v>
+      </c>
+      <c r="X2">
+        <v>0.9998723815614684</v>
+      </c>
+      <c r="Y2">
         <v>0</v>
       </c>
-      <c r="R2" t="s">
-        <v>99</v>
-      </c>
-      <c r="S2" t="s">
-        <v>103</v>
-      </c>
-      <c r="T2">
-        <v>-0.9199361538026168</v>
-      </c>
-      <c r="U2">
-        <v>0.9639637521852494</v>
-      </c>
-      <c r="V2" t="s">
-        <v>92</v>
-      </c>
-      <c r="W2" t="s">
-        <v>95</v>
-      </c>
-      <c r="X2">
-        <v>0.9999699318962872</v>
-      </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
       <c r="Z2">
-        <v>-147.1263839496164</v>
+        <v>91.78558942711715</v>
       </c>
       <c r="AA2">
-        <v>-5.999999999999996</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB2">
-        <v>-0.8398699001648156</v>
+        <v>-0.03115937024934096</v>
       </c>
       <c r="AC2">
-        <v>-0.5427877585181364</v>
+        <v>0.9995144289332017</v>
       </c>
       <c r="AD2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="AE2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AG2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AH2">
-        <v>-0.8398446468695522</v>
+        <v>-0.01557769686958205</v>
       </c>
       <c r="AI2">
-        <v>0.9458517462217577</v>
+        <v>0.4448547990031296</v>
       </c>
       <c r="AJ2">
-        <v>-2.547891424492321</v>
+        <v>-0.03853955374076883</v>
       </c>
       <c r="AK2">
-        <v>-1.693309253773119</v>
+        <v>1.023611027881948</v>
       </c>
       <c r="AL2">
-        <v>-3.732074298369752</v>
+        <v>0.02052277034608236</v>
       </c>
       <c r="AM2">
-        <v>5.170479060669843</v>
+        <v>0.2014498284857335</v>
       </c>
       <c r="AN2">
-        <v>3.236897597500552</v>
+        <v>0.08409136317548631</v>
       </c>
       <c r="AO2">
-        <v>0.04065799994258394</v>
+        <v>0.4296556374545773</v>
       </c>
       <c r="AP2">
-        <v>1.125345</v>
+        <v>158.325</v>
       </c>
       <c r="AQ2">
-        <v>1.125134288537906</v>
+        <v>160.9913260037643</v>
       </c>
       <c r="AR2">
-        <v>1.15626968011145</v>
+        <v>160.6247098451819</v>
       </c>
       <c r="AS2">
-        <v>1.125345</v>
+        <v>158.325</v>
       </c>
       <c r="AT2">
-        <v>1.090795</v>
+        <v>163.135</v>
+      </c>
+      <c r="AU2">
+        <v>160.9913260037643</v>
+      </c>
+      <c r="AV2">
+        <v>156.5474493308238</v>
       </c>
       <c r="AW2">
-        <v>-0.000187241656642337</v>
+        <v>0.01684084006798852</v>
+      </c>
+      <c r="AX2">
+        <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.000187241656642337</v>
+        <v>0.01684084006798852</v>
       </c>
       <c r="AZ2">
-        <v>0.4189297067387882</v>
+        <v>0.4707320362818145</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3810702932612118</v>
+        <v>0.3292679637181854</v>
       </c>
       <c r="BC2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1171,52 +1168,55 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="BG2">
+        <v>0.01122722671199235</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>44534.59548170747</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>44534.59548170747</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>281.2859338809884</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>445.3459548170748</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>0.004453459548170748</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="BO2">
-        <v>0.02074145600507162</v>
+        <v>2.698702711289627</v>
       </c>
       <c r="BP2">
-        <v>0.01739231066546624</v>
+        <v>1.356418458894436</v>
       </c>
       <c r="BQ2">
-        <v>0.01229772261637768</v>
+        <v>2.592607718475479</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BU2" t="s">
         <v>89</v>
       </c>
       <c r="BV2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="BW2" s="2">
         <v>46330</v>
@@ -1239,13 +1239,13 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s">
         <v>92</v>
@@ -1254,139 +1254,139 @@
         <v>46301</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0.002177776906038563</v>
+        <v>2.696719377268863</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N3">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="O3" t="s">
         <v>94</v>
       </c>
       <c r="P3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T3">
-        <v>-0.6507469057837999</v>
+        <v>0.9889860594949241</v>
       </c>
       <c r="U3">
-        <v>0.6678042029930771</v>
+        <v>0.994894244187264</v>
       </c>
       <c r="V3" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="W3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="X3">
-        <v>0.9998723815614684</v>
+        <v>0.9994020696581923</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>91.78558942711715</v>
+        <v>-12.05007180912457</v>
       </c>
       <c r="AA3">
-        <v>-3.000000000000004</v>
+        <v>-25</v>
       </c>
       <c r="AB3">
-        <v>-0.03115937024934096</v>
+        <v>0.97796552948057</v>
       </c>
       <c r="AC3">
-        <v>0.9995144289332017</v>
+        <v>-0.2087664320425777</v>
       </c>
       <c r="AD3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE3" t="s">
         <v>108</v>
       </c>
-      <c r="AE3" t="s">
-        <v>110</v>
-      </c>
       <c r="AF3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AG3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AH3">
-        <v>-0.01557769686958205</v>
+        <v>0.9773807742172516</v>
       </c>
       <c r="AI3">
-        <v>0.4448547990031296</v>
+        <v>0.9881850231608122</v>
       </c>
       <c r="AJ3">
-        <v>-0.03853955374076883</v>
+        <v>2.120294982223862</v>
       </c>
       <c r="AK3">
-        <v>1.023611027881948</v>
+        <v>-0.3438991264746123</v>
       </c>
       <c r="AL3">
-        <v>0.02052277034608236</v>
+        <v>3.047661417731772</v>
       </c>
       <c r="AM3">
-        <v>0.2014498284857335</v>
+        <v>-4.240237424373629</v>
       </c>
       <c r="AN3">
-        <v>0.08409136317548631</v>
+        <v>2.684528356714271</v>
       </c>
       <c r="AO3">
-        <v>0.4296556374545773</v>
+        <v>0.03330240042484071</v>
       </c>
       <c r="AP3">
-        <v>158.325</v>
+        <v>0.832335</v>
       </c>
       <c r="AQ3">
-        <v>160.7458868424893</v>
+        <v>0.8402490251588426</v>
       </c>
       <c r="AR3">
-        <v>160.1690033653171</v>
+        <v>0.8356661940352523</v>
       </c>
       <c r="AS3">
-        <v>158.325</v>
+        <v>0.832335</v>
       </c>
       <c r="AT3">
-        <v>163.135</v>
+        <v>0.8482250000000001</v>
       </c>
       <c r="AU3">
-        <v>160.7458868424893</v>
+        <v>0.8402490251588426</v>
       </c>
       <c r="AV3">
-        <v>156.7110754383405</v>
+        <v>0.82496375</v>
       </c>
       <c r="AW3">
-        <v>0.01529061640605903</v>
+        <v>0.00950822103941627</v>
       </c>
       <c r="AX3">
-        <v>1.5</v>
+        <v>1.073634072761402</v>
       </c>
       <c r="AY3">
-        <v>0.01529061640605903</v>
+        <v>0.00950822103941627</v>
       </c>
       <c r="AZ3">
-        <v>0.4811580501551425</v>
+        <v>0.3820406856054071</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3188419498448576</v>
+        <v>0.4179593143945929</v>
       </c>
       <c r="BC3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1398,22 +1398,22 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.01019374427070602</v>
+        <v>0.008856109619324011</v>
       </c>
       <c r="BH3">
-        <v>49049.69035145022</v>
+        <v>56458.19908427975</v>
       </c>
       <c r="BI3">
-        <v>49049.69035145022</v>
+        <v>56458.19908427975</v>
       </c>
       <c r="BJ3">
-        <v>309.8038234735527</v>
+        <v>67831.10055960611</v>
       </c>
       <c r="BK3">
-        <v>490.4969035145022</v>
+        <v>564.5819908427975</v>
       </c>
       <c r="BL3">
-        <v>0.004904969035145022</v>
+        <v>0.005645819908427975</v>
       </c>
       <c r="BM3">
         <v>500</v>
@@ -1422,28 +1422,28 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>2.695770751454349</v>
+        <v>0.01520208853300778</v>
       </c>
       <c r="BP3">
-        <v>1.579982334883066</v>
+        <v>0.006314615167071252</v>
       </c>
       <c r="BQ3">
-        <v>3.012788336553901</v>
+        <v>0.005002395209896033</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BV3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW3" s="2">
         <v>46330</v>
@@ -1466,154 +1466,154 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J4" s="2">
         <v>46301</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2.696719377268863</v>
+        <v>1.461090899523458</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="O4" t="s">
+        <v>93</v>
+      </c>
+      <c r="P4" t="s">
         <v>95</v>
-      </c>
-      <c r="P4" t="s">
-        <v>98</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="T4">
-        <v>0.9889860594949241</v>
+        <v>-0.9986655881761152</v>
       </c>
       <c r="U4">
-        <v>0.994894244187264</v>
+        <v>0.8491583172689934</v>
       </c>
       <c r="V4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="W4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9994020696581923</v>
+        <v>0.9990352103589665</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>-12.05007180912457</v>
+        <v>174.9313750264995</v>
       </c>
       <c r="AA4">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="AB4">
-        <v>0.97796552948057</v>
+        <v>-0.99608959436648</v>
       </c>
       <c r="AC4">
-        <v>-0.2087664320425777</v>
+        <v>0.0883488539530722</v>
       </c>
       <c r="AD4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AE4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AH4">
-        <v>0.9773807742172516</v>
+        <v>-0.497564288722147</v>
       </c>
       <c r="AI4">
-        <v>0.9881850231608122</v>
+        <v>0.792502680820846</v>
       </c>
       <c r="AJ4">
-        <v>2.120294982223862</v>
+        <v>-1.03560922134312</v>
       </c>
       <c r="AK4">
-        <v>-0.3438991264746123</v>
+        <v>0.1340434818816628</v>
       </c>
       <c r="AL4">
-        <v>3.047661417731772</v>
+        <v>-2.148195515030185</v>
       </c>
       <c r="AM4">
-        <v>-4.240237424373629</v>
+        <v>0.5831554618618305</v>
       </c>
       <c r="AN4">
-        <v>2.684528356714271</v>
+        <v>2.083980118395606</v>
       </c>
       <c r="AO4">
-        <v>0.03330240042484071</v>
+        <v>0.03991014076490834</v>
       </c>
       <c r="AP4">
-        <v>0.832335</v>
+        <v>6.702685000000001</v>
       </c>
       <c r="AQ4">
-        <v>0.8412785922560549</v>
+        <v>6.73931299702166</v>
       </c>
       <c r="AR4">
-        <v>0.8383694593080617</v>
+        <v>6.794668241336089</v>
       </c>
       <c r="AS4">
-        <v>0.832335</v>
+        <v>6.702685000000001</v>
       </c>
       <c r="AT4">
-        <v>0.8482250000000001</v>
+        <v>6.697545000000002</v>
       </c>
       <c r="AU4">
-        <v>0.8412785922560549</v>
+        <v>6.73931299702166</v>
       </c>
       <c r="AV4">
-        <v>0.82496375</v>
+        <v>6.678266335318894</v>
       </c>
       <c r="AW4">
-        <v>0.01074518343702343</v>
+        <v>0.005464675278885878</v>
       </c>
       <c r="AX4">
-        <v>1.213307411369149</v>
+        <v>1.5</v>
       </c>
       <c r="AY4">
-        <v>0.01074518343702343</v>
+        <v>0.005464675278885878</v>
       </c>
       <c r="AZ4">
-        <v>0.382364383826005</v>
+        <v>0.4194670241768401</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.417635616173995</v>
+        <v>0.3805329758231599</v>
       </c>
       <c r="BC4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1625,22 +1625,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.008856109619324011</v>
+        <v>0.003643116852590586</v>
       </c>
       <c r="BH4">
-        <v>56458.19908427975</v>
+        <v>137245.117362748</v>
       </c>
       <c r="BI4">
-        <v>56458.19908427975</v>
+        <v>137245.117362748</v>
       </c>
       <c r="BJ4">
-        <v>67831.10055960611</v>
+        <v>20476.14013828011</v>
       </c>
       <c r="BK4">
-        <v>564.5819908427975</v>
+        <v>1372.45117362748</v>
       </c>
       <c r="BL4">
-        <v>0.005645819908427975</v>
+        <v>0.0137245117362748</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1649,28 +1649,28 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.01589280173866453</v>
+        <v>0.03591883909300873</v>
       </c>
       <c r="BP4">
-        <v>0.006807506596170394</v>
+        <v>0.01720029375025792</v>
       </c>
       <c r="BQ4">
-        <v>0.005304479483922261</v>
+        <v>0.01890963456037817</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="BV4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW4" s="2">
         <v>46330</v>
@@ -1702,145 +1702,145 @@
         <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J5" s="2">
         <v>46301</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1.461090899523458</v>
+        <v>3.256613153033321</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="O5" t="s">
         <v>94</v>
       </c>
       <c r="P5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T5">
-        <v>-0.9986655881761152</v>
+        <v>-0.9199361538026168</v>
       </c>
       <c r="U5">
-        <v>0.8491583172689934</v>
+        <v>0.9639637521852494</v>
       </c>
       <c r="V5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X5">
-        <v>0.9990352103589665</v>
+        <v>0.9999699318962872</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>174.9313750264995</v>
+        <v>-147.1263839496164</v>
       </c>
       <c r="AA5">
-        <v>25</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB5">
-        <v>-0.99608959436648</v>
+        <v>-0.8398699001648156</v>
       </c>
       <c r="AC5">
-        <v>0.0883488539530722</v>
+        <v>-0.5427877585181364</v>
       </c>
       <c r="AD5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE5" t="s">
         <v>109</v>
       </c>
       <c r="AF5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AH5">
-        <v>-0.497564288722147</v>
+        <v>-0.8398446468695522</v>
       </c>
       <c r="AI5">
-        <v>0.792502680820846</v>
+        <v>0.9458517462217577</v>
       </c>
       <c r="AJ5">
-        <v>-1.03560922134312</v>
+        <v>-2.547891424492321</v>
       </c>
       <c r="AK5">
-        <v>0.1340434818816628</v>
+        <v>-1.693309253773119</v>
       </c>
       <c r="AL5">
-        <v>-2.148195515030185</v>
+        <v>-3.732074298369752</v>
       </c>
       <c r="AM5">
-        <v>0.5831554618618305</v>
+        <v>5.170479060669843</v>
       </c>
       <c r="AN5">
-        <v>2.083980118395606</v>
+        <v>3.236897597500552</v>
       </c>
       <c r="AO5">
-        <v>0.03991014076490834</v>
+        <v>0.04065799994258394</v>
       </c>
       <c r="AP5">
-        <v>6.702685000000001</v>
+        <v>1.125345</v>
       </c>
       <c r="AQ5">
-        <v>6.743230552550399</v>
+        <v>1.123021124580156</v>
       </c>
       <c r="AR5">
-        <v>6.803670919197419</v>
+        <v>1.152402238859409</v>
       </c>
       <c r="AS5">
-        <v>6.702685000000001</v>
+        <v>1.125345</v>
       </c>
       <c r="AT5">
-        <v>6.697545000000002</v>
+        <v>1.090795</v>
       </c>
       <c r="AU5">
-        <v>6.743230552550399</v>
+        <v>1.123021124580156</v>
       </c>
       <c r="AV5">
-        <v>6.675654631633068</v>
+        <v>1.135705</v>
       </c>
       <c r="AW5">
-        <v>0.006049150832897287</v>
+        <v>-0.002065033762841144</v>
       </c>
       <c r="AX5">
-        <v>1.5</v>
+        <v>0.2243122992127857</v>
       </c>
       <c r="AY5">
-        <v>0.006049150832897287</v>
+        <v>0.002065033762841144</v>
       </c>
       <c r="AZ5">
-        <v>0.4207977927364186</v>
+        <v>0.4109277586344737</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3792022072635814</v>
+        <v>0.3890722413655263</v>
       </c>
       <c r="BC5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1852,22 +1852,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.004032767221931525</v>
+        <v>0.009206065695408995</v>
       </c>
       <c r="BH5">
-        <v>123984.3443680147</v>
+        <v>54312.01737451719</v>
       </c>
       <c r="BI5">
-        <v>123984.3443680147</v>
+        <v>54312.01737451719</v>
       </c>
       <c r="BJ5">
-        <v>18497.71313555905</v>
+        <v>48262.54826254809</v>
       </c>
       <c r="BK5">
-        <v>1239.843443680146</v>
+        <v>543.1201737451719</v>
       </c>
       <c r="BL5">
-        <v>0.01239843443680146</v>
+        <v>0.005431201737451719</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1876,28 +1876,28 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.03711910361811745</v>
+        <v>0.02051877473967162</v>
       </c>
       <c r="BP5">
-        <v>0.01719439126974981</v>
+        <v>0.01637814451623821</v>
       </c>
       <c r="BQ5">
-        <v>0.01965447369598544</v>
+        <v>0.01107201721481868</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU5" t="s">
         <v>90</v>
       </c>
       <c r="BV5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW5" s="2">
         <v>46330</v>
@@ -1920,16 +1920,16 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" t="s">
         <v>91</v>
-      </c>
-      <c r="H6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" t="s">
-        <v>92</v>
       </c>
       <c r="J6" s="2">
         <v>46301</v>
@@ -1947,19 +1947,19 @@
         <v>19</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T6">
         <v>-0.9978536348105105</v>
@@ -1968,10 +1968,10 @@
         <v>0.9989361574110378</v>
       </c>
       <c r="V6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X6">
         <v>0.9996080869852325</v>
@@ -1992,16 +1992,16 @@
         <v>0.09256732163582181</v>
       </c>
       <c r="AD6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE6" t="s">
         <v>109</v>
       </c>
       <c r="AF6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AH6">
         <v>-0.9953161977947057</v>
@@ -2031,10 +2031,10 @@
         <v>8.893829999999999</v>
       </c>
       <c r="AQ6">
-        <v>8.827935909289558</v>
+        <v>8.838319973424904</v>
       </c>
       <c r="AR6">
-        <v>8.887568777580498</v>
+        <v>8.909695023139358</v>
       </c>
       <c r="AS6">
         <v>8.893829999999999</v>
@@ -2043,31 +2043,31 @@
         <v>8.720999999999998</v>
       </c>
       <c r="AU6">
-        <v>8.827935909289558</v>
+        <v>8.838319973424904</v>
       </c>
       <c r="AV6">
         <v>8.949942499999999</v>
       </c>
       <c r="AW6">
-        <v>-0.007408966745535045</v>
+        <v>-0.006241408546722374</v>
       </c>
       <c r="AX6">
-        <v>1.174321064120174</v>
+        <v>0.9892631156176777</v>
       </c>
       <c r="AY6">
-        <v>0.007408966745535045</v>
+        <v>0.006241408546722374</v>
       </c>
       <c r="AZ6">
-        <v>0.4344746376888231</v>
+        <v>0.4385593856589832</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.365525362311177</v>
+        <v>0.3614406143410169</v>
       </c>
       <c r="BC6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2103,28 +2103,28 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.1089524077517103</v>
+        <v>0.1020325909977342</v>
       </c>
       <c r="BP6">
-        <v>0.06791435132412199</v>
+        <v>0.05951026908138376</v>
       </c>
       <c r="BQ6">
-        <v>0.07211022188834387</v>
+        <v>0.06965725173385524</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW6" s="2">
         <v>46330</v>
@@ -2147,154 +2147,154 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" t="s">
         <v>91</v>
-      </c>
-      <c r="H7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I7" t="s">
-        <v>92</v>
       </c>
       <c r="J7" s="2">
         <v>46301</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.5206325096177565</v>
       </c>
       <c r="L7">
-        <v>1.41384031359683</v>
+        <v>2.114622406007593</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.8801581274044391</v>
       </c>
       <c r="R7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T7">
-        <v>-0.9312053040770206</v>
+        <v>-0.9471943794584506</v>
       </c>
       <c r="U7">
-        <v>0.9689152835989751</v>
+        <v>0.9038615815922336</v>
       </c>
       <c r="V7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9994915870572633</v>
+        <v>0.9981169375730693</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0.9303371883403148</v>
       </c>
       <c r="Z7">
-        <v>-149.5843723307099</v>
+        <v>-154.212432023279</v>
       </c>
       <c r="AA7">
-        <v>-22.99999999999999</v>
+        <v>-37.99999999999999</v>
       </c>
       <c r="AB7">
-        <v>-0.8623756142488881</v>
+        <v>-0.90041318653816</v>
       </c>
       <c r="AC7">
-        <v>-0.5062689995929565</v>
+        <v>-0.4350357381965263</v>
       </c>
       <c r="AD7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE7" t="s">
         <v>109</v>
       </c>
       <c r="AF7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH7">
-        <v>-0.8619371713251034</v>
+        <v>-0.8674140530242463</v>
       </c>
       <c r="AI7">
-        <v>0.9528918082725243</v>
+        <v>0.9501034015349541</v>
       </c>
       <c r="AJ7">
-        <v>-1.123718285723238</v>
+        <v>-1.730949690210708</v>
       </c>
       <c r="AK7">
-        <v>-0.7452867368265162</v>
+        <v>-1.059460664405853</v>
       </c>
       <c r="AL7">
-        <v>-1.552801375349311</v>
+        <v>-2.102664683571918</v>
       </c>
       <c r="AM7">
-        <v>2.72310269088192</v>
+        <v>4.863130987710345</v>
       </c>
       <c r="AN7">
-        <v>1.291695185302931</v>
+        <v>1.648412988117296</v>
       </c>
       <c r="AO7">
-        <v>0.03761954314789425</v>
+        <v>0.03619280163420795</v>
       </c>
       <c r="AP7">
-        <v>4.67878</v>
+        <v>0.69811</v>
       </c>
       <c r="AQ7">
-        <v>4.634894458762735</v>
+        <v>0.6924399251631854</v>
       </c>
       <c r="AR7">
-        <v>4.673628236402769</v>
+        <v>0.6988453578378797</v>
       </c>
       <c r="AS7">
-        <v>4.67878</v>
+        <v>0.69811</v>
       </c>
       <c r="AT7">
-        <v>4.54991</v>
+        <v>0.67987</v>
       </c>
       <c r="AU7">
-        <v>4.634894458762735</v>
+        <v>0.6924399251631854</v>
       </c>
       <c r="AV7">
-        <v>4.721425</v>
+        <v>0.70391</v>
       </c>
       <c r="AW7">
-        <v>-0.009379697535952598</v>
+        <v>-0.008122036408036824</v>
       </c>
       <c r="AX7">
-        <v>1.02908995749242</v>
+        <v>0.9775991097956138</v>
       </c>
       <c r="AY7">
-        <v>0.009379697535952598</v>
+        <v>0.008122036408036824</v>
       </c>
       <c r="AZ7">
-        <v>0.478591196288746</v>
+        <v>0.4701848175624421</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.321408803711254</v>
+        <v>0.3298151824375579</v>
       </c>
       <c r="BC7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2303,55 +2303,55 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>500</v>
+        <v>440.0790637022196</v>
       </c>
       <c r="BG7">
-        <v>0.009114555503785185</v>
+        <v>0.008308146280672139</v>
       </c>
       <c r="BH7">
-        <v>54857.31035291353</v>
+        <v>60181.89655172386</v>
       </c>
       <c r="BI7">
-        <v>54857.31035291353</v>
+        <v>52969.58537261294</v>
       </c>
       <c r="BJ7">
-        <v>11724.70395122522</v>
+        <v>75875.70063831337</v>
       </c>
       <c r="BK7">
-        <v>548.5731035291352</v>
+        <v>529.6958537261294</v>
       </c>
       <c r="BL7">
-        <v>0.005485731035291352</v>
+        <v>0.005296958537261294</v>
       </c>
       <c r="BM7">
-        <v>500</v>
+        <v>440.0790637022196</v>
       </c>
       <c r="BN7">
-        <v>0.005</v>
+        <v>0.004400790637022196</v>
       </c>
       <c r="BO7">
-        <v>0.05320166801388212</v>
+        <v>0.009848675048003748</v>
       </c>
       <c r="BP7">
-        <v>0.07150128445095107</v>
+        <v>0.009901272247688797</v>
       </c>
       <c r="BQ7">
-        <v>0.06247093602912388</v>
+        <v>0.01031808605856937</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW7" s="2">
         <v>46330</v>
@@ -2374,154 +2374,154 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" t="s">
         <v>91</v>
-      </c>
-      <c r="H8" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8" t="s">
-        <v>92</v>
       </c>
       <c r="J8" s="2">
         <v>46301</v>
       </c>
       <c r="K8">
-        <v>0.5206325096177565</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>2.114622406007593</v>
+        <v>1.41384031359683</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q8">
-        <v>0.8801581274044391</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T8">
-        <v>-0.9471943794584506</v>
+        <v>-0.9312053040770206</v>
       </c>
       <c r="U8">
-        <v>0.9038615815922336</v>
+        <v>0.9689152835989751</v>
       </c>
       <c r="V8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X8">
-        <v>0.9981169375730693</v>
+        <v>0.9994915870572633</v>
       </c>
       <c r="Y8">
-        <v>0.9303371883403148</v>
+        <v>1</v>
       </c>
       <c r="Z8">
-        <v>-154.212432023279</v>
+        <v>-149.5843723307099</v>
       </c>
       <c r="AA8">
-        <v>-37.99999999999999</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="AB8">
-        <v>-0.90041318653816</v>
+        <v>-0.8623756142488881</v>
       </c>
       <c r="AC8">
-        <v>-0.4350357381965263</v>
+        <v>-0.5062689995929565</v>
       </c>
       <c r="AD8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE8" t="s">
         <v>109</v>
       </c>
       <c r="AF8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH8">
-        <v>-0.8674140530242463</v>
+        <v>-0.8619371713251034</v>
       </c>
       <c r="AI8">
-        <v>0.9501034015349541</v>
+        <v>0.9528918082725243</v>
       </c>
       <c r="AJ8">
-        <v>-1.730949690210708</v>
+        <v>-1.123718285723238</v>
       </c>
       <c r="AK8">
-        <v>-1.059460664405853</v>
+        <v>-0.7452867368265162</v>
       </c>
       <c r="AL8">
-        <v>-2.102664683571918</v>
+        <v>-1.552801375349311</v>
       </c>
       <c r="AM8">
-        <v>4.863130987710345</v>
+        <v>2.72310269088192</v>
       </c>
       <c r="AN8">
-        <v>1.648412988117296</v>
+        <v>1.291695185302931</v>
       </c>
       <c r="AO8">
-        <v>0.03619280163420795</v>
+        <v>0.03761954314789425</v>
       </c>
       <c r="AP8">
-        <v>0.69811</v>
+        <v>4.67878</v>
       </c>
       <c r="AQ8">
-        <v>0.6914529257505855</v>
+        <v>4.63994896940714</v>
       </c>
       <c r="AR8">
-        <v>0.6966185852863654</v>
+        <v>4.68564737545134</v>
       </c>
       <c r="AS8">
-        <v>0.69811</v>
+        <v>4.67878</v>
       </c>
       <c r="AT8">
-        <v>0.67987</v>
+        <v>4.54991</v>
       </c>
       <c r="AU8">
-        <v>0.6914529257505855</v>
+        <v>4.63994896940714</v>
       </c>
       <c r="AV8">
-        <v>0.70391</v>
+        <v>4.721425</v>
       </c>
       <c r="AW8">
-        <v>-0.00953585287335023</v>
+        <v>-0.008299392275947974</v>
       </c>
       <c r="AX8">
-        <v>1.147771422312845</v>
+        <v>0.9105646756445028</v>
       </c>
       <c r="AY8">
-        <v>0.00953585287335023</v>
+        <v>0.008299392275947974</v>
       </c>
       <c r="AZ8">
-        <v>0.4737669250814356</v>
+        <v>0.4734508030190847</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3262330749185643</v>
+        <v>0.3265491969809152</v>
       </c>
       <c r="BC8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2530,55 +2530,55 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>440.0790637022196</v>
+        <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.008308146280672139</v>
+        <v>0.009114555503785185</v>
       </c>
       <c r="BH8">
-        <v>60181.89655172386</v>
+        <v>54857.31035291353</v>
       </c>
       <c r="BI8">
-        <v>52969.58537261294</v>
+        <v>54857.31035291353</v>
       </c>
       <c r="BJ8">
-        <v>75875.70063831337</v>
+        <v>11724.70395122522</v>
       </c>
       <c r="BK8">
-        <v>529.6958537261294</v>
+        <v>548.5731035291352</v>
       </c>
       <c r="BL8">
-        <v>0.005296958537261294</v>
+        <v>0.005485731035291352</v>
       </c>
       <c r="BM8">
-        <v>440.0790637022196</v>
+        <v>500</v>
       </c>
       <c r="BN8">
-        <v>0.004400790637022196</v>
+        <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.01013385624181444</v>
+        <v>0.05240715669435765</v>
       </c>
       <c r="BP8">
-        <v>0.01055374653169943</v>
+        <v>0.06773622461395878</v>
       </c>
       <c r="BQ8">
-        <v>0.01107590721002824</v>
+        <v>0.05809900568708407</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW8" s="2">
         <v>46330</v>
@@ -2601,16 +2601,16 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" t="s">
         <v>91</v>
-      </c>
-      <c r="H9" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" t="s">
-        <v>92</v>
       </c>
       <c r="J9" s="2">
         <v>46301</v>
@@ -2628,19 +2628,19 @@
         <v>13</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="S9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T9">
         <v>-0.9971996562992052</v>
@@ -2649,10 +2649,10 @@
         <v>0.9985561363126866</v>
       </c>
       <c r="V9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X9">
         <v>0.9992651639121771</v>
@@ -2673,16 +2673,16 @@
         <v>0.1085097815662903</v>
       </c>
       <c r="AD9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE9" t="s">
         <v>109</v>
       </c>
       <c r="AF9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="AG9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AH9">
         <v>-0.9190581859065532</v>
@@ -2712,10 +2712,10 @@
         <v>1.326815</v>
       </c>
       <c r="AQ9">
-        <v>1.313752245007693</v>
+        <v>1.315698969481049</v>
       </c>
       <c r="AR9">
-        <v>1.31809250107805</v>
+        <v>1.322327917406295</v>
       </c>
       <c r="AS9">
         <v>1.326815</v>
@@ -2724,31 +2724,31 @@
         <v>1.301035</v>
       </c>
       <c r="AU9">
-        <v>1.313752245007693</v>
+        <v>1.315698969481049</v>
       </c>
       <c r="AV9">
         <v>1.338465</v>
       </c>
       <c r="AW9">
-        <v>-0.009845196950823774</v>
+        <v>-0.008377980742568852</v>
       </c>
       <c r="AX9">
-        <v>1.121266522944829</v>
+        <v>0.9541657097812445</v>
       </c>
       <c r="AY9">
-        <v>0.009845196950823774</v>
+        <v>0.008377980742568852</v>
       </c>
       <c r="AZ9">
-        <v>0.4432797613844443</v>
+        <v>0.4465320228141921</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3567202386155557</v>
+        <v>0.3534679771858079</v>
       </c>
       <c r="BC9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2784,28 +2784,28 @@
         <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.02038591771463159</v>
+        <v>0.01926574515095794</v>
       </c>
       <c r="BP9">
-        <v>0.01176897456789048</v>
+        <v>0.01049563285310059</v>
       </c>
       <c r="BQ9">
-        <v>0.01463473880735201</v>
+        <v>0.01417141629622287</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW9" s="2">
         <v>46330</v>
@@ -2828,16 +2828,16 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" t="s">
         <v>91</v>
-      </c>
-      <c r="H10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I10" t="s">
-        <v>92</v>
       </c>
       <c r="J10" s="2">
         <v>46301</v>
@@ -2855,19 +2855,19 @@
         <v>15</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T10">
         <v>-0.9318473998340459</v>
@@ -2876,10 +2876,10 @@
         <v>0.9693302174354312</v>
       </c>
       <c r="V10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X10">
         <v>0.9999955500404425</v>
@@ -2900,16 +2900,16 @@
         <v>-0.5040156911296367</v>
       </c>
       <c r="AD10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE10" t="s">
         <v>109</v>
       </c>
       <c r="AF10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH10">
         <v>-0.8636906529848487</v>
@@ -2939,10 +2939,10 @@
         <v>7.5442</v>
       </c>
       <c r="AQ10">
-        <v>7.444494758812539</v>
+        <v>7.452836647467224</v>
       </c>
       <c r="AR10">
-        <v>7.510684976994754</v>
+        <v>7.53222402225918</v>
       </c>
       <c r="AS10">
         <v>7.5442</v>
@@ -2951,31 +2951,31 @@
         <v>7.3095</v>
       </c>
       <c r="AU10">
-        <v>7.444494758812539</v>
+        <v>7.452836647467224</v>
       </c>
       <c r="AV10">
-        <v>7.610670160791641</v>
+        <v>7.605108901688517</v>
       </c>
       <c r="AW10">
-        <v>-0.01321614501040021</v>
+        <v>-0.01211040965679273</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01321614501040021</v>
+        <v>0.01211040965679273</v>
       </c>
       <c r="AZ10">
-        <v>0.4376805869298792</v>
+        <v>0.4328075907099503</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3623194130701208</v>
+        <v>0.3671924092900496</v>
       </c>
       <c r="BC10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2987,22 +2987,22 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.008810763340266807</v>
+        <v>0.00807360643786182</v>
       </c>
       <c r="BH10">
-        <v>56748.77200649666</v>
+        <v>61930.19239273421</v>
       </c>
       <c r="BI10">
-        <v>56748.77200649666</v>
+        <v>61930.19239273421</v>
       </c>
       <c r="BJ10">
-        <v>7522.17226564734</v>
+        <v>8208.980725952944</v>
       </c>
       <c r="BK10">
-        <v>567.4877200649667</v>
+        <v>619.301923927342</v>
       </c>
       <c r="BL10">
-        <v>0.005674877200649666</v>
+        <v>0.006193019239273421</v>
       </c>
       <c r="BM10">
         <v>500</v>
@@ -3011,28 +3011,28 @@
         <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.1025947435030273</v>
+        <v>0.1008186386230895</v>
       </c>
       <c r="BP10">
-        <v>0.1235147620335832</v>
+        <v>0.1181220543985215</v>
       </c>
       <c r="BQ10">
-        <v>0.07792545720117591</v>
+        <v>0.07260509893331897</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW10" s="2">
         <v>46330</v>
@@ -3055,16 +3055,16 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" t="s">
         <v>91</v>
-      </c>
-      <c r="H11" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11" t="s">
-        <v>92</v>
       </c>
       <c r="J11" s="2">
         <v>46301</v>
@@ -3082,19 +3082,19 @@
         <v>8</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T11">
         <v>-0.9369233410214868</v>
@@ -3103,10 +3103,10 @@
         <v>0.8214132020955007</v>
       </c>
       <c r="V11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X11">
         <v>0.9991907945433268</v>
@@ -3127,16 +3127,16 @@
         <v>-0.5209385805694251</v>
       </c>
       <c r="AD11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE11" t="s">
         <v>109</v>
       </c>
       <c r="AF11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH11">
         <v>-0.5323168518364058</v>
@@ -3166,10 +3166,10 @@
         <v>4164.190000000001</v>
       </c>
       <c r="AQ11">
-        <v>4059.231636985722</v>
+        <v>4079.12324815377</v>
       </c>
       <c r="AR11">
-        <v>4101.572363305086</v>
+        <v>4159.342342095461</v>
       </c>
       <c r="AS11">
         <v>4164.190000000001</v>
@@ -3178,31 +3178,31 @@
         <v>3981.700000000003</v>
       </c>
       <c r="AU11">
-        <v>4059.231636985722</v>
+        <v>4079.12324815377</v>
       </c>
       <c r="AV11">
         <v>4297.827500000001</v>
       </c>
       <c r="AW11">
-        <v>-0.02520498896887022</v>
+        <v>-0.02042816294314895</v>
       </c>
       <c r="AX11">
-        <v>0.7853960378956475</v>
+        <v>0.6365485125524748</v>
       </c>
       <c r="AY11">
-        <v>0.02520498896887022</v>
+        <v>0.02042816294314895</v>
       </c>
       <c r="AZ11">
-        <v>0.3423110703280764</v>
+        <v>0.3429658010308648</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4576889296719236</v>
+        <v>0.4570341989691352</v>
       </c>
       <c r="BC11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3238,28 +3238,28 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="BO11">
-        <v>608.5603399473235</v>
+        <v>595.623806403785</v>
       </c>
       <c r="BP11">
-        <v>162.4205869871446</v>
+        <v>159.1420202819173</v>
       </c>
       <c r="BQ11">
-        <v>100.9496079619278</v>
+        <v>99.75720777625422</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.05419478678603245</v>
+        <v>0.06101869837460699</v>
       </c>
       <c r="BT11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BU11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="BW11" s="2">
         <v>46330</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -253,18 +253,18 @@
     <t>EURUSD</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -289,28 +289,28 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
+    <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>ALIGNED</t>
+    <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>CONFIRM</t>
-  </si>
-  <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
-    <t>UP_STEADY</t>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
   </si>
   <si>
     <t>DOWN_STEADY</t>
@@ -319,10 +319,10 @@
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>空头减速</t>
-  </si>
-  <si>
-    <t>多头稳态</t>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头减速</t>
   </si>
   <si>
     <t>空头稳态</t>
@@ -349,7 +349,7 @@
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
-    <t>UP_SLOPE</t>
+    <t>UP_CREST_FLATTENING</t>
   </si>
   <si>
     <t>DOWN_SLOPE</t>
@@ -361,7 +361,7 @@
     <t>地形转换区</t>
   </si>
   <si>
-    <t>上升坡延续</t>
+    <t>上升坡顶钝化</t>
   </si>
   <si>
     <t>下降坡延续</t>
@@ -370,34 +370,34 @@
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.699,naive=1.356,drift4=2.593; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.0152,naive=0.006315,drift4=0.005002; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03592,naive=0.0172,drift4=0.01891; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.02052,naive=0.01638,drift4=0.01107; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.102,naive=0.05951,drift4=0.06966; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.009849,naive=0.009901,drift4=0.01032; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.05241,naive=0.06774,drift4=0.0581; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01927,naive=0.0105,drift4=0.01417; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.1008,naive=0.1181,drift4=0.07261; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=595.6,naive=159.1,drift4=99.76; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.716,naive=1.321,drift4=2.569; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=drift4; scores=model=0.01541,naive=0.007412,drift4=0.004392; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03548,naive=0.01648,drift4=0.01864; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.01684,naive=0.02072,drift4=0.01172; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.0521,naive=0.07053,drift4=0.05542; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.1041,naive=0.07205,drift4=0.04575; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.01752,naive=0.01219,drift4=0.009787; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.0104,naive=0.01126,drift4=0.009524; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.19,drift4=0.37); metric_best=drift4; scores=model=0.1031,naive=0.1421,drift4=0.07664</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=585.1,naive=174.8,drift4=96.35; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -1000,7 +1000,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1024,19 +1024,19 @@
         <v>91</v>
       </c>
       <c r="J2" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.002177776906038563</v>
+        <v>0.006113735974351001</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O2" t="s">
         <v>93</v>
@@ -1045,7 +1045,7 @@
         <v>95</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R2" t="s">
         <v>97</v>
@@ -1054,10 +1054,10 @@
         <v>101</v>
       </c>
       <c r="T2">
-        <v>-0.6507469057837999</v>
+        <v>0.6728424278029234</v>
       </c>
       <c r="U2">
-        <v>0.6678042029930771</v>
+        <v>0.7027442126399238</v>
       </c>
       <c r="V2" t="s">
         <v>105</v>
@@ -1066,22 +1066,22 @@
         <v>105</v>
       </c>
       <c r="X2">
-        <v>0.9998723815614684</v>
+        <v>0.999860480514433</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>91.78558942711715</v>
+        <v>87.60390032828413</v>
       </c>
       <c r="AA2">
-        <v>-3.000000000000004</v>
+        <v>-1.000000000000001</v>
       </c>
       <c r="AB2">
-        <v>-0.03115937024934096</v>
+        <v>0.04180763977384645</v>
       </c>
       <c r="AC2">
-        <v>0.9995144289332017</v>
+        <v>0.999125678409148</v>
       </c>
       <c r="AD2" t="s">
         <v>106</v>
@@ -1096,67 +1096,67 @@
         <v>114</v>
       </c>
       <c r="AH2">
-        <v>-0.01557769686958205</v>
+        <v>0.02090090339672621</v>
       </c>
       <c r="AI2">
-        <v>0.4448547990031296</v>
+        <v>0.4489464051765425</v>
       </c>
       <c r="AJ2">
-        <v>-0.03853955374076883</v>
+        <v>0.03983407559273991</v>
       </c>
       <c r="AK2">
-        <v>1.023611027881948</v>
+        <v>1.010713257934639</v>
       </c>
       <c r="AL2">
-        <v>0.02052277034608236</v>
+        <v>0.07047616432409684</v>
       </c>
       <c r="AM2">
-        <v>0.2014498284857335</v>
+        <v>-0.08944521840588067</v>
       </c>
       <c r="AN2">
-        <v>0.08409136317548631</v>
+        <v>0.1074088415136309</v>
       </c>
       <c r="AO2">
-        <v>0.4296556374545773</v>
+        <v>0.4236470329044199</v>
       </c>
       <c r="AP2">
-        <v>158.325</v>
+        <v>158.264</v>
       </c>
       <c r="AQ2">
-        <v>160.9913260037643</v>
+        <v>160.814172605683</v>
       </c>
       <c r="AR2">
-        <v>160.6247098451819</v>
+        <v>160.3552457245526</v>
       </c>
       <c r="AS2">
-        <v>158.325</v>
+        <v>158.264</v>
       </c>
       <c r="AT2">
-        <v>163.135</v>
+        <v>163.013</v>
       </c>
       <c r="AU2">
-        <v>160.9913260037643</v>
+        <v>160.814172605683</v>
       </c>
       <c r="AV2">
-        <v>156.5474493308238</v>
+        <v>156.5638849295447</v>
       </c>
       <c r="AW2">
-        <v>0.01684084006798852</v>
+        <v>0.01611340927616516</v>
       </c>
       <c r="AX2">
         <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.01684084006798852</v>
+        <v>0.01611340927616516</v>
       </c>
       <c r="AZ2">
-        <v>0.4707320362818145</v>
+        <v>0.4699559345480634</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3292679637181854</v>
+        <v>0.3300440654519366</v>
       </c>
       <c r="BC2" t="s">
         <v>118</v>
@@ -1168,46 +1168,46 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG2">
-        <v>0.01122722671199235</v>
+        <v>0.01074227285077677</v>
       </c>
       <c r="BH2">
-        <v>44534.59548170747</v>
+        <v>46545.08472700404</v>
       </c>
       <c r="BI2">
-        <v>44534.59548170747</v>
+        <v>34908.81354525303</v>
       </c>
       <c r="BJ2">
-        <v>281.2859338809884</v>
+        <v>220.5733050172688</v>
       </c>
       <c r="BK2">
-        <v>445.3459548170748</v>
+        <v>349.0881354525303</v>
       </c>
       <c r="BL2">
-        <v>0.004453459548170748</v>
+        <v>0.003490881354525303</v>
       </c>
       <c r="BM2">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BN2">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="BO2">
-        <v>2.698702711289627</v>
+        <v>2.715989949580807</v>
       </c>
       <c r="BP2">
-        <v>1.356418458894436</v>
+        <v>1.320835193777395</v>
       </c>
       <c r="BQ2">
-        <v>2.592607718475479</v>
+        <v>2.569289031024483</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT2" t="s">
         <v>128</v>
@@ -1219,7 +1219,7 @@
         <v>129</v>
       </c>
       <c r="BW2" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1227,7 +1227,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1248,28 +1248,28 @@
         <v>89</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J3" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2.696719377268863</v>
+        <v>2.776844219695286</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -1281,37 +1281,37 @@
         <v>102</v>
       </c>
       <c r="T3">
-        <v>0.9889860594949241</v>
+        <v>0.9815614463182903</v>
       </c>
       <c r="U3">
-        <v>0.994894244187264</v>
+        <v>0.9915972031276785</v>
       </c>
       <c r="V3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X3">
-        <v>0.9994020696581923</v>
+        <v>0.9995782091377913</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>-12.05007180912457</v>
+        <v>-15.61010744709516</v>
       </c>
       <c r="AA3">
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="AB3">
-        <v>0.97796552948057</v>
+        <v>0.9631151121413833</v>
       </c>
       <c r="AC3">
-        <v>-0.2087664320425777</v>
+        <v>-0.2690897262343743</v>
       </c>
       <c r="AD3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AE3" t="s">
         <v>108</v>
@@ -1323,67 +1323,67 @@
         <v>115</v>
       </c>
       <c r="AH3">
-        <v>0.9773807742172516</v>
+        <v>0.962708878987827</v>
       </c>
       <c r="AI3">
-        <v>0.9881850231608122</v>
+        <v>0.9836270268585893</v>
       </c>
       <c r="AJ3">
-        <v>2.120294982223862</v>
+        <v>2.169259678534663</v>
       </c>
       <c r="AK3">
-        <v>-0.3438991264746123</v>
+        <v>-0.5199204015390586</v>
       </c>
       <c r="AL3">
-        <v>3.047661417731772</v>
+        <v>3.193281331514531</v>
       </c>
       <c r="AM3">
-        <v>-4.240237424373629</v>
+        <v>-4.01984093452021</v>
       </c>
       <c r="AN3">
-        <v>2.684528356714271</v>
+        <v>2.850847450119219</v>
       </c>
       <c r="AO3">
-        <v>0.03330240042484071</v>
+        <v>0.03439919988035113</v>
       </c>
       <c r="AP3">
-        <v>0.832335</v>
+        <v>0.8338650000000001</v>
       </c>
       <c r="AQ3">
-        <v>0.8402490251588426</v>
+        <v>0.8438109414915499</v>
       </c>
       <c r="AR3">
-        <v>0.8356661940352523</v>
+        <v>0.8403798111372953</v>
       </c>
       <c r="AS3">
-        <v>0.832335</v>
+        <v>0.8338650000000001</v>
       </c>
       <c r="AT3">
-        <v>0.8482250000000001</v>
+        <v>0.8512850000000002</v>
       </c>
       <c r="AU3">
-        <v>0.8402490251588426</v>
+        <v>0.8438109414915499</v>
       </c>
       <c r="AV3">
-        <v>0.82496375</v>
+        <v>0.82649375</v>
       </c>
       <c r="AW3">
-        <v>0.00950822103941627</v>
+        <v>0.01192752003207931</v>
       </c>
       <c r="AX3">
-        <v>1.073634072761402</v>
+        <v>1.349288314946548</v>
       </c>
       <c r="AY3">
-        <v>0.00950822103941627</v>
+        <v>0.01192752003207931</v>
       </c>
       <c r="AZ3">
-        <v>0.3820406856054071</v>
+        <v>0.3658862362389771</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.4179593143945929</v>
+        <v>0.4341137637610228</v>
       </c>
       <c r="BC3" t="s">
         <v>119</v>
@@ -1398,22 +1398,22 @@
         <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.008856109619324011</v>
+        <v>0.008839860169212104</v>
       </c>
       <c r="BH3">
-        <v>56458.19908427975</v>
+        <v>56561.98066813595</v>
       </c>
       <c r="BI3">
-        <v>56458.19908427975</v>
+        <v>56561.98066813595</v>
       </c>
       <c r="BJ3">
-        <v>67831.10055960611</v>
+        <v>67831.1005596061</v>
       </c>
       <c r="BK3">
-        <v>564.5819908427975</v>
+        <v>565.6198066813595</v>
       </c>
       <c r="BL3">
-        <v>0.005645819908427975</v>
+        <v>0.005656198066813595</v>
       </c>
       <c r="BM3">
         <v>500</v>
@@ -1422,19 +1422,19 @@
         <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>0.01520208853300778</v>
+        <v>0.01541444177061994</v>
       </c>
       <c r="BP3">
-        <v>0.006314615167071252</v>
+        <v>0.007411878555495011</v>
       </c>
       <c r="BQ3">
-        <v>0.005002395209896033</v>
+        <v>0.00439209708709224</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT3" t="s">
         <v>128</v>
@@ -1446,7 +1446,7 @@
         <v>129</v>
       </c>
       <c r="BW3" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1454,7 +1454,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1475,28 +1475,28 @@
         <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J4" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.461090899523458</v>
+        <v>1.473457504260679</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q4">
         <v>1</v>
@@ -1508,37 +1508,37 @@
         <v>103</v>
       </c>
       <c r="T4">
-        <v>-0.9986655881761152</v>
+        <v>-0.9973821418480858</v>
       </c>
       <c r="U4">
-        <v>0.8491583172689934</v>
+        <v>0.8485921692882007</v>
       </c>
       <c r="V4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X4">
-        <v>0.9990352103589665</v>
+        <v>0.999080821826248</v>
       </c>
       <c r="Y4">
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>174.9313750264995</v>
+        <v>-172.8985318845068</v>
       </c>
       <c r="AA4">
         <v>25</v>
       </c>
       <c r="AB4">
-        <v>-0.99608959436648</v>
+        <v>-0.992328770463571</v>
       </c>
       <c r="AC4">
-        <v>0.0883488539530722</v>
+        <v>-0.1236269036668696</v>
       </c>
       <c r="AD4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE4" t="s">
         <v>109</v>
@@ -1550,67 +1550,67 @@
         <v>116</v>
       </c>
       <c r="AH4">
-        <v>-0.497564288722147</v>
+        <v>-0.4957083217582874</v>
       </c>
       <c r="AI4">
-        <v>0.792502680820846</v>
+        <v>0.7916245929786799</v>
       </c>
       <c r="AJ4">
-        <v>-1.03560922134312</v>
+        <v>-1.050693820784933</v>
       </c>
       <c r="AK4">
-        <v>0.1340434818816628</v>
+        <v>-0.09083334132185701</v>
       </c>
       <c r="AL4">
-        <v>-2.148195515030185</v>
+        <v>-2.145484640321218</v>
       </c>
       <c r="AM4">
-        <v>0.5831554618618305</v>
+        <v>0.838610488219484</v>
       </c>
       <c r="AN4">
-        <v>2.083980118395606</v>
+        <v>2.053129172877732</v>
       </c>
       <c r="AO4">
-        <v>0.03991014076490834</v>
+        <v>0.03834883866385444</v>
       </c>
       <c r="AP4">
-        <v>6.702685000000001</v>
+        <v>6.70457</v>
       </c>
       <c r="AQ4">
-        <v>6.73931299702166</v>
+        <v>6.74037729135374</v>
       </c>
       <c r="AR4">
-        <v>6.794668241336089</v>
+        <v>6.792761553043736</v>
       </c>
       <c r="AS4">
-        <v>6.702685000000001</v>
+        <v>6.70457</v>
       </c>
       <c r="AT4">
-        <v>6.697545000000002</v>
+        <v>6.701315000000001</v>
       </c>
       <c r="AU4">
-        <v>6.73931299702166</v>
+        <v>6.74037729135374</v>
       </c>
       <c r="AV4">
-        <v>6.678266335318894</v>
+        <v>6.680698472430841</v>
       </c>
       <c r="AW4">
-        <v>0.005464675278885878</v>
+        <v>0.005340728988397391</v>
       </c>
       <c r="AX4">
         <v>1.5</v>
       </c>
       <c r="AY4">
-        <v>0.005464675278885878</v>
+        <v>0.005340728988397391</v>
       </c>
       <c r="AZ4">
-        <v>0.4194670241768401</v>
+        <v>0.4200408880952546</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.3805329758231599</v>
+        <v>0.3799591119047454</v>
       </c>
       <c r="BC4" t="s">
         <v>120</v>
@@ -1625,22 +1625,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.003643116852590586</v>
+        <v>0.003560485992264928</v>
       </c>
       <c r="BH4">
-        <v>137245.117362748</v>
+        <v>140430.2674090667</v>
       </c>
       <c r="BI4">
-        <v>137245.117362748</v>
+        <v>140430.2674090667</v>
       </c>
       <c r="BJ4">
-        <v>20476.14013828011</v>
+        <v>20945.45472850111</v>
       </c>
       <c r="BK4">
-        <v>1372.45117362748</v>
+        <v>1404.302674090667</v>
       </c>
       <c r="BL4">
-        <v>0.0137245117362748</v>
+        <v>0.01404302674090667</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1649,19 +1649,19 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.03591883909300873</v>
+        <v>0.03547545303663666</v>
       </c>
       <c r="BP4">
-        <v>0.01720029375025792</v>
+        <v>0.01648193147039735</v>
       </c>
       <c r="BQ4">
-        <v>0.01890963456037817</v>
+        <v>0.01864062116403285</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT4" t="s">
         <v>128</v>
@@ -1673,7 +1673,7 @@
         <v>129</v>
       </c>
       <c r="BW4" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1681,7 +1681,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1702,28 +1702,28 @@
         <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>3.256613153033321</v>
+        <v>3.34311840529356</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -1735,37 +1735,37 @@
         <v>104</v>
       </c>
       <c r="T5">
-        <v>-0.9199361538026168</v>
+        <v>-0.9246486633344464</v>
       </c>
       <c r="U5">
-        <v>0.9639637521852494</v>
+        <v>0.966086802965567</v>
       </c>
       <c r="V5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X5">
-        <v>0.9999699318962872</v>
+        <v>0.9999796178602646</v>
       </c>
       <c r="Y5">
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>-147.1263839496164</v>
+        <v>-148.1351581301081</v>
       </c>
       <c r="AA5">
-        <v>-5.999999999999996</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AB5">
-        <v>-0.8398699001648156</v>
+        <v>-0.8492957908161154</v>
       </c>
       <c r="AC5">
-        <v>-0.5427877585181364</v>
+        <v>-0.5279172849055325</v>
       </c>
       <c r="AD5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE5" t="s">
         <v>109</v>
@@ -1777,67 +1777,67 @@
         <v>117</v>
       </c>
       <c r="AH5">
-        <v>-0.8398446468695522</v>
+        <v>-0.8492784803506302</v>
       </c>
       <c r="AI5">
-        <v>0.9458517462217577</v>
+        <v>0.9484288963646974</v>
       </c>
       <c r="AJ5">
-        <v>-2.547891424492321</v>
+        <v>-2.588035441970133</v>
       </c>
       <c r="AK5">
-        <v>-1.693309253773119</v>
+        <v>-1.638530576511015</v>
       </c>
       <c r="AL5">
-        <v>-3.732074298369752</v>
+        <v>-3.939449303748471</v>
       </c>
       <c r="AM5">
-        <v>5.170479060669843</v>
+        <v>4.600080156351499</v>
       </c>
       <c r="AN5">
-        <v>3.236897597500552</v>
+        <v>3.502935469794273</v>
       </c>
       <c r="AO5">
-        <v>0.04065799994258394</v>
+        <v>0.04235138087486535</v>
       </c>
       <c r="AP5">
-        <v>1.125345</v>
+        <v>1.117815</v>
       </c>
       <c r="AQ5">
-        <v>1.123021124580156</v>
+        <v>1.109542182637402</v>
       </c>
       <c r="AR5">
-        <v>1.152402238859409</v>
+        <v>1.134942941436532</v>
       </c>
       <c r="AS5">
-        <v>1.125345</v>
+        <v>1.117815</v>
       </c>
       <c r="AT5">
-        <v>1.090795</v>
+        <v>1.075735</v>
       </c>
       <c r="AU5">
-        <v>1.123021124580156</v>
+        <v>1.109542182637402</v>
       </c>
       <c r="AV5">
-        <v>1.135705</v>
+        <v>1.128175</v>
       </c>
       <c r="AW5">
-        <v>-0.002065033762841144</v>
+        <v>-0.007400882402363436</v>
       </c>
       <c r="AX5">
-        <v>0.2243122992127857</v>
+        <v>0.7985344944592524</v>
       </c>
       <c r="AY5">
-        <v>0.002065033762841144</v>
+        <v>0.007400882402363436</v>
       </c>
       <c r="AZ5">
-        <v>0.4109277586344737</v>
+        <v>0.4288475839785803</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.3890722413655263</v>
+        <v>0.3711524160214197</v>
       </c>
       <c r="BC5" t="s">
         <v>121</v>
@@ -1852,22 +1852,22 @@
         <v>500</v>
       </c>
       <c r="BG5">
-        <v>0.009206065695408995</v>
+        <v>0.009268081033086902</v>
       </c>
       <c r="BH5">
-        <v>54312.01737451719</v>
+        <v>53948.6003861002</v>
       </c>
       <c r="BI5">
-        <v>54312.01737451719</v>
+        <v>53948.6003861002</v>
       </c>
       <c r="BJ5">
-        <v>48262.54826254809</v>
+        <v>48262.5482625481</v>
       </c>
       <c r="BK5">
-        <v>543.1201737451719</v>
+        <v>539.486003861002</v>
       </c>
       <c r="BL5">
-        <v>0.005431201737451719</v>
+        <v>0.00539486003861002</v>
       </c>
       <c r="BM5">
         <v>500</v>
@@ -1876,19 +1876,19 @@
         <v>0.005</v>
       </c>
       <c r="BO5">
-        <v>0.02051877473967162</v>
+        <v>0.016844137966935</v>
       </c>
       <c r="BP5">
-        <v>0.01637814451623821</v>
+        <v>0.02071549627878559</v>
       </c>
       <c r="BQ5">
-        <v>0.01107201721481868</v>
+        <v>0.01171675719880854</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT5" t="s">
         <v>128</v>
@@ -1900,7 +1900,7 @@
         <v>129</v>
       </c>
       <c r="BW5" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1908,7 +1908,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1929,142 +1929,142 @@
         <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6">
-        <v>1.506347676435477</v>
+        <v>1.45055166491455</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T6">
-        <v>-0.9978536348105105</v>
+        <v>-0.9834030781674964</v>
       </c>
       <c r="U6">
-        <v>0.9989361574110378</v>
+        <v>0.9921912264379433</v>
       </c>
       <c r="V6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X6">
-        <v>0.9996080869852325</v>
+        <v>0.9986393650502798</v>
       </c>
       <c r="Y6">
         <v>1</v>
       </c>
       <c r="Z6">
-        <v>174.6886794591638</v>
+        <v>-165.1910654254902</v>
       </c>
       <c r="AA6">
-        <v>-21</v>
+        <v>-36</v>
       </c>
       <c r="AB6">
-        <v>-0.9957064281027668</v>
+        <v>-0.9667835432148884</v>
       </c>
       <c r="AC6">
-        <v>0.09256732163582181</v>
+        <v>-0.255596519085973</v>
       </c>
       <c r="AD6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE6" t="s">
         <v>109</v>
       </c>
       <c r="AF6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH6">
-        <v>-0.9953161977947057</v>
+        <v>-0.9654681037371758</v>
       </c>
       <c r="AI6">
-        <v>0.9936570242774376</v>
+        <v>0.9841882005477584</v>
       </c>
       <c r="AJ6">
-        <v>-1.216661059825341</v>
+        <v>-1.160528554167572</v>
       </c>
       <c r="AK6">
-        <v>0.05698617845660994</v>
+        <v>-0.4148216390195625</v>
       </c>
       <c r="AL6">
-        <v>-1.560013788358898</v>
+        <v>-1.555536263347624</v>
       </c>
       <c r="AM6">
-        <v>2.84983750976704</v>
+        <v>2.77309859881427</v>
       </c>
       <c r="AN6">
-        <v>1.31691237659644</v>
+        <v>1.301521619601928</v>
       </c>
       <c r="AO6">
-        <v>0.0327848973214919</v>
+        <v>0.03580426789537371</v>
       </c>
       <c r="AP6">
-        <v>8.893829999999999</v>
+        <v>4.66853</v>
       </c>
       <c r="AQ6">
-        <v>8.838319973424904</v>
+        <v>4.624685900347355</v>
       </c>
       <c r="AR6">
-        <v>8.909695023139358</v>
+        <v>4.673168199706018</v>
       </c>
       <c r="AS6">
-        <v>8.893829999999999</v>
+        <v>4.66853</v>
       </c>
       <c r="AT6">
-        <v>8.720999999999998</v>
+        <v>4.529409999999999</v>
       </c>
       <c r="AU6">
-        <v>8.838319973424904</v>
+        <v>4.624685900347355</v>
       </c>
       <c r="AV6">
-        <v>8.949942499999999</v>
+        <v>4.711175</v>
       </c>
       <c r="AW6">
-        <v>-0.006241408546722374</v>
+        <v>-0.009391414353692566</v>
       </c>
       <c r="AX6">
-        <v>0.9892631156176777</v>
+        <v>1.028118176870543</v>
       </c>
       <c r="AY6">
-        <v>0.006241408546722374</v>
+        <v>0.009391414353692566</v>
       </c>
       <c r="AZ6">
-        <v>0.4385593856589832</v>
+        <v>0.4692038470521554</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3614406143410169</v>
+        <v>0.3307961529478446</v>
       </c>
       <c r="BC6" t="s">
         <v>122</v>
@@ -2079,22 +2079,22 @@
         <v>500</v>
       </c>
       <c r="BG6">
-        <v>0.006309149151715166</v>
+        <v>0.009134566983611554</v>
       </c>
       <c r="BH6">
-        <v>79249.9888616634</v>
+        <v>54737.13213741347</v>
       </c>
       <c r="BI6">
-        <v>79249.9888616634</v>
+        <v>54737.13213741347</v>
       </c>
       <c r="BJ6">
-        <v>8910.670527957405</v>
+        <v>11724.70395122522</v>
       </c>
       <c r="BK6">
-        <v>792.4998886166339</v>
+        <v>547.3713213741347</v>
       </c>
       <c r="BL6">
-        <v>0.007924998886166339</v>
+        <v>0.005473713213741347</v>
       </c>
       <c r="BM6">
         <v>500</v>
@@ -2103,19 +2103,19 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.1020325909977342</v>
+        <v>0.05210186551428068</v>
       </c>
       <c r="BP6">
-        <v>0.05951026908138376</v>
+        <v>0.07052789749143122</v>
       </c>
       <c r="BQ6">
-        <v>0.06965725173385524</v>
+        <v>0.05542113326165151</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT6" t="s">
         <v>128</v>
@@ -2127,7 +2127,7 @@
         <v>129</v>
       </c>
       <c r="BW6" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2135,7 +2135,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2156,142 +2156,142 @@
         <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J7" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K7">
-        <v>0.5206325096177565</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>2.114622406007593</v>
+        <v>1.540104790959755</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q7">
-        <v>0.8801581274044391</v>
+        <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T7">
-        <v>-0.9471943794584506</v>
+        <v>-0.9998770847917888</v>
       </c>
       <c r="U7">
-        <v>0.9038615815922336</v>
+        <v>0.9998852909602977</v>
       </c>
       <c r="V7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X7">
-        <v>0.9981169375730693</v>
+        <v>0.9997624112159706</v>
       </c>
       <c r="Y7">
-        <v>0.9303371883403148</v>
+        <v>1</v>
       </c>
       <c r="Z7">
-        <v>-154.212432023279</v>
+        <v>178.7294547482969</v>
       </c>
       <c r="AA7">
-        <v>-37.99999999999999</v>
+        <v>-9</v>
       </c>
       <c r="AB7">
-        <v>-0.90041318653816</v>
+        <v>-0.999754140373363</v>
       </c>
       <c r="AC7">
-        <v>-0.4350357381965263</v>
+        <v>0.02217338057938198</v>
       </c>
       <c r="AD7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE7" t="s">
         <v>109</v>
       </c>
       <c r="AF7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AH7">
-        <v>-0.8674140530242463</v>
+        <v>-0.9995166100028233</v>
       </c>
       <c r="AI7">
-        <v>0.9501034015349541</v>
+        <v>0.9947645386166181</v>
       </c>
       <c r="AJ7">
-        <v>-1.730949690210708</v>
+        <v>-1.234097001384251</v>
       </c>
       <c r="AK7">
-        <v>-1.059460664405853</v>
+        <v>0.003068617618633421</v>
       </c>
       <c r="AL7">
-        <v>-2.102664683571918</v>
+        <v>-1.632617315044742</v>
       </c>
       <c r="AM7">
-        <v>4.863130987710345</v>
+        <v>2.63470103692516</v>
       </c>
       <c r="AN7">
-        <v>1.648412988117296</v>
+        <v>1.413334024223858</v>
       </c>
       <c r="AO7">
-        <v>0.03619280163420795</v>
+        <v>0.03385698280653627</v>
       </c>
       <c r="AP7">
-        <v>0.69811</v>
+        <v>8.85975</v>
       </c>
       <c r="AQ7">
-        <v>0.6924399251631854</v>
+        <v>8.77136404263751</v>
       </c>
       <c r="AR7">
-        <v>0.6988453578378797</v>
+        <v>8.848263466101178</v>
       </c>
       <c r="AS7">
-        <v>0.69811</v>
+        <v>8.85975</v>
       </c>
       <c r="AT7">
-        <v>0.67987</v>
+        <v>8.652839999999999</v>
       </c>
       <c r="AU7">
-        <v>0.6924399251631854</v>
+        <v>8.77136404263751</v>
       </c>
       <c r="AV7">
-        <v>0.70391</v>
+        <v>8.918673971574993</v>
       </c>
       <c r="AW7">
-        <v>-0.008122036408036824</v>
+        <v>-0.00997612318208644</v>
       </c>
       <c r="AX7">
-        <v>0.9775991097956138</v>
+        <v>1.5</v>
       </c>
       <c r="AY7">
-        <v>0.008122036408036824</v>
+        <v>0.00997612318208644</v>
       </c>
       <c r="AZ7">
-        <v>0.4701848175624421</v>
+        <v>0.394742986482345</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3298151824375579</v>
+        <v>0.405257013517655</v>
       </c>
       <c r="BC7" t="s">
         <v>123</v>
@@ -2303,46 +2303,46 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>440.0790637022196</v>
+        <v>500</v>
       </c>
       <c r="BG7">
-        <v>0.008308146280672139</v>
+        <v>0.006650748788057626</v>
       </c>
       <c r="BH7">
-        <v>60181.89655172386</v>
+        <v>75179.50473453783</v>
       </c>
       <c r="BI7">
-        <v>52969.58537261294</v>
+        <v>75179.50473453783</v>
       </c>
       <c r="BJ7">
-        <v>75875.70063831337</v>
+        <v>8485.510847883725</v>
       </c>
       <c r="BK7">
-        <v>529.6958537261294</v>
+        <v>751.7950473453783</v>
       </c>
       <c r="BL7">
-        <v>0.005296958537261294</v>
+        <v>0.007517950473453783</v>
       </c>
       <c r="BM7">
-        <v>440.0790637022196</v>
+        <v>500</v>
       </c>
       <c r="BN7">
-        <v>0.004400790637022196</v>
+        <v>0.005</v>
       </c>
       <c r="BO7">
-        <v>0.009848675048003748</v>
+        <v>0.1041437762757271</v>
       </c>
       <c r="BP7">
-        <v>0.009901272247688797</v>
+        <v>0.07205070083715533</v>
       </c>
       <c r="BQ7">
-        <v>0.01031808605856937</v>
+        <v>0.0457530893388113</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT7" t="s">
         <v>128</v>
@@ -2354,7 +2354,7 @@
         <v>129</v>
       </c>
       <c r="BW7" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2362,7 +2362,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2383,142 +2383,142 @@
         <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J8" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1.41384031359683</v>
+        <v>2.013370626712889</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T8">
-        <v>-0.9312053040770206</v>
+        <v>-0.9997675492920802</v>
       </c>
       <c r="U8">
-        <v>0.9689152835989751</v>
+        <v>0.9997626282502808</v>
       </c>
       <c r="V8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X8">
-        <v>0.9994915870572633</v>
+        <v>0.9994689242753788</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0.80410148193718</v>
       </c>
       <c r="Z8">
-        <v>-149.5843723307099</v>
+        <v>178.1899570853641</v>
       </c>
       <c r="AA8">
-        <v>-22.99999999999999</v>
+        <v>-10</v>
       </c>
       <c r="AB8">
-        <v>-0.8623756142488881</v>
+        <v>-0.9995010392730865</v>
       </c>
       <c r="AC8">
-        <v>-0.5062689995929565</v>
+        <v>0.03158595403054688</v>
       </c>
       <c r="AD8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE8" t="s">
         <v>109</v>
       </c>
       <c r="AF8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AH8">
-        <v>-0.8619371713251034</v>
+        <v>-0.9011218348550127</v>
       </c>
       <c r="AI8">
-        <v>0.9528918082725243</v>
+        <v>0.9551107866849627</v>
       </c>
       <c r="AJ8">
-        <v>-1.123718285723238</v>
+        <v>-1.640455754305864</v>
       </c>
       <c r="AK8">
-        <v>-0.7452867368265162</v>
+        <v>0.01445650272255401</v>
       </c>
       <c r="AL8">
-        <v>-1.552801375349311</v>
+        <v>-2.00388182563575</v>
       </c>
       <c r="AM8">
-        <v>2.72310269088192</v>
+        <v>3.604303994921653</v>
       </c>
       <c r="AN8">
-        <v>1.291695185302931</v>
+        <v>1.716975064652542</v>
       </c>
       <c r="AO8">
-        <v>0.03761954314789425</v>
+        <v>0.03582629987187833</v>
       </c>
       <c r="AP8">
-        <v>4.67878</v>
+        <v>1.319575</v>
       </c>
       <c r="AQ8">
-        <v>4.63994896940714</v>
+        <v>1.30564442808694</v>
       </c>
       <c r="AR8">
-        <v>4.68564737545134</v>
+        <v>1.316515734399394</v>
       </c>
       <c r="AS8">
-        <v>4.67878</v>
+        <v>1.319575</v>
       </c>
       <c r="AT8">
-        <v>4.54991</v>
+        <v>1.286555</v>
       </c>
       <c r="AU8">
-        <v>4.63994896940714</v>
+        <v>1.30564442808694</v>
       </c>
       <c r="AV8">
-        <v>4.721425</v>
+        <v>1.331225</v>
       </c>
       <c r="AW8">
-        <v>-0.008299392275947974</v>
+        <v>-0.01055686256033969</v>
       </c>
       <c r="AX8">
-        <v>0.9105646756445028</v>
+        <v>1.195757245756244</v>
       </c>
       <c r="AY8">
-        <v>0.008299392275947974</v>
+        <v>0.01055686256033969</v>
       </c>
       <c r="AZ8">
-        <v>0.4734508030190847</v>
+        <v>0.4167263699381163</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3265491969809152</v>
+        <v>0.3832736300618836</v>
       </c>
       <c r="BC8" t="s">
         <v>124</v>
@@ -2533,22 +2533,22 @@
         <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.009114555503785185</v>
+        <v>0.008828600117462056</v>
       </c>
       <c r="BH8">
-        <v>54857.31035291353</v>
+        <v>56634.12017167385</v>
       </c>
       <c r="BI8">
-        <v>54857.31035291353</v>
+        <v>56634.12017167385</v>
       </c>
       <c r="BJ8">
-        <v>11724.70395122522</v>
+        <v>42918.45493562234</v>
       </c>
       <c r="BK8">
-        <v>548.5731035291352</v>
+        <v>566.3412017167385</v>
       </c>
       <c r="BL8">
-        <v>0.005485731035291352</v>
+        <v>0.005663412017167385</v>
       </c>
       <c r="BM8">
         <v>500</v>
@@ -2557,19 +2557,19 @@
         <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.05240715669435765</v>
+        <v>0.01751832726699448</v>
       </c>
       <c r="BP8">
-        <v>0.06773622461395878</v>
+        <v>0.01218796362668838</v>
       </c>
       <c r="BQ8">
-        <v>0.05809900568708407</v>
+        <v>0.009787334379114823</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT8" t="s">
         <v>128</v>
@@ -2581,7 +2581,7 @@
         <v>129</v>
       </c>
       <c r="BW8" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2589,7 +2589,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2610,142 +2610,142 @@
         <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J9" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0.6133616187621953</v>
       </c>
       <c r="L9">
-        <v>1.974934095296505</v>
+        <v>2.204449411330788</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.9033404046905489</v>
       </c>
       <c r="R9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T9">
-        <v>-0.9971996562992052</v>
+        <v>-0.9758541079835924</v>
       </c>
       <c r="U9">
-        <v>0.9985561363126866</v>
+        <v>0.9308345985550868</v>
       </c>
       <c r="V9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X9">
-        <v>0.9992651639121771</v>
+        <v>0.9987840285925634</v>
       </c>
       <c r="Y9">
-        <v>0.8503939498892883</v>
+        <v>0.7789797891513551</v>
       </c>
       <c r="Z9">
-        <v>173.7705818678119</v>
+        <v>-162.0211462119973</v>
       </c>
       <c r="AA9">
-        <v>-25</v>
+        <v>-35</v>
       </c>
       <c r="AB9">
-        <v>-0.9940953813917636</v>
+        <v>-0.9511705007376822</v>
       </c>
       <c r="AC9">
-        <v>0.1085097815662903</v>
+        <v>-0.3086659659347415</v>
       </c>
       <c r="AD9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE9" t="s">
         <v>109</v>
       </c>
       <c r="AF9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH9">
-        <v>-0.9190581859065532</v>
+        <v>-0.8450277678526964</v>
       </c>
       <c r="AI9">
-        <v>0.9630370270288057</v>
+        <v>0.934996782145068</v>
       </c>
       <c r="AJ9">
-        <v>-1.656667388225915</v>
+        <v>-1.777695303795773</v>
       </c>
       <c r="AK9">
-        <v>0.08241201497533358</v>
+        <v>-0.7498397685437406</v>
       </c>
       <c r="AL9">
-        <v>-1.77255413036166</v>
+        <v>-2.291567922100585</v>
       </c>
       <c r="AM9">
-        <v>4.572304537091131</v>
+        <v>4.222128439541687</v>
       </c>
       <c r="AN9">
-        <v>1.397114876266881</v>
+        <v>1.911713276317474</v>
       </c>
       <c r="AO9">
-        <v>0.03342123157228699</v>
+        <v>0.03816490609269878</v>
       </c>
       <c r="AP9">
-        <v>1.326815</v>
+        <v>0.693975</v>
       </c>
       <c r="AQ9">
-        <v>1.315698969481049</v>
+        <v>0.685569284817948</v>
       </c>
       <c r="AR9">
-        <v>1.322327917406295</v>
+        <v>0.6923821101399421</v>
       </c>
       <c r="AS9">
-        <v>1.326815</v>
+        <v>0.693975</v>
       </c>
       <c r="AT9">
-        <v>1.301035</v>
+        <v>0.6716</v>
       </c>
       <c r="AU9">
-        <v>1.315698969481049</v>
+        <v>0.685569284817948</v>
       </c>
       <c r="AV9">
-        <v>1.338465</v>
+        <v>0.699775</v>
       </c>
       <c r="AW9">
-        <v>-0.008377980742568852</v>
+        <v>-0.01211241785662599</v>
       </c>
       <c r="AX9">
-        <v>0.9541657097812445</v>
+        <v>1.449261238284824</v>
       </c>
       <c r="AY9">
-        <v>0.008377980742568852</v>
+        <v>0.01211241785662599</v>
       </c>
       <c r="AZ9">
-        <v>0.4465320228141921</v>
+        <v>0.4568489317983392</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3534679771858079</v>
+        <v>0.3431510682016608</v>
       </c>
       <c r="BC9" t="s">
         <v>125</v>
@@ -2757,46 +2757,46 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>500</v>
+        <v>451.6702023452744</v>
       </c>
       <c r="BG9">
-        <v>0.008780425304205931</v>
+        <v>0.008357649771245401</v>
       </c>
       <c r="BH9">
-        <v>56944.84978540777</v>
+        <v>59825.43103448248</v>
       </c>
       <c r="BI9">
-        <v>56944.84978540777</v>
+        <v>54042.72908147593</v>
       </c>
       <c r="BJ9">
-        <v>42918.45493562234</v>
+        <v>77874.1728181504</v>
       </c>
       <c r="BK9">
-        <v>569.4484978540777</v>
+        <v>540.4272908147592</v>
       </c>
       <c r="BL9">
-        <v>0.005694484978540777</v>
+        <v>0.005404272908147592</v>
       </c>
       <c r="BM9">
-        <v>500</v>
+        <v>451.6702023452744</v>
       </c>
       <c r="BN9">
-        <v>0.005</v>
+        <v>0.004516702023452744</v>
       </c>
       <c r="BO9">
-        <v>0.01926574515095794</v>
+        <v>0.01040298062925951</v>
       </c>
       <c r="BP9">
-        <v>0.01049563285310059</v>
+        <v>0.01126281448920933</v>
       </c>
       <c r="BQ9">
-        <v>0.01417141629622287</v>
+        <v>0.009524033384095231</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT9" t="s">
         <v>128</v>
@@ -2808,7 +2808,7 @@
         <v>129</v>
       </c>
       <c r="BW9" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2816,7 +2816,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2828,7 +2828,7 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
         <v>90</v>
@@ -2837,28 +2837,28 @@
         <v>90</v>
       </c>
       <c r="I10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>3.143653764222756</v>
+        <v>3.117324038070099</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -2870,37 +2870,37 @@
         <v>104</v>
       </c>
       <c r="T10">
-        <v>-0.9318473998340459</v>
+        <v>-0.9318949938952101</v>
       </c>
       <c r="U10">
-        <v>0.9693302174354312</v>
+        <v>0.9693518816195936</v>
       </c>
       <c r="V10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X10">
-        <v>0.9999955500404425</v>
+        <v>0.9999965374669967</v>
       </c>
       <c r="Y10">
         <v>1</v>
       </c>
       <c r="Z10">
-        <v>-149.7339664761072</v>
+        <v>-149.744796748058</v>
       </c>
       <c r="AA10">
-        <v>-3.999999999999993</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AB10">
-        <v>-0.8636944963904277</v>
+        <v>-0.8637897519737722</v>
       </c>
       <c r="AC10">
-        <v>-0.5040156911296367</v>
+        <v>-0.5038524232204199</v>
       </c>
       <c r="AD10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE10" t="s">
         <v>109</v>
@@ -2912,67 +2912,67 @@
         <v>117</v>
       </c>
       <c r="AH10">
-        <v>-0.8636906529848487</v>
+        <v>-0.863786761073248</v>
       </c>
       <c r="AI10">
-        <v>0.952854627449048</v>
+        <v>0.9528864746495984</v>
       </c>
       <c r="AJ10">
-        <v>-2.416449289337514</v>
+        <v>-2.392376283787254</v>
       </c>
       <c r="AK10">
-        <v>-1.436407037481282</v>
+        <v>-1.408328011633546</v>
       </c>
       <c r="AL10">
-        <v>-3.791539223637096</v>
+        <v>-3.771937364661929</v>
       </c>
       <c r="AM10">
-        <v>4.317520847982976</v>
+        <v>4.099146198948727</v>
       </c>
       <c r="AN10">
-        <v>3.369330601403916</v>
+        <v>3.376428300448871</v>
       </c>
       <c r="AO10">
-        <v>0.04168109321489994</v>
+        <v>0.04166159370654634</v>
       </c>
       <c r="AP10">
-        <v>7.5442</v>
+        <v>7.5034</v>
       </c>
       <c r="AQ10">
-        <v>7.452836647467224</v>
+        <v>7.391444690673132</v>
       </c>
       <c r="AR10">
-        <v>7.53222402225918</v>
+        <v>7.479917133398652</v>
       </c>
       <c r="AS10">
-        <v>7.5442</v>
+        <v>7.5034</v>
       </c>
       <c r="AT10">
-        <v>7.3095</v>
+        <v>7.2279</v>
       </c>
       <c r="AU10">
-        <v>7.452836647467224</v>
+        <v>7.391444690673132</v>
       </c>
       <c r="AV10">
-        <v>7.605108901688517</v>
+        <v>7.578036872884579</v>
       </c>
       <c r="AW10">
-        <v>-0.01211040965679273</v>
+        <v>-0.01492061056679214</v>
       </c>
       <c r="AX10">
         <v>1.5</v>
       </c>
       <c r="AY10">
-        <v>0.01211040965679273</v>
+        <v>0.01492061056679214</v>
       </c>
       <c r="AZ10">
-        <v>0.4328075907099503</v>
+        <v>0.437834181965325</v>
       </c>
       <c r="BA10">
-        <v>0.2</v>
+        <v>0.1931142476598409</v>
       </c>
       <c r="BB10">
-        <v>0.3671924092900496</v>
+        <v>0.3690515703748342</v>
       </c>
       <c r="BC10" t="s">
         <v>126</v>
@@ -2987,22 +2987,22 @@
         <v>500</v>
       </c>
       <c r="BG10">
-        <v>0.00807360643786182</v>
+        <v>0.00994707371119476</v>
       </c>
       <c r="BH10">
-        <v>61930.19239273421</v>
+        <v>50266.03949232665</v>
       </c>
       <c r="BI10">
-        <v>61930.19239273421</v>
+        <v>50266.03949232665</v>
       </c>
       <c r="BJ10">
-        <v>8208.980725952944</v>
+        <v>6699.101672885179</v>
       </c>
       <c r="BK10">
-        <v>619.301923927342</v>
+        <v>502.6603949232665</v>
       </c>
       <c r="BL10">
-        <v>0.006193019239273421</v>
+        <v>0.005026603949232665</v>
       </c>
       <c r="BM10">
         <v>500</v>
@@ -3011,19 +3011,19 @@
         <v>0.005</v>
       </c>
       <c r="BO10">
-        <v>0.1008186386230895</v>
+        <v>0.1031024408536954</v>
       </c>
       <c r="BP10">
-        <v>0.1181220543985215</v>
+        <v>0.1421386661445752</v>
       </c>
       <c r="BQ10">
-        <v>0.07260509893331897</v>
+        <v>0.07664223354487559</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT10" t="s">
         <v>128</v>
@@ -3035,7 +3035,7 @@
         <v>129</v>
       </c>
       <c r="BW10" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3043,7 +3043,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3064,31 +3064,31 @@
         <v>90</v>
       </c>
       <c r="I11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J11" s="2">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.08818545360662332</v>
       </c>
       <c r="L11">
-        <v>1.599304465565033</v>
+        <v>1.730993707506369</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q11">
-        <v>0.75</v>
+        <v>0.7720463634016558</v>
       </c>
       <c r="R11" t="s">
         <v>100</v>
@@ -3097,37 +3097,37 @@
         <v>104</v>
       </c>
       <c r="T11">
-        <v>-0.9369233410214868</v>
+        <v>-0.947146817769185</v>
       </c>
       <c r="U11">
-        <v>0.8214132020955007</v>
+        <v>0.8393497317922511</v>
       </c>
       <c r="V11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X11">
-        <v>0.9991907945433268</v>
+        <v>0.9996233830204979</v>
       </c>
       <c r="Y11">
-        <v>0.2482464792281063</v>
+        <v>0.3116808528742547</v>
       </c>
       <c r="Z11">
-        <v>-148.6047692938305</v>
+        <v>-151.6205708619519</v>
       </c>
       <c r="AA11">
-        <v>-25</v>
+        <v>-19</v>
       </c>
       <c r="AB11">
-        <v>-0.853594163097612</v>
+        <v>-0.8798192791817795</v>
       </c>
       <c r="AC11">
-        <v>-0.5209385805694251</v>
+        <v>-0.4753083588367176</v>
       </c>
       <c r="AD11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AE11" t="s">
         <v>109</v>
@@ -3139,67 +3139,67 @@
         <v>117</v>
       </c>
       <c r="AH11">
-        <v>-0.5323168518364058</v>
+        <v>-0.5768037353207548</v>
       </c>
       <c r="AI11">
-        <v>0.7990491246692972</v>
+        <v>0.8197787197684544</v>
       </c>
       <c r="AJ11">
-        <v>-1.255285529206324</v>
+        <v>-1.353656303502145</v>
       </c>
       <c r="AK11">
-        <v>-0.8723776306932588</v>
+        <v>-0.8088064505157689</v>
       </c>
       <c r="AL11">
-        <v>-1.811219957742462</v>
+        <v>-1.976335778246574</v>
       </c>
       <c r="AM11">
-        <v>2.541659773996094</v>
+        <v>2.514447121742387</v>
       </c>
       <c r="AN11">
-        <v>1.564963027451948</v>
+        <v>1.740052641499567</v>
       </c>
       <c r="AO11">
-        <v>0.04263465463848008</v>
+        <v>0.04247612412069771</v>
       </c>
       <c r="AP11">
-        <v>4164.190000000001</v>
+        <v>4124.799999999999</v>
       </c>
       <c r="AQ11">
-        <v>4079.12324815377</v>
+        <v>4013.30198396131</v>
       </c>
       <c r="AR11">
-        <v>4159.342342095461</v>
+        <v>4098.182223738469</v>
       </c>
       <c r="AS11">
-        <v>4164.190000000001</v>
+        <v>4124.799999999999</v>
       </c>
       <c r="AT11">
-        <v>3981.700000000003</v>
+        <v>3902.919999999998</v>
       </c>
       <c r="AU11">
-        <v>4079.12324815377</v>
+        <v>4013.30198396131</v>
       </c>
       <c r="AV11">
-        <v>4297.827500000001</v>
+        <v>4258.437499999999</v>
       </c>
       <c r="AW11">
-        <v>-0.02042816294314895</v>
+        <v>-0.02703113267035711</v>
       </c>
       <c r="AX11">
-        <v>0.6365485125524748</v>
+        <v>0.8343318008694331</v>
       </c>
       <c r="AY11">
-        <v>0.02042816294314895</v>
+        <v>0.02703113267035711</v>
       </c>
       <c r="AZ11">
-        <v>0.3429658010308648</v>
+        <v>0.3380376536616651</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.4570341989691352</v>
+        <v>0.4619623463383349</v>
       </c>
       <c r="BC11" t="s">
         <v>127</v>
@@ -3211,46 +3211,46 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>375</v>
+        <v>386.0231817008279</v>
       </c>
       <c r="BG11">
-        <v>0.03209207552969488</v>
+        <v>0.03239854053529873</v>
       </c>
       <c r="BH11">
-        <v>15580.17023664763</v>
+        <v>15432.79393882703</v>
       </c>
       <c r="BI11">
-        <v>11685.12767748573</v>
+        <v>11914.83243759852</v>
       </c>
       <c r="BJ11">
-        <v>2.806098587597041</v>
+        <v>2.888584279867757</v>
       </c>
       <c r="BK11">
-        <v>116.8512767748573</v>
+        <v>119.1483243759852</v>
       </c>
       <c r="BL11">
-        <v>0.001168512767748573</v>
+        <v>0.001191483243759852</v>
       </c>
       <c r="BM11">
-        <v>374.9999999999999</v>
+        <v>386.0231817008279</v>
       </c>
       <c r="BN11">
-        <v>0.003749999999999999</v>
+        <v>0.003860231817008279</v>
       </c>
       <c r="BO11">
-        <v>595.623806403785</v>
+        <v>585.1478917168006</v>
       </c>
       <c r="BP11">
-        <v>159.1420202819173</v>
+        <v>174.7885094667614</v>
       </c>
       <c r="BQ11">
-        <v>99.75720777625422</v>
+        <v>96.35455436784321</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.06101869837460699</v>
+        <v>0.05886240200635821</v>
       </c>
       <c r="BT11" t="s">
         <v>128</v>
@@ -3262,7 +3262,7 @@
         <v>129</v>
       </c>
       <c r="BW11" s="2">
-        <v>46330</v>
+        <v>46331</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="130">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,78 @@
     <t>TerrainSizeMultiplier</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>EntryPrice</t>
   </si>
   <si>
@@ -172,33 +244,33 @@
     <t>USDJPY</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -235,34 +307,97 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.363,naive=0.4803,drift4=1.708; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=760.4,naive=73.82,drift4=111.3; naive_cap_applied; model_divergence_guard(abs=439.5,thr=400.9)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01605,naive=0.002033,drift4=0.007804; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.1118,naive=0.01372,drift4=0.01319; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.009774,naive=0.003667,drift4=0.009589; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.0164,naive=0.003067,drift4=0.01349; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.135,naive=0.02319,drift4=0.07888; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.05584,naive=0.03161,drift4=0.05665; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01827,naive=0.008448,drift4=0.01018; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.082,naive=0.06809,drift4=0.07305; naive_cap_applied</t>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>转换</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=2.693,naive=0.8993,drift4=1.821; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01342,naive=0.00449,drift4=0.005354; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.03854,naive=0.02362,drift4=0.02181; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.01712,naive=0.01677,drift4=0.008532; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.009308,naive=0.008426,drift4=0.008986; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01463,naive=0.00799,drift4=0.01018; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.0884,naive=0.05091,drift4=0.04608; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=drift4; scores=model=0.04859,naive=0.06339,drift4=0.04649; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.19,drift4=0.38); metric_best=drift4; scores=model=0.09309,naive=0.1262,drift4=0.0648</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=547.3,naive=145.6,drift4=105.8; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -630,10 +765,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BW11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,34 +922,106 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:75">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="J2" s="2">
         <v>46303</v>
@@ -823,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01458900230138204</v>
+        <v>0.02407460330786746</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -832,618 +1039,906 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q2">
         <v>0.75</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S2" t="s">
+        <v>101</v>
+      </c>
+      <c r="T2">
+        <v>0.6928206902461822</v>
+      </c>
+      <c r="U2">
+        <v>0.7117406889278118</v>
+      </c>
+      <c r="V2" t="s">
+        <v>105</v>
+      </c>
+      <c r="W2" t="s">
+        <v>105</v>
+      </c>
+      <c r="X2">
+        <v>0.9998855132681196</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>84.24150280635747</v>
+      </c>
+      <c r="AA2">
+        <v>1.000000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.1003356183271042</v>
+      </c>
+      <c r="AC2">
+        <v>0.9949536490183438</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH2">
+        <v>0.05016206561503538</v>
+      </c>
+      <c r="AI2">
+        <v>0.5048307433445822</v>
+      </c>
+      <c r="AJ2">
+        <v>0.1020999449508141</v>
+      </c>
+      <c r="AK2">
+        <v>0.9880503871214641</v>
+      </c>
+      <c r="AL2">
+        <v>0.07027793773615976</v>
+      </c>
+      <c r="AM2">
+        <v>-0.3980355034554053</v>
+      </c>
+      <c r="AN2">
+        <v>0.1188075714840639</v>
+      </c>
+      <c r="AO2">
+        <v>0.1681991453159395</v>
+      </c>
+      <c r="AP2">
         <v>158.238</v>
       </c>
-      <c r="S2">
-        <v>160.5837465181098</v>
-      </c>
-      <c r="T2">
-        <v>159.894142898648</v>
-      </c>
-      <c r="U2">
+      <c r="AQ2">
+        <v>160.8655542825491</v>
+      </c>
+      <c r="AR2">
+        <v>160.4029470429022</v>
+      </c>
+      <c r="AS2">
         <v>158.238</v>
       </c>
-      <c r="V2">
+      <c r="AT2">
         <v>162.961</v>
       </c>
-      <c r="W2">
-        <v>160.5837465181098</v>
-      </c>
-      <c r="X2">
-        <v>156.6741689879268</v>
-      </c>
-      <c r="Y2">
-        <v>0.01482416687590695</v>
-      </c>
-      <c r="Z2">
+      <c r="AU2">
+        <v>160.8655542825491</v>
+      </c>
+      <c r="AV2">
+        <v>156.4862971449673</v>
+      </c>
+      <c r="AW2">
+        <v>0.01660507768392619</v>
+      </c>
+      <c r="AX2">
         <v>1.5</v>
       </c>
-      <c r="AA2">
-        <v>0.01482416687590695</v>
-      </c>
-      <c r="AB2">
-        <v>0.4671406050378624</v>
-      </c>
-      <c r="AC2">
+      <c r="AY2">
+        <v>0.01660507768392619</v>
+      </c>
+      <c r="AZ2">
+        <v>0.4498912793254098</v>
+      </c>
+      <c r="BA2">
         <v>0.2</v>
       </c>
-      <c r="AD2">
-        <v>0.3328593949621375</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF2">
+      <c r="BB2">
+        <v>0.3501087206745902</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2">
         <v>100000</v>
       </c>
-      <c r="AG2">
+      <c r="BE2">
         <v>100</v>
       </c>
-      <c r="AH2">
+      <c r="BF2">
         <v>375</v>
       </c>
-      <c r="AI2">
-        <v>0.009882777917271298</v>
-      </c>
-      <c r="AJ2">
-        <v>50593.06241478847</v>
-      </c>
-      <c r="AK2">
-        <v>37944.79681109136</v>
-      </c>
-      <c r="AL2">
-        <v>239.7957305520252</v>
-      </c>
-      <c r="AM2">
-        <v>379.4479681109136</v>
-      </c>
-      <c r="AN2">
-        <v>0.003794479681109136</v>
-      </c>
-      <c r="AO2">
+      <c r="BG2">
+        <v>0.01107005178928413</v>
+      </c>
+      <c r="BH2">
+        <v>45166.90703145606</v>
+      </c>
+      <c r="BI2">
+        <v>33875.18027359204</v>
+      </c>
+      <c r="BJ2">
+        <v>214.0774041228532</v>
+      </c>
+      <c r="BK2">
+        <v>338.7518027359204</v>
+      </c>
+      <c r="BL2">
+        <v>0.003387518027359204</v>
+      </c>
+      <c r="BM2">
         <v>375</v>
       </c>
-      <c r="AP2">
+      <c r="BN2">
         <v>0.00375</v>
       </c>
-      <c r="AQ2">
-        <v>2.363441303142246</v>
-      </c>
-      <c r="AR2">
-        <v>0.4802600311475448</v>
-      </c>
-      <c r="AS2">
-        <v>1.707830471656357</v>
-      </c>
-      <c r="AT2">
+      <c r="BO2">
+        <v>2.693198589668274</v>
+      </c>
+      <c r="BP2">
+        <v>0.899311987045616</v>
+      </c>
+      <c r="BQ2">
+        <v>1.821069122178493</v>
+      </c>
+      <c r="BR2">
         <v>1</v>
       </c>
-      <c r="AU2">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY2" s="2">
-        <v>46332</v>
+      <c r="BS2">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>46333</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:75">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="J3" s="2">
         <v>46303</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1.450586121121411</v>
+        <v>2.608648260835368</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="P3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
-      <c r="R3">
-        <v>4183.43</v>
-      </c>
-      <c r="S3">
-        <v>4225.49331633665</v>
+      <c r="R3" t="s">
+        <v>98</v>
+      </c>
+      <c r="S3" t="s">
+        <v>102</v>
       </c>
       <c r="T3">
-        <v>4541.307721122167</v>
+        <v>0.9947843442471344</v>
       </c>
       <c r="U3">
-        <v>4183.43</v>
-      </c>
-      <c r="V3">
-        <v>4020.18</v>
-      </c>
-      <c r="W3">
-        <v>4225.49331633665</v>
+        <v>0.9975588236658219</v>
+      </c>
+      <c r="V3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W3" t="s">
+        <v>93</v>
       </c>
       <c r="X3">
-        <v>4049.7925</v>
+        <v>0.9996234750184455</v>
       </c>
       <c r="Y3">
-        <v>0.01005474367603859</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>0.3147568334984572</v>
+        <v>-8.283736904266698</v>
       </c>
       <c r="AA3">
-        <v>0.01005474367603859</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB3">
-        <v>0.3</v>
+        <v>0.9895667239298753</v>
       </c>
       <c r="AC3">
-        <v>0.3</v>
-      </c>
-      <c r="AD3">
-        <v>0.4</v>
+        <v>-0.1440753236702729</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>91</v>
       </c>
       <c r="AE3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF3">
+        <v>108</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH3">
+        <v>0.9891941273374006</v>
+      </c>
+      <c r="AI3">
+        <v>0.9918665639464317</v>
+      </c>
+      <c r="AJ3">
+        <v>2.061287736769802</v>
+      </c>
+      <c r="AK3">
+        <v>-0.278026538595509</v>
+      </c>
+      <c r="AL3">
+        <v>2.902286626427481</v>
+      </c>
+      <c r="AM3">
+        <v>-4.208624520274346</v>
+      </c>
+      <c r="AN3">
+        <v>2.545408818367472</v>
+      </c>
+      <c r="AO3">
+        <v>0.03247779659324525</v>
+      </c>
+      <c r="AP3">
+        <v>0.8311200000000001</v>
+      </c>
+      <c r="AQ3">
+        <v>0.8369311650412498</v>
+      </c>
+      <c r="AR3">
+        <v>0.8311628896731881</v>
+      </c>
+      <c r="AS3">
+        <v>0.8311200000000001</v>
+      </c>
+      <c r="AT3">
+        <v>0.8457950000000002</v>
+      </c>
+      <c r="AU3">
+        <v>0.8369311650412498</v>
+      </c>
+      <c r="AV3">
+        <v>0.82374875</v>
+      </c>
+      <c r="AW3">
+        <v>0.006991968718415724</v>
+      </c>
+      <c r="AX3">
+        <v>0.7883554405629488</v>
+      </c>
+      <c r="AY3">
+        <v>0.006991968718415724</v>
+      </c>
+      <c r="AZ3">
+        <v>0.4051934291314289</v>
+      </c>
+      <c r="BA3">
+        <v>0.2</v>
+      </c>
+      <c r="BB3">
+        <v>0.3948065708685712</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3">
         <v>100000</v>
       </c>
-      <c r="AG3">
+      <c r="BE3">
         <v>100</v>
       </c>
-      <c r="AH3">
+      <c r="BF3">
         <v>500</v>
       </c>
-      <c r="AI3">
-        <v>0.03194448096418493</v>
-      </c>
-      <c r="AJ3">
-        <v>15652.15601908145</v>
-      </c>
-      <c r="AK3">
-        <v>15652.15601908145</v>
-      </c>
-      <c r="AL3">
-        <v>3.741464783462721</v>
-      </c>
-      <c r="AM3">
-        <v>156.5215601908145</v>
-      </c>
-      <c r="AN3">
-        <v>0.001565215601908145</v>
-      </c>
-      <c r="AO3">
+      <c r="BG3">
+        <v>0.008869056213302593</v>
+      </c>
+      <c r="BH3">
+        <v>56375.78429709983</v>
+      </c>
+      <c r="BI3">
+        <v>56375.78429709983</v>
+      </c>
+      <c r="BJ3">
+        <v>67831.1005596061</v>
+      </c>
+      <c r="BK3">
+        <v>563.7578429709984</v>
+      </c>
+      <c r="BL3">
+        <v>0.005637578429709984</v>
+      </c>
+      <c r="BM3">
         <v>500</v>
       </c>
-      <c r="AP3">
+      <c r="BN3">
         <v>0.005</v>
       </c>
-      <c r="AQ3">
-        <v>760.3931588411428</v>
-      </c>
-      <c r="AR3">
-        <v>73.81855286726629</v>
-      </c>
-      <c r="AS3">
-        <v>111.2853536175391</v>
-      </c>
-      <c r="AT3">
+      <c r="BO3">
+        <v>0.01341981242253103</v>
+      </c>
+      <c r="BP3">
+        <v>0.004489758188444173</v>
+      </c>
+      <c r="BQ3">
+        <v>0.005353564305822857</v>
+      </c>
+      <c r="BR3">
         <v>1</v>
       </c>
-      <c r="AU3">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY3" s="2">
-        <v>46332</v>
+      <c r="BS3">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW3" s="2">
+        <v>46333</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:75">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="J4" s="2">
         <v>46303</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2.522454260273243</v>
+        <v>1.599741836940297</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="O4" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
-      <c r="R4">
-        <v>0.8311200000000001</v>
-      </c>
-      <c r="S4">
-        <v>0.8361829099810705</v>
+      <c r="R4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" t="s">
+        <v>103</v>
       </c>
       <c r="T4">
-        <v>0.831099808869319</v>
+        <v>-0.9832340230473647</v>
       </c>
       <c r="U4">
-        <v>0.8311200000000001</v>
-      </c>
-      <c r="V4">
-        <v>0.8457950000000002</v>
-      </c>
-      <c r="W4">
-        <v>0.8361829099810705</v>
+        <v>0.8423036380005806</v>
+      </c>
+      <c r="V4" t="s">
+        <v>92</v>
+      </c>
+      <c r="W4" t="s">
+        <v>93</v>
       </c>
       <c r="X4">
-        <v>0.82374875</v>
+        <v>0.9993933105170658</v>
       </c>
       <c r="Y4">
-        <v>0.006091671456673399</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>0.686845512100439</v>
+        <v>-161.9673021607393</v>
       </c>
       <c r="AA4">
-        <v>0.006091671456673399</v>
+        <v>18</v>
       </c>
       <c r="AB4">
-        <v>0.4543724514742123</v>
+        <v>-0.9508800100850302</v>
       </c>
       <c r="AC4">
+        <v>-0.3095596976686286</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH4">
+        <v>-0.4751515605916896</v>
+      </c>
+      <c r="AI4">
+        <v>0.7781613949933719</v>
+      </c>
+      <c r="AJ4">
+        <v>-1.119423828492007</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3346260015955845</v>
+      </c>
+      <c r="AL4">
+        <v>-2.414739600526622</v>
+      </c>
+      <c r="AM4">
+        <v>0.4690975117885404</v>
+      </c>
+      <c r="AN4">
+        <v>2.349218443534146</v>
+      </c>
+      <c r="AO4">
+        <v>0.04593511142073507</v>
+      </c>
+      <c r="AP4">
+        <v>6.69229</v>
+      </c>
+      <c r="AQ4">
+        <v>6.719049558989266</v>
+      </c>
+      <c r="AR4">
+        <v>6.769964307006608</v>
+      </c>
+      <c r="AS4">
+        <v>6.69229</v>
+      </c>
+      <c r="AT4">
+        <v>6.676755</v>
+      </c>
+      <c r="AU4">
+        <v>6.719049558989266</v>
+      </c>
+      <c r="AV4">
+        <v>6.67011125</v>
+      </c>
+      <c r="AW4">
+        <v>0.003998565362419535</v>
+      </c>
+      <c r="AX4">
+        <v>1.206540449270901</v>
+      </c>
+      <c r="AY4">
+        <v>0.003998565362419535</v>
+      </c>
+      <c r="AZ4">
+        <v>0.4204253872039641</v>
+      </c>
+      <c r="BA4">
         <v>0.2</v>
       </c>
-      <c r="AD4">
-        <v>0.3456275485257876</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF4">
+      <c r="BB4">
+        <v>0.3795746127960358</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD4">
         <v>100000</v>
       </c>
-      <c r="AG4">
+      <c r="BE4">
         <v>100</v>
       </c>
-      <c r="AH4">
+      <c r="BF4">
         <v>500</v>
       </c>
-      <c r="AI4">
-        <v>0.008869056213302593</v>
-      </c>
-      <c r="AJ4">
-        <v>56375.78429709983</v>
-      </c>
-      <c r="AK4">
-        <v>56375.78429709983</v>
-      </c>
-      <c r="AL4">
-        <v>67831.1005596061</v>
-      </c>
-      <c r="AM4">
-        <v>563.7578429709984</v>
-      </c>
-      <c r="AN4">
-        <v>0.005637578429709984</v>
-      </c>
-      <c r="AO4">
+      <c r="BG4">
+        <v>0.00331407485330129</v>
+      </c>
+      <c r="BH4">
+        <v>150871.6676999401</v>
+      </c>
+      <c r="BI4">
+        <v>150871.6676999401</v>
+      </c>
+      <c r="BJ4">
+        <v>22544.1018993409</v>
+      </c>
+      <c r="BK4">
+        <v>1508.716676999401</v>
+      </c>
+      <c r="BL4">
+        <v>0.01508716676999401</v>
+      </c>
+      <c r="BM4">
         <v>500</v>
       </c>
-      <c r="AP4">
+      <c r="BN4">
         <v>0.005</v>
       </c>
-      <c r="AQ4">
-        <v>0.01605339513942283</v>
-      </c>
-      <c r="AR4">
-        <v>0.002033140302407837</v>
-      </c>
-      <c r="AS4">
-        <v>0.007803653049425891</v>
-      </c>
-      <c r="AT4">
+      <c r="BO4">
+        <v>0.03854380591276182</v>
+      </c>
+      <c r="BP4">
+        <v>0.02362384395631738</v>
+      </c>
+      <c r="BQ4">
+        <v>0.02180680098797023</v>
+      </c>
+      <c r="BR4">
         <v>1</v>
       </c>
-      <c r="AU4">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY4" s="2">
-        <v>46332</v>
+      <c r="BS4">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW4" s="2">
+        <v>46333</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:75">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2">
         <v>46303</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1.604464541811283</v>
+        <v>3.200473376265913</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
-      <c r="R5">
-        <v>6.69229</v>
-      </c>
-      <c r="S5">
-        <v>6.721109288235791</v>
+      <c r="R5" t="s">
+        <v>99</v>
+      </c>
+      <c r="S5" t="s">
+        <v>103</v>
       </c>
       <c r="T5">
-        <v>6.794682099967996</v>
+        <v>-0.9664969282168556</v>
       </c>
       <c r="U5">
-        <v>6.69229</v>
-      </c>
-      <c r="V5">
-        <v>6.676755</v>
-      </c>
-      <c r="W5">
-        <v>6.721109288235791</v>
+        <v>0.9848763988887411</v>
+      </c>
+      <c r="V5" t="s">
+        <v>92</v>
+      </c>
+      <c r="W5" t="s">
+        <v>93</v>
       </c>
       <c r="X5">
-        <v>6.67011125</v>
+        <v>0.9998111247646242</v>
       </c>
       <c r="Y5">
-        <v>0.004306341810619558</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>1.299409941308305</v>
+        <v>-158.9054107864368</v>
       </c>
       <c r="AA5">
-        <v>0.004306341810619558</v>
+        <v>-13.99999999999999</v>
       </c>
       <c r="AB5">
-        <v>0.3497693765638661</v>
+        <v>-0.9329875273377329</v>
       </c>
       <c r="AC5">
+        <v>-0.3599087020790454</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH5">
+        <v>-0.9328113090989043</v>
+      </c>
+      <c r="AI5">
+        <v>0.9738630519562776</v>
+      </c>
+      <c r="AJ5">
+        <v>-2.505823902354199</v>
+      </c>
+      <c r="AK5">
+        <v>-1.05543138205493</v>
+      </c>
+      <c r="AL5">
+        <v>-3.653403311976424</v>
+      </c>
+      <c r="AM5">
+        <v>4.91948676051057</v>
+      </c>
+      <c r="AN5">
+        <v>3.194076018056693</v>
+      </c>
+      <c r="AO5">
+        <v>0.03978066608440503</v>
+      </c>
+      <c r="AP5">
+        <v>1.121</v>
+      </c>
+      <c r="AQ5">
+        <v>1.116196066395072</v>
+      </c>
+      <c r="AR5">
+        <v>1.147884126853173</v>
+      </c>
+      <c r="AS5">
+        <v>1.121</v>
+      </c>
+      <c r="AT5">
+        <v>1.082105</v>
+      </c>
+      <c r="AU5">
+        <v>1.116196066395072</v>
+      </c>
+      <c r="AV5">
+        <v>1.13136</v>
+      </c>
+      <c r="AW5">
+        <v>-0.004285400182808138</v>
+      </c>
+      <c r="AX5">
+        <v>0.4637001549158211</v>
+      </c>
+      <c r="AY5">
+        <v>0.004285400182808138</v>
+      </c>
+      <c r="AZ5">
+        <v>0.4000063189315961</v>
+      </c>
+      <c r="BA5">
         <v>0.2</v>
       </c>
-      <c r="AD5">
-        <v>0.4502306234361339</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF5">
+      <c r="BB5">
+        <v>0.3999936810684039</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD5">
         <v>100000</v>
       </c>
-      <c r="AG5">
+      <c r="BE5">
         <v>100</v>
       </c>
-      <c r="AH5">
+      <c r="BF5">
         <v>500</v>
       </c>
-      <c r="AI5">
-        <v>0.00331407485330129</v>
-      </c>
-      <c r="AJ5">
-        <v>150871.6676999401</v>
-      </c>
-      <c r="AK5">
-        <v>150871.6676999401</v>
-      </c>
-      <c r="AL5">
-        <v>22544.1018993409</v>
-      </c>
-      <c r="AM5">
-        <v>1508.716676999401</v>
-      </c>
-      <c r="AN5">
-        <v>0.01508716676999401</v>
-      </c>
-      <c r="AO5">
+      <c r="BG5">
+        <v>0.009241748438893877</v>
+      </c>
+      <c r="BH5">
+        <v>54102.31660231642</v>
+      </c>
+      <c r="BI5">
+        <v>54102.31660231642</v>
+      </c>
+      <c r="BJ5">
+        <v>48262.54826254809</v>
+      </c>
+      <c r="BK5">
+        <v>541.0231660231642</v>
+      </c>
+      <c r="BL5">
+        <v>0.005410231660231642</v>
+      </c>
+      <c r="BM5">
         <v>500</v>
       </c>
-      <c r="AP5">
+      <c r="BN5">
         <v>0.005</v>
       </c>
-      <c r="AQ5">
-        <v>0.1118440610143663</v>
-      </c>
-      <c r="AR5">
-        <v>0.01372103154163541</v>
-      </c>
-      <c r="AS5">
-        <v>0.01318840020862756</v>
-      </c>
-      <c r="AT5">
+      <c r="BO5">
+        <v>0.01712378927432025</v>
+      </c>
+      <c r="BP5">
+        <v>0.0167679313608971</v>
+      </c>
+      <c r="BQ5">
+        <v>0.008532293031640189</v>
+      </c>
+      <c r="BR5">
         <v>1</v>
       </c>
-      <c r="AU5">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY5" s="2">
-        <v>46332</v>
+      <c r="BS5">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW5" s="2">
+        <v>46333</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:75">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2">
         <v>46303</v>
       </c>
       <c r="K6">
-        <v>0.2490613807029616</v>
+        <v>0.2458364833958997</v>
       </c>
       <c r="L6">
-        <v>1.877789107100387</v>
+        <v>1.870085070879273</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1452,153 +1947,225 @@
         <v>9</v>
       </c>
       <c r="O6" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P6" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q6">
-        <v>0.8122653451757404</v>
-      </c>
-      <c r="R6">
+        <v>0.811459120848975</v>
+      </c>
+      <c r="R6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S6" t="s">
+        <v>104</v>
+      </c>
+      <c r="T6">
+        <v>-0.9995938486339263</v>
+      </c>
+      <c r="U6">
+        <v>0.8861237918375293</v>
+      </c>
+      <c r="V6" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" t="s">
+        <v>93</v>
+      </c>
+      <c r="X6">
+        <v>0.9977243497715103</v>
+      </c>
+      <c r="Y6">
+        <v>0.2911998906324461</v>
+      </c>
+      <c r="Z6">
+        <v>177.4683987736891</v>
+      </c>
+      <c r="AA6">
+        <v>-51</v>
+      </c>
+      <c r="AB6">
+        <v>-0.9990240115521648</v>
+      </c>
+      <c r="AC6">
+        <v>0.04417040120057805</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH6">
+        <v>-0.6435021214474587</v>
+      </c>
+      <c r="AI6">
+        <v>0.8519747578786325</v>
+      </c>
+      <c r="AJ6">
+        <v>-1.551665785897048</v>
+      </c>
+      <c r="AK6">
+        <v>-0.11508525126393</v>
+      </c>
+      <c r="AL6">
+        <v>-1.756890816628371</v>
+      </c>
+      <c r="AM6">
+        <v>4.266061616456902</v>
+      </c>
+      <c r="AN6">
+        <v>1.386310705155682</v>
+      </c>
+      <c r="AO6">
+        <v>0.03450630755689727</v>
+      </c>
+      <c r="AP6">
         <v>0.69814</v>
       </c>
-      <c r="S6">
-        <v>0.6970112888125866</v>
-      </c>
-      <c r="T6">
-        <v>0.7081177700278455</v>
-      </c>
-      <c r="U6">
+      <c r="AQ6">
+        <v>0.6926922374134484</v>
+      </c>
+      <c r="AR6">
+        <v>0.69959817395104</v>
+      </c>
+      <c r="AS6">
         <v>0.69814</v>
       </c>
-      <c r="V6">
+      <c r="AT6">
         <v>0.6799299999999999</v>
       </c>
-      <c r="W6">
-        <v>0.6970112888125866</v>
-      </c>
-      <c r="X6">
+      <c r="AU6">
+        <v>0.6926922374134484</v>
+      </c>
+      <c r="AV6">
         <v>0.70394</v>
       </c>
-      <c r="Y6">
-        <v>-0.001616740463823048</v>
-      </c>
-      <c r="Z6">
-        <v>0.1946053771402444</v>
-      </c>
-      <c r="AA6">
-        <v>0.001616740463823048</v>
-      </c>
-      <c r="AB6">
-        <v>0.4767772973637329</v>
-      </c>
-      <c r="AC6">
+      <c r="AW6">
+        <v>-0.007803252336997669</v>
+      </c>
+      <c r="AX6">
+        <v>0.9392694114744011</v>
+      </c>
+      <c r="AY6">
+        <v>0.007803252336997669</v>
+      </c>
+      <c r="AZ6">
+        <v>0.46370534631997</v>
+      </c>
+      <c r="BA6">
         <v>0.2</v>
       </c>
-      <c r="AD6">
-        <v>0.3232227026362672</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF6">
+      <c r="BB6">
+        <v>0.33629465368003</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD6">
         <v>100000</v>
       </c>
-      <c r="AG6">
+      <c r="BE6">
         <v>100</v>
       </c>
-      <c r="AH6">
-        <v>406.1326725878702</v>
-      </c>
-      <c r="AI6">
+      <c r="BF6">
+        <v>405.7295604244875</v>
+      </c>
+      <c r="BG6">
         <v>0.008307789268628109</v>
       </c>
-      <c r="AJ6">
+      <c r="BH6">
         <v>60184.4827586204</v>
       </c>
-      <c r="AK6">
-        <v>48885.7696621542</v>
-      </c>
-      <c r="AL6">
-        <v>70022.87458411523</v>
-      </c>
-      <c r="AM6">
-        <v>488.857696621542</v>
-      </c>
-      <c r="AN6">
-        <v>0.00488857696621542</v>
-      </c>
-      <c r="AO6">
-        <v>406.1326725878702</v>
-      </c>
-      <c r="AP6">
-        <v>0.004061326725878702</v>
-      </c>
-      <c r="AQ6">
-        <v>0.009774096977956162</v>
-      </c>
-      <c r="AR6">
-        <v>0.003666794577212861</v>
-      </c>
-      <c r="AS6">
-        <v>0.0095891843231839</v>
-      </c>
-      <c r="AT6">
+      <c r="BI6">
+        <v>48837.2474680604</v>
+      </c>
+      <c r="BJ6">
+        <v>69953.37248698027</v>
+      </c>
+      <c r="BK6">
+        <v>488.372474680604</v>
+      </c>
+      <c r="BL6">
+        <v>0.00488372474680604</v>
+      </c>
+      <c r="BM6">
+        <v>405.7295604244875</v>
+      </c>
+      <c r="BN6">
+        <v>0.004057295604244874</v>
+      </c>
+      <c r="BO6">
+        <v>0.009307614201695968</v>
+      </c>
+      <c r="BP6">
+        <v>0.008426058373794502</v>
+      </c>
+      <c r="BQ6">
+        <v>0.008986365524649287</v>
+      </c>
+      <c r="BR6">
         <v>1</v>
       </c>
-      <c r="AU6">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>46332</v>
+      <c r="BS6">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW6" s="2">
+        <v>46333</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:75">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J7" s="2">
         <v>46303</v>
       </c>
       <c r="K7">
-        <v>0.993999687655255</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>1.954194566810592</v>
+        <v>1.966146195077531</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1607,735 +2174,1095 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q7">
-        <v>0.9984999219138138</v>
-      </c>
-      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>100</v>
+      </c>
+      <c r="S7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T7">
+        <v>-0.9906297688353383</v>
+      </c>
+      <c r="U7">
+        <v>0.9957038738817446</v>
+      </c>
+      <c r="V7" t="s">
+        <v>92</v>
+      </c>
+      <c r="W7" t="s">
+        <v>93</v>
+      </c>
+      <c r="X7">
+        <v>0.9996819116233699</v>
+      </c>
+      <c r="Y7">
+        <v>0.7881904656904419</v>
+      </c>
+      <c r="Z7">
+        <v>168.4527775590838</v>
+      </c>
+      <c r="AA7">
+        <v>-16</v>
+      </c>
+      <c r="AB7">
+        <v>-0.9797600553410217</v>
+      </c>
+      <c r="AC7">
+        <v>0.2001755078878486</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH7">
+        <v>-0.8757201497780056</v>
+      </c>
+      <c r="AI7">
+        <v>0.946173802198252</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.609977239368594</v>
+      </c>
+      <c r="AK7">
+        <v>0.2691642661490886</v>
+      </c>
+      <c r="AL7">
+        <v>-1.922705979066893</v>
+      </c>
+      <c r="AM7">
+        <v>3.652326886723105</v>
+      </c>
+      <c r="AN7">
+        <v>1.63064600777599</v>
+      </c>
+      <c r="AO7">
+        <v>0.03520651073548164</v>
+      </c>
+      <c r="AP7">
         <v>1.32289</v>
       </c>
-      <c r="S7">
-        <v>1.319299297150041</v>
-      </c>
-      <c r="T7">
-        <v>1.335433373699483</v>
-      </c>
-      <c r="U7">
+      <c r="AQ7">
+        <v>1.311618205549053</v>
+      </c>
+      <c r="AR7">
+        <v>1.321476570357083</v>
+      </c>
+      <c r="AS7">
         <v>1.32289</v>
       </c>
-      <c r="V7">
+      <c r="AT7">
         <v>1.293185</v>
       </c>
-      <c r="W7">
-        <v>1.319299297150041</v>
-      </c>
-      <c r="X7">
+      <c r="AU7">
+        <v>1.311618205549053</v>
+      </c>
+      <c r="AV7">
         <v>1.33454</v>
       </c>
-      <c r="Y7">
-        <v>-0.002714286788742151</v>
-      </c>
-      <c r="Z7">
-        <v>0.308214836906361</v>
-      </c>
-      <c r="AA7">
-        <v>0.002714286788742151</v>
-      </c>
-      <c r="AB7">
-        <v>0.4774928685666284</v>
-      </c>
-      <c r="AC7">
+      <c r="AW7">
+        <v>-0.008520583306962244</v>
+      </c>
+      <c r="AX7">
+        <v>0.9675360043731577</v>
+      </c>
+      <c r="AY7">
+        <v>0.008520583306962244</v>
+      </c>
+      <c r="AZ7">
+        <v>0.4415522147191451</v>
+      </c>
+      <c r="BA7">
         <v>0.2</v>
       </c>
-      <c r="AD7">
-        <v>0.3225071314333716</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF7">
+      <c r="BB7">
+        <v>0.358447785280855</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD7">
         <v>100000</v>
       </c>
-      <c r="AG7">
+      <c r="BE7">
         <v>100</v>
       </c>
-      <c r="AH7">
-        <v>499.2499609569069</v>
-      </c>
-      <c r="AI7">
+      <c r="BF7">
+        <v>500</v>
+      </c>
+      <c r="BG7">
         <v>0.00880647672897973</v>
       </c>
-      <c r="AJ7">
+      <c r="BH7">
         <v>56776.39484978544</v>
       </c>
-      <c r="AK7">
-        <v>56691.22582405862</v>
-      </c>
-      <c r="AL7">
-        <v>42854.07390188045</v>
-      </c>
-      <c r="AM7">
-        <v>566.9122582405862</v>
-      </c>
-      <c r="AN7">
-        <v>0.005669122582405862</v>
-      </c>
-      <c r="AO7">
-        <v>499.2499609569069</v>
-      </c>
-      <c r="AP7">
-        <v>0.004992499609569069</v>
-      </c>
-      <c r="AQ7">
-        <v>0.01639702406608828</v>
-      </c>
-      <c r="AR7">
-        <v>0.00306728181981787</v>
-      </c>
-      <c r="AS7">
-        <v>0.01348520778130016</v>
-      </c>
-      <c r="AT7">
+      <c r="BI7">
+        <v>56776.39484978544</v>
+      </c>
+      <c r="BJ7">
+        <v>42918.45493562234</v>
+      </c>
+      <c r="BK7">
+        <v>567.7639484978544</v>
+      </c>
+      <c r="BL7">
+        <v>0.005677639484978543</v>
+      </c>
+      <c r="BM7">
+        <v>500</v>
+      </c>
+      <c r="BN7">
+        <v>0.005</v>
+      </c>
+      <c r="BO7">
+        <v>0.01463399577979556</v>
+      </c>
+      <c r="BP7">
+        <v>0.00799003682239416</v>
+      </c>
+      <c r="BQ7">
+        <v>0.01018317840457146</v>
+      </c>
+      <c r="BR7">
         <v>1</v>
       </c>
-      <c r="AU7">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY7" s="2">
-        <v>46332</v>
+      <c r="BS7">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW7" s="2">
+        <v>46333</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:75">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J8" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1.529786498764099</v>
+        <v>1.504100250601936</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P8" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="s">
+        <v>100</v>
+      </c>
+      <c r="S8" t="s">
+        <v>104</v>
+      </c>
+      <c r="T8">
+        <v>-0.9944317966357554</v>
+      </c>
+      <c r="U8">
+        <v>0.9974555167659012</v>
+      </c>
+      <c r="V8" t="s">
+        <v>92</v>
+      </c>
+      <c r="W8" t="s">
+        <v>93</v>
+      </c>
+      <c r="X8">
+        <v>0.999844833119245</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>171.4408444705665</v>
+      </c>
+      <c r="AA8">
+        <v>-6.999999999999997</v>
+      </c>
+      <c r="AB8">
+        <v>-0.9888627291366784</v>
+      </c>
+      <c r="AC8">
+        <v>0.1488304502592137</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH8">
+        <v>-0.9887092903915033</v>
+      </c>
+      <c r="AI8">
+        <v>0.9915682451923054</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.206847608800289</v>
+      </c>
+      <c r="AK8">
+        <v>0.1628464539605917</v>
+      </c>
+      <c r="AL8">
+        <v>-1.585084138197813</v>
+      </c>
+      <c r="AM8">
+        <v>2.523731344160301</v>
+      </c>
+      <c r="AN8">
+        <v>1.37968017748996</v>
+      </c>
+      <c r="AO8">
+        <v>0.03357510093622675</v>
+      </c>
+      <c r="AP8">
         <v>8.86997</v>
       </c>
-      <c r="S8">
-        <v>8.802851663718453</v>
-      </c>
-      <c r="T8">
-        <v>8.870694670444534</v>
-      </c>
-      <c r="U8">
+      <c r="AQ8">
+        <v>8.793249894505548</v>
+      </c>
+      <c r="AR8">
+        <v>8.867917266924447</v>
+      </c>
+      <c r="AS8">
         <v>8.86997</v>
       </c>
-      <c r="V8">
+      <c r="AT8">
         <v>8.67328</v>
       </c>
-      <c r="W8">
-        <v>8.802851663718453</v>
-      </c>
-      <c r="X8">
+      <c r="AU8">
+        <v>8.793249894505548</v>
+      </c>
+      <c r="AV8">
         <v>8.9260825</v>
       </c>
-      <c r="Y8">
-        <v>-0.00756691807092327</v>
-      </c>
-      <c r="Z8">
-        <v>1.196138761979035</v>
-      </c>
-      <c r="AA8">
-        <v>0.00756691807092327</v>
-      </c>
-      <c r="AB8">
-        <v>0.4570767892541459</v>
-      </c>
-      <c r="AC8">
+      <c r="AW8">
+        <v>-0.008649421079716411</v>
+      </c>
+      <c r="AX8">
+        <v>1.367255165862396</v>
+      </c>
+      <c r="AY8">
+        <v>0.008649421079716411</v>
+      </c>
+      <c r="AZ8">
+        <v>0.4142675027226242</v>
+      </c>
+      <c r="BA8">
         <v>0.2</v>
       </c>
-      <c r="AD8">
-        <v>0.3429232107458541</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF8">
+      <c r="BB8">
+        <v>0.3857324972773759</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD8">
         <v>100000</v>
       </c>
-      <c r="AG8">
+      <c r="BE8">
         <v>100</v>
       </c>
-      <c r="AH8">
+      <c r="BF8">
         <v>500</v>
       </c>
-      <c r="AI8">
+      <c r="BG8">
         <v>0.006326120606946686</v>
       </c>
-      <c r="AJ8">
+      <c r="BH8">
         <v>79037.38026286634</v>
       </c>
-      <c r="AK8">
+      <c r="BI8">
         <v>79037.38026286634</v>
       </c>
-      <c r="AL8">
+      <c r="BJ8">
         <v>8910.670527957403</v>
       </c>
-      <c r="AM8">
+      <c r="BK8">
         <v>790.3738026286634</v>
       </c>
-      <c r="AN8">
+      <c r="BL8">
         <v>0.007903738026286633</v>
       </c>
-      <c r="AO8">
+      <c r="BM8">
         <v>500</v>
       </c>
-      <c r="AP8">
+      <c r="BN8">
         <v>0.005</v>
       </c>
-      <c r="AQ8">
-        <v>0.1349903807831879</v>
-      </c>
-      <c r="AR8">
-        <v>0.02319094642305747</v>
-      </c>
-      <c r="AS8">
-        <v>0.07888157989077144</v>
-      </c>
-      <c r="AT8">
+      <c r="BO8">
+        <v>0.08840440293024392</v>
+      </c>
+      <c r="BP8">
+        <v>0.0509058285460141</v>
+      </c>
+      <c r="BQ8">
+        <v>0.04607860186730026</v>
+      </c>
+      <c r="BR8">
         <v>1</v>
       </c>
-      <c r="AU8">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY8" s="2">
-        <v>46332</v>
+      <c r="BS8">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW8" s="2">
+        <v>46333</v>
       </c>
     </row>
-    <row r="9" spans="1:51">
+    <row r="9" spans="1:75">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J9" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1.457646960458371</v>
+        <v>1.409466085787301</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O9" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="s">
+        <v>100</v>
+      </c>
+      <c r="S9" t="s">
+        <v>104</v>
+      </c>
+      <c r="T9">
+        <v>-0.9936108756894084</v>
+      </c>
+      <c r="U9">
+        <v>0.996791477885986</v>
+      </c>
+      <c r="V9" t="s">
+        <v>92</v>
+      </c>
+      <c r="W9" t="s">
+        <v>93</v>
+      </c>
+      <c r="X9">
+        <v>0.9986663353030091</v>
+      </c>
+      <c r="Y9">
+        <v>0.8524073679593994</v>
+      </c>
+      <c r="Z9">
+        <v>170.5867373744173</v>
+      </c>
+      <c r="AA9">
+        <v>-39</v>
+      </c>
+      <c r="AB9">
+        <v>-0.9865343290569012</v>
+      </c>
+      <c r="AC9">
+        <v>0.1635543261190295</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH9">
+        <v>-0.9125131181941951</v>
+      </c>
+      <c r="AI9">
+        <v>0.9609889996655083</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.150576665151099</v>
+      </c>
+      <c r="AK9">
+        <v>0.09271125474085967</v>
+      </c>
+      <c r="AL9">
+        <v>-1.407305197902939</v>
+      </c>
+      <c r="AM9">
+        <v>2.887102683106255</v>
+      </c>
+      <c r="AN9">
+        <v>1.160703551299741</v>
+      </c>
+      <c r="AO9">
+        <v>0.03323993332996663</v>
+      </c>
+      <c r="AP9">
         <v>4.66636</v>
       </c>
-      <c r="S9">
-        <v>4.621683463620208</v>
-      </c>
-      <c r="T9">
-        <v>4.669399294548362</v>
-      </c>
-      <c r="U9">
+      <c r="AQ9">
+        <v>4.620642050255284</v>
+      </c>
+      <c r="AR9">
+        <v>4.671617180535127</v>
+      </c>
+      <c r="AS9">
         <v>4.66636</v>
       </c>
-      <c r="V9">
+      <c r="AT9">
         <v>4.52507</v>
       </c>
-      <c r="W9">
-        <v>4.621683463620208</v>
-      </c>
-      <c r="X9">
+      <c r="AU9">
+        <v>4.620642050255284</v>
+      </c>
+      <c r="AV9">
         <v>4.709005</v>
       </c>
-      <c r="Y9">
-        <v>-0.009574172669873751</v>
-      </c>
-      <c r="Z9">
-        <v>1.047638325238411</v>
-      </c>
-      <c r="AA9">
-        <v>0.009574172669873751</v>
-      </c>
-      <c r="AB9">
-        <v>0.4736076888209541</v>
-      </c>
-      <c r="AC9">
+      <c r="AW9">
+        <v>-0.009797347342407451</v>
+      </c>
+      <c r="AX9">
+        <v>1.072058852027586</v>
+      </c>
+      <c r="AY9">
+        <v>0.009797347342407451</v>
+      </c>
+      <c r="AZ9">
+        <v>0.4593336426499773</v>
+      </c>
+      <c r="BA9">
         <v>0.2</v>
       </c>
-      <c r="AD9">
-        <v>0.3263923111790459</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF9">
+      <c r="BB9">
+        <v>0.3406663573500228</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD9">
         <v>100000</v>
       </c>
-      <c r="AG9">
+      <c r="BE9">
         <v>100</v>
       </c>
-      <c r="AH9">
+      <c r="BF9">
         <v>500</v>
       </c>
-      <c r="AI9">
+      <c r="BG9">
         <v>0.009138814836403544</v>
       </c>
-      <c r="AJ9">
+      <c r="BH9">
         <v>54711.68952983932</v>
       </c>
-      <c r="AK9">
+      <c r="BI9">
         <v>54711.68952983932</v>
       </c>
-      <c r="AL9">
+      <c r="BJ9">
         <v>11724.70395122522</v>
       </c>
-      <c r="AM9">
+      <c r="BK9">
         <v>547.1168952983932</v>
       </c>
-      <c r="AN9">
+      <c r="BL9">
         <v>0.005471168952983932</v>
       </c>
-      <c r="AO9">
+      <c r="BM9">
         <v>500</v>
       </c>
-      <c r="AP9">
+      <c r="BN9">
         <v>0.005</v>
       </c>
-      <c r="AQ9">
-        <v>0.05583920324254457</v>
-      </c>
-      <c r="AR9">
-        <v>0.03161281388442377</v>
-      </c>
-      <c r="AS9">
-        <v>0.05664805801824233</v>
-      </c>
-      <c r="AT9">
+      <c r="BO9">
+        <v>0.04858936509788791</v>
+      </c>
+      <c r="BP9">
+        <v>0.0633892580717977</v>
+      </c>
+      <c r="BQ9">
+        <v>0.04649484837029631</v>
+      </c>
+      <c r="BR9">
         <v>1</v>
       </c>
-      <c r="AU9">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV9" t="s">
+      <c r="BS9">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW9" s="2">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:75">
+      <c r="A10" t="s">
         <v>83</v>
       </c>
-      <c r="AW9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY9" s="2">
-        <v>46332</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51">
-      <c r="A10" t="s">
-        <v>59</v>
-      </c>
       <c r="B10" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J10" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>3.111706344378135</v>
+        <v>3.061238907503078</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
-      <c r="R10">
-        <v>1.121</v>
-      </c>
-      <c r="S10">
-        <v>1.101864685363431</v>
+      <c r="R10" t="s">
+        <v>99</v>
+      </c>
+      <c r="S10" t="s">
+        <v>103</v>
       </c>
       <c r="T10">
-        <v>1.110267646632525</v>
+        <v>-0.9746198314191159</v>
       </c>
       <c r="U10">
-        <v>1.121</v>
-      </c>
-      <c r="V10">
-        <v>1.082105</v>
-      </c>
-      <c r="W10">
-        <v>1.101864685363431</v>
+        <v>0.9885556652336881</v>
+      </c>
+      <c r="V10" t="s">
+        <v>92</v>
+      </c>
+      <c r="W10" t="s">
+        <v>93</v>
       </c>
       <c r="X10">
-        <v>1.133756876424379</v>
+        <v>0.9999069643803437</v>
       </c>
       <c r="Y10">
-        <v>-0.01706986140639492</v>
+        <v>1</v>
       </c>
       <c r="Z10">
+        <v>-161.6656935826206</v>
+      </c>
+      <c r="AA10">
+        <v>-10</v>
+      </c>
+      <c r="AB10">
+        <v>-0.9492373013588192</v>
+      </c>
+      <c r="AC10">
+        <v>-0.3145608775881486</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH10">
+        <v>-0.9491489884782864</v>
+      </c>
+      <c r="AI10">
+        <v>0.9789578689314791</v>
+      </c>
+      <c r="AJ10">
+        <v>-2.377430401374961</v>
+      </c>
+      <c r="AK10">
+        <v>-0.8435569835128667</v>
+      </c>
+      <c r="AL10">
+        <v>-3.583344725562733</v>
+      </c>
+      <c r="AM10">
+        <v>4.438944894702015</v>
+      </c>
+      <c r="AN10">
+        <v>3.170392461621871</v>
+      </c>
+      <c r="AO10">
+        <v>0.03853839339524651</v>
+      </c>
+      <c r="AP10">
+        <v>7.5138</v>
+      </c>
+      <c r="AQ10">
+        <v>7.403433790169089</v>
+      </c>
+      <c r="AR10">
+        <v>7.489270367096571</v>
+      </c>
+      <c r="AS10">
+        <v>7.5138</v>
+      </c>
+      <c r="AT10">
+        <v>7.248699999999999</v>
+      </c>
+      <c r="AU10">
+        <v>7.403433790169089</v>
+      </c>
+      <c r="AV10">
+        <v>7.587377473220607</v>
+      </c>
+      <c r="AW10">
+        <v>-0.01468846786325306</v>
+      </c>
+      <c r="AX10">
         <v>1.5</v>
       </c>
-      <c r="AA10">
-        <v>0.01706986140639492</v>
-      </c>
-      <c r="AB10">
-        <v>0.4254104921230813</v>
-      </c>
-      <c r="AC10">
-        <v>0.2</v>
-      </c>
-      <c r="AD10">
-        <v>0.3745895078769187</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF10">
+      <c r="AY10">
+        <v>0.01468846786325306</v>
+      </c>
+      <c r="AZ10">
+        <v>0.4325173857116943</v>
+      </c>
+      <c r="BA10">
+        <v>0.191184171681543</v>
+      </c>
+      <c r="BB10">
+        <v>0.3762984426067627</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BD10">
         <v>100000</v>
       </c>
-      <c r="AG10">
+      <c r="BE10">
         <v>100</v>
       </c>
-      <c r="AH10">
+      <c r="BF10">
         <v>500</v>
       </c>
-      <c r="AI10">
-        <v>0.01137990760426328</v>
-      </c>
-      <c r="AJ10">
-        <v>43937.0878382777</v>
-      </c>
-      <c r="AK10">
-        <v>43937.0878382777</v>
-      </c>
-      <c r="AL10">
-        <v>39194.54758097922</v>
-      </c>
-      <c r="AM10">
-        <v>439.370878382777</v>
-      </c>
-      <c r="AN10">
-        <v>0.00439370878382777</v>
-      </c>
-      <c r="AO10">
+      <c r="BG10">
+        <v>0.009792311908835373</v>
+      </c>
+      <c r="BH10">
+        <v>51060.46505206414</v>
+      </c>
+      <c r="BI10">
+        <v>51060.46505206414</v>
+      </c>
+      <c r="BJ10">
+        <v>6795.558179890886</v>
+      </c>
+      <c r="BK10">
+        <v>510.6046505206414</v>
+      </c>
+      <c r="BL10">
+        <v>0.005106046505206414</v>
+      </c>
+      <c r="BM10">
         <v>500</v>
       </c>
-      <c r="AP10">
+      <c r="BN10">
         <v>0.005</v>
       </c>
-      <c r="AQ10">
-        <v>0.01826654841922811</v>
-      </c>
-      <c r="AR10">
-        <v>0.008448211778001181</v>
-      </c>
-      <c r="AS10">
-        <v>0.01018246576958416</v>
-      </c>
-      <c r="AT10">
+      <c r="BO10">
+        <v>0.09309397738808024</v>
+      </c>
+      <c r="BP10">
+        <v>0.1262127166845696</v>
+      </c>
+      <c r="BQ10">
+        <v>0.06479903164492998</v>
+      </c>
+      <c r="BR10">
         <v>1</v>
       </c>
-      <c r="AU10">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX10" t="s">
+      <c r="BS10">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW10" s="2">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:75">
+      <c r="A11" t="s">
         <v>84</v>
       </c>
-      <c r="AY10" s="2">
-        <v>46332</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51">
-      <c r="A11" t="s">
-        <v>60</v>
-      </c>
       <c r="B11" s="2">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J11" s="2">
         <v>46303</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>3.087842468067774</v>
+        <v>1.463127748378913</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O11" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q11">
+        <v>0.75</v>
+      </c>
+      <c r="R11" t="s">
+        <v>99</v>
+      </c>
+      <c r="S11" t="s">
+        <v>103</v>
+      </c>
+      <c r="T11">
+        <v>-0.9849837491747254</v>
+      </c>
+      <c r="U11">
+        <v>0.8430269307424129</v>
+      </c>
+      <c r="V11" t="s">
+        <v>92</v>
+      </c>
+      <c r="W11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X11">
+        <v>0.9991369744551456</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>-162.9401487027914</v>
+      </c>
+      <c r="AA11">
+        <v>-28</v>
+      </c>
+      <c r="AB11">
+        <v>-0.9559988221363884</v>
+      </c>
+      <c r="AC11">
+        <v>-0.2933705030739082</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH11">
+        <v>-0.477586885366017</v>
+      </c>
+      <c r="AI11">
+        <v>0.7810759562582975</v>
+      </c>
+      <c r="AJ11">
+        <v>-1.182397965058</v>
+      </c>
+      <c r="AK11">
+        <v>-0.4516021298893421</v>
+      </c>
+      <c r="AL11">
+        <v>-1.509037865407516</v>
+      </c>
+      <c r="AM11">
+        <v>2.784771657094342</v>
+      </c>
+      <c r="AN11">
+        <v>1.25894103794398</v>
+      </c>
+      <c r="AO11">
+        <v>0.03614420961279985</v>
+      </c>
+      <c r="AP11">
+        <v>4183.43</v>
+      </c>
+      <c r="AQ11">
+        <v>4114.072840231664</v>
+      </c>
+      <c r="AR11">
+        <v>4193.313085983336</v>
+      </c>
+      <c r="AS11">
+        <v>4183.43</v>
+      </c>
+      <c r="AT11">
+        <v>4020.18</v>
+      </c>
+      <c r="AU11">
+        <v>4114.072840231664</v>
+      </c>
+      <c r="AV11">
+        <v>4317.0675</v>
+      </c>
+      <c r="AW11">
+        <v>-0.01657901764062882</v>
+      </c>
+      <c r="AX11">
+        <v>0.5189947415084517</v>
+      </c>
+      <c r="AY11">
+        <v>0.01657901764062882</v>
+      </c>
+      <c r="AZ11">
+        <v>0.3537327362001669</v>
+      </c>
+      <c r="BA11">
+        <v>0.2</v>
+      </c>
+      <c r="BB11">
+        <v>0.4462672637998331</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>127</v>
+      </c>
+      <c r="BD11">
+        <v>100000</v>
+      </c>
+      <c r="BE11">
+        <v>100</v>
+      </c>
+      <c r="BF11">
+        <v>375</v>
+      </c>
+      <c r="BG11">
+        <v>0.03194448096418493</v>
+      </c>
+      <c r="BH11">
+        <v>15652.15601908145</v>
+      </c>
+      <c r="BI11">
+        <v>11739.11701431109</v>
+      </c>
+      <c r="BJ11">
+        <v>2.806098587597041</v>
+      </c>
+      <c r="BK11">
+        <v>117.3911701431109</v>
+      </c>
+      <c r="BL11">
+        <v>0.001173911701431109</v>
+      </c>
+      <c r="BM11">
+        <v>375</v>
+      </c>
+      <c r="BN11">
+        <v>0.00375</v>
+      </c>
+      <c r="BO11">
+        <v>547.2567010437193</v>
+      </c>
+      <c r="BP11">
+        <v>145.6165379517798</v>
+      </c>
+      <c r="BQ11">
+        <v>105.7819641208196</v>
+      </c>
+      <c r="BR11">
         <v>1</v>
       </c>
-      <c r="R11">
-        <v>7.5138</v>
-      </c>
-      <c r="S11">
-        <v>7.380730626902807</v>
-      </c>
-      <c r="T11">
-        <v>7.421476056136551</v>
-      </c>
-      <c r="U11">
-        <v>7.5138</v>
-      </c>
-      <c r="V11">
-        <v>7.248699999999999</v>
-      </c>
-      <c r="W11">
-        <v>7.380730626902807</v>
-      </c>
-      <c r="X11">
-        <v>7.602512915398129</v>
-      </c>
-      <c r="Y11">
-        <v>-0.017709996685724</v>
-      </c>
-      <c r="Z11">
-        <v>1.5</v>
-      </c>
-      <c r="AA11">
-        <v>0.017709996685724</v>
-      </c>
-      <c r="AB11">
-        <v>0.4573007896439217</v>
-      </c>
-      <c r="AC11">
-        <v>0.2</v>
-      </c>
-      <c r="AD11">
-        <v>0.3426992103560783</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF11">
-        <v>100000</v>
-      </c>
-      <c r="AG11">
-        <v>100</v>
-      </c>
-      <c r="AH11">
-        <v>500</v>
-      </c>
-      <c r="AI11">
-        <v>0.01180666445714934</v>
-      </c>
-      <c r="AJ11">
-        <v>42348.96331768224</v>
-      </c>
-      <c r="AK11">
-        <v>42348.96331768224</v>
-      </c>
-      <c r="AL11">
-        <v>5636.15791179992</v>
-      </c>
-      <c r="AM11">
-        <v>423.4896331768224</v>
-      </c>
-      <c r="AN11">
-        <v>0.004234896331768224</v>
-      </c>
-      <c r="AO11">
-        <v>499.9999999999999</v>
-      </c>
-      <c r="AP11">
-        <v>0.004999999999999999</v>
-      </c>
-      <c r="AQ11">
-        <v>0.08199934787309396</v>
-      </c>
-      <c r="AR11">
-        <v>0.06809082658223674</v>
-      </c>
-      <c r="AS11">
-        <v>0.07304692337405704</v>
-      </c>
-      <c r="AT11">
-        <v>1</v>
-      </c>
-      <c r="AU11">
-        <v>0.05864565212620911</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY11" s="2">
-        <v>46332</v>
+      <c r="BS11">
+        <v>0.05973872430498751</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>129</v>
+      </c>
+      <c r="BW11" s="2">
+        <v>46333</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="127">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,78 @@
     <t>TerrainSizeMultiplier</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>EntryPrice</t>
   </si>
   <si>
@@ -172,30 +244,30 @@
     <t>USDJPY</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -235,34 +307,88 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.312,naive=0.4836,drift4=1.643; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=737,naive=66.32,drift4=119.4; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.01645,naive=0.0008856,drift4=0.008374; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=0.1059,naive=0.01231,drift4=0.0112; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.009302,naive=0.002845,drift4=0.009197; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.01557,naive=0.001887,drift4=0.01356; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.1261,naive=0.02255,drift4=0.07513; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.05237,naive=0.02668,drift4=0.06223; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01617,naive=0.008449,drift4=0.01013; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.06964,naive=0.07013,drift4=0.07304; naive_cap_applied</t>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=2.623,naive=0.9405,drift4=1.791; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.0368,naive=0.02224,drift4=0.02023; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01282,naive=0.003084,drift4=0.006728; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.19,drift4=0.40); metric_best=drift4; scores=model=0.01542,naive=0.01741,drift4=0.008396</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01339,naive=0.006914,drift4=0.01052; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.04936,naive=0.05745,drift4=0.05057; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.009039,naive=0.007752,drift4=0.008141; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.08386,naive=0.05236,drift4=0.03909; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=508.7,naive=138.1,drift4=113.3; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.19,drift4=0.37); metric_best=drift4; scores=model=0.08986,naive=0.1354,drift4=0.06847</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -630,10 +756,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BW11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,10 +913,82 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:75">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
         <v>46307</v>
@@ -799,22 +997,22 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="J2" s="2">
         <v>46304</v>
@@ -823,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.05059162212856247</v>
+        <v>0.06615792576073938</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -832,120 +1030,192 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q2">
         <v>0.75</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S2" t="s">
+        <v>101</v>
+      </c>
+      <c r="T2">
+        <v>0.7162025119611628</v>
+      </c>
+      <c r="U2">
+        <v>0.7222628639974663</v>
+      </c>
+      <c r="V2" t="s">
+        <v>91</v>
+      </c>
+      <c r="W2" t="s">
+        <v>93</v>
+      </c>
+      <c r="X2">
+        <v>0.9998869344597723</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>80.28096206226725</v>
+      </c>
+      <c r="AA2">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AB2">
+        <v>0.1688168945785773</v>
+      </c>
+      <c r="AC2">
+        <v>0.9856474299184499</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AH2">
+        <v>0.08439890360259611</v>
+      </c>
+      <c r="AI2">
+        <v>0.5355619450914663</v>
+      </c>
+      <c r="AJ2">
+        <v>0.1757691715172014</v>
+      </c>
+      <c r="AK2">
+        <v>0.9810580982504591</v>
+      </c>
+      <c r="AL2">
+        <v>0.1037209690977838</v>
+      </c>
+      <c r="AM2">
+        <v>-0.641657935670563</v>
+      </c>
+      <c r="AN2">
+        <v>0.1500875380662124</v>
+      </c>
+      <c r="AO2">
+        <v>0.1002903356201814</v>
+      </c>
+      <c r="AP2">
         <v>158.322</v>
       </c>
-      <c r="S2">
-        <v>160.6982983002724</v>
-      </c>
-      <c r="T2">
-        <v>159.9712610104251</v>
-      </c>
-      <c r="U2">
+      <c r="AQ2">
+        <v>160.990289372439</v>
+      </c>
+      <c r="AR2">
+        <v>160.5068632473895</v>
+      </c>
+      <c r="AS2">
         <v>158.322</v>
       </c>
-      <c r="V2">
+      <c r="AT2">
         <v>163.129</v>
       </c>
-      <c r="W2">
-        <v>160.6982983002724</v>
-      </c>
-      <c r="X2">
-        <v>156.7378011331517</v>
-      </c>
-      <c r="Y2">
-        <v>0.01500927413923755</v>
-      </c>
-      <c r="Z2">
+      <c r="AU2">
+        <v>160.990289372439</v>
+      </c>
+      <c r="AV2">
+        <v>156.543140418374</v>
+      </c>
+      <c r="AW2">
+        <v>0.0168535602912986</v>
+      </c>
+      <c r="AX2">
         <v>1.5</v>
       </c>
-      <c r="AA2">
-        <v>0.01500927413923755</v>
-      </c>
-      <c r="AB2">
-        <v>0.4653018202512832</v>
-      </c>
-      <c r="AC2">
+      <c r="AY2">
+        <v>0.0168535602912986</v>
+      </c>
+      <c r="AZ2">
+        <v>0.4489890263690312</v>
+      </c>
+      <c r="BA2">
         <v>0.2</v>
       </c>
-      <c r="AD2">
-        <v>0.3346981797487168</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF2">
+      <c r="BB2">
+        <v>0.3510109736309688</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>115</v>
+      </c>
+      <c r="BD2">
         <v>100000</v>
       </c>
-      <c r="AG2">
+      <c r="BE2">
         <v>100</v>
       </c>
-      <c r="AH2">
+      <c r="BF2">
         <v>375</v>
       </c>
-      <c r="AI2">
-        <v>0.0100061827594917</v>
-      </c>
-      <c r="AJ2">
-        <v>49969.105303989</v>
-      </c>
-      <c r="AK2">
-        <v>37476.82897799175</v>
-      </c>
-      <c r="AL2">
-        <v>236.7127056125602</v>
-      </c>
-      <c r="AM2">
-        <v>374.7682897799176</v>
-      </c>
-      <c r="AN2">
-        <v>0.003747682897799176</v>
-      </c>
-      <c r="AO2">
-        <v>375</v>
-      </c>
-      <c r="AP2">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ2">
-        <v>2.311632860677646</v>
-      </c>
-      <c r="AR2">
-        <v>0.4835657032891513</v>
-      </c>
-      <c r="AS2">
-        <v>1.643478038757006</v>
-      </c>
-      <c r="AT2">
+      <c r="BG2">
+        <v>0.01123570686086573</v>
+      </c>
+      <c r="BH2">
+        <v>44500.98299925511</v>
+      </c>
+      <c r="BI2">
+        <v>33375.73724944133</v>
+      </c>
+      <c r="BJ2">
+        <v>210.8092194984988</v>
+      </c>
+      <c r="BK2">
+        <v>333.7573724944133</v>
+      </c>
+      <c r="BL2">
+        <v>0.003337573724944133</v>
+      </c>
+      <c r="BM2">
+        <v>374.9999999999999</v>
+      </c>
+      <c r="BN2">
+        <v>0.003749999999999999</v>
+      </c>
+      <c r="BO2">
+        <v>2.622884902008138</v>
+      </c>
+      <c r="BP2">
+        <v>0.9404835060643784</v>
+      </c>
+      <c r="BQ2">
+        <v>1.790821100624553</v>
+      </c>
+      <c r="BR2">
         <v>1</v>
       </c>
-      <c r="AU2">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY2" s="2">
+      <c r="BS2">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW2" s="2">
         <v>46335</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:75">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2">
         <v>46307</v>
@@ -954,22 +1224,22 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J3" s="2">
         <v>46304</v>
@@ -978,129 +1248,201 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1.444037059975954</v>
+        <v>1.772050083852844</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
-      <c r="R3">
-        <v>4195.629999999999</v>
-      </c>
-      <c r="S3">
-        <v>4222.481066502511</v>
+      <c r="R3" t="s">
+        <v>98</v>
+      </c>
+      <c r="S3" t="s">
+        <v>102</v>
       </c>
       <c r="T3">
-        <v>4423.82442108763</v>
+        <v>-0.9774719878463359</v>
       </c>
       <c r="U3">
-        <v>4195.629999999999</v>
-      </c>
-      <c r="V3">
-        <v>4044.579999999998</v>
-      </c>
-      <c r="W3">
-        <v>4222.481066502511</v>
+        <v>0.8397681994766076</v>
+      </c>
+      <c r="V3" t="s">
+        <v>92</v>
+      </c>
+      <c r="W3" t="s">
+        <v>93</v>
       </c>
       <c r="X3">
-        <v>4061.992499999999</v>
+        <v>0.9996232197830258</v>
       </c>
       <c r="Y3">
-        <v>0.006399769880211425</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>0.2009246394351243</v>
+        <v>-159.0685841963589</v>
       </c>
       <c r="AA3">
-        <v>0.006399769880211425</v>
+        <v>10</v>
       </c>
       <c r="AB3">
-        <v>0.3894350405444333</v>
+        <v>-0.9340087311689881</v>
       </c>
       <c r="AC3">
+        <v>-0.357250178586515</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH3">
+        <v>-0.4668284075783012</v>
+      </c>
+      <c r="AI3">
+        <v>0.7730708670312956</v>
+      </c>
+      <c r="AJ3">
+        <v>-1.245880694328789</v>
+      </c>
+      <c r="AK3">
+        <v>-0.4564362172145745</v>
+      </c>
+      <c r="AL3">
+        <v>-2.653729337996243</v>
+      </c>
+      <c r="AM3">
+        <v>0.7435308808855795</v>
+      </c>
+      <c r="AN3">
+        <v>2.553571094002639</v>
+      </c>
+      <c r="AO3">
+        <v>0.04666586162306566</v>
+      </c>
+      <c r="AP3">
+        <v>6.694155</v>
+      </c>
+      <c r="AQ3">
+        <v>6.726471833778877</v>
+      </c>
+      <c r="AR3">
+        <v>6.783933731935033</v>
+      </c>
+      <c r="AS3">
+        <v>6.694155</v>
+      </c>
+      <c r="AT3">
+        <v>6.680485000000001</v>
+      </c>
+      <c r="AU3">
+        <v>6.726471833778877</v>
+      </c>
+      <c r="AV3">
+        <v>6.67197625</v>
+      </c>
+      <c r="AW3">
+        <v>0.00482761958438023</v>
+      </c>
+      <c r="AX3">
+        <v>1.457107987550123</v>
+      </c>
+      <c r="AY3">
+        <v>0.00482761958438023</v>
+      </c>
+      <c r="AZ3">
+        <v>0.4181088832102814</v>
+      </c>
+      <c r="BA3">
         <v>0.2</v>
       </c>
-      <c r="AD3">
-        <v>0.4105649594555667</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF3">
+      <c r="BB3">
+        <v>0.3818911167897185</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>116</v>
+      </c>
+      <c r="BD3">
         <v>100000</v>
       </c>
-      <c r="AG3">
+      <c r="BE3">
         <v>100</v>
       </c>
-      <c r="AH3">
+      <c r="BF3">
         <v>500</v>
       </c>
-      <c r="AI3">
-        <v>0.03185159320531129</v>
-      </c>
-      <c r="AJ3">
-        <v>15697.80188943969</v>
-      </c>
-      <c r="AK3">
-        <v>15697.80188943969</v>
-      </c>
-      <c r="AL3">
-        <v>3.741464783462721</v>
-      </c>
-      <c r="AM3">
-        <v>156.9780188943969</v>
-      </c>
-      <c r="AN3">
-        <v>0.001569780188943969</v>
-      </c>
-      <c r="AO3">
-        <v>500</v>
-      </c>
-      <c r="AP3">
-        <v>0.005</v>
-      </c>
-      <c r="AQ3">
-        <v>736.9732326457529</v>
-      </c>
-      <c r="AR3">
-        <v>66.32220306725264</v>
-      </c>
-      <c r="AS3">
-        <v>119.4357348634255</v>
-      </c>
-      <c r="AT3">
+      <c r="BG3">
+        <v>0.003313151547880157</v>
+      </c>
+      <c r="BH3">
+        <v>150913.7124499824</v>
+      </c>
+      <c r="BI3">
+        <v>150913.7124499824</v>
+      </c>
+      <c r="BJ3">
+        <v>22544.1018993409</v>
+      </c>
+      <c r="BK3">
+        <v>1509.137124499824</v>
+      </c>
+      <c r="BL3">
+        <v>0.01509137124499824</v>
+      </c>
+      <c r="BM3">
+        <v>500.0000000000001</v>
+      </c>
+      <c r="BN3">
+        <v>0.005000000000000001</v>
+      </c>
+      <c r="BO3">
+        <v>0.03679723706875769</v>
+      </c>
+      <c r="BP3">
+        <v>0.02223567826964404</v>
+      </c>
+      <c r="BQ3">
+        <v>0.02023357663690688</v>
+      </c>
+      <c r="BR3">
         <v>1</v>
       </c>
-      <c r="AU3">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY3" s="2">
+      <c r="BS3">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW3" s="2">
         <v>46335</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:75">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2">
         <v>46307</v>
@@ -1109,22 +1451,22 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="J4" s="2">
         <v>46304</v>
@@ -1133,129 +1475,201 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.417729807169544</v>
+        <v>2.495726305891031</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O4" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P4" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" t="s">
+        <v>103</v>
+      </c>
+      <c r="T4">
+        <v>0.9893909414873521</v>
+      </c>
+      <c r="U4">
+        <v>0.9951752336444051</v>
+      </c>
+      <c r="V4" t="s">
+        <v>91</v>
+      </c>
+      <c r="W4" t="s">
+        <v>93</v>
+      </c>
+      <c r="X4">
+        <v>0.9997972399003866</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>-11.82453471546573</v>
+      </c>
+      <c r="AA4">
+        <v>-5.999999999999996</v>
+      </c>
+      <c r="AB4">
+        <v>0.9787797314446991</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2049151954176232</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH4">
+        <v>0.9785812739688518</v>
+      </c>
+      <c r="AI4">
+        <v>0.9889795393949125</v>
+      </c>
+      <c r="AJ4">
+        <v>2.001710751052217</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3920580590569097</v>
+      </c>
+      <c r="AL4">
+        <v>2.651466514246533</v>
+      </c>
+      <c r="AM4">
+        <v>-4.514083647108024</v>
+      </c>
+      <c r="AN4">
+        <v>2.276727884740602</v>
+      </c>
+      <c r="AO4">
+        <v>0.03055609335754993</v>
+      </c>
+      <c r="AP4">
         <v>0.829295</v>
       </c>
-      <c r="S4">
-        <v>0.8333052744472704</v>
-      </c>
-      <c r="T4">
-        <v>0.8291675547508008</v>
-      </c>
-      <c r="U4">
+      <c r="AQ4">
+        <v>0.8323052712373362</v>
+      </c>
+      <c r="AR4">
+        <v>0.8255713715493158</v>
+      </c>
+      <c r="AS4">
         <v>0.829295</v>
       </c>
-      <c r="V4">
+      <c r="AT4">
         <v>0.842145</v>
       </c>
-      <c r="W4">
-        <v>0.8333052744472704</v>
-      </c>
-      <c r="X4">
+      <c r="AU4">
+        <v>0.8323052712373362</v>
+      </c>
+      <c r="AV4">
         <v>0.82192375</v>
       </c>
-      <c r="Y4">
-        <v>0.004835763446385693</v>
-      </c>
-      <c r="Z4">
-        <v>0.5440426586088377</v>
-      </c>
-      <c r="AA4">
-        <v>0.004835763446385693</v>
-      </c>
-      <c r="AB4">
-        <v>0.4831247932343598</v>
-      </c>
-      <c r="AC4">
+      <c r="AW4">
+        <v>0.003629916058020626</v>
+      </c>
+      <c r="AX4">
+        <v>0.4083800220228854</v>
+      </c>
+      <c r="AY4">
+        <v>0.003629916058020626</v>
+      </c>
+      <c r="AZ4">
+        <v>0.438632299758336</v>
+      </c>
+      <c r="BA4">
         <v>0.2</v>
       </c>
-      <c r="AD4">
-        <v>0.3168752067656402</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF4">
+      <c r="BB4">
+        <v>0.361367700241664</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD4">
         <v>100000</v>
       </c>
-      <c r="AG4">
+      <c r="BE4">
         <v>100</v>
       </c>
-      <c r="AH4">
+      <c r="BF4">
         <v>500</v>
       </c>
-      <c r="AI4">
+      <c r="BG4">
         <v>0.008888574029748221</v>
       </c>
-      <c r="AJ4">
+      <c r="BH4">
         <v>56251.99253857855</v>
       </c>
-      <c r="AK4">
+      <c r="BI4">
         <v>56251.99253857855</v>
       </c>
-      <c r="AL4">
+      <c r="BJ4">
         <v>67831.1005596061</v>
       </c>
-      <c r="AM4">
+      <c r="BK4">
         <v>562.5199253857854</v>
       </c>
-      <c r="AN4">
+      <c r="BL4">
         <v>0.005625199253857854</v>
       </c>
-      <c r="AO4">
+      <c r="BM4">
         <v>499.9999999999999</v>
       </c>
-      <c r="AP4">
+      <c r="BN4">
         <v>0.004999999999999999</v>
       </c>
-      <c r="AQ4">
-        <v>0.01644762070435504</v>
-      </c>
-      <c r="AR4">
-        <v>0.0008855517387687664</v>
-      </c>
-      <c r="AS4">
-        <v>0.008374485287249401</v>
-      </c>
-      <c r="AT4">
+      <c r="BO4">
+        <v>0.01281824077193947</v>
+      </c>
+      <c r="BP4">
+        <v>0.003083693615176796</v>
+      </c>
+      <c r="BQ4">
+        <v>0.006728161113478901</v>
+      </c>
+      <c r="BR4">
         <v>1</v>
       </c>
-      <c r="AU4">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY4" s="2">
+      <c r="BS4">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW4" s="2">
         <v>46335</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:75">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2">
         <v>46307</v>
@@ -1264,153 +1678,225 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2">
         <v>46304</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1.773592640123581</v>
+        <v>3.395165354385198</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
-      <c r="R5">
-        <v>6.694155</v>
-      </c>
-      <c r="S5">
-        <v>6.723577094348116</v>
+      <c r="R5" t="s">
+        <v>98</v>
+      </c>
+      <c r="S5" t="s">
+        <v>102</v>
       </c>
       <c r="T5">
-        <v>6.797597437313392</v>
+        <v>-0.9766829969796371</v>
       </c>
       <c r="U5">
-        <v>6.694155</v>
-      </c>
-      <c r="V5">
-        <v>6.680485000000001</v>
-      </c>
-      <c r="W5">
-        <v>6.723577094348116</v>
+        <v>0.989470875962453</v>
+      </c>
+      <c r="V5" t="s">
+        <v>92</v>
+      </c>
+      <c r="W5" t="s">
+        <v>93</v>
       </c>
       <c r="X5">
-        <v>6.67197625</v>
+        <v>0.9998541092864648</v>
       </c>
       <c r="Y5">
-        <v>0.004395191678130455</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>1.32658938615187</v>
+        <v>-162.4326069517044</v>
       </c>
       <c r="AA5">
-        <v>0.004395191678130455</v>
+        <v>-12</v>
       </c>
       <c r="AB5">
-        <v>0.3446098063873144</v>
+        <v>-0.9533625917287122</v>
       </c>
       <c r="AC5">
-        <v>0.2</v>
-      </c>
-      <c r="AD5">
-        <v>0.4553901936126857</v>
+        <v>-0.3018273822772097</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>92</v>
       </c>
       <c r="AE5" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF5">
+        <v>106</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH5">
+        <v>-0.9532235049799471</v>
+      </c>
+      <c r="AI5">
+        <v>0.980174823462981</v>
+      </c>
+      <c r="AJ5">
+        <v>-2.669941367678096</v>
+      </c>
+      <c r="AK5">
+        <v>-0.9224748832514461</v>
+      </c>
+      <c r="AL5">
+        <v>-3.823959005266689</v>
+      </c>
+      <c r="AM5">
+        <v>5.345176519911814</v>
+      </c>
+      <c r="AN5">
+        <v>3.333493334301382</v>
+      </c>
+      <c r="AO5">
+        <v>0.03855261537263439</v>
+      </c>
+      <c r="AP5">
+        <v>1.11895</v>
+      </c>
+      <c r="AQ5">
+        <v>1.112125712321921</v>
+      </c>
+      <c r="AR5">
+        <v>1.141959287169594</v>
+      </c>
+      <c r="AS5">
+        <v>1.11895</v>
+      </c>
+      <c r="AT5">
+        <v>1.078005</v>
+      </c>
+      <c r="AU5">
+        <v>1.112125712321921</v>
+      </c>
+      <c r="AV5">
+        <v>1.12931</v>
+      </c>
+      <c r="AW5">
+        <v>-0.00609883165295954</v>
+      </c>
+      <c r="AX5">
+        <v>0.6587150268416075</v>
+      </c>
+      <c r="AY5">
+        <v>0.00609883165295954</v>
+      </c>
+      <c r="AZ5">
+        <v>0.4093247752591768</v>
+      </c>
+      <c r="BA5">
+        <v>0.1939831017063407</v>
+      </c>
+      <c r="BB5">
+        <v>0.3966921230344825</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD5">
         <v>100000</v>
       </c>
-      <c r="AG5">
+      <c r="BE5">
         <v>100</v>
       </c>
-      <c r="AH5">
+      <c r="BF5">
         <v>500</v>
       </c>
-      <c r="AI5">
-        <v>0.003313151547880157</v>
-      </c>
-      <c r="AJ5">
-        <v>150913.7124499824</v>
-      </c>
-      <c r="AK5">
-        <v>150913.7124499824</v>
-      </c>
-      <c r="AL5">
-        <v>22544.1018993409</v>
-      </c>
-      <c r="AM5">
-        <v>1509.137124499824</v>
-      </c>
-      <c r="AN5">
-        <v>0.01509137124499824</v>
-      </c>
-      <c r="AO5">
+      <c r="BG5">
+        <v>0.009258680012511762</v>
+      </c>
+      <c r="BH5">
+        <v>54003.37837837819</v>
+      </c>
+      <c r="BI5">
+        <v>54003.37837837819</v>
+      </c>
+      <c r="BJ5">
+        <v>48262.5482625481</v>
+      </c>
+      <c r="BK5">
+        <v>540.0337837837819</v>
+      </c>
+      <c r="BL5">
+        <v>0.005400337837837819</v>
+      </c>
+      <c r="BM5">
         <v>500.0000000000001</v>
       </c>
-      <c r="AP5">
+      <c r="BN5">
         <v>0.005000000000000001</v>
       </c>
-      <c r="AQ5">
-        <v>0.1058706843671524</v>
-      </c>
-      <c r="AR5">
-        <v>0.01230743820862033</v>
-      </c>
-      <c r="AS5">
-        <v>0.01119693364272329</v>
-      </c>
-      <c r="AT5">
+      <c r="BO5">
+        <v>0.01542033590270082</v>
+      </c>
+      <c r="BP5">
+        <v>0.01740863303146617</v>
+      </c>
+      <c r="BQ5">
+        <v>0.008396430048403982</v>
+      </c>
+      <c r="BR5">
         <v>1</v>
       </c>
-      <c r="AU5">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY5" s="2">
+      <c r="BS5">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW5" s="2">
         <v>46335</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:75">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2">
         <v>46307</v>
@@ -1419,153 +1905,225 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2">
         <v>46304</v>
       </c>
       <c r="K6">
-        <v>0.2535097888689165</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>1.884873205538164</v>
+        <v>2.055793720422582</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P6" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q6">
-        <v>0.8133774472172292</v>
-      </c>
-      <c r="R6">
-        <v>0.697225</v>
-      </c>
-      <c r="S6">
-        <v>0.6958999322782452</v>
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S6" t="s">
+        <v>104</v>
       </c>
       <c r="T6">
-        <v>0.7071821498742045</v>
+        <v>-0.987873502193279</v>
       </c>
       <c r="U6">
-        <v>0.697225</v>
-      </c>
-      <c r="V6">
-        <v>0.6780999999999999</v>
-      </c>
-      <c r="W6">
-        <v>0.6958999322782452</v>
+        <v>0.9944785455584353</v>
+      </c>
+      <c r="V6" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" t="s">
+        <v>93</v>
       </c>
       <c r="X6">
-        <v>0.703025</v>
+        <v>0.9997418782858389</v>
       </c>
       <c r="Y6">
-        <v>-0.001900487965512969</v>
+        <v>0.909492657910695</v>
       </c>
       <c r="Z6">
-        <v>0.2284599520266851</v>
+        <v>167.1577415465099</v>
       </c>
       <c r="AA6">
-        <v>0.001900487965512969</v>
+        <v>-11</v>
       </c>
       <c r="AB6">
-        <v>0.4805329846209456</v>
+        <v>-0.9749856861839791</v>
       </c>
       <c r="AC6">
+        <v>0.2222676578730147</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH6">
+        <v>-0.9306237284556287</v>
+      </c>
+      <c r="AI6">
+        <v>0.969103005779609</v>
+      </c>
+      <c r="AJ6">
+        <v>-1.692389824687916</v>
+      </c>
+      <c r="AK6">
+        <v>0.3413676704089463</v>
+      </c>
+      <c r="AL6">
+        <v>-1.971374147575125</v>
+      </c>
+      <c r="AM6">
+        <v>3.946461092591154</v>
+      </c>
+      <c r="AN6">
+        <v>1.657084790809492</v>
+      </c>
+      <c r="AO6">
+        <v>0.03467259371844893</v>
+      </c>
+      <c r="AP6">
+        <v>1.32324</v>
+      </c>
+      <c r="AQ6">
+        <v>1.312611488048471</v>
+      </c>
+      <c r="AR6">
+        <v>1.322244705453943</v>
+      </c>
+      <c r="AS6">
+        <v>1.32324</v>
+      </c>
+      <c r="AT6">
+        <v>1.293885</v>
+      </c>
+      <c r="AU6">
+        <v>1.312611488048471</v>
+      </c>
+      <c r="AV6">
+        <v>1.33489</v>
+      </c>
+      <c r="AW6">
+        <v>-0.008032187623959982</v>
+      </c>
+      <c r="AX6">
+        <v>0.9123186224488251</v>
+      </c>
+      <c r="AY6">
+        <v>0.008032187623959982</v>
+      </c>
+      <c r="AZ6">
+        <v>0.4533011835877003</v>
+      </c>
+      <c r="BA6">
         <v>0.2</v>
       </c>
-      <c r="AD6">
-        <v>0.3194670153790544</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF6">
+      <c r="BB6">
+        <v>0.3466988164122997</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD6">
         <v>100000</v>
       </c>
-      <c r="AG6">
+      <c r="BE6">
         <v>100</v>
       </c>
-      <c r="AH6">
-        <v>406.6887236086146</v>
-      </c>
-      <c r="AI6">
-        <v>0.008318691957402599</v>
-      </c>
-      <c r="AJ6">
-        <v>60105.60344827558</v>
-      </c>
-      <c r="AK6">
-        <v>48888.54229620947</v>
-      </c>
-      <c r="AL6">
-        <v>70118.7454497608</v>
-      </c>
-      <c r="AM6">
-        <v>488.8854229620948</v>
-      </c>
-      <c r="AN6">
-        <v>0.004888854229620948</v>
-      </c>
-      <c r="AO6">
-        <v>406.6887236086146</v>
-      </c>
-      <c r="AP6">
-        <v>0.004066887236086146</v>
-      </c>
-      <c r="AQ6">
-        <v>0.009302417311791284</v>
-      </c>
-      <c r="AR6">
-        <v>0.002845228580769128</v>
-      </c>
-      <c r="AS6">
-        <v>0.009196518566406808</v>
-      </c>
-      <c r="AT6">
+      <c r="BF6">
+        <v>500</v>
+      </c>
+      <c r="BG6">
+        <v>0.008804147395786097</v>
+      </c>
+      <c r="BH6">
+        <v>56791.4163090129</v>
+      </c>
+      <c r="BI6">
+        <v>56791.4163090129</v>
+      </c>
+      <c r="BJ6">
+        <v>42918.45493562234</v>
+      </c>
+      <c r="BK6">
+        <v>567.914163090129</v>
+      </c>
+      <c r="BL6">
+        <v>0.00567914163090129</v>
+      </c>
+      <c r="BM6">
+        <v>500</v>
+      </c>
+      <c r="BN6">
+        <v>0.005</v>
+      </c>
+      <c r="BO6">
+        <v>0.01338984322726786</v>
+      </c>
+      <c r="BP6">
+        <v>0.006913522951227255</v>
+      </c>
+      <c r="BQ6">
+        <v>0.01052051280019401</v>
+      </c>
+      <c r="BR6">
         <v>1</v>
       </c>
-      <c r="AU6">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY6" s="2">
+      <c r="BS6">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW6" s="2">
         <v>46335</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:75">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B7" s="2">
         <v>46307</v>
@@ -1574,22 +2132,22 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J7" s="2">
         <v>46304</v>
@@ -1598,129 +2156,201 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>2.043382501726599</v>
+        <v>1.409466085787301</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O7" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
-      <c r="R7">
-        <v>1.32324</v>
-      </c>
-      <c r="S7">
-        <v>1.319859691980235</v>
+      <c r="R7" t="s">
+        <v>100</v>
+      </c>
+      <c r="S7" t="s">
+        <v>104</v>
       </c>
       <c r="T7">
-        <v>1.334974863264457</v>
+        <v>-0.9936108756894084</v>
       </c>
       <c r="U7">
-        <v>1.32324</v>
-      </c>
-      <c r="V7">
-        <v>1.293885</v>
-      </c>
-      <c r="W7">
-        <v>1.319859691980235</v>
+        <v>0.996791477885986</v>
+      </c>
+      <c r="V7" t="s">
+        <v>92</v>
+      </c>
+      <c r="W7" t="s">
+        <v>93</v>
       </c>
       <c r="X7">
-        <v>1.33489</v>
+        <v>0.9986663353030091</v>
       </c>
       <c r="Y7">
-        <v>-0.002554569102932759</v>
+        <v>0.8524073679593994</v>
       </c>
       <c r="Z7">
-        <v>0.2901551948295919</v>
+        <v>170.5867373744173</v>
       </c>
       <c r="AA7">
-        <v>0.002554569102932759</v>
+        <v>-39</v>
       </c>
       <c r="AB7">
-        <v>0.4892615935674157</v>
+        <v>-0.9865343290569012</v>
       </c>
       <c r="AC7">
+        <v>0.1635543261190295</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH7">
+        <v>-0.9125131181941951</v>
+      </c>
+      <c r="AI7">
+        <v>0.9609889996655083</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.150576665151099</v>
+      </c>
+      <c r="AK7">
+        <v>0.09271125474085967</v>
+      </c>
+      <c r="AL7">
+        <v>-1.407305197902939</v>
+      </c>
+      <c r="AM7">
+        <v>2.887102683106255</v>
+      </c>
+      <c r="AN7">
+        <v>1.160703551299741</v>
+      </c>
+      <c r="AO7">
+        <v>0.03323993332996663</v>
+      </c>
+      <c r="AP7">
+        <v>4.67727</v>
+      </c>
+      <c r="AQ7">
+        <v>4.637436860421202</v>
+      </c>
+      <c r="AR7">
+        <v>4.684991378018259</v>
+      </c>
+      <c r="AS7">
+        <v>4.67727</v>
+      </c>
+      <c r="AT7">
+        <v>4.54689</v>
+      </c>
+      <c r="AU7">
+        <v>4.637436860421202</v>
+      </c>
+      <c r="AV7">
+        <v>4.719915</v>
+      </c>
+      <c r="AW7">
+        <v>-0.008516322465625906</v>
+      </c>
+      <c r="AX7">
+        <v>0.9340635380184791</v>
+      </c>
+      <c r="AY7">
+        <v>0.008516322465625906</v>
+      </c>
+      <c r="AZ7">
+        <v>0.4668371984867384</v>
+      </c>
+      <c r="BA7">
         <v>0.2</v>
       </c>
-      <c r="AD7">
-        <v>0.3107384064325843</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF7">
+      <c r="BB7">
+        <v>0.3331628015132617</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD7">
         <v>100000</v>
       </c>
-      <c r="AG7">
+      <c r="BE7">
         <v>100</v>
       </c>
-      <c r="AH7">
+      <c r="BF7">
         <v>500</v>
       </c>
-      <c r="AI7">
-        <v>0.008804147395786097</v>
-      </c>
-      <c r="AJ7">
-        <v>56791.4163090129</v>
-      </c>
-      <c r="AK7">
-        <v>56791.4163090129</v>
-      </c>
-      <c r="AL7">
-        <v>42918.45493562234</v>
-      </c>
-      <c r="AM7">
-        <v>567.914163090129</v>
-      </c>
-      <c r="AN7">
-        <v>0.00567914163090129</v>
-      </c>
-      <c r="AO7">
+      <c r="BG7">
+        <v>0.009117498027695653</v>
+      </c>
+      <c r="BH7">
+        <v>54839.60604994718</v>
+      </c>
+      <c r="BI7">
+        <v>54839.60604994718</v>
+      </c>
+      <c r="BJ7">
+        <v>11724.70395122522</v>
+      </c>
+      <c r="BK7">
+        <v>548.3960604994718</v>
+      </c>
+      <c r="BL7">
+        <v>0.005483960604994718</v>
+      </c>
+      <c r="BM7">
         <v>500</v>
       </c>
-      <c r="AP7">
+      <c r="BN7">
         <v>0.005</v>
       </c>
-      <c r="AQ7">
-        <v>0.01556974693570295</v>
-      </c>
-      <c r="AR7">
-        <v>0.001886710849201949</v>
-      </c>
-      <c r="AS7">
-        <v>0.01356246182274598</v>
-      </c>
-      <c r="AT7">
+      <c r="BO7">
+        <v>0.04935643734942342</v>
+      </c>
+      <c r="BP7">
+        <v>0.05744767418596648</v>
+      </c>
+      <c r="BQ7">
+        <v>0.050573124607282</v>
+      </c>
+      <c r="BR7">
         <v>1</v>
       </c>
-      <c r="AU7">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY7" s="2">
+      <c r="BS7">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW7" s="2">
         <v>46335</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:75">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
         <v>46307</v>
@@ -1729,153 +2359,225 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J8" s="2">
         <v>46304</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.249996583801431</v>
       </c>
       <c r="L8">
-        <v>1.504100250601936</v>
+        <v>1.877381592236885</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P8" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q8">
+        <v>0.8124991459503578</v>
+      </c>
+      <c r="R8" t="s">
+        <v>100</v>
+      </c>
+      <c r="S8" t="s">
+        <v>104</v>
+      </c>
+      <c r="T8">
+        <v>-0.992675505904978</v>
+      </c>
+      <c r="U8">
+        <v>0.8837936080072615</v>
+      </c>
+      <c r="V8" t="s">
+        <v>92</v>
+      </c>
+      <c r="W8" t="s">
+        <v>93</v>
+      </c>
+      <c r="X8">
+        <v>0.998360571119227</v>
+      </c>
+      <c r="Y8">
+        <v>0.302875974097834</v>
+      </c>
+      <c r="Z8">
+        <v>169.2744964234522</v>
+      </c>
+      <c r="AA8">
+        <v>-44</v>
+      </c>
+      <c r="AB8">
+        <v>-0.9825300550219199</v>
+      </c>
+      <c r="AC8">
+        <v>0.1861039789435543</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH8">
+        <v>-0.6390080726695654</v>
+      </c>
+      <c r="AI8">
+        <v>0.8495928345362319</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.571999080587123</v>
+      </c>
+      <c r="AK8">
+        <v>0.1388823164316986</v>
+      </c>
+      <c r="AL8">
+        <v>-1.696045041873733</v>
+      </c>
+      <c r="AM8">
+        <v>4.329319079501524</v>
+      </c>
+      <c r="AN8">
+        <v>1.334531895020916</v>
+      </c>
+      <c r="AO8">
+        <v>0.03445051121093546</v>
+      </c>
+      <c r="AP8">
+        <v>0.697225</v>
+      </c>
+      <c r="AQ8">
+        <v>0.6909232407627918</v>
+      </c>
+      <c r="AR8">
+        <v>0.6977505765541704</v>
+      </c>
+      <c r="AS8">
+        <v>0.697225</v>
+      </c>
+      <c r="AT8">
+        <v>0.6780999999999999</v>
+      </c>
+      <c r="AU8">
+        <v>0.6909232407627918</v>
+      </c>
+      <c r="AV8">
+        <v>0.703025</v>
+      </c>
+      <c r="AW8">
+        <v>-0.009038343773112288</v>
+      </c>
+      <c r="AX8">
+        <v>1.086510213311756</v>
+      </c>
+      <c r="AY8">
+        <v>0.009038343773112288</v>
+      </c>
+      <c r="AZ8">
+        <v>0.4579123028775482</v>
+      </c>
+      <c r="BA8">
+        <v>0.2</v>
+      </c>
+      <c r="BB8">
+        <v>0.3420876971224517</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD8">
+        <v>100000</v>
+      </c>
+      <c r="BE8">
+        <v>100</v>
+      </c>
+      <c r="BF8">
+        <v>406.2495729751789</v>
+      </c>
+      <c r="BG8">
+        <v>0.008318691957402599</v>
+      </c>
+      <c r="BH8">
+        <v>60105.60344827558</v>
+      </c>
+      <c r="BI8">
+        <v>48835.75146855479</v>
+      </c>
+      <c r="BJ8">
+        <v>70043.02982330638</v>
+      </c>
+      <c r="BK8">
+        <v>488.3575146855479</v>
+      </c>
+      <c r="BL8">
+        <v>0.004883575146855479</v>
+      </c>
+      <c r="BM8">
+        <v>406.2495729751789</v>
+      </c>
+      <c r="BN8">
+        <v>0.00406249572975179</v>
+      </c>
+      <c r="BO8">
+        <v>0.009039297266560345</v>
+      </c>
+      <c r="BP8">
+        <v>0.007751638754503872</v>
+      </c>
+      <c r="BQ8">
+        <v>0.008140840527309965</v>
+      </c>
+      <c r="BR8">
         <v>1</v>
       </c>
-      <c r="R8">
-        <v>8.861319999999999</v>
-      </c>
-      <c r="S8">
-        <v>8.803123810694256</v>
-      </c>
-      <c r="T8">
-        <v>8.887977759717607</v>
-      </c>
-      <c r="U8">
-        <v>8.861319999999999</v>
-      </c>
-      <c r="V8">
-        <v>8.655979999999998</v>
-      </c>
-      <c r="W8">
-        <v>8.803123810694256</v>
-      </c>
-      <c r="X8">
-        <v>8.917432499999999</v>
-      </c>
-      <c r="Y8">
-        <v>-0.006567440212715851</v>
-      </c>
-      <c r="Z8">
-        <v>1.037134137772232</v>
-      </c>
-      <c r="AA8">
-        <v>0.006567440212715851</v>
-      </c>
-      <c r="AB8">
-        <v>0.4572277371271787</v>
-      </c>
-      <c r="AC8">
-        <v>0.2</v>
-      </c>
-      <c r="AD8">
-        <v>0.3427722628728214</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF8">
-        <v>100000</v>
-      </c>
-      <c r="AG8">
-        <v>100</v>
-      </c>
-      <c r="AH8">
-        <v>500</v>
-      </c>
-      <c r="AI8">
-        <v>0.006332295865627119</v>
-      </c>
-      <c r="AJ8">
-        <v>78960.30296279948</v>
-      </c>
-      <c r="AK8">
-        <v>78960.30296279948</v>
-      </c>
-      <c r="AL8">
-        <v>8910.670527957403</v>
-      </c>
-      <c r="AM8">
-        <v>789.6030296279948</v>
-      </c>
-      <c r="AN8">
-        <v>0.007896030296279949</v>
-      </c>
-      <c r="AO8">
-        <v>499.9999999999999</v>
-      </c>
-      <c r="AP8">
-        <v>0.004999999999999999</v>
-      </c>
-      <c r="AQ8">
-        <v>0.126109550101479</v>
-      </c>
-      <c r="AR8">
-        <v>0.02255404964711423</v>
-      </c>
-      <c r="AS8">
-        <v>0.07512899363741413</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY8" s="2">
+      <c r="BS8">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW8" s="2">
         <v>46335</v>
       </c>
     </row>
-    <row r="9" spans="1:51">
+    <row r="9" spans="1:75">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2">
         <v>46307</v>
@@ -1884,22 +2586,22 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J9" s="2">
         <v>46304</v>
@@ -1908,129 +2610,201 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1.409466085787301</v>
+        <v>1.504100250601936</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O9" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
-      <c r="R9">
-        <v>4.67727</v>
-      </c>
-      <c r="S9">
-        <v>4.639466690224419</v>
+      <c r="R9" t="s">
+        <v>100</v>
+      </c>
+      <c r="S9" t="s">
+        <v>104</v>
       </c>
       <c r="T9">
-        <v>4.683317390146225</v>
+        <v>-0.9944317966357554</v>
       </c>
       <c r="U9">
-        <v>4.67727</v>
-      </c>
-      <c r="V9">
-        <v>4.54689</v>
-      </c>
-      <c r="W9">
-        <v>4.639466690224419</v>
+        <v>0.9974555167659012</v>
+      </c>
+      <c r="V9" t="s">
+        <v>92</v>
+      </c>
+      <c r="W9" t="s">
+        <v>93</v>
       </c>
       <c r="X9">
-        <v>4.719915</v>
+        <v>0.999844833119245</v>
       </c>
       <c r="Y9">
-        <v>-0.008082344995174844</v>
+        <v>1</v>
       </c>
       <c r="Z9">
-        <v>0.8864652309903014</v>
+        <v>171.4408444705665</v>
       </c>
       <c r="AA9">
-        <v>0.008082344995174844</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB9">
-        <v>0.4874438347984357</v>
+        <v>-0.9888627291366784</v>
       </c>
       <c r="AC9">
+        <v>0.1488304502592137</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH9">
+        <v>-0.9887092903915033</v>
+      </c>
+      <c r="AI9">
+        <v>0.9915682451923054</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.206847608800289</v>
+      </c>
+      <c r="AK9">
+        <v>0.1628464539605917</v>
+      </c>
+      <c r="AL9">
+        <v>-1.585084138197813</v>
+      </c>
+      <c r="AM9">
+        <v>2.523731344160301</v>
+      </c>
+      <c r="AN9">
+        <v>1.37968017748996</v>
+      </c>
+      <c r="AO9">
+        <v>0.03357510093622675</v>
+      </c>
+      <c r="AP9">
+        <v>8.861319999999999</v>
+      </c>
+      <c r="AQ9">
+        <v>8.775635788256935</v>
+      </c>
+      <c r="AR9">
+        <v>8.851324093403699</v>
+      </c>
+      <c r="AS9">
+        <v>8.861319999999999</v>
+      </c>
+      <c r="AT9">
+        <v>8.655979999999998</v>
+      </c>
+      <c r="AU9">
+        <v>8.775635788256935</v>
+      </c>
+      <c r="AV9">
+        <v>8.918442807828709</v>
+      </c>
+      <c r="AW9">
+        <v>-0.009669463662644449</v>
+      </c>
+      <c r="AX9">
+        <v>1.5</v>
+      </c>
+      <c r="AY9">
+        <v>0.009669463662644449</v>
+      </c>
+      <c r="AZ9">
+        <v>0.4023043998290992</v>
+      </c>
+      <c r="BA9">
         <v>0.2</v>
       </c>
-      <c r="AD9">
-        <v>0.3125561652015643</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF9">
+      <c r="BB9">
+        <v>0.3976956001709008</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD9">
         <v>100000</v>
       </c>
-      <c r="AG9">
+      <c r="BE9">
         <v>100</v>
       </c>
-      <c r="AH9">
+      <c r="BF9">
         <v>500</v>
       </c>
-      <c r="AI9">
-        <v>0.009117498027695653</v>
-      </c>
-      <c r="AJ9">
-        <v>54839.60604994718</v>
-      </c>
-      <c r="AK9">
-        <v>54839.60604994718</v>
-      </c>
-      <c r="AL9">
-        <v>11724.70395122522</v>
-      </c>
-      <c r="AM9">
-        <v>548.3960604994718</v>
-      </c>
-      <c r="AN9">
-        <v>0.005483960604994718</v>
-      </c>
-      <c r="AO9">
-        <v>500</v>
-      </c>
-      <c r="AP9">
-        <v>0.005</v>
-      </c>
-      <c r="AQ9">
-        <v>0.05237449529819002</v>
-      </c>
-      <c r="AR9">
-        <v>0.02668106652683165</v>
-      </c>
-      <c r="AS9">
-        <v>0.06223244948117326</v>
-      </c>
-      <c r="AT9">
+      <c r="BG9">
+        <v>0.006446309108429633</v>
+      </c>
+      <c r="BH9">
+        <v>77563.76425483009</v>
+      </c>
+      <c r="BI9">
+        <v>77563.76425483009</v>
+      </c>
+      <c r="BJ9">
+        <v>8753.07112877428</v>
+      </c>
+      <c r="BK9">
+        <v>775.637642548301</v>
+      </c>
+      <c r="BL9">
+        <v>0.00775637642548301</v>
+      </c>
+      <c r="BM9">
+        <v>500.0000000000001</v>
+      </c>
+      <c r="BN9">
+        <v>0.005000000000000001</v>
+      </c>
+      <c r="BO9">
+        <v>0.0838575150110859</v>
+      </c>
+      <c r="BP9">
+        <v>0.05235533095852363</v>
+      </c>
+      <c r="BQ9">
+        <v>0.03908692170619526</v>
+      </c>
+      <c r="BR9">
         <v>1</v>
       </c>
-      <c r="AU9">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV9" t="s">
+      <c r="BS9">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW9" s="2">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:75">
+      <c r="A10" t="s">
         <v>83</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY9" s="2">
-        <v>46335</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51">
-      <c r="A10" t="s">
-        <v>59</v>
       </c>
       <c r="B10" s="2">
         <v>46307</v>
@@ -2039,153 +2813,225 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J10" s="2">
         <v>46304</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>3.304917062447236</v>
+        <v>1.453657243820792</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O10" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P10" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q10">
+        <v>0.75</v>
+      </c>
+      <c r="R10" t="s">
+        <v>100</v>
+      </c>
+      <c r="S10" t="s">
+        <v>104</v>
+      </c>
+      <c r="T10">
+        <v>-0.9987753755745803</v>
+      </c>
+      <c r="U10">
+        <v>0.8489103186503497</v>
+      </c>
+      <c r="V10" t="s">
+        <v>92</v>
+      </c>
+      <c r="W10" t="s">
+        <v>93</v>
+      </c>
+      <c r="X10">
+        <v>0.9978455985671545</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>175.1425807481146</v>
+      </c>
+      <c r="AA10">
+        <v>-46.99999999999999</v>
+      </c>
+      <c r="AB10">
+        <v>-0.9964085006983606</v>
+      </c>
+      <c r="AC10">
+        <v>0.08467644144651515</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH10">
+        <v>-0.4971309183983783</v>
+      </c>
+      <c r="AI10">
+        <v>0.7932020759331244</v>
+      </c>
+      <c r="AJ10">
+        <v>-1.206425120164056</v>
+      </c>
+      <c r="AK10">
+        <v>-0.02690346497028458</v>
+      </c>
+      <c r="AL10">
+        <v>-1.36143194983145</v>
+      </c>
+      <c r="AM10">
+        <v>3.199793938222641</v>
+      </c>
+      <c r="AN10">
+        <v>1.089023131623034</v>
+      </c>
+      <c r="AO10">
+        <v>0.03310955849925291</v>
+      </c>
+      <c r="AP10">
+        <v>4195.629999999999</v>
+      </c>
+      <c r="AQ10">
+        <v>4136.549473815716</v>
+      </c>
+      <c r="AR10">
+        <v>4214.250498545569</v>
+      </c>
+      <c r="AS10">
+        <v>4195.629999999999</v>
+      </c>
+      <c r="AT10">
+        <v>4044.579999999998</v>
+      </c>
+      <c r="AU10">
+        <v>4136.549473815716</v>
+      </c>
+      <c r="AV10">
+        <v>4329.267499999999</v>
+      </c>
+      <c r="AW10">
+        <v>-0.0140814433551775</v>
+      </c>
+      <c r="AX10">
+        <v>0.4420954162138868</v>
+      </c>
+      <c r="AY10">
+        <v>0.0140814433551775</v>
+      </c>
+      <c r="AZ10">
+        <v>0.3639965364935277</v>
+      </c>
+      <c r="BA10">
+        <v>0.2</v>
+      </c>
+      <c r="BB10">
+        <v>0.4360034635064723</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD10">
+        <v>100000</v>
+      </c>
+      <c r="BE10">
+        <v>100</v>
+      </c>
+      <c r="BF10">
+        <v>375</v>
+      </c>
+      <c r="BG10">
+        <v>0.03185159320531129</v>
+      </c>
+      <c r="BH10">
+        <v>15697.80188943969</v>
+      </c>
+      <c r="BI10">
+        <v>11773.35141707977</v>
+      </c>
+      <c r="BJ10">
+        <v>2.806098587597041</v>
+      </c>
+      <c r="BK10">
+        <v>117.7335141707977</v>
+      </c>
+      <c r="BL10">
+        <v>0.001177335141707977</v>
+      </c>
+      <c r="BM10">
+        <v>375</v>
+      </c>
+      <c r="BN10">
+        <v>0.00375</v>
+      </c>
+      <c r="BO10">
+        <v>508.7343108685552</v>
+      </c>
+      <c r="BP10">
+        <v>138.0628247282922</v>
+      </c>
+      <c r="BQ10">
+        <v>113.3130143265598</v>
+      </c>
+      <c r="BR10">
         <v>1</v>
       </c>
-      <c r="R10">
-        <v>1.11895</v>
-      </c>
-      <c r="S10">
-        <v>1.098473398897783</v>
-      </c>
-      <c r="T10">
-        <v>1.106357672767456</v>
-      </c>
-      <c r="U10">
-        <v>1.11895</v>
-      </c>
-      <c r="V10">
-        <v>1.078005</v>
-      </c>
-      <c r="W10">
-        <v>1.098473398897783</v>
-      </c>
-      <c r="X10">
-        <v>1.132601067401478</v>
-      </c>
-      <c r="Y10">
-        <v>-0.018299835651474</v>
-      </c>
-      <c r="Z10">
-        <v>1.5</v>
-      </c>
-      <c r="AA10">
-        <v>0.018299835651474</v>
-      </c>
-      <c r="AB10">
-        <v>0.4330949324776751</v>
-      </c>
-      <c r="AC10">
-        <v>0.2</v>
-      </c>
-      <c r="AD10">
-        <v>0.366905067522325</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF10">
-        <v>100000</v>
-      </c>
-      <c r="AG10">
-        <v>100</v>
-      </c>
-      <c r="AH10">
-        <v>500</v>
-      </c>
-      <c r="AI10">
-        <v>0.012199890434316</v>
-      </c>
-      <c r="AJ10">
-        <v>40983.97462600107</v>
-      </c>
-      <c r="AK10">
-        <v>40983.97462600107</v>
-      </c>
-      <c r="AL10">
-        <v>36627.17246168378</v>
-      </c>
-      <c r="AM10">
-        <v>409.8397462600107</v>
-      </c>
-      <c r="AN10">
-        <v>0.004098397462600107</v>
-      </c>
-      <c r="AO10">
-        <v>500.0000000000001</v>
-      </c>
-      <c r="AP10">
-        <v>0.005000000000000001</v>
-      </c>
-      <c r="AQ10">
-        <v>0.01616926522867659</v>
-      </c>
-      <c r="AR10">
-        <v>0.008448525205869063</v>
-      </c>
-      <c r="AS10">
-        <v>0.01013453201585273</v>
-      </c>
-      <c r="AT10">
-        <v>1</v>
-      </c>
-      <c r="AU10">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX10" t="s">
+      <c r="BS10">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW10" s="2">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:75">
+      <c r="A11" t="s">
         <v>84</v>
-      </c>
-      <c r="AY10" s="2">
-        <v>46335</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51">
-      <c r="A11" t="s">
-        <v>60</v>
       </c>
       <c r="B11" s="2">
         <v>46307</v>
@@ -2194,22 +3040,22 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J11" s="2">
         <v>46304</v>
@@ -2227,114 +3073,186 @@
         <v>18</v>
       </c>
       <c r="O11" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="s">
+        <v>98</v>
+      </c>
+      <c r="S11" t="s">
+        <v>102</v>
+      </c>
+      <c r="T11">
+        <v>-0.9746198314191159</v>
+      </c>
+      <c r="U11">
+        <v>0.9885556652336881</v>
+      </c>
+      <c r="V11" t="s">
+        <v>92</v>
+      </c>
+      <c r="W11" t="s">
+        <v>93</v>
+      </c>
+      <c r="X11">
+        <v>0.9999069643803437</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>-161.6656935826206</v>
+      </c>
+      <c r="AA11">
+        <v>-10</v>
+      </c>
+      <c r="AB11">
+        <v>-0.9492373013588192</v>
+      </c>
+      <c r="AC11">
+        <v>-0.3145608775881486</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AH11">
+        <v>-0.9491489884782864</v>
+      </c>
+      <c r="AI11">
+        <v>0.9789578689314791</v>
+      </c>
+      <c r="AJ11">
+        <v>-2.377430401374961</v>
+      </c>
+      <c r="AK11">
+        <v>-0.8435569835128667</v>
+      </c>
+      <c r="AL11">
+        <v>-3.583344725562733</v>
+      </c>
+      <c r="AM11">
+        <v>4.438944894702015</v>
+      </c>
+      <c r="AN11">
+        <v>3.170392461621871</v>
+      </c>
+      <c r="AO11">
+        <v>0.03853839339524651</v>
+      </c>
+      <c r="AP11">
         <v>7.4965</v>
       </c>
-      <c r="S11">
-        <v>7.354312632692238</v>
-      </c>
-      <c r="T11">
-        <v>7.39214950202128</v>
-      </c>
-      <c r="U11">
+      <c r="AQ11">
+        <v>7.381340076159068</v>
+      </c>
+      <c r="AR11">
+        <v>7.472718662462803</v>
+      </c>
+      <c r="AS11">
         <v>7.4965</v>
       </c>
-      <c r="V11">
+      <c r="AT11">
         <v>7.2141</v>
       </c>
-      <c r="W11">
-        <v>7.354312632692238</v>
-      </c>
-      <c r="X11">
-        <v>7.591291578205174</v>
-      </c>
-      <c r="Y11">
-        <v>-0.0189671669856282</v>
-      </c>
-      <c r="Z11">
+      <c r="AU11">
+        <v>7.381340076159068</v>
+      </c>
+      <c r="AV11">
+        <v>7.573273282560621</v>
+      </c>
+      <c r="AW11">
+        <v>-0.01536182536396078</v>
+      </c>
+      <c r="AX11">
         <v>1.5</v>
       </c>
-      <c r="AA11">
-        <v>0.0189671669856282</v>
-      </c>
-      <c r="AB11">
-        <v>0.4702772641410168</v>
-      </c>
-      <c r="AC11">
-        <v>0.2</v>
-      </c>
-      <c r="AD11">
-        <v>0.3297227358589833</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF11">
+      <c r="AY11">
+        <v>0.01536182536396078</v>
+      </c>
+      <c r="AZ11">
+        <v>0.4430034407861836</v>
+      </c>
+      <c r="BA11">
+        <v>0.1865124604692818</v>
+      </c>
+      <c r="BB11">
+        <v>0.3704840987445346</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD11">
         <v>100000</v>
       </c>
-      <c r="AG11">
+      <c r="BE11">
         <v>100</v>
       </c>
-      <c r="AH11">
+      <c r="BF11">
         <v>500</v>
       </c>
-      <c r="AI11">
-        <v>0.0126447779904188</v>
-      </c>
-      <c r="AJ11">
-        <v>39542.01492338259</v>
-      </c>
-      <c r="AK11">
-        <v>39542.01492338259</v>
-      </c>
-      <c r="AL11">
-        <v>5274.73019720971</v>
-      </c>
-      <c r="AM11">
-        <v>395.420149233826</v>
-      </c>
-      <c r="AN11">
-        <v>0.003954201492338261</v>
-      </c>
-      <c r="AO11">
-        <v>500.0000000000001</v>
-      </c>
-      <c r="AP11">
-        <v>0.005000000000000001</v>
-      </c>
-      <c r="AQ11">
-        <v>0.06963579400793847</v>
-      </c>
-      <c r="AR11">
-        <v>0.07013187059556132</v>
-      </c>
-      <c r="AS11">
-        <v>0.07304081366321984</v>
-      </c>
-      <c r="AT11">
+      <c r="BG11">
+        <v>0.01024121690930719</v>
+      </c>
+      <c r="BH11">
+        <v>48822.32301374279</v>
+      </c>
+      <c r="BI11">
+        <v>48822.32301374279</v>
+      </c>
+      <c r="BJ11">
+        <v>6512.682320248487</v>
+      </c>
+      <c r="BK11">
+        <v>488.2232301374279</v>
+      </c>
+      <c r="BL11">
+        <v>0.004882232301374279</v>
+      </c>
+      <c r="BM11">
+        <v>500</v>
+      </c>
+      <c r="BN11">
+        <v>0.005</v>
+      </c>
+      <c r="BO11">
+        <v>0.08986049342282525</v>
+      </c>
+      <c r="BP11">
+        <v>0.1353828264773835</v>
+      </c>
+      <c r="BQ11">
+        <v>0.06847147786050077</v>
+      </c>
+      <c r="BR11">
         <v>1</v>
       </c>
-      <c r="AU11">
-        <v>0.05803461930233451</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY11" s="2">
+      <c r="BS11">
+        <v>0.0593171033129548</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>125</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW11" s="2">
         <v>46335</v>
       </c>
     </row>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -361,34 +361,34 @@
     <t>下降坡延续</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=2.623,naive=0.9405,drift4=1.791; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.0368,naive=0.02224,drift4=0.02023; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01282,naive=0.003084,drift4=0.006728; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.19,drift4=0.40); metric_best=drift4; scores=model=0.01542,naive=0.01741,drift4=0.008396</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01339,naive=0.006914,drift4=0.01052; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.04936,naive=0.05745,drift4=0.05057; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.009039,naive=0.007752,drift4=0.008141; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.08386,naive=0.05236,drift4=0.03909; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=508.7,naive=138.1,drift4=113.3; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.19,drift4=0.37); metric_best=drift4; scores=model=0.08986,naive=0.1354,drift4=0.06847</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=2.542,naive=0.9146,drift4=1.714; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.03576,naive=0.0222,drift4=0.01967; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01186,naive=0.0026,drift4=0.00672; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.19,drift4=0.40); metric_best=drift4; scores=model=0.01446,naive=0.01659,drift4=0.007929</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01258,naive=0.00579,drift4=0.01059; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=model; scores=model=0.04925,naive=0.05405,drift4=0.05045; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.00882,naive=0.006851,drift4=0.007719; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.08153,naive=0.04816,drift4=0.03939; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=drift4; scores=model=466.4,naive=131.2,drift4=115.5; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.19,drift4=0.37); metric_best=drift4; scores=model=0.08439,naive=0.1321,drift4=0.06773</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -1114,10 +1114,10 @@
         <v>158.322</v>
       </c>
       <c r="AQ2">
-        <v>160.990289372439</v>
+        <v>160.9950412532351</v>
       </c>
       <c r="AR2">
-        <v>160.5068632473895</v>
+        <v>160.511008546436</v>
       </c>
       <c r="AS2">
         <v>158.322</v>
@@ -1126,28 +1126,28 @@
         <v>163.129</v>
       </c>
       <c r="AU2">
-        <v>160.990289372439</v>
+        <v>160.9950412532351</v>
       </c>
       <c r="AV2">
-        <v>156.543140418374</v>
+        <v>156.5399724978433</v>
       </c>
       <c r="AW2">
-        <v>0.0168535602912986</v>
+        <v>0.01688357431838368</v>
       </c>
       <c r="AX2">
         <v>1.5</v>
       </c>
       <c r="AY2">
-        <v>0.0168535602912986</v>
+        <v>0.01688357431838368</v>
       </c>
       <c r="AZ2">
-        <v>0.4489890263690312</v>
+        <v>0.4478848642414759</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3510109736309688</v>
+        <v>0.3521151357585242</v>
       </c>
       <c r="BC2" t="s">
         <v>115</v>
@@ -1162,43 +1162,43 @@
         <v>375</v>
       </c>
       <c r="BG2">
-        <v>0.01123570686086573</v>
+        <v>0.01125571621225579</v>
       </c>
       <c r="BH2">
-        <v>44500.98299925511</v>
+        <v>44421.87334605816</v>
       </c>
       <c r="BI2">
-        <v>33375.73724944133</v>
+        <v>33316.40500954362</v>
       </c>
       <c r="BJ2">
-        <v>210.8092194984988</v>
+        <v>210.4344627376083</v>
       </c>
       <c r="BK2">
-        <v>333.7573724944133</v>
+        <v>333.1640500954362</v>
       </c>
       <c r="BL2">
-        <v>0.003337573724944133</v>
+        <v>0.003331640500954362</v>
       </c>
       <c r="BM2">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="BN2">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="BO2">
-        <v>2.622884902008138</v>
+        <v>2.541509152261594</v>
       </c>
       <c r="BP2">
-        <v>0.9404835060643784</v>
+        <v>0.9145588968065255</v>
       </c>
       <c r="BQ2">
-        <v>1.790821100624553</v>
+        <v>1.71398809583145</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT2" t="s">
         <v>125</v>
@@ -1341,10 +1341,10 @@
         <v>6.694155</v>
       </c>
       <c r="AQ3">
-        <v>6.726471833778877</v>
+        <v>6.726393786293027</v>
       </c>
       <c r="AR3">
-        <v>6.783933731935033</v>
+        <v>6.783880066678135</v>
       </c>
       <c r="AS3">
         <v>6.694155</v>
@@ -1353,28 +1353,28 @@
         <v>6.680485000000001</v>
       </c>
       <c r="AU3">
-        <v>6.726471833778877</v>
+        <v>6.726393786293027</v>
       </c>
       <c r="AV3">
         <v>6.67197625</v>
       </c>
       <c r="AW3">
-        <v>0.00482761958438023</v>
+        <v>0.004815960534679384</v>
       </c>
       <c r="AX3">
-        <v>1.457107987550123</v>
+        <v>1.453588966602136</v>
       </c>
       <c r="AY3">
-        <v>0.00482761958438023</v>
+        <v>0.004815960534679384</v>
       </c>
       <c r="AZ3">
-        <v>0.4181088832102814</v>
+        <v>0.4175710474410581</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3818911167897185</v>
+        <v>0.3824289525589419</v>
       </c>
       <c r="BC3" t="s">
         <v>116</v>
@@ -1413,19 +1413,19 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO3">
-        <v>0.03679723706875769</v>
+        <v>0.03576492307226967</v>
       </c>
       <c r="BP3">
-        <v>0.02223567826964404</v>
+        <v>0.02219557313557077</v>
       </c>
       <c r="BQ3">
-        <v>0.02023357663690688</v>
+        <v>0.01967052573569687</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT3" t="s">
         <v>125</v>
@@ -1568,10 +1568,10 @@
         <v>0.829295</v>
       </c>
       <c r="AQ4">
-        <v>0.8323052712373362</v>
+        <v>0.8320853704050494</v>
       </c>
       <c r="AR4">
-        <v>0.8255713715493158</v>
+        <v>0.8254063296941311</v>
       </c>
       <c r="AS4">
         <v>0.829295</v>
@@ -1580,28 +1580,28 @@
         <v>0.842145</v>
       </c>
       <c r="AU4">
-        <v>0.8323052712373362</v>
+        <v>0.8320853704050494</v>
       </c>
       <c r="AV4">
         <v>0.82192375</v>
       </c>
       <c r="AW4">
-        <v>0.003629916058020626</v>
+        <v>0.003364750064873621</v>
       </c>
       <c r="AX4">
-        <v>0.4083800220228854</v>
+        <v>0.3785477910869052</v>
       </c>
       <c r="AY4">
-        <v>0.003629916058020626</v>
+        <v>0.003364750064873621</v>
       </c>
       <c r="AZ4">
-        <v>0.438632299758336</v>
+        <v>0.44744471681987</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.361367700241664</v>
+        <v>0.3525552831801301</v>
       </c>
       <c r="BC4" t="s">
         <v>117</v>
@@ -1640,19 +1640,19 @@
         <v>0.004999999999999999</v>
       </c>
       <c r="BO4">
-        <v>0.01281824077193947</v>
+        <v>0.0118632464264908</v>
       </c>
       <c r="BP4">
-        <v>0.003083693615176796</v>
+        <v>0.002599802405455804</v>
       </c>
       <c r="BQ4">
-        <v>0.006728161113478901</v>
+        <v>0.00672040716275162</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT4" t="s">
         <v>125</v>
@@ -1795,10 +1795,10 @@
         <v>1.11895</v>
       </c>
       <c r="AQ5">
-        <v>1.112125712321921</v>
+        <v>1.112154886737789</v>
       </c>
       <c r="AR5">
-        <v>1.141959287169594</v>
+        <v>1.141985381704055</v>
       </c>
       <c r="AS5">
         <v>1.11895</v>
@@ -1807,28 +1807,28 @@
         <v>1.078005</v>
       </c>
       <c r="AU5">
-        <v>1.112125712321921</v>
+        <v>1.112154886737789</v>
       </c>
       <c r="AV5">
         <v>1.12931</v>
       </c>
       <c r="AW5">
-        <v>-0.00609883165295954</v>
+        <v>-0.006072758623898343</v>
       </c>
       <c r="AX5">
-        <v>0.6587150268416075</v>
+        <v>0.6558989635338829</v>
       </c>
       <c r="AY5">
-        <v>0.00609883165295954</v>
+        <v>0.006072758623898343</v>
       </c>
       <c r="AZ5">
-        <v>0.4093247752591768</v>
+        <v>0.4102919297394347</v>
       </c>
       <c r="BA5">
-        <v>0.1939831017063407</v>
+        <v>0.1929234940277644</v>
       </c>
       <c r="BB5">
-        <v>0.3966921230344825</v>
+        <v>0.3967845762328009</v>
       </c>
       <c r="BC5" t="s">
         <v>118</v>
@@ -1867,19 +1867,19 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="BO5">
-        <v>0.01542033590270082</v>
+        <v>0.01446348850713787</v>
       </c>
       <c r="BP5">
-        <v>0.01740863303146617</v>
+        <v>0.0165937524750929</v>
       </c>
       <c r="BQ5">
-        <v>0.008396430048403982</v>
+        <v>0.00792915546330133</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT5" t="s">
         <v>125</v>
@@ -2022,10 +2022,10 @@
         <v>1.32324</v>
       </c>
       <c r="AQ6">
-        <v>1.312611488048471</v>
+        <v>1.312890246923144</v>
       </c>
       <c r="AR6">
-        <v>1.322244705453943</v>
+        <v>1.322364990737785</v>
       </c>
       <c r="AS6">
         <v>1.32324</v>
@@ -2034,28 +2034,28 @@
         <v>1.293885</v>
       </c>
       <c r="AU6">
-        <v>1.312611488048471</v>
+        <v>1.312890246923144</v>
       </c>
       <c r="AV6">
         <v>1.33489</v>
       </c>
       <c r="AW6">
-        <v>-0.008032187623959982</v>
+        <v>-0.007821523742371699</v>
       </c>
       <c r="AX6">
-        <v>0.9123186224488251</v>
+        <v>0.8883908220477196</v>
       </c>
       <c r="AY6">
-        <v>0.008032187623959982</v>
+        <v>0.007821523742371699</v>
       </c>
       <c r="AZ6">
-        <v>0.4533011835877003</v>
+        <v>0.4611745503736541</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3466988164122997</v>
+        <v>0.338825449626346</v>
       </c>
       <c r="BC6" t="s">
         <v>119</v>
@@ -2094,19 +2094,19 @@
         <v>0.005</v>
       </c>
       <c r="BO6">
-        <v>0.01338984322726786</v>
+        <v>0.01258447833854159</v>
       </c>
       <c r="BP6">
-        <v>0.006913522951227255</v>
+        <v>0.005790018622239624</v>
       </c>
       <c r="BQ6">
-        <v>0.01052051280019401</v>
+        <v>0.0105863492697829</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT6" t="s">
         <v>125</v>
@@ -2249,10 +2249,10 @@
         <v>4.67727</v>
       </c>
       <c r="AQ7">
-        <v>4.637436860421202</v>
+        <v>4.638084430998688</v>
       </c>
       <c r="AR7">
-        <v>4.684991378018259</v>
+        <v>4.686234317728189</v>
       </c>
       <c r="AS7">
         <v>4.67727</v>
@@ -2261,28 +2261,28 @@
         <v>4.54689</v>
       </c>
       <c r="AU7">
-        <v>4.637436860421202</v>
+        <v>4.638084430998688</v>
       </c>
       <c r="AV7">
         <v>4.719915</v>
       </c>
       <c r="AW7">
-        <v>-0.008516322465625906</v>
+        <v>-0.008377871921294184</v>
       </c>
       <c r="AX7">
-        <v>0.9340635380184791</v>
+        <v>0.9188783914013743</v>
       </c>
       <c r="AY7">
-        <v>0.008516322465625906</v>
+        <v>0.008377871921294184</v>
       </c>
       <c r="AZ7">
-        <v>0.4668371984867384</v>
+        <v>0.4673203189075212</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3331628015132617</v>
+        <v>0.3326796810924788</v>
       </c>
       <c r="BC7" t="s">
         <v>120</v>
@@ -2321,19 +2321,19 @@
         <v>0.005</v>
       </c>
       <c r="BO7">
-        <v>0.04935643734942342</v>
+        <v>0.04924506932714251</v>
       </c>
       <c r="BP7">
-        <v>0.05744767418596648</v>
+        <v>0.05405129543317525</v>
       </c>
       <c r="BQ7">
-        <v>0.050573124607282</v>
+        <v>0.05044654322589623</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT7" t="s">
         <v>125</v>
@@ -2476,10 +2476,10 @@
         <v>0.697225</v>
       </c>
       <c r="AQ8">
-        <v>0.6909232407627918</v>
+        <v>0.6909780625424546</v>
       </c>
       <c r="AR8">
-        <v>0.6977505765541704</v>
+        <v>0.6979297962852261</v>
       </c>
       <c r="AS8">
         <v>0.697225</v>
@@ -2488,28 +2488,28 @@
         <v>0.6780999999999999</v>
       </c>
       <c r="AU8">
-        <v>0.6909232407627918</v>
+        <v>0.6909780625424546</v>
       </c>
       <c r="AV8">
         <v>0.703025</v>
       </c>
       <c r="AW8">
-        <v>-0.009038343773112288</v>
+        <v>-0.008959715239048146</v>
       </c>
       <c r="AX8">
-        <v>1.086510213311756</v>
+        <v>1.077058182335399</v>
       </c>
       <c r="AY8">
-        <v>0.009038343773112288</v>
+        <v>0.008959715239048146</v>
       </c>
       <c r="AZ8">
-        <v>0.4579123028775482</v>
+        <v>0.4565383533062086</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3420876971224517</v>
+        <v>0.3434616466937914</v>
       </c>
       <c r="BC8" t="s">
         <v>121</v>
@@ -2548,19 +2548,19 @@
         <v>0.00406249572975179</v>
       </c>
       <c r="BO8">
-        <v>0.009039297266560345</v>
+        <v>0.00881980424548166</v>
       </c>
       <c r="BP8">
-        <v>0.007751638754503872</v>
+        <v>0.006851120333492802</v>
       </c>
       <c r="BQ8">
-        <v>0.008140840527309965</v>
+        <v>0.007719384975259034</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT8" t="s">
         <v>125</v>
@@ -2703,10 +2703,10 @@
         <v>8.861319999999999</v>
       </c>
       <c r="AQ9">
-        <v>8.775635788256935</v>
+        <v>8.776622195904338</v>
       </c>
       <c r="AR9">
-        <v>8.851324093403699</v>
+        <v>8.851595484738551</v>
       </c>
       <c r="AS9">
         <v>8.861319999999999</v>
@@ -2715,28 +2715,28 @@
         <v>8.655979999999998</v>
       </c>
       <c r="AU9">
-        <v>8.775635788256935</v>
+        <v>8.776622195904338</v>
       </c>
       <c r="AV9">
-        <v>8.918442807828709</v>
+        <v>8.917785202730441</v>
       </c>
       <c r="AW9">
-        <v>-0.009669463662644449</v>
+        <v>-0.009558147555404998</v>
       </c>
       <c r="AX9">
         <v>1.5</v>
       </c>
       <c r="AY9">
-        <v>0.009669463662644449</v>
+        <v>0.009558147555404998</v>
       </c>
       <c r="AZ9">
-        <v>0.4023043998290992</v>
+        <v>0.4067888388830403</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3976956001709008</v>
+        <v>0.3932111611169597</v>
       </c>
       <c r="BC9" t="s">
         <v>122</v>
@@ -2751,43 +2751,43 @@
         <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.006446309108429633</v>
+        <v>0.006372098370269999</v>
       </c>
       <c r="BH9">
-        <v>77563.76425483009</v>
+        <v>78467.08744058732</v>
       </c>
       <c r="BI9">
-        <v>77563.76425483009</v>
+        <v>78467.08744058732</v>
       </c>
       <c r="BJ9">
-        <v>8753.07112877428</v>
+        <v>8855.011154160704</v>
       </c>
       <c r="BK9">
-        <v>775.637642548301</v>
+        <v>784.6708744058732</v>
       </c>
       <c r="BL9">
-        <v>0.00775637642548301</v>
+        <v>0.007846708744058732</v>
       </c>
       <c r="BM9">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN9">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>0.0838575150110859</v>
+        <v>0.08153440678605803</v>
       </c>
       <c r="BP9">
-        <v>0.05235533095852363</v>
+        <v>0.04816438339836328</v>
       </c>
       <c r="BQ9">
-        <v>0.03908692170619526</v>
+        <v>0.0393911675298305</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT9" t="s">
         <v>125</v>
@@ -2930,10 +2930,10 @@
         <v>4195.629999999999</v>
       </c>
       <c r="AQ10">
-        <v>4136.549473815716</v>
+        <v>4140.227725053534</v>
       </c>
       <c r="AR10">
-        <v>4214.250498545569</v>
+        <v>4220.882170784045</v>
       </c>
       <c r="AS10">
         <v>4195.629999999999</v>
@@ -2942,28 +2942,28 @@
         <v>4044.579999999998</v>
       </c>
       <c r="AU10">
-        <v>4136.549473815716</v>
+        <v>4140.227725053534</v>
       </c>
       <c r="AV10">
         <v>4329.267499999999</v>
       </c>
       <c r="AW10">
-        <v>-0.0140814433551775</v>
+        <v>-0.01320475707973909</v>
       </c>
       <c r="AX10">
-        <v>0.4420954162138868</v>
+        <v>0.4145713212718408</v>
       </c>
       <c r="AY10">
-        <v>0.0140814433551775</v>
+        <v>0.01320475707973909</v>
       </c>
       <c r="AZ10">
-        <v>0.3639965364935277</v>
+        <v>0.3711680052634715</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.4360034635064723</v>
+        <v>0.4288319947365286</v>
       </c>
       <c r="BC10" t="s">
         <v>123</v>
@@ -3002,19 +3002,19 @@
         <v>0.00375</v>
       </c>
       <c r="BO10">
-        <v>508.7343108685552</v>
+        <v>466.4325932395168</v>
       </c>
       <c r="BP10">
-        <v>138.0628247282922</v>
+        <v>131.2459550676453</v>
       </c>
       <c r="BQ10">
-        <v>113.3130143265598</v>
+        <v>115.533219984968</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT10" t="s">
         <v>125</v>
@@ -3157,10 +3157,10 @@
         <v>7.4965</v>
       </c>
       <c r="AQ11">
-        <v>7.381340076159068</v>
+        <v>7.38228392431403</v>
       </c>
       <c r="AR11">
-        <v>7.472718662462803</v>
+        <v>7.472254374568385</v>
       </c>
       <c r="AS11">
         <v>7.4965</v>
@@ -3169,28 +3169,28 @@
         <v>7.2141</v>
       </c>
       <c r="AU11">
-        <v>7.381340076159068</v>
+        <v>7.38228392431403</v>
       </c>
       <c r="AV11">
-        <v>7.573273282560621</v>
+        <v>7.572644050457313</v>
       </c>
       <c r="AW11">
-        <v>-0.01536182536396078</v>
+        <v>-0.01523592018755022</v>
       </c>
       <c r="AX11">
         <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0.01536182536396078</v>
+        <v>0.01523592018755022</v>
       </c>
       <c r="AZ11">
-        <v>0.4430034407861836</v>
+        <v>0.4483116776563395</v>
       </c>
       <c r="BA11">
-        <v>0.1865124604692818</v>
+        <v>0.1857305366747679</v>
       </c>
       <c r="BB11">
-        <v>0.3704840987445346</v>
+        <v>0.3659577856688925</v>
       </c>
       <c r="BC11" t="s">
         <v>124</v>
@@ -3205,22 +3205,22 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.01024121690930719</v>
+        <v>0.01015728012503348</v>
       </c>
       <c r="BH11">
-        <v>48822.32301374279</v>
+        <v>49225.77637370731</v>
       </c>
       <c r="BI11">
-        <v>48822.32301374279</v>
+        <v>49225.77637370731</v>
       </c>
       <c r="BJ11">
-        <v>6512.682320248487</v>
+        <v>6566.50121706227</v>
       </c>
       <c r="BK11">
-        <v>488.2232301374279</v>
+        <v>492.2577637370731</v>
       </c>
       <c r="BL11">
-        <v>0.004882232301374279</v>
+        <v>0.004922577637370731</v>
       </c>
       <c r="BM11">
         <v>500</v>
@@ -3229,19 +3229,19 @@
         <v>0.005</v>
       </c>
       <c r="BO11">
-        <v>0.08986049342282525</v>
+        <v>0.08439061233345679</v>
       </c>
       <c r="BP11">
-        <v>0.1353828264773835</v>
+        <v>0.1320853220906493</v>
       </c>
       <c r="BQ11">
-        <v>0.06847147786050077</v>
+        <v>0.06772563701121495</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.0593171033129548</v>
+        <v>0.05944184774353721</v>
       </c>
       <c r="BT11" t="s">
         <v>125</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,78 @@
     <t>TerrainSizeMultiplier</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>EntryPrice</t>
   </si>
   <si>
@@ -169,19 +241,28 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>USDCHF</t>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
   </si>
   <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>EURCNH</t>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
   </si>
   <si>
     <t>GBPCNH</t>
@@ -190,28 +271,22 @@
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>LOW</t>
+    <t>FLAT</t>
   </si>
   <si>
     <t>LONG</t>
@@ -226,10 +301,13 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
+    <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -238,37 +316,97 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=2.643,naive=1.111,drift4=4.601; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.20,drift4=0.48); metric_best=drift4; scores=model=0.333,naive=0.03735,drift4=0.02489; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05047,naive=0.004243,drift4=0.01862; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.0146,naive=0.003733,drift4=0.01336; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.15,drift4=0.44); metric_best=drift4; scores=model=0.1248,naive=0.2348,drift4=0.06061</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1393,naive=0.07689,drift4=0.1585; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.20,drift4=0.48); metric_best=drift4; scores=model=1801,naive=119.2,drift4=86.56; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.52,naive=0.20,drift4=0.28); metric_best=naive; scores=model=0.01956,naive=0.001406,drift4=0.03837; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.1626,naive=0.07555,drift4=0.04057; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.29,naive=0.11,drift4=0.60); metric_best=drift4; scores=model=0.03922,naive=0.02341,drift4=0.00157</t>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01374,naive=0.003608,drift4=0.006887; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=2.587,naive=0.7483,drift4=1.875; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.04966,naive=0.02029,drift4=0.01725; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.01662,naive=0.01431,drift4=0.009863; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1298,naive=0.1281,drift4=0.06419; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.008587,naive=0.00531,drift4=0.01015; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.01416,naive=0.004488,drift4=0.01445; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=model; scores=model=0.04607,naive=0.0467,drift4=0.05382; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.09115,naive=0.0486,drift4=0.05623; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=463,naive=102.3,drift4=125.3; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -633,10 +771,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BW11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,10 +928,82 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:75">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
         <v>46308</v>
@@ -802,153 +1012,213 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2">
         <v>46307</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0.04448033581276137</v>
+        <v>2.421591097647279</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q2">
-        <v>0.75</v>
-      </c>
-      <c r="R2">
-        <v>158.139</v>
-      </c>
-      <c r="S2">
-        <v>159.1442513194972</v>
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S2" t="s">
+        <v>104</v>
       </c>
       <c r="T2">
-        <v>159.3886673061649</v>
+        <v>0.9849260705978544</v>
       </c>
       <c r="U2">
-        <v>158.139</v>
-      </c>
-      <c r="V2">
-        <v>159.408</v>
-      </c>
-      <c r="W2">
-        <v>159.1442513194972</v>
+        <v>0.9931832513933914</v>
+      </c>
+      <c r="V2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W2" t="s">
+        <v>96</v>
       </c>
       <c r="X2">
-        <v>156.640875</v>
+        <v>0.9998660784974276</v>
       </c>
       <c r="Y2">
-        <v>0.006356757785853889</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>0.6710063042116896</v>
+        <v>-14.10514811019718</v>
       </c>
       <c r="AA2">
-        <v>0.006356757785853889</v>
+        <v>-4.999999999999995</v>
       </c>
       <c r="AB2">
-        <v>0.5146039443695818</v>
+        <v>0.9698501222020469</v>
       </c>
       <c r="AC2">
+        <v>-0.2437021552319034</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH2">
+        <v>0.9697202384164115</v>
+      </c>
+      <c r="AI2">
+        <v>0.9861764905904619</v>
+      </c>
+      <c r="AJ2">
+        <v>1.925079983758004</v>
+      </c>
+      <c r="AK2">
+        <v>-0.4620407768399371</v>
+      </c>
+      <c r="AL2">
+        <v>2.639692820720451</v>
+      </c>
+      <c r="AM2">
+        <v>-3.923864906747239</v>
+      </c>
+      <c r="AN2">
+        <v>2.322718934029044</v>
+      </c>
+      <c r="AO2">
+        <v>0.03154449029501143</v>
+      </c>
+      <c r="AP2">
+        <v>0.8321000000000001</v>
+      </c>
+      <c r="AQ2">
+        <v>0.8249246063801707</v>
+      </c>
+      <c r="AR2">
+        <v>0.8069941048396037</v>
+      </c>
+      <c r="AS2">
+        <v>0.8321000000000001</v>
+      </c>
+      <c r="AT2">
+        <v>0.8420900000000001</v>
+      </c>
+      <c r="AW2">
+        <v>-0.008623234731197365</v>
+      </c>
+      <c r="AY2">
+        <v>0.008623234731197365</v>
+      </c>
+      <c r="AZ2">
+        <v>0.4321700173342462</v>
+      </c>
+      <c r="BA2">
         <v>0.2</v>
       </c>
-      <c r="AD2">
-        <v>0.2853960556304182</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2">
+      <c r="BB2">
+        <v>0.3678299826657538</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2">
         <v>100000</v>
       </c>
-      <c r="AG2">
+      <c r="BE2">
         <v>100</v>
       </c>
-      <c r="AH2">
-        <v>375</v>
-      </c>
-      <c r="AI2">
-        <v>0.009473469542617671</v>
-      </c>
-      <c r="AJ2">
-        <v>52778.97371714587</v>
-      </c>
-      <c r="AK2">
-        <v>39584.23028785941</v>
-      </c>
-      <c r="AL2">
-        <v>250.3128911138897</v>
-      </c>
-      <c r="AM2">
-        <v>395.8423028785941</v>
-      </c>
-      <c r="AN2">
-        <v>0.003958423028785941</v>
-      </c>
-      <c r="AO2">
-        <v>375</v>
-      </c>
-      <c r="AP2">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ2">
-        <v>2.327534826905761</v>
-      </c>
-      <c r="AR2">
-        <v>0.3829889881637994</v>
-      </c>
-      <c r="AS2">
-        <v>1.877761606900539</v>
-      </c>
-      <c r="AT2">
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0.01373652560671497</v>
+      </c>
+      <c r="BP2">
+        <v>0.003607773891601695</v>
+      </c>
+      <c r="BQ2">
+        <v>0.006886549405780873</v>
+      </c>
+      <c r="BR2">
         <v>1</v>
       </c>
-      <c r="AU2">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY2" s="2">
+      <c r="BS2">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW2" s="2">
         <v>46336</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:75">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2">
         <v>46308</v>
@@ -957,22 +1227,22 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
         <v>46307</v>
@@ -981,129 +1251,201 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1.929537385921455</v>
+        <v>0.05986987560256773</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="Q3">
+        <v>0.75</v>
+      </c>
+      <c r="R3" t="s">
+        <v>101</v>
+      </c>
+      <c r="S3" t="s">
+        <v>105</v>
+      </c>
+      <c r="T3">
+        <v>0.738067466506483</v>
+      </c>
+      <c r="U3">
+        <v>0.7320751826858796</v>
+      </c>
+      <c r="V3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W3" t="s">
+        <v>96</v>
+      </c>
+      <c r="X3">
+        <v>0.9997792910318488</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>76.53800372305302</v>
+      </c>
+      <c r="AA3">
+        <v>5.000000000000007</v>
+      </c>
+      <c r="AB3">
+        <v>0.2328003492134589</v>
+      </c>
+      <c r="AC3">
+        <v>0.9725245484850712</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH3">
+        <v>0.1163744840442994</v>
+      </c>
+      <c r="AI3">
+        <v>0.5594596829097556</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1929176118059248</v>
+      </c>
+      <c r="AK3">
+        <v>0.7564869611555672</v>
+      </c>
+      <c r="AL3">
+        <v>0.008638114975920014</v>
+      </c>
+      <c r="AM3">
+        <v>-0.9259049184787623</v>
+      </c>
+      <c r="AN3">
+        <v>0.1710167166703472</v>
+      </c>
+      <c r="AO3">
+        <v>0.06868782476952809</v>
+      </c>
+      <c r="AP3">
+        <v>158.139</v>
+      </c>
+      <c r="AQ3">
+        <v>158.8912166306558</v>
+      </c>
+      <c r="AR3">
+        <v>158.8348120928184</v>
+      </c>
+      <c r="AS3">
+        <v>158.139</v>
+      </c>
+      <c r="AT3">
+        <v>159.408</v>
+      </c>
+      <c r="AU3">
+        <v>158.8912166306558</v>
+      </c>
+      <c r="AV3">
+        <v>156.640875</v>
+      </c>
+      <c r="AW3">
+        <v>0.004756680076741495</v>
+      </c>
+      <c r="AX3">
+        <v>0.5021053855024216</v>
+      </c>
+      <c r="AY3">
+        <v>0.004756680076741495</v>
+      </c>
+      <c r="AZ3">
+        <v>0.4588083001215095</v>
+      </c>
+      <c r="BA3">
+        <v>0.2</v>
+      </c>
+      <c r="BB3">
+        <v>0.3411916998784905</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3">
+        <v>100000</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>375</v>
+      </c>
+      <c r="BG3">
+        <v>0.009473469542617671</v>
+      </c>
+      <c r="BH3">
+        <v>52778.97371714587</v>
+      </c>
+      <c r="BI3">
+        <v>39584.23028785941</v>
+      </c>
+      <c r="BJ3">
+        <v>250.3128911138897</v>
+      </c>
+      <c r="BK3">
+        <v>395.8423028785941</v>
+      </c>
+      <c r="BL3">
+        <v>0.003958423028785941</v>
+      </c>
+      <c r="BM3">
+        <v>375</v>
+      </c>
+      <c r="BN3">
+        <v>0.00375</v>
+      </c>
+      <c r="BO3">
+        <v>2.587025760162605</v>
+      </c>
+      <c r="BP3">
+        <v>0.7482541259286681</v>
+      </c>
+      <c r="BQ3">
+        <v>1.874714141982437</v>
+      </c>
+      <c r="BR3">
         <v>1</v>
       </c>
-      <c r="R3">
-        <v>6.69204</v>
-      </c>
-      <c r="S3">
-        <v>6.730069273808365</v>
-      </c>
-      <c r="T3">
-        <v>6.81635890241904</v>
-      </c>
-      <c r="U3">
-        <v>6.69204</v>
-      </c>
-      <c r="V3">
-        <v>6.687505000000001</v>
-      </c>
-      <c r="W3">
-        <v>6.730069273808365</v>
-      </c>
-      <c r="X3">
-        <v>6.666687150794425</v>
-      </c>
-      <c r="Y3">
-        <v>0.005682762477266168</v>
-      </c>
-      <c r="Z3">
-        <v>1.5</v>
-      </c>
-      <c r="AA3">
-        <v>0.005682762477266168</v>
-      </c>
-      <c r="AB3">
-        <v>0.3232907426652241</v>
-      </c>
-      <c r="AC3">
-        <v>0.2</v>
-      </c>
-      <c r="AD3">
-        <v>0.476709257334776</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF3">
-        <v>100000</v>
-      </c>
-      <c r="AG3">
-        <v>100</v>
-      </c>
-      <c r="AH3">
-        <v>500</v>
-      </c>
-      <c r="AI3">
-        <v>0.003788508318177446</v>
-      </c>
-      <c r="AJ3">
-        <v>131978.065773533</v>
-      </c>
-      <c r="AK3">
-        <v>131978.065773533</v>
-      </c>
-      <c r="AL3">
-        <v>19721.64926891248</v>
-      </c>
-      <c r="AM3">
-        <v>1319.78065773533</v>
-      </c>
-      <c r="AN3">
-        <v>0.0131978065773533</v>
-      </c>
-      <c r="AO3">
-        <v>500</v>
-      </c>
-      <c r="AP3">
-        <v>0.005</v>
-      </c>
-      <c r="AQ3">
-        <v>0.09802740436694164</v>
-      </c>
-      <c r="AR3">
-        <v>0.01139631658907858</v>
-      </c>
-      <c r="AS3">
-        <v>0.00990009265947657</v>
-      </c>
-      <c r="AT3">
-        <v>1</v>
-      </c>
-      <c r="AU3">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY3" s="2">
+      <c r="BS3">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW3" s="2">
         <v>46336</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:75">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2">
         <v>46308</v>
@@ -1112,153 +1454,225 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="J4" s="2">
         <v>46307</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2.353154044419519</v>
+        <v>1.930639250352429</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="O4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
-      <c r="R4">
-        <v>0.8321000000000001</v>
-      </c>
-      <c r="S4">
-        <v>0.8331391857527548</v>
+      <c r="R4" t="s">
+        <v>102</v>
+      </c>
+      <c r="S4" t="s">
+        <v>106</v>
       </c>
       <c r="T4">
-        <v>0.8266948047884078</v>
+        <v>-0.9795423367062644</v>
       </c>
       <c r="U4">
-        <v>0.8321000000000001</v>
-      </c>
-      <c r="V4">
-        <v>0.8420900000000001</v>
-      </c>
-      <c r="W4">
-        <v>0.8333481500000001</v>
+        <v>0.8407328846763799</v>
+      </c>
+      <c r="V4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W4" t="s">
+        <v>96</v>
       </c>
       <c r="X4">
-        <v>0.8250025000000001</v>
+        <v>0.9997553326342432</v>
       </c>
       <c r="Y4">
-        <v>0.001248871232730135</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>0.1758576963719618</v>
+        <v>-160.0647631826654</v>
       </c>
       <c r="AA4">
-        <v>0.001248871232730135</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AB4">
-        <v>0.4516223504597067</v>
+        <v>-0.9400786162981162</v>
       </c>
       <c r="AC4">
+        <v>-0.3409577615761506</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH4">
+        <v>-0.4699243048697311</v>
+      </c>
+      <c r="AI4">
+        <v>0.7749428401187133</v>
+      </c>
+      <c r="AJ4">
+        <v>-1.364347044964132</v>
+      </c>
+      <c r="AK4">
+        <v>-0.4878975160737243</v>
+      </c>
+      <c r="AL4">
+        <v>-2.8642164131662</v>
+      </c>
+      <c r="AM4">
+        <v>1.012127000953872</v>
+      </c>
+      <c r="AN4">
+        <v>2.733038406265766</v>
+      </c>
+      <c r="AO4">
+        <v>0.04663407461804406</v>
+      </c>
+      <c r="AP4">
+        <v>6.69204</v>
+      </c>
+      <c r="AQ4">
+        <v>6.711522194588685</v>
+      </c>
+      <c r="AR4">
+        <v>6.747196693773782</v>
+      </c>
+      <c r="AS4">
+        <v>6.69204</v>
+      </c>
+      <c r="AT4">
+        <v>6.687505000000001</v>
+      </c>
+      <c r="AU4">
+        <v>6.711522194588685</v>
+      </c>
+      <c r="AV4">
+        <v>6.66986125</v>
+      </c>
+      <c r="AW4">
+        <v>0.002911248974704981</v>
+      </c>
+      <c r="AX4">
+        <v>0.8784171600601923</v>
+      </c>
+      <c r="AY4">
+        <v>0.002911248974704981</v>
+      </c>
+      <c r="AZ4">
+        <v>0.3871593035417488</v>
+      </c>
+      <c r="BA4">
         <v>0.2</v>
       </c>
-      <c r="AD4">
-        <v>0.3483776495402934</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF4">
+      <c r="BB4">
+        <v>0.4128406964582513</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD4">
         <v>100000</v>
       </c>
-      <c r="AG4">
+      <c r="BE4">
         <v>100</v>
       </c>
-      <c r="AH4">
+      <c r="BF4">
         <v>500</v>
       </c>
-      <c r="AI4">
-        <v>0.008529623843288073</v>
-      </c>
-      <c r="AJ4">
-        <v>58619.23212398728</v>
-      </c>
-      <c r="AK4">
-        <v>58619.23212398728</v>
-      </c>
-      <c r="AL4">
-        <v>70447.3406128918</v>
-      </c>
-      <c r="AM4">
-        <v>586.1923212398727</v>
-      </c>
-      <c r="AN4">
-        <v>0.005861923212398728</v>
-      </c>
-      <c r="AO4">
-        <v>500.0000000000001</v>
-      </c>
-      <c r="AP4">
-        <v>0.005000000000000001</v>
-      </c>
-      <c r="AQ4">
-        <v>0.01780480232547726</v>
-      </c>
-      <c r="AR4">
-        <v>0.001849267831851319</v>
-      </c>
-      <c r="AS4">
-        <v>0.00787177349288249</v>
-      </c>
-      <c r="AT4">
+      <c r="BG4">
+        <v>0.003314198659900373</v>
+      </c>
+      <c r="BH4">
+        <v>150866.0316744653</v>
+      </c>
+      <c r="BI4">
+        <v>150866.0316744653</v>
+      </c>
+      <c r="BJ4">
+        <v>22544.1018993409</v>
+      </c>
+      <c r="BK4">
+        <v>1508.660316744653</v>
+      </c>
+      <c r="BL4">
+        <v>0.01508660316744653</v>
+      </c>
+      <c r="BM4">
+        <v>500</v>
+      </c>
+      <c r="BN4">
+        <v>0.005</v>
+      </c>
+      <c r="BO4">
+        <v>0.04966034117266323</v>
+      </c>
+      <c r="BP4">
+        <v>0.02029224430433617</v>
+      </c>
+      <c r="BQ4">
+        <v>0.01725169477365541</v>
+      </c>
+      <c r="BR4">
         <v>1</v>
       </c>
-      <c r="AU4">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY4" s="2">
+      <c r="BS4">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW4" s="2">
         <v>46336</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:75">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2">
         <v>46308</v>
@@ -1267,153 +1681,225 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J5" s="2">
         <v>46307</v>
       </c>
       <c r="K5">
-        <v>0.2456298906748639</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1.880289322218486</v>
+        <v>3.503562166633421</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q5">
-        <v>0.8114074726687159</v>
-      </c>
-      <c r="R5">
-        <v>0.6979</v>
-      </c>
-      <c r="S5">
-        <v>0.694640238840002</v>
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>102</v>
+      </c>
+      <c r="S5" t="s">
+        <v>106</v>
       </c>
       <c r="T5">
-        <v>0.7009417542865404</v>
+        <v>-0.9808182008113934</v>
       </c>
       <c r="U5">
-        <v>0.6979</v>
-      </c>
-      <c r="V5">
-        <v>0.6832449999999999</v>
-      </c>
-      <c r="W5">
-        <v>0.694640238840002</v>
+        <v>0.9913440350160262</v>
+      </c>
+      <c r="V5" t="s">
+        <v>94</v>
+      </c>
+      <c r="W5" t="s">
+        <v>96</v>
       </c>
       <c r="X5">
-        <v>0.7033287500000001</v>
+        <v>0.9999033786035966</v>
       </c>
       <c r="Y5">
-        <v>-0.004670814099438217</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>0.6004625668888588</v>
+        <v>-164.0776871761149</v>
       </c>
       <c r="AA5">
-        <v>0.004670814099438217</v>
+        <v>-9</v>
       </c>
       <c r="AB5">
-        <v>0.4782932905634382</v>
+        <v>-0.961634548071471</v>
       </c>
       <c r="AC5">
+        <v>-0.2743337309835919</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH5">
+        <v>-0.9615416335986066</v>
+      </c>
+      <c r="AI5">
+        <v>0.9828846523926651</v>
+      </c>
+      <c r="AJ5">
+        <v>-2.771328789355583</v>
+      </c>
+      <c r="AK5">
+        <v>-0.8495958211085892</v>
+      </c>
+      <c r="AL5">
+        <v>-3.875838079564343</v>
+      </c>
+      <c r="AM5">
+        <v>5.727641660372683</v>
+      </c>
+      <c r="AN5">
+        <v>3.359438477404302</v>
+      </c>
+      <c r="AO5">
+        <v>0.0371459636002333</v>
+      </c>
+      <c r="AP5">
+        <v>1.118705</v>
+      </c>
+      <c r="AQ5">
+        <v>1.114865291831381</v>
+      </c>
+      <c r="AR5">
+        <v>1.136711796300315</v>
+      </c>
+      <c r="AS5">
+        <v>1.118705</v>
+      </c>
+      <c r="AT5">
+        <v>1.088875</v>
+      </c>
+      <c r="AU5">
+        <v>1.114865291831381</v>
+      </c>
+      <c r="AV5">
+        <v>1.129065</v>
+      </c>
+      <c r="AW5">
+        <v>-0.003432279437938712</v>
+      </c>
+      <c r="AX5">
+        <v>0.3706282016041712</v>
+      </c>
+      <c r="AY5">
+        <v>0.003432279437938712</v>
+      </c>
+      <c r="AZ5">
+        <v>0.4185960051687039</v>
+      </c>
+      <c r="BA5">
         <v>0.2</v>
       </c>
-      <c r="AD5">
-        <v>0.3217067094365619</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF5">
+      <c r="BB5">
+        <v>0.3814039948312962</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD5">
         <v>100000</v>
       </c>
-      <c r="AG5">
+      <c r="BE5">
         <v>100</v>
       </c>
-      <c r="AH5">
-        <v>405.703736334358</v>
-      </c>
-      <c r="AI5">
-        <v>0.007778693222524811</v>
-      </c>
-      <c r="AJ5">
-        <v>64278.14874510629</v>
-      </c>
-      <c r="AK5">
-        <v>52155.77022109049</v>
-      </c>
-      <c r="AL5">
-        <v>74732.44049446983</v>
-      </c>
-      <c r="AM5">
-        <v>521.5577022109049</v>
-      </c>
-      <c r="AN5">
-        <v>0.00521557702210905</v>
-      </c>
-      <c r="AO5">
-        <v>405.7037363343579</v>
-      </c>
-      <c r="AP5">
-        <v>0.004057037363343579</v>
-      </c>
-      <c r="AQ5">
-        <v>0.008886029525009147</v>
-      </c>
-      <c r="AR5">
-        <v>0.001768653507525128</v>
-      </c>
-      <c r="AS5">
-        <v>0.01162976913314246</v>
-      </c>
-      <c r="AT5">
+      <c r="BF5">
+        <v>500</v>
+      </c>
+      <c r="BG5">
+        <v>0.009260707693270375</v>
+      </c>
+      <c r="BH5">
+        <v>53991.55405405387</v>
+      </c>
+      <c r="BI5">
+        <v>53991.55405405387</v>
+      </c>
+      <c r="BJ5">
+        <v>48262.54826254809</v>
+      </c>
+      <c r="BK5">
+        <v>539.9155405405387</v>
+      </c>
+      <c r="BL5">
+        <v>0.005399155405405387</v>
+      </c>
+      <c r="BM5">
+        <v>500</v>
+      </c>
+      <c r="BN5">
+        <v>0.005</v>
+      </c>
+      <c r="BO5">
+        <v>0.01661605617198948</v>
+      </c>
+      <c r="BP5">
+        <v>0.01431122280182408</v>
+      </c>
+      <c r="BQ5">
+        <v>0.009863229970537695</v>
+      </c>
+      <c r="BR5">
         <v>1</v>
       </c>
-      <c r="AU5">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY5" s="2">
+      <c r="BS5">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW5" s="2">
         <v>46336</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:75">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2">
         <v>46308</v>
@@ -1422,22 +1908,22 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2">
         <v>46307</v>
@@ -1455,120 +1941,192 @@
         <v>19</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="s">
+        <v>102</v>
+      </c>
+      <c r="S6" t="s">
+        <v>106</v>
+      </c>
+      <c r="T6">
+        <v>-0.9812378977169776</v>
+      </c>
+      <c r="U6">
+        <v>0.99153940792491</v>
+      </c>
+      <c r="V6" t="s">
+        <v>94</v>
+      </c>
+      <c r="W6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X6">
+        <v>0.9999294158090806</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>-164.2540605542891</v>
+      </c>
+      <c r="AA6">
+        <v>-9</v>
+      </c>
+      <c r="AB6">
+        <v>-0.9624744710326638</v>
+      </c>
+      <c r="AC6">
+        <v>-0.2713722399406285</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH6">
+        <v>-0.9624065355508453</v>
+      </c>
+      <c r="AI6">
+        <v>0.982841603090765</v>
+      </c>
+      <c r="AJ6">
+        <v>-2.439417318172367</v>
+      </c>
+      <c r="AK6">
+        <v>-0.7369627437232636</v>
+      </c>
+      <c r="AL6">
+        <v>-3.727647648181441</v>
+      </c>
+      <c r="AM6">
+        <v>4.310233809280708</v>
+      </c>
+      <c r="AN6">
+        <v>3.329366576306081</v>
+      </c>
+      <c r="AO6">
+        <v>0.03917355834808257</v>
+      </c>
+      <c r="AP6">
         <v>7.4666</v>
       </c>
-      <c r="S6">
-        <v>7.405288685448182</v>
-      </c>
-      <c r="T6">
-        <v>7.552518006982547</v>
-      </c>
-      <c r="U6">
+      <c r="AQ6">
+        <v>7.433308562504356</v>
+      </c>
+      <c r="AR6">
+        <v>7.606022154613115</v>
+      </c>
+      <c r="AS6">
         <v>7.4666</v>
       </c>
-      <c r="V6">
+      <c r="AT6">
         <v>7.244699999999999</v>
       </c>
-      <c r="W6">
-        <v>7.405288685448182</v>
-      </c>
-      <c r="X6">
+      <c r="AU6">
+        <v>7.433308562504356</v>
+      </c>
+      <c r="AV6">
         <v>7.5174</v>
       </c>
-      <c r="Y6">
-        <v>-0.008211410086494172</v>
-      </c>
-      <c r="Z6">
-        <v>1.206915640783792</v>
-      </c>
-      <c r="AA6">
-        <v>0.008211410086494172</v>
-      </c>
-      <c r="AB6">
-        <v>0.4142848983948091</v>
-      </c>
-      <c r="AC6">
-        <v>0.1490055597175571</v>
-      </c>
-      <c r="AD6">
-        <v>0.4367095418876338</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF6">
+      <c r="AW6">
+        <v>-0.004458714474545771</v>
+      </c>
+      <c r="AX6">
+        <v>0.6553432577882489</v>
+      </c>
+      <c r="AY6">
+        <v>0.004458714474545771</v>
+      </c>
+      <c r="AZ6">
+        <v>0.3991688875507495</v>
+      </c>
+      <c r="BA6">
+        <v>0.2</v>
+      </c>
+      <c r="BB6">
+        <v>0.4008311124492506</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD6">
         <v>100000</v>
       </c>
-      <c r="AG6">
+      <c r="BE6">
         <v>100</v>
       </c>
-      <c r="AH6">
+      <c r="BF6">
         <v>500</v>
       </c>
-      <c r="AI6">
+      <c r="BG6">
         <v>0.006803632175287363</v>
       </c>
-      <c r="AJ6">
+      <c r="BH6">
         <v>73490.15748031405</v>
       </c>
-      <c r="AK6">
+      <c r="BI6">
         <v>73490.15748031405</v>
       </c>
-      <c r="AL6">
+      <c r="BJ6">
         <v>9842.519685039249</v>
       </c>
-      <c r="AM6">
+      <c r="BK6">
         <v>734.9015748031405</v>
       </c>
-      <c r="AN6">
+      <c r="BL6">
         <v>0.007349015748031405</v>
       </c>
-      <c r="AO6">
+      <c r="BM6">
         <v>500</v>
       </c>
-      <c r="AP6">
+      <c r="BN6">
         <v>0.005</v>
       </c>
-      <c r="AQ6">
-        <v>0.07401516908415127</v>
-      </c>
-      <c r="AR6">
-        <v>0.0672758664342694</v>
-      </c>
-      <c r="AS6">
-        <v>0.08755516968581209</v>
-      </c>
-      <c r="AT6">
+      <c r="BO6">
+        <v>0.1298139061736034</v>
+      </c>
+      <c r="BP6">
+        <v>0.128088888440355</v>
+      </c>
+      <c r="BQ6">
+        <v>0.06418913060685907</v>
+      </c>
+      <c r="BR6">
         <v>1</v>
       </c>
-      <c r="AU6">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY6" s="2">
+      <c r="BS6">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW6" s="2">
         <v>46336</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:75">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B7" s="2">
         <v>46308</v>
@@ -1577,153 +2135,225 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J7" s="2">
         <v>46307</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.2415476484852667</v>
       </c>
       <c r="L7">
-        <v>1.567658745515618</v>
+        <v>1.872722056502411</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q7">
+        <v>0.8103869121213166</v>
+      </c>
+      <c r="R7" t="s">
+        <v>103</v>
+      </c>
+      <c r="S7" t="s">
+        <v>107</v>
+      </c>
+      <c r="T7">
+        <v>-0.9908040602135986</v>
+      </c>
+      <c r="U7">
+        <v>0.88181123092184</v>
+      </c>
+      <c r="V7" t="s">
+        <v>94</v>
+      </c>
+      <c r="W7" t="s">
+        <v>96</v>
+      </c>
+      <c r="X7">
+        <v>0.9988690262117227</v>
+      </c>
+      <c r="Y7">
+        <v>0.3085495683883835</v>
+      </c>
+      <c r="Z7">
+        <v>168.015572570718</v>
+      </c>
+      <c r="AA7">
+        <v>-32.99999999999999</v>
+      </c>
+      <c r="AB7">
+        <v>-0.9782040734703017</v>
+      </c>
+      <c r="AC7">
+        <v>0.2076458298307691</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH7">
+        <v>-0.6392904197165317</v>
+      </c>
+      <c r="AI7">
+        <v>0.8495361137341224</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.587004802603548</v>
+      </c>
+      <c r="AK7">
+        <v>0.2103964585847024</v>
+      </c>
+      <c r="AL7">
+        <v>-1.605093322667548</v>
+      </c>
+      <c r="AM7">
+        <v>4.463323355156293</v>
+      </c>
+      <c r="AN7">
+        <v>1.2454008776845</v>
+      </c>
+      <c r="AO7">
+        <v>0.03492787439165116</v>
+      </c>
+      <c r="AP7">
+        <v>0.6979</v>
+      </c>
+      <c r="AQ7">
+        <v>0.6910500214958726</v>
+      </c>
+      <c r="AR7">
+        <v>0.6932914750280691</v>
+      </c>
+      <c r="AS7">
+        <v>0.6979</v>
+      </c>
+      <c r="AT7">
+        <v>0.6832449999999999</v>
+      </c>
+      <c r="AU7">
+        <v>0.6910500214958726</v>
+      </c>
+      <c r="AV7">
+        <v>0.7033287500000001</v>
+      </c>
+      <c r="AW7">
+        <v>-0.00981512896421749</v>
+      </c>
+      <c r="AX7">
+        <v>1.261796639028746</v>
+      </c>
+      <c r="AY7">
+        <v>0.00981512896421749</v>
+      </c>
+      <c r="AZ7">
+        <v>0.4851474255651895</v>
+      </c>
+      <c r="BA7">
+        <v>0.2</v>
+      </c>
+      <c r="BB7">
+        <v>0.3148525744348106</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD7">
+        <v>100000</v>
+      </c>
+      <c r="BE7">
+        <v>100</v>
+      </c>
+      <c r="BF7">
+        <v>405.1934560606583</v>
+      </c>
+      <c r="BG7">
+        <v>0.007778693222524811</v>
+      </c>
+      <c r="BH7">
+        <v>64278.14874510629</v>
+      </c>
+      <c r="BI7">
+        <v>52090.17047842137</v>
+      </c>
+      <c r="BJ7">
+        <v>74638.44458865364</v>
+      </c>
+      <c r="BK7">
+        <v>520.9017047842137</v>
+      </c>
+      <c r="BL7">
+        <v>0.005209017047842137</v>
+      </c>
+      <c r="BM7">
+        <v>405.1934560606583</v>
+      </c>
+      <c r="BN7">
+        <v>0.004051934560606583</v>
+      </c>
+      <c r="BO7">
+        <v>0.008587464356869443</v>
+      </c>
+      <c r="BP7">
+        <v>0.005310347729212244</v>
+      </c>
+      <c r="BQ7">
+        <v>0.01014842704455164</v>
+      </c>
+      <c r="BR7">
         <v>1</v>
       </c>
-      <c r="R7">
-        <v>8.84564</v>
-      </c>
-      <c r="S7">
-        <v>8.766909975796237</v>
-      </c>
-      <c r="T7">
-        <v>8.761489114180206</v>
-      </c>
-      <c r="U7">
-        <v>8.84564</v>
-      </c>
-      <c r="V7">
-        <v>8.72547</v>
-      </c>
-      <c r="W7">
-        <v>8.766909975796237</v>
-      </c>
-      <c r="X7">
-        <v>8.901752499999999</v>
-      </c>
-      <c r="Y7">
-        <v>-0.008900432778607624</v>
-      </c>
-      <c r="Z7">
-        <v>1.403074612675683</v>
-      </c>
-      <c r="AA7">
-        <v>0.008900432778607624</v>
-      </c>
-      <c r="AB7">
-        <v>0.4832427502007242</v>
-      </c>
-      <c r="AC7">
-        <v>0.2</v>
-      </c>
-      <c r="AD7">
-        <v>0.3167572497992758</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF7">
-        <v>100000</v>
-      </c>
-      <c r="AG7">
-        <v>100</v>
-      </c>
-      <c r="AH7">
-        <v>500</v>
-      </c>
-      <c r="AI7">
-        <v>0.006343520649721095</v>
-      </c>
-      <c r="AJ7">
-        <v>78820.58364892112</v>
-      </c>
-      <c r="AK7">
-        <v>78820.58364892112</v>
-      </c>
-      <c r="AL7">
-        <v>8910.670527957403</v>
-      </c>
-      <c r="AM7">
-        <v>788.2058364892113</v>
-      </c>
-      <c r="AN7">
-        <v>0.007882058364892112</v>
-      </c>
-      <c r="AO7">
-        <v>500</v>
-      </c>
-      <c r="AP7">
-        <v>0.005</v>
-      </c>
-      <c r="AQ7">
-        <v>0.1117676864527808</v>
-      </c>
-      <c r="AR7">
-        <v>0.02312336601394763</v>
-      </c>
-      <c r="AS7">
-        <v>0.08293157922472867</v>
-      </c>
-      <c r="AT7">
-        <v>1</v>
-      </c>
-      <c r="AU7">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY7" s="2">
+      <c r="BS7">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW7" s="2">
         <v>46336</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:75">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
         <v>46308</v>
@@ -1732,153 +2362,225 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J8" s="2">
         <v>46307</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>1.408334433515801</v>
+        <v>2.053953351593582</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O8" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
-      </c>
-      <c r="R8">
-        <v>4187.870000000001</v>
-      </c>
-      <c r="S8">
-        <v>4149.548154052424</v>
+        <v>1</v>
+      </c>
+      <c r="R8" t="s">
+        <v>103</v>
+      </c>
+      <c r="S8" t="s">
+        <v>107</v>
       </c>
       <c r="T8">
-        <v>4357.167874996753</v>
+        <v>-0.9924318290308553</v>
       </c>
       <c r="U8">
-        <v>4187.870000000001</v>
-      </c>
-      <c r="V8">
-        <v>3994.820000000002</v>
-      </c>
-      <c r="W8">
-        <v>4149.548154052424</v>
+        <v>0.9965227220591538</v>
+      </c>
+      <c r="V8" t="s">
+        <v>94</v>
+      </c>
+      <c r="W8" t="s">
+        <v>96</v>
       </c>
       <c r="X8">
-        <v>4321.507500000001</v>
+        <v>0.999713595981076</v>
       </c>
       <c r="Y8">
-        <v>-0.009150677061985338</v>
+        <v>0.90541915369835</v>
       </c>
       <c r="Z8">
-        <v>0.2867596741002825</v>
+        <v>169.8551477164966</v>
       </c>
       <c r="AA8">
-        <v>0.009150677061985338</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB8">
-        <v>0.3204604250913957</v>
+        <v>-0.984365597748401</v>
       </c>
       <c r="AC8">
+        <v>0.1761373610834256</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH8">
+        <v>-0.9375459382447667</v>
+      </c>
+      <c r="AI8">
+        <v>0.9711683618887865</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.706882738923895</v>
+      </c>
+      <c r="AK8">
+        <v>0.2929514251590964</v>
+      </c>
+      <c r="AL8">
+        <v>-1.900573765259989</v>
+      </c>
+      <c r="AM8">
+        <v>4.175049137250193</v>
+      </c>
+      <c r="AN8">
+        <v>1.571541160648133</v>
+      </c>
+      <c r="AO8">
+        <v>0.03416604512520295</v>
+      </c>
+      <c r="AP8">
+        <v>1.32449</v>
+      </c>
+      <c r="AQ8">
+        <v>1.311274945915412</v>
+      </c>
+      <c r="AR8">
+        <v>1.306677175046762</v>
+      </c>
+      <c r="AS8">
+        <v>1.32449</v>
+      </c>
+      <c r="AT8">
+        <v>1.309935</v>
+      </c>
+      <c r="AU8">
+        <v>1.311274945915412</v>
+      </c>
+      <c r="AV8">
+        <v>1.33614</v>
+      </c>
+      <c r="AW8">
+        <v>-0.009977466107398577</v>
+      </c>
+      <c r="AX8">
+        <v>1.134339406402433</v>
+      </c>
+      <c r="AY8">
+        <v>0.009977466107398577</v>
+      </c>
+      <c r="AZ8">
+        <v>0.4822401777686388</v>
+      </c>
+      <c r="BA8">
         <v>0.2</v>
       </c>
-      <c r="AD8">
-        <v>0.4795395749086043</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF8">
+      <c r="BB8">
+        <v>0.3177598222313613</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD8">
         <v>100000</v>
       </c>
-      <c r="AG8">
+      <c r="BE8">
         <v>100</v>
       </c>
-      <c r="AH8">
-        <v>375</v>
-      </c>
-      <c r="AI8">
-        <v>0.03191061327118562</v>
-      </c>
-      <c r="AJ8">
-        <v>15668.76812272003</v>
-      </c>
-      <c r="AK8">
-        <v>11751.57609204002</v>
-      </c>
-      <c r="AL8">
-        <v>2.806098587597041</v>
-      </c>
-      <c r="AM8">
-        <v>117.5157609204002</v>
-      </c>
-      <c r="AN8">
-        <v>0.001175157609204002</v>
-      </c>
-      <c r="AO8">
-        <v>375</v>
-      </c>
-      <c r="AP8">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ8">
-        <v>669.8455655833625</v>
-      </c>
-      <c r="AR8">
-        <v>48.73869139606033</v>
-      </c>
-      <c r="AS8">
-        <v>135.4323623549431</v>
-      </c>
-      <c r="AT8">
+      <c r="BF8">
+        <v>500</v>
+      </c>
+      <c r="BG8">
+        <v>0.008795838398175897</v>
+      </c>
+      <c r="BH8">
+        <v>56845.06437768244</v>
+      </c>
+      <c r="BI8">
+        <v>56845.06437768244</v>
+      </c>
+      <c r="BJ8">
+        <v>42918.45493562234</v>
+      </c>
+      <c r="BK8">
+        <v>568.4506437768243</v>
+      </c>
+      <c r="BL8">
+        <v>0.005684506437768243</v>
+      </c>
+      <c r="BM8">
+        <v>500</v>
+      </c>
+      <c r="BN8">
+        <v>0.005</v>
+      </c>
+      <c r="BO8">
+        <v>0.01415551227168181</v>
+      </c>
+      <c r="BP8">
+        <v>0.004488111676903775</v>
+      </c>
+      <c r="BQ8">
+        <v>0.01445495062180422</v>
+      </c>
+      <c r="BR8">
         <v>1</v>
       </c>
-      <c r="AU8">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY8" s="2">
+      <c r="BS8">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW8" s="2">
         <v>46336</v>
       </c>
     </row>
-    <row r="9" spans="1:51">
+    <row r="9" spans="1:75">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2">
         <v>46308</v>
@@ -1887,22 +2589,22 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
         <v>46307</v>
@@ -1911,129 +2613,201 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>2.041404400373534</v>
+        <v>1.453416665520049</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
-      <c r="R9">
-        <v>1.32449</v>
-      </c>
-      <c r="S9">
-        <v>1.312073518266369</v>
+      <c r="R9" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" t="s">
+        <v>107</v>
       </c>
       <c r="T9">
-        <v>1.30844634116951</v>
+        <v>-0.9959638211245221</v>
       </c>
       <c r="U9">
-        <v>1.32449</v>
-      </c>
-      <c r="V9">
-        <v>1.309935</v>
-      </c>
-      <c r="W9">
-        <v>1.312073518266369</v>
+        <v>0.9979875156176221</v>
+      </c>
+      <c r="V9" t="s">
+        <v>94</v>
+      </c>
+      <c r="W9" t="s">
+        <v>96</v>
       </c>
       <c r="X9">
-        <v>1.33614</v>
+        <v>0.9992151844463486</v>
       </c>
       <c r="Y9">
-        <v>-0.009374537922997844</v>
+        <v>0.8752183312826824</v>
       </c>
       <c r="Z9">
-        <v>1.065792423487675</v>
+        <v>172.5542169613442</v>
       </c>
       <c r="AA9">
-        <v>0.009374537922997844</v>
+        <v>-24</v>
       </c>
       <c r="AB9">
-        <v>0.518911195641249</v>
+        <v>-0.9915679297775538</v>
       </c>
       <c r="AC9">
+        <v>0.1295879648603839</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH9">
+        <v>-0.9289735338000383</v>
+      </c>
+      <c r="AI9">
+        <v>0.9670733777173066</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.177251493368894</v>
+      </c>
+      <c r="AK9">
+        <v>0.09126587126114025</v>
+      </c>
+      <c r="AL9">
+        <v>-1.484966144868667</v>
+      </c>
+      <c r="AM9">
+        <v>2.679603106211793</v>
+      </c>
+      <c r="AN9">
+        <v>1.262755767512773</v>
+      </c>
+      <c r="AO9">
+        <v>0.03443988019145269</v>
+      </c>
+      <c r="AP9">
+        <v>4.65983</v>
+      </c>
+      <c r="AQ9">
+        <v>4.609798593081385</v>
+      </c>
+      <c r="AR9">
+        <v>4.625308468473888</v>
+      </c>
+      <c r="AS9">
+        <v>4.65983</v>
+      </c>
+      <c r="AT9">
+        <v>4.555260000000001</v>
+      </c>
+      <c r="AU9">
+        <v>4.609798593081385</v>
+      </c>
+      <c r="AV9">
+        <v>4.699630000000001</v>
+      </c>
+      <c r="AW9">
+        <v>-0.0107367450998461</v>
+      </c>
+      <c r="AX9">
+        <v>1.257070525593361</v>
+      </c>
+      <c r="AY9">
+        <v>0.0107367450998461</v>
+      </c>
+      <c r="AZ9">
+        <v>0.4800189613555726</v>
+      </c>
+      <c r="BA9">
         <v>0.2</v>
       </c>
-      <c r="AD9">
-        <v>0.2810888043587511</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF9">
+      <c r="BB9">
+        <v>0.3199810386444274</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD9">
         <v>100000</v>
       </c>
-      <c r="AG9">
+      <c r="BE9">
         <v>100</v>
       </c>
-      <c r="AH9">
+      <c r="BF9">
         <v>500</v>
       </c>
-      <c r="AI9">
-        <v>0.008795838398175897</v>
-      </c>
-      <c r="AJ9">
-        <v>56845.06437768244</v>
-      </c>
-      <c r="AK9">
-        <v>56845.06437768244</v>
-      </c>
-      <c r="AL9">
-        <v>42918.45493562234</v>
-      </c>
-      <c r="AM9">
-        <v>568.4506437768243</v>
-      </c>
-      <c r="AN9">
-        <v>0.005684506437768243</v>
-      </c>
-      <c r="AO9">
+      <c r="BG9">
+        <v>0.008541084116802556</v>
+      </c>
+      <c r="BH9">
+        <v>58540.57788944715</v>
+      </c>
+      <c r="BI9">
+        <v>58540.57788944715</v>
+      </c>
+      <c r="BJ9">
+        <v>12562.81407035174</v>
+      </c>
+      <c r="BK9">
+        <v>585.4057788944715</v>
+      </c>
+      <c r="BL9">
+        <v>0.005854057788944715</v>
+      </c>
+      <c r="BM9">
         <v>500</v>
       </c>
-      <c r="AP9">
+      <c r="BN9">
         <v>0.005</v>
       </c>
-      <c r="AQ9">
-        <v>0.01382335848228925</v>
-      </c>
-      <c r="AR9">
-        <v>0.0006845636959630745</v>
-      </c>
-      <c r="AS9">
-        <v>0.01628546092838712</v>
-      </c>
-      <c r="AT9">
+      <c r="BO9">
+        <v>0.0460661043105115</v>
+      </c>
+      <c r="BP9">
+        <v>0.04670446275357128</v>
+      </c>
+      <c r="BQ9">
+        <v>0.05381643765742006</v>
+      </c>
+      <c r="BR9">
         <v>1</v>
       </c>
-      <c r="AU9">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY9" s="2">
+      <c r="BS9">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW9" s="2">
         <v>46336</v>
       </c>
     </row>
-    <row r="10" spans="1:51">
+    <row r="10" spans="1:75">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2">
         <v>46308</v>
@@ -2042,22 +2816,22 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J10" s="2">
         <v>46307</v>
@@ -2066,129 +2840,201 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>1.453416665520049</v>
+        <v>1.567658745515618</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
-      <c r="R10">
-        <v>4.65983</v>
-      </c>
-      <c r="S10">
-        <v>4.604642269515173</v>
+      <c r="R10" t="s">
+        <v>103</v>
+      </c>
+      <c r="S10" t="s">
+        <v>107</v>
       </c>
       <c r="T10">
-        <v>4.635206666683556</v>
+        <v>-0.9942412435910051</v>
       </c>
       <c r="U10">
-        <v>4.65983</v>
-      </c>
-      <c r="V10">
-        <v>4.555260000000001</v>
-      </c>
-      <c r="W10">
-        <v>4.604642269515173</v>
+        <v>0.9973799764313247</v>
+      </c>
+      <c r="V10" t="s">
+        <v>94</v>
+      </c>
+      <c r="W10" t="s">
+        <v>96</v>
       </c>
       <c r="X10">
-        <v>4.699630000000001</v>
+        <v>0.9998856672614895</v>
       </c>
       <c r="Y10">
-        <v>-0.01184329267051102</v>
+        <v>1</v>
       </c>
       <c r="Z10">
-        <v>1.386626394091139</v>
+        <v>171.2954337196475</v>
       </c>
       <c r="AA10">
-        <v>0.01184329267051102</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB10">
-        <v>0.3560907627062877</v>
+        <v>-0.9884818286923324</v>
       </c>
       <c r="AC10">
+        <v>0.1513395993950775</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH10">
+        <v>-0.9883688128578901</v>
+      </c>
+      <c r="AI10">
+        <v>0.9913550170259099</v>
+      </c>
+      <c r="AJ10">
+        <v>-1.248061920355512</v>
+      </c>
+      <c r="AK10">
+        <v>0.1828314122820174</v>
+      </c>
+      <c r="AL10">
+        <v>-1.692333494607456</v>
+      </c>
+      <c r="AM10">
+        <v>2.431053080095155</v>
+      </c>
+      <c r="AN10">
+        <v>1.495044984487824</v>
+      </c>
+      <c r="AO10">
+        <v>0.03433010082207424</v>
+      </c>
+      <c r="AP10">
+        <v>8.84564</v>
+      </c>
+      <c r="AQ10">
+        <v>8.75007280567635</v>
+      </c>
+      <c r="AR10">
+        <v>8.726789021256661</v>
+      </c>
+      <c r="AS10">
+        <v>8.84564</v>
+      </c>
+      <c r="AT10">
+        <v>8.72547</v>
+      </c>
+      <c r="AU10">
+        <v>8.75007280567635</v>
+      </c>
+      <c r="AV10">
+        <v>8.909351462882432</v>
+      </c>
+      <c r="AW10">
+        <v>-0.01080387561823108</v>
+      </c>
+      <c r="AX10">
+        <v>1.5</v>
+      </c>
+      <c r="AY10">
+        <v>0.01080387561823108</v>
+      </c>
+      <c r="AZ10">
+        <v>0.4312331385701689</v>
+      </c>
+      <c r="BA10">
         <v>0.2</v>
       </c>
-      <c r="AD10">
-        <v>0.4439092372937124</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF10">
+      <c r="BB10">
+        <v>0.3687668614298311</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BD10">
         <v>100000</v>
       </c>
-      <c r="AG10">
+      <c r="BE10">
         <v>100</v>
       </c>
-      <c r="AH10">
+      <c r="BF10">
         <v>500</v>
       </c>
-      <c r="AI10">
-        <v>0.008541084116802556</v>
-      </c>
-      <c r="AJ10">
-        <v>58540.57788944715</v>
-      </c>
-      <c r="AK10">
-        <v>58540.57788944715</v>
-      </c>
-      <c r="AL10">
-        <v>12562.81407035174</v>
-      </c>
-      <c r="AM10">
-        <v>585.4057788944715</v>
-      </c>
-      <c r="AN10">
-        <v>0.005854057788944715</v>
-      </c>
-      <c r="AO10">
-        <v>500</v>
-      </c>
-      <c r="AP10">
-        <v>0.005</v>
-      </c>
-      <c r="AQ10">
-        <v>0.05206800674326861</v>
-      </c>
-      <c r="AR10">
-        <v>0.02198003339261078</v>
-      </c>
-      <c r="AS10">
-        <v>0.0675446033809948</v>
-      </c>
-      <c r="AT10">
+      <c r="BG10">
+        <v>0.007202583745487388</v>
+      </c>
+      <c r="BH10">
+        <v>69419.53299928841</v>
+      </c>
+      <c r="BI10">
+        <v>69419.53299928841</v>
+      </c>
+      <c r="BJ10">
+        <v>7847.881329026324</v>
+      </c>
+      <c r="BK10">
+        <v>694.1953299928841</v>
+      </c>
+      <c r="BL10">
+        <v>0.006941953299928841</v>
+      </c>
+      <c r="BM10">
+        <v>500.0000000000001</v>
+      </c>
+      <c r="BN10">
+        <v>0.005000000000000001</v>
+      </c>
+      <c r="BO10">
+        <v>0.09115442766913008</v>
+      </c>
+      <c r="BP10">
+        <v>0.04860495656929226</v>
+      </c>
+      <c r="BQ10">
+        <v>0.0562326961528193</v>
+      </c>
+      <c r="BR10">
         <v>1</v>
       </c>
-      <c r="AU10">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV10" t="s">
+      <c r="BS10">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW10" s="2">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:75">
+      <c r="A11" t="s">
         <v>84</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY10" s="2">
-        <v>46336</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51">
-      <c r="A11" t="s">
-        <v>60</v>
       </c>
       <c r="B11" s="2">
         <v>46308</v>
@@ -2197,147 +3043,219 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J11" s="2">
         <v>46307</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>3.413009816926103</v>
+        <v>1.415342175083034</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O11" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P11" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q11">
+        <v>0.75</v>
+      </c>
+      <c r="R11" t="s">
+        <v>103</v>
+      </c>
+      <c r="S11" t="s">
+        <v>107</v>
+      </c>
+      <c r="T11">
+        <v>-0.9895171659088532</v>
+      </c>
+      <c r="U11">
+        <v>0.8448780551072674</v>
+      </c>
+      <c r="V11" t="s">
+        <v>94</v>
+      </c>
+      <c r="W11" t="s">
+        <v>96</v>
+      </c>
+      <c r="X11">
+        <v>0.9983813217931343</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>165.7585179963324</v>
+      </c>
+      <c r="AA11">
+        <v>-43</v>
+      </c>
+      <c r="AB11">
+        <v>-0.9692674938874155</v>
+      </c>
+      <c r="AC11">
+        <v>0.2460091975784825</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH11">
+        <v>-0.4838492808592183</v>
+      </c>
+      <c r="AI11">
+        <v>0.7851395534657122</v>
+      </c>
+      <c r="AJ11">
+        <v>-1.185725123855359</v>
+      </c>
+      <c r="AK11">
+        <v>0.1838522971462773</v>
+      </c>
+      <c r="AL11">
+        <v>-1.271948999062554</v>
+      </c>
+      <c r="AM11">
+        <v>3.119219713132203</v>
+      </c>
+      <c r="AN11">
+        <v>1.020691304471279</v>
+      </c>
+      <c r="AO11">
+        <v>0.03382771552073009</v>
+      </c>
+      <c r="AP11">
+        <v>4187.870000000001</v>
+      </c>
+      <c r="AQ11">
+        <v>4025.421027431403</v>
+      </c>
+      <c r="AR11">
+        <v>3974.153283423017</v>
+      </c>
+      <c r="AS11">
+        <v>4187.870000000001</v>
+      </c>
+      <c r="AT11">
+        <v>3994.820000000002</v>
+      </c>
+      <c r="AU11">
+        <v>4025.421027431403</v>
+      </c>
+      <c r="AV11">
+        <v>4321.507500000001</v>
+      </c>
+      <c r="AW11">
+        <v>-0.0387903570475201</v>
+      </c>
+      <c r="AX11">
+        <v>1.215594219950222</v>
+      </c>
+      <c r="AY11">
+        <v>0.0387903570475201</v>
+      </c>
+      <c r="AZ11">
+        <v>0.3875299948477561</v>
+      </c>
+      <c r="BA11">
+        <v>0.2</v>
+      </c>
+      <c r="BB11">
+        <v>0.412470005152244</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>127</v>
+      </c>
+      <c r="BD11">
+        <v>100000</v>
+      </c>
+      <c r="BE11">
+        <v>100</v>
+      </c>
+      <c r="BF11">
+        <v>375</v>
+      </c>
+      <c r="BG11">
+        <v>0.03191061327118562</v>
+      </c>
+      <c r="BH11">
+        <v>15668.76812272003</v>
+      </c>
+      <c r="BI11">
+        <v>11751.57609204002</v>
+      </c>
+      <c r="BJ11">
+        <v>2.806098587597041</v>
+      </c>
+      <c r="BK11">
+        <v>117.5157609204002</v>
+      </c>
+      <c r="BL11">
+        <v>0.001175157609204002</v>
+      </c>
+      <c r="BM11">
+        <v>375</v>
+      </c>
+      <c r="BN11">
+        <v>0.00375</v>
+      </c>
+      <c r="BO11">
+        <v>462.9602023664124</v>
+      </c>
+      <c r="BP11">
+        <v>102.3236179351064</v>
+      </c>
+      <c r="BQ11">
+        <v>125.2673066148402</v>
+      </c>
+      <c r="BR11">
         <v>1</v>
       </c>
-      <c r="R11">
-        <v>1.118705</v>
-      </c>
-      <c r="S11">
-        <v>1.103216891160175</v>
-      </c>
-      <c r="T11">
-        <v>1.127094750137517</v>
-      </c>
-      <c r="U11">
-        <v>1.118705</v>
-      </c>
-      <c r="V11">
-        <v>1.088875</v>
-      </c>
-      <c r="W11">
-        <v>1.103216891160175</v>
-      </c>
-      <c r="X11">
-        <v>1.129065</v>
-      </c>
-      <c r="Y11">
-        <v>-0.01384467651420644</v>
-      </c>
-      <c r="Z11">
-        <v>1.494991200755335</v>
-      </c>
-      <c r="AA11">
-        <v>0.01384467651420644</v>
-      </c>
-      <c r="AB11">
-        <v>0.2930767622014101</v>
-      </c>
-      <c r="AC11">
-        <v>0.1052822842012881</v>
-      </c>
-      <c r="AD11">
-        <v>0.6016409535973019</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF11">
-        <v>100000</v>
-      </c>
-      <c r="AG11">
-        <v>100</v>
-      </c>
-      <c r="AH11">
-        <v>500</v>
-      </c>
-      <c r="AI11">
-        <v>0.009260707693270375</v>
-      </c>
-      <c r="AJ11">
-        <v>53991.55405405387</v>
-      </c>
-      <c r="AK11">
-        <v>53991.55405405387</v>
-      </c>
-      <c r="AL11">
-        <v>48262.54826254809</v>
-      </c>
-      <c r="AM11">
-        <v>539.9155405405387</v>
-      </c>
-      <c r="AN11">
-        <v>0.005399155405405387</v>
-      </c>
-      <c r="AO11">
-        <v>500</v>
-      </c>
-      <c r="AP11">
-        <v>0.005</v>
-      </c>
-      <c r="AQ11">
-        <v>0.01691199775050386</v>
-      </c>
-      <c r="AR11">
-        <v>0.006995167259153817</v>
-      </c>
-      <c r="AS11">
-        <v>0.01416620795662987</v>
-      </c>
-      <c r="AT11">
-        <v>1</v>
-      </c>
-      <c r="AU11">
-        <v>0.0615776811948929</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY11" s="2">
+      <c r="BS11">
+        <v>0.05665788953335721</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW11" s="2">
         <v>46336</v>
       </c>
     </row>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="122">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,78 @@
     <t>TerrainSizeMultiplier</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>EntryPrice</t>
   </si>
   <si>
@@ -169,6 +241,9 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
@@ -178,40 +253,37 @@
     <t>USDCHF</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>AUDUSD</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
-    <t>horizon_ensemble_terrain_v1</t>
-  </si>
-  <si>
-    <t>HIGH</t>
+    <t>fixed_origin_weekly_v2_20261015</t>
+  </si>
+  <si>
+    <t>LOW</t>
   </si>
   <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>LOW</t>
+    <t>FLAT</t>
   </si>
   <si>
     <t>LONG</t>
@@ -220,55 +292,91 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.52,naive=0.20,drift4=0.28); metric_best=naive; scores=model=2.692,naive=1.477,drift4=4.967; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.20,drift4=0.48); metric_best=drift4; scores=model=0.3431,naive=0.03496,drift4=0.02265; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05014,naive=0.005551,drift4=0.01739; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.52,naive=0.20,drift4=0.28); metric_best=naive; scores=model=0.01089,naive=7.368e-05,drift4=0.01679; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.53,naive=0.20,drift4=0.27); metric_best=naive; scores=model=0.09005,naive=0.04218,drift4=0.191; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.12,drift4=0.49); metric_best=drift4; scores=model=0.08757,naive=0.202,drift4=0.0299</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.53,naive=0.20,drift4=0.27); metric_best=naive; scores=model=0.01565,naive=0.004059,drift4=0.04102; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.141,naive=0.05682,drift4=0.05811; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.31,naive=0.12,drift4=0.57); metric_best=drift4; scores=model=0.03635,naive=0.0223,drift4=0.00261</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.28,naive=0.16,drift4=0.56); metric_best=drift4; scores=model=1861,naive=172.3,drift4=36.8</t>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=fixed_origin_weekly_v2_20261015; weights(model=0.55,naive=0.15,drift4=0.30); metric_best=insufficient_history</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -633,10 +741,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BW11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,1555 +898,2245 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:75">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0.1280705824382753</v>
+        <v>3.395165354385198</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="Q2">
-        <v>0.75</v>
-      </c>
-      <c r="R2">
-        <v>158.437</v>
-      </c>
-      <c r="S2">
-        <v>159.4530838762201</v>
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S2" t="s">
+        <v>103</v>
       </c>
       <c r="T2">
-        <v>159.5455232776606</v>
+        <v>-0.9766829969796371</v>
       </c>
       <c r="U2">
-        <v>158.437</v>
-      </c>
-      <c r="V2">
-        <v>160.004</v>
-      </c>
-      <c r="W2">
-        <v>159.4530838762201</v>
+        <v>0.989470875962453</v>
+      </c>
+      <c r="V2" t="s">
+        <v>92</v>
+      </c>
+      <c r="W2" t="s">
+        <v>94</v>
       </c>
       <c r="X2">
-        <v>156.938875</v>
+        <v>0.9998541092864648</v>
       </c>
       <c r="Y2">
-        <v>0.006413172909232563</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>0.6782370471222821</v>
+        <v>-162.4326069517044</v>
       </c>
       <c r="AA2">
-        <v>0.006413172909232563</v>
+        <v>-12</v>
       </c>
       <c r="AB2">
-        <v>0.5180549245073885</v>
+        <v>-0.9533625917287122</v>
       </c>
       <c r="AC2">
-        <v>0.2</v>
-      </c>
-      <c r="AD2">
-        <v>0.2819450754926115</v>
+        <v>-0.3018273822772097</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>92</v>
       </c>
       <c r="AE2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF2">
+        <v>107</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH2">
+        <v>-0.9532235049799471</v>
+      </c>
+      <c r="AI2">
+        <v>0.980174823462981</v>
+      </c>
+      <c r="AJ2">
+        <v>-2.669941367678096</v>
+      </c>
+      <c r="AK2">
+        <v>-0.9224748832514461</v>
+      </c>
+      <c r="AL2">
+        <v>-3.823959005266689</v>
+      </c>
+      <c r="AM2">
+        <v>5.345176519911814</v>
+      </c>
+      <c r="AN2">
+        <v>3.333493334301382</v>
+      </c>
+      <c r="AO2">
+        <v>0.03855261537263439</v>
+      </c>
+      <c r="AP2">
+        <v>1.11895</v>
+      </c>
+      <c r="AQ2">
+        <v>1.118757737712577</v>
+      </c>
+      <c r="AR2">
+        <v>1.140934068568321</v>
+      </c>
+      <c r="AS2">
+        <v>1.11895</v>
+      </c>
+      <c r="AT2">
+        <v>1.078005</v>
+      </c>
+      <c r="AW2">
+        <v>-0.0001718238414793387</v>
+      </c>
+      <c r="AY2">
+        <v>0.0001718238414793387</v>
+      </c>
+      <c r="AZ2">
+        <v>0.55</v>
+      </c>
+      <c r="BA2">
+        <v>0.15</v>
+      </c>
+      <c r="BB2">
+        <v>0.3</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD2">
         <v>100000</v>
       </c>
-      <c r="AG2">
+      <c r="BE2">
         <v>100</v>
       </c>
-      <c r="AH2">
-        <v>375</v>
-      </c>
-      <c r="AI2">
-        <v>0.009455651142094434</v>
-      </c>
-      <c r="AJ2">
-        <v>52878.43137254846</v>
-      </c>
-      <c r="AK2">
-        <v>39658.82352941135</v>
-      </c>
-      <c r="AL2">
-        <v>250.3128911138897</v>
-      </c>
-      <c r="AM2">
-        <v>396.5882352941135</v>
-      </c>
-      <c r="AN2">
-        <v>0.003965882352941135</v>
-      </c>
-      <c r="AO2">
-        <v>375</v>
-      </c>
-      <c r="AP2">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ2">
-        <v>2.072058053637502</v>
-      </c>
-      <c r="AR2">
-        <v>0.4096918972335535</v>
-      </c>
-      <c r="AS2">
-        <v>1.684793431304435</v>
-      </c>
-      <c r="AT2">
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BR2">
         <v>1</v>
       </c>
-      <c r="AU2">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY2" s="2">
-        <v>46337</v>
+      <c r="BS2">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>46338</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:75">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>2.070892633006796</v>
+        <v>0.06615792576073938</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="Q3">
+        <v>0.75</v>
+      </c>
+      <c r="R3" t="s">
+        <v>100</v>
+      </c>
+      <c r="S3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T3">
+        <v>0.7162025119611628</v>
+      </c>
+      <c r="U3">
+        <v>0.7222628639974663</v>
+      </c>
+      <c r="V3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X3">
+        <v>0.9998869344597723</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>80.28096206226725</v>
+      </c>
+      <c r="AA3">
+        <v>3.000000000000004</v>
+      </c>
+      <c r="AB3">
+        <v>0.1688168945785773</v>
+      </c>
+      <c r="AC3">
+        <v>0.9856474299184499</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH3">
+        <v>0.08439890360259611</v>
+      </c>
+      <c r="AI3">
+        <v>0.5355619450914663</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1757691715172014</v>
+      </c>
+      <c r="AK3">
+        <v>0.9810580982504591</v>
+      </c>
+      <c r="AL3">
+        <v>0.1037209690977838</v>
+      </c>
+      <c r="AM3">
+        <v>-0.641657935670563</v>
+      </c>
+      <c r="AN3">
+        <v>0.1500875380662124</v>
+      </c>
+      <c r="AO3">
+        <v>0.1002903356201814</v>
+      </c>
+      <c r="AP3">
+        <v>158.322</v>
+      </c>
+      <c r="AQ3">
+        <v>161.0738022194565</v>
+      </c>
+      <c r="AR3">
+        <v>160.7032767626481</v>
+      </c>
+      <c r="AS3">
+        <v>158.322</v>
+      </c>
+      <c r="AT3">
+        <v>163.129</v>
+      </c>
+      <c r="AU3">
+        <v>161.0738022194565</v>
+      </c>
+      <c r="AV3">
+        <v>156.487465187029</v>
+      </c>
+      <c r="AW3">
+        <v>0.01738104760839596</v>
+      </c>
+      <c r="AX3">
+        <v>1.5</v>
+      </c>
+      <c r="AY3">
+        <v>0.01738104760839596</v>
+      </c>
+      <c r="AZ3">
+        <v>0.55</v>
+      </c>
+      <c r="BA3">
+        <v>0.15</v>
+      </c>
+      <c r="BB3">
+        <v>0.3</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD3">
+        <v>100000</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>375</v>
+      </c>
+      <c r="BG3">
+        <v>0.01158736507226397</v>
+      </c>
+      <c r="BH3">
+        <v>43150.44851713717</v>
+      </c>
+      <c r="BI3">
+        <v>32362.83638785288</v>
+      </c>
+      <c r="BJ3">
+        <v>204.4114929564614</v>
+      </c>
+      <c r="BK3">
+        <v>323.6283638785288</v>
+      </c>
+      <c r="BL3">
+        <v>0.003236283638785288</v>
+      </c>
+      <c r="BM3">
+        <v>375</v>
+      </c>
+      <c r="BN3">
+        <v>0.00375</v>
+      </c>
+      <c r="BR3">
         <v>1</v>
       </c>
-      <c r="R3">
-        <v>6.69399</v>
-      </c>
-      <c r="S3">
-        <v>6.731289061000098</v>
-      </c>
-      <c r="T3">
-        <v>6.814482155952833</v>
-      </c>
-      <c r="U3">
-        <v>6.69399</v>
-      </c>
-      <c r="V3">
-        <v>6.691405</v>
-      </c>
-      <c r="W3">
-        <v>6.731289061000098</v>
-      </c>
-      <c r="X3">
-        <v>6.669123959333269</v>
-      </c>
-      <c r="Y3">
-        <v>0.005572022216958404</v>
-      </c>
-      <c r="Z3">
-        <v>1.5</v>
-      </c>
-      <c r="AA3">
-        <v>0.005572022216958404</v>
-      </c>
-      <c r="AB3">
-        <v>0.3198567654194415</v>
-      </c>
-      <c r="AC3">
-        <v>0.2</v>
-      </c>
-      <c r="AD3">
-        <v>0.4801432345805585</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF3">
-        <v>100000</v>
-      </c>
-      <c r="AG3">
-        <v>100</v>
-      </c>
-      <c r="AH3">
-        <v>500</v>
-      </c>
-      <c r="AI3">
-        <v>0.003714681477972269</v>
-      </c>
-      <c r="AJ3">
-        <v>134601.0426371562</v>
-      </c>
-      <c r="AK3">
-        <v>134601.0426371562</v>
-      </c>
-      <c r="AL3">
-        <v>20107.74480349631</v>
-      </c>
-      <c r="AM3">
-        <v>1346.010426371562</v>
-      </c>
-      <c r="AN3">
-        <v>0.01346010426371562</v>
-      </c>
-      <c r="AO3">
-        <v>500</v>
-      </c>
-      <c r="AP3">
-        <v>0.005</v>
-      </c>
-      <c r="AQ3">
-        <v>0.088991961479597</v>
-      </c>
-      <c r="AR3">
-        <v>0.009842667883956097</v>
-      </c>
-      <c r="AS3">
-        <v>0.00908522477719087</v>
-      </c>
-      <c r="AT3">
-        <v>1</v>
-      </c>
-      <c r="AU3">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY3" s="2">
-        <v>46337</v>
+      <c r="BS3">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW3" s="2">
+        <v>46338</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:75">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J4" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>2.525458690587854</v>
+        <v>1.772050083852844</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
-      <c r="R4">
-        <v>0.8331649999999999</v>
-      </c>
-      <c r="S4">
-        <v>0.834200638972781</v>
+      <c r="R4" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" t="s">
+        <v>103</v>
       </c>
       <c r="T4">
-        <v>0.8263206596913995</v>
+        <v>-0.9774719878463359</v>
       </c>
       <c r="U4">
-        <v>0.8331649999999999</v>
-      </c>
-      <c r="V4">
-        <v>0.8442199999999999</v>
-      </c>
-      <c r="W4">
-        <v>0.8344147474999999</v>
+        <v>0.8397681994766076</v>
+      </c>
+      <c r="V4" t="s">
+        <v>92</v>
+      </c>
+      <c r="W4" t="s">
+        <v>94</v>
       </c>
       <c r="X4">
-        <v>0.8260675</v>
+        <v>0.9996232197830258</v>
       </c>
       <c r="Y4">
-        <v>0.001243017856944336</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>0.17608277562522</v>
+        <v>-159.0685841963589</v>
       </c>
       <c r="AA4">
-        <v>0.001243017856944336</v>
+        <v>10</v>
       </c>
       <c r="AB4">
-        <v>0.4362373636455826</v>
+        <v>-0.9340087311689881</v>
       </c>
       <c r="AC4">
-        <v>0.2</v>
-      </c>
-      <c r="AD4">
-        <v>0.3637626363544175</v>
+        <v>-0.357250178586515</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>92</v>
       </c>
       <c r="AE4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF4">
+        <v>107</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH4">
+        <v>-0.4668284075783012</v>
+      </c>
+      <c r="AI4">
+        <v>0.7730708670312956</v>
+      </c>
+      <c r="AJ4">
+        <v>-1.245880694328789</v>
+      </c>
+      <c r="AK4">
+        <v>-0.4564362172145745</v>
+      </c>
+      <c r="AL4">
+        <v>-2.653729337996243</v>
+      </c>
+      <c r="AM4">
+        <v>0.7435308808855795</v>
+      </c>
+      <c r="AN4">
+        <v>2.553571094002639</v>
+      </c>
+      <c r="AO4">
+        <v>0.04666586162306566</v>
+      </c>
+      <c r="AP4">
+        <v>6.694155</v>
+      </c>
+      <c r="AQ4">
+        <v>6.743418562284115</v>
+      </c>
+      <c r="AR4">
+        <v>6.791181476880206</v>
+      </c>
+      <c r="AS4">
+        <v>6.694155</v>
+      </c>
+      <c r="AT4">
+        <v>6.680485000000001</v>
+      </c>
+      <c r="AU4">
+        <v>6.743418562284115</v>
+      </c>
+      <c r="AV4">
+        <v>6.661312625143924</v>
+      </c>
+      <c r="AW4">
+        <v>0.007359190560140035</v>
+      </c>
+      <c r="AX4">
+        <v>1.5</v>
+      </c>
+      <c r="AY4">
+        <v>0.007359190560140035</v>
+      </c>
+      <c r="AZ4">
+        <v>0.55</v>
+      </c>
+      <c r="BA4">
+        <v>0.15</v>
+      </c>
+      <c r="BB4">
+        <v>0.3</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD4">
         <v>100000</v>
       </c>
-      <c r="AG4">
+      <c r="BE4">
         <v>100</v>
       </c>
-      <c r="AH4">
+      <c r="BF4">
         <v>500</v>
       </c>
-      <c r="AI4">
-        <v>0.008518720781597891</v>
-      </c>
-      <c r="AJ4">
-        <v>58694.25854173999</v>
-      </c>
-      <c r="AK4">
-        <v>58694.25854173999</v>
-      </c>
-      <c r="AL4">
-        <v>70447.3406128918</v>
-      </c>
-      <c r="AM4">
-        <v>586.9425854173999</v>
-      </c>
-      <c r="AN4">
-        <v>0.005869425854173999</v>
-      </c>
-      <c r="AO4">
+      <c r="BG4">
+        <v>0.004906127040093356</v>
+      </c>
+      <c r="BH4">
+        <v>101913.3821676346</v>
+      </c>
+      <c r="BI4">
+        <v>101913.3821676346</v>
+      </c>
+      <c r="BJ4">
+        <v>15224.23400229522</v>
+      </c>
+      <c r="BK4">
+        <v>1019.133821676346</v>
+      </c>
+      <c r="BL4">
+        <v>0.01019133821676346</v>
+      </c>
+      <c r="BM4">
         <v>500</v>
       </c>
-      <c r="AP4">
+      <c r="BN4">
         <v>0.005</v>
       </c>
-      <c r="AQ4">
-        <v>0.01664434733056803</v>
-      </c>
-      <c r="AR4">
-        <v>0.002461803641238357</v>
-      </c>
-      <c r="AS4">
-        <v>0.007140993420804226</v>
-      </c>
-      <c r="AT4">
+      <c r="BR4">
         <v>1</v>
       </c>
-      <c r="AU4">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY4" s="2">
-        <v>46337</v>
+      <c r="BS4">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW4" s="2">
+        <v>46338</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:75">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K5">
-        <v>0.01556700568526159</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1.67003601429171</v>
+        <v>2.495726305891031</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q5">
-        <v>0.7538917514213154</v>
-      </c>
-      <c r="R5">
-        <v>0.7008799999999999</v>
-      </c>
-      <c r="S5">
-        <v>0.6997844735549901</v>
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>101</v>
+      </c>
+      <c r="S5" t="s">
+        <v>105</v>
       </c>
       <c r="T5">
-        <v>0.7051445862850889</v>
+        <v>0.9893909414873521</v>
       </c>
       <c r="U5">
-        <v>0.7008799999999999</v>
-      </c>
-      <c r="V5">
-        <v>0.6892049999999998</v>
-      </c>
-      <c r="W5">
-        <v>0.6997844735549901</v>
+        <v>0.9951752336444051</v>
+      </c>
+      <c r="V5" t="s">
+        <v>93</v>
+      </c>
+      <c r="W5" t="s">
+        <v>94</v>
       </c>
       <c r="X5">
-        <v>0.70630875</v>
+        <v>0.9997972399003866</v>
       </c>
       <c r="Y5">
-        <v>-0.001563072772813999</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>0.2018008648417891</v>
+        <v>-11.82453471546573</v>
       </c>
       <c r="AA5">
-        <v>0.001563072772813999</v>
+        <v>-5.999999999999996</v>
       </c>
       <c r="AB5">
-        <v>0.5172325935901235</v>
+        <v>0.9787797314446991</v>
       </c>
       <c r="AC5">
-        <v>0.2</v>
-      </c>
-      <c r="AD5">
-        <v>0.2827674064098765</v>
+        <v>-0.2049151954176232</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF5">
+        <v>108</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH5">
+        <v>0.9785812739688518</v>
+      </c>
+      <c r="AI5">
+        <v>0.9889795393949125</v>
+      </c>
+      <c r="AJ5">
+        <v>2.001710751052217</v>
+      </c>
+      <c r="AK5">
+        <v>-0.3920580590569097</v>
+      </c>
+      <c r="AL5">
+        <v>2.651466514246533</v>
+      </c>
+      <c r="AM5">
+        <v>-4.514083647108024</v>
+      </c>
+      <c r="AN5">
+        <v>2.276727884740602</v>
+      </c>
+      <c r="AO5">
+        <v>0.03055609335754993</v>
+      </c>
+      <c r="AP5">
+        <v>0.829295</v>
+      </c>
+      <c r="AQ5">
+        <v>0.8312985415704889</v>
+      </c>
+      <c r="AR5">
+        <v>0.8259287119463432</v>
+      </c>
+      <c r="AS5">
+        <v>0.829295</v>
+      </c>
+      <c r="AT5">
+        <v>0.842145</v>
+      </c>
+      <c r="AU5">
+        <v>0.8312985415704889</v>
+      </c>
+      <c r="AV5">
+        <v>0.82192375</v>
+      </c>
+      <c r="AW5">
+        <v>0.002415957615189861</v>
+      </c>
+      <c r="AX5">
+        <v>0.2718048594863642</v>
+      </c>
+      <c r="AY5">
+        <v>0.002415957615189861</v>
+      </c>
+      <c r="AZ5">
+        <v>0.55</v>
+      </c>
+      <c r="BA5">
+        <v>0.15</v>
+      </c>
+      <c r="BB5">
+        <v>0.3</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD5">
         <v>100000</v>
       </c>
-      <c r="AG5">
+      <c r="BE5">
         <v>100</v>
       </c>
-      <c r="AH5">
-        <v>376.9458757106577</v>
-      </c>
-      <c r="AI5">
-        <v>0.007745619792261251</v>
-      </c>
-      <c r="AJ5">
-        <v>64552.61340087419</v>
-      </c>
-      <c r="AK5">
-        <v>48665.68277560812</v>
-      </c>
-      <c r="AL5">
-        <v>69435.11410741942</v>
-      </c>
-      <c r="AM5">
-        <v>486.6568277560812</v>
-      </c>
-      <c r="AN5">
-        <v>0.004866568277560812</v>
-      </c>
-      <c r="AO5">
-        <v>376.9458757106577</v>
-      </c>
-      <c r="AP5">
-        <v>0.003769458757106577</v>
-      </c>
-      <c r="AQ5">
-        <v>0.008543992696761963</v>
-      </c>
-      <c r="AR5">
-        <v>0.002751065083187518</v>
-      </c>
-      <c r="AS5">
-        <v>0.01308547618213284</v>
-      </c>
-      <c r="AT5">
+      <c r="BF5">
+        <v>500</v>
+      </c>
+      <c r="BG5">
+        <v>0.008888574029748221</v>
+      </c>
+      <c r="BH5">
+        <v>56251.99253857855</v>
+      </c>
+      <c r="BI5">
+        <v>56251.99253857855</v>
+      </c>
+      <c r="BJ5">
+        <v>67831.1005596061</v>
+      </c>
+      <c r="BK5">
+        <v>562.5199253857854</v>
+      </c>
+      <c r="BL5">
+        <v>0.005625199253857854</v>
+      </c>
+      <c r="BM5">
+        <v>499.9999999999999</v>
+      </c>
+      <c r="BN5">
+        <v>0.004999999999999999</v>
+      </c>
+      <c r="BR5">
         <v>1</v>
       </c>
-      <c r="AU5">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY5" s="2">
-        <v>46337</v>
+      <c r="BS5">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW5" s="2">
+        <v>46338</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:75">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C6">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1.607245778193405</v>
+        <v>1.453657243820792</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q6">
+        <v>0.75</v>
+      </c>
+      <c r="R6" t="s">
+        <v>102</v>
+      </c>
+      <c r="S6" t="s">
+        <v>106</v>
+      </c>
+      <c r="T6">
+        <v>-0.9987753755745803</v>
+      </c>
+      <c r="U6">
+        <v>0.8489103186503497</v>
+      </c>
+      <c r="V6" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" t="s">
+        <v>94</v>
+      </c>
+      <c r="X6">
+        <v>0.9978455985671545</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>175.1425807481146</v>
+      </c>
+      <c r="AA6">
+        <v>-46.99999999999999</v>
+      </c>
+      <c r="AB6">
+        <v>-0.9964085006983606</v>
+      </c>
+      <c r="AC6">
+        <v>0.08467644144651515</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH6">
+        <v>-0.4971309183983783</v>
+      </c>
+      <c r="AI6">
+        <v>0.7932020759331244</v>
+      </c>
+      <c r="AJ6">
+        <v>-1.206425120164056</v>
+      </c>
+      <c r="AK6">
+        <v>-0.02690346497028458</v>
+      </c>
+      <c r="AL6">
+        <v>-1.36143194983145</v>
+      </c>
+      <c r="AM6">
+        <v>3.199793938222641</v>
+      </c>
+      <c r="AN6">
+        <v>1.089023131623034</v>
+      </c>
+      <c r="AO6">
+        <v>0.03310955849925291</v>
+      </c>
+      <c r="AP6">
+        <v>4195.629999999999</v>
+      </c>
+      <c r="AQ6">
+        <v>4177.32434515046</v>
+      </c>
+      <c r="AR6">
+        <v>4244.737900273565</v>
+      </c>
+      <c r="AS6">
+        <v>4195.629999999999</v>
+      </c>
+      <c r="AT6">
+        <v>4044.579999999998</v>
+      </c>
+      <c r="AU6">
+        <v>4177.32434515046</v>
+      </c>
+      <c r="AV6">
+        <v>4329.267499999999</v>
+      </c>
+      <c r="AW6">
+        <v>-0.004363028877555641</v>
+      </c>
+      <c r="AX6">
+        <v>0.1369799259155458</v>
+      </c>
+      <c r="AY6">
+        <v>0.004363028877555641</v>
+      </c>
+      <c r="AZ6">
+        <v>0.55</v>
+      </c>
+      <c r="BA6">
+        <v>0.15</v>
+      </c>
+      <c r="BB6">
+        <v>0.3</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD6">
+        <v>100000</v>
+      </c>
+      <c r="BE6">
+        <v>100</v>
+      </c>
+      <c r="BF6">
+        <v>375</v>
+      </c>
+      <c r="BG6">
+        <v>0.03185159320531129</v>
+      </c>
+      <c r="BH6">
+        <v>15697.80188943969</v>
+      </c>
+      <c r="BI6">
+        <v>11773.35141707977</v>
+      </c>
+      <c r="BJ6">
+        <v>2.806098587597041</v>
+      </c>
+      <c r="BK6">
+        <v>117.7335141707977</v>
+      </c>
+      <c r="BL6">
+        <v>0.001177335141707977</v>
+      </c>
+      <c r="BM6">
+        <v>375</v>
+      </c>
+      <c r="BN6">
+        <v>0.00375</v>
+      </c>
+      <c r="BR6">
         <v>1</v>
       </c>
-      <c r="R6">
-        <v>8.873900000000001</v>
-      </c>
-      <c r="S6">
-        <v>8.816217224749744</v>
-      </c>
-      <c r="T6">
-        <v>8.812109740130886</v>
-      </c>
-      <c r="U6">
-        <v>8.873900000000001</v>
-      </c>
-      <c r="V6">
-        <v>8.781990000000002</v>
-      </c>
-      <c r="W6">
-        <v>8.816217224749744</v>
-      </c>
-      <c r="X6">
-        <v>8.9300125</v>
-      </c>
-      <c r="Y6">
-        <v>-0.006500273301508543</v>
-      </c>
-      <c r="Z6">
-        <v>1.027984410786506</v>
-      </c>
-      <c r="AA6">
-        <v>0.006500273301508543</v>
-      </c>
-      <c r="AB6">
-        <v>0.5260744176704831</v>
-      </c>
-      <c r="AC6">
-        <v>0.2</v>
-      </c>
-      <c r="AD6">
-        <v>0.2739255823295169</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF6">
-        <v>100000</v>
-      </c>
-      <c r="AG6">
-        <v>100</v>
-      </c>
-      <c r="AH6">
-        <v>500</v>
-      </c>
-      <c r="AI6">
-        <v>0.006323318946573535</v>
-      </c>
-      <c r="AJ6">
-        <v>79072.39919804121</v>
-      </c>
-      <c r="AK6">
-        <v>79072.39919804121</v>
-      </c>
-      <c r="AL6">
-        <v>8910.670527957403</v>
-      </c>
-      <c r="AM6">
-        <v>790.7239919804121</v>
-      </c>
-      <c r="AN6">
-        <v>0.00790723991980412</v>
-      </c>
-      <c r="AO6">
-        <v>500</v>
-      </c>
-      <c r="AP6">
-        <v>0.005</v>
-      </c>
-      <c r="AQ6">
-        <v>0.1092038757217041</v>
-      </c>
-      <c r="AR6">
-        <v>0.01470764792109314</v>
-      </c>
-      <c r="AS6">
-        <v>0.09646455827994289</v>
-      </c>
-      <c r="AT6">
-        <v>1</v>
-      </c>
-      <c r="AU6">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>46337</v>
+      <c r="BS6">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW6" s="2">
+        <v>46338</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:75">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J7" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>3.12955570067431</v>
+        <v>1.409466085787301</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
-      <c r="R7">
-        <v>7.4933</v>
-      </c>
-      <c r="S7">
-        <v>7.437393777286564</v>
+      <c r="R7" t="s">
+        <v>102</v>
+      </c>
+      <c r="S7" t="s">
+        <v>106</v>
       </c>
       <c r="T7">
-        <v>7.593146340562244</v>
+        <v>-0.9936108756894084</v>
       </c>
       <c r="U7">
-        <v>7.4933</v>
-      </c>
-      <c r="V7">
-        <v>7.298099999999999</v>
-      </c>
-      <c r="W7">
-        <v>7.437393777286564</v>
+        <v>0.996791477885986</v>
+      </c>
+      <c r="V7" t="s">
+        <v>92</v>
+      </c>
+      <c r="W7" t="s">
+        <v>94</v>
       </c>
       <c r="X7">
-        <v>7.5441</v>
+        <v>0.9986663353030091</v>
       </c>
       <c r="Y7">
-        <v>-0.007460828034835851</v>
+        <v>0.8524073679593994</v>
       </c>
       <c r="Z7">
-        <v>1.100516195146354</v>
+        <v>170.5867373744173</v>
       </c>
       <c r="AA7">
-        <v>0.007460828034835851</v>
+        <v>-39</v>
       </c>
       <c r="AB7">
-        <v>0.3896155336100223</v>
+        <v>-0.9865343290569012</v>
       </c>
       <c r="AC7">
-        <v>0.1246882165405836</v>
-      </c>
-      <c r="AD7">
-        <v>0.4856962498493941</v>
+        <v>0.1635543261190295</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>92</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF7">
+        <v>107</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH7">
+        <v>-0.9125131181941951</v>
+      </c>
+      <c r="AI7">
+        <v>0.9609889996655083</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.150576665151099</v>
+      </c>
+      <c r="AK7">
+        <v>0.09271125474085967</v>
+      </c>
+      <c r="AL7">
+        <v>-1.407305197902939</v>
+      </c>
+      <c r="AM7">
+        <v>2.887102683106255</v>
+      </c>
+      <c r="AN7">
+        <v>1.160703551299741</v>
+      </c>
+      <c r="AO7">
+        <v>0.03323993332996663</v>
+      </c>
+      <c r="AP7">
+        <v>4.67727</v>
+      </c>
+      <c r="AQ7">
+        <v>4.641780597968038</v>
+      </c>
+      <c r="AR7">
+        <v>4.683860178123705</v>
+      </c>
+      <c r="AS7">
+        <v>4.67727</v>
+      </c>
+      <c r="AT7">
+        <v>4.54689</v>
+      </c>
+      <c r="AU7">
+        <v>4.641780597968038</v>
+      </c>
+      <c r="AV7">
+        <v>4.719915</v>
+      </c>
+      <c r="AW7">
+        <v>-0.007587631680865463</v>
+      </c>
+      <c r="AX7">
+        <v>0.8322054644615211</v>
+      </c>
+      <c r="AY7">
+        <v>0.007587631680865463</v>
+      </c>
+      <c r="AZ7">
+        <v>0.55</v>
+      </c>
+      <c r="BA7">
+        <v>0.15</v>
+      </c>
+      <c r="BB7">
+        <v>0.3</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD7">
         <v>100000</v>
       </c>
-      <c r="AG7">
+      <c r="BE7">
         <v>100</v>
       </c>
-      <c r="AH7">
+      <c r="BF7">
         <v>500</v>
       </c>
-      <c r="AI7">
-        <v>0.006779389588032059</v>
-      </c>
-      <c r="AJ7">
-        <v>73752.9527559046</v>
-      </c>
-      <c r="AK7">
-        <v>73752.9527559046</v>
-      </c>
-      <c r="AL7">
-        <v>9842.519685039248</v>
-      </c>
-      <c r="AM7">
-        <v>737.529527559046</v>
-      </c>
-      <c r="AN7">
-        <v>0.00737529527559046</v>
-      </c>
-      <c r="AO7">
+      <c r="BG7">
+        <v>0.009117498027695653</v>
+      </c>
+      <c r="BH7">
+        <v>54839.60604994718</v>
+      </c>
+      <c r="BI7">
+        <v>54839.60604994718</v>
+      </c>
+      <c r="BJ7">
+        <v>11724.70395122522</v>
+      </c>
+      <c r="BK7">
+        <v>548.3960604994718</v>
+      </c>
+      <c r="BL7">
+        <v>0.005483960604994718</v>
+      </c>
+      <c r="BM7">
         <v>500</v>
       </c>
-      <c r="AP7">
+      <c r="BN7">
         <v>0.005</v>
       </c>
-      <c r="AQ7">
-        <v>0.08681319210067268</v>
-      </c>
-      <c r="AR7">
-        <v>0.05252956601731581</v>
-      </c>
-      <c r="AS7">
-        <v>0.09895081418892179</v>
-      </c>
-      <c r="AT7">
+      <c r="BR7">
         <v>1</v>
       </c>
-      <c r="AU7">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY7" s="2">
-        <v>46337</v>
+      <c r="BS7">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW7" s="2">
+        <v>46338</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:75">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J8" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K8">
-        <v>0.9423515466031241</v>
+        <v>0.249996583801431</v>
       </c>
       <c r="L8">
-        <v>1.942504454543852</v>
+        <v>1.877381592236885</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="O8" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q8">
-        <v>0.985587886650781</v>
-      </c>
-      <c r="R8">
-        <v>1.32665</v>
-      </c>
-      <c r="S8">
-        <v>1.314093346687467</v>
+        <v>0.8124991459503578</v>
+      </c>
+      <c r="R8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S8" t="s">
+        <v>106</v>
       </c>
       <c r="T8">
-        <v>1.309293132687539</v>
+        <v>-0.992675505904978</v>
       </c>
       <c r="U8">
-        <v>1.32665</v>
-      </c>
-      <c r="V8">
-        <v>1.314255</v>
-      </c>
-      <c r="W8">
-        <v>1.314093346687467</v>
+        <v>0.8837936080072615</v>
+      </c>
+      <c r="V8" t="s">
+        <v>92</v>
+      </c>
+      <c r="W8" t="s">
+        <v>94</v>
       </c>
       <c r="X8">
-        <v>1.3383</v>
+        <v>0.998360571119227</v>
       </c>
       <c r="Y8">
-        <v>-0.009464932960866238</v>
+        <v>0.302875974097834</v>
       </c>
       <c r="Z8">
-        <v>1.077824318672378</v>
+        <v>169.2744964234522</v>
       </c>
       <c r="AA8">
-        <v>0.009464932960866238</v>
+        <v>-44</v>
       </c>
       <c r="AB8">
-        <v>0.5321894251185421</v>
+        <v>-0.9825300550219199</v>
       </c>
       <c r="AC8">
-        <v>0.2</v>
-      </c>
-      <c r="AD8">
-        <v>0.267810574881458</v>
+        <v>0.1861039789435543</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>92</v>
       </c>
       <c r="AE8" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF8">
+        <v>107</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH8">
+        <v>-0.6390080726695654</v>
+      </c>
+      <c r="AI8">
+        <v>0.8495928345362319</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.571999080587123</v>
+      </c>
+      <c r="AK8">
+        <v>0.1388823164316986</v>
+      </c>
+      <c r="AL8">
+        <v>-1.696045041873733</v>
+      </c>
+      <c r="AM8">
+        <v>4.329319079501524</v>
+      </c>
+      <c r="AN8">
+        <v>1.334531895020916</v>
+      </c>
+      <c r="AO8">
+        <v>0.03445051121093546</v>
+      </c>
+      <c r="AP8">
+        <v>0.697225</v>
+      </c>
+      <c r="AQ8">
+        <v>0.6918618809822571</v>
+      </c>
+      <c r="AR8">
+        <v>0.6979056926950129</v>
+      </c>
+      <c r="AS8">
+        <v>0.697225</v>
+      </c>
+      <c r="AT8">
+        <v>0.6780999999999999</v>
+      </c>
+      <c r="AU8">
+        <v>0.6918618809822571</v>
+      </c>
+      <c r="AV8">
+        <v>0.703025</v>
+      </c>
+      <c r="AW8">
+        <v>-0.007692092248188017</v>
+      </c>
+      <c r="AX8">
+        <v>0.9246756927142871</v>
+      </c>
+      <c r="AY8">
+        <v>0.007692092248188017</v>
+      </c>
+      <c r="AZ8">
+        <v>0.55</v>
+      </c>
+      <c r="BA8">
+        <v>0.15</v>
+      </c>
+      <c r="BB8">
+        <v>0.3</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD8">
         <v>100000</v>
       </c>
-      <c r="AG8">
+      <c r="BE8">
         <v>100</v>
       </c>
-      <c r="AH8">
-        <v>492.7939433253905</v>
-      </c>
-      <c r="AI8">
-        <v>0.00878151735574567</v>
-      </c>
-      <c r="AJ8">
-        <v>56937.76824034338</v>
-      </c>
-      <c r="AK8">
-        <v>56117.17467061199</v>
-      </c>
-      <c r="AL8">
-        <v>42299.9092983168</v>
-      </c>
-      <c r="AM8">
-        <v>561.1717467061198</v>
-      </c>
-      <c r="AN8">
-        <v>0.005611717467061198</v>
-      </c>
-      <c r="AO8">
-        <v>492.7939433253904</v>
-      </c>
-      <c r="AP8">
-        <v>0.004927939433253904</v>
-      </c>
-      <c r="AQ8">
-        <v>0.01297327426009851</v>
-      </c>
-      <c r="AR8">
-        <v>0.0019260058888834</v>
-      </c>
-      <c r="AS8">
-        <v>0.01679619077236926</v>
-      </c>
-      <c r="AT8">
+      <c r="BF8">
+        <v>406.2495729751789</v>
+      </c>
+      <c r="BG8">
+        <v>0.008318691957402599</v>
+      </c>
+      <c r="BH8">
+        <v>60105.60344827558</v>
+      </c>
+      <c r="BI8">
+        <v>48835.75146855479</v>
+      </c>
+      <c r="BJ8">
+        <v>70043.02982330638</v>
+      </c>
+      <c r="BK8">
+        <v>488.3575146855479</v>
+      </c>
+      <c r="BL8">
+        <v>0.004883575146855479</v>
+      </c>
+      <c r="BM8">
+        <v>406.2495729751789</v>
+      </c>
+      <c r="BN8">
+        <v>0.00406249572975179</v>
+      </c>
+      <c r="BR8">
         <v>1</v>
       </c>
-      <c r="AU8">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY8" s="2">
-        <v>46337</v>
+      <c r="BS8">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW8" s="2">
+        <v>46338</v>
       </c>
     </row>
-    <row r="9" spans="1:51">
+    <row r="9" spans="1:75">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J9" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1.514216501539898</v>
+        <v>2.055793720422582</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
-      <c r="R9">
-        <v>4.67508</v>
-      </c>
-      <c r="S9">
-        <v>4.629696031168616</v>
+      <c r="R9" t="s">
+        <v>102</v>
+      </c>
+      <c r="S9" t="s">
+        <v>106</v>
       </c>
       <c r="T9">
-        <v>4.650551491528174</v>
+        <v>-0.987873502193279</v>
       </c>
       <c r="U9">
-        <v>4.67508</v>
-      </c>
-      <c r="V9">
-        <v>4.585760000000001</v>
-      </c>
-      <c r="W9">
-        <v>4.629696031168616</v>
+        <v>0.9944785455584353</v>
+      </c>
+      <c r="V9" t="s">
+        <v>92</v>
+      </c>
+      <c r="W9" t="s">
+        <v>94</v>
       </c>
       <c r="X9">
-        <v>4.714880000000001</v>
+        <v>0.9997418782858389</v>
       </c>
       <c r="Y9">
-        <v>-0.00970763469959534</v>
+        <v>0.909492657910695</v>
       </c>
       <c r="Z9">
-        <v>1.140300724406636</v>
+        <v>167.1577415465099</v>
       </c>
       <c r="AA9">
-        <v>0.00970763469959534</v>
+        <v>-11</v>
       </c>
       <c r="AB9">
-        <v>0.4023989964373353</v>
+        <v>-0.9749856861839791</v>
       </c>
       <c r="AC9">
-        <v>0.2</v>
-      </c>
-      <c r="AD9">
-        <v>0.3976010035626648</v>
+        <v>0.2222676578730147</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>92</v>
       </c>
       <c r="AE9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF9">
+        <v>107</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH9">
+        <v>-0.9306237284556287</v>
+      </c>
+      <c r="AI9">
+        <v>0.969103005779609</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.692389824687916</v>
+      </c>
+      <c r="AK9">
+        <v>0.3413676704089463</v>
+      </c>
+      <c r="AL9">
+        <v>-1.971374147575125</v>
+      </c>
+      <c r="AM9">
+        <v>3.946461092591154</v>
+      </c>
+      <c r="AN9">
+        <v>1.657084790809492</v>
+      </c>
+      <c r="AO9">
+        <v>0.03467259371844893</v>
+      </c>
+      <c r="AP9">
+        <v>1.32324</v>
+      </c>
+      <c r="AQ9">
+        <v>1.312828815943879</v>
+      </c>
+      <c r="AR9">
+        <v>1.320322392625234</v>
+      </c>
+      <c r="AS9">
+        <v>1.32324</v>
+      </c>
+      <c r="AT9">
+        <v>1.293885</v>
+      </c>
+      <c r="AU9">
+        <v>1.312828815943879</v>
+      </c>
+      <c r="AV9">
+        <v>1.33489</v>
+      </c>
+      <c r="AW9">
+        <v>-0.007867948411566612</v>
+      </c>
+      <c r="AX9">
+        <v>0.8936638674782325</v>
+      </c>
+      <c r="AY9">
+        <v>0.007867948411566612</v>
+      </c>
+      <c r="AZ9">
+        <v>0.55</v>
+      </c>
+      <c r="BA9">
+        <v>0.15</v>
+      </c>
+      <c r="BB9">
+        <v>0.3</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD9">
         <v>100000</v>
       </c>
-      <c r="AG9">
+      <c r="BE9">
         <v>100</v>
       </c>
-      <c r="AH9">
+      <c r="BF9">
         <v>500</v>
       </c>
-      <c r="AI9">
-        <v>0.008513223303130653</v>
-      </c>
-      <c r="AJ9">
-        <v>58732.16080402002</v>
-      </c>
-      <c r="AK9">
-        <v>58732.16080402002</v>
-      </c>
-      <c r="AL9">
-        <v>12562.81407035174</v>
-      </c>
-      <c r="AM9">
-        <v>587.3216080402002</v>
-      </c>
-      <c r="AN9">
-        <v>0.005873216080402002</v>
-      </c>
-      <c r="AO9">
+      <c r="BG9">
+        <v>0.008804147395786097</v>
+      </c>
+      <c r="BH9">
+        <v>56791.4163090129</v>
+      </c>
+      <c r="BI9">
+        <v>56791.4163090129</v>
+      </c>
+      <c r="BJ9">
+        <v>42918.45493562234</v>
+      </c>
+      <c r="BK9">
+        <v>567.914163090129</v>
+      </c>
+      <c r="BL9">
+        <v>0.00567914163090129</v>
+      </c>
+      <c r="BM9">
         <v>500</v>
       </c>
-      <c r="AP9">
+      <c r="BN9">
         <v>0.005</v>
       </c>
-      <c r="AQ9">
-        <v>0.04611450407618726</v>
-      </c>
-      <c r="AR9">
-        <v>0.01696896240155651</v>
-      </c>
-      <c r="AS9">
-        <v>0.07506228490231315</v>
-      </c>
-      <c r="AT9">
+      <c r="BR9">
         <v>1</v>
       </c>
-      <c r="AU9">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY9" s="2">
-        <v>46337</v>
+      <c r="BS9">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW9" s="2">
+        <v>46338</v>
       </c>
     </row>
-    <row r="10" spans="1:51">
+    <row r="10" spans="1:75">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J10" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
-        <v>3.483974962867336</v>
+        <v>1.504100250601936</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
-      <c r="R10">
-        <v>1.11961</v>
-      </c>
-      <c r="S10">
-        <v>1.105728199528193</v>
+      <c r="R10" t="s">
+        <v>102</v>
+      </c>
+      <c r="S10" t="s">
+        <v>106</v>
       </c>
       <c r="T10">
-        <v>1.128200587177537</v>
+        <v>-0.9944317966357554</v>
       </c>
       <c r="U10">
-        <v>1.11961</v>
-      </c>
-      <c r="V10">
-        <v>1.090685</v>
-      </c>
-      <c r="W10">
-        <v>1.105728199528193</v>
+        <v>0.9974555167659012</v>
+      </c>
+      <c r="V10" t="s">
+        <v>92</v>
+      </c>
+      <c r="W10" t="s">
+        <v>94</v>
       </c>
       <c r="X10">
-        <v>1.12997</v>
+        <v>0.999844833119245</v>
       </c>
       <c r="Y10">
-        <v>-0.01239878214003704</v>
+        <v>1</v>
       </c>
       <c r="Z10">
-        <v>1.339942130483284</v>
+        <v>171.4408444705665</v>
       </c>
       <c r="AA10">
-        <v>0.01239878214003704</v>
+        <v>-6.999999999999997</v>
       </c>
       <c r="AB10">
-        <v>0.3052010703032794</v>
+        <v>-0.9888627291366784</v>
       </c>
       <c r="AC10">
-        <v>0.1242317085065818</v>
-      </c>
-      <c r="AD10">
-        <v>0.5705672211901388</v>
+        <v>0.1488304502592137</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>92</v>
       </c>
       <c r="AE10" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF10">
+        <v>107</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH10">
+        <v>-0.9887092903915033</v>
+      </c>
+      <c r="AI10">
+        <v>0.9915682451923054</v>
+      </c>
+      <c r="AJ10">
+        <v>-1.206847608800289</v>
+      </c>
+      <c r="AK10">
+        <v>0.1628464539605917</v>
+      </c>
+      <c r="AL10">
+        <v>-1.585084138197813</v>
+      </c>
+      <c r="AM10">
+        <v>2.523731344160301</v>
+      </c>
+      <c r="AN10">
+        <v>1.37968017748996</v>
+      </c>
+      <c r="AO10">
+        <v>0.03357510093622675</v>
+      </c>
+      <c r="AP10">
+        <v>8.861319999999999</v>
+      </c>
+      <c r="AQ10">
+        <v>8.78375050864409</v>
+      </c>
+      <c r="AR10">
+        <v>8.832288197534709</v>
+      </c>
+      <c r="AS10">
+        <v>8.861319999999999</v>
+      </c>
+      <c r="AT10">
+        <v>8.655979999999998</v>
+      </c>
+      <c r="AU10">
+        <v>8.78375050864409</v>
+      </c>
+      <c r="AV10">
+        <v>8.917432499999999</v>
+      </c>
+      <c r="AW10">
+        <v>-0.008753717432155627</v>
+      </c>
+      <c r="AX10">
+        <v>1.382392360987495</v>
+      </c>
+      <c r="AY10">
+        <v>0.008753717432155627</v>
+      </c>
+      <c r="AZ10">
+        <v>0.55</v>
+      </c>
+      <c r="BA10">
+        <v>0.15</v>
+      </c>
+      <c r="BB10">
+        <v>0.3</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD10">
         <v>100000</v>
       </c>
-      <c r="AG10">
+      <c r="BE10">
         <v>100</v>
       </c>
-      <c r="AH10">
+      <c r="BF10">
         <v>500</v>
       </c>
-      <c r="AI10">
-        <v>0.009253222104125576</v>
-      </c>
-      <c r="AJ10">
-        <v>54035.23166023147</v>
-      </c>
-      <c r="AK10">
-        <v>54035.23166023147</v>
-      </c>
-      <c r="AL10">
-        <v>48262.54826254809</v>
-      </c>
-      <c r="AM10">
-        <v>540.3523166023147</v>
-      </c>
-      <c r="AN10">
-        <v>0.005403523166023147</v>
-      </c>
-      <c r="AO10">
-        <v>500</v>
-      </c>
-      <c r="AP10">
-        <v>0.005</v>
-      </c>
-      <c r="AQ10">
-        <v>0.01701517445751234</v>
-      </c>
-      <c r="AR10">
-        <v>0.006119591737185486</v>
-      </c>
-      <c r="AS10">
-        <v>0.01518666195523304</v>
-      </c>
-      <c r="AT10">
+      <c r="BG10">
+        <v>0.006332295865627119</v>
+      </c>
+      <c r="BH10">
+        <v>78960.30296279948</v>
+      </c>
+      <c r="BI10">
+        <v>78960.30296279948</v>
+      </c>
+      <c r="BJ10">
+        <v>8910.670527957403</v>
+      </c>
+      <c r="BK10">
+        <v>789.6030296279948</v>
+      </c>
+      <c r="BL10">
+        <v>0.007896030296279949</v>
+      </c>
+      <c r="BM10">
+        <v>499.9999999999999</v>
+      </c>
+      <c r="BN10">
+        <v>0.004999999999999999</v>
+      </c>
+      <c r="BR10">
         <v>1</v>
       </c>
-      <c r="AU10">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV10" t="s">
+      <c r="BS10">
+        <v>0.04986901509516638</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>119</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>121</v>
+      </c>
+      <c r="BW10" s="2">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:75">
+      <c r="A11" t="s">
         <v>84</v>
       </c>
-      <c r="AW10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY10" s="2">
-        <v>46337</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51">
-      <c r="A11" t="s">
-        <v>60</v>
-      </c>
       <c r="B11" s="2">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J11" s="2">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>1.523816910000768</v>
+        <v>3.061238907503078</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O11" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P11" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="Q11">
-        <v>0.75</v>
-      </c>
-      <c r="R11">
-        <v>4144.6</v>
-      </c>
-      <c r="S11">
-        <v>4041.47587186302</v>
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>99</v>
+      </c>
+      <c r="S11" t="s">
+        <v>103</v>
       </c>
       <c r="T11">
-        <v>4243.983191151621</v>
+        <v>-0.9746198314191159</v>
       </c>
       <c r="U11">
-        <v>4144.6</v>
-      </c>
-      <c r="V11">
-        <v>3908.280000000001</v>
-      </c>
-      <c r="W11">
-        <v>4041.47587186302</v>
+        <v>0.9885556652336881</v>
+      </c>
+      <c r="V11" t="s">
+        <v>92</v>
+      </c>
+      <c r="W11" t="s">
+        <v>94</v>
       </c>
       <c r="X11">
-        <v>4278.2375</v>
+        <v>0.9999069643803437</v>
       </c>
       <c r="Y11">
-        <v>-0.02488156351324139</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <v>0.7716705874996177</v>
+        <v>-161.6656935826206</v>
       </c>
       <c r="AA11">
-        <v>0.02488156351324139</v>
+        <v>-10</v>
       </c>
       <c r="AB11">
-        <v>0.2830183723616791</v>
+        <v>-0.9492373013588192</v>
       </c>
       <c r="AC11">
-        <v>0.1615847203227206</v>
-      </c>
-      <c r="AD11">
-        <v>0.5553969073156004</v>
+        <v>-0.3145608775881486</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>92</v>
       </c>
       <c r="AE11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF11">
+        <v>107</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>109</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH11">
+        <v>-0.9491489884782864</v>
+      </c>
+      <c r="AI11">
+        <v>0.9789578689314791</v>
+      </c>
+      <c r="AJ11">
+        <v>-2.377430401374961</v>
+      </c>
+      <c r="AK11">
+        <v>-0.8435569835128667</v>
+      </c>
+      <c r="AL11">
+        <v>-3.583344725562733</v>
+      </c>
+      <c r="AM11">
+        <v>4.438944894702015</v>
+      </c>
+      <c r="AN11">
+        <v>3.170392461621871</v>
+      </c>
+      <c r="AO11">
+        <v>0.03853839339524651</v>
+      </c>
+      <c r="AP11">
+        <v>7.4965</v>
+      </c>
+      <c r="AQ11">
+        <v>7.397795193243351</v>
+      </c>
+      <c r="AR11">
+        <v>7.471073078624273</v>
+      </c>
+      <c r="AS11">
+        <v>7.4965</v>
+      </c>
+      <c r="AT11">
+        <v>7.2141</v>
+      </c>
+      <c r="AU11">
+        <v>7.397795193243351</v>
+      </c>
+      <c r="AV11">
+        <v>7.562303204504433</v>
+      </c>
+      <c r="AW11">
+        <v>-0.01316678540074029</v>
+      </c>
+      <c r="AX11">
+        <v>1.5</v>
+      </c>
+      <c r="AY11">
+        <v>0.01316678540074029</v>
+      </c>
+      <c r="AZ11">
+        <v>0.55</v>
+      </c>
+      <c r="BA11">
+        <v>0.15</v>
+      </c>
+      <c r="BB11">
+        <v>0.3</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>117</v>
+      </c>
+      <c r="BD11">
         <v>100000</v>
       </c>
-      <c r="AG11">
+      <c r="BE11">
         <v>100</v>
       </c>
-      <c r="AH11">
-        <v>375</v>
-      </c>
-      <c r="AI11">
-        <v>0.03224376296868218</v>
-      </c>
-      <c r="AJ11">
-        <v>15506.87494153959</v>
-      </c>
-      <c r="AK11">
-        <v>11630.1562061547</v>
-      </c>
-      <c r="AL11">
-        <v>2.806098587597041</v>
-      </c>
-      <c r="AM11">
-        <v>116.301562061547</v>
-      </c>
-      <c r="AN11">
-        <v>0.00116301562061547</v>
-      </c>
-      <c r="AO11">
-        <v>375</v>
-      </c>
-      <c r="AP11">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ11">
-        <v>632.3875216837746</v>
-      </c>
-      <c r="AR11">
-        <v>50.5279835173754</v>
-      </c>
-      <c r="AS11">
-        <v>121.6537532567972</v>
-      </c>
-      <c r="AT11">
+      <c r="BF11">
+        <v>500</v>
+      </c>
+      <c r="BG11">
+        <v>0.008777856933826862</v>
+      </c>
+      <c r="BH11">
+        <v>56961.51165020368</v>
+      </c>
+      <c r="BI11">
+        <v>56961.51165020368</v>
+      </c>
+      <c r="BJ11">
+        <v>7598.414146628917</v>
+      </c>
+      <c r="BK11">
+        <v>569.6151165020368</v>
+      </c>
+      <c r="BL11">
+        <v>0.005696151165020368</v>
+      </c>
+      <c r="BM11">
+        <v>500</v>
+      </c>
+      <c r="BN11">
+        <v>0.005</v>
+      </c>
+      <c r="BR11">
         <v>1</v>
       </c>
-      <c r="AU11">
-        <v>0.06149598827788796</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY11" s="2">
-        <v>46337</v>
+  